--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TeraoAyato\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D274CF5D-3E4A-474B-BF7B-933B7C087CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34CAAD2C-27B7-419C-801E-9BD444F71C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>
-    <sheet name="スケジュール" sheetId="3" r:id="rId2"/>
-    <sheet name="素材" sheetId="4" r:id="rId3"/>
+    <sheet name="アルファ" sheetId="5" r:id="rId2"/>
+    <sheet name="ベータ・マスター" sheetId="6" r:id="rId3"/>
+    <sheet name="スケジュール" sheetId="3" r:id="rId4"/>
+    <sheet name="素材" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -74,28 +76,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>経路探索</t>
-    <rPh sb="0" eb="4">
-      <t>ケイロタンサク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プレイヤー追従</t>
-    <rPh sb="5" eb="7">
-      <t>ツイジュウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>スポーン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>残機</t>
-    <rPh sb="0" eb="2">
-      <t>ザンキ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -124,10 +105,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ミニマップ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>コスト</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -139,17 +116,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ー　カメラのぼかし</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 移動(常時ダッシュ)</t>
-    <rPh sb="1" eb="3">
-      <t>イドウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>担当</t>
     <rPh sb="0" eb="2">
       <t>タントウ</t>
@@ -314,19 +280,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>移動(歩きか走り)</t>
-    <rPh sb="0" eb="2">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>アル</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ハシ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>待機</t>
     <rPh sb="0" eb="2">
       <t>タイキ</t>
@@ -352,14 +305,93 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ー　階段(？)</t>
+    <t>ドア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 移動</t>
+    <rPh sb="1" eb="3">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー　歩行</t>
     <rPh sb="2" eb="4">
-      <t>カイダン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ドア</t>
+      <t>ホコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー　ダッシュ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ランダム移動</t>
+    <rPh sb="4" eb="6">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プレイヤー追従</t>
+    <rPh sb="5" eb="7">
+      <t>ツイショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー　壁</t>
+    <rPh sb="2" eb="3">
+      <t>カベ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー　床</t>
+    <rPh sb="2" eb="3">
+      <t>ユカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー　床</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>計コスト</t>
+    <rPh sb="0" eb="1">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動(アニメーション)</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1コスト１時間</t>
+    <rPh sb="5" eb="7">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー　敵</t>
+    <rPh sb="2" eb="3">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー　プレイヤー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボタン</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -399,7 +431,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -448,8 +480,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="35">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -865,32 +903,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -899,34 +911,94 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -939,9 +1011,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -954,81 +1023,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="56" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1045,13 +1048,10 @@
     <xf numFmtId="56" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="56" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1064,6 +1064,176 @@
     <xf numFmtId="56" fontId="0" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1350,357 +1520,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B1:J28"/>
+  <dimension ref="B1:J32"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="9" style="11" customWidth="1"/>
-    <col min="2" max="2" width="17.125" style="11" customWidth="1"/>
-    <col min="3" max="3" width="9" style="11"/>
-    <col min="4" max="4" width="6.25" style="11" customWidth="1"/>
-    <col min="5" max="5" width="12.125" style="11" customWidth="1"/>
-    <col min="6" max="6" width="15.375" style="11" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="11"/>
+    <col min="1" max="1" width="9" style="4" customWidth="1"/>
+    <col min="2" max="2" width="17.125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="9" style="4"/>
+    <col min="4" max="4" width="6.25" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:10" ht="19.5" thickBot="1">
-      <c r="B2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="25" t="s">
+      <c r="B2" s="57" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="58"/>
+      <c r="D2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" ht="19.5" thickBot="1">
+      <c r="B3" s="101" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="102"/>
+      <c r="D3" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="96">
+        <f>SUM(E4:E12)</f>
+        <v>17</v>
+      </c>
+      <c r="F3" s="12"/>
+    </row>
+    <row r="4" spans="2:10">
+      <c r="B4" s="98" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="99"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="100">
+        <v>5</v>
+      </c>
+      <c r="F4" s="93"/>
+    </row>
+    <row r="5" spans="2:10">
+      <c r="B5" s="76" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="77"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="84">
+        <v>2</v>
+      </c>
+      <c r="F5" s="85"/>
+    </row>
+    <row r="6" spans="2:10">
+      <c r="B6" s="76" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="77"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="84">
+        <v>1</v>
+      </c>
+      <c r="F6" s="85"/>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="B7" s="47" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="60"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="84">
+        <v>1</v>
+      </c>
+      <c r="F7" s="85"/>
+    </row>
+    <row r="8" spans="2:10">
+      <c r="B8" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="44"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="86">
+        <v>2</v>
+      </c>
+      <c r="F8" s="87"/>
+    </row>
+    <row r="9" spans="2:10">
+      <c r="B9" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="60"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="86">
+        <v>3</v>
+      </c>
+      <c r="F9" s="87"/>
+    </row>
+    <row r="10" spans="2:10">
+      <c r="B10" s="74" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="75"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="84">
+        <v>1</v>
+      </c>
+      <c r="F10" s="85"/>
+    </row>
+    <row r="11" spans="2:10">
+      <c r="B11" s="76" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="77"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="88">
+        <v>1</v>
+      </c>
+      <c r="F11" s="87"/>
+    </row>
+    <row r="12" spans="2:10" ht="19.5" thickBot="1">
+      <c r="B12" s="78" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="79"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="89">
+        <v>1</v>
+      </c>
+      <c r="F12" s="90"/>
+    </row>
+    <row r="13" spans="2:10">
+      <c r="B13" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="65"/>
+      <c r="D13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="91">
+        <f>SUM(E14:E20)</f>
+        <v>18</v>
+      </c>
+      <c r="F13" s="92"/>
+    </row>
+    <row r="14" spans="2:10">
+      <c r="B14" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="62"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="84">
+        <v>3</v>
+      </c>
+      <c r="F14" s="85"/>
+    </row>
+    <row r="15" spans="2:10">
+      <c r="B15" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="62"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="84">
+        <v>3</v>
+      </c>
+      <c r="F15" s="85"/>
+      <c r="J15" s="61"/>
+    </row>
+    <row r="16" spans="2:10">
+      <c r="B16" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="48"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="84">
+        <v>4</v>
+      </c>
+      <c r="F16" s="85"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="61"/>
+    </row>
+    <row r="17" spans="2:10">
+      <c r="B17" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="60"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="85">
+        <f>SUM(E18:E20)</f>
+        <v>4</v>
+      </c>
+      <c r="F17" s="85"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="61"/>
+    </row>
+    <row r="18" spans="2:10">
+      <c r="B18" s="76" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" s="77"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="89">
+        <v>1</v>
+      </c>
+      <c r="F18" s="93"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="61"/>
+    </row>
+    <row r="19" spans="2:10">
+      <c r="B19" s="80" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="81"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="87">
+        <v>1</v>
+      </c>
+      <c r="F19" s="94"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="61"/>
+    </row>
+    <row r="20" spans="2:10" ht="19.5" thickBot="1">
+      <c r="B20" s="82" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="83"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="90">
+        <v>2</v>
+      </c>
+      <c r="F20" s="90"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+    </row>
+    <row r="21" spans="2:10">
+      <c r="B21" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="52"/>
+      <c r="D21" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="91">
+        <f>SUM(E22:E25)</f>
+        <v>11</v>
+      </c>
+      <c r="F21" s="92"/>
+      <c r="I21" s="61"/>
+      <c r="J21" s="61"/>
+    </row>
+    <row r="22" spans="2:10">
+      <c r="B22" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="48"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="84">
+        <v>3</v>
+      </c>
+      <c r="F22" s="85"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="61"/>
+    </row>
+    <row r="23" spans="2:10">
+      <c r="B23" s="76" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="77"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="84">
+        <v>3</v>
+      </c>
+      <c r="F23" s="85"/>
+      <c r="J23" s="61"/>
+    </row>
+    <row r="24" spans="2:10">
+      <c r="B24" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="48"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="84">
+        <v>1</v>
+      </c>
+      <c r="F24" s="85"/>
+      <c r="G24" s="13"/>
+    </row>
+    <row r="25" spans="2:10" ht="19.5" thickBot="1">
+      <c r="B25" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="46"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="86">
+        <v>4</v>
+      </c>
+      <c r="F25" s="87"/>
+      <c r="G25" s="13"/>
+    </row>
+    <row r="26" spans="2:10">
+      <c r="B26" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="52"/>
+      <c r="D26" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="91">
+        <f>SUM(E27:E31)</f>
+        <v>15</v>
+      </c>
+      <c r="F26" s="92"/>
+    </row>
+    <row r="27" spans="2:10">
+      <c r="B27" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" s="54"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="84">
+        <v>3</v>
+      </c>
+      <c r="F27" s="85"/>
+    </row>
+    <row r="28" spans="2:10">
+      <c r="B28" s="76" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="77"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="84">
+        <v>3</v>
+      </c>
+      <c r="F28" s="85"/>
+    </row>
+    <row r="29" spans="2:10">
+      <c r="B29" s="53" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="54"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="84">
+        <v>3</v>
+      </c>
+      <c r="F29" s="85"/>
+    </row>
+    <row r="30" spans="2:10">
+      <c r="B30" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="56"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="84">
+        <v>3</v>
+      </c>
+      <c r="F30" s="85"/>
+    </row>
+    <row r="31" spans="2:10" ht="19.5" thickBot="1">
+      <c r="B31" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10">
-      <c r="B3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="20"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-    </row>
-    <row r="4" spans="2:10">
-      <c r="B4" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="36"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-    </row>
-    <row r="5" spans="2:10">
-      <c r="B5" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-    </row>
-    <row r="6" spans="2:10">
-      <c r="B6" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-    </row>
-    <row r="7" spans="2:10">
-      <c r="B7" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-    </row>
-    <row r="8" spans="2:10">
-      <c r="B8" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-    </row>
-    <row r="9" spans="2:10" ht="19.5" thickBot="1">
-      <c r="B9" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="37"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-    </row>
-    <row r="10" spans="2:10">
-      <c r="B10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="23"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-    </row>
-    <row r="11" spans="2:10">
-      <c r="B11" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="21"/>
-      <c r="F11" s="16"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-    </row>
-    <row r="12" spans="2:10" ht="19.5" thickBot="1">
-      <c r="B12" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="J12" s="15"/>
-    </row>
-    <row r="13" spans="2:10">
-      <c r="B13" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="J13" s="34"/>
-    </row>
-    <row r="14" spans="2:10" ht="19.5" thickBot="1">
-      <c r="B14" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="38"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="J14" s="33"/>
-    </row>
-    <row r="15" spans="2:10">
-      <c r="B15" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15" s="35"/>
-      <c r="D15" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="23"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="J15" s="15"/>
-    </row>
-    <row r="16" spans="2:10">
-      <c r="B16" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-    </row>
-    <row r="17" spans="2:9">
-      <c r="B17" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-    </row>
-    <row r="18" spans="2:9">
-      <c r="B18" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="39"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="15"/>
-    </row>
-    <row r="19" spans="2:9" ht="19.5" thickBot="1">
-      <c r="B19" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="38"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="15"/>
-    </row>
-    <row r="20" spans="2:9">
-      <c r="B20" s="7" t="s">
+      <c r="C31" s="50"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="95">
         <v>3</v>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="23"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-    </row>
-    <row r="21" spans="2:9">
-      <c r="B21" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="28"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-    </row>
-    <row r="22" spans="2:9">
-      <c r="B22" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-    </row>
-    <row r="23" spans="2:9">
-      <c r="B23" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="40"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-    </row>
-    <row r="24" spans="2:9">
-      <c r="B24" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="41"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-    </row>
-    <row r="25" spans="2:9">
-      <c r="B25" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-    </row>
-    <row r="26" spans="2:9">
-      <c r="B26" s="8"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-    </row>
-    <row r="27" spans="2:9">
-      <c r="B27" s="8"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15"/>
-    </row>
-    <row r="28" spans="2:9" ht="19.5" thickBot="1">
-      <c r="B28" s="9"/>
-      <c r="C28" s="42"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="15"/>
+      <c r="F31" s="90"/>
+    </row>
+    <row r="32" spans="2:10" ht="19.5" thickBot="1">
+      <c r="B32" s="72" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="73"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="96">
+        <f>SUM(E3,E13,E21,E26)</f>
+        <v>61</v>
+      </c>
+      <c r="F32" s="97"/>
     </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="31">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B7:C7"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B24:C24"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B8:C8"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1709,185 +1951,207 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DBF476-724A-4DAE-8D66-8B0809F96B84}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF80DA5A-1B69-4377-A99E-364B8197EABC}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D63B4141-FE5F-4FCB-9F3D-2486D26F1F00}">
-  <dimension ref="B1:K29"/>
+  <dimension ref="B1:K13"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="46" t="s">
-        <v>37</v>
-      </c>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
+      <c r="C1" s="59" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
     </row>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="70" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="70" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="70" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="70" t="s">
-        <v>34</v>
-      </c>
-      <c r="G2" s="70" t="s">
-        <v>35</v>
-      </c>
-      <c r="H2" s="71" t="s">
-        <v>36</v>
+      <c r="J2" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="2:11">
-      <c r="B3" s="66"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="67">
+      <c r="B3" s="33"/>
+      <c r="D3" s="34">
         <v>46266</v>
       </c>
-      <c r="E3" s="67">
+      <c r="E3" s="34">
         <f>SUM(D3)+1</f>
         <v>46267</v>
       </c>
-      <c r="F3" s="67">
+      <c r="F3" s="34">
         <f t="shared" ref="F3:H3" si="0">SUM(E3)+1</f>
         <v>46268</v>
       </c>
-      <c r="G3" s="67">
+      <c r="G3" s="34">
         <f t="shared" si="0"/>
         <v>46269</v>
       </c>
-      <c r="H3" s="68">
+      <c r="H3" s="35">
         <f t="shared" si="0"/>
         <v>46270</v>
       </c>
-      <c r="J3" s="50"/>
+      <c r="J3" s="20"/>
       <c r="K3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="54">
+      <c r="B4" s="24">
         <f>SUM(H3)+1</f>
         <v>46271</v>
       </c>
-      <c r="C4" s="53">
+      <c r="C4" s="23">
         <f>SUM(B4)+1</f>
         <v>46272</v>
       </c>
-      <c r="D4" s="53">
-        <f t="shared" ref="B4:H5" si="1">SUM(C4)+1</f>
+      <c r="D4" s="23">
+        <f t="shared" ref="D4:H4" si="1">SUM(C4)+1</f>
         <v>46273</v>
       </c>
-      <c r="E4" s="43">
+      <c r="E4" s="14">
         <f t="shared" si="1"/>
         <v>46274</v>
       </c>
-      <c r="F4" s="43">
+      <c r="F4" s="14">
         <f t="shared" si="1"/>
         <v>46275</v>
       </c>
-      <c r="G4" s="43">
+      <c r="G4" s="14">
         <f t="shared" si="1"/>
         <v>46276</v>
       </c>
-      <c r="H4" s="49">
+      <c r="H4" s="19">
         <f t="shared" si="1"/>
         <v>46277</v>
       </c>
-      <c r="J4" s="51"/>
+      <c r="J4" s="21"/>
       <c r="K4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="48">
+      <c r="B5" s="18">
         <f>SUM(H4)+1</f>
         <v>46278</v>
       </c>
-      <c r="C5" s="47">
+      <c r="C5" s="17">
         <f>SUM(B5)+1</f>
         <v>46279</v>
       </c>
-      <c r="D5" s="47">
+      <c r="D5" s="17">
         <f t="shared" ref="D5:H5" si="2">SUM(C5)+1</f>
         <v>46280</v>
       </c>
-      <c r="E5" s="47">
+      <c r="E5" s="17">
         <f t="shared" si="2"/>
         <v>46281</v>
       </c>
-      <c r="F5" s="47">
+      <c r="F5" s="17">
         <f t="shared" si="2"/>
         <v>46282</v>
       </c>
-      <c r="G5" s="47">
+      <c r="G5" s="17">
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="H5" s="49">
+      <c r="H5" s="19">
         <f t="shared" si="2"/>
         <v>46284</v>
       </c>
-      <c r="J5" s="52"/>
+      <c r="J5" s="22"/>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" s="48">
+      <c r="B6" s="18">
         <f>SUM(H5)+1</f>
         <v>46285</v>
       </c>
-      <c r="C6" s="47">
+      <c r="C6" s="17">
         <f>SUM(B6)+1</f>
         <v>46286</v>
       </c>
-      <c r="D6" s="47">
+      <c r="D6" s="17">
         <f t="shared" ref="D6:H6" si="3">SUM(C6)+1</f>
         <v>46287</v>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="17">
         <f t="shared" si="3"/>
         <v>46288</v>
       </c>
-      <c r="F6" s="47">
+      <c r="F6" s="17">
         <f t="shared" si="3"/>
         <v>46289</v>
       </c>
-      <c r="G6" s="47">
+      <c r="G6" s="17">
         <f t="shared" si="3"/>
         <v>46290</v>
       </c>
-      <c r="H6" s="49">
+      <c r="H6" s="19">
         <f t="shared" si="3"/>
         <v>46291</v>
       </c>
-      <c r="J6" s="61"/>
+      <c r="J6" s="31"/>
       <c r="K6" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B7" s="74">
+      <c r="B7" s="41">
         <f>SUM(H6)+1</f>
         <v>46292</v>
       </c>
-      <c r="C7" s="75">
+      <c r="C7" s="42">
         <f>SUM(B7)+1</f>
         <v>46293</v>
       </c>
-      <c r="D7" s="75">
-        <f t="shared" ref="D7:G7" si="4">SUM(C7)+1</f>
+      <c r="D7" s="42">
+        <f t="shared" ref="D7:E7" si="4">SUM(C7)+1</f>
         <v>46294</v>
       </c>
-      <c r="E7" s="75">
+      <c r="E7" s="42">
         <f t="shared" si="4"/>
         <v>46295</v>
       </c>
@@ -1896,299 +2160,150 @@
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="2:11">
-      <c r="B8" s="66"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="72">
+      <c r="F8" s="39">
         <f>SUM(E7)+1</f>
         <v>46296</v>
       </c>
-      <c r="G8" s="72">
+      <c r="G8" s="39">
         <f>SUM(F8)+1</f>
         <v>46297</v>
       </c>
-      <c r="H8" s="73">
+      <c r="H8" s="40">
         <f>SUM(G8)+1</f>
         <v>46298</v>
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="55">
+      <c r="B9" s="25">
         <f>SUM(H8)+1</f>
         <v>46299</v>
       </c>
-      <c r="C9" s="56">
+      <c r="C9" s="26">
         <f>SUM(B9)+1</f>
         <v>46300</v>
       </c>
-      <c r="D9" s="56">
+      <c r="D9" s="26">
         <f t="shared" ref="D9:H9" si="5">SUM(C9)+1</f>
         <v>46301</v>
       </c>
-      <c r="E9" s="56">
+      <c r="E9" s="26">
         <f t="shared" si="5"/>
         <v>46302</v>
       </c>
-      <c r="F9" s="56">
+      <c r="F9" s="26">
         <f t="shared" si="5"/>
         <v>46303</v>
       </c>
-      <c r="G9" s="56">
+      <c r="G9" s="26">
         <f t="shared" si="5"/>
         <v>46304</v>
       </c>
-      <c r="H9" s="57">
+      <c r="H9" s="27">
         <f t="shared" si="5"/>
         <v>46305</v>
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="55">
+      <c r="B10" s="30">
         <f t="shared" ref="B10:B12" si="6">SUM(H9)+1</f>
         <v>46306</v>
       </c>
-      <c r="C10" s="56">
+      <c r="C10" s="28">
         <f>SUM(B10)+1</f>
         <v>46307</v>
       </c>
-      <c r="D10" s="56">
+      <c r="D10" s="28">
         <f t="shared" ref="D10:G10" si="7">SUM(C10)+1</f>
         <v>46308</v>
       </c>
-      <c r="E10" s="56">
+      <c r="E10" s="28">
         <f t="shared" si="7"/>
         <v>46309</v>
       </c>
-      <c r="F10" s="58">
+      <c r="F10" s="28">
         <f t="shared" si="7"/>
         <v>46310</v>
       </c>
-      <c r="G10" s="58">
+      <c r="G10" s="28">
         <f t="shared" si="7"/>
         <v>46311</v>
       </c>
-      <c r="H10" s="59">
+      <c r="H10" s="29">
         <f>SUM(G10)+1</f>
         <v>46312</v>
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="60">
+      <c r="B11" s="30">
         <f t="shared" si="6"/>
         <v>46313</v>
       </c>
-      <c r="C11" s="58">
+      <c r="C11" s="32">
         <f>SUM(B11)+1</f>
         <v>46314</v>
       </c>
-      <c r="D11" s="58">
+      <c r="D11" s="32">
         <f t="shared" ref="D11:F11" si="8">SUM(C11)+1</f>
         <v>46315</v>
       </c>
-      <c r="E11" s="58">
+      <c r="E11" s="32">
         <f t="shared" si="8"/>
         <v>46316</v>
       </c>
-      <c r="F11" s="62">
+      <c r="F11" s="71">
         <f t="shared" si="8"/>
         <v>46317</v>
       </c>
-      <c r="G11" s="62">
-        <f t="shared" ref="D11:G11" si="9">SUM(F11)+1</f>
+      <c r="G11" s="67">
+        <f t="shared" ref="G11" si="9">SUM(F11)+1</f>
         <v>46318</v>
       </c>
-      <c r="H11" s="63">
+      <c r="H11" s="68">
         <f>SUM(G11)+1</f>
         <v>46319</v>
       </c>
     </row>
     <row r="12" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B12" s="64">
+      <c r="B12" s="69">
         <f t="shared" si="6"/>
         <v>46320</v>
       </c>
-      <c r="C12" s="65">
+      <c r="C12" s="70">
         <f>SUM(B12)+1</f>
         <v>46321</v>
       </c>
-      <c r="D12" s="44">
+      <c r="D12" s="15">
         <f t="shared" ref="D12:H12" si="10">SUM(C12)+1</f>
         <v>46322</v>
       </c>
-      <c r="E12" s="44">
+      <c r="E12" s="15">
         <f t="shared" si="10"/>
         <v>46323</v>
       </c>
-      <c r="F12" s="44">
+      <c r="F12" s="15">
         <f t="shared" si="10"/>
         <v>46324</v>
       </c>
-      <c r="G12" s="44">
+      <c r="G12" s="15">
         <f t="shared" si="10"/>
         <v>46325</v>
       </c>
-      <c r="H12" s="45">
+      <c r="H12" s="16">
         <f t="shared" si="10"/>
         <v>46326</v>
       </c>
     </row>
     <row r="13" spans="2:11">
-      <c r="B13" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11">
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-    </row>
-    <row r="15" spans="2:11">
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-    </row>
-    <row r="16" spans="2:11">
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-    </row>
-    <row r="17" spans="2:8">
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-    </row>
-    <row r="18" spans="2:8">
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-    </row>
-    <row r="19" spans="2:8">
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-    </row>
-    <row r="20" spans="2:8">
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-    </row>
-    <row r="21" spans="2:8">
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-    </row>
-    <row r="22" spans="2:8">
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-    </row>
-    <row r="23" spans="2:8">
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-    </row>
-    <row r="24" spans="2:8">
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-    </row>
-    <row r="25" spans="2:8">
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-    </row>
-    <row r="26" spans="2:8">
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-    </row>
-    <row r="27" spans="2:8">
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-    </row>
-    <row r="28" spans="2:8">
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
-    </row>
-    <row r="29" spans="2:8">
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2199,9 +2314,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F8B42D-C760-44A9-BC69-9B00588EFF82}">
-  <dimension ref="B2:B15"/>
+  <dimension ref="B2:B14"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="2:2">
@@ -2211,17 +2326,17 @@
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="2:2">
@@ -2231,46 +2346,41 @@
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" spans="2:2">
-      <c r="B15" t="s">
         <v>3</v>
       </c>
     </row>

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TeraoAyato\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34CAAD2C-27B7-419C-801E-9BD444F71C5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{195F1719-7AE2-4204-B0CC-31D6602EC37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -994,7 +994,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1064,10 +1064,133 @@
     <xf numFmtId="56" fontId="0" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1076,163 +1199,23 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1520,7 +1503,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B1:J32"/>
+  <dimension ref="B1:G32"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9" style="4" customWidth="1"/>
@@ -1532,12 +1515,12 @@
     <col min="7" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="19.5" thickBot="1"/>
-    <row r="2" spans="2:10" ht="19.5" thickBot="1">
-      <c r="B2" s="57" t="s">
+    <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
+    <row r="2" spans="2:6" ht="19.5" thickBot="1">
+      <c r="B2" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="58"/>
+      <c r="C2" s="64"/>
       <c r="D2" s="12" t="s">
         <v>14</v>
       </c>
@@ -1548,370 +1531,369 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="2:10" ht="19.5" thickBot="1">
-      <c r="B3" s="101" t="s">
+    <row r="3" spans="2:6" ht="19.5" thickBot="1">
+      <c r="B3" s="69" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="102"/>
+      <c r="C3" s="70"/>
       <c r="D3" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="96">
+      <c r="E3" s="60">
         <f>SUM(E4:E12)</f>
         <v>17</v>
       </c>
       <c r="F3" s="12"/>
     </row>
-    <row r="4" spans="2:10">
-      <c r="B4" s="98" t="s">
+    <row r="4" spans="2:6">
+      <c r="B4" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="99"/>
+      <c r="C4" s="81"/>
       <c r="D4" s="11"/>
-      <c r="E4" s="100">
+      <c r="E4" s="62">
         <v>5</v>
       </c>
-      <c r="F4" s="93"/>
-    </row>
-    <row r="5" spans="2:10">
-      <c r="B5" s="76" t="s">
+      <c r="F4" s="57"/>
+    </row>
+    <row r="5" spans="2:6">
+      <c r="B5" s="75" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="77"/>
+      <c r="C5" s="76"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="84">
+      <c r="E5" s="48">
         <v>2</v>
       </c>
-      <c r="F5" s="85"/>
-    </row>
-    <row r="6" spans="2:10">
-      <c r="B6" s="76" t="s">
+      <c r="F5" s="49"/>
+    </row>
+    <row r="6" spans="2:6">
+      <c r="B6" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="77"/>
+      <c r="C6" s="76"/>
       <c r="D6" s="8"/>
-      <c r="E6" s="84">
+      <c r="E6" s="48">
         <v>1</v>
       </c>
-      <c r="F6" s="85"/>
-    </row>
-    <row r="7" spans="2:10">
-      <c r="B7" s="47" t="s">
+      <c r="F6" s="49"/>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="B7" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="60"/>
+      <c r="C7" s="72"/>
       <c r="D7" s="8"/>
-      <c r="E7" s="84">
+      <c r="E7" s="48">
         <v>1</v>
       </c>
-      <c r="F7" s="85"/>
-    </row>
-    <row r="8" spans="2:10">
-      <c r="B8" s="43" t="s">
+      <c r="F7" s="49"/>
+    </row>
+    <row r="8" spans="2:6">
+      <c r="B8" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="44"/>
+      <c r="C8" s="77"/>
       <c r="D8" s="10"/>
-      <c r="E8" s="86">
+      <c r="E8" s="50">
         <v>2</v>
       </c>
-      <c r="F8" s="87"/>
-    </row>
-    <row r="9" spans="2:10">
-      <c r="B9" s="47" t="s">
+      <c r="F8" s="51"/>
+    </row>
+    <row r="9" spans="2:6">
+      <c r="B9" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="60"/>
+      <c r="C9" s="72"/>
       <c r="D9" s="10"/>
-      <c r="E9" s="86">
+      <c r="E9" s="50">
         <v>3</v>
       </c>
-      <c r="F9" s="87"/>
-    </row>
-    <row r="10" spans="2:10">
-      <c r="B10" s="74" t="s">
+      <c r="F9" s="51"/>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="75"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="84">
+      <c r="C10" s="83"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="48">
         <v>1</v>
       </c>
-      <c r="F10" s="85"/>
-    </row>
-    <row r="11" spans="2:10">
-      <c r="B11" s="76" t="s">
+      <c r="F10" s="49"/>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="77"/>
+      <c r="C11" s="76"/>
       <c r="D11" s="8"/>
-      <c r="E11" s="88">
+      <c r="E11" s="52">
         <v>1</v>
       </c>
-      <c r="F11" s="87"/>
-    </row>
-    <row r="12" spans="2:10" ht="19.5" thickBot="1">
-      <c r="B12" s="78" t="s">
+      <c r="F11" s="51"/>
+    </row>
+    <row r="12" spans="2:6" ht="19.5" thickBot="1">
+      <c r="B12" s="92" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="79"/>
-      <c r="D12" s="63"/>
-      <c r="E12" s="89">
+      <c r="C12" s="93"/>
+      <c r="D12" s="44"/>
+      <c r="E12" s="53">
         <v>1</v>
       </c>
-      <c r="F12" s="90"/>
-    </row>
-    <row r="13" spans="2:10">
-      <c r="B13" s="64" t="s">
+      <c r="F12" s="54"/>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="65"/>
+      <c r="C13" s="74"/>
       <c r="D13" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E13" s="91">
+      <c r="E13" s="55">
         <f>SUM(E14:E20)</f>
         <v>18</v>
       </c>
-      <c r="F13" s="92"/>
-    </row>
-    <row r="14" spans="2:10">
-      <c r="B14" s="43" t="s">
+      <c r="F13" s="56"/>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="62"/>
+      <c r="C14" s="76"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="84">
+      <c r="E14" s="48">
         <v>3</v>
       </c>
-      <c r="F14" s="85"/>
-    </row>
-    <row r="15" spans="2:10">
-      <c r="B15" s="43" t="s">
+      <c r="F14" s="49"/>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="B15" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="62"/>
+      <c r="C15" s="76"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="84">
+      <c r="E15" s="48">
         <v>3</v>
       </c>
-      <c r="F15" s="85"/>
-      <c r="J15" s="61"/>
-    </row>
-    <row r="16" spans="2:10">
-      <c r="B16" s="47" t="s">
+      <c r="F15" s="49"/>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="B16" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="48"/>
+      <c r="C16" s="77"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="84">
+      <c r="E16" s="48">
         <v>4</v>
       </c>
-      <c r="F16" s="85"/>
-      <c r="I16" s="61"/>
-      <c r="J16" s="61"/>
-    </row>
-    <row r="17" spans="2:10">
-      <c r="B17" s="47" t="s">
+      <c r="F16" s="49"/>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="60"/>
+      <c r="C17" s="72"/>
       <c r="D17" s="10"/>
-      <c r="E17" s="85">
+      <c r="E17" s="49">
         <f>SUM(E18:E20)</f>
         <v>4</v>
       </c>
-      <c r="F17" s="85"/>
-      <c r="I17" s="61"/>
-      <c r="J17" s="61"/>
-    </row>
-    <row r="18" spans="2:10">
-      <c r="B18" s="76" t="s">
+      <c r="F17" s="49"/>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="C18" s="77"/>
+      <c r="C18" s="76"/>
       <c r="D18" s="8"/>
-      <c r="E18" s="89">
+      <c r="E18" s="53">
         <v>1</v>
       </c>
-      <c r="F18" s="93"/>
-      <c r="I18" s="61"/>
-      <c r="J18" s="61"/>
-    </row>
-    <row r="19" spans="2:10">
-      <c r="B19" s="80" t="s">
+      <c r="F18" s="57"/>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="90" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="81"/>
+      <c r="C19" s="91"/>
       <c r="D19" s="10"/>
-      <c r="E19" s="87">
+      <c r="E19" s="51">
         <v>1</v>
       </c>
-      <c r="F19" s="94"/>
-      <c r="I19" s="61"/>
-      <c r="J19" s="61"/>
-    </row>
-    <row r="20" spans="2:10" ht="19.5" thickBot="1">
-      <c r="B20" s="82" t="s">
+      <c r="F19" s="58"/>
+    </row>
+    <row r="20" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B20" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="83"/>
+      <c r="C20" s="94"/>
       <c r="D20" s="9"/>
-      <c r="E20" s="90">
+      <c r="E20" s="54">
         <v>2</v>
       </c>
-      <c r="F20" s="90"/>
-      <c r="I20" s="61"/>
-      <c r="J20" s="61"/>
-    </row>
-    <row r="21" spans="2:10">
-      <c r="B21" s="51" t="s">
+      <c r="F20" s="54"/>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="52"/>
+      <c r="C21" s="79"/>
       <c r="D21" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E21" s="91">
+      <c r="E21" s="55">
         <f>SUM(E22:E25)</f>
         <v>11</v>
       </c>
-      <c r="F21" s="92"/>
-      <c r="I21" s="61"/>
-      <c r="J21" s="61"/>
-    </row>
-    <row r="22" spans="2:10">
-      <c r="B22" s="47" t="s">
+      <c r="F21" s="56"/>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="48"/>
+      <c r="C22" s="77"/>
       <c r="D22" s="8"/>
-      <c r="E22" s="84">
+      <c r="E22" s="48">
         <v>3</v>
       </c>
-      <c r="F22" s="85"/>
-      <c r="I22" s="61"/>
-      <c r="J22" s="61"/>
-    </row>
-    <row r="23" spans="2:10">
-      <c r="B23" s="76" t="s">
+      <c r="F22" s="49"/>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" s="75" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="77"/>
+      <c r="C23" s="76"/>
       <c r="D23" s="8"/>
-      <c r="E23" s="84">
+      <c r="E23" s="48">
         <v>3</v>
       </c>
-      <c r="F23" s="85"/>
-      <c r="J23" s="61"/>
-    </row>
-    <row r="24" spans="2:10">
-      <c r="B24" s="47" t="s">
+      <c r="F23" s="49"/>
+    </row>
+    <row r="24" spans="2:7">
+      <c r="B24" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="48"/>
+      <c r="C24" s="77"/>
       <c r="D24" s="8"/>
-      <c r="E24" s="84">
+      <c r="E24" s="48">
         <v>1</v>
       </c>
-      <c r="F24" s="85"/>
+      <c r="F24" s="49"/>
       <c r="G24" s="13"/>
     </row>
-    <row r="25" spans="2:10" ht="19.5" thickBot="1">
-      <c r="B25" s="45" t="s">
+    <row r="25" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B25" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="46"/>
+      <c r="C25" s="89"/>
       <c r="D25" s="10"/>
-      <c r="E25" s="86">
+      <c r="E25" s="50">
         <v>4</v>
       </c>
-      <c r="F25" s="87"/>
+      <c r="F25" s="51"/>
       <c r="G25" s="13"/>
     </row>
-    <row r="26" spans="2:10">
-      <c r="B26" s="51" t="s">
+    <row r="26" spans="2:7">
+      <c r="B26" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="C26" s="52"/>
+      <c r="C26" s="79"/>
       <c r="D26" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="91">
+      <c r="E26" s="55">
         <f>SUM(E27:E31)</f>
         <v>15</v>
       </c>
-      <c r="F26" s="92"/>
-    </row>
-    <row r="27" spans="2:10">
-      <c r="B27" s="53" t="s">
+      <c r="F26" s="56"/>
+    </row>
+    <row r="27" spans="2:7">
+      <c r="B27" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="C27" s="54"/>
+      <c r="C27" s="85"/>
       <c r="D27" s="8"/>
-      <c r="E27" s="84">
+      <c r="E27" s="48">
         <v>3</v>
       </c>
-      <c r="F27" s="85"/>
-    </row>
-    <row r="28" spans="2:10">
-      <c r="B28" s="76" t="s">
+      <c r="F27" s="49"/>
+    </row>
+    <row r="28" spans="2:7">
+      <c r="B28" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="77"/>
+      <c r="C28" s="76"/>
       <c r="D28" s="8"/>
-      <c r="E28" s="84">
+      <c r="E28" s="48">
         <v>3</v>
       </c>
-      <c r="F28" s="85"/>
-    </row>
-    <row r="29" spans="2:10">
-      <c r="B29" s="53" t="s">
+      <c r="F28" s="49"/>
+    </row>
+    <row r="29" spans="2:7">
+      <c r="B29" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="54"/>
+      <c r="C29" s="85"/>
       <c r="D29" s="8"/>
-      <c r="E29" s="84">
+      <c r="E29" s="48">
         <v>3</v>
       </c>
-      <c r="F29" s="85"/>
-    </row>
-    <row r="30" spans="2:10">
-      <c r="B30" s="55" t="s">
+      <c r="F29" s="49"/>
+    </row>
+    <row r="30" spans="2:7">
+      <c r="B30" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="56"/>
+      <c r="C30" s="87"/>
       <c r="D30" s="8"/>
-      <c r="E30" s="84">
+      <c r="E30" s="48">
         <v>3</v>
       </c>
-      <c r="F30" s="85"/>
-    </row>
-    <row r="31" spans="2:10" ht="19.5" thickBot="1">
-      <c r="B31" s="49" t="s">
+      <c r="F30" s="49"/>
+    </row>
+    <row r="31" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B31" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="C31" s="50"/>
+      <c r="C31" s="66"/>
       <c r="D31" s="9"/>
-      <c r="E31" s="95">
+      <c r="E31" s="59">
         <v>3</v>
       </c>
-      <c r="F31" s="90"/>
-    </row>
-    <row r="32" spans="2:10" ht="19.5" thickBot="1">
-      <c r="B32" s="72" t="s">
+      <c r="F31" s="54"/>
+    </row>
+    <row r="32" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B32" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="C32" s="73"/>
+      <c r="C32" s="68"/>
       <c r="D32" s="12"/>
-      <c r="E32" s="96">
+      <c r="E32" s="60">
         <f>SUM(E3,E13,E21,E26)</f>
         <v>61</v>
       </c>
-      <c r="F32" s="97"/>
+      <c r="F32" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B32:C32"/>
@@ -1928,21 +1910,6 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B20:C20"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1976,13 +1943,13 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="59" t="s">
+      <c r="C1" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="59"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
     </row>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
       <c r="B2" s="36" t="s">
@@ -2254,25 +2221,25 @@
         <f t="shared" si="8"/>
         <v>46316</v>
       </c>
-      <c r="F11" s="71">
+      <c r="F11" s="47">
         <f t="shared" si="8"/>
         <v>46317</v>
       </c>
-      <c r="G11" s="67">
+      <c r="G11" s="14">
         <f t="shared" ref="G11" si="9">SUM(F11)+1</f>
         <v>46318</v>
       </c>
-      <c r="H11" s="68">
+      <c r="H11" s="45">
         <f>SUM(G11)+1</f>
         <v>46319</v>
       </c>
     </row>
     <row r="12" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B12" s="69">
+      <c r="B12" s="46">
         <f t="shared" si="6"/>
         <v>46320</v>
       </c>
-      <c r="C12" s="70">
+      <c r="C12" s="15">
         <f>SUM(B12)+1</f>
         <v>46321</v>
       </c>

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TeraoAyato\Documents\GitHub\GlassesGame\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nodasouma\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{195F1719-7AE2-4204-B0CC-31D6602EC37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3718906E-F73B-4F27-9B66-D2106061731E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3690" yWindow="1530" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="81">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -69,14 +69,247 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>カメラ(一人称)</t>
-    <rPh sb="4" eb="7">
-      <t>イチニンショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>スポーン</t>
+    <t>アイテム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>コスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実コスト</t>
+    <rPh sb="0" eb="1">
+      <t>ジツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>担当</t>
+    <rPh sb="0" eb="2">
+      <t>タントウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>武部</t>
+    <rPh sb="0" eb="2">
+      <t>タケベ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>野田</t>
+    <rPh sb="0" eb="2">
+      <t>ノダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 寺尾</t>
+    <rPh sb="1" eb="3">
+      <t>テラオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やること(プロト)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>船迫</t>
+    <rPh sb="0" eb="2">
+      <t>フナサコ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>日</t>
+    <rPh sb="0" eb="1">
+      <t>ニチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>月</t>
+    <rPh sb="0" eb="1">
+      <t>ゲツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>火</t>
+    <rPh sb="0" eb="1">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>水</t>
+    <rPh sb="0" eb="1">
+      <t>スイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>木</t>
+    <rPh sb="0" eb="1">
+      <t>モク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金</t>
+    <rPh sb="0" eb="1">
+      <t>キン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>土</t>
+    <rPh sb="0" eb="1">
+      <t>ド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スケジュール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10/31が締切？</t>
+    <rPh sb="6" eb="7">
+      <t>シ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アルファ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベータ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マスタ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9/9~9/11は素材探し</t>
+    <rPh sb="9" eb="12">
+      <t>ソザイサガ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>歩き</t>
+    <rPh sb="0" eb="1">
+      <t>アル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死亡</t>
+    <rPh sb="0" eb="2">
+      <t>シボウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>待機</t>
+    <rPh sb="0" eb="2">
+      <t>タイキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー　壁</t>
+    <rPh sb="2" eb="3">
+      <t>カベ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップテクスチャ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー　地面</t>
+    <rPh sb="2" eb="4">
+      <t>ジメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ドア</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>計コスト</t>
+    <rPh sb="0" eb="1">
+      <t>ケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動(アニメーション)</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1コスト１時間</t>
+    <rPh sb="5" eb="7">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー歩行</t>
+    <rPh sb="1" eb="3">
+      <t>ホコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ーダッシュ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>クイックターン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>死亡</t>
+    <rPh sb="0" eb="2">
+      <t>シボウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>復活</t>
+    <rPh sb="0" eb="2">
+      <t>フッカツ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -90,240 +323,24 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ロビー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>経路づくり</t>
-    <rPh sb="0" eb="2">
-      <t>ケイロ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アイテム</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>コスト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>実コスト</t>
-    <rPh sb="0" eb="1">
-      <t>ジツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>担当</t>
-    <rPh sb="0" eb="2">
-      <t>タントウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>武部</t>
-    <rPh sb="0" eb="2">
-      <t>タケベ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>野田</t>
-    <rPh sb="0" eb="2">
-      <t>ノダ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 寺尾</t>
-    <rPh sb="1" eb="3">
-      <t>テラオ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>やること(プロト)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>船迫</t>
-    <rPh sb="0" eb="2">
-      <t>フナサコ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>スコアの計算</t>
-    <rPh sb="4" eb="6">
-      <t>ケイサン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ゲームオーバー(シーン内)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ー　アイテムの取得</t>
-    <rPh sb="7" eb="9">
-      <t>シュトク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>死亡</t>
-    <rPh sb="0" eb="2">
-      <t>シボウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>日</t>
-    <rPh sb="0" eb="1">
-      <t>ニチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>月</t>
-    <rPh sb="0" eb="1">
-      <t>ゲツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>火</t>
-    <rPh sb="0" eb="1">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>水</t>
-    <rPh sb="0" eb="1">
-      <t>スイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>木</t>
-    <rPh sb="0" eb="1">
-      <t>モク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>金</t>
-    <rPh sb="0" eb="1">
-      <t>キン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>土</t>
-    <rPh sb="0" eb="1">
-      <t>ド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>スケジュール</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>10/31が締切？</t>
-    <rPh sb="6" eb="7">
-      <t>シ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>キ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プロト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アルファ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ベータ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>マスタ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>9/9~9/11は素材探し</t>
-    <rPh sb="9" eb="12">
-      <t>ソザイサガ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>歩き</t>
-    <rPh sb="0" eb="1">
-      <t>アル</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>死亡</t>
-    <rPh sb="0" eb="2">
-      <t>シボウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>待機</t>
-    <rPh sb="0" eb="2">
-      <t>タイキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ー　壁</t>
-    <rPh sb="2" eb="3">
+    <t>ー壁</t>
+    <rPh sb="1" eb="2">
       <t>カベ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>マップテクスチャ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ー　地面</t>
-    <rPh sb="2" eb="4">
-      <t>ジメン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ドア</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> 移動</t>
-    <rPh sb="1" eb="3">
-      <t>イドウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ー　歩行</t>
-    <rPh sb="2" eb="4">
-      <t>ホコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ー　ダッシュ</t>
+    <t>ー床</t>
+    <rPh sb="1" eb="2">
+      <t>ユカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー敵</t>
+    <rPh sb="1" eb="2">
+      <t>テキ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -334,64 +351,186 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>プレイヤー追従</t>
+    <t>プレイヤー発見</t>
     <rPh sb="5" eb="7">
-      <t>ツイショウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ー　壁</t>
-    <rPh sb="2" eb="3">
-      <t>カベ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ー　床</t>
-    <rPh sb="2" eb="3">
-      <t>ユカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ー　床</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>計コスト</t>
+      <t>ハッケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>追跡</t>
+    <rPh sb="0" eb="2">
+      <t>ツイセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>見失い</t>
+    <rPh sb="0" eb="2">
+      <t>ミウシナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スポーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ープレイヤー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>仮マップ制作</t>
     <rPh sb="0" eb="1">
-      <t>ケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>移動(アニメーション)</t>
+      <t>カリ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ーアイテム配置</t>
+    <rPh sb="5" eb="7">
+      <t>ハイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ーアイテム取得</t>
+    <rPh sb="5" eb="7">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロビー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー残りアイテム表示</t>
+    <rPh sb="1" eb="2">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>シーン遷移</t>
+    <rPh sb="3" eb="5">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タイトル仮UI</t>
+    <rPh sb="4" eb="5">
+      <t>カリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム中仮UI</t>
+    <rPh sb="3" eb="4">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>カリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>インゲームUI</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>残機表示</t>
     <rPh sb="0" eb="2">
-      <t>イドウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1コスト１時間</t>
+      <t>ザンキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スコア表示</t>
+    <rPh sb="3" eb="5">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やること(アルファ)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ミニマップ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3Dモデル導入</t>
     <rPh sb="5" eb="7">
-      <t>ジカン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ー　敵</t>
-    <rPh sb="2" eb="3">
-      <t>テキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ー　プレイヤー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ボタン</t>
+      <t>ドウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アニメーション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本デザイン差し替え</t>
+    <rPh sb="0" eb="1">
+      <t>ホン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>サ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サウンド</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（サウンド）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(サウンド）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テクスチャ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲーム内BGM</t>
+    <rPh sb="3" eb="4">
+      <t>ナイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>やること(β・Ｍ)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バグとり</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>バグどり</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -446,12 +585,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -486,8 +619,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="40">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -796,17 +935,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -855,38 +983,9 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -936,15 +1035,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -990,11 +1080,96 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1017,16 +1192,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1036,187 +1208,205 @@
     <xf numFmtId="56" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="56" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="56" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="56" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="0" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1503,7 +1693,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B1:G32"/>
+  <dimension ref="B1:G40"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9" style="4" customWidth="1"/>
@@ -1517,399 +1707,466 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="63" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="64"/>
-      <c r="D2" s="12" t="s">
-        <v>14</v>
+      <c r="B2" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="83"/>
+      <c r="D2" s="82" t="s">
+        <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="19.5" thickBot="1">
+      <c r="B3" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="84"/>
+      <c r="D3" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="69" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="70"/>
-      <c r="D3" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="60">
-        <f>SUM(E4:E12)</f>
-        <v>17</v>
-      </c>
+      <c r="E3" s="53"/>
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="80" t="s">
+      <c r="B4" s="69" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="85"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+    </row>
+    <row r="5" spans="2:6">
+      <c r="B5" s="70" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="71"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="46">
+        <v>2</v>
+      </c>
+      <c r="F5" s="46"/>
+    </row>
+    <row r="6" spans="2:6">
+      <c r="B6" s="70" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="71"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="46">
+        <v>1</v>
+      </c>
+      <c r="F6" s="46"/>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="B7" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="71"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="46">
+        <v>2</v>
+      </c>
+      <c r="F7" s="46"/>
+    </row>
+    <row r="8" spans="2:6">
+      <c r="B8" s="70" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="71"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="47">
+        <v>1</v>
+      </c>
+      <c r="F8" s="47"/>
+    </row>
+    <row r="9" spans="2:6">
+      <c r="B9" s="70" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="71"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="47">
+        <v>1</v>
+      </c>
+      <c r="F9" s="47"/>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="81"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="62">
-        <v>5</v>
-      </c>
-      <c r="F4" s="57"/>
-    </row>
-    <row r="5" spans="2:6">
-      <c r="B5" s="75" t="s">
+      <c r="C10" s="73"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="46">
+        <v>2</v>
+      </c>
+      <c r="F10" s="46"/>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="76"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="48">
-        <v>2</v>
-      </c>
-      <c r="F5" s="49"/>
-    </row>
-    <row r="6" spans="2:6">
-      <c r="B6" s="75" t="s">
+      <c r="C11" s="71"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="47"/>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="B12" s="72" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="76"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="48">
+      <c r="C12" s="73"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="46">
         <v>1</v>
       </c>
-      <c r="F6" s="49"/>
-    </row>
-    <row r="7" spans="2:6">
-      <c r="B7" s="71" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="72"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="48">
+      <c r="F12" s="46"/>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13" s="70" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="71"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="46">
         <v>1</v>
       </c>
-      <c r="F7" s="49"/>
-    </row>
-    <row r="8" spans="2:6">
-      <c r="B8" s="71" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="77"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="50">
-        <v>2</v>
-      </c>
-      <c r="F8" s="51"/>
-    </row>
-    <row r="9" spans="2:6">
-      <c r="B9" s="71" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="72"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="50">
+      <c r="F13" s="46"/>
+    </row>
+    <row r="14" spans="2:6" ht="19.5" thickBot="1">
+      <c r="B14" s="74" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="75"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="48">
+        <v>1</v>
+      </c>
+      <c r="F14" s="48"/>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="B15" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="79"/>
+      <c r="D15" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="B16" s="56" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="57"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="46">
         <v>3</v>
       </c>
-      <c r="F9" s="51"/>
-    </row>
-    <row r="10" spans="2:6">
-      <c r="B10" s="82" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="83"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="48">
+      <c r="F16" s="46"/>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="70" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="71"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="46">
+        <v>3</v>
+      </c>
+      <c r="F17" s="46"/>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="70" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="71"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="46">
+        <v>3</v>
+      </c>
+      <c r="F18" s="46"/>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="70" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="71"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="46">
+        <v>3</v>
+      </c>
+      <c r="F19" s="46"/>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="70" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="71"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="51">
         <v>1</v>
       </c>
-      <c r="F10" s="49"/>
-    </row>
-    <row r="11" spans="2:6">
-      <c r="B11" s="75" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="76"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="52">
+      <c r="F20" s="50"/>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="72" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="73"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="46"/>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" s="66" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="67"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="46">
         <v>1</v>
       </c>
-      <c r="F11" s="51"/>
-    </row>
-    <row r="12" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B12" s="92" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="93"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="53">
+      <c r="F22" s="46"/>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" s="66" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="67"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="46">
         <v>1</v>
       </c>
-      <c r="F12" s="54"/>
-    </row>
-    <row r="13" spans="2:6">
-      <c r="B13" s="73" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="74"/>
-      <c r="D13" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" s="55">
-        <f>SUM(E14:E20)</f>
-        <v>18</v>
-      </c>
-      <c r="F13" s="56"/>
-    </row>
-    <row r="14" spans="2:6">
-      <c r="B14" s="75" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="76"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="48">
-        <v>3</v>
-      </c>
-      <c r="F14" s="49"/>
-    </row>
-    <row r="15" spans="2:6">
-      <c r="B15" s="75" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="76"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="48">
-        <v>3</v>
-      </c>
-      <c r="F15" s="49"/>
-    </row>
-    <row r="16" spans="2:6">
-      <c r="B16" s="71" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="77"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="48">
-        <v>4</v>
-      </c>
-      <c r="F16" s="49"/>
-    </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="71" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="72"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="49">
-        <f>SUM(E18:E20)</f>
-        <v>4</v>
-      </c>
-      <c r="F17" s="49"/>
-    </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="75" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="76"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="53">
-        <v>1</v>
-      </c>
-      <c r="F18" s="57"/>
-    </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="90" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="91"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="51">
-        <v>1</v>
-      </c>
-      <c r="F19" s="58"/>
-    </row>
-    <row r="20" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B20" s="65" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="94"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="54">
-        <v>2</v>
-      </c>
-      <c r="F20" s="54"/>
-    </row>
-    <row r="21" spans="2:7">
-      <c r="B21" s="78" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="79"/>
-      <c r="D21" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="55">
-        <f>SUM(E22:E25)</f>
-        <v>11</v>
-      </c>
-      <c r="F21" s="56"/>
-    </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="71" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="77"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="48">
-        <v>3</v>
-      </c>
-      <c r="F22" s="49"/>
-    </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="75" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="76"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="48">
-        <v>3</v>
-      </c>
-      <c r="F23" s="49"/>
-    </row>
-    <row r="24" spans="2:7">
-      <c r="B24" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="77"/>
-      <c r="D24" s="8"/>
+      <c r="F23" s="46"/>
+    </row>
+    <row r="24" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B24" s="89" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="90"/>
+      <c r="D24" s="9"/>
       <c r="E24" s="48">
         <v>1</v>
       </c>
-      <c r="F24" s="49"/>
-      <c r="G24" s="13"/>
-    </row>
-    <row r="25" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B25" s="88" t="s">
+      <c r="F24" s="48"/>
+    </row>
+    <row r="25" spans="2:7">
+      <c r="B25" s="91" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="92"/>
+      <c r="D25" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="89"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="50">
-        <v>4</v>
-      </c>
-      <c r="F25" s="51"/>
-      <c r="G25" s="13"/>
+      <c r="E25" s="94"/>
+      <c r="F25" s="94"/>
     </row>
     <row r="26" spans="2:7">
-      <c r="B26" s="78" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="79"/>
-      <c r="D26" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" s="55">
-        <f>SUM(E27:E31)</f>
-        <v>15</v>
-      </c>
-      <c r="F26" s="56"/>
+      <c r="B26" s="72" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="73"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="46">
+        <v>5</v>
+      </c>
+      <c r="F26" s="46"/>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="84" t="s">
-        <v>4</v>
-      </c>
-      <c r="C27" s="85"/>
+      <c r="B27" s="72" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="73"/>
       <c r="D27" s="8"/>
-      <c r="E27" s="48">
-        <v>3</v>
-      </c>
-      <c r="F27" s="49"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="75" t="s">
+      <c r="B28" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="76"/>
+      <c r="C28" s="73"/>
       <c r="D28" s="8"/>
-      <c r="E28" s="48">
-        <v>3</v>
-      </c>
-      <c r="F28" s="49"/>
+      <c r="E28" s="46">
+        <v>2</v>
+      </c>
+      <c r="F28" s="46"/>
+      <c r="G28" s="81"/>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="84" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="85"/>
+      <c r="B29" s="72" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="73"/>
       <c r="D29" s="8"/>
-      <c r="E29" s="48">
-        <v>3</v>
-      </c>
-      <c r="F29" s="49"/>
-    </row>
-    <row r="30" spans="2:7">
-      <c r="B30" s="86" t="s">
-        <v>21</v>
-      </c>
-      <c r="C30" s="87"/>
-      <c r="D30" s="8"/>
+      <c r="E29" s="46">
+        <v>2</v>
+      </c>
+      <c r="F29" s="46"/>
+      <c r="G29" s="81"/>
+    </row>
+    <row r="30" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B30" s="74" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="75"/>
+      <c r="D30" s="9"/>
       <c r="E30" s="48">
         <v>3</v>
       </c>
-      <c r="F30" s="49"/>
-    </row>
-    <row r="31" spans="2:7" ht="19.5" thickBot="1">
+      <c r="F30" s="48"/>
+      <c r="G30" s="81"/>
+    </row>
+    <row r="31" spans="2:7">
       <c r="B31" s="65" t="s">
-        <v>20</v>
-      </c>
-      <c r="C31" s="66"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="59">
+        <v>65</v>
+      </c>
+      <c r="C31" s="88"/>
+      <c r="D31" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="55"/>
+      <c r="F31" s="50"/>
+    </row>
+    <row r="32" spans="2:7">
+      <c r="B32" s="70" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="71"/>
+      <c r="D32" s="95"/>
+      <c r="E32" s="96"/>
+      <c r="F32" s="97"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="70" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" s="71"/>
+      <c r="D33" s="95"/>
+      <c r="E33" s="96">
+        <v>2</v>
+      </c>
+      <c r="F33" s="97"/>
+    </row>
+    <row r="34" spans="2:6">
+      <c r="B34" s="61" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="78"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="45"/>
+      <c r="F34" s="46"/>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="56" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" s="57"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="45">
+        <v>2</v>
+      </c>
+      <c r="F35" s="46"/>
+    </row>
+    <row r="36" spans="2:6">
+      <c r="B36" s="56" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="57"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="45">
+        <v>2</v>
+      </c>
+      <c r="F36" s="46"/>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37" s="61" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="78"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="45"/>
+      <c r="F37" s="46"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="76" t="s">
+        <v>66</v>
+      </c>
+      <c r="C38" s="77"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="45">
+        <v>2</v>
+      </c>
+      <c r="F38" s="46"/>
+    </row>
+    <row r="39" spans="2:6" ht="19.5" thickBot="1">
+      <c r="B39" s="58" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" s="59"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="52">
         <v>3</v>
       </c>
-      <c r="F31" s="54"/>
-    </row>
-    <row r="32" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B32" s="67" t="s">
-        <v>53</v>
-      </c>
-      <c r="C32" s="68"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="60">
-        <f>SUM(E3,E13,E21,E26)</f>
-        <v>61</v>
-      </c>
-      <c r="F32" s="61"/>
+      <c r="F39" s="48"/>
+    </row>
+    <row r="40" spans="2:6" ht="19.5" thickBot="1">
+      <c r="B40" s="63" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="80"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="54"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B25:C25"/>
+  <mergeCells count="39">
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1919,9 +2176,242 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DBF476-724A-4DAE-8D66-8B0809F96B84}">
-  <dimension ref="A1"/>
+  <dimension ref="B1:F20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
-  <sheetData/>
+  <cols>
+    <col min="3" max="3" width="18.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
+    <row r="2" spans="2:6" ht="19.5" thickBot="1">
+      <c r="B2" s="62" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2" s="83"/>
+      <c r="D2" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="19.5" thickBot="1">
+      <c r="B3" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="84"/>
+      <c r="D3" s="82" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="53"/>
+      <c r="F3" s="12"/>
+    </row>
+    <row r="4" spans="2:6">
+      <c r="B4" s="69" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="85"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="49">
+        <v>2</v>
+      </c>
+      <c r="F4" s="49"/>
+    </row>
+    <row r="5" spans="2:6" ht="19.5" thickBot="1">
+      <c r="B5" s="70" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="71"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="46">
+        <v>2</v>
+      </c>
+      <c r="F5" s="46"/>
+    </row>
+    <row r="6" spans="2:6">
+      <c r="B6" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="79"/>
+      <c r="D6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="B7" s="56" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="57"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="46">
+        <v>2</v>
+      </c>
+      <c r="F7" s="46"/>
+    </row>
+    <row r="8" spans="2:6">
+      <c r="B8" s="70" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="71"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="46">
+        <v>3</v>
+      </c>
+      <c r="F8" s="46"/>
+    </row>
+    <row r="9" spans="2:6" ht="19.5" thickBot="1">
+      <c r="B9" s="70" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="71"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="46">
+        <v>2</v>
+      </c>
+      <c r="F9" s="46"/>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" s="91" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="92"/>
+      <c r="D10" s="93" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="94"/>
+      <c r="F10" s="94"/>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11" s="72" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="73"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="46">
+        <v>5</v>
+      </c>
+      <c r="F11" s="46"/>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="B12" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="73"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="46">
+        <v>1</v>
+      </c>
+      <c r="F12" s="46"/>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13" s="72" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="73"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="46">
+        <v>2</v>
+      </c>
+      <c r="F13" s="46"/>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="88"/>
+      <c r="D14" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="55"/>
+      <c r="F14" s="50"/>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="B15" s="70" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="71"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="96">
+        <v>5</v>
+      </c>
+      <c r="F15" s="97"/>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="B16" s="61" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="78"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="46"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="56" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="57"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="45">
+        <v>2</v>
+      </c>
+      <c r="F17" s="46"/>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="61" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="78"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="46"/>
+    </row>
+    <row r="19" spans="2:6" ht="19.5" thickBot="1">
+      <c r="B19" s="76" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="77"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="45">
+        <v>2</v>
+      </c>
+      <c r="F19" s="46"/>
+    </row>
+    <row r="20" spans="2:6" ht="19.5" thickBot="1">
+      <c r="B20" s="63" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="80"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="54"/>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1929,9 +2419,215 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF80DA5A-1B69-4377-A99E-364B8197EABC}">
-  <dimension ref="A1"/>
+  <dimension ref="B1:F18"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
+    <row r="2" spans="2:6" ht="19.5" thickBot="1">
+      <c r="B2" s="62" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="83"/>
+      <c r="D2" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="19.5" thickBot="1">
+      <c r="B3" s="64" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="84"/>
+      <c r="D3" s="82" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="53"/>
+      <c r="F3" s="12"/>
+    </row>
+    <row r="4" spans="2:6" ht="19.5" thickBot="1">
+      <c r="B4" s="69" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="85"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="49">
+        <v>3</v>
+      </c>
+      <c r="F4" s="49"/>
+    </row>
+    <row r="5" spans="2:6">
+      <c r="B5" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="79"/>
+      <c r="D5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+    </row>
+    <row r="6" spans="2:6" ht="19.5" thickBot="1">
+      <c r="B6" s="56" t="s">
+        <v>80</v>
+      </c>
+      <c r="C6" s="57"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="46">
+        <v>3</v>
+      </c>
+      <c r="F6" s="46"/>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="B7" s="91" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="92"/>
+      <c r="D7" s="93" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="94"/>
+      <c r="F7" s="94"/>
+    </row>
+    <row r="8" spans="2:6">
+      <c r="B8" s="72" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="73"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="46">
+        <v>3</v>
+      </c>
+      <c r="F8" s="46"/>
+    </row>
+    <row r="9" spans="2:6" ht="19.5" thickBot="1">
+      <c r="B9" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="71"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="46">
+        <v>2</v>
+      </c>
+      <c r="F9" s="46"/>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" s="60" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="79"/>
+      <c r="D10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11" s="70" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="71"/>
+      <c r="D11" s="95"/>
+      <c r="E11" s="97">
+        <v>2</v>
+      </c>
+      <c r="F11" s="97"/>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="B12" s="61" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="78"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13" s="56" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="57"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="46">
+        <v>1</v>
+      </c>
+      <c r="F13" s="46"/>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14" s="56" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="57"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="46">
+        <v>1</v>
+      </c>
+      <c r="F14" s="46"/>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="B15" s="61" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="78"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="B16" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="67"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="46">
+        <v>1</v>
+      </c>
+      <c r="F16" s="46"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="66" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="67"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="46">
+        <v>1</v>
+      </c>
+      <c r="F17" s="46"/>
+    </row>
+    <row r="18" spans="2:6" ht="19.5" thickBot="1">
+      <c r="B18" s="98" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="99"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="87"/>
+      <c r="F18" s="87"/>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1943,182 +2639,182 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="95" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
-      <c r="G1" s="95"/>
+      <c r="C1" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
     </row>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B2" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="G2" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="H2" s="38" t="s">
-        <v>30</v>
+      <c r="B2" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="36" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>21</v>
       </c>
       <c r="J2" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="2:11">
-      <c r="B3" s="33"/>
-      <c r="D3" s="34">
+      <c r="B3" s="32"/>
+      <c r="D3" s="33">
         <v>46266</v>
       </c>
-      <c r="E3" s="34">
+      <c r="E3" s="33">
         <f>SUM(D3)+1</f>
         <v>46267</v>
       </c>
-      <c r="F3" s="34">
+      <c r="F3" s="33">
         <f t="shared" ref="F3:H3" si="0">SUM(E3)+1</f>
         <v>46268</v>
       </c>
-      <c r="G3" s="34">
+      <c r="G3" s="33">
         <f t="shared" si="0"/>
         <v>46269</v>
       </c>
-      <c r="H3" s="35">
+      <c r="H3" s="34">
         <f t="shared" si="0"/>
         <v>46270</v>
       </c>
-      <c r="J3" s="20"/>
+      <c r="J3" s="19"/>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="24">
+      <c r="B4" s="23">
         <f>SUM(H3)+1</f>
         <v>46271</v>
       </c>
-      <c r="C4" s="23">
+      <c r="C4" s="22">
         <f>SUM(B4)+1</f>
         <v>46272</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="22">
         <f t="shared" ref="D4:H4" si="1">SUM(C4)+1</f>
         <v>46273</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="100">
         <f t="shared" si="1"/>
         <v>46274</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="100">
         <f t="shared" si="1"/>
         <v>46275</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="100">
         <f t="shared" si="1"/>
         <v>46276</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="101">
         <f t="shared" si="1"/>
         <v>46277</v>
       </c>
-      <c r="J4" s="21"/>
+      <c r="J4" s="20"/>
       <c r="K4" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="18">
+      <c r="B5" s="102">
         <f>SUM(H4)+1</f>
         <v>46278</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="100">
         <f>SUM(B5)+1</f>
         <v>46279</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="16">
         <f t="shared" ref="D5:H5" si="2">SUM(C5)+1</f>
         <v>46280</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="16">
         <f t="shared" si="2"/>
         <v>46281</v>
       </c>
-      <c r="F5" s="17">
+      <c r="F5" s="16">
         <f t="shared" si="2"/>
         <v>46282</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="16">
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="H5" s="19">
+      <c r="H5" s="18">
         <f t="shared" si="2"/>
         <v>46284</v>
       </c>
-      <c r="J5" s="22"/>
+      <c r="J5" s="21"/>
       <c r="K5" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" s="18">
+      <c r="B6" s="17">
         <f>SUM(H5)+1</f>
         <v>46285</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="16">
         <f>SUM(B6)+1</f>
         <v>46286</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="16">
         <f t="shared" ref="D6:H6" si="3">SUM(C6)+1</f>
         <v>46287</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="16">
         <f t="shared" si="3"/>
         <v>46288</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="16">
         <f t="shared" si="3"/>
         <v>46289</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="16">
         <f t="shared" si="3"/>
         <v>46290</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="18">
         <f t="shared" si="3"/>
         <v>46291</v>
       </c>
-      <c r="J6" s="31"/>
+      <c r="J6" s="30"/>
       <c r="K6" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B7" s="41">
+      <c r="B7" s="40">
         <f>SUM(H6)+1</f>
         <v>46292</v>
       </c>
-      <c r="C7" s="42">
+      <c r="C7" s="41">
         <f>SUM(B7)+1</f>
         <v>46293</v>
       </c>
-      <c r="D7" s="42">
+      <c r="D7" s="41">
         <f t="shared" ref="D7:E7" si="4">SUM(C7)+1</f>
         <v>46294</v>
       </c>
-      <c r="E7" s="42">
+      <c r="E7" s="41">
         <f t="shared" si="4"/>
         <v>46295</v>
       </c>
@@ -2127,149 +2823,149 @@
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="2:11">
-      <c r="B8" s="33"/>
+      <c r="B8" s="32"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="39">
+      <c r="F8" s="38">
         <f>SUM(E7)+1</f>
         <v>46296</v>
       </c>
-      <c r="G8" s="39">
+      <c r="G8" s="38">
         <f>SUM(F8)+1</f>
         <v>46297</v>
       </c>
-      <c r="H8" s="40">
+      <c r="H8" s="39">
         <f>SUM(G8)+1</f>
         <v>46298</v>
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="25">
+      <c r="B9" s="24">
         <f>SUM(H8)+1</f>
         <v>46299</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="25">
         <f>SUM(B9)+1</f>
         <v>46300</v>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="25">
         <f t="shared" ref="D9:H9" si="5">SUM(C9)+1</f>
         <v>46301</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="25">
         <f t="shared" si="5"/>
         <v>46302</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="25">
         <f t="shared" si="5"/>
         <v>46303</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="25">
         <f t="shared" si="5"/>
         <v>46304</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="26">
         <f t="shared" si="5"/>
         <v>46305</v>
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="30">
+      <c r="B10" s="29">
         <f t="shared" ref="B10:B12" si="6">SUM(H9)+1</f>
         <v>46306</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="27">
         <f>SUM(B10)+1</f>
         <v>46307</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="27">
         <f t="shared" ref="D10:G10" si="7">SUM(C10)+1</f>
         <v>46308</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="27">
         <f t="shared" si="7"/>
         <v>46309</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="27">
         <f t="shared" si="7"/>
         <v>46310</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="27">
         <f t="shared" si="7"/>
         <v>46311</v>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="28">
         <f>SUM(G10)+1</f>
         <v>46312</v>
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="30">
+      <c r="B11" s="29">
         <f t="shared" si="6"/>
         <v>46313</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="31">
         <f>SUM(B11)+1</f>
         <v>46314</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="31">
         <f t="shared" ref="D11:F11" si="8">SUM(C11)+1</f>
         <v>46315</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="31">
         <f t="shared" si="8"/>
         <v>46316</v>
       </c>
-      <c r="F11" s="47">
+      <c r="F11" s="44">
         <f t="shared" si="8"/>
         <v>46317</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="13">
         <f t="shared" ref="G11" si="9">SUM(F11)+1</f>
         <v>46318</v>
       </c>
-      <c r="H11" s="45">
+      <c r="H11" s="42">
         <f>SUM(G11)+1</f>
         <v>46319</v>
       </c>
     </row>
     <row r="12" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B12" s="46">
+      <c r="B12" s="43">
         <f t="shared" si="6"/>
         <v>46320</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="14">
         <f>SUM(B12)+1</f>
         <v>46321</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="14">
         <f t="shared" ref="D12:H12" si="10">SUM(C12)+1</f>
         <v>46322</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="14">
         <f t="shared" si="10"/>
         <v>46323</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="14">
         <f t="shared" si="10"/>
         <v>46324</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="14">
         <f t="shared" si="10"/>
         <v>46325</v>
       </c>
-      <c r="H12" s="16">
+      <c r="H12" s="15">
         <f t="shared" si="10"/>
         <v>46326</v>
       </c>
     </row>
     <row r="13" spans="2:11">
       <c r="B13" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2293,17 +2989,17 @@
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="2:2">
@@ -2313,37 +3009,37 @@
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="2:2">

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nodasouma\Documents\GitHub\GlassesGame\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ayato Terao\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3718906E-F73B-4F27-9B66-D2106061731E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{795448E6-7026-495F-9866-4CBD7639C9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3690" yWindow="1530" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>
@@ -1272,94 +1272,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1368,21 +1284,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1397,16 +1298,115 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1707,11 +1707,11 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="84" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="82" t="s">
+      <c r="C2" s="85"/>
+      <c r="D2" s="57" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -1722,30 +1722,33 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="84"/>
-      <c r="D3" s="82" t="s">
+      <c r="C3" s="87"/>
+      <c r="D3" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="53"/>
+      <c r="E3" s="53">
+        <f>SUM(E4:E14)</f>
+        <v>12</v>
+      </c>
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="69" t="s">
+      <c r="B4" s="88" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="85"/>
+      <c r="C4" s="89"/>
       <c r="D4" s="7"/>
       <c r="E4" s="49"/>
       <c r="F4" s="49"/>
     </row>
     <row r="5" spans="2:6">
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="71"/>
+      <c r="C5" s="73"/>
       <c r="D5" s="8"/>
       <c r="E5" s="46">
         <v>2</v>
@@ -1753,10 +1756,10 @@
       <c r="F5" s="46"/>
     </row>
     <row r="6" spans="2:6">
-      <c r="B6" s="70" t="s">
+      <c r="B6" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="71"/>
+      <c r="C6" s="73"/>
       <c r="D6" s="8"/>
       <c r="E6" s="46">
         <v>1</v>
@@ -1764,10 +1767,10 @@
       <c r="F6" s="46"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="70" t="s">
+      <c r="B7" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="71"/>
+      <c r="C7" s="73"/>
       <c r="D7" s="8"/>
       <c r="E7" s="46">
         <v>2</v>
@@ -1775,10 +1778,10 @@
       <c r="F7" s="46"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="70" t="s">
+      <c r="B8" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="71"/>
+      <c r="C8" s="73"/>
       <c r="D8" s="10"/>
       <c r="E8" s="47">
         <v>1</v>
@@ -1786,10 +1789,10 @@
       <c r="F8" s="47"/>
     </row>
     <row r="9" spans="2:6">
-      <c r="B9" s="70" t="s">
+      <c r="B9" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="71"/>
+      <c r="C9" s="73"/>
       <c r="D9" s="10"/>
       <c r="E9" s="47">
         <v>1</v>
@@ -1797,10 +1800,10 @@
       <c r="F9" s="47"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="72" t="s">
+      <c r="B10" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="73"/>
+      <c r="C10" s="79"/>
       <c r="D10" s="8"/>
       <c r="E10" s="46">
         <v>2</v>
@@ -1808,19 +1811,19 @@
       <c r="F10" s="46"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="70" t="s">
+      <c r="B11" s="72" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="71"/>
+      <c r="C11" s="73"/>
       <c r="D11" s="8"/>
       <c r="E11" s="46"/>
       <c r="F11" s="47"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="72" t="s">
+      <c r="B12" s="78" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="73"/>
+      <c r="C12" s="79"/>
       <c r="D12" s="8"/>
       <c r="E12" s="46">
         <v>1</v>
@@ -1828,10 +1831,10 @@
       <c r="F12" s="46"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="70" t="s">
+      <c r="B13" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="71"/>
+      <c r="C13" s="73"/>
       <c r="D13" s="8"/>
       <c r="E13" s="46">
         <v>1</v>
@@ -1839,10 +1842,10 @@
       <c r="F13" s="46"/>
     </row>
     <row r="14" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B14" s="74" t="s">
+      <c r="B14" s="94" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="75"/>
+      <c r="C14" s="95"/>
       <c r="D14" s="9"/>
       <c r="E14" s="48">
         <v>1</v>
@@ -1850,21 +1853,24 @@
       <c r="F14" s="48"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="60" t="s">
+      <c r="B15" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="79"/>
+      <c r="C15" s="81"/>
       <c r="D15" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="49"/>
+      <c r="E15" s="49">
+        <f>SUM(E16:E24)</f>
+        <v>16</v>
+      </c>
       <c r="F15" s="49"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="56" t="s">
+      <c r="B16" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="57"/>
+      <c r="C16" s="77"/>
       <c r="D16" s="8"/>
       <c r="E16" s="46">
         <v>3</v>
@@ -1872,10 +1878,10 @@
       <c r="F16" s="46"/>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="70" t="s">
+      <c r="B17" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="71"/>
+      <c r="C17" s="73"/>
       <c r="D17" s="8"/>
       <c r="E17" s="46">
         <v>3</v>
@@ -1883,10 +1889,10 @@
       <c r="F17" s="46"/>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="70" t="s">
+      <c r="B18" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="71"/>
+      <c r="C18" s="73"/>
       <c r="D18" s="8"/>
       <c r="E18" s="46">
         <v>3</v>
@@ -1894,10 +1900,10 @@
       <c r="F18" s="46"/>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="70" t="s">
+      <c r="B19" s="72" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="71"/>
+      <c r="C19" s="73"/>
       <c r="D19" s="10"/>
       <c r="E19" s="46">
         <v>3</v>
@@ -1905,10 +1911,10 @@
       <c r="F19" s="46"/>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="70" t="s">
+      <c r="B20" s="72" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="71"/>
+      <c r="C20" s="73"/>
       <c r="D20" s="8"/>
       <c r="E20" s="51">
         <v>1</v>
@@ -1916,19 +1922,19 @@
       <c r="F20" s="50"/>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="72" t="s">
+      <c r="B21" s="78" t="s">
         <v>46</v>
       </c>
-      <c r="C21" s="73"/>
+      <c r="C21" s="79"/>
       <c r="D21" s="8"/>
       <c r="E21" s="46"/>
       <c r="F21" s="46"/>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="66" t="s">
+      <c r="B22" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="67"/>
+      <c r="C22" s="69"/>
       <c r="D22" s="8"/>
       <c r="E22" s="46">
         <v>1</v>
@@ -1936,10 +1942,10 @@
       <c r="F22" s="46"/>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="66" t="s">
+      <c r="B23" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="67"/>
+      <c r="C23" s="69"/>
       <c r="D23" s="8"/>
       <c r="E23" s="46">
         <v>1</v>
@@ -1947,10 +1953,10 @@
       <c r="F23" s="46"/>
     </row>
     <row r="24" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B24" s="89" t="s">
+      <c r="B24" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="90"/>
+      <c r="C24" s="97"/>
       <c r="D24" s="9"/>
       <c r="E24" s="48">
         <v>1</v>
@@ -1958,21 +1964,24 @@
       <c r="F24" s="48"/>
     </row>
     <row r="25" spans="2:7">
-      <c r="B25" s="91" t="s">
+      <c r="B25" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="92"/>
-      <c r="D25" s="93" t="s">
+      <c r="C25" s="83"/>
+      <c r="D25" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="94"/>
-      <c r="F25" s="94"/>
+      <c r="E25" s="61">
+        <f>SUM(E26:E30)</f>
+        <v>12</v>
+      </c>
+      <c r="F25" s="61"/>
     </row>
     <row r="26" spans="2:7">
-      <c r="B26" s="72" t="s">
+      <c r="B26" s="78" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="73"/>
+      <c r="C26" s="79"/>
       <c r="D26" s="8"/>
       <c r="E26" s="46">
         <v>5</v>
@@ -1980,95 +1989,98 @@
       <c r="F26" s="46"/>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="72" t="s">
+      <c r="B27" s="78" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="73"/>
+      <c r="C27" s="79"/>
       <c r="D27" s="8"/>
       <c r="E27" s="46"/>
       <c r="F27" s="46"/>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="72" t="s">
+      <c r="B28" s="78" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="73"/>
+      <c r="C28" s="79"/>
       <c r="D28" s="8"/>
       <c r="E28" s="46">
         <v>2</v>
       </c>
       <c r="F28" s="46"/>
-      <c r="G28" s="81"/>
+      <c r="G28" s="56"/>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="72" t="s">
+      <c r="B29" s="78" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="73"/>
+      <c r="C29" s="79"/>
       <c r="D29" s="8"/>
       <c r="E29" s="46">
         <v>2</v>
       </c>
       <c r="F29" s="46"/>
-      <c r="G29" s="81"/>
+      <c r="G29" s="56"/>
     </row>
     <row r="30" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B30" s="74" t="s">
+      <c r="B30" s="94" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="75"/>
+      <c r="C30" s="95"/>
       <c r="D30" s="9"/>
       <c r="E30" s="48">
         <v>3</v>
       </c>
       <c r="F30" s="48"/>
-      <c r="G30" s="81"/>
+      <c r="G30" s="56"/>
     </row>
     <row r="31" spans="2:7">
-      <c r="B31" s="65" t="s">
+      <c r="B31" s="98" t="s">
         <v>65</v>
       </c>
-      <c r="C31" s="88"/>
+      <c r="C31" s="99"/>
       <c r="D31" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="55"/>
+      <c r="E31" s="55">
+        <f>SUM(E32:E39)</f>
+        <v>11</v>
+      </c>
       <c r="F31" s="50"/>
     </row>
     <row r="32" spans="2:7">
-      <c r="B32" s="70" t="s">
+      <c r="B32" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="C32" s="71"/>
-      <c r="D32" s="95"/>
-      <c r="E32" s="96"/>
-      <c r="F32" s="97"/>
+      <c r="C32" s="73"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="63"/>
+      <c r="F32" s="64"/>
     </row>
     <row r="33" spans="2:6">
-      <c r="B33" s="70" t="s">
+      <c r="B33" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="C33" s="71"/>
-      <c r="D33" s="95"/>
-      <c r="E33" s="96">
+      <c r="C33" s="73"/>
+      <c r="D33" s="62"/>
+      <c r="E33" s="63">
         <v>2</v>
       </c>
-      <c r="F33" s="97"/>
+      <c r="F33" s="64"/>
     </row>
     <row r="34" spans="2:6">
-      <c r="B34" s="61" t="s">
+      <c r="B34" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="78"/>
+      <c r="C34" s="75"/>
       <c r="D34" s="8"/>
       <c r="E34" s="45"/>
       <c r="F34" s="46"/>
     </row>
     <row r="35" spans="2:6">
-      <c r="B35" s="56" t="s">
+      <c r="B35" s="76" t="s">
         <v>62</v>
       </c>
-      <c r="C35" s="57"/>
+      <c r="C35" s="77"/>
       <c r="D35" s="8"/>
       <c r="E35" s="45">
         <v>2</v>
@@ -2076,10 +2088,10 @@
       <c r="F35" s="46"/>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="56" t="s">
+      <c r="B36" s="76" t="s">
         <v>63</v>
       </c>
-      <c r="C36" s="57"/>
+      <c r="C36" s="77"/>
       <c r="D36" s="8"/>
       <c r="E36" s="45">
         <v>2</v>
@@ -2087,19 +2099,19 @@
       <c r="F36" s="46"/>
     </row>
     <row r="37" spans="2:6">
-      <c r="B37" s="61" t="s">
+      <c r="B37" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="78"/>
+      <c r="C37" s="75"/>
       <c r="D37" s="8"/>
       <c r="E37" s="45"/>
       <c r="F37" s="46"/>
     </row>
     <row r="38" spans="2:6">
-      <c r="B38" s="76" t="s">
+      <c r="B38" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="C38" s="77"/>
+      <c r="C38" s="101"/>
       <c r="D38" s="8"/>
       <c r="E38" s="45">
         <v>2</v>
@@ -2107,10 +2119,10 @@
       <c r="F38" s="46"/>
     </row>
     <row r="39" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B39" s="58" t="s">
+      <c r="B39" s="92" t="s">
         <v>67</v>
       </c>
-      <c r="C39" s="59"/>
+      <c r="C39" s="93"/>
       <c r="D39" s="9"/>
       <c r="E39" s="52">
         <v>3</v>
@@ -2118,42 +2130,19 @@
       <c r="F39" s="48"/>
     </row>
     <row r="40" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B40" s="63" t="s">
+      <c r="B40" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="C40" s="80"/>
+      <c r="C40" s="91"/>
       <c r="D40" s="12"/>
-      <c r="E40" s="53"/>
+      <c r="E40" s="53">
+        <f>SUM(E3+E15+E25+F31)</f>
+        <v>40</v>
+      </c>
       <c r="F40" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B17:C17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B29:C29"/>
     <mergeCell ref="B27:C27"/>
@@ -2167,6 +2156,32 @@
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B17:C17"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2184,11 +2199,11 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="84" t="s">
         <v>68</v>
       </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="82" t="s">
+      <c r="C2" s="85"/>
+      <c r="D2" s="57" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -2199,21 +2214,21 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="84"/>
-      <c r="D3" s="82" t="s">
+      <c r="C3" s="87"/>
+      <c r="D3" s="57" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="53"/>
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="69" t="s">
+      <c r="B4" s="88" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="85"/>
+      <c r="C4" s="89"/>
       <c r="D4" s="7"/>
       <c r="E4" s="49">
         <v>2</v>
@@ -2221,10 +2236,10 @@
       <c r="F4" s="49"/>
     </row>
     <row r="5" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B5" s="70" t="s">
+      <c r="B5" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="71"/>
+      <c r="C5" s="73"/>
       <c r="D5" s="8"/>
       <c r="E5" s="46">
         <v>2</v>
@@ -2232,10 +2247,10 @@
       <c r="F5" s="46"/>
     </row>
     <row r="6" spans="2:6">
-      <c r="B6" s="60" t="s">
+      <c r="B6" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="79"/>
+      <c r="C6" s="81"/>
       <c r="D6" s="7" t="s">
         <v>11</v>
       </c>
@@ -2243,10 +2258,10 @@
       <c r="F6" s="49"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="56" t="s">
+      <c r="B7" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="57"/>
+      <c r="C7" s="77"/>
       <c r="D7" s="8"/>
       <c r="E7" s="46">
         <v>2</v>
@@ -2254,10 +2269,10 @@
       <c r="F7" s="46"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="70" t="s">
+      <c r="B8" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="71"/>
+      <c r="C8" s="73"/>
       <c r="D8" s="8"/>
       <c r="E8" s="46">
         <v>3</v>
@@ -2265,10 +2280,10 @@
       <c r="F8" s="46"/>
     </row>
     <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="70" t="s">
+      <c r="B9" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="71"/>
+      <c r="C9" s="73"/>
       <c r="D9" s="8"/>
       <c r="E9" s="46">
         <v>2</v>
@@ -2276,21 +2291,21 @@
       <c r="F9" s="46"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="91" t="s">
+      <c r="B10" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="92"/>
-      <c r="D10" s="93" t="s">
+      <c r="C10" s="83"/>
+      <c r="D10" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="72" t="s">
+      <c r="B11" s="78" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="73"/>
+      <c r="C11" s="79"/>
       <c r="D11" s="8"/>
       <c r="E11" s="46">
         <v>5</v>
@@ -2298,10 +2313,10 @@
       <c r="F11" s="46"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="72" t="s">
+      <c r="B12" s="78" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="73"/>
+      <c r="C12" s="79"/>
       <c r="D12" s="8"/>
       <c r="E12" s="46">
         <v>1</v>
@@ -2309,10 +2324,10 @@
       <c r="F12" s="46"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="72" t="s">
+      <c r="B13" s="78" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="73"/>
+      <c r="C13" s="79"/>
       <c r="D13" s="8"/>
       <c r="E13" s="46">
         <v>2</v>
@@ -2320,10 +2335,10 @@
       <c r="F13" s="46"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="65" t="s">
+      <c r="B14" s="98" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="88"/>
+      <c r="C14" s="99"/>
       <c r="D14" s="11" t="s">
         <v>14</v>
       </c>
@@ -2331,30 +2346,30 @@
       <c r="F14" s="50"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="70" t="s">
+      <c r="B15" s="72" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="71"/>
-      <c r="D15" s="95"/>
-      <c r="E15" s="96">
+      <c r="C15" s="73"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="63">
         <v>5</v>
       </c>
-      <c r="F15" s="97"/>
+      <c r="F15" s="64"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="61" t="s">
+      <c r="B16" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="78"/>
+      <c r="C16" s="75"/>
       <c r="D16" s="8"/>
       <c r="E16" s="45"/>
       <c r="F16" s="46"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="57"/>
+      <c r="C17" s="77"/>
       <c r="D17" s="8"/>
       <c r="E17" s="45">
         <v>2</v>
@@ -2362,19 +2377,19 @@
       <c r="F17" s="46"/>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="61" t="s">
+      <c r="B18" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="78"/>
+      <c r="C18" s="75"/>
       <c r="D18" s="8"/>
       <c r="E18" s="45"/>
       <c r="F18" s="46"/>
     </row>
     <row r="19" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B19" s="76" t="s">
+      <c r="B19" s="100" t="s">
         <v>72</v>
       </c>
-      <c r="C19" s="77"/>
+      <c r="C19" s="101"/>
       <c r="D19" s="8"/>
       <c r="E19" s="45">
         <v>2</v>
@@ -2382,27 +2397,16 @@
       <c r="F19" s="46"/>
     </row>
     <row r="20" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B20" s="63" t="s">
+      <c r="B20" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="80"/>
+      <c r="C20" s="91"/>
       <c r="D20" s="12"/>
       <c r="E20" s="53"/>
       <c r="F20" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
@@ -2411,6 +2415,17 @@
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2424,11 +2439,11 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="84" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="82" t="s">
+      <c r="C2" s="85"/>
+      <c r="D2" s="57" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -2439,21 +2454,21 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="84"/>
-      <c r="D3" s="82" t="s">
+      <c r="C3" s="87"/>
+      <c r="D3" s="57" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="53"/>
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B4" s="69" t="s">
+      <c r="B4" s="88" t="s">
         <v>79</v>
       </c>
-      <c r="C4" s="85"/>
+      <c r="C4" s="89"/>
       <c r="D4" s="7"/>
       <c r="E4" s="49">
         <v>3</v>
@@ -2461,10 +2476,10 @@
       <c r="F4" s="49"/>
     </row>
     <row r="5" spans="2:6">
-      <c r="B5" s="60" t="s">
+      <c r="B5" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="79"/>
+      <c r="C5" s="81"/>
       <c r="D5" s="7" t="s">
         <v>11</v>
       </c>
@@ -2472,10 +2487,10 @@
       <c r="F5" s="49"/>
     </row>
     <row r="6" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B6" s="56" t="s">
+      <c r="B6" s="76" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="57"/>
+      <c r="C6" s="77"/>
       <c r="D6" s="8"/>
       <c r="E6" s="46">
         <v>3</v>
@@ -2483,21 +2498,21 @@
       <c r="F6" s="46"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="91" t="s">
+      <c r="B7" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="92"/>
-      <c r="D7" s="93" t="s">
+      <c r="C7" s="83"/>
+      <c r="D7" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="72" t="s">
+      <c r="B8" s="78" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="73"/>
+      <c r="C8" s="79"/>
       <c r="D8" s="8"/>
       <c r="E8" s="46">
         <v>3</v>
@@ -2505,10 +2520,10 @@
       <c r="F8" s="46"/>
     </row>
     <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="70" t="s">
+      <c r="B9" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="71"/>
+      <c r="C9" s="73"/>
       <c r="D9" s="8"/>
       <c r="E9" s="46">
         <v>2</v>
@@ -2516,10 +2531,10 @@
       <c r="F9" s="46"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="60" t="s">
+      <c r="B10" s="80" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="79"/>
+      <c r="C10" s="81"/>
       <c r="D10" s="7" t="s">
         <v>14</v>
       </c>
@@ -2527,30 +2542,30 @@
       <c r="F10" s="49"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="70" t="s">
+      <c r="B11" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="71"/>
-      <c r="D11" s="95"/>
-      <c r="E11" s="97">
+      <c r="C11" s="73"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="64">
         <v>2</v>
       </c>
-      <c r="F11" s="97"/>
+      <c r="F11" s="64"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="61" t="s">
+      <c r="B12" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="78"/>
+      <c r="C12" s="75"/>
       <c r="D12" s="8"/>
       <c r="E12" s="46"/>
       <c r="F12" s="46"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="56" t="s">
+      <c r="B13" s="76" t="s">
         <v>73</v>
       </c>
-      <c r="C13" s="57"/>
+      <c r="C13" s="77"/>
       <c r="D13" s="8"/>
       <c r="E13" s="46">
         <v>1</v>
@@ -2558,10 +2573,10 @@
       <c r="F13" s="46"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="56" t="s">
+      <c r="B14" s="76" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="57"/>
+      <c r="C14" s="77"/>
       <c r="D14" s="8"/>
       <c r="E14" s="46">
         <v>1</v>
@@ -2569,19 +2584,19 @@
       <c r="F14" s="46"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="61" t="s">
+      <c r="B15" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="78"/>
+      <c r="C15" s="75"/>
       <c r="D15" s="8"/>
       <c r="E15" s="46"/>
       <c r="F15" s="46"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="66" t="s">
+      <c r="B16" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="67"/>
+      <c r="C16" s="69"/>
       <c r="D16" s="8"/>
       <c r="E16" s="46">
         <v>1</v>
@@ -2589,10 +2604,10 @@
       <c r="F16" s="46"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="66" t="s">
+      <c r="B17" s="68" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="67"/>
+      <c r="C17" s="69"/>
       <c r="D17" s="8"/>
       <c r="E17" s="46">
         <v>1</v>
@@ -2600,16 +2615,25 @@
       <c r="F17" s="46"/>
     </row>
     <row r="18" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B18" s="98" t="s">
+      <c r="B18" s="70" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="99"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="87"/>
-      <c r="F18" s="87"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
@@ -2618,15 +2642,6 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2639,13 +2654,13 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
     </row>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
       <c r="B2" s="35" t="s">
@@ -2712,19 +2727,19 @@
         <f t="shared" ref="D4:H4" si="1">SUM(C4)+1</f>
         <v>46273</v>
       </c>
-      <c r="E4" s="100">
+      <c r="E4" s="65">
         <f t="shared" si="1"/>
         <v>46274</v>
       </c>
-      <c r="F4" s="100">
+      <c r="F4" s="65">
         <f t="shared" si="1"/>
         <v>46275</v>
       </c>
-      <c r="G4" s="100">
+      <c r="G4" s="65">
         <f t="shared" si="1"/>
         <v>46276</v>
       </c>
-      <c r="H4" s="101">
+      <c r="H4" s="66">
         <f t="shared" si="1"/>
         <v>46277</v>
       </c>
@@ -2734,11 +2749,11 @@
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="102">
+      <c r="B5" s="67">
         <f>SUM(H4)+1</f>
         <v>46278</v>
       </c>
-      <c r="C5" s="100">
+      <c r="C5" s="65">
         <f>SUM(B5)+1</f>
         <v>46279</v>
       </c>

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ayato Terao\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{795448E6-7026-495F-9866-4CBD7639C9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95493794-0C64-4C93-884D-F2DD17246525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,8 +31,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -40,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="90">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -291,18 +289,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>カメラ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>クイックターン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>死亡</t>
-    <rPh sb="0" eb="2">
-      <t>シボウ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -531,6 +518,113 @@
   </si>
   <si>
     <t>バグどり</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完全提出日</t>
+    <rPh sb="0" eb="5">
+      <t>カンゼンテイシュツビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>今日の日付</t>
+    <rPh sb="0" eb="2">
+      <t>キョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヒヅケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロト終了予定日</t>
+    <rPh sb="3" eb="5">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アルファ終了予定日</t>
+    <rPh sb="4" eb="6">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ベータ終了予定日</t>
+    <rPh sb="3" eb="5">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マスタ終了予定日</t>
+    <rPh sb="3" eb="5">
+      <t>シュウリョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>判定</t>
+    <rPh sb="0" eb="2">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未完</t>
+    <rPh sb="0" eb="2">
+      <t>ミカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラ(一人称)</t>
+    <rPh sb="4" eb="7">
+      <t>イチニンショウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>総コスト</t>
+    <rPh sb="0" eb="1">
+      <t>ソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>残日数</t>
+    <rPh sb="0" eb="1">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ニッスウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -570,7 +664,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -625,8 +719,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF3300"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="42">
+  <borders count="46">
     <border>
       <left/>
       <right/>
@@ -1165,11 +1277,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1216,7 +1374,6 @@
     <xf numFmtId="56" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="56" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1272,9 +1429,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1288,124 +1442,196 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1415,6 +1641,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF3300"/>
       <color rgb="FFCC99FF"/>
     </mruColors>
   </colors>
@@ -1693,7 +1920,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B1:G40"/>
+  <dimension ref="B1:K40"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9" style="4" customWidth="1"/>
@@ -1702,470 +1929,627 @@
     <col min="4" max="4" width="6.25" style="4" customWidth="1"/>
     <col min="5" max="5" width="7.125" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="4"/>
+    <col min="7" max="8" width="9" style="4"/>
+    <col min="9" max="9" width="17.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9" style="4"/>
+    <col min="12" max="12" width="9" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
-    <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="84" t="s">
+    <row r="1" spans="2:11" ht="19.5" thickBot="1"/>
+    <row r="2" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B2" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="85"/>
-      <c r="D2" s="57" t="s">
+      <c r="C2" s="73"/>
+      <c r="D2" s="55" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="96" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="86" t="s">
+      <c r="G2" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B3" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="87"/>
-      <c r="D3" s="57" t="s">
+      <c r="C3" s="75"/>
+      <c r="D3" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="53">
+      <c r="E3" s="52">
         <f>SUM(E4:E14)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="12"/>
-    </row>
-    <row r="4" spans="2:6">
-      <c r="B4" s="88" t="s">
+      <c r="G3" s="55" t="s">
+        <v>86</v>
+      </c>
+      <c r="I3" s="113" t="s">
+        <v>80</v>
+      </c>
+      <c r="J3" s="117">
+        <f ca="1">TODAY()</f>
+        <v>46281</v>
+      </c>
+      <c r="K3" s="55" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11">
+      <c r="B4" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="89"/>
-      <c r="D4" s="7"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="11"/>
       <c r="E4" s="49"/>
       <c r="F4" s="49"/>
-    </row>
-    <row r="5" spans="2:6">
-      <c r="B5" s="72" t="s">
+      <c r="G4" s="64" t="s">
+        <v>86</v>
+      </c>
+      <c r="I4" s="118" t="s">
+        <v>81</v>
+      </c>
+      <c r="J4" s="114">
+        <v>46295</v>
+      </c>
+      <c r="K4" s="112" t="str">
+        <f ca="1">SUM($J4-J3)&amp; "日"</f>
+        <v>14日</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11">
+      <c r="B5" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="73"/>
+      <c r="C5" s="67"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="46">
+      <c r="E5" s="45">
         <v>2</v>
       </c>
-      <c r="F5" s="46"/>
-    </row>
-    <row r="6" spans="2:6">
-      <c r="B6" s="72" t="s">
+      <c r="F5" s="45"/>
+      <c r="G5" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5" s="119" t="s">
+        <v>82</v>
+      </c>
+      <c r="J5" s="115">
+        <v>46305</v>
+      </c>
+      <c r="K5" s="110" t="str">
+        <f ca="1">SUM($J5-J3)&amp; "日"</f>
+        <v>24日</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11">
+      <c r="B6" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="73"/>
+      <c r="C6" s="67"/>
       <c r="D6" s="8"/>
-      <c r="E6" s="46">
+      <c r="E6" s="45">
         <v>1</v>
       </c>
-      <c r="F6" s="46"/>
-    </row>
-    <row r="7" spans="2:6">
-      <c r="B7" s="72" t="s">
+      <c r="F6" s="45"/>
+      <c r="G6" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="120" t="s">
+        <v>83</v>
+      </c>
+      <c r="J6" s="115">
+        <v>46310</v>
+      </c>
+      <c r="K6" s="110" t="str">
+        <f ca="1">SUM($J6-J3)&amp; "日"</f>
+        <v>29日</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11">
+      <c r="B7" s="101" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="73"/>
+      <c r="C7" s="102"/>
       <c r="D7" s="8"/>
-      <c r="E7" s="46">
+      <c r="E7" s="45">
         <v>2</v>
       </c>
-      <c r="F7" s="46"/>
-    </row>
-    <row r="8" spans="2:6">
-      <c r="B8" s="72" t="s">
+      <c r="F7" s="45"/>
+      <c r="G7" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="I7" s="121" t="s">
+        <v>84</v>
+      </c>
+      <c r="J7" s="115">
+        <v>46313</v>
+      </c>
+      <c r="K7" s="110" t="str">
+        <f ca="1">SUM($J7-J3)&amp; "日"</f>
+        <v>32日</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B8" s="101" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="102"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="46">
+        <v>2</v>
+      </c>
+      <c r="F8" s="46"/>
+      <c r="G8" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="I8" s="122" t="s">
+        <v>79</v>
+      </c>
+      <c r="J8" s="116">
+        <v>46314</v>
+      </c>
+      <c r="K8" s="111" t="str">
+        <f ca="1">SUM(J8-J3)&amp; "日"</f>
+        <v>33日</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11">
+      <c r="B9" s="101" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="73"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="47">
+      <c r="C9" s="102"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="46">
+        <v>2</v>
+      </c>
+      <c r="F9" s="46"/>
+      <c r="G9" s="63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11">
+      <c r="B10" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="104"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="45">
         <v>1</v>
       </c>
-      <c r="F8" s="47"/>
-    </row>
-    <row r="9" spans="2:6">
-      <c r="B9" s="72" t="s">
+      <c r="F10" s="45"/>
+      <c r="G10" s="63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11">
+      <c r="B11" s="101" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="73"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="47">
+      <c r="C11" s="102"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11">
+      <c r="B12" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="69"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="45">
         <v>1</v>
       </c>
-      <c r="F9" s="47"/>
-    </row>
-    <row r="10" spans="2:6">
-      <c r="B10" s="78" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="79"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="46">
-        <v>2</v>
-      </c>
-      <c r="F10" s="46"/>
-    </row>
-    <row r="11" spans="2:6">
-      <c r="B11" s="72" t="s">
+      <c r="F12" s="45"/>
+      <c r="G12" s="63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11">
+      <c r="B13" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="73"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="47"/>
-    </row>
-    <row r="12" spans="2:6">
-      <c r="B12" s="78" t="s">
+      <c r="C13" s="67"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="45">
+        <v>1</v>
+      </c>
+      <c r="F13" s="45"/>
+      <c r="G13" s="63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B14" s="97" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="79"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="46">
+      <c r="C14" s="98"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="46">
         <v>1</v>
       </c>
-      <c r="F12" s="46"/>
-    </row>
-    <row r="13" spans="2:6">
-      <c r="B13" s="72" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="73"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="46">
+      <c r="F14" s="46"/>
+      <c r="G14" s="123" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11">
+      <c r="B15" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="F13" s="46"/>
-    </row>
-    <row r="14" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B14" s="94" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="95"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="48">
-        <v>1</v>
-      </c>
-      <c r="F14" s="48"/>
-    </row>
-    <row r="15" spans="2:6">
-      <c r="B15" s="80" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="81"/>
+      <c r="C15" s="77"/>
       <c r="D15" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="49">
+      <c r="E15" s="48">
         <f>SUM(E16:E24)</f>
         <v>16</v>
       </c>
-      <c r="F15" s="49"/>
-    </row>
-    <row r="16" spans="2:6">
-      <c r="B16" s="76" t="s">
+      <c r="F15" s="48"/>
+      <c r="G15" s="109" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11">
+      <c r="B16" s="101" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="102"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="45">
+        <v>3</v>
+      </c>
+      <c r="F16" s="45"/>
+      <c r="G16" s="63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="101" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="102"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="45">
+        <v>3</v>
+      </c>
+      <c r="F17" s="45"/>
+      <c r="G17" s="63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="101" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="77"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="46">
+      <c r="C18" s="102"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="45">
         <v>3</v>
       </c>
-      <c r="F16" s="46"/>
-    </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="72" t="s">
+      <c r="F18" s="45"/>
+      <c r="G18" s="63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="73"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="46">
+      <c r="C19" s="102"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="45">
         <v>3</v>
       </c>
-      <c r="F17" s="46"/>
-    </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="72" t="s">
+      <c r="F19" s="45"/>
+      <c r="G19" s="63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="101" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="73"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="46">
-        <v>3</v>
-      </c>
-      <c r="F18" s="46"/>
-    </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="72" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="73"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="46">
-        <v>3</v>
-      </c>
-      <c r="F19" s="46"/>
-    </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="72" t="s">
-        <v>54</v>
-      </c>
-      <c r="C20" s="73"/>
+      <c r="C20" s="102"/>
       <c r="D20" s="8"/>
-      <c r="E20" s="51">
+      <c r="E20" s="50">
         <v>1</v>
       </c>
-      <c r="F20" s="50"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="63" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="78" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="79"/>
+      <c r="B21" s="103" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="104"/>
       <c r="D21" s="8"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="46"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="63" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="22" spans="2:7">
       <c r="B22" s="68" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C22" s="69"/>
       <c r="D22" s="8"/>
-      <c r="E22" s="46">
+      <c r="E22" s="45">
         <v>1</v>
       </c>
-      <c r="F22" s="46"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="63" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="23" spans="2:7">
       <c r="B23" s="68" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C23" s="69"/>
       <c r="D23" s="8"/>
-      <c r="E23" s="46">
+      <c r="E23" s="45">
         <v>1</v>
       </c>
-      <c r="F23" s="46"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="63" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="24" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B24" s="96" t="s">
-        <v>55</v>
-      </c>
-      <c r="C24" s="97"/>
+      <c r="B24" s="82" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="83"/>
       <c r="D24" s="9"/>
-      <c r="E24" s="48">
+      <c r="E24" s="47">
         <v>1</v>
       </c>
-      <c r="F24" s="48"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="65" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="25" spans="2:7">
-      <c r="B25" s="82" t="s">
+      <c r="B25" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="83"/>
-      <c r="D25" s="60" t="s">
+      <c r="C25" s="71"/>
+      <c r="D25" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="61">
+      <c r="E25" s="59">
         <f>SUM(E26:E30)</f>
         <v>12</v>
       </c>
-      <c r="F25" s="61"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="109" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="26" spans="2:7">
-      <c r="B26" s="78" t="s">
+      <c r="B26" s="103" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="104"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="45">
+        <v>5</v>
+      </c>
+      <c r="F26" s="45"/>
+      <c r="G26" s="63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7">
+      <c r="B27" s="103" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="104"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7">
+      <c r="B28" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="79"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="46">
-        <v>5</v>
-      </c>
-      <c r="F26" s="46"/>
-    </row>
-    <row r="27" spans="2:7">
-      <c r="B27" s="78" t="s">
+      <c r="C28" s="69"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="45">
+        <v>2</v>
+      </c>
+      <c r="F28" s="45"/>
+      <c r="G28" s="63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7">
+      <c r="B29" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="79"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-    </row>
-    <row r="28" spans="2:7">
-      <c r="B28" s="78" t="s">
+      <c r="C29" s="69"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="45">
+        <v>2</v>
+      </c>
+      <c r="F29" s="45"/>
+      <c r="G29" s="63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B30" s="105" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="79"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="46">
-        <v>2</v>
-      </c>
-      <c r="F28" s="46"/>
-      <c r="G28" s="56"/>
-    </row>
-    <row r="29" spans="2:7">
-      <c r="B29" s="78" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="79"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="46">
-        <v>2</v>
-      </c>
-      <c r="F29" s="46"/>
-      <c r="G29" s="56"/>
-    </row>
-    <row r="30" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B30" s="94" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="95"/>
+      <c r="C30" s="106"/>
       <c r="D30" s="9"/>
-      <c r="E30" s="48">
+      <c r="E30" s="47">
         <v>3</v>
       </c>
-      <c r="F30" s="48"/>
-      <c r="G30" s="56"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="65" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="31" spans="2:7">
-      <c r="B31" s="98" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="99"/>
-      <c r="D31" s="11" t="s">
+      <c r="B31" s="76" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="77"/>
+      <c r="D31" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="55">
+      <c r="E31" s="126">
         <f>SUM(E32:E39)</f>
         <v>11</v>
       </c>
-      <c r="F31" s="50"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="109" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="32" spans="2:7">
-      <c r="B32" s="72" t="s">
+      <c r="B32" s="101" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="102"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="49"/>
+      <c r="G32" s="63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="66" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="67"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="54">
+        <v>2</v>
+      </c>
+      <c r="F33" s="49"/>
+      <c r="G33" s="63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="86" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" s="87"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="44"/>
+      <c r="F34" s="45"/>
+      <c r="G34" s="63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="B35" s="101" t="s">
+        <v>60</v>
+      </c>
+      <c r="C35" s="102"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="44">
+        <v>2</v>
+      </c>
+      <c r="F35" s="45"/>
+      <c r="G35" s="63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="101" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" s="102"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="44">
+        <v>2</v>
+      </c>
+      <c r="F36" s="45"/>
+      <c r="G36" s="63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="86" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="87"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="44"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="107" t="s">
         <v>64</v>
       </c>
-      <c r="C32" s="73"/>
-      <c r="D32" s="62"/>
-      <c r="E32" s="63"/>
-      <c r="F32" s="64"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="C33" s="73"/>
-      <c r="D33" s="62"/>
-      <c r="E33" s="63">
+      <c r="C38" s="108"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="44">
         <v>2</v>
       </c>
-      <c r="F33" s="64"/>
-    </row>
-    <row r="34" spans="2:6">
-      <c r="B34" s="74" t="s">
-        <v>4</v>
-      </c>
-      <c r="C34" s="75"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="45"/>
-      <c r="F34" s="46"/>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" s="76" t="s">
-        <v>62</v>
-      </c>
-      <c r="C35" s="77"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="45">
-        <v>2</v>
-      </c>
-      <c r="F35" s="46"/>
-    </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="76" t="s">
-        <v>63</v>
-      </c>
-      <c r="C36" s="77"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="45">
-        <v>2</v>
-      </c>
-      <c r="F36" s="46"/>
-    </row>
-    <row r="37" spans="2:6">
-      <c r="B37" s="74" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" s="75"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="45"/>
-      <c r="F37" s="46"/>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="100" t="s">
-        <v>66</v>
-      </c>
-      <c r="C38" s="101"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="45">
-        <v>2</v>
-      </c>
-      <c r="F38" s="46"/>
-    </row>
-    <row r="39" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B39" s="92" t="s">
-        <v>67</v>
-      </c>
-      <c r="C39" s="93"/>
+      <c r="F38" s="45"/>
+      <c r="G38" s="63" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B39" s="105" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" s="106"/>
       <c r="D39" s="9"/>
-      <c r="E39" s="52">
+      <c r="E39" s="51">
         <v>3</v>
       </c>
-      <c r="F39" s="48"/>
-    </row>
-    <row r="40" spans="2:6" ht="19.5" thickBot="1">
+      <c r="F39" s="47"/>
+      <c r="G39" s="65" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" ht="19.5" thickBot="1">
       <c r="B40" s="90" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="C40" s="91"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="53">
+      <c r="D40" s="56"/>
+      <c r="E40" s="124">
         <f>SUM(E3+E15+E25+F31)</f>
-        <v>40</v>
-      </c>
-      <c r="F40" s="54"/>
+        <v>41</v>
+      </c>
+      <c r="F40" s="125">
+        <f>SUM(F4:F39)</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B13:C13"/>
@@ -2182,6 +2566,29 @@
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2199,11 +2606,11 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="84" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" s="85"/>
-      <c r="D2" s="57" t="s">
+      <c r="B2" s="72" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="55" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -2214,199 +2621,210 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="86" t="s">
+      <c r="B3" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="87"/>
-      <c r="D3" s="57" t="s">
+      <c r="C3" s="75"/>
+      <c r="D3" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="53"/>
+      <c r="E3" s="52"/>
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="88" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="89"/>
+      <c r="B4" s="78" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="79"/>
       <c r="D4" s="7"/>
-      <c r="E4" s="49">
+      <c r="E4" s="48">
         <v>2</v>
       </c>
-      <c r="F4" s="49"/>
+      <c r="F4" s="48"/>
     </row>
     <row r="5" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B5" s="72" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="73"/>
+      <c r="B5" s="66" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="67"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="46">
+      <c r="E5" s="45">
         <v>2</v>
       </c>
-      <c r="F5" s="46"/>
+      <c r="F5" s="45"/>
     </row>
     <row r="6" spans="2:6">
-      <c r="B6" s="80" t="s">
+      <c r="B6" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="81"/>
+      <c r="C6" s="77"/>
       <c r="D6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="76" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="77"/>
+      <c r="B7" s="66" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="67"/>
       <c r="D7" s="8"/>
-      <c r="E7" s="46">
+      <c r="E7" s="45">
         <v>2</v>
       </c>
-      <c r="F7" s="46"/>
+      <c r="F7" s="45"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="72" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" s="73"/>
+      <c r="B8" s="66" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="67"/>
       <c r="D8" s="8"/>
-      <c r="E8" s="46">
+      <c r="E8" s="45">
         <v>3</v>
       </c>
-      <c r="F8" s="46"/>
+      <c r="F8" s="45"/>
     </row>
     <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="66" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" s="67"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="45">
+        <v>2</v>
+      </c>
+      <c r="F9" s="45"/>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" s="70" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="71"/>
+      <c r="D10" s="58" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11" s="68" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="69"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="45">
+        <v>5</v>
+      </c>
+      <c r="F11" s="45"/>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="B12" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="73"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="46">
+      <c r="C12" s="69"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="45">
+        <v>1</v>
+      </c>
+      <c r="F12" s="45"/>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13" s="68" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="69"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="45">
         <v>2</v>
       </c>
-      <c r="F9" s="46"/>
-    </row>
-    <row r="10" spans="2:6">
-      <c r="B10" s="82" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="83"/>
-      <c r="D10" s="60" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
-    </row>
-    <row r="11" spans="2:6">
-      <c r="B11" s="78" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" s="79"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="46">
-        <v>5</v>
-      </c>
-      <c r="F11" s="46"/>
-    </row>
-    <row r="12" spans="2:6">
-      <c r="B12" s="78" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="79"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="46">
-        <v>1</v>
-      </c>
-      <c r="F12" s="46"/>
-    </row>
-    <row r="13" spans="2:6">
-      <c r="B13" s="78" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="79"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="46">
-        <v>2</v>
-      </c>
-      <c r="F13" s="46"/>
+      <c r="F13" s="45"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="98" t="s">
-        <v>65</v>
-      </c>
-      <c r="C14" s="99"/>
+      <c r="B14" s="84" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="85"/>
       <c r="D14" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="55"/>
-      <c r="F14" s="50"/>
+      <c r="E14" s="54"/>
+      <c r="F14" s="49"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="72" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="73"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="63">
+      <c r="B15" s="66" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="67"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="54">
         <v>5</v>
       </c>
-      <c r="F15" s="64"/>
+      <c r="F15" s="49"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="74" t="s">
+      <c r="B16" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="75"/>
+      <c r="C16" s="87"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="46"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="45"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="76" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="77"/>
+      <c r="B17" s="66" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="67"/>
       <c r="D17" s="8"/>
-      <c r="E17" s="45">
+      <c r="E17" s="44">
         <v>2</v>
       </c>
-      <c r="F17" s="46"/>
+      <c r="F17" s="45"/>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="74" t="s">
+      <c r="B18" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="75"/>
+      <c r="C18" s="87"/>
       <c r="D18" s="8"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="46"/>
+      <c r="E18" s="44"/>
+      <c r="F18" s="45"/>
     </row>
     <row r="19" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B19" s="100" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="101"/>
+      <c r="B19" s="88" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="89"/>
       <c r="D19" s="8"/>
-      <c r="E19" s="45">
+      <c r="E19" s="44">
         <v>2</v>
       </c>
-      <c r="F19" s="46"/>
+      <c r="F19" s="45"/>
     </row>
     <row r="20" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B20" s="90" t="s">
+      <c r="B20" s="80" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="91"/>
+      <c r="C20" s="81"/>
       <c r="D20" s="12"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="54"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
@@ -2415,17 +2833,6 @@
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2439,11 +2846,11 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="84" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" s="85"/>
-      <c r="D2" s="57" t="s">
+      <c r="B2" s="72" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="73"/>
+      <c r="D2" s="55" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -2454,187 +2861,177 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="86" t="s">
+      <c r="B3" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="87"/>
-      <c r="D3" s="57" t="s">
+      <c r="C3" s="75"/>
+      <c r="D3" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="53"/>
+      <c r="E3" s="52"/>
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B4" s="88" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="89"/>
+      <c r="B4" s="78" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="79"/>
       <c r="D4" s="7"/>
-      <c r="E4" s="49">
+      <c r="E4" s="48">
         <v>3</v>
       </c>
-      <c r="F4" s="49"/>
+      <c r="F4" s="48"/>
     </row>
     <row r="5" spans="2:6">
-      <c r="B5" s="80" t="s">
+      <c r="B5" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="81"/>
+      <c r="C5" s="77"/>
       <c r="D5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
     </row>
     <row r="6" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B6" s="76" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" s="77"/>
+      <c r="B6" s="66" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" s="67"/>
       <c r="D6" s="8"/>
-      <c r="E6" s="46">
+      <c r="E6" s="45">
         <v>3</v>
       </c>
-      <c r="F6" s="46"/>
+      <c r="F6" s="45"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="82" t="s">
+      <c r="B7" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="83"/>
-      <c r="D7" s="60" t="s">
+      <c r="C7" s="71"/>
+      <c r="D7" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="61"/>
-      <c r="F7" s="61"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="78" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="79"/>
+      <c r="B8" s="68" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="69"/>
       <c r="D8" s="8"/>
-      <c r="E8" s="46">
+      <c r="E8" s="45">
         <v>3</v>
       </c>
-      <c r="F8" s="46"/>
+      <c r="F8" s="45"/>
     </row>
     <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="72" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="73"/>
+      <c r="B9" s="66" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="67"/>
       <c r="D9" s="8"/>
-      <c r="E9" s="46">
+      <c r="E9" s="45">
         <v>2</v>
       </c>
-      <c r="F9" s="46"/>
+      <c r="F9" s="45"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="80" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" s="81"/>
+      <c r="B10" s="76" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="77"/>
       <c r="D10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="72" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" s="73"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="64">
+      <c r="B11" s="66" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="67"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="49">
         <v>2</v>
       </c>
-      <c r="F11" s="64"/>
+      <c r="F11" s="49"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="74" t="s">
+      <c r="B12" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="75"/>
+      <c r="C12" s="87"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="76" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" s="77"/>
+      <c r="B13" s="66" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="67"/>
       <c r="D13" s="8"/>
-      <c r="E13" s="46">
+      <c r="E13" s="45">
         <v>1</v>
       </c>
-      <c r="F13" s="46"/>
+      <c r="F13" s="45"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="76" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" s="77"/>
+      <c r="B14" s="66" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="67"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="46">
+      <c r="E14" s="45">
         <v>1</v>
       </c>
-      <c r="F14" s="46"/>
+      <c r="F14" s="45"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="74" t="s">
+      <c r="B15" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="75"/>
+      <c r="C15" s="87"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
     </row>
     <row r="16" spans="2:6">
       <c r="B16" s="68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C16" s="69"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="46">
+      <c r="E16" s="45">
         <v>1</v>
       </c>
-      <c r="F16" s="46"/>
+      <c r="F16" s="45"/>
     </row>
     <row r="17" spans="2:6">
       <c r="B17" s="68" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C17" s="69"/>
       <c r="D17" s="8"/>
-      <c r="E17" s="46">
+      <c r="E17" s="45">
         <v>1</v>
       </c>
-      <c r="F17" s="46"/>
+      <c r="F17" s="45"/>
     </row>
     <row r="18" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B18" s="70" t="s">
+      <c r="B18" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="71"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="59"/>
-      <c r="F18" s="59"/>
+      <c r="C18" s="91"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B11:C11"/>
@@ -2642,6 +3039,16 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2654,34 +3061,34 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="102" t="s">
+      <c r="C1" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
     </row>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="36" t="s">
+      <c r="G2" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="37" t="s">
+      <c r="H2" s="36" t="s">
         <v>21</v>
       </c>
       <c r="J2" t="s">
@@ -2689,23 +3096,23 @@
       </c>
     </row>
     <row r="3" spans="2:11">
-      <c r="B3" s="32"/>
-      <c r="D3" s="33">
+      <c r="B3" s="31"/>
+      <c r="D3" s="32">
         <v>46266</v>
       </c>
-      <c r="E3" s="33">
+      <c r="E3" s="32">
         <f>SUM(D3)+1</f>
         <v>46267</v>
       </c>
-      <c r="F3" s="33">
+      <c r="F3" s="32">
         <f t="shared" ref="F3:H3" si="0">SUM(E3)+1</f>
         <v>46268</v>
       </c>
-      <c r="G3" s="33">
+      <c r="G3" s="32">
         <f t="shared" si="0"/>
         <v>46269</v>
       </c>
-      <c r="H3" s="34">
+      <c r="H3" s="33">
         <f t="shared" si="0"/>
         <v>46270</v>
       </c>
@@ -2727,19 +3134,19 @@
         <f t="shared" ref="D4:H4" si="1">SUM(C4)+1</f>
         <v>46273</v>
       </c>
-      <c r="E4" s="65">
+      <c r="E4" s="60">
         <f t="shared" si="1"/>
         <v>46274</v>
       </c>
-      <c r="F4" s="65">
+      <c r="F4" s="60">
         <f t="shared" si="1"/>
         <v>46275</v>
       </c>
-      <c r="G4" s="65">
+      <c r="G4" s="60">
         <f t="shared" si="1"/>
         <v>46276</v>
       </c>
-      <c r="H4" s="66">
+      <c r="H4" s="61">
         <f t="shared" si="1"/>
         <v>46277</v>
       </c>
@@ -2749,15 +3156,15 @@
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="67">
+      <c r="B5" s="62">
         <f>SUM(H4)+1</f>
         <v>46278</v>
       </c>
-      <c r="C5" s="65">
+      <c r="C5" s="60">
         <f>SUM(B5)+1</f>
         <v>46279</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="60">
         <f t="shared" ref="D5:H5" si="2">SUM(C5)+1</f>
         <v>46280</v>
       </c>
@@ -2811,25 +3218,25 @@
         <f t="shared" si="3"/>
         <v>46291</v>
       </c>
-      <c r="J6" s="30"/>
+      <c r="J6" s="29"/>
       <c r="K6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B7" s="40">
+      <c r="B7" s="39">
         <f>SUM(H6)+1</f>
         <v>46292</v>
       </c>
-      <c r="C7" s="41">
+      <c r="C7" s="40">
         <f>SUM(B7)+1</f>
         <v>46293</v>
       </c>
-      <c r="D7" s="41">
+      <c r="D7" s="40">
         <f t="shared" ref="D7:E7" si="4">SUM(C7)+1</f>
         <v>46294</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="40">
         <f t="shared" si="4"/>
         <v>46295</v>
       </c>
@@ -2838,19 +3245,19 @@
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="2:11">
-      <c r="B8" s="32"/>
+      <c r="B8" s="31"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="38">
+      <c r="F8" s="37">
         <f>SUM(E7)+1</f>
         <v>46296</v>
       </c>
-      <c r="G8" s="38">
+      <c r="G8" s="37">
         <f>SUM(F8)+1</f>
         <v>46297</v>
       </c>
-      <c r="H8" s="39">
+      <c r="H8" s="38">
         <f>SUM(G8)+1</f>
         <v>46298</v>
       </c>
@@ -2886,7 +3293,7 @@
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="29">
+      <c r="B10" s="28">
         <f t="shared" ref="B10:B12" si="6">SUM(H9)+1</f>
         <v>46306</v>
       </c>
@@ -2906,33 +3313,33 @@
         <f t="shared" si="7"/>
         <v>46310</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="30">
         <f t="shared" si="7"/>
         <v>46311</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="95">
         <f>SUM(G10)+1</f>
         <v>46312</v>
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="29">
+      <c r="B11" s="94">
         <f t="shared" si="6"/>
         <v>46313</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="43">
         <f>SUM(B11)+1</f>
         <v>46314</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="93">
         <f t="shared" ref="D11:F11" si="8">SUM(C11)+1</f>
         <v>46315</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="93">
         <f t="shared" si="8"/>
         <v>46316</v>
       </c>
-      <c r="F11" s="44">
+      <c r="F11" s="93">
         <f t="shared" si="8"/>
         <v>46317</v>
       </c>
@@ -2940,13 +3347,13 @@
         <f t="shared" ref="G11" si="9">SUM(F11)+1</f>
         <v>46318</v>
       </c>
-      <c r="H11" s="42">
+      <c r="H11" s="41">
         <f>SUM(G11)+1</f>
         <v>46319</v>
       </c>
     </row>
     <row r="12" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B12" s="43">
+      <c r="B12" s="42">
         <f t="shared" si="6"/>
         <v>46320</v>
       </c>

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ayato Terao\Documents\GitHub\GlassesGame\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95493794-0C64-4C93-884D-F2DD17246525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA0A265-64C4-4A5E-A49B-D64CD1D06AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="91">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -289,10 +289,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>クイックターン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>復活</t>
     <rPh sb="0" eb="2">
       <t>フッカツ</t>
@@ -624,6 +620,20 @@
     </rPh>
     <rPh sb="1" eb="3">
       <t>ニッスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完了</t>
+    <rPh sb="0" eb="2">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>視点反転</t>
+    <rPh sb="0" eb="4">
+      <t>シテンハンテン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1327,7 +1337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1456,127 +1466,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1621,9 +1516,6 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1632,6 +1524,123 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1939,28 +1948,28 @@
   <sheetData>
     <row r="1" spans="2:11" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="73"/>
+      <c r="C2" s="108"/>
       <c r="D2" s="55" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="96" t="s">
+      <c r="F2" s="68" t="s">
         <v>8</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B3" s="74" t="s">
+      <c r="B3" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="75"/>
+      <c r="C3" s="110"/>
       <c r="D3" s="55" t="s">
         <v>12</v>
       </c>
@@ -1968,226 +1977,237 @@
         <f>SUM(E4:E14)</f>
         <v>13</v>
       </c>
-      <c r="F3" s="12"/>
+      <c r="F3" s="53">
+        <f>SUM(F4:F14)</f>
+        <v>7</v>
+      </c>
       <c r="G3" s="55" t="s">
-        <v>86</v>
-      </c>
-      <c r="I3" s="113" t="s">
-        <v>80</v>
-      </c>
-      <c r="J3" s="117">
+        <v>85</v>
+      </c>
+      <c r="I3" s="74" t="s">
+        <v>79</v>
+      </c>
+      <c r="J3" s="78">
         <f ca="1">TODAY()</f>
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="K3" s="55" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="99" t="s">
+      <c r="B4" s="111" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="100"/>
+      <c r="C4" s="112"/>
       <c r="D4" s="11"/>
       <c r="E4" s="49"/>
       <c r="F4" s="49"/>
       <c r="G4" s="64" t="s">
-        <v>86</v>
-      </c>
-      <c r="I4" s="118" t="s">
-        <v>81</v>
-      </c>
-      <c r="J4" s="114">
+        <v>89</v>
+      </c>
+      <c r="I4" s="79" t="s">
+        <v>80</v>
+      </c>
+      <c r="J4" s="75">
         <v>46295</v>
       </c>
-      <c r="K4" s="112" t="str">
+      <c r="K4" s="73" t="str">
         <f ca="1">SUM($J4-J3)&amp; "日"</f>
-        <v>14日</v>
+        <v>7日</v>
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="66" t="s">
+      <c r="B5" s="91" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="67"/>
+      <c r="C5" s="92"/>
       <c r="D5" s="8"/>
       <c r="E5" s="45">
         <v>2</v>
       </c>
-      <c r="F5" s="45"/>
-      <c r="G5" s="63" t="s">
-        <v>86</v>
-      </c>
-      <c r="I5" s="119" t="s">
-        <v>82</v>
-      </c>
-      <c r="J5" s="115">
+      <c r="F5" s="45">
+        <v>2</v>
+      </c>
+      <c r="G5" s="64" t="s">
+        <v>89</v>
+      </c>
+      <c r="I5" s="80" t="s">
+        <v>81</v>
+      </c>
+      <c r="J5" s="76">
         <v>46305</v>
       </c>
-      <c r="K5" s="110" t="str">
+      <c r="K5" s="71" t="str">
         <f ca="1">SUM($J5-J3)&amp; "日"</f>
-        <v>24日</v>
+        <v>17日</v>
       </c>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" s="66" t="s">
+      <c r="B6" s="91" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="67"/>
+      <c r="C6" s="92"/>
       <c r="D6" s="8"/>
       <c r="E6" s="45">
         <v>1</v>
       </c>
-      <c r="F6" s="45"/>
-      <c r="G6" s="63" t="s">
-        <v>86</v>
-      </c>
-      <c r="I6" s="120" t="s">
-        <v>83</v>
-      </c>
-      <c r="J6" s="115">
+      <c r="F6" s="45">
+        <v>2</v>
+      </c>
+      <c r="G6" s="64" t="s">
+        <v>89</v>
+      </c>
+      <c r="I6" s="81" t="s">
+        <v>82</v>
+      </c>
+      <c r="J6" s="76">
         <v>46310</v>
       </c>
-      <c r="K6" s="110" t="str">
+      <c r="K6" s="71" t="str">
         <f ca="1">SUM($J6-J3)&amp; "日"</f>
-        <v>29日</v>
+        <v>22日</v>
       </c>
     </row>
     <row r="7" spans="2:11">
-      <c r="B7" s="101" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="102"/>
+      <c r="B7" s="99" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="100"/>
       <c r="D7" s="8"/>
       <c r="E7" s="45">
         <v>2</v>
       </c>
-      <c r="F7" s="45"/>
-      <c r="G7" s="63" t="s">
-        <v>86</v>
-      </c>
-      <c r="I7" s="121" t="s">
-        <v>84</v>
-      </c>
-      <c r="J7" s="115">
+      <c r="F7" s="49">
+        <v>2</v>
+      </c>
+      <c r="G7" s="64" t="s">
+        <v>89</v>
+      </c>
+      <c r="I7" s="82" t="s">
+        <v>83</v>
+      </c>
+      <c r="J7" s="76">
         <v>46313</v>
       </c>
-      <c r="K7" s="110" t="str">
+      <c r="K7" s="71" t="str">
         <f ca="1">SUM($J7-J3)&amp; "日"</f>
-        <v>32日</v>
+        <v>25日</v>
       </c>
     </row>
     <row r="8" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B8" s="101" t="s">
+      <c r="B8" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="102"/>
+      <c r="C8" s="100"/>
       <c r="D8" s="10"/>
       <c r="E8" s="46">
         <v>2</v>
       </c>
       <c r="F8" s="46"/>
       <c r="G8" s="63" t="s">
-        <v>86</v>
-      </c>
-      <c r="I8" s="122" t="s">
-        <v>79</v>
-      </c>
-      <c r="J8" s="116">
+        <v>85</v>
+      </c>
+      <c r="I8" s="83" t="s">
+        <v>78</v>
+      </c>
+      <c r="J8" s="77">
         <v>46314</v>
       </c>
-      <c r="K8" s="111" t="str">
+      <c r="K8" s="72" t="str">
         <f ca="1">SUM(J8-J3)&amp; "日"</f>
-        <v>33日</v>
+        <v>26日</v>
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="101" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="102"/>
+      <c r="B9" s="99" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="100"/>
       <c r="D9" s="10"/>
       <c r="E9" s="46">
         <v>2</v>
       </c>
       <c r="F9" s="46"/>
       <c r="G9" s="63" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11">
+      <c r="B10" s="113" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="10" spans="2:11">
-      <c r="B10" s="103" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" s="104"/>
+      <c r="C10" s="114"/>
       <c r="D10" s="8"/>
       <c r="E10" s="45">
         <v>1</v>
       </c>
-      <c r="F10" s="45"/>
+      <c r="F10" s="45">
+        <v>1</v>
+      </c>
       <c r="G10" s="63" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="101" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="102"/>
+      <c r="B11" s="99" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="100"/>
       <c r="D11" s="8"/>
       <c r="E11" s="45"/>
       <c r="F11" s="46"/>
       <c r="G11" s="63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="2:11">
-      <c r="B12" s="68" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="69"/>
+      <c r="B12" s="95" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="96"/>
       <c r="D12" s="8"/>
       <c r="E12" s="45">
         <v>1</v>
       </c>
       <c r="F12" s="45"/>
       <c r="G12" s="63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="2:11">
-      <c r="B13" s="66" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="67"/>
+      <c r="B13" s="91" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="92"/>
       <c r="D13" s="8"/>
       <c r="E13" s="45">
         <v>1</v>
       </c>
       <c r="F13" s="45"/>
       <c r="G13" s="63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B14" s="97" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="98"/>
+      <c r="B14" s="93" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="94"/>
       <c r="D14" s="10"/>
       <c r="E14" s="46">
         <v>1</v>
       </c>
       <c r="F14" s="46"/>
-      <c r="G14" s="123" t="s">
-        <v>86</v>
+      <c r="G14" s="69" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="2:11">
-      <c r="B15" s="76" t="s">
+      <c r="B15" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="77"/>
+      <c r="C15" s="102"/>
       <c r="D15" s="7" t="s">
         <v>11</v>
       </c>
@@ -2196,139 +2216,139 @@
         <v>16</v>
       </c>
       <c r="F15" s="48"/>
-      <c r="G15" s="109" t="s">
-        <v>86</v>
+      <c r="G15" s="70" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="16" spans="2:11">
-      <c r="B16" s="101" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="102"/>
+      <c r="B16" s="99" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="100"/>
       <c r="D16" s="8"/>
       <c r="E16" s="45">
         <v>3</v>
       </c>
       <c r="F16" s="45"/>
       <c r="G16" s="63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="101" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="102"/>
+      <c r="B17" s="99" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="100"/>
       <c r="D17" s="8"/>
       <c r="E17" s="45">
         <v>3</v>
       </c>
       <c r="F17" s="45"/>
       <c r="G17" s="63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="101" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="102"/>
+      <c r="B18" s="99" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="100"/>
       <c r="D18" s="8"/>
       <c r="E18" s="45">
         <v>3</v>
       </c>
       <c r="F18" s="45"/>
       <c r="G18" s="63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="101" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="102"/>
+      <c r="B19" s="99" t="s">
+        <v>50</v>
+      </c>
+      <c r="C19" s="100"/>
       <c r="D19" s="10"/>
       <c r="E19" s="45">
         <v>3</v>
       </c>
       <c r="F19" s="45"/>
       <c r="G19" s="63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="101" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="102"/>
+      <c r="B20" s="99" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="100"/>
       <c r="D20" s="8"/>
       <c r="E20" s="50">
         <v>1</v>
       </c>
       <c r="F20" s="49"/>
       <c r="G20" s="63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="103" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="104"/>
+      <c r="B21" s="113" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="114"/>
       <c r="D21" s="8"/>
       <c r="E21" s="45"/>
       <c r="F21" s="45"/>
       <c r="G21" s="63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="68" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="69"/>
+      <c r="B22" s="95" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="96"/>
       <c r="D22" s="8"/>
       <c r="E22" s="45">
         <v>1</v>
       </c>
       <c r="F22" s="45"/>
       <c r="G22" s="63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="68" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="69"/>
+      <c r="B23" s="95" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="96"/>
       <c r="D23" s="8"/>
       <c r="E23" s="45">
         <v>1</v>
       </c>
       <c r="F23" s="45"/>
       <c r="G23" s="63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B24" s="82" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="83"/>
+      <c r="B24" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="98"/>
       <c r="D24" s="9"/>
       <c r="E24" s="47">
         <v>1</v>
       </c>
       <c r="F24" s="47"/>
       <c r="G24" s="65" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="2:7">
-      <c r="B25" s="70" t="s">
+      <c r="B25" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="71"/>
+      <c r="C25" s="116"/>
       <c r="D25" s="58" t="s">
         <v>10</v>
       </c>
@@ -2337,219 +2357,242 @@
         <v>12</v>
       </c>
       <c r="F25" s="59"/>
-      <c r="G25" s="109" t="s">
-        <v>86</v>
+      <c r="G25" s="70" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="2:7">
-      <c r="B26" s="103" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="104"/>
+      <c r="B26" s="113" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="114"/>
       <c r="D26" s="8"/>
       <c r="E26" s="45">
         <v>5</v>
       </c>
       <c r="F26" s="45"/>
       <c r="G26" s="63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="103" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="104"/>
+      <c r="B27" s="113" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="114"/>
       <c r="D27" s="8"/>
       <c r="E27" s="45"/>
       <c r="F27" s="45"/>
       <c r="G27" s="63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="68" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="69"/>
+      <c r="B28" s="95" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="96"/>
       <c r="D28" s="8"/>
       <c r="E28" s="45">
         <v>2</v>
       </c>
       <c r="F28" s="45"/>
       <c r="G28" s="63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="68" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="69"/>
+      <c r="B29" s="95" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="96"/>
       <c r="D29" s="8"/>
       <c r="E29" s="45">
         <v>2</v>
       </c>
       <c r="F29" s="45"/>
       <c r="G29" s="63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B30" s="105" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="106"/>
+      <c r="B30" s="89" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="90"/>
       <c r="D30" s="9"/>
       <c r="E30" s="47">
         <v>3</v>
       </c>
       <c r="F30" s="47"/>
       <c r="G30" s="65" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="2:7">
-      <c r="B31" s="76" t="s">
-        <v>63</v>
-      </c>
-      <c r="C31" s="77"/>
+      <c r="B31" s="101" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="102"/>
       <c r="D31" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="126">
+      <c r="E31" s="86">
         <f>SUM(E32:E39)</f>
         <v>11</v>
       </c>
       <c r="F31" s="48"/>
-      <c r="G31" s="109" t="s">
-        <v>86</v>
+      <c r="G31" s="70" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="2:7">
-      <c r="B32" s="101" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" s="102"/>
+      <c r="B32" s="99" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="100"/>
       <c r="D32" s="11"/>
       <c r="E32" s="54"/>
       <c r="F32" s="49"/>
       <c r="G32" s="63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="66" t="s">
-        <v>59</v>
-      </c>
-      <c r="C33" s="67"/>
+      <c r="B33" s="91" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="92"/>
       <c r="D33" s="11"/>
       <c r="E33" s="54">
         <v>2</v>
       </c>
       <c r="F33" s="49"/>
       <c r="G33" s="63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="86" t="s">
+      <c r="B34" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="87"/>
+      <c r="C34" s="104"/>
       <c r="D34" s="8"/>
       <c r="E34" s="44"/>
       <c r="F34" s="45"/>
       <c r="G34" s="63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="101" t="s">
-        <v>60</v>
-      </c>
-      <c r="C35" s="102"/>
+      <c r="B35" s="99" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="100"/>
       <c r="D35" s="8"/>
       <c r="E35" s="44">
         <v>2</v>
       </c>
       <c r="F35" s="45"/>
       <c r="G35" s="63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="101" t="s">
-        <v>61</v>
-      </c>
-      <c r="C36" s="102"/>
+      <c r="B36" s="99" t="s">
+        <v>60</v>
+      </c>
+      <c r="C36" s="100"/>
       <c r="D36" s="8"/>
       <c r="E36" s="44">
         <v>2</v>
       </c>
       <c r="F36" s="45"/>
       <c r="G36" s="63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="86" t="s">
+      <c r="B37" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="87"/>
+      <c r="C37" s="104"/>
       <c r="D37" s="8"/>
       <c r="E37" s="44"/>
       <c r="F37" s="45"/>
       <c r="G37" s="63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="107" t="s">
-        <v>64</v>
-      </c>
-      <c r="C38" s="108"/>
+      <c r="B38" s="105" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" s="106"/>
       <c r="D38" s="8"/>
       <c r="E38" s="44">
         <v>2</v>
       </c>
       <c r="F38" s="45"/>
       <c r="G38" s="63" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B39" s="105" t="s">
-        <v>65</v>
-      </c>
-      <c r="C39" s="106"/>
+      <c r="B39" s="89" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" s="90"/>
       <c r="D39" s="9"/>
       <c r="E39" s="51">
         <v>3</v>
       </c>
       <c r="F39" s="47"/>
       <c r="G39" s="65" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B40" s="90" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" s="91"/>
+      <c r="B40" s="87" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="88"/>
       <c r="D40" s="56"/>
-      <c r="E40" s="124">
+      <c r="E40" s="84">
         <f>SUM(E3+E15+E25+F31)</f>
         <v>41</v>
       </c>
-      <c r="F40" s="125">
+      <c r="F40" s="85">
         <f>SUM(F4:F39)</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G40" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B13:C13"/>
@@ -2566,29 +2609,6 @@
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2606,10 +2626,10 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="72" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" s="73"/>
+      <c r="B2" s="107" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="108"/>
       <c r="D2" s="55" t="s">
         <v>9</v>
       </c>
@@ -2621,10 +2641,10 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="74" t="s">
+      <c r="B3" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="75"/>
+      <c r="C3" s="110"/>
       <c r="D3" s="55" t="s">
         <v>12</v>
       </c>
@@ -2632,10 +2652,10 @@
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="78" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" s="79"/>
+      <c r="B4" s="123" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="124"/>
       <c r="D4" s="7"/>
       <c r="E4" s="48">
         <v>2</v>
@@ -2643,10 +2663,10 @@
       <c r="F4" s="48"/>
     </row>
     <row r="5" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B5" s="66" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="67"/>
+      <c r="B5" s="91" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="92"/>
       <c r="D5" s="8"/>
       <c r="E5" s="45">
         <v>2</v>
@@ -2654,10 +2674,10 @@
       <c r="F5" s="45"/>
     </row>
     <row r="6" spans="2:6">
-      <c r="B6" s="76" t="s">
+      <c r="B6" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="77"/>
+      <c r="C6" s="102"/>
       <c r="D6" s="7" t="s">
         <v>11</v>
       </c>
@@ -2665,10 +2685,10 @@
       <c r="F6" s="48"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="66" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" s="67"/>
+      <c r="B7" s="91" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="92"/>
       <c r="D7" s="8"/>
       <c r="E7" s="45">
         <v>2</v>
@@ -2676,10 +2696,10 @@
       <c r="F7" s="45"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="66" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="67"/>
+      <c r="B8" s="91" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="92"/>
       <c r="D8" s="8"/>
       <c r="E8" s="45">
         <v>3</v>
@@ -2687,10 +2707,10 @@
       <c r="F8" s="45"/>
     </row>
     <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="66" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="67"/>
+      <c r="B9" s="91" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="92"/>
       <c r="D9" s="8"/>
       <c r="E9" s="45">
         <v>2</v>
@@ -2698,10 +2718,10 @@
       <c r="F9" s="45"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="70" t="s">
+      <c r="B10" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="71"/>
+      <c r="C10" s="116"/>
       <c r="D10" s="58" t="s">
         <v>10</v>
       </c>
@@ -2709,10 +2729,10 @@
       <c r="F10" s="59"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="68" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="69"/>
+      <c r="B11" s="95" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="96"/>
       <c r="D11" s="8"/>
       <c r="E11" s="45">
         <v>5</v>
@@ -2720,10 +2740,10 @@
       <c r="F11" s="45"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="68" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" s="69"/>
+      <c r="B12" s="95" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="96"/>
       <c r="D12" s="8"/>
       <c r="E12" s="45">
         <v>1</v>
@@ -2731,10 +2751,10 @@
       <c r="F12" s="45"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="68" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" s="69"/>
+      <c r="B13" s="95" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="96"/>
       <c r="D13" s="8"/>
       <c r="E13" s="45">
         <v>2</v>
@@ -2742,10 +2762,10 @@
       <c r="F13" s="45"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="84" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="85"/>
+      <c r="B14" s="121" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="122"/>
       <c r="D14" s="11" t="s">
         <v>14</v>
       </c>
@@ -2753,10 +2773,10 @@
       <c r="F14" s="49"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="66" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" s="67"/>
+      <c r="B15" s="91" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="92"/>
       <c r="D15" s="11"/>
       <c r="E15" s="54">
         <v>5</v>
@@ -2764,19 +2784,19 @@
       <c r="F15" s="49"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="86" t="s">
+      <c r="B16" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="87"/>
+      <c r="C16" s="104"/>
       <c r="D16" s="8"/>
       <c r="E16" s="44"/>
       <c r="F16" s="45"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="66" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="67"/>
+      <c r="B17" s="91" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="92"/>
       <c r="D17" s="8"/>
       <c r="E17" s="44">
         <v>2</v>
@@ -2784,19 +2804,19 @@
       <c r="F17" s="45"/>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="86" t="s">
+      <c r="B18" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="87"/>
+      <c r="C18" s="104"/>
       <c r="D18" s="8"/>
       <c r="E18" s="44"/>
       <c r="F18" s="45"/>
     </row>
     <row r="19" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B19" s="88" t="s">
-        <v>70</v>
-      </c>
-      <c r="C19" s="89"/>
+      <c r="B19" s="117" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="118"/>
       <c r="D19" s="8"/>
       <c r="E19" s="44">
         <v>2</v>
@@ -2804,27 +2824,16 @@
       <c r="F19" s="45"/>
     </row>
     <row r="20" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B20" s="80" t="s">
+      <c r="B20" s="119" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="81"/>
+      <c r="C20" s="120"/>
       <c r="D20" s="12"/>
       <c r="E20" s="52"/>
       <c r="F20" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
@@ -2833,6 +2842,17 @@
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2846,10 +2866,10 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="72" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" s="73"/>
+      <c r="B2" s="107" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="108"/>
       <c r="D2" s="55" t="s">
         <v>9</v>
       </c>
@@ -2861,10 +2881,10 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="74" t="s">
+      <c r="B3" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="75"/>
+      <c r="C3" s="110"/>
       <c r="D3" s="55" t="s">
         <v>12</v>
       </c>
@@ -2872,10 +2892,10 @@
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B4" s="78" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" s="79"/>
+      <c r="B4" s="123" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="124"/>
       <c r="D4" s="7"/>
       <c r="E4" s="48">
         <v>3</v>
@@ -2883,10 +2903,10 @@
       <c r="F4" s="48"/>
     </row>
     <row r="5" spans="2:6">
-      <c r="B5" s="76" t="s">
+      <c r="B5" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="77"/>
+      <c r="C5" s="102"/>
       <c r="D5" s="7" t="s">
         <v>11</v>
       </c>
@@ -2894,10 +2914,10 @@
       <c r="F5" s="48"/>
     </row>
     <row r="6" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B6" s="66" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="67"/>
+      <c r="B6" s="91" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="92"/>
       <c r="D6" s="8"/>
       <c r="E6" s="45">
         <v>3</v>
@@ -2905,10 +2925,10 @@
       <c r="F6" s="45"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="70" t="s">
+      <c r="B7" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="71"/>
+      <c r="C7" s="116"/>
       <c r="D7" s="58" t="s">
         <v>10</v>
       </c>
@@ -2916,10 +2936,10 @@
       <c r="F7" s="59"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="68" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="69"/>
+      <c r="B8" s="95" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="96"/>
       <c r="D8" s="8"/>
       <c r="E8" s="45">
         <v>3</v>
@@ -2927,10 +2947,10 @@
       <c r="F8" s="45"/>
     </row>
     <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="66" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" s="67"/>
+      <c r="B9" s="91" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="92"/>
       <c r="D9" s="8"/>
       <c r="E9" s="45">
         <v>2</v>
@@ -2938,10 +2958,10 @@
       <c r="F9" s="45"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="76" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="77"/>
+      <c r="B10" s="101" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="102"/>
       <c r="D10" s="7" t="s">
         <v>14</v>
       </c>
@@ -2949,10 +2969,10 @@
       <c r="F10" s="48"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="66" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" s="67"/>
+      <c r="B11" s="91" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="92"/>
       <c r="D11" s="11"/>
       <c r="E11" s="49">
         <v>2</v>
@@ -2960,19 +2980,19 @@
       <c r="F11" s="49"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="86" t="s">
+      <c r="B12" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="87"/>
+      <c r="C12" s="104"/>
       <c r="D12" s="8"/>
       <c r="E12" s="45"/>
       <c r="F12" s="45"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="66" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" s="67"/>
+      <c r="B13" s="91" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="92"/>
       <c r="D13" s="8"/>
       <c r="E13" s="45">
         <v>1</v>
@@ -2980,10 +3000,10 @@
       <c r="F13" s="45"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="66" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" s="67"/>
+      <c r="B14" s="91" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="92"/>
       <c r="D14" s="8"/>
       <c r="E14" s="45">
         <v>1</v>
@@ -2991,19 +3011,19 @@
       <c r="F14" s="45"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="86" t="s">
+      <c r="B15" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="87"/>
+      <c r="C15" s="104"/>
       <c r="D15" s="8"/>
       <c r="E15" s="45"/>
       <c r="F15" s="45"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="68" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="69"/>
+      <c r="B16" s="95" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="96"/>
       <c r="D16" s="8"/>
       <c r="E16" s="45">
         <v>1</v>
@@ -3011,10 +3031,10 @@
       <c r="F16" s="45"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="68" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" s="69"/>
+      <c r="B17" s="95" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="96"/>
       <c r="D17" s="8"/>
       <c r="E17" s="45">
         <v>1</v>
@@ -3022,16 +3042,26 @@
       <c r="F17" s="45"/>
     </row>
     <row r="18" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B18" s="90" t="s">
+      <c r="B18" s="87" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="91"/>
+      <c r="C18" s="88"/>
       <c r="D18" s="56"/>
       <c r="E18" s="57"/>
       <c r="F18" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B11:C11"/>
@@ -3039,16 +3069,6 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3061,13 +3081,13 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="92" t="s">
+      <c r="C1" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="125"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
     </row>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
       <c r="B2" s="34" t="s">
@@ -3317,13 +3337,13 @@
         <f t="shared" si="7"/>
         <v>46311</v>
       </c>
-      <c r="H10" s="95">
+      <c r="H10" s="67">
         <f>SUM(G10)+1</f>
         <v>46312</v>
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="94">
+      <c r="B11" s="66">
         <f t="shared" si="6"/>
         <v>46313</v>
       </c>
@@ -3331,15 +3351,15 @@
         <f>SUM(B11)+1</f>
         <v>46314</v>
       </c>
-      <c r="D11" s="93">
+      <c r="D11" s="13">
         <f t="shared" ref="D11:F11" si="8">SUM(C11)+1</f>
         <v>46315</v>
       </c>
-      <c r="E11" s="93">
+      <c r="E11" s="13">
         <f t="shared" si="8"/>
         <v>46316</v>
       </c>
-      <c r="F11" s="93">
+      <c r="F11" s="13">
         <f t="shared" si="8"/>
         <v>46317</v>
       </c>

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\Documents\GitHub\GlassesGame\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ayato Terao\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA0A265-64C4-4A5E-A49B-D64CD1D06AC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D92DA032-F98F-4DA3-B34F-3F89C25017C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1337,7 +1337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1471,9 +1471,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1525,6 +1522,60 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1537,42 +1588,18 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1585,34 +1612,16 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1625,18 +1634,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1948,10 +1945,10 @@
   <sheetData>
     <row r="1" spans="2:11" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="94" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="108"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="55" t="s">
         <v>9</v>
       </c>
@@ -1966,10 +1963,10 @@
       </c>
     </row>
     <row r="3" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B3" s="109" t="s">
+      <c r="B3" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="110"/>
+      <c r="C3" s="97"/>
       <c r="D3" s="55" t="s">
         <v>12</v>
       </c>
@@ -1979,49 +1976,49 @@
       </c>
       <c r="F3" s="53">
         <f>SUM(F4:F14)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G3" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="I3" s="74" t="s">
+      <c r="I3" s="73" t="s">
         <v>79</v>
       </c>
-      <c r="J3" s="78">
+      <c r="J3" s="77">
         <f ca="1">TODAY()</f>
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="K3" s="55" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="111" t="s">
+      <c r="B4" s="100" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="112"/>
+      <c r="C4" s="101"/>
       <c r="D4" s="11"/>
       <c r="E4" s="49"/>
       <c r="F4" s="49"/>
       <c r="G4" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="I4" s="79" t="s">
+      <c r="I4" s="78" t="s">
         <v>80</v>
       </c>
-      <c r="J4" s="75">
+      <c r="J4" s="74">
         <v>46295</v>
       </c>
-      <c r="K4" s="73" t="str">
+      <c r="K4" s="72" t="str">
         <f ca="1">SUM($J4-J3)&amp; "日"</f>
-        <v>7日</v>
+        <v>6日</v>
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="91" t="s">
+      <c r="B5" s="102" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="92"/>
+      <c r="C5" s="103"/>
       <c r="D5" s="8"/>
       <c r="E5" s="45">
         <v>2</v>
@@ -2032,22 +2029,22 @@
       <c r="G5" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="I5" s="80" t="s">
+      <c r="I5" s="79" t="s">
         <v>81</v>
       </c>
-      <c r="J5" s="76">
+      <c r="J5" s="75">
         <v>46305</v>
       </c>
-      <c r="K5" s="71" t="str">
+      <c r="K5" s="70" t="str">
         <f ca="1">SUM($J5-J3)&amp; "日"</f>
-        <v>17日</v>
+        <v>16日</v>
       </c>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" s="91" t="s">
+      <c r="B6" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="92"/>
+      <c r="C6" s="103"/>
       <c r="D6" s="8"/>
       <c r="E6" s="45">
         <v>1</v>
@@ -2058,22 +2055,22 @@
       <c r="G6" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="I6" s="81" t="s">
+      <c r="I6" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="J6" s="76">
+      <c r="J6" s="75">
         <v>46310</v>
       </c>
-      <c r="K6" s="71" t="str">
+      <c r="K6" s="70" t="str">
         <f ca="1">SUM($J6-J3)&amp; "日"</f>
-        <v>22日</v>
+        <v>21日</v>
       </c>
     </row>
     <row r="7" spans="2:11">
-      <c r="B7" s="99" t="s">
+      <c r="B7" s="86" t="s">
         <v>90</v>
       </c>
-      <c r="C7" s="100"/>
+      <c r="C7" s="87"/>
       <c r="D7" s="8"/>
       <c r="E7" s="45">
         <v>2</v>
@@ -2084,22 +2081,22 @@
       <c r="G7" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="I7" s="82" t="s">
+      <c r="I7" s="81" t="s">
         <v>83</v>
       </c>
-      <c r="J7" s="76">
+      <c r="J7" s="75">
         <v>46313</v>
       </c>
-      <c r="K7" s="71" t="str">
+      <c r="K7" s="70" t="str">
         <f ca="1">SUM($J7-J3)&amp; "日"</f>
-        <v>25日</v>
+        <v>24日</v>
       </c>
     </row>
     <row r="8" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B8" s="99" t="s">
+      <c r="B8" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="100"/>
+      <c r="C8" s="87"/>
       <c r="D8" s="10"/>
       <c r="E8" s="46">
         <v>2</v>
@@ -2108,22 +2105,22 @@
       <c r="G8" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="I8" s="83" t="s">
+      <c r="I8" s="82" t="s">
         <v>78</v>
       </c>
-      <c r="J8" s="77">
+      <c r="J8" s="76">
         <v>46314</v>
       </c>
-      <c r="K8" s="72" t="str">
+      <c r="K8" s="71" t="str">
         <f ca="1">SUM(J8-J3)&amp; "日"</f>
-        <v>26日</v>
+        <v>25日</v>
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="99" t="s">
+      <c r="B9" s="86" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="100"/>
+      <c r="C9" s="87"/>
       <c r="D9" s="10"/>
       <c r="E9" s="46">
         <v>2</v>
@@ -2134,10 +2131,10 @@
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="113" t="s">
+      <c r="B10" s="90" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="114"/>
+      <c r="C10" s="91"/>
       <c r="D10" s="8"/>
       <c r="E10" s="45">
         <v>1</v>
@@ -2150,64 +2147,70 @@
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="99" t="s">
+      <c r="B11" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="100"/>
+      <c r="C11" s="87"/>
       <c r="D11" s="8"/>
       <c r="E11" s="45"/>
       <c r="F11" s="46"/>
       <c r="G11" s="63" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="2:11">
-      <c r="B12" s="95" t="s">
+      <c r="B12" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="96"/>
+      <c r="C12" s="89"/>
       <c r="D12" s="8"/>
       <c r="E12" s="45">
         <v>1</v>
       </c>
-      <c r="F12" s="45"/>
+      <c r="F12" s="45">
+        <v>1</v>
+      </c>
       <c r="G12" s="63" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="2:11">
-      <c r="B13" s="91" t="s">
+      <c r="B13" s="102" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="92"/>
+      <c r="C13" s="103"/>
       <c r="D13" s="8"/>
       <c r="E13" s="45">
         <v>1</v>
       </c>
-      <c r="F13" s="45"/>
+      <c r="F13" s="45">
+        <v>1</v>
+      </c>
       <c r="G13" s="63" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B14" s="93" t="s">
+      <c r="B14" s="108" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="94"/>
+      <c r="C14" s="109"/>
       <c r="D14" s="10"/>
       <c r="E14" s="46">
         <v>1</v>
       </c>
-      <c r="F14" s="46"/>
-      <c r="G14" s="69" t="s">
-        <v>85</v>
+      <c r="F14" s="46">
+        <v>1</v>
+      </c>
+      <c r="G14" s="63" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="2:11">
-      <c r="B15" s="101" t="s">
+      <c r="B15" s="98" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="102"/>
+      <c r="C15" s="99"/>
       <c r="D15" s="7" t="s">
         <v>11</v>
       </c>
@@ -2216,15 +2219,15 @@
         <v>16</v>
       </c>
       <c r="F15" s="48"/>
-      <c r="G15" s="70" t="s">
+      <c r="G15" s="69" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="16" spans="2:11">
-      <c r="B16" s="99" t="s">
+      <c r="B16" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="100"/>
+      <c r="C16" s="87"/>
       <c r="D16" s="8"/>
       <c r="E16" s="45">
         <v>3</v>
@@ -2235,10 +2238,10 @@
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="99" t="s">
+      <c r="B17" s="86" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="100"/>
+      <c r="C17" s="87"/>
       <c r="D17" s="8"/>
       <c r="E17" s="45">
         <v>3</v>
@@ -2249,24 +2252,26 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="99" t="s">
+      <c r="B18" s="86" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="100"/>
+      <c r="C18" s="87"/>
       <c r="D18" s="8"/>
       <c r="E18" s="45">
         <v>3</v>
       </c>
-      <c r="F18" s="45"/>
+      <c r="F18" s="45">
+        <v>1</v>
+      </c>
       <c r="G18" s="63" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="99" t="s">
+      <c r="B19" s="86" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="100"/>
+      <c r="C19" s="87"/>
       <c r="D19" s="10"/>
       <c r="E19" s="45">
         <v>3</v>
@@ -2277,10 +2282,10 @@
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="99" t="s">
+      <c r="B20" s="86" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="100"/>
+      <c r="C20" s="87"/>
       <c r="D20" s="8"/>
       <c r="E20" s="50">
         <v>1</v>
@@ -2291,64 +2296,70 @@
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="113" t="s">
+      <c r="B21" s="90" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="114"/>
+      <c r="C21" s="91"/>
       <c r="D21" s="8"/>
       <c r="E21" s="45"/>
       <c r="F21" s="45"/>
       <c r="G21" s="63" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="95" t="s">
+      <c r="B22" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="96"/>
+      <c r="C22" s="89"/>
       <c r="D22" s="8"/>
       <c r="E22" s="45">
         <v>1</v>
       </c>
-      <c r="F22" s="45"/>
+      <c r="F22" s="45">
+        <v>1</v>
+      </c>
       <c r="G22" s="63" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="95" t="s">
+      <c r="B23" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="96"/>
+      <c r="C23" s="89"/>
       <c r="D23" s="8"/>
       <c r="E23" s="45">
         <v>1</v>
       </c>
-      <c r="F23" s="45"/>
+      <c r="F23" s="45">
+        <v>1</v>
+      </c>
       <c r="G23" s="63" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B24" s="97" t="s">
+      <c r="B24" s="110" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="98"/>
+      <c r="C24" s="111"/>
       <c r="D24" s="9"/>
       <c r="E24" s="47">
         <v>1</v>
       </c>
-      <c r="F24" s="47"/>
-      <c r="G24" s="65" t="s">
-        <v>85</v>
+      <c r="F24" s="47">
+        <v>1</v>
+      </c>
+      <c r="G24" s="63" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="2:7">
-      <c r="B25" s="115" t="s">
+      <c r="B25" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="116"/>
+      <c r="C25" s="93"/>
       <c r="D25" s="58" t="s">
         <v>10</v>
       </c>
@@ -2357,15 +2368,15 @@
         <v>12</v>
       </c>
       <c r="F25" s="59"/>
-      <c r="G25" s="70" t="s">
+      <c r="G25" s="69" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="26" spans="2:7">
-      <c r="B26" s="113" t="s">
+      <c r="B26" s="90" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="114"/>
+      <c r="C26" s="91"/>
       <c r="D26" s="8"/>
       <c r="E26" s="45">
         <v>5</v>
@@ -2376,10 +2387,10 @@
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="113" t="s">
+      <c r="B27" s="90" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="114"/>
+      <c r="C27" s="91"/>
       <c r="D27" s="8"/>
       <c r="E27" s="45"/>
       <c r="F27" s="45"/>
@@ -2388,10 +2399,10 @@
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="95" t="s">
+      <c r="B28" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="96"/>
+      <c r="C28" s="89"/>
       <c r="D28" s="8"/>
       <c r="E28" s="45">
         <v>2</v>
@@ -2402,10 +2413,10 @@
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="95" t="s">
+      <c r="B29" s="88" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="96"/>
+      <c r="C29" s="89"/>
       <c r="D29" s="8"/>
       <c r="E29" s="45">
         <v>2</v>
@@ -2416,10 +2427,10 @@
       </c>
     </row>
     <row r="30" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B30" s="89" t="s">
+      <c r="B30" s="106" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="90"/>
+      <c r="C30" s="107"/>
       <c r="D30" s="9"/>
       <c r="E30" s="47">
         <v>3</v>
@@ -2430,27 +2441,27 @@
       </c>
     </row>
     <row r="31" spans="2:7">
-      <c r="B31" s="101" t="s">
+      <c r="B31" s="98" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="102"/>
+      <c r="C31" s="99"/>
       <c r="D31" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="86">
+      <c r="E31" s="85">
         <f>SUM(E32:E39)</f>
         <v>11</v>
       </c>
       <c r="F31" s="48"/>
-      <c r="G31" s="70" t="s">
+      <c r="G31" s="69" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="32" spans="2:7">
-      <c r="B32" s="99" t="s">
+      <c r="B32" s="86" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="100"/>
+      <c r="C32" s="87"/>
       <c r="D32" s="11"/>
       <c r="E32" s="54"/>
       <c r="F32" s="49"/>
@@ -2459,10 +2470,10 @@
       </c>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="91" t="s">
+      <c r="B33" s="102" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="92"/>
+      <c r="C33" s="103"/>
       <c r="D33" s="11"/>
       <c r="E33" s="54">
         <v>2</v>
@@ -2473,10 +2484,10 @@
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="103" t="s">
+      <c r="B34" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="104"/>
+      <c r="C34" s="113"/>
       <c r="D34" s="8"/>
       <c r="E34" s="44"/>
       <c r="F34" s="45"/>
@@ -2485,10 +2496,10 @@
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="99" t="s">
+      <c r="B35" s="86" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="100"/>
+      <c r="C35" s="87"/>
       <c r="D35" s="8"/>
       <c r="E35" s="44">
         <v>2</v>
@@ -2499,10 +2510,10 @@
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="99" t="s">
+      <c r="B36" s="86" t="s">
         <v>60</v>
       </c>
-      <c r="C36" s="100"/>
+      <c r="C36" s="87"/>
       <c r="D36" s="8"/>
       <c r="E36" s="44">
         <v>2</v>
@@ -2513,10 +2524,10 @@
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="103" t="s">
+      <c r="B37" s="112" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="104"/>
+      <c r="C37" s="113"/>
       <c r="D37" s="8"/>
       <c r="E37" s="44"/>
       <c r="F37" s="45"/>
@@ -2525,10 +2536,10 @@
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="105" t="s">
+      <c r="B38" s="114" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="106"/>
+      <c r="C38" s="115"/>
       <c r="D38" s="8"/>
       <c r="E38" s="44">
         <v>2</v>
@@ -2539,10 +2550,10 @@
       </c>
     </row>
     <row r="39" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B39" s="89" t="s">
+      <c r="B39" s="106" t="s">
         <v>64</v>
       </c>
-      <c r="C39" s="90"/>
+      <c r="C39" s="107"/>
       <c r="D39" s="9"/>
       <c r="E39" s="51">
         <v>3</v>
@@ -2553,46 +2564,23 @@
       </c>
     </row>
     <row r="40" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B40" s="87" t="s">
+      <c r="B40" s="104" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="88"/>
+      <c r="C40" s="105"/>
       <c r="D40" s="56"/>
-      <c r="E40" s="84">
+      <c r="E40" s="83">
         <f>SUM(E3+E15+E25+F31)</f>
         <v>41</v>
       </c>
-      <c r="F40" s="85">
+      <c r="F40" s="84">
         <f>SUM(F4:F39)</f>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G40" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B13:C13"/>
@@ -2609,6 +2597,29 @@
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2626,10 +2637,10 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="94" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="108"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="55" t="s">
         <v>9</v>
       </c>
@@ -2641,10 +2652,10 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="109" t="s">
+      <c r="B3" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="110"/>
+      <c r="C3" s="97"/>
       <c r="D3" s="55" t="s">
         <v>12</v>
       </c>
@@ -2652,10 +2663,10 @@
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="123" t="s">
+      <c r="B4" s="116" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="124"/>
+      <c r="C4" s="117"/>
       <c r="D4" s="7"/>
       <c r="E4" s="48">
         <v>2</v>
@@ -2663,10 +2674,10 @@
       <c r="F4" s="48"/>
     </row>
     <row r="5" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B5" s="91" t="s">
+      <c r="B5" s="102" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="92"/>
+      <c r="C5" s="103"/>
       <c r="D5" s="8"/>
       <c r="E5" s="45">
         <v>2</v>
@@ -2674,10 +2685,10 @@
       <c r="F5" s="45"/>
     </row>
     <row r="6" spans="2:6">
-      <c r="B6" s="101" t="s">
+      <c r="B6" s="98" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="102"/>
+      <c r="C6" s="99"/>
       <c r="D6" s="7" t="s">
         <v>11</v>
       </c>
@@ -2685,10 +2696,10 @@
       <c r="F6" s="48"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="91" t="s">
+      <c r="B7" s="102" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="92"/>
+      <c r="C7" s="103"/>
       <c r="D7" s="8"/>
       <c r="E7" s="45">
         <v>2</v>
@@ -2696,10 +2707,10 @@
       <c r="F7" s="45"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="91" t="s">
+      <c r="B8" s="102" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="92"/>
+      <c r="C8" s="103"/>
       <c r="D8" s="8"/>
       <c r="E8" s="45">
         <v>3</v>
@@ -2707,10 +2718,10 @@
       <c r="F8" s="45"/>
     </row>
     <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="91" t="s">
+      <c r="B9" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="92"/>
+      <c r="C9" s="103"/>
       <c r="D9" s="8"/>
       <c r="E9" s="45">
         <v>2</v>
@@ -2718,10 +2729,10 @@
       <c r="F9" s="45"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="115" t="s">
+      <c r="B10" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="116"/>
+      <c r="C10" s="93"/>
       <c r="D10" s="58" t="s">
         <v>10</v>
       </c>
@@ -2729,10 +2740,10 @@
       <c r="F10" s="59"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="95" t="s">
+      <c r="B11" s="88" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="96"/>
+      <c r="C11" s="89"/>
       <c r="D11" s="8"/>
       <c r="E11" s="45">
         <v>5</v>
@@ -2740,10 +2751,10 @@
       <c r="F11" s="45"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="95" t="s">
+      <c r="B12" s="88" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="96"/>
+      <c r="C12" s="89"/>
       <c r="D12" s="8"/>
       <c r="E12" s="45">
         <v>1</v>
@@ -2751,10 +2762,10 @@
       <c r="F12" s="45"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="95" t="s">
+      <c r="B13" s="88" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="96"/>
+      <c r="C13" s="89"/>
       <c r="D13" s="8"/>
       <c r="E13" s="45">
         <v>2</v>
@@ -2762,10 +2773,10 @@
       <c r="F13" s="45"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="121" t="s">
+      <c r="B14" s="118" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="122"/>
+      <c r="C14" s="119"/>
       <c r="D14" s="11" t="s">
         <v>14</v>
       </c>
@@ -2773,10 +2784,10 @@
       <c r="F14" s="49"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="91" t="s">
+      <c r="B15" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="92"/>
+      <c r="C15" s="103"/>
       <c r="D15" s="11"/>
       <c r="E15" s="54">
         <v>5</v>
@@ -2784,19 +2795,19 @@
       <c r="F15" s="49"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="103" t="s">
+      <c r="B16" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="104"/>
+      <c r="C16" s="113"/>
       <c r="D16" s="8"/>
       <c r="E16" s="44"/>
       <c r="F16" s="45"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="91" t="s">
+      <c r="B17" s="102" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="92"/>
+      <c r="C17" s="103"/>
       <c r="D17" s="8"/>
       <c r="E17" s="44">
         <v>2</v>
@@ -2804,19 +2815,19 @@
       <c r="F17" s="45"/>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="103" t="s">
+      <c r="B18" s="112" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="104"/>
+      <c r="C18" s="113"/>
       <c r="D18" s="8"/>
       <c r="E18" s="44"/>
       <c r="F18" s="45"/>
     </row>
     <row r="19" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B19" s="117" t="s">
+      <c r="B19" s="120" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="118"/>
+      <c r="C19" s="121"/>
       <c r="D19" s="8"/>
       <c r="E19" s="44">
         <v>2</v>
@@ -2824,16 +2835,27 @@
       <c r="F19" s="45"/>
     </row>
     <row r="20" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B20" s="119" t="s">
+      <c r="B20" s="122" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="120"/>
+      <c r="C20" s="123"/>
       <c r="D20" s="12"/>
       <c r="E20" s="52"/>
       <c r="F20" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
@@ -2842,17 +2864,6 @@
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2866,10 +2877,10 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="94" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="108"/>
+      <c r="C2" s="95"/>
       <c r="D2" s="55" t="s">
         <v>9</v>
       </c>
@@ -2881,10 +2892,10 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="109" t="s">
+      <c r="B3" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="110"/>
+      <c r="C3" s="97"/>
       <c r="D3" s="55" t="s">
         <v>12</v>
       </c>
@@ -2892,10 +2903,10 @@
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B4" s="123" t="s">
+      <c r="B4" s="116" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="124"/>
+      <c r="C4" s="117"/>
       <c r="D4" s="7"/>
       <c r="E4" s="48">
         <v>3</v>
@@ -2903,10 +2914,10 @@
       <c r="F4" s="48"/>
     </row>
     <row r="5" spans="2:6">
-      <c r="B5" s="101" t="s">
+      <c r="B5" s="98" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="102"/>
+      <c r="C5" s="99"/>
       <c r="D5" s="7" t="s">
         <v>11</v>
       </c>
@@ -2914,10 +2925,10 @@
       <c r="F5" s="48"/>
     </row>
     <row r="6" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B6" s="91" t="s">
+      <c r="B6" s="102" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="92"/>
+      <c r="C6" s="103"/>
       <c r="D6" s="8"/>
       <c r="E6" s="45">
         <v>3</v>
@@ -2925,10 +2936,10 @@
       <c r="F6" s="45"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="115" t="s">
+      <c r="B7" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="116"/>
+      <c r="C7" s="93"/>
       <c r="D7" s="58" t="s">
         <v>10</v>
       </c>
@@ -2936,10 +2947,10 @@
       <c r="F7" s="59"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="95" t="s">
+      <c r="B8" s="88" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="96"/>
+      <c r="C8" s="89"/>
       <c r="D8" s="8"/>
       <c r="E8" s="45">
         <v>3</v>
@@ -2947,10 +2958,10 @@
       <c r="F8" s="45"/>
     </row>
     <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="91" t="s">
+      <c r="B9" s="102" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="92"/>
+      <c r="C9" s="103"/>
       <c r="D9" s="8"/>
       <c r="E9" s="45">
         <v>2</v>
@@ -2958,10 +2969,10 @@
       <c r="F9" s="45"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="101" t="s">
+      <c r="B10" s="98" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="102"/>
+      <c r="C10" s="99"/>
       <c r="D10" s="7" t="s">
         <v>14</v>
       </c>
@@ -2969,10 +2980,10 @@
       <c r="F10" s="48"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="91" t="s">
+      <c r="B11" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="92"/>
+      <c r="C11" s="103"/>
       <c r="D11" s="11"/>
       <c r="E11" s="49">
         <v>2</v>
@@ -2980,19 +2991,19 @@
       <c r="F11" s="49"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="103" t="s">
+      <c r="B12" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="104"/>
+      <c r="C12" s="113"/>
       <c r="D12" s="8"/>
       <c r="E12" s="45"/>
       <c r="F12" s="45"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="91" t="s">
+      <c r="B13" s="102" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="92"/>
+      <c r="C13" s="103"/>
       <c r="D13" s="8"/>
       <c r="E13" s="45">
         <v>1</v>
@@ -3000,10 +3011,10 @@
       <c r="F13" s="45"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="91" t="s">
+      <c r="B14" s="102" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="92"/>
+      <c r="C14" s="103"/>
       <c r="D14" s="8"/>
       <c r="E14" s="45">
         <v>1</v>
@@ -3011,19 +3022,19 @@
       <c r="F14" s="45"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="103" t="s">
+      <c r="B15" s="112" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="104"/>
+      <c r="C15" s="113"/>
       <c r="D15" s="8"/>
       <c r="E15" s="45"/>
       <c r="F15" s="45"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="95" t="s">
+      <c r="B16" s="88" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="96"/>
+      <c r="C16" s="89"/>
       <c r="D16" s="8"/>
       <c r="E16" s="45">
         <v>1</v>
@@ -3031,10 +3042,10 @@
       <c r="F16" s="45"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="95" t="s">
+      <c r="B17" s="88" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="96"/>
+      <c r="C17" s="89"/>
       <c r="D17" s="8"/>
       <c r="E17" s="45">
         <v>1</v>
@@ -3042,26 +3053,16 @@
       <c r="F17" s="45"/>
     </row>
     <row r="18" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B18" s="87" t="s">
+      <c r="B18" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="88"/>
+      <c r="C18" s="105"/>
       <c r="D18" s="56"/>
       <c r="E18" s="57"/>
       <c r="F18" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B11:C11"/>
@@ -3069,6 +3070,16 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3081,13 +3092,13 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="125" t="s">
+      <c r="C1" s="124" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
     </row>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
       <c r="B2" s="34" t="s">

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ayato Terao\Documents\GitHub\GlassesGame\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nodasouma\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D92DA032-F98F-4DA3-B34F-3F89C25017C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0422574A-4523-4602-BE73-D37AA57A426D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1635" yWindow="-15045" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>
@@ -1337,7 +1337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1522,16 +1522,82 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1546,98 +1612,35 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1945,10 +1948,10 @@
   <sheetData>
     <row r="1" spans="2:11" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B2" s="94" t="s">
+      <c r="B2" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="95"/>
+      <c r="C2" s="107"/>
       <c r="D2" s="55" t="s">
         <v>9</v>
       </c>
@@ -1963,10 +1966,10 @@
       </c>
     </row>
     <row r="3" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="97"/>
+      <c r="C3" s="109"/>
       <c r="D3" s="55" t="s">
         <v>12</v>
       </c>
@@ -1993,10 +1996,10 @@
       </c>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="100" t="s">
+      <c r="B4" s="110" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="101"/>
+      <c r="C4" s="111"/>
       <c r="D4" s="11"/>
       <c r="E4" s="49"/>
       <c r="F4" s="49"/>
@@ -2015,10 +2018,10 @@
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="102" t="s">
+      <c r="B5" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="103"/>
+      <c r="C5" s="91"/>
       <c r="D5" s="8"/>
       <c r="E5" s="45">
         <v>2</v>
@@ -2041,10 +2044,10 @@
       </c>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" s="102" t="s">
+      <c r="B6" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="103"/>
+      <c r="C6" s="91"/>
       <c r="D6" s="8"/>
       <c r="E6" s="45">
         <v>1</v>
@@ -2067,10 +2070,10 @@
       </c>
     </row>
     <row r="7" spans="2:11">
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="98" t="s">
         <v>90</v>
       </c>
-      <c r="C7" s="87"/>
+      <c r="C7" s="99"/>
       <c r="D7" s="8"/>
       <c r="E7" s="45">
         <v>2</v>
@@ -2093,10 +2096,10 @@
       </c>
     </row>
     <row r="8" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B8" s="86" t="s">
+      <c r="B8" s="98" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="87"/>
+      <c r="C8" s="99"/>
       <c r="D8" s="10"/>
       <c r="E8" s="46">
         <v>2</v>
@@ -2117,10 +2120,10 @@
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="86" t="s">
+      <c r="B9" s="98" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="87"/>
+      <c r="C9" s="99"/>
       <c r="D9" s="10"/>
       <c r="E9" s="46">
         <v>2</v>
@@ -2131,10 +2134,10 @@
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="90" t="s">
+      <c r="B10" s="112" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="91"/>
+      <c r="C10" s="113"/>
       <c r="D10" s="8"/>
       <c r="E10" s="45">
         <v>1</v>
@@ -2147,10 +2150,10 @@
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="86" t="s">
+      <c r="B11" s="98" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="87"/>
+      <c r="C11" s="99"/>
       <c r="D11" s="8"/>
       <c r="E11" s="45"/>
       <c r="F11" s="46"/>
@@ -2159,10 +2162,10 @@
       </c>
     </row>
     <row r="12" spans="2:11">
-      <c r="B12" s="88" t="s">
+      <c r="B12" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="89"/>
+      <c r="C12" s="95"/>
       <c r="D12" s="8"/>
       <c r="E12" s="45">
         <v>1</v>
@@ -2175,10 +2178,10 @@
       </c>
     </row>
     <row r="13" spans="2:11">
-      <c r="B13" s="102" t="s">
+      <c r="B13" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="103"/>
+      <c r="C13" s="91"/>
       <c r="D13" s="8"/>
       <c r="E13" s="45">
         <v>1</v>
@@ -2191,10 +2194,10 @@
       </c>
     </row>
     <row r="14" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B14" s="108" t="s">
+      <c r="B14" s="92" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="109"/>
+      <c r="C14" s="93"/>
       <c r="D14" s="10"/>
       <c r="E14" s="46">
         <v>1</v>
@@ -2207,10 +2210,10 @@
       </c>
     </row>
     <row r="15" spans="2:11">
-      <c r="B15" s="98" t="s">
+      <c r="B15" s="100" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="99"/>
+      <c r="C15" s="101"/>
       <c r="D15" s="7" t="s">
         <v>11</v>
       </c>
@@ -2218,44 +2221,50 @@
         <f>SUM(E16:E24)</f>
         <v>16</v>
       </c>
-      <c r="F15" s="48"/>
+      <c r="F15" s="48">
+        <v>8</v>
+      </c>
       <c r="G15" s="69" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="16" spans="2:11">
-      <c r="B16" s="86" t="s">
+      <c r="B16" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="87"/>
+      <c r="C16" s="99"/>
       <c r="D16" s="8"/>
       <c r="E16" s="45">
         <v>3</v>
       </c>
-      <c r="F16" s="45"/>
+      <c r="F16" s="45">
+        <v>1</v>
+      </c>
       <c r="G16" s="63" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="86" t="s">
+      <c r="B17" s="98" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="87"/>
+      <c r="C17" s="99"/>
       <c r="D17" s="8"/>
       <c r="E17" s="45">
         <v>3</v>
       </c>
-      <c r="F17" s="45"/>
+      <c r="F17" s="45">
+        <v>1</v>
+      </c>
       <c r="G17" s="63" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="86" t="s">
+      <c r="B18" s="98" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="87"/>
+      <c r="C18" s="99"/>
       <c r="D18" s="8"/>
       <c r="E18" s="45">
         <v>3</v>
@@ -2268,50 +2277,56 @@
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="86" t="s">
+      <c r="B19" s="98" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="87"/>
+      <c r="C19" s="99"/>
       <c r="D19" s="10"/>
       <c r="E19" s="45">
         <v>3</v>
       </c>
-      <c r="F19" s="45"/>
+      <c r="F19" s="125">
+        <v>1</v>
+      </c>
       <c r="G19" s="63" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="86" t="s">
+      <c r="B20" s="98" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="87"/>
+      <c r="C20" s="99"/>
       <c r="D20" s="8"/>
       <c r="E20" s="50">
         <v>1</v>
       </c>
-      <c r="F20" s="49"/>
+      <c r="F20" s="125">
+        <v>1</v>
+      </c>
       <c r="G20" s="63" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="90" t="s">
+      <c r="B21" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="91"/>
+      <c r="C21" s="113"/>
       <c r="D21" s="8"/>
       <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
+      <c r="F21" s="125">
+        <v>3</v>
+      </c>
       <c r="G21" s="63" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="88" t="s">
+      <c r="B22" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="89"/>
+      <c r="C22" s="95"/>
       <c r="D22" s="8"/>
       <c r="E22" s="45">
         <v>1</v>
@@ -2324,10 +2339,10 @@
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="88" t="s">
+      <c r="B23" s="94" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="89"/>
+      <c r="C23" s="95"/>
       <c r="D23" s="8"/>
       <c r="E23" s="45">
         <v>1</v>
@@ -2340,10 +2355,10 @@
       </c>
     </row>
     <row r="24" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B24" s="110" t="s">
+      <c r="B24" s="96" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="111"/>
+      <c r="C24" s="97"/>
       <c r="D24" s="9"/>
       <c r="E24" s="47">
         <v>1</v>
@@ -2356,10 +2371,10 @@
       </c>
     </row>
     <row r="25" spans="2:7">
-      <c r="B25" s="92" t="s">
+      <c r="B25" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="93"/>
+      <c r="C25" s="115"/>
       <c r="D25" s="58" t="s">
         <v>10</v>
       </c>
@@ -2373,10 +2388,10 @@
       </c>
     </row>
     <row r="26" spans="2:7">
-      <c r="B26" s="90" t="s">
+      <c r="B26" s="112" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="91"/>
+      <c r="C26" s="113"/>
       <c r="D26" s="8"/>
       <c r="E26" s="45">
         <v>5</v>
@@ -2387,10 +2402,10 @@
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="90" t="s">
+      <c r="B27" s="112" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="91"/>
+      <c r="C27" s="113"/>
       <c r="D27" s="8"/>
       <c r="E27" s="45"/>
       <c r="F27" s="45"/>
@@ -2399,10 +2414,10 @@
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="88" t="s">
+      <c r="B28" s="94" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="89"/>
+      <c r="C28" s="95"/>
       <c r="D28" s="8"/>
       <c r="E28" s="45">
         <v>2</v>
@@ -2413,10 +2428,10 @@
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="88" t="s">
+      <c r="B29" s="94" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="89"/>
+      <c r="C29" s="95"/>
       <c r="D29" s="8"/>
       <c r="E29" s="45">
         <v>2</v>
@@ -2427,10 +2442,10 @@
       </c>
     </row>
     <row r="30" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B30" s="106" t="s">
+      <c r="B30" s="88" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="107"/>
+      <c r="C30" s="89"/>
       <c r="D30" s="9"/>
       <c r="E30" s="47">
         <v>3</v>
@@ -2441,10 +2456,10 @@
       </c>
     </row>
     <row r="31" spans="2:7">
-      <c r="B31" s="98" t="s">
+      <c r="B31" s="100" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="99"/>
+      <c r="C31" s="101"/>
       <c r="D31" s="7" t="s">
         <v>14</v>
       </c>
@@ -2458,10 +2473,10 @@
       </c>
     </row>
     <row r="32" spans="2:7">
-      <c r="B32" s="86" t="s">
+      <c r="B32" s="98" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="87"/>
+      <c r="C32" s="99"/>
       <c r="D32" s="11"/>
       <c r="E32" s="54"/>
       <c r="F32" s="49"/>
@@ -2470,10 +2485,10 @@
       </c>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="102" t="s">
+      <c r="B33" s="90" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="103"/>
+      <c r="C33" s="91"/>
       <c r="D33" s="11"/>
       <c r="E33" s="54">
         <v>2</v>
@@ -2484,10 +2499,10 @@
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="112" t="s">
+      <c r="B34" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="113"/>
+      <c r="C34" s="103"/>
       <c r="D34" s="8"/>
       <c r="E34" s="44"/>
       <c r="F34" s="45"/>
@@ -2496,10 +2511,10 @@
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="86" t="s">
+      <c r="B35" s="98" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="87"/>
+      <c r="C35" s="99"/>
       <c r="D35" s="8"/>
       <c r="E35" s="44">
         <v>2</v>
@@ -2510,10 +2525,10 @@
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="86" t="s">
+      <c r="B36" s="98" t="s">
         <v>60</v>
       </c>
-      <c r="C36" s="87"/>
+      <c r="C36" s="99"/>
       <c r="D36" s="8"/>
       <c r="E36" s="44">
         <v>2</v>
@@ -2524,10 +2539,10 @@
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="112" t="s">
+      <c r="B37" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="113"/>
+      <c r="C37" s="103"/>
       <c r="D37" s="8"/>
       <c r="E37" s="44"/>
       <c r="F37" s="45"/>
@@ -2536,10 +2551,10 @@
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="114" t="s">
+      <c r="B38" s="104" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="115"/>
+      <c r="C38" s="105"/>
       <c r="D38" s="8"/>
       <c r="E38" s="44">
         <v>2</v>
@@ -2550,10 +2565,10 @@
       </c>
     </row>
     <row r="39" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B39" s="106" t="s">
+      <c r="B39" s="88" t="s">
         <v>64</v>
       </c>
-      <c r="C39" s="107"/>
+      <c r="C39" s="89"/>
       <c r="D39" s="9"/>
       <c r="E39" s="51">
         <v>3</v>
@@ -2564,10 +2579,10 @@
       </c>
     </row>
     <row r="40" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B40" s="104" t="s">
+      <c r="B40" s="86" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="105"/>
+      <c r="C40" s="87"/>
       <c r="D40" s="56"/>
       <c r="E40" s="83">
         <f>SUM(E3+E15+E25+F31)</f>
@@ -2575,12 +2590,35 @@
       </c>
       <c r="F40" s="84">
         <f>SUM(F4:F39)</f>
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="G40" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B13:C13"/>
@@ -2597,29 +2635,6 @@
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2637,10 +2652,10 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="94" t="s">
+      <c r="B2" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="95"/>
+      <c r="C2" s="107"/>
       <c r="D2" s="55" t="s">
         <v>9</v>
       </c>
@@ -2652,10 +2667,10 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="97"/>
+      <c r="C3" s="109"/>
       <c r="D3" s="55" t="s">
         <v>12</v>
       </c>
@@ -2663,10 +2678,10 @@
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="116" t="s">
+      <c r="B4" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="117"/>
+      <c r="C4" s="123"/>
       <c r="D4" s="7"/>
       <c r="E4" s="48">
         <v>2</v>
@@ -2674,10 +2689,10 @@
       <c r="F4" s="48"/>
     </row>
     <row r="5" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B5" s="102" t="s">
+      <c r="B5" s="90" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="103"/>
+      <c r="C5" s="91"/>
       <c r="D5" s="8"/>
       <c r="E5" s="45">
         <v>2</v>
@@ -2685,10 +2700,10 @@
       <c r="F5" s="45"/>
     </row>
     <row r="6" spans="2:6">
-      <c r="B6" s="98" t="s">
+      <c r="B6" s="100" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="99"/>
+      <c r="C6" s="101"/>
       <c r="D6" s="7" t="s">
         <v>11</v>
       </c>
@@ -2696,10 +2711,10 @@
       <c r="F6" s="48"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="102" t="s">
+      <c r="B7" s="90" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="103"/>
+      <c r="C7" s="91"/>
       <c r="D7" s="8"/>
       <c r="E7" s="45">
         <v>2</v>
@@ -2707,10 +2722,10 @@
       <c r="F7" s="45"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="102" t="s">
+      <c r="B8" s="90" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="103"/>
+      <c r="C8" s="91"/>
       <c r="D8" s="8"/>
       <c r="E8" s="45">
         <v>3</v>
@@ -2718,10 +2733,10 @@
       <c r="F8" s="45"/>
     </row>
     <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="102" t="s">
+      <c r="B9" s="90" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="103"/>
+      <c r="C9" s="91"/>
       <c r="D9" s="8"/>
       <c r="E9" s="45">
         <v>2</v>
@@ -2729,10 +2744,10 @@
       <c r="F9" s="45"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="92" t="s">
+      <c r="B10" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="93"/>
+      <c r="C10" s="115"/>
       <c r="D10" s="58" t="s">
         <v>10</v>
       </c>
@@ -2740,10 +2755,10 @@
       <c r="F10" s="59"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="88" t="s">
+      <c r="B11" s="94" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="89"/>
+      <c r="C11" s="95"/>
       <c r="D11" s="8"/>
       <c r="E11" s="45">
         <v>5</v>
@@ -2751,10 +2766,10 @@
       <c r="F11" s="45"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="88" t="s">
+      <c r="B12" s="94" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="89"/>
+      <c r="C12" s="95"/>
       <c r="D12" s="8"/>
       <c r="E12" s="45">
         <v>1</v>
@@ -2762,10 +2777,10 @@
       <c r="F12" s="45"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="88" t="s">
+      <c r="B13" s="94" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="89"/>
+      <c r="C13" s="95"/>
       <c r="D13" s="8"/>
       <c r="E13" s="45">
         <v>2</v>
@@ -2773,10 +2788,10 @@
       <c r="F13" s="45"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="118" t="s">
+      <c r="B14" s="120" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="119"/>
+      <c r="C14" s="121"/>
       <c r="D14" s="11" t="s">
         <v>14</v>
       </c>
@@ -2784,10 +2799,10 @@
       <c r="F14" s="49"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="102" t="s">
+      <c r="B15" s="90" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="103"/>
+      <c r="C15" s="91"/>
       <c r="D15" s="11"/>
       <c r="E15" s="54">
         <v>5</v>
@@ -2795,19 +2810,19 @@
       <c r="F15" s="49"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="112" t="s">
+      <c r="B16" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="113"/>
+      <c r="C16" s="103"/>
       <c r="D16" s="8"/>
       <c r="E16" s="44"/>
       <c r="F16" s="45"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="102" t="s">
+      <c r="B17" s="90" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="103"/>
+      <c r="C17" s="91"/>
       <c r="D17" s="8"/>
       <c r="E17" s="44">
         <v>2</v>
@@ -2815,19 +2830,19 @@
       <c r="F17" s="45"/>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="112" t="s">
+      <c r="B18" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="113"/>
+      <c r="C18" s="103"/>
       <c r="D18" s="8"/>
       <c r="E18" s="44"/>
       <c r="F18" s="45"/>
     </row>
     <row r="19" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B19" s="120" t="s">
+      <c r="B19" s="116" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="121"/>
+      <c r="C19" s="117"/>
       <c r="D19" s="8"/>
       <c r="E19" s="44">
         <v>2</v>
@@ -2835,27 +2850,16 @@
       <c r="F19" s="45"/>
     </row>
     <row r="20" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B20" s="122" t="s">
+      <c r="B20" s="118" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="123"/>
+      <c r="C20" s="119"/>
       <c r="D20" s="12"/>
       <c r="E20" s="52"/>
       <c r="F20" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
@@ -2864,6 +2868,17 @@
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2877,10 +2892,10 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="94" t="s">
+      <c r="B2" s="106" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="95"/>
+      <c r="C2" s="107"/>
       <c r="D2" s="55" t="s">
         <v>9</v>
       </c>
@@ -2892,10 +2907,10 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="97"/>
+      <c r="C3" s="109"/>
       <c r="D3" s="55" t="s">
         <v>12</v>
       </c>
@@ -2903,10 +2918,10 @@
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B4" s="116" t="s">
+      <c r="B4" s="122" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="117"/>
+      <c r="C4" s="123"/>
       <c r="D4" s="7"/>
       <c r="E4" s="48">
         <v>3</v>
@@ -2914,10 +2929,10 @@
       <c r="F4" s="48"/>
     </row>
     <row r="5" spans="2:6">
-      <c r="B5" s="98" t="s">
+      <c r="B5" s="100" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="99"/>
+      <c r="C5" s="101"/>
       <c r="D5" s="7" t="s">
         <v>11</v>
       </c>
@@ -2925,10 +2940,10 @@
       <c r="F5" s="48"/>
     </row>
     <row r="6" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B6" s="102" t="s">
+      <c r="B6" s="90" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="103"/>
+      <c r="C6" s="91"/>
       <c r="D6" s="8"/>
       <c r="E6" s="45">
         <v>3</v>
@@ -2936,10 +2951,10 @@
       <c r="F6" s="45"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="92" t="s">
+      <c r="B7" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="93"/>
+      <c r="C7" s="115"/>
       <c r="D7" s="58" t="s">
         <v>10</v>
       </c>
@@ -2947,10 +2962,10 @@
       <c r="F7" s="59"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="88" t="s">
+      <c r="B8" s="94" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="89"/>
+      <c r="C8" s="95"/>
       <c r="D8" s="8"/>
       <c r="E8" s="45">
         <v>3</v>
@@ -2958,10 +2973,10 @@
       <c r="F8" s="45"/>
     </row>
     <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="102" t="s">
+      <c r="B9" s="90" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="103"/>
+      <c r="C9" s="91"/>
       <c r="D9" s="8"/>
       <c r="E9" s="45">
         <v>2</v>
@@ -2969,10 +2984,10 @@
       <c r="F9" s="45"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="98" t="s">
+      <c r="B10" s="100" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="99"/>
+      <c r="C10" s="101"/>
       <c r="D10" s="7" t="s">
         <v>14</v>
       </c>
@@ -2980,10 +2995,10 @@
       <c r="F10" s="48"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="102" t="s">
+      <c r="B11" s="90" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="103"/>
+      <c r="C11" s="91"/>
       <c r="D11" s="11"/>
       <c r="E11" s="49">
         <v>2</v>
@@ -2991,19 +3006,19 @@
       <c r="F11" s="49"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="112" t="s">
+      <c r="B12" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="113"/>
+      <c r="C12" s="103"/>
       <c r="D12" s="8"/>
       <c r="E12" s="45"/>
       <c r="F12" s="45"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="102" t="s">
+      <c r="B13" s="90" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="103"/>
+      <c r="C13" s="91"/>
       <c r="D13" s="8"/>
       <c r="E13" s="45">
         <v>1</v>
@@ -3011,10 +3026,10 @@
       <c r="F13" s="45"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="102" t="s">
+      <c r="B14" s="90" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="103"/>
+      <c r="C14" s="91"/>
       <c r="D14" s="8"/>
       <c r="E14" s="45">
         <v>1</v>
@@ -3022,19 +3037,19 @@
       <c r="F14" s="45"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="112" t="s">
+      <c r="B15" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="113"/>
+      <c r="C15" s="103"/>
       <c r="D15" s="8"/>
       <c r="E15" s="45"/>
       <c r="F15" s="45"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="88" t="s">
+      <c r="B16" s="94" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="89"/>
+      <c r="C16" s="95"/>
       <c r="D16" s="8"/>
       <c r="E16" s="45">
         <v>1</v>
@@ -3042,10 +3057,10 @@
       <c r="F16" s="45"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="88" t="s">
+      <c r="B17" s="94" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="89"/>
+      <c r="C17" s="95"/>
       <c r="D17" s="8"/>
       <c r="E17" s="45">
         <v>1</v>
@@ -3053,16 +3068,26 @@
       <c r="F17" s="45"/>
     </row>
     <row r="18" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B18" s="104" t="s">
+      <c r="B18" s="86" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="105"/>
+      <c r="C18" s="87"/>
       <c r="D18" s="56"/>
       <c r="E18" s="57"/>
       <c r="F18" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B11:C11"/>
@@ -3070,16 +3095,6 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nodasouma\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0422574A-4523-4602-BE73-D37AA57A426D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09055683-AC3C-46D9-9D9B-97B912B79C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1635" yWindow="-15045" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3180" yWindow="-14925" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>
@@ -1337,7 +1337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1373,7 +1373,6 @@
     <xf numFmtId="56" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -1948,17 +1947,17 @@
   <sheetData>
     <row r="1" spans="2:11" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="55" t="s">
+      <c r="C2" s="106"/>
+      <c r="D2" s="54" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="68" t="s">
+      <c r="F2" s="67" t="s">
         <v>8</v>
       </c>
       <c r="G2" s="12" t="s">
@@ -1966,633 +1965,633 @@
       </c>
     </row>
     <row r="3" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B3" s="108" t="s">
+      <c r="B3" s="107" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="109"/>
-      <c r="D3" s="55" t="s">
+      <c r="C3" s="108"/>
+      <c r="D3" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="52">
+      <c r="E3" s="51">
         <f>SUM(E4:E14)</f>
         <v>13</v>
       </c>
-      <c r="F3" s="53">
+      <c r="F3" s="52">
         <f>SUM(F4:F14)</f>
         <v>10</v>
       </c>
-      <c r="G3" s="55" t="s">
+      <c r="G3" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="I3" s="73" t="s">
+      <c r="I3" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="J3" s="77">
+      <c r="J3" s="76">
         <f ca="1">TODAY()</f>
         <v>46289</v>
       </c>
-      <c r="K3" s="55" t="s">
+      <c r="K3" s="54" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="110" t="s">
+      <c r="B4" s="109" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="111"/>
+      <c r="C4" s="110"/>
       <c r="D4" s="11"/>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="G4" s="64" t="s">
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="63" t="s">
         <v>89</v>
       </c>
-      <c r="I4" s="78" t="s">
+      <c r="I4" s="77" t="s">
         <v>80</v>
       </c>
-      <c r="J4" s="74">
+      <c r="J4" s="73">
         <v>46295</v>
       </c>
-      <c r="K4" s="72" t="str">
+      <c r="K4" s="71" t="str">
         <f ca="1">SUM($J4-J3)&amp; "日"</f>
         <v>6日</v>
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="90" t="s">
+      <c r="B5" s="89" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="91"/>
+      <c r="C5" s="90"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="45">
+      <c r="E5" s="44">
         <v>2</v>
       </c>
-      <c r="F5" s="45">
+      <c r="F5" s="44">
         <v>2</v>
       </c>
-      <c r="G5" s="64" t="s">
+      <c r="G5" s="63" t="s">
         <v>89</v>
       </c>
-      <c r="I5" s="79" t="s">
+      <c r="I5" s="78" t="s">
         <v>81</v>
       </c>
-      <c r="J5" s="75">
+      <c r="J5" s="74">
         <v>46305</v>
       </c>
-      <c r="K5" s="70" t="str">
+      <c r="K5" s="69" t="str">
         <f ca="1">SUM($J5-J3)&amp; "日"</f>
         <v>16日</v>
       </c>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" s="90" t="s">
+      <c r="B6" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="91"/>
+      <c r="C6" s="90"/>
       <c r="D6" s="8"/>
-      <c r="E6" s="45">
+      <c r="E6" s="44">
         <v>1</v>
       </c>
-      <c r="F6" s="45">
+      <c r="F6" s="44">
         <v>2</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="G6" s="63" t="s">
         <v>89</v>
       </c>
-      <c r="I6" s="80" t="s">
+      <c r="I6" s="79" t="s">
         <v>82</v>
       </c>
-      <c r="J6" s="75">
+      <c r="J6" s="74">
         <v>46310</v>
       </c>
-      <c r="K6" s="70" t="str">
+      <c r="K6" s="69" t="str">
         <f ca="1">SUM($J6-J3)&amp; "日"</f>
         <v>21日</v>
       </c>
     </row>
     <row r="7" spans="2:11">
-      <c r="B7" s="98" t="s">
+      <c r="B7" s="97" t="s">
         <v>90</v>
       </c>
-      <c r="C7" s="99"/>
+      <c r="C7" s="98"/>
       <c r="D7" s="8"/>
-      <c r="E7" s="45">
+      <c r="E7" s="44">
         <v>2</v>
       </c>
-      <c r="F7" s="49">
+      <c r="F7" s="48">
         <v>2</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="63" t="s">
         <v>89</v>
       </c>
-      <c r="I7" s="81" t="s">
+      <c r="I7" s="80" t="s">
         <v>83</v>
       </c>
-      <c r="J7" s="75">
+      <c r="J7" s="74">
         <v>46313</v>
       </c>
-      <c r="K7" s="70" t="str">
+      <c r="K7" s="69" t="str">
         <f ca="1">SUM($J7-J3)&amp; "日"</f>
         <v>24日</v>
       </c>
     </row>
     <row r="8" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B8" s="98" t="s">
+      <c r="B8" s="97" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="99"/>
+      <c r="C8" s="98"/>
       <c r="D8" s="10"/>
-      <c r="E8" s="46">
+      <c r="E8" s="45">
         <v>2</v>
       </c>
-      <c r="F8" s="46"/>
-      <c r="G8" s="63" t="s">
+      <c r="F8" s="45"/>
+      <c r="G8" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="I8" s="82" t="s">
+      <c r="I8" s="81" t="s">
         <v>78</v>
       </c>
-      <c r="J8" s="76">
+      <c r="J8" s="75">
         <v>46314</v>
       </c>
-      <c r="K8" s="71" t="str">
+      <c r="K8" s="70" t="str">
         <f ca="1">SUM(J8-J3)&amp; "日"</f>
         <v>25日</v>
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="98" t="s">
+      <c r="B9" s="97" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="99"/>
+      <c r="C9" s="98"/>
       <c r="D9" s="10"/>
-      <c r="E9" s="46">
+      <c r="E9" s="45">
         <v>2</v>
       </c>
-      <c r="F9" s="46"/>
-      <c r="G9" s="63" t="s">
+      <c r="F9" s="45"/>
+      <c r="G9" s="62" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="112" t="s">
+      <c r="B10" s="111" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="113"/>
+      <c r="C10" s="112"/>
       <c r="D10" s="8"/>
-      <c r="E10" s="45">
+      <c r="E10" s="44">
         <v>1</v>
       </c>
-      <c r="F10" s="45">
+      <c r="F10" s="44">
         <v>1</v>
       </c>
-      <c r="G10" s="63" t="s">
+      <c r="G10" s="62" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="98" t="s">
+      <c r="B11" s="97" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="99"/>
+      <c r="C11" s="98"/>
       <c r="D11" s="8"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="63" t="s">
+      <c r="E11" s="44"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="62" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="12" spans="2:11">
-      <c r="B12" s="94" t="s">
+      <c r="B12" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="95"/>
+      <c r="C12" s="94"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="45">
+      <c r="E12" s="44">
         <v>1</v>
       </c>
-      <c r="F12" s="45">
+      <c r="F12" s="44">
         <v>1</v>
       </c>
-      <c r="G12" s="63" t="s">
+      <c r="G12" s="62" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="13" spans="2:11">
-      <c r="B13" s="90" t="s">
+      <c r="B13" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="91"/>
+      <c r="C13" s="90"/>
       <c r="D13" s="8"/>
-      <c r="E13" s="45">
+      <c r="E13" s="44">
         <v>1</v>
       </c>
-      <c r="F13" s="45">
+      <c r="F13" s="44">
         <v>1</v>
       </c>
-      <c r="G13" s="63" t="s">
+      <c r="G13" s="62" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="14" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B14" s="92" t="s">
+      <c r="B14" s="91" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="93"/>
+      <c r="C14" s="92"/>
       <c r="D14" s="10"/>
-      <c r="E14" s="46">
+      <c r="E14" s="45">
         <v>1</v>
       </c>
-      <c r="F14" s="46">
+      <c r="F14" s="45">
         <v>1</v>
       </c>
-      <c r="G14" s="63" t="s">
+      <c r="G14" s="62" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="15" spans="2:11">
-      <c r="B15" s="100" t="s">
+      <c r="B15" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="101"/>
+      <c r="C15" s="100"/>
       <c r="D15" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="48">
+      <c r="E15" s="47">
         <f>SUM(E16:E24)</f>
         <v>16</v>
       </c>
-      <c r="F15" s="48">
+      <c r="F15" s="47">
         <v>8</v>
       </c>
-      <c r="G15" s="69" t="s">
+      <c r="G15" s="68" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="16" spans="2:11">
-      <c r="B16" s="98" t="s">
+      <c r="B16" s="97" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="99"/>
+      <c r="C16" s="98"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="45">
+      <c r="E16" s="44">
         <v>3</v>
       </c>
-      <c r="F16" s="45">
+      <c r="F16" s="44">
         <v>1</v>
       </c>
-      <c r="G16" s="63" t="s">
+      <c r="G16" s="62" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="98" t="s">
+      <c r="B17" s="97" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="99"/>
+      <c r="C17" s="98"/>
       <c r="D17" s="8"/>
-      <c r="E17" s="45">
+      <c r="E17" s="44">
         <v>3</v>
       </c>
-      <c r="F17" s="45">
+      <c r="F17" s="44">
         <v>1</v>
       </c>
-      <c r="G17" s="63" t="s">
+      <c r="G17" s="62" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="98" t="s">
+      <c r="B18" s="97" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="99"/>
+      <c r="C18" s="98"/>
       <c r="D18" s="8"/>
-      <c r="E18" s="45">
+      <c r="E18" s="44">
         <v>3</v>
       </c>
-      <c r="F18" s="45">
+      <c r="F18" s="44">
         <v>1</v>
       </c>
-      <c r="G18" s="63" t="s">
+      <c r="G18" s="62" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="97" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="99"/>
+      <c r="C19" s="98"/>
       <c r="D19" s="10"/>
-      <c r="E19" s="45">
+      <c r="E19" s="44">
         <v>3</v>
       </c>
-      <c r="F19" s="125">
+      <c r="F19" s="124">
         <v>1</v>
       </c>
-      <c r="G19" s="63" t="s">
+      <c r="G19" s="62" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="98" t="s">
+      <c r="B20" s="97" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="99"/>
+      <c r="C20" s="98"/>
       <c r="D20" s="8"/>
-      <c r="E20" s="50">
+      <c r="E20" s="49">
         <v>1</v>
       </c>
-      <c r="F20" s="125">
+      <c r="F20" s="124">
         <v>1</v>
       </c>
-      <c r="G20" s="63" t="s">
+      <c r="G20" s="62" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="112" t="s">
+      <c r="B21" s="111" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="113"/>
+      <c r="C21" s="112"/>
       <c r="D21" s="8"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="125">
+      <c r="E21" s="44"/>
+      <c r="F21" s="124">
         <v>3</v>
       </c>
-      <c r="G21" s="63" t="s">
+      <c r="G21" s="62" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="94" t="s">
+      <c r="B22" s="93" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="95"/>
+      <c r="C22" s="94"/>
       <c r="D22" s="8"/>
-      <c r="E22" s="45">
+      <c r="E22" s="44">
         <v>1</v>
       </c>
-      <c r="F22" s="45">
+      <c r="F22" s="44">
         <v>1</v>
       </c>
-      <c r="G22" s="63" t="s">
+      <c r="G22" s="62" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="94" t="s">
+      <c r="B23" s="93" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="95"/>
+      <c r="C23" s="94"/>
       <c r="D23" s="8"/>
-      <c r="E23" s="45">
+      <c r="E23" s="44">
         <v>1</v>
       </c>
-      <c r="F23" s="45">
+      <c r="F23" s="44">
         <v>1</v>
       </c>
-      <c r="G23" s="63" t="s">
+      <c r="G23" s="62" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B24" s="96" t="s">
+      <c r="B24" s="95" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="97"/>
+      <c r="C24" s="96"/>
       <c r="D24" s="9"/>
-      <c r="E24" s="47">
+      <c r="E24" s="46">
         <v>1</v>
       </c>
-      <c r="F24" s="47">
+      <c r="F24" s="46">
         <v>1</v>
       </c>
-      <c r="G24" s="63" t="s">
+      <c r="G24" s="62" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="25" spans="2:7">
-      <c r="B25" s="114" t="s">
+      <c r="B25" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="115"/>
-      <c r="D25" s="58" t="s">
+      <c r="C25" s="114"/>
+      <c r="D25" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="59">
+      <c r="E25" s="58">
         <f>SUM(E26:E30)</f>
         <v>12</v>
       </c>
-      <c r="F25" s="59"/>
-      <c r="G25" s="69" t="s">
+      <c r="F25" s="58"/>
+      <c r="G25" s="68" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="26" spans="2:7">
-      <c r="B26" s="112" t="s">
+      <c r="B26" s="111" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="113"/>
+      <c r="C26" s="112"/>
       <c r="D26" s="8"/>
-      <c r="E26" s="45">
+      <c r="E26" s="44">
         <v>5</v>
       </c>
-      <c r="F26" s="45"/>
-      <c r="G26" s="63" t="s">
+      <c r="F26" s="44"/>
+      <c r="G26" s="62" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="112" t="s">
+      <c r="B27" s="111" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="113"/>
+      <c r="C27" s="112"/>
       <c r="D27" s="8"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="63" t="s">
+      <c r="E27" s="44"/>
+      <c r="F27" s="44"/>
+      <c r="G27" s="62" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="94" t="s">
+      <c r="B28" s="93" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="95"/>
+      <c r="C28" s="94"/>
       <c r="D28" s="8"/>
-      <c r="E28" s="45">
+      <c r="E28" s="44">
         <v>2</v>
       </c>
-      <c r="F28" s="45"/>
-      <c r="G28" s="63" t="s">
+      <c r="F28" s="44"/>
+      <c r="G28" s="62" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="94" t="s">
+      <c r="B29" s="93" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="95"/>
+      <c r="C29" s="94"/>
       <c r="D29" s="8"/>
-      <c r="E29" s="45">
+      <c r="E29" s="44">
         <v>2</v>
       </c>
-      <c r="F29" s="45"/>
-      <c r="G29" s="63" t="s">
+      <c r="F29" s="44"/>
+      <c r="G29" s="62" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B30" s="88" t="s">
+      <c r="B30" s="87" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="89"/>
+      <c r="C30" s="88"/>
       <c r="D30" s="9"/>
-      <c r="E30" s="47">
+      <c r="E30" s="46">
         <v>3</v>
       </c>
-      <c r="F30" s="47"/>
-      <c r="G30" s="65" t="s">
+      <c r="F30" s="46"/>
+      <c r="G30" s="64" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="31" spans="2:7">
-      <c r="B31" s="100" t="s">
+      <c r="B31" s="99" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="101"/>
+      <c r="C31" s="100"/>
       <c r="D31" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="85">
+      <c r="E31" s="84">
         <f>SUM(E32:E39)</f>
         <v>11</v>
       </c>
-      <c r="F31" s="48"/>
-      <c r="G31" s="69" t="s">
+      <c r="F31" s="47"/>
+      <c r="G31" s="68" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="32" spans="2:7">
-      <c r="B32" s="98" t="s">
+      <c r="B32" s="97" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="99"/>
+      <c r="C32" s="98"/>
       <c r="D32" s="11"/>
-      <c r="E32" s="54"/>
-      <c r="F32" s="49"/>
-      <c r="G32" s="63" t="s">
+      <c r="E32" s="53"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="62" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="90" t="s">
+      <c r="B33" s="89" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="91"/>
+      <c r="C33" s="90"/>
       <c r="D33" s="11"/>
-      <c r="E33" s="54">
+      <c r="E33" s="53">
         <v>2</v>
       </c>
-      <c r="F33" s="49"/>
-      <c r="G33" s="63" t="s">
+      <c r="F33" s="48"/>
+      <c r="G33" s="62" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="102" t="s">
+      <c r="B34" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="103"/>
+      <c r="C34" s="102"/>
       <c r="D34" s="8"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="45"/>
-      <c r="G34" s="63" t="s">
+      <c r="E34" s="43"/>
+      <c r="F34" s="44"/>
+      <c r="G34" s="62" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="98" t="s">
+      <c r="B35" s="97" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="99"/>
+      <c r="C35" s="98"/>
       <c r="D35" s="8"/>
-      <c r="E35" s="44">
+      <c r="E35" s="43">
         <v>2</v>
       </c>
-      <c r="F35" s="45"/>
-      <c r="G35" s="63" t="s">
+      <c r="F35" s="44"/>
+      <c r="G35" s="62" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="98" t="s">
+      <c r="B36" s="97" t="s">
         <v>60</v>
       </c>
-      <c r="C36" s="99"/>
+      <c r="C36" s="98"/>
       <c r="D36" s="8"/>
-      <c r="E36" s="44">
+      <c r="E36" s="43">
         <v>2</v>
       </c>
-      <c r="F36" s="45"/>
-      <c r="G36" s="63" t="s">
+      <c r="F36" s="44"/>
+      <c r="G36" s="62" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="102" t="s">
+      <c r="B37" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="103"/>
+      <c r="C37" s="102"/>
       <c r="D37" s="8"/>
-      <c r="E37" s="44"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="63" t="s">
+      <c r="E37" s="43"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="62" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="104" t="s">
+      <c r="B38" s="103" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="105"/>
+      <c r="C38" s="104"/>
       <c r="D38" s="8"/>
-      <c r="E38" s="44">
+      <c r="E38" s="43">
         <v>2</v>
       </c>
-      <c r="F38" s="45"/>
-      <c r="G38" s="63" t="s">
+      <c r="F38" s="44"/>
+      <c r="G38" s="62" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="39" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B39" s="88" t="s">
+      <c r="B39" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="C39" s="89"/>
+      <c r="C39" s="88"/>
       <c r="D39" s="9"/>
-      <c r="E39" s="51">
+      <c r="E39" s="50">
         <v>3</v>
       </c>
-      <c r="F39" s="47"/>
-      <c r="G39" s="65" t="s">
+      <c r="F39" s="46"/>
+      <c r="G39" s="64" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="40" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B40" s="86" t="s">
+      <c r="B40" s="85" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="87"/>
-      <c r="D40" s="56"/>
-      <c r="E40" s="83">
+      <c r="C40" s="86"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="82">
         <f>SUM(E3+E15+E25+F31)</f>
         <v>41</v>
       </c>
-      <c r="F40" s="84">
+      <c r="F40" s="83">
         <f>SUM(F4:F39)</f>
         <v>29</v>
       </c>
-      <c r="G40" s="56"/>
+      <c r="G40" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="39">
@@ -2652,11 +2651,11 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="55" t="s">
+      <c r="C2" s="106"/>
+      <c r="D2" s="54" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -2667,196 +2666,196 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="108" t="s">
+      <c r="B3" s="107" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="109"/>
-      <c r="D3" s="55" t="s">
+      <c r="C3" s="108"/>
+      <c r="D3" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="52"/>
+      <c r="E3" s="51"/>
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="122" t="s">
+      <c r="B4" s="121" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="123"/>
+      <c r="C4" s="122"/>
       <c r="D4" s="7"/>
-      <c r="E4" s="48">
+      <c r="E4" s="47">
         <v>2</v>
       </c>
-      <c r="F4" s="48"/>
+      <c r="F4" s="47"/>
     </row>
     <row r="5" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B5" s="90" t="s">
+      <c r="B5" s="89" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="91"/>
+      <c r="C5" s="90"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="45">
+      <c r="E5" s="44">
         <v>2</v>
       </c>
-      <c r="F5" s="45"/>
+      <c r="F5" s="44"/>
     </row>
     <row r="6" spans="2:6">
-      <c r="B6" s="100" t="s">
+      <c r="B6" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="101"/>
+      <c r="C6" s="100"/>
       <c r="D6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="90" t="s">
+      <c r="B7" s="89" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="91"/>
+      <c r="C7" s="90"/>
       <c r="D7" s="8"/>
-      <c r="E7" s="45">
+      <c r="E7" s="44">
         <v>2</v>
       </c>
-      <c r="F7" s="45"/>
+      <c r="F7" s="44"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="90" t="s">
+      <c r="B8" s="89" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="91"/>
+      <c r="C8" s="90"/>
       <c r="D8" s="8"/>
-      <c r="E8" s="45">
+      <c r="E8" s="44">
         <v>3</v>
       </c>
-      <c r="F8" s="45"/>
+      <c r="F8" s="44"/>
     </row>
     <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="90" t="s">
+      <c r="B9" s="89" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="91"/>
+      <c r="C9" s="90"/>
       <c r="D9" s="8"/>
-      <c r="E9" s="45">
+      <c r="E9" s="44">
         <v>2</v>
       </c>
-      <c r="F9" s="45"/>
+      <c r="F9" s="44"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="114" t="s">
+      <c r="B10" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="115"/>
-      <c r="D10" s="58" t="s">
+      <c r="C10" s="114"/>
+      <c r="D10" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="94" t="s">
+      <c r="B11" s="93" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="95"/>
+      <c r="C11" s="94"/>
       <c r="D11" s="8"/>
-      <c r="E11" s="45">
+      <c r="E11" s="44">
         <v>5</v>
       </c>
-      <c r="F11" s="45"/>
+      <c r="F11" s="44"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="94" t="s">
+      <c r="B12" s="93" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="95"/>
+      <c r="C12" s="94"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="45">
+      <c r="E12" s="44">
         <v>1</v>
       </c>
-      <c r="F12" s="45"/>
+      <c r="F12" s="44"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="94" t="s">
+      <c r="B13" s="93" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="95"/>
+      <c r="C13" s="94"/>
       <c r="D13" s="8"/>
-      <c r="E13" s="45">
+      <c r="E13" s="44">
         <v>2</v>
       </c>
-      <c r="F13" s="45"/>
+      <c r="F13" s="44"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="120" t="s">
+      <c r="B14" s="119" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="121"/>
+      <c r="C14" s="120"/>
       <c r="D14" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="54"/>
-      <c r="F14" s="49"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="48"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="90" t="s">
+      <c r="B15" s="89" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="91"/>
+      <c r="C15" s="90"/>
       <c r="D15" s="11"/>
-      <c r="E15" s="54">
+      <c r="E15" s="53">
         <v>5</v>
       </c>
-      <c r="F15" s="49"/>
+      <c r="F15" s="48"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="102" t="s">
+      <c r="B16" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="103"/>
+      <c r="C16" s="102"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="45"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="44"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="90" t="s">
+      <c r="B17" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="91"/>
+      <c r="C17" s="90"/>
       <c r="D17" s="8"/>
-      <c r="E17" s="44">
+      <c r="E17" s="43">
         <v>2</v>
       </c>
-      <c r="F17" s="45"/>
+      <c r="F17" s="44"/>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="102" t="s">
+      <c r="B18" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="103"/>
+      <c r="C18" s="102"/>
       <c r="D18" s="8"/>
-      <c r="E18" s="44"/>
-      <c r="F18" s="45"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="44"/>
     </row>
     <row r="19" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B19" s="116" t="s">
+      <c r="B19" s="115" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="117"/>
+      <c r="C19" s="116"/>
       <c r="D19" s="8"/>
-      <c r="E19" s="44">
+      <c r="E19" s="43">
         <v>2</v>
       </c>
-      <c r="F19" s="45"/>
+      <c r="F19" s="44"/>
     </row>
     <row r="20" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B20" s="118" t="s">
+      <c r="B20" s="117" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="119"/>
+      <c r="C20" s="118"/>
       <c r="D20" s="12"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="53"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -2892,11 +2891,11 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="105" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="107"/>
-      <c r="D2" s="55" t="s">
+      <c r="C2" s="106"/>
+      <c r="D2" s="54" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -2907,174 +2906,174 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="108" t="s">
+      <c r="B3" s="107" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="109"/>
-      <c r="D3" s="55" t="s">
+      <c r="C3" s="108"/>
+      <c r="D3" s="54" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="52"/>
+      <c r="E3" s="51"/>
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B4" s="122" t="s">
+      <c r="B4" s="121" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="123"/>
+      <c r="C4" s="122"/>
       <c r="D4" s="7"/>
-      <c r="E4" s="48">
+      <c r="E4" s="47">
         <v>3</v>
       </c>
-      <c r="F4" s="48"/>
+      <c r="F4" s="47"/>
     </row>
     <row r="5" spans="2:6">
-      <c r="B5" s="100" t="s">
+      <c r="B5" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="101"/>
+      <c r="C5" s="100"/>
       <c r="D5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
     </row>
     <row r="6" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B6" s="90" t="s">
+      <c r="B6" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="91"/>
+      <c r="C6" s="90"/>
       <c r="D6" s="8"/>
-      <c r="E6" s="45">
+      <c r="E6" s="44">
         <v>3</v>
       </c>
-      <c r="F6" s="45"/>
+      <c r="F6" s="44"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="114" t="s">
+      <c r="B7" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="115"/>
-      <c r="D7" s="58" t="s">
+      <c r="C7" s="114"/>
+      <c r="D7" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="59"/>
-      <c r="F7" s="59"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="94" t="s">
+      <c r="B8" s="93" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="95"/>
+      <c r="C8" s="94"/>
       <c r="D8" s="8"/>
-      <c r="E8" s="45">
+      <c r="E8" s="44">
         <v>3</v>
       </c>
-      <c r="F8" s="45"/>
+      <c r="F8" s="44"/>
     </row>
     <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="90" t="s">
+      <c r="B9" s="89" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="91"/>
+      <c r="C9" s="90"/>
       <c r="D9" s="8"/>
-      <c r="E9" s="45">
+      <c r="E9" s="44">
         <v>2</v>
       </c>
-      <c r="F9" s="45"/>
+      <c r="F9" s="44"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="100" t="s">
+      <c r="B10" s="99" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="101"/>
+      <c r="C10" s="100"/>
       <c r="D10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="48"/>
-      <c r="F10" s="48"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="90" t="s">
+      <c r="B11" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="91"/>
+      <c r="C11" s="90"/>
       <c r="D11" s="11"/>
-      <c r="E11" s="49">
+      <c r="E11" s="48">
         <v>2</v>
       </c>
-      <c r="F11" s="49"/>
+      <c r="F11" s="48"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="102" t="s">
+      <c r="B12" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="103"/>
+      <c r="C12" s="102"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="44"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="90" t="s">
+      <c r="B13" s="89" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="91"/>
+      <c r="C13" s="90"/>
       <c r="D13" s="8"/>
-      <c r="E13" s="45">
+      <c r="E13" s="44">
         <v>1</v>
       </c>
-      <c r="F13" s="45"/>
+      <c r="F13" s="44"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="90" t="s">
+      <c r="B14" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="91"/>
+      <c r="C14" s="90"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="45">
+      <c r="E14" s="44">
         <v>1</v>
       </c>
-      <c r="F14" s="45"/>
+      <c r="F14" s="44"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="102" t="s">
+      <c r="B15" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="103"/>
+      <c r="C15" s="102"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
+      <c r="E15" s="44"/>
+      <c r="F15" s="44"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="94" t="s">
+      <c r="B16" s="93" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="95"/>
+      <c r="C16" s="94"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="45">
+      <c r="E16" s="44">
         <v>1</v>
       </c>
-      <c r="F16" s="45"/>
+      <c r="F16" s="44"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="94" t="s">
+      <c r="B17" s="93" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="95"/>
+      <c r="C17" s="94"/>
       <c r="D17" s="8"/>
-      <c r="E17" s="45">
+      <c r="E17" s="44">
         <v>1</v>
       </c>
-      <c r="F17" s="45"/>
+      <c r="F17" s="44"/>
     </row>
     <row r="18" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B18" s="86" t="s">
+      <c r="B18" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="87"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
+      <c r="C18" s="86"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="56"/>
+      <c r="F18" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -3107,34 +3106,34 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="124" t="s">
+      <c r="C1" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
     </row>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="35" t="s">
+      <c r="D2" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="35" t="s">
+      <c r="E2" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="G2" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="36" t="s">
+      <c r="H2" s="35" t="s">
         <v>21</v>
       </c>
       <c r="J2" t="s">
@@ -3142,113 +3141,113 @@
       </c>
     </row>
     <row r="3" spans="2:11">
-      <c r="B3" s="31"/>
-      <c r="D3" s="32">
+      <c r="B3" s="30"/>
+      <c r="D3" s="31">
         <v>46266</v>
       </c>
-      <c r="E3" s="32">
+      <c r="E3" s="31">
         <f>SUM(D3)+1</f>
         <v>46267</v>
       </c>
-      <c r="F3" s="32">
+      <c r="F3" s="31">
         <f t="shared" ref="F3:H3" si="0">SUM(E3)+1</f>
         <v>46268</v>
       </c>
-      <c r="G3" s="32">
+      <c r="G3" s="31">
         <f t="shared" si="0"/>
         <v>46269</v>
       </c>
-      <c r="H3" s="33">
+      <c r="H3" s="32">
         <f t="shared" si="0"/>
         <v>46270</v>
       </c>
-      <c r="J3" s="19"/>
+      <c r="J3" s="18"/>
       <c r="K3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="23">
+      <c r="B4" s="22">
         <f>SUM(H3)+1</f>
         <v>46271</v>
       </c>
-      <c r="C4" s="22">
+      <c r="C4" s="21">
         <f>SUM(B4)+1</f>
         <v>46272</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="21">
         <f t="shared" ref="D4:H4" si="1">SUM(C4)+1</f>
         <v>46273</v>
       </c>
-      <c r="E4" s="60">
+      <c r="E4" s="59">
         <f t="shared" si="1"/>
         <v>46274</v>
       </c>
-      <c r="F4" s="60">
+      <c r="F4" s="59">
         <f t="shared" si="1"/>
         <v>46275</v>
       </c>
-      <c r="G4" s="60">
+      <c r="G4" s="59">
         <f t="shared" si="1"/>
         <v>46276</v>
       </c>
-      <c r="H4" s="61">
+      <c r="H4" s="60">
         <f t="shared" si="1"/>
         <v>46277</v>
       </c>
-      <c r="J4" s="20"/>
+      <c r="J4" s="19"/>
       <c r="K4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="62">
+      <c r="B5" s="61">
         <f>SUM(H4)+1</f>
         <v>46278</v>
       </c>
-      <c r="C5" s="60">
+      <c r="C5" s="59">
         <f>SUM(B5)+1</f>
         <v>46279</v>
       </c>
-      <c r="D5" s="60">
+      <c r="D5" s="59">
         <f t="shared" ref="D5:H5" si="2">SUM(C5)+1</f>
         <v>46280</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="59">
         <f t="shared" si="2"/>
         <v>46281</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="59">
         <f t="shared" si="2"/>
         <v>46282</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="59">
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="60">
         <f t="shared" si="2"/>
         <v>46284</v>
       </c>
-      <c r="J5" s="21"/>
+      <c r="J5" s="20"/>
       <c r="K5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" s="17">
+      <c r="B6" s="61">
         <f>SUM(H5)+1</f>
         <v>46285</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="59">
         <f>SUM(B6)+1</f>
         <v>46286</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="59">
         <f t="shared" ref="D6:H6" si="3">SUM(C6)+1</f>
         <v>46287</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="59">
         <f t="shared" si="3"/>
         <v>46288</v>
       </c>
@@ -3260,29 +3259,29 @@
         <f t="shared" si="3"/>
         <v>46290</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="17">
         <f t="shared" si="3"/>
         <v>46291</v>
       </c>
-      <c r="J6" s="29"/>
+      <c r="J6" s="28"/>
       <c r="K6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B7" s="39">
+      <c r="B7" s="38">
         <f>SUM(H6)+1</f>
         <v>46292</v>
       </c>
-      <c r="C7" s="40">
+      <c r="C7" s="39">
         <f>SUM(B7)+1</f>
         <v>46293</v>
       </c>
-      <c r="D7" s="40">
+      <c r="D7" s="39">
         <f t="shared" ref="D7:E7" si="4">SUM(C7)+1</f>
         <v>46294</v>
       </c>
-      <c r="E7" s="40">
+      <c r="E7" s="39">
         <f t="shared" si="4"/>
         <v>46295</v>
       </c>
@@ -3291,89 +3290,89 @@
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="2:11">
-      <c r="B8" s="31"/>
+      <c r="B8" s="30"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="37">
+      <c r="F8" s="36">
         <f>SUM(E7)+1</f>
         <v>46296</v>
       </c>
-      <c r="G8" s="37">
+      <c r="G8" s="36">
         <f>SUM(F8)+1</f>
         <v>46297</v>
       </c>
-      <c r="H8" s="38">
+      <c r="H8" s="37">
         <f>SUM(G8)+1</f>
         <v>46298</v>
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="24">
+      <c r="B9" s="23">
         <f>SUM(H8)+1</f>
         <v>46299</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="24">
         <f>SUM(B9)+1</f>
         <v>46300</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="24">
         <f t="shared" ref="D9:H9" si="5">SUM(C9)+1</f>
         <v>46301</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="24">
         <f t="shared" si="5"/>
         <v>46302</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="24">
         <f t="shared" si="5"/>
         <v>46303</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="24">
         <f t="shared" si="5"/>
         <v>46304</v>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="25">
         <f t="shared" si="5"/>
         <v>46305</v>
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="28">
+      <c r="B10" s="27">
         <f t="shared" ref="B10:B12" si="6">SUM(H9)+1</f>
         <v>46306</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="26">
         <f>SUM(B10)+1</f>
         <v>46307</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="26">
         <f t="shared" ref="D10:G10" si="7">SUM(C10)+1</f>
         <v>46308</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="26">
         <f t="shared" si="7"/>
         <v>46309</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="26">
         <f t="shared" si="7"/>
         <v>46310</v>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="29">
         <f t="shared" si="7"/>
         <v>46311</v>
       </c>
-      <c r="H10" s="67">
+      <c r="H10" s="66">
         <f>SUM(G10)+1</f>
         <v>46312</v>
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="66">
+      <c r="B11" s="65">
         <f t="shared" si="6"/>
         <v>46313</v>
       </c>
-      <c r="C11" s="43">
+      <c r="C11" s="42">
         <f>SUM(B11)+1</f>
         <v>46314</v>
       </c>
@@ -3393,13 +3392,13 @@
         <f t="shared" ref="G11" si="9">SUM(F11)+1</f>
         <v>46318</v>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="40">
         <f>SUM(G11)+1</f>
         <v>46319</v>
       </c>
     </row>
     <row r="12" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B12" s="42">
+      <c r="B12" s="41">
         <f t="shared" si="6"/>
         <v>46320</v>
       </c>

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nodasouma\Documents\GitHub\GlassesGame\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ayato Terao\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09055683-AC3C-46D9-9D9B-97B912B79C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2054054-4258-4099-88D8-9D9E75E6F3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="-14925" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>
@@ -1149,17 +1149,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top/>
       <bottom style="thin">
@@ -1333,11 +1322,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1423,9 +1421,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1438,19 +1433,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1459,186 +1454,195 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="37" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1947,17 +1951,17 @@
   <sheetData>
     <row r="1" spans="2:11" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B2" s="105" t="s">
+      <c r="B2" s="92" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="106"/>
-      <c r="D2" s="54" t="s">
+      <c r="C2" s="93"/>
+      <c r="D2" s="53" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="67" t="s">
+      <c r="F2" s="66" t="s">
         <v>8</v>
       </c>
       <c r="G2" s="12" t="s">
@@ -1965,62 +1969,62 @@
       </c>
     </row>
     <row r="3" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="54" t="s">
+      <c r="C3" s="95"/>
+      <c r="D3" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="51">
+      <c r="E3" s="50">
         <f>SUM(E4:E14)</f>
         <v>13</v>
       </c>
-      <c r="F3" s="52">
+      <c r="F3" s="51">
         <f>SUM(F4:F14)</f>
-        <v>10</v>
-      </c>
-      <c r="G3" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="I3" s="72" t="s">
+      <c r="I3" s="71" t="s">
         <v>79</v>
       </c>
-      <c r="J3" s="76">
+      <c r="J3" s="75">
         <f ca="1">TODAY()</f>
-        <v>46289</v>
-      </c>
-      <c r="K3" s="54" t="s">
+        <v>46290</v>
+      </c>
+      <c r="K3" s="53" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="109" t="s">
+      <c r="B4" s="98" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="110"/>
+      <c r="C4" s="99"/>
       <c r="D4" s="11"/>
       <c r="E4" s="48"/>
       <c r="F4" s="48"/>
-      <c r="G4" s="63" t="s">
+      <c r="G4" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="I4" s="77" t="s">
+      <c r="I4" s="76" t="s">
         <v>80</v>
       </c>
-      <c r="J4" s="73">
+      <c r="J4" s="72">
         <v>46295</v>
       </c>
-      <c r="K4" s="71" t="str">
+      <c r="K4" s="70" t="str">
         <f ca="1">SUM($J4-J3)&amp; "日"</f>
-        <v>6日</v>
+        <v>5日</v>
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="89" t="s">
+      <c r="B5" s="100" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="90"/>
+      <c r="C5" s="101"/>
       <c r="D5" s="8"/>
       <c r="E5" s="44">
         <v>2</v>
@@ -2028,25 +2032,25 @@
       <c r="F5" s="44">
         <v>2</v>
       </c>
-      <c r="G5" s="63" t="s">
+      <c r="G5" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="I5" s="78" t="s">
+      <c r="I5" s="77" t="s">
         <v>81</v>
       </c>
-      <c r="J5" s="74">
+      <c r="J5" s="73">
         <v>46305</v>
       </c>
-      <c r="K5" s="69" t="str">
+      <c r="K5" s="68" t="str">
         <f ca="1">SUM($J5-J3)&amp; "日"</f>
-        <v>16日</v>
+        <v>15日</v>
       </c>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" s="89" t="s">
+      <c r="B6" s="100" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="90"/>
+      <c r="C6" s="101"/>
       <c r="D6" s="8"/>
       <c r="E6" s="44">
         <v>1</v>
@@ -2054,25 +2058,25 @@
       <c r="F6" s="44">
         <v>2</v>
       </c>
-      <c r="G6" s="63" t="s">
+      <c r="G6" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="I6" s="79" t="s">
+      <c r="I6" s="78" t="s">
         <v>82</v>
       </c>
-      <c r="J6" s="74">
+      <c r="J6" s="73">
         <v>46310</v>
       </c>
-      <c r="K6" s="69" t="str">
+      <c r="K6" s="68" t="str">
         <f ca="1">SUM($J6-J3)&amp; "日"</f>
-        <v>21日</v>
+        <v>20日</v>
       </c>
     </row>
     <row r="7" spans="2:11">
-      <c r="B7" s="97" t="s">
+      <c r="B7" s="84" t="s">
         <v>90</v>
       </c>
-      <c r="C7" s="98"/>
+      <c r="C7" s="85"/>
       <c r="D7" s="8"/>
       <c r="E7" s="44">
         <v>2</v>
@@ -2080,63 +2084,65 @@
       <c r="F7" s="48">
         <v>2</v>
       </c>
-      <c r="G7" s="63" t="s">
+      <c r="G7" s="62" t="s">
         <v>89</v>
       </c>
-      <c r="I7" s="80" t="s">
+      <c r="I7" s="79" t="s">
         <v>83</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="73">
         <v>46313</v>
       </c>
-      <c r="K7" s="69" t="str">
+      <c r="K7" s="68" t="str">
         <f ca="1">SUM($J7-J3)&amp; "日"</f>
-        <v>24日</v>
+        <v>23日</v>
       </c>
     </row>
     <row r="8" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B8" s="97" t="s">
+      <c r="B8" s="84" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="98"/>
+      <c r="C8" s="85"/>
       <c r="D8" s="10"/>
       <c r="E8" s="45">
         <v>2</v>
       </c>
-      <c r="F8" s="45"/>
+      <c r="F8" s="45">
+        <v>1</v>
+      </c>
       <c r="G8" s="62" t="s">
-        <v>85</v>
-      </c>
-      <c r="I8" s="81" t="s">
+        <v>89</v>
+      </c>
+      <c r="I8" s="80" t="s">
         <v>78</v>
       </c>
-      <c r="J8" s="75">
+      <c r="J8" s="74">
         <v>46314</v>
       </c>
-      <c r="K8" s="70" t="str">
+      <c r="K8" s="69" t="str">
         <f ca="1">SUM(J8-J3)&amp; "日"</f>
-        <v>25日</v>
+        <v>24日</v>
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="97" t="s">
+      <c r="B9" s="84" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="98"/>
+      <c r="C9" s="85"/>
       <c r="D9" s="10"/>
       <c r="E9" s="45">
         <v>2</v>
       </c>
       <c r="F9" s="45"/>
-      <c r="G9" s="62" t="s">
+      <c r="G9" s="61" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="111" t="s">
+      <c r="B10" s="88" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="112"/>
+      <c r="C10" s="89"/>
       <c r="D10" s="8"/>
       <c r="E10" s="44">
         <v>1</v>
@@ -2144,27 +2150,27 @@
       <c r="F10" s="44">
         <v>1</v>
       </c>
-      <c r="G10" s="62" t="s">
+      <c r="G10" s="61" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="97" t="s">
+      <c r="B11" s="84" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="98"/>
+      <c r="C11" s="85"/>
       <c r="D11" s="8"/>
       <c r="E11" s="44"/>
       <c r="F11" s="45"/>
-      <c r="G11" s="62" t="s">
+      <c r="G11" s="61" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="12" spans="2:11">
-      <c r="B12" s="93" t="s">
+      <c r="B12" s="86" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="94"/>
+      <c r="C12" s="87"/>
       <c r="D12" s="8"/>
       <c r="E12" s="44">
         <v>1</v>
@@ -2172,15 +2178,15 @@
       <c r="F12" s="44">
         <v>1</v>
       </c>
-      <c r="G12" s="62" t="s">
+      <c r="G12" s="61" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="13" spans="2:11">
-      <c r="B13" s="89" t="s">
+      <c r="B13" s="100" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="90"/>
+      <c r="C13" s="101"/>
       <c r="D13" s="8"/>
       <c r="E13" s="44">
         <v>1</v>
@@ -2188,15 +2194,15 @@
       <c r="F13" s="44">
         <v>1</v>
       </c>
-      <c r="G13" s="62" t="s">
+      <c r="G13" s="61" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="14" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B14" s="91" t="s">
+      <c r="B14" s="106" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="92"/>
+      <c r="C14" s="107"/>
       <c r="D14" s="10"/>
       <c r="E14" s="45">
         <v>1</v>
@@ -2204,420 +2210,397 @@
       <c r="F14" s="45">
         <v>1</v>
       </c>
-      <c r="G14" s="62" t="s">
+      <c r="G14" s="61" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="15" spans="2:11">
-      <c r="B15" s="99" t="s">
+      <c r="B15" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="100"/>
+      <c r="C15" s="97"/>
       <c r="D15" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="47">
+      <c r="E15" s="125">
         <f>SUM(E16:E24)</f>
         <v>16</v>
       </c>
       <c r="F15" s="47">
         <v>8</v>
       </c>
-      <c r="G15" s="68" t="s">
+      <c r="G15" s="67" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="16" spans="2:11">
-      <c r="B16" s="97" t="s">
+      <c r="B16" s="84" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="98"/>
+      <c r="C16" s="85"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="44">
+      <c r="E16" s="123">
         <v>3</v>
       </c>
       <c r="F16" s="44">
         <v>1</v>
       </c>
-      <c r="G16" s="62" t="s">
+      <c r="G16" s="61" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="97" t="s">
+      <c r="B17" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="98"/>
+      <c r="C17" s="85"/>
       <c r="D17" s="8"/>
-      <c r="E17" s="44">
+      <c r="E17" s="123">
         <v>3</v>
       </c>
       <c r="F17" s="44">
         <v>1</v>
       </c>
-      <c r="G17" s="62" t="s">
+      <c r="G17" s="61" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="97" t="s">
+      <c r="B18" s="84" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="98"/>
+      <c r="C18" s="85"/>
       <c r="D18" s="8"/>
-      <c r="E18" s="44">
+      <c r="E18" s="123">
         <v>3</v>
       </c>
       <c r="F18" s="44">
         <v>1</v>
       </c>
-      <c r="G18" s="62" t="s">
+      <c r="G18" s="61" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="97" t="s">
+      <c r="B19" s="84" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="98"/>
+      <c r="C19" s="85"/>
       <c r="D19" s="10"/>
-      <c r="E19" s="44">
+      <c r="E19" s="123">
         <v>3</v>
       </c>
-      <c r="F19" s="124">
+      <c r="F19" s="44">
         <v>1</v>
       </c>
-      <c r="G19" s="62" t="s">
+      <c r="G19" s="61" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="97" t="s">
+      <c r="B20" s="84" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="98"/>
+      <c r="C20" s="85"/>
       <c r="D20" s="8"/>
-      <c r="E20" s="49">
+      <c r="E20" s="124">
         <v>1</v>
       </c>
-      <c r="F20" s="124">
+      <c r="F20" s="44">
         <v>1</v>
       </c>
-      <c r="G20" s="62" t="s">
+      <c r="G20" s="61" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="111" t="s">
+      <c r="B21" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="112"/>
+      <c r="C21" s="89"/>
       <c r="D21" s="8"/>
-      <c r="E21" s="44"/>
-      <c r="F21" s="124">
+      <c r="E21" s="123"/>
+      <c r="F21" s="44">
         <v>3</v>
       </c>
-      <c r="G21" s="62" t="s">
+      <c r="G21" s="61" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="93" t="s">
+      <c r="B22" s="86" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="94"/>
+      <c r="C22" s="87"/>
       <c r="D22" s="8"/>
-      <c r="E22" s="44">
+      <c r="E22" s="123">
         <v>1</v>
       </c>
       <c r="F22" s="44">
         <v>1</v>
       </c>
-      <c r="G22" s="62" t="s">
+      <c r="G22" s="61" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="93" t="s">
+      <c r="B23" s="86" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="94"/>
+      <c r="C23" s="87"/>
       <c r="D23" s="8"/>
-      <c r="E23" s="44">
+      <c r="E23" s="123">
         <v>1</v>
       </c>
       <c r="F23" s="44">
         <v>1</v>
       </c>
-      <c r="G23" s="62" t="s">
+      <c r="G23" s="61" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B24" s="95" t="s">
+      <c r="B24" s="108" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="96"/>
+      <c r="C24" s="109"/>
       <c r="D24" s="9"/>
-      <c r="E24" s="46">
+      <c r="E24" s="126">
         <v>1</v>
       </c>
       <c r="F24" s="46">
         <v>1</v>
       </c>
-      <c r="G24" s="62" t="s">
+      <c r="G24" s="61" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="25" spans="2:7">
-      <c r="B25" s="113" t="s">
+      <c r="B25" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="114"/>
-      <c r="D25" s="57" t="s">
+      <c r="C25" s="91"/>
+      <c r="D25" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="58">
+      <c r="E25" s="57">
         <f>SUM(E26:E30)</f>
         <v>12</v>
       </c>
-      <c r="F25" s="58"/>
-      <c r="G25" s="68" t="s">
+      <c r="F25" s="57"/>
+      <c r="G25" s="67" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="26" spans="2:7">
-      <c r="B26" s="111" t="s">
+      <c r="B26" s="88" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="112"/>
+      <c r="C26" s="89"/>
       <c r="D26" s="8"/>
       <c r="E26" s="44">
         <v>5</v>
       </c>
       <c r="F26" s="44"/>
-      <c r="G26" s="62" t="s">
+      <c r="G26" s="61" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="111" t="s">
+      <c r="B27" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="112"/>
+      <c r="C27" s="89"/>
       <c r="D27" s="8"/>
       <c r="E27" s="44"/>
       <c r="F27" s="44"/>
-      <c r="G27" s="62" t="s">
+      <c r="G27" s="61" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="93" t="s">
+      <c r="B28" s="86" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="94"/>
+      <c r="C28" s="87"/>
       <c r="D28" s="8"/>
       <c r="E28" s="44">
         <v>2</v>
       </c>
       <c r="F28" s="44"/>
-      <c r="G28" s="62" t="s">
+      <c r="G28" s="61" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="93" t="s">
+      <c r="B29" s="86" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="94"/>
+      <c r="C29" s="87"/>
       <c r="D29" s="8"/>
       <c r="E29" s="44">
         <v>2</v>
       </c>
       <c r="F29" s="44"/>
-      <c r="G29" s="62" t="s">
+      <c r="G29" s="61" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B30" s="87" t="s">
+      <c r="B30" s="104" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="88"/>
+      <c r="C30" s="105"/>
       <c r="D30" s="9"/>
       <c r="E30" s="46">
         <v>3</v>
       </c>
       <c r="F30" s="46"/>
-      <c r="G30" s="64" t="s">
+      <c r="G30" s="63" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="31" spans="2:7">
-      <c r="B31" s="99" t="s">
+      <c r="B31" s="96" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="100"/>
+      <c r="C31" s="97"/>
       <c r="D31" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="84">
+      <c r="E31" s="83">
         <f>SUM(E32:E39)</f>
         <v>11</v>
       </c>
       <c r="F31" s="47"/>
-      <c r="G31" s="68" t="s">
+      <c r="G31" s="67" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="32" spans="2:7">
-      <c r="B32" s="97" t="s">
+      <c r="B32" s="84" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="98"/>
+      <c r="C32" s="85"/>
       <c r="D32" s="11"/>
-      <c r="E32" s="53"/>
+      <c r="E32" s="52"/>
       <c r="F32" s="48"/>
-      <c r="G32" s="62" t="s">
+      <c r="G32" s="61" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="89" t="s">
+      <c r="B33" s="100" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="90"/>
+      <c r="C33" s="101"/>
       <c r="D33" s="11"/>
-      <c r="E33" s="53">
+      <c r="E33" s="52">
         <v>2</v>
       </c>
       <c r="F33" s="48"/>
-      <c r="G33" s="62" t="s">
+      <c r="G33" s="61" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="101" t="s">
+      <c r="B34" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="102"/>
+      <c r="C34" s="111"/>
       <c r="D34" s="8"/>
       <c r="E34" s="43"/>
       <c r="F34" s="44"/>
-      <c r="G34" s="62" t="s">
+      <c r="G34" s="61" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="97" t="s">
+      <c r="B35" s="84" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="98"/>
+      <c r="C35" s="85"/>
       <c r="D35" s="8"/>
       <c r="E35" s="43">
         <v>2</v>
       </c>
       <c r="F35" s="44"/>
-      <c r="G35" s="62" t="s">
+      <c r="G35" s="61" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="97" t="s">
+      <c r="B36" s="84" t="s">
         <v>60</v>
       </c>
-      <c r="C36" s="98"/>
+      <c r="C36" s="85"/>
       <c r="D36" s="8"/>
       <c r="E36" s="43">
         <v>2</v>
       </c>
       <c r="F36" s="44"/>
-      <c r="G36" s="62" t="s">
+      <c r="G36" s="61" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="101" t="s">
+      <c r="B37" s="110" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="102"/>
+      <c r="C37" s="111"/>
       <c r="D37" s="8"/>
       <c r="E37" s="43"/>
       <c r="F37" s="44"/>
-      <c r="G37" s="62" t="s">
+      <c r="G37" s="61" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="103" t="s">
+      <c r="B38" s="112" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="104"/>
+      <c r="C38" s="113"/>
       <c r="D38" s="8"/>
       <c r="E38" s="43">
         <v>2</v>
       </c>
       <c r="F38" s="44"/>
-      <c r="G38" s="62" t="s">
+      <c r="G38" s="61" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="39" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B39" s="87" t="s">
+      <c r="B39" s="104" t="s">
         <v>64</v>
       </c>
-      <c r="C39" s="88"/>
+      <c r="C39" s="105"/>
       <c r="D39" s="9"/>
-      <c r="E39" s="50">
+      <c r="E39" s="49">
         <v>3</v>
       </c>
       <c r="F39" s="46"/>
-      <c r="G39" s="64" t="s">
+      <c r="G39" s="63" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="40" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B40" s="85" t="s">
+      <c r="B40" s="102" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="86"/>
-      <c r="D40" s="55"/>
-      <c r="E40" s="82">
+      <c r="C40" s="103"/>
+      <c r="D40" s="54"/>
+      <c r="E40" s="81">
         <f>SUM(E3+E15+E25+F31)</f>
         <v>41</v>
       </c>
-      <c r="F40" s="83">
+      <c r="F40" s="82">
         <f>SUM(F4:F39)</f>
-        <v>29</v>
-      </c>
-      <c r="G40" s="55"/>
+        <v>30</v>
+      </c>
+      <c r="G40" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B13:C13"/>
@@ -2634,6 +2617,29 @@
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2651,11 +2657,11 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="105" t="s">
+      <c r="B2" s="92" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="106"/>
-      <c r="D2" s="54" t="s">
+      <c r="C2" s="93"/>
+      <c r="D2" s="53" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -2666,21 +2672,21 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="54" t="s">
+      <c r="C3" s="95"/>
+      <c r="D3" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="51"/>
+      <c r="E3" s="50"/>
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="121" t="s">
+      <c r="B4" s="114" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="122"/>
+      <c r="C4" s="115"/>
       <c r="D4" s="7"/>
       <c r="E4" s="47">
         <v>2</v>
@@ -2688,10 +2694,10 @@
       <c r="F4" s="47"/>
     </row>
     <row r="5" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B5" s="89" t="s">
+      <c r="B5" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="90"/>
+      <c r="C5" s="101"/>
       <c r="D5" s="8"/>
       <c r="E5" s="44">
         <v>2</v>
@@ -2699,10 +2705,10 @@
       <c r="F5" s="44"/>
     </row>
     <row r="6" spans="2:6">
-      <c r="B6" s="99" t="s">
+      <c r="B6" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="100"/>
+      <c r="C6" s="97"/>
       <c r="D6" s="7" t="s">
         <v>11</v>
       </c>
@@ -2710,10 +2716,10 @@
       <c r="F6" s="47"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="89" t="s">
+      <c r="B7" s="100" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="90"/>
+      <c r="C7" s="101"/>
       <c r="D7" s="8"/>
       <c r="E7" s="44">
         <v>2</v>
@@ -2721,10 +2727,10 @@
       <c r="F7" s="44"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="89" t="s">
+      <c r="B8" s="100" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="90"/>
+      <c r="C8" s="101"/>
       <c r="D8" s="8"/>
       <c r="E8" s="44">
         <v>3</v>
@@ -2732,10 +2738,10 @@
       <c r="F8" s="44"/>
     </row>
     <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="89" t="s">
+      <c r="B9" s="100" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="90"/>
+      <c r="C9" s="101"/>
       <c r="D9" s="8"/>
       <c r="E9" s="44">
         <v>2</v>
@@ -2743,21 +2749,21 @@
       <c r="F9" s="44"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="113" t="s">
+      <c r="B10" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="114"/>
-      <c r="D10" s="57" t="s">
+      <c r="C10" s="91"/>
+      <c r="D10" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="93" t="s">
+      <c r="B11" s="86" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="94"/>
+      <c r="C11" s="87"/>
       <c r="D11" s="8"/>
       <c r="E11" s="44">
         <v>5</v>
@@ -2765,10 +2771,10 @@
       <c r="F11" s="44"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="93" t="s">
+      <c r="B12" s="86" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="94"/>
+      <c r="C12" s="87"/>
       <c r="D12" s="8"/>
       <c r="E12" s="44">
         <v>1</v>
@@ -2776,10 +2782,10 @@
       <c r="F12" s="44"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="93" t="s">
+      <c r="B13" s="86" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="94"/>
+      <c r="C13" s="87"/>
       <c r="D13" s="8"/>
       <c r="E13" s="44">
         <v>2</v>
@@ -2787,41 +2793,41 @@
       <c r="F13" s="44"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="119" t="s">
+      <c r="B14" s="116" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="120"/>
+      <c r="C14" s="117"/>
       <c r="D14" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="53"/>
+      <c r="E14" s="52"/>
       <c r="F14" s="48"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="89" t="s">
+      <c r="B15" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="90"/>
+      <c r="C15" s="101"/>
       <c r="D15" s="11"/>
-      <c r="E15" s="53">
+      <c r="E15" s="52">
         <v>5</v>
       </c>
       <c r="F15" s="48"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="101" t="s">
+      <c r="B16" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="102"/>
+      <c r="C16" s="111"/>
       <c r="D16" s="8"/>
       <c r="E16" s="43"/>
       <c r="F16" s="44"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="89" t="s">
+      <c r="B17" s="100" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="90"/>
+      <c r="C17" s="101"/>
       <c r="D17" s="8"/>
       <c r="E17" s="43">
         <v>2</v>
@@ -2829,19 +2835,19 @@
       <c r="F17" s="44"/>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="101" t="s">
+      <c r="B18" s="110" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="102"/>
+      <c r="C18" s="111"/>
       <c r="D18" s="8"/>
       <c r="E18" s="43"/>
       <c r="F18" s="44"/>
     </row>
     <row r="19" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B19" s="115" t="s">
+      <c r="B19" s="118" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="116"/>
+      <c r="C19" s="119"/>
       <c r="D19" s="8"/>
       <c r="E19" s="43">
         <v>2</v>
@@ -2849,16 +2855,27 @@
       <c r="F19" s="44"/>
     </row>
     <row r="20" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B20" s="117" t="s">
+      <c r="B20" s="120" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="118"/>
+      <c r="C20" s="121"/>
       <c r="D20" s="12"/>
-      <c r="E20" s="51"/>
-      <c r="F20" s="52"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
@@ -2867,17 +2884,6 @@
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2891,11 +2897,11 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="105" t="s">
+      <c r="B2" s="92" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="106"/>
-      <c r="D2" s="54" t="s">
+      <c r="C2" s="93"/>
+      <c r="D2" s="53" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -2906,21 +2912,21 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="54" t="s">
+      <c r="C3" s="95"/>
+      <c r="D3" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="51"/>
+      <c r="E3" s="50"/>
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B4" s="121" t="s">
+      <c r="B4" s="114" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="122"/>
+      <c r="C4" s="115"/>
       <c r="D4" s="7"/>
       <c r="E4" s="47">
         <v>3</v>
@@ -2928,10 +2934,10 @@
       <c r="F4" s="47"/>
     </row>
     <row r="5" spans="2:6">
-      <c r="B5" s="99" t="s">
+      <c r="B5" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="100"/>
+      <c r="C5" s="97"/>
       <c r="D5" s="7" t="s">
         <v>11</v>
       </c>
@@ -2939,10 +2945,10 @@
       <c r="F5" s="47"/>
     </row>
     <row r="6" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B6" s="89" t="s">
+      <c r="B6" s="100" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="90"/>
+      <c r="C6" s="101"/>
       <c r="D6" s="8"/>
       <c r="E6" s="44">
         <v>3</v>
@@ -2950,21 +2956,21 @@
       <c r="F6" s="44"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="113" t="s">
+      <c r="B7" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="114"/>
-      <c r="D7" s="57" t="s">
+      <c r="C7" s="91"/>
+      <c r="D7" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="93" t="s">
+      <c r="B8" s="86" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="94"/>
+      <c r="C8" s="87"/>
       <c r="D8" s="8"/>
       <c r="E8" s="44">
         <v>3</v>
@@ -2972,10 +2978,10 @@
       <c r="F8" s="44"/>
     </row>
     <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="89" t="s">
+      <c r="B9" s="100" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="90"/>
+      <c r="C9" s="101"/>
       <c r="D9" s="8"/>
       <c r="E9" s="44">
         <v>2</v>
@@ -2983,10 +2989,10 @@
       <c r="F9" s="44"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="99" t="s">
+      <c r="B10" s="96" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="100"/>
+      <c r="C10" s="97"/>
       <c r="D10" s="7" t="s">
         <v>14</v>
       </c>
@@ -2994,10 +3000,10 @@
       <c r="F10" s="47"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="89" t="s">
+      <c r="B11" s="100" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="90"/>
+      <c r="C11" s="101"/>
       <c r="D11" s="11"/>
       <c r="E11" s="48">
         <v>2</v>
@@ -3005,19 +3011,19 @@
       <c r="F11" s="48"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="101" t="s">
+      <c r="B12" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="102"/>
+      <c r="C12" s="111"/>
       <c r="D12" s="8"/>
       <c r="E12" s="44"/>
       <c r="F12" s="44"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="89" t="s">
+      <c r="B13" s="100" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="90"/>
+      <c r="C13" s="101"/>
       <c r="D13" s="8"/>
       <c r="E13" s="44">
         <v>1</v>
@@ -3025,10 +3031,10 @@
       <c r="F13" s="44"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="89" t="s">
+      <c r="B14" s="100" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="90"/>
+      <c r="C14" s="101"/>
       <c r="D14" s="8"/>
       <c r="E14" s="44">
         <v>1</v>
@@ -3036,19 +3042,19 @@
       <c r="F14" s="44"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="101" t="s">
+      <c r="B15" s="110" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="102"/>
+      <c r="C15" s="111"/>
       <c r="D15" s="8"/>
       <c r="E15" s="44"/>
       <c r="F15" s="44"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="93" t="s">
+      <c r="B16" s="86" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="94"/>
+      <c r="C16" s="87"/>
       <c r="D16" s="8"/>
       <c r="E16" s="44">
         <v>1</v>
@@ -3056,10 +3062,10 @@
       <c r="F16" s="44"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="93" t="s">
+      <c r="B17" s="86" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="94"/>
+      <c r="C17" s="87"/>
       <c r="D17" s="8"/>
       <c r="E17" s="44">
         <v>1</v>
@@ -3067,26 +3073,16 @@
       <c r="F17" s="44"/>
     </row>
     <row r="18" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B18" s="85" t="s">
+      <c r="B18" s="102" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="86"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="56"/>
+      <c r="C18" s="103"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="55"/>
+      <c r="F18" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B11:C11"/>
@@ -3094,6 +3090,16 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3106,13 +3112,13 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="123" t="s">
+      <c r="C1" s="122" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
     </row>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
       <c r="B2" s="33" t="s">
@@ -3179,19 +3185,19 @@
         <f t="shared" ref="D4:H4" si="1">SUM(C4)+1</f>
         <v>46273</v>
       </c>
-      <c r="E4" s="59">
+      <c r="E4" s="58">
         <f t="shared" si="1"/>
         <v>46274</v>
       </c>
-      <c r="F4" s="59">
+      <c r="F4" s="58">
         <f t="shared" si="1"/>
         <v>46275</v>
       </c>
-      <c r="G4" s="59">
+      <c r="G4" s="58">
         <f t="shared" si="1"/>
         <v>46276</v>
       </c>
-      <c r="H4" s="60">
+      <c r="H4" s="59">
         <f t="shared" si="1"/>
         <v>46277</v>
       </c>
@@ -3201,31 +3207,31 @@
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="61">
+      <c r="B5" s="60">
         <f>SUM(H4)+1</f>
         <v>46278</v>
       </c>
-      <c r="C5" s="59">
+      <c r="C5" s="58">
         <f>SUM(B5)+1</f>
         <v>46279</v>
       </c>
-      <c r="D5" s="59">
+      <c r="D5" s="58">
         <f t="shared" ref="D5:H5" si="2">SUM(C5)+1</f>
         <v>46280</v>
       </c>
-      <c r="E5" s="59">
+      <c r="E5" s="58">
         <f t="shared" si="2"/>
         <v>46281</v>
       </c>
-      <c r="F5" s="59">
+      <c r="F5" s="58">
         <f t="shared" si="2"/>
         <v>46282</v>
       </c>
-      <c r="G5" s="59">
+      <c r="G5" s="58">
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="H5" s="60">
+      <c r="H5" s="59">
         <f t="shared" si="2"/>
         <v>46284</v>
       </c>
@@ -3235,19 +3241,19 @@
       </c>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" s="61">
+      <c r="B6" s="60">
         <f>SUM(H5)+1</f>
         <v>46285</v>
       </c>
-      <c r="C6" s="59">
+      <c r="C6" s="58">
         <f>SUM(B6)+1</f>
         <v>46286</v>
       </c>
-      <c r="D6" s="59">
+      <c r="D6" s="58">
         <f t="shared" ref="D6:H6" si="3">SUM(C6)+1</f>
         <v>46287</v>
       </c>
-      <c r="E6" s="59">
+      <c r="E6" s="58">
         <f t="shared" si="3"/>
         <v>46288</v>
       </c>
@@ -3362,13 +3368,13 @@
         <f t="shared" si="7"/>
         <v>46311</v>
       </c>
-      <c r="H10" s="66">
+      <c r="H10" s="65">
         <f>SUM(G10)+1</f>
         <v>46312</v>
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="65">
+      <c r="B11" s="64">
         <f t="shared" si="6"/>
         <v>46313</v>
       </c>

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ayato Terao\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2054054-4258-4099-88D8-9D9E75E6F3A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A35BD4-F5C2-4C2A-BCA8-4A8801F4C28C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1516,16 +1516,94 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1540,110 +1618,32 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1951,10 +1951,10 @@
   <sheetData>
     <row r="1" spans="2:11" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B2" s="92" t="s">
+      <c r="B2" s="108" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="93"/>
+      <c r="C2" s="109"/>
       <c r="D2" s="53" t="s">
         <v>9</v>
       </c>
@@ -1969,10 +1969,10 @@
       </c>
     </row>
     <row r="3" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B3" s="94" t="s">
+      <c r="B3" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="95"/>
+      <c r="C3" s="111"/>
       <c r="D3" s="53" t="s">
         <v>12</v>
       </c>
@@ -1999,10 +1999,10 @@
       </c>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="98" t="s">
+      <c r="B4" s="112" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="99"/>
+      <c r="C4" s="113"/>
       <c r="D4" s="11"/>
       <c r="E4" s="48"/>
       <c r="F4" s="48"/>
@@ -2021,10 +2021,10 @@
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="100" t="s">
+      <c r="B5" s="92" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="101"/>
+      <c r="C5" s="93"/>
       <c r="D5" s="8"/>
       <c r="E5" s="44">
         <v>2</v>
@@ -2047,10 +2047,10 @@
       </c>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" s="100" t="s">
+      <c r="B6" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="101"/>
+      <c r="C6" s="93"/>
       <c r="D6" s="8"/>
       <c r="E6" s="44">
         <v>1</v>
@@ -2073,10 +2073,10 @@
       </c>
     </row>
     <row r="7" spans="2:11">
-      <c r="B7" s="84" t="s">
+      <c r="B7" s="100" t="s">
         <v>90</v>
       </c>
-      <c r="C7" s="85"/>
+      <c r="C7" s="101"/>
       <c r="D7" s="8"/>
       <c r="E7" s="44">
         <v>2</v>
@@ -2099,10 +2099,10 @@
       </c>
     </row>
     <row r="8" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B8" s="84" t="s">
+      <c r="B8" s="100" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="85"/>
+      <c r="C8" s="101"/>
       <c r="D8" s="10"/>
       <c r="E8" s="45">
         <v>2</v>
@@ -2125,10 +2125,10 @@
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="84" t="s">
+      <c r="B9" s="100" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="85"/>
+      <c r="C9" s="101"/>
       <c r="D9" s="10"/>
       <c r="E9" s="45">
         <v>2</v>
@@ -2139,10 +2139,10 @@
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="88" t="s">
+      <c r="B10" s="114" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="89"/>
+      <c r="C10" s="115"/>
       <c r="D10" s="8"/>
       <c r="E10" s="44">
         <v>1</v>
@@ -2155,10 +2155,10 @@
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="100" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="85"/>
+      <c r="C11" s="101"/>
       <c r="D11" s="8"/>
       <c r="E11" s="44"/>
       <c r="F11" s="45"/>
@@ -2167,10 +2167,10 @@
       </c>
     </row>
     <row r="12" spans="2:11">
-      <c r="B12" s="86" t="s">
+      <c r="B12" s="96" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="87"/>
+      <c r="C12" s="97"/>
       <c r="D12" s="8"/>
       <c r="E12" s="44">
         <v>1</v>
@@ -2183,10 +2183,10 @@
       </c>
     </row>
     <row r="13" spans="2:11">
-      <c r="B13" s="100" t="s">
+      <c r="B13" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="101"/>
+      <c r="C13" s="93"/>
       <c r="D13" s="8"/>
       <c r="E13" s="44">
         <v>1</v>
@@ -2199,10 +2199,10 @@
       </c>
     </row>
     <row r="14" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B14" s="106" t="s">
+      <c r="B14" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="107"/>
+      <c r="C14" s="95"/>
       <c r="D14" s="10"/>
       <c r="E14" s="45">
         <v>1</v>
@@ -2215,14 +2215,14 @@
       </c>
     </row>
     <row r="15" spans="2:11">
-      <c r="B15" s="96" t="s">
+      <c r="B15" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="97"/>
+      <c r="C15" s="103"/>
       <c r="D15" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="125">
+      <c r="E15" s="86">
         <f>SUM(E16:E24)</f>
         <v>16</v>
       </c>
@@ -2234,12 +2234,12 @@
       </c>
     </row>
     <row r="16" spans="2:11">
-      <c r="B16" s="84" t="s">
+      <c r="B16" s="100" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="85"/>
+      <c r="C16" s="101"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="123">
+      <c r="E16" s="84">
         <v>3</v>
       </c>
       <c r="F16" s="44">
@@ -2250,12 +2250,12 @@
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="84" t="s">
+      <c r="B17" s="100" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="85"/>
+      <c r="C17" s="101"/>
       <c r="D17" s="8"/>
-      <c r="E17" s="123">
+      <c r="E17" s="84">
         <v>3</v>
       </c>
       <c r="F17" s="44">
@@ -2266,12 +2266,12 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="84" t="s">
+      <c r="B18" s="100" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="85"/>
+      <c r="C18" s="101"/>
       <c r="D18" s="8"/>
-      <c r="E18" s="123">
+      <c r="E18" s="84">
         <v>3</v>
       </c>
       <c r="F18" s="44">
@@ -2282,12 +2282,12 @@
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="84" t="s">
+      <c r="B19" s="100" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="85"/>
+      <c r="C19" s="101"/>
       <c r="D19" s="10"/>
-      <c r="E19" s="123">
+      <c r="E19" s="84">
         <v>3</v>
       </c>
       <c r="F19" s="44">
@@ -2298,12 +2298,12 @@
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="84" t="s">
+      <c r="B20" s="100" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="85"/>
+      <c r="C20" s="101"/>
       <c r="D20" s="8"/>
-      <c r="E20" s="124">
+      <c r="E20" s="85">
         <v>1</v>
       </c>
       <c r="F20" s="44">
@@ -2314,12 +2314,12 @@
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="88" t="s">
+      <c r="B21" s="114" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="89"/>
+      <c r="C21" s="115"/>
       <c r="D21" s="8"/>
-      <c r="E21" s="123"/>
+      <c r="E21" s="84"/>
       <c r="F21" s="44">
         <v>3</v>
       </c>
@@ -2328,12 +2328,12 @@
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="86" t="s">
+      <c r="B22" s="96" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="87"/>
+      <c r="C22" s="97"/>
       <c r="D22" s="8"/>
-      <c r="E22" s="123">
+      <c r="E22" s="84">
         <v>1</v>
       </c>
       <c r="F22" s="44">
@@ -2344,12 +2344,12 @@
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="86" t="s">
+      <c r="B23" s="96" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="87"/>
+      <c r="C23" s="97"/>
       <c r="D23" s="8"/>
-      <c r="E23" s="123">
+      <c r="E23" s="84">
         <v>1</v>
       </c>
       <c r="F23" s="44">
@@ -2360,12 +2360,12 @@
       </c>
     </row>
     <row r="24" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B24" s="108" t="s">
+      <c r="B24" s="98" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="109"/>
+      <c r="C24" s="99"/>
       <c r="D24" s="9"/>
-      <c r="E24" s="126">
+      <c r="E24" s="87">
         <v>1</v>
       </c>
       <c r="F24" s="46">
@@ -2376,10 +2376,10 @@
       </c>
     </row>
     <row r="25" spans="2:7">
-      <c r="B25" s="90" t="s">
+      <c r="B25" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="91"/>
+      <c r="C25" s="117"/>
       <c r="D25" s="56" t="s">
         <v>10</v>
       </c>
@@ -2387,16 +2387,19 @@
         <f>SUM(E26:E30)</f>
         <v>12</v>
       </c>
-      <c r="F25" s="57"/>
+      <c r="F25" s="57">
+        <f>SUM(F26,F27,F30)</f>
+        <v>0</v>
+      </c>
       <c r="G25" s="67" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="26" spans="2:7">
-      <c r="B26" s="88" t="s">
+      <c r="B26" s="114" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="89"/>
+      <c r="C26" s="115"/>
       <c r="D26" s="8"/>
       <c r="E26" s="44">
         <v>5</v>
@@ -2407,10 +2410,10 @@
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="88" t="s">
+      <c r="B27" s="114" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="89"/>
+      <c r="C27" s="115"/>
       <c r="D27" s="8"/>
       <c r="E27" s="44"/>
       <c r="F27" s="44"/>
@@ -2419,10 +2422,10 @@
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="86" t="s">
+      <c r="B28" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="87"/>
+      <c r="C28" s="97"/>
       <c r="D28" s="8"/>
       <c r="E28" s="44">
         <v>2</v>
@@ -2433,10 +2436,10 @@
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="86" t="s">
+      <c r="B29" s="96" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="87"/>
+      <c r="C29" s="97"/>
       <c r="D29" s="8"/>
       <c r="E29" s="44">
         <v>2</v>
@@ -2447,10 +2450,10 @@
       </c>
     </row>
     <row r="30" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B30" s="104" t="s">
+      <c r="B30" s="90" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="105"/>
+      <c r="C30" s="91"/>
       <c r="D30" s="9"/>
       <c r="E30" s="46">
         <v>3</v>
@@ -2461,10 +2464,10 @@
       </c>
     </row>
     <row r="31" spans="2:7">
-      <c r="B31" s="96" t="s">
+      <c r="B31" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="97"/>
+      <c r="C31" s="103"/>
       <c r="D31" s="7" t="s">
         <v>14</v>
       </c>
@@ -2472,16 +2475,19 @@
         <f>SUM(E32:E39)</f>
         <v>11</v>
       </c>
-      <c r="F31" s="47"/>
+      <c r="F31" s="47">
+        <f>SUM(F33,F35,F36,F38,F39)</f>
+        <v>0</v>
+      </c>
       <c r="G31" s="67" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="32" spans="2:7">
-      <c r="B32" s="84" t="s">
+      <c r="B32" s="100" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="85"/>
+      <c r="C32" s="101"/>
       <c r="D32" s="11"/>
       <c r="E32" s="52"/>
       <c r="F32" s="48"/>
@@ -2490,10 +2496,10 @@
       </c>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="100" t="s">
+      <c r="B33" s="92" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="101"/>
+      <c r="C33" s="93"/>
       <c r="D33" s="11"/>
       <c r="E33" s="52">
         <v>2</v>
@@ -2504,10 +2510,10 @@
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="110" t="s">
+      <c r="B34" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="C34" s="111"/>
+      <c r="C34" s="105"/>
       <c r="D34" s="8"/>
       <c r="E34" s="43"/>
       <c r="F34" s="44"/>
@@ -2516,10 +2522,10 @@
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="84" t="s">
+      <c r="B35" s="100" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="85"/>
+      <c r="C35" s="101"/>
       <c r="D35" s="8"/>
       <c r="E35" s="43">
         <v>2</v>
@@ -2530,10 +2536,10 @@
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="84" t="s">
+      <c r="B36" s="100" t="s">
         <v>60</v>
       </c>
-      <c r="C36" s="85"/>
+      <c r="C36" s="101"/>
       <c r="D36" s="8"/>
       <c r="E36" s="43">
         <v>2</v>
@@ -2544,10 +2550,10 @@
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="110" t="s">
+      <c r="B37" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="111"/>
+      <c r="C37" s="105"/>
       <c r="D37" s="8"/>
       <c r="E37" s="43"/>
       <c r="F37" s="44"/>
@@ -2556,10 +2562,10 @@
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="112" t="s">
+      <c r="B38" s="106" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="113"/>
+      <c r="C38" s="107"/>
       <c r="D38" s="8"/>
       <c r="E38" s="43">
         <v>2</v>
@@ -2570,10 +2576,10 @@
       </c>
     </row>
     <row r="39" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B39" s="104" t="s">
+      <c r="B39" s="90" t="s">
         <v>64</v>
       </c>
-      <c r="C39" s="105"/>
+      <c r="C39" s="91"/>
       <c r="D39" s="9"/>
       <c r="E39" s="49">
         <v>3</v>
@@ -2584,10 +2590,10 @@
       </c>
     </row>
     <row r="40" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B40" s="102" t="s">
+      <c r="B40" s="88" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="103"/>
+      <c r="C40" s="89"/>
       <c r="D40" s="54"/>
       <c r="E40" s="81">
         <f>SUM(E3+E15+E25+F31)</f>
@@ -2601,6 +2607,29 @@
     </row>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B13:C13"/>
@@ -2617,29 +2646,6 @@
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2657,10 +2663,10 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="92" t="s">
+      <c r="B2" s="108" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="93"/>
+      <c r="C2" s="109"/>
       <c r="D2" s="53" t="s">
         <v>9</v>
       </c>
@@ -2672,10 +2678,10 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="94" t="s">
+      <c r="B3" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="95"/>
+      <c r="C3" s="111"/>
       <c r="D3" s="53" t="s">
         <v>12</v>
       </c>
@@ -2683,10 +2689,10 @@
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="115"/>
+      <c r="C4" s="125"/>
       <c r="D4" s="7"/>
       <c r="E4" s="47">
         <v>2</v>
@@ -2694,10 +2700,10 @@
       <c r="F4" s="47"/>
     </row>
     <row r="5" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B5" s="100" t="s">
+      <c r="B5" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="101"/>
+      <c r="C5" s="93"/>
       <c r="D5" s="8"/>
       <c r="E5" s="44">
         <v>2</v>
@@ -2705,10 +2711,10 @@
       <c r="F5" s="44"/>
     </row>
     <row r="6" spans="2:6">
-      <c r="B6" s="96" t="s">
+      <c r="B6" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="97"/>
+      <c r="C6" s="103"/>
       <c r="D6" s="7" t="s">
         <v>11</v>
       </c>
@@ -2716,10 +2722,10 @@
       <c r="F6" s="47"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="100" t="s">
+      <c r="B7" s="92" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="101"/>
+      <c r="C7" s="93"/>
       <c r="D7" s="8"/>
       <c r="E7" s="44">
         <v>2</v>
@@ -2727,10 +2733,10 @@
       <c r="F7" s="44"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="100" t="s">
+      <c r="B8" s="92" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="101"/>
+      <c r="C8" s="93"/>
       <c r="D8" s="8"/>
       <c r="E8" s="44">
         <v>3</v>
@@ -2738,10 +2744,10 @@
       <c r="F8" s="44"/>
     </row>
     <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="100" t="s">
+      <c r="B9" s="92" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="101"/>
+      <c r="C9" s="93"/>
       <c r="D9" s="8"/>
       <c r="E9" s="44">
         <v>2</v>
@@ -2749,10 +2755,10 @@
       <c r="F9" s="44"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="90" t="s">
+      <c r="B10" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="91"/>
+      <c r="C10" s="117"/>
       <c r="D10" s="56" t="s">
         <v>10</v>
       </c>
@@ -2760,10 +2766,10 @@
       <c r="F10" s="57"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="86" t="s">
+      <c r="B11" s="96" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="87"/>
+      <c r="C11" s="97"/>
       <c r="D11" s="8"/>
       <c r="E11" s="44">
         <v>5</v>
@@ -2771,10 +2777,10 @@
       <c r="F11" s="44"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="86" t="s">
+      <c r="B12" s="96" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="87"/>
+      <c r="C12" s="97"/>
       <c r="D12" s="8"/>
       <c r="E12" s="44">
         <v>1</v>
@@ -2782,10 +2788,10 @@
       <c r="F12" s="44"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="86" t="s">
+      <c r="B13" s="96" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="87"/>
+      <c r="C13" s="97"/>
       <c r="D13" s="8"/>
       <c r="E13" s="44">
         <v>2</v>
@@ -2793,10 +2799,10 @@
       <c r="F13" s="44"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="116" t="s">
+      <c r="B14" s="122" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="117"/>
+      <c r="C14" s="123"/>
       <c r="D14" s="11" t="s">
         <v>14</v>
       </c>
@@ -2804,10 +2810,10 @@
       <c r="F14" s="48"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="100" t="s">
+      <c r="B15" s="92" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="101"/>
+      <c r="C15" s="93"/>
       <c r="D15" s="11"/>
       <c r="E15" s="52">
         <v>5</v>
@@ -2815,19 +2821,19 @@
       <c r="F15" s="48"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="110" t="s">
+      <c r="B16" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="111"/>
+      <c r="C16" s="105"/>
       <c r="D16" s="8"/>
       <c r="E16" s="43"/>
       <c r="F16" s="44"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="100" t="s">
+      <c r="B17" s="92" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="101"/>
+      <c r="C17" s="93"/>
       <c r="D17" s="8"/>
       <c r="E17" s="43">
         <v>2</v>
@@ -2835,10 +2841,10 @@
       <c r="F17" s="44"/>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="110" t="s">
+      <c r="B18" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="111"/>
+      <c r="C18" s="105"/>
       <c r="D18" s="8"/>
       <c r="E18" s="43"/>
       <c r="F18" s="44"/>
@@ -2865,17 +2871,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
@@ -2884,6 +2879,17 @@
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2897,10 +2903,10 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="92" t="s">
+      <c r="B2" s="108" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="93"/>
+      <c r="C2" s="109"/>
       <c r="D2" s="53" t="s">
         <v>9</v>
       </c>
@@ -2912,10 +2918,10 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="94" t="s">
+      <c r="B3" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="95"/>
+      <c r="C3" s="111"/>
       <c r="D3" s="53" t="s">
         <v>12</v>
       </c>
@@ -2923,10 +2929,10 @@
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="124" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="115"/>
+      <c r="C4" s="125"/>
       <c r="D4" s="7"/>
       <c r="E4" s="47">
         <v>3</v>
@@ -2934,10 +2940,10 @@
       <c r="F4" s="47"/>
     </row>
     <row r="5" spans="2:6">
-      <c r="B5" s="96" t="s">
+      <c r="B5" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="97"/>
+      <c r="C5" s="103"/>
       <c r="D5" s="7" t="s">
         <v>11</v>
       </c>
@@ -2945,10 +2951,10 @@
       <c r="F5" s="47"/>
     </row>
     <row r="6" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B6" s="100" t="s">
+      <c r="B6" s="92" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="101"/>
+      <c r="C6" s="93"/>
       <c r="D6" s="8"/>
       <c r="E6" s="44">
         <v>3</v>
@@ -2956,10 +2962,10 @@
       <c r="F6" s="44"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="90" t="s">
+      <c r="B7" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="91"/>
+      <c r="C7" s="117"/>
       <c r="D7" s="56" t="s">
         <v>10</v>
       </c>
@@ -2967,10 +2973,10 @@
       <c r="F7" s="57"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="86" t="s">
+      <c r="B8" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="87"/>
+      <c r="C8" s="97"/>
       <c r="D8" s="8"/>
       <c r="E8" s="44">
         <v>3</v>
@@ -2978,10 +2984,10 @@
       <c r="F8" s="44"/>
     </row>
     <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="100" t="s">
+      <c r="B9" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="101"/>
+      <c r="C9" s="93"/>
       <c r="D9" s="8"/>
       <c r="E9" s="44">
         <v>2</v>
@@ -2989,10 +2995,10 @@
       <c r="F9" s="44"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="96" t="s">
+      <c r="B10" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="97"/>
+      <c r="C10" s="103"/>
       <c r="D10" s="7" t="s">
         <v>14</v>
       </c>
@@ -3000,10 +3006,10 @@
       <c r="F10" s="47"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="100" t="s">
+      <c r="B11" s="92" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="101"/>
+      <c r="C11" s="93"/>
       <c r="D11" s="11"/>
       <c r="E11" s="48">
         <v>2</v>
@@ -3011,19 +3017,19 @@
       <c r="F11" s="48"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="110" t="s">
+      <c r="B12" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="111"/>
+      <c r="C12" s="105"/>
       <c r="D12" s="8"/>
       <c r="E12" s="44"/>
       <c r="F12" s="44"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="100" t="s">
+      <c r="B13" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="101"/>
+      <c r="C13" s="93"/>
       <c r="D13" s="8"/>
       <c r="E13" s="44">
         <v>1</v>
@@ -3031,10 +3037,10 @@
       <c r="F13" s="44"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="100" t="s">
+      <c r="B14" s="92" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="101"/>
+      <c r="C14" s="93"/>
       <c r="D14" s="8"/>
       <c r="E14" s="44">
         <v>1</v>
@@ -3042,19 +3048,19 @@
       <c r="F14" s="44"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="110" t="s">
+      <c r="B15" s="104" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="111"/>
+      <c r="C15" s="105"/>
       <c r="D15" s="8"/>
       <c r="E15" s="44"/>
       <c r="F15" s="44"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="86" t="s">
+      <c r="B16" s="96" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="87"/>
+      <c r="C16" s="97"/>
       <c r="D16" s="8"/>
       <c r="E16" s="44">
         <v>1</v>
@@ -3062,10 +3068,10 @@
       <c r="F16" s="44"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="86" t="s">
+      <c r="B17" s="96" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="87"/>
+      <c r="C17" s="97"/>
       <c r="D17" s="8"/>
       <c r="E17" s="44">
         <v>1</v>
@@ -3073,16 +3079,26 @@
       <c r="F17" s="44"/>
     </row>
     <row r="18" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B18" s="102" t="s">
+      <c r="B18" s="88" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="103"/>
+      <c r="C18" s="89"/>
       <c r="D18" s="54"/>
       <c r="E18" s="55"/>
       <c r="F18" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B11:C11"/>
@@ -3090,16 +3106,6 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3112,13 +3118,13 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="122" t="s">
+      <c r="C1" s="126" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126"/>
     </row>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
       <c r="B2" s="33" t="s">

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ayato Terao\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A35BD4-F5C2-4C2A-BCA8-4A8801F4C28C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B1E12B-8DB3-496D-AF8A-E76030A64821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -635,6 +635,10 @@
     <rPh sb="0" eb="4">
       <t>シテンハンテン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ージャンプ</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1335,7 +1339,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1528,6 +1532,60 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1540,42 +1598,18 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1588,34 +1622,16 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1628,22 +1644,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1932,7 +1945,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B1:K40"/>
+  <dimension ref="B1:S41"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9" style="4" customWidth="1"/>
@@ -1949,12 +1962,12 @@
     <col min="13" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="19.5" thickBot="1"/>
-    <row r="2" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B2" s="108" t="s">
+    <row r="1" spans="2:19" ht="19.5" thickBot="1"/>
+    <row r="2" spans="2:19" ht="19.5" thickBot="1">
+      <c r="B2" s="96" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="109"/>
+      <c r="C2" s="97"/>
       <c r="D2" s="53" t="s">
         <v>9</v>
       </c>
@@ -1968,21 +1981,21 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B3" s="110" t="s">
+    <row r="3" spans="2:19" ht="19.5" thickBot="1">
+      <c r="B3" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="111"/>
+      <c r="C3" s="99"/>
       <c r="D3" s="53" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="50">
-        <f>SUM(E4:E14)</f>
-        <v>13</v>
+        <f>SUM(E4:E15)</f>
+        <v>14</v>
       </c>
       <c r="F3" s="51">
-        <f>SUM(F4:F14)</f>
-        <v>11</v>
+        <f>SUM(F4:F15)</f>
+        <v>12</v>
       </c>
       <c r="G3" s="53" t="s">
         <v>85</v>
@@ -1992,17 +2005,17 @@
       </c>
       <c r="J3" s="75">
         <f ca="1">TODAY()</f>
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="K3" s="53" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="2:11">
-      <c r="B4" s="112" t="s">
+    <row r="4" spans="2:19">
+      <c r="B4" s="102" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="113"/>
+      <c r="C4" s="103"/>
       <c r="D4" s="11"/>
       <c r="E4" s="48"/>
       <c r="F4" s="48"/>
@@ -2017,14 +2030,14 @@
       </c>
       <c r="K4" s="70" t="str">
         <f ca="1">SUM($J4-J3)&amp; "日"</f>
-        <v>5日</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11">
-      <c r="B5" s="92" t="s">
+        <v>2日</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19">
+      <c r="B5" s="104" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="93"/>
+      <c r="C5" s="105"/>
       <c r="D5" s="8"/>
       <c r="E5" s="44">
         <v>2</v>
@@ -2043,14 +2056,14 @@
       </c>
       <c r="K5" s="68" t="str">
         <f ca="1">SUM($J5-J3)&amp; "日"</f>
-        <v>15日</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11">
-      <c r="B6" s="92" t="s">
+        <v>12日</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19">
+      <c r="B6" s="104" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="93"/>
+      <c r="C6" s="105"/>
       <c r="D6" s="8"/>
       <c r="E6" s="44">
         <v>1</v>
@@ -2069,20 +2082,20 @@
       </c>
       <c r="K6" s="68" t="str">
         <f ca="1">SUM($J6-J3)&amp; "日"</f>
-        <v>20日</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11">
-      <c r="B7" s="100" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" s="101"/>
+        <v>17日</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19">
+      <c r="B7" s="104" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="105"/>
       <c r="D7" s="8"/>
       <c r="E7" s="44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="62" t="s">
         <v>89</v>
@@ -2095,20 +2108,20 @@
       </c>
       <c r="K7" s="68" t="str">
         <f ca="1">SUM($J7-J3)&amp; "日"</f>
-        <v>23日</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B8" s="100" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="101"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="45">
+        <v>20日</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" ht="19.5" thickBot="1">
+      <c r="B8" s="88" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="89"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="44">
         <v>2</v>
       </c>
-      <c r="F8" s="45">
-        <v>1</v>
+      <c r="F8" s="48">
+        <v>2</v>
       </c>
       <c r="G8" s="62" t="s">
         <v>89</v>
@@ -2121,72 +2134,72 @@
       </c>
       <c r="K8" s="69" t="str">
         <f ca="1">SUM(J8-J3)&amp; "日"</f>
-        <v>24日</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11">
-      <c r="B9" s="100" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="101"/>
+        <v>21日</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19">
+      <c r="B9" s="88" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="89"/>
       <c r="D9" s="10"/>
       <c r="E9" s="45">
         <v>2</v>
       </c>
-      <c r="F9" s="45"/>
-      <c r="G9" s="61" t="s">
+      <c r="F9" s="45">
+        <v>1</v>
+      </c>
+      <c r="G9" s="62" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19">
+      <c r="B10" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="89"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="45">
+        <v>2</v>
+      </c>
+      <c r="F10" s="45"/>
+      <c r="G10" s="61" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="2:11">
-      <c r="B10" s="114" t="s">
+    <row r="11" spans="2:19">
+      <c r="B11" s="92" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="115"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="44">
+      <c r="C11" s="93"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="44">
         <v>1</v>
       </c>
-      <c r="F10" s="44">
+      <c r="F11" s="44">
         <v>1</v>
       </c>
-      <c r="G10" s="61" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11">
-      <c r="B11" s="100" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="101"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="45"/>
       <c r="G11" s="61" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="2:11">
-      <c r="B12" s="96" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="97"/>
+    <row r="12" spans="2:19">
+      <c r="B12" s="88" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="89"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="44">
-        <v>1</v>
-      </c>
-      <c r="F12" s="44">
-        <v>1</v>
-      </c>
+      <c r="E12" s="44"/>
+      <c r="F12" s="45"/>
       <c r="G12" s="61" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="2:11">
-      <c r="B13" s="92" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="93"/>
+    <row r="13" spans="2:19">
+      <c r="B13" s="90" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="91"/>
       <c r="D13" s="8"/>
       <c r="E13" s="44">
         <v>1</v>
@@ -2198,62 +2211,65 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B14" s="94" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="95"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="45">
+    <row r="14" spans="2:19">
+      <c r="B14" s="104" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="105"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="44">
         <v>1</v>
       </c>
-      <c r="F14" s="45">
+      <c r="F14" s="44">
         <v>1</v>
       </c>
       <c r="G14" s="61" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="15" spans="2:11">
-      <c r="B15" s="102" t="s">
+      <c r="Q14" s="129"/>
+      <c r="R14" s="127"/>
+      <c r="S14" s="128"/>
+    </row>
+    <row r="15" spans="2:19" ht="19.5" thickBot="1">
+      <c r="B15" s="110" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="111"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="45">
         <v>1</v>
       </c>
-      <c r="C15" s="103"/>
-      <c r="D15" s="7" t="s">
+      <c r="F15" s="45">
+        <v>1</v>
+      </c>
+      <c r="G15" s="61" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19">
+      <c r="B16" s="100" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="101"/>
+      <c r="D16" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="86">
-        <f>SUM(E16:E24)</f>
+      <c r="E16" s="86">
+        <f>SUM(E17:E25)</f>
         <v>16</v>
       </c>
-      <c r="F15" s="47">
+      <c r="F16" s="47">
         <v>8</v>
       </c>
-      <c r="G15" s="67" t="s">
+      <c r="G16" s="67" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="16" spans="2:11">
-      <c r="B16" s="100" t="s">
+    <row r="17" spans="2:7">
+      <c r="B17" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="101"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="84">
-        <v>3</v>
-      </c>
-      <c r="F16" s="44">
-        <v>1</v>
-      </c>
-      <c r="G16" s="61" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="100" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="101"/>
+      <c r="C17" s="89"/>
       <c r="D17" s="8"/>
       <c r="E17" s="84">
         <v>3</v>
@@ -2266,10 +2282,10 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="100" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="101"/>
+      <c r="B18" s="88" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="89"/>
       <c r="D18" s="8"/>
       <c r="E18" s="84">
         <v>3</v>
@@ -2282,11 +2298,11 @@
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="100" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="101"/>
-      <c r="D19" s="10"/>
+      <c r="B19" s="88" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="89"/>
+      <c r="D19" s="8"/>
       <c r="E19" s="84">
         <v>3</v>
       </c>
@@ -2298,13 +2314,13 @@
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="100" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="101"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="85">
-        <v>1</v>
+      <c r="B20" s="88" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" s="89"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="84">
+        <v>3</v>
       </c>
       <c r="F20" s="44">
         <v>1</v>
@@ -2314,40 +2330,40 @@
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="114" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="115"/>
+      <c r="B21" s="88" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="89"/>
       <c r="D21" s="8"/>
-      <c r="E21" s="84"/>
+      <c r="E21" s="85">
+        <v>1</v>
+      </c>
       <c r="F21" s="44">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21" s="61" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="96" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="97"/>
+      <c r="B22" s="92" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="93"/>
       <c r="D22" s="8"/>
-      <c r="E22" s="84">
-        <v>1</v>
-      </c>
+      <c r="E22" s="84"/>
       <c r="F22" s="44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" s="61" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="96" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" s="97"/>
+      <c r="B23" s="90" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="91"/>
       <c r="D23" s="8"/>
       <c r="E23" s="84">
         <v>1</v>
@@ -2359,87 +2375,91 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B24" s="98" t="s">
-        <v>52</v>
-      </c>
-      <c r="C24" s="99"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="87">
+    <row r="24" spans="2:7">
+      <c r="B24" s="90" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="91"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="84">
         <v>1</v>
       </c>
-      <c r="F24" s="46">
+      <c r="F24" s="44">
         <v>1</v>
       </c>
       <c r="G24" s="61" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
-      <c r="B25" s="116" t="s">
+    <row r="25" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B25" s="112" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="113"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="87">
+        <v>1</v>
+      </c>
+      <c r="F25" s="46">
+        <v>1</v>
+      </c>
+      <c r="G25" s="61" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7">
+      <c r="B26" s="94" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="117"/>
-      <c r="D25" s="56" t="s">
+      <c r="C26" s="95"/>
+      <c r="D26" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="E25" s="57">
-        <f>SUM(E26:E30)</f>
+      <c r="E26" s="57">
+        <f>SUM(E27:E31)</f>
         <v>12</v>
       </c>
-      <c r="F25" s="57">
-        <f>SUM(F26,F27,F30)</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="67" t="s">
+      <c r="F26" s="57">
+        <f>SUM(F27,F28,F31)</f>
+        <v>8</v>
+      </c>
+      <c r="G26" s="67" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="26" spans="2:7">
-      <c r="B26" s="114" t="s">
+    <row r="27" spans="2:7">
+      <c r="B27" s="92" t="s">
         <v>53</v>
       </c>
-      <c r="C26" s="115"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="44">
+      <c r="C27" s="93"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="44">
         <v>5</v>
       </c>
-      <c r="F26" s="44"/>
-      <c r="G26" s="61" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7">
-      <c r="B27" s="114" t="s">
+      <c r="F27" s="44">
+        <v>5</v>
+      </c>
+      <c r="G27" s="61" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7">
+      <c r="B28" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="115"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="44"/>
-      <c r="G27" s="61" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7">
-      <c r="B28" s="96" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="97"/>
+      <c r="C28" s="93"/>
       <c r="D28" s="8"/>
-      <c r="E28" s="44">
-        <v>2</v>
-      </c>
+      <c r="E28" s="44"/>
       <c r="F28" s="44"/>
       <c r="G28" s="61" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="96" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="97"/>
+      <c r="B29" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="91"/>
       <c r="D29" s="8"/>
       <c r="E29" s="44">
         <v>2</v>
@@ -2449,61 +2469,63 @@
         <v>85</v>
       </c>
     </row>
-    <row r="30" spans="2:7" ht="19.5" thickBot="1">
+    <row r="30" spans="2:7">
       <c r="B30" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="91"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="44">
+        <v>2</v>
+      </c>
+      <c r="F30" s="44"/>
+      <c r="G30" s="61" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B31" s="108" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="91"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="46">
+      <c r="C31" s="109"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="46">
         <v>3</v>
       </c>
-      <c r="F30" s="46"/>
-      <c r="G30" s="63" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7">
-      <c r="B31" s="102" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" s="103"/>
-      <c r="D31" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="83">
-        <f>SUM(E32:E39)</f>
-        <v>11</v>
-      </c>
-      <c r="F31" s="47">
-        <f>SUM(F33,F35,F36,F38,F39)</f>
-        <v>0</v>
-      </c>
-      <c r="G31" s="67" t="s">
-        <v>85</v>
+      <c r="F31" s="46">
+        <v>3</v>
+      </c>
+      <c r="G31" s="63" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="2:7">
       <c r="B32" s="100" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="101"/>
+      <c r="D32" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="83">
+        <f>SUM(E33:E40)</f>
+        <v>11</v>
+      </c>
+      <c r="F32" s="47">
+        <f>SUM(F34,F36,F37,F39,F40)</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="67" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="88" t="s">
         <v>61</v>
       </c>
-      <c r="C32" s="101"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="48"/>
-      <c r="G32" s="61" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="92" t="s">
-        <v>58</v>
-      </c>
-      <c r="C33" s="93"/>
+      <c r="C33" s="89"/>
       <c r="D33" s="11"/>
-      <c r="E33" s="52">
-        <v>2</v>
-      </c>
+      <c r="E33" s="52"/>
       <c r="F33" s="48"/>
       <c r="G33" s="61" t="s">
         <v>85</v>
@@ -2511,35 +2533,35 @@
     </row>
     <row r="34" spans="2:7">
       <c r="B34" s="104" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="C34" s="105"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="44"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="52">
+        <v>2</v>
+      </c>
+      <c r="F34" s="48"/>
       <c r="G34" s="61" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="100" t="s">
-        <v>59</v>
-      </c>
-      <c r="C35" s="101"/>
+      <c r="B35" s="114" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="115"/>
       <c r="D35" s="8"/>
-      <c r="E35" s="43">
-        <v>2</v>
-      </c>
+      <c r="E35" s="43"/>
       <c r="F35" s="44"/>
       <c r="G35" s="61" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="100" t="s">
-        <v>60</v>
-      </c>
-      <c r="C36" s="101"/>
+      <c r="B36" s="88" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="89"/>
       <c r="D36" s="8"/>
       <c r="E36" s="43">
         <v>2</v>
@@ -2550,102 +2572,117 @@
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="104" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" s="105"/>
+      <c r="B37" s="88" t="s">
+        <v>60</v>
+      </c>
+      <c r="C37" s="89"/>
       <c r="D37" s="8"/>
-      <c r="E37" s="43"/>
+      <c r="E37" s="43">
+        <v>2</v>
+      </c>
       <c r="F37" s="44"/>
       <c r="G37" s="61" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="106" t="s">
-        <v>63</v>
-      </c>
-      <c r="C38" s="107"/>
+      <c r="B38" s="114" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="115"/>
       <c r="D38" s="8"/>
-      <c r="E38" s="43">
-        <v>2</v>
-      </c>
+      <c r="E38" s="43"/>
       <c r="F38" s="44"/>
       <c r="G38" s="61" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B39" s="90" t="s">
+    <row r="39" spans="2:7">
+      <c r="B39" s="116" t="s">
+        <v>63</v>
+      </c>
+      <c r="C39" s="117"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="43">
+        <v>2</v>
+      </c>
+      <c r="F39" s="44"/>
+      <c r="G39" s="61" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B40" s="108" t="s">
         <v>64</v>
       </c>
-      <c r="C39" s="91"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="49">
+      <c r="C40" s="109"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="49">
         <v>3</v>
       </c>
-      <c r="F39" s="46"/>
-      <c r="G39" s="63" t="s">
+      <c r="F40" s="46"/>
+      <c r="G40" s="63" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="40" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B40" s="88" t="s">
+    <row r="41" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B41" s="106" t="s">
         <v>87</v>
       </c>
-      <c r="C40" s="89"/>
-      <c r="D40" s="54"/>
-      <c r="E40" s="81">
-        <f>SUM(E3+E15+E25+F31)</f>
-        <v>41</v>
-      </c>
-      <c r="F40" s="82">
-        <f>SUM(F4:F39)</f>
-        <v>30</v>
-      </c>
-      <c r="G40" s="54"/>
+      <c r="C41" s="107"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="81">
+        <f>SUM(E3+E16+E26+F32)</f>
+        <v>42</v>
+      </c>
+      <c r="F41" s="82">
+        <f>SUM(F4:F40)</f>
+        <v>47</v>
+      </c>
+      <c r="G41" s="54"/>
     </row>
   </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B26:C26"/>
+  <mergeCells count="40">
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B19:C19"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2663,10 +2700,10 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="108" t="s">
+      <c r="B2" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="109"/>
+      <c r="C2" s="97"/>
       <c r="D2" s="53" t="s">
         <v>9</v>
       </c>
@@ -2678,10 +2715,10 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="110" t="s">
+      <c r="B3" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="111"/>
+      <c r="C3" s="99"/>
       <c r="D3" s="53" t="s">
         <v>12</v>
       </c>
@@ -2689,10 +2726,10 @@
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="124" t="s">
+      <c r="B4" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="125"/>
+      <c r="C4" s="119"/>
       <c r="D4" s="7"/>
       <c r="E4" s="47">
         <v>2</v>
@@ -2700,10 +2737,10 @@
       <c r="F4" s="47"/>
     </row>
     <row r="5" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B5" s="92" t="s">
+      <c r="B5" s="104" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="93"/>
+      <c r="C5" s="105"/>
       <c r="D5" s="8"/>
       <c r="E5" s="44">
         <v>2</v>
@@ -2711,10 +2748,10 @@
       <c r="F5" s="44"/>
     </row>
     <row r="6" spans="2:6">
-      <c r="B6" s="102" t="s">
+      <c r="B6" s="100" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="103"/>
+      <c r="C6" s="101"/>
       <c r="D6" s="7" t="s">
         <v>11</v>
       </c>
@@ -2722,10 +2759,10 @@
       <c r="F6" s="47"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="92" t="s">
+      <c r="B7" s="104" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="93"/>
+      <c r="C7" s="105"/>
       <c r="D7" s="8"/>
       <c r="E7" s="44">
         <v>2</v>
@@ -2733,10 +2770,10 @@
       <c r="F7" s="44"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="92" t="s">
+      <c r="B8" s="104" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="93"/>
+      <c r="C8" s="105"/>
       <c r="D8" s="8"/>
       <c r="E8" s="44">
         <v>3</v>
@@ -2744,10 +2781,10 @@
       <c r="F8" s="44"/>
     </row>
     <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="92" t="s">
+      <c r="B9" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="93"/>
+      <c r="C9" s="105"/>
       <c r="D9" s="8"/>
       <c r="E9" s="44">
         <v>2</v>
@@ -2755,10 +2792,10 @@
       <c r="F9" s="44"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="116" t="s">
+      <c r="B10" s="94" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="117"/>
+      <c r="C10" s="95"/>
       <c r="D10" s="56" t="s">
         <v>10</v>
       </c>
@@ -2766,10 +2803,10 @@
       <c r="F10" s="57"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="96" t="s">
+      <c r="B11" s="90" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="97"/>
+      <c r="C11" s="91"/>
       <c r="D11" s="8"/>
       <c r="E11" s="44">
         <v>5</v>
@@ -2777,10 +2814,10 @@
       <c r="F11" s="44"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="96" t="s">
+      <c r="B12" s="90" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="97"/>
+      <c r="C12" s="91"/>
       <c r="D12" s="8"/>
       <c r="E12" s="44">
         <v>1</v>
@@ -2788,10 +2825,10 @@
       <c r="F12" s="44"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="96" t="s">
+      <c r="B13" s="90" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="97"/>
+      <c r="C13" s="91"/>
       <c r="D13" s="8"/>
       <c r="E13" s="44">
         <v>2</v>
@@ -2799,10 +2836,10 @@
       <c r="F13" s="44"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="122" t="s">
+      <c r="B14" s="120" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="123"/>
+      <c r="C14" s="121"/>
       <c r="D14" s="11" t="s">
         <v>14</v>
       </c>
@@ -2810,10 +2847,10 @@
       <c r="F14" s="48"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="92" t="s">
+      <c r="B15" s="104" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="93"/>
+      <c r="C15" s="105"/>
       <c r="D15" s="11"/>
       <c r="E15" s="52">
         <v>5</v>
@@ -2821,19 +2858,19 @@
       <c r="F15" s="48"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="104" t="s">
+      <c r="B16" s="114" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="105"/>
+      <c r="C16" s="115"/>
       <c r="D16" s="8"/>
       <c r="E16" s="43"/>
       <c r="F16" s="44"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="92" t="s">
+      <c r="B17" s="104" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="93"/>
+      <c r="C17" s="105"/>
       <c r="D17" s="8"/>
       <c r="E17" s="43">
         <v>2</v>
@@ -2841,19 +2878,19 @@
       <c r="F17" s="44"/>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="104" t="s">
+      <c r="B18" s="114" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="105"/>
+      <c r="C18" s="115"/>
       <c r="D18" s="8"/>
       <c r="E18" s="43"/>
       <c r="F18" s="44"/>
     </row>
     <row r="19" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B19" s="118" t="s">
+      <c r="B19" s="122" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="119"/>
+      <c r="C19" s="123"/>
       <c r="D19" s="8"/>
       <c r="E19" s="43">
         <v>2</v>
@@ -2861,16 +2898,27 @@
       <c r="F19" s="44"/>
     </row>
     <row r="20" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B20" s="120" t="s">
+      <c r="B20" s="124" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="121"/>
+      <c r="C20" s="125"/>
       <c r="D20" s="12"/>
       <c r="E20" s="50"/>
       <c r="F20" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
@@ -2879,17 +2927,6 @@
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2903,10 +2940,10 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="108" t="s">
+      <c r="B2" s="96" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="109"/>
+      <c r="C2" s="97"/>
       <c r="D2" s="53" t="s">
         <v>9</v>
       </c>
@@ -2918,10 +2955,10 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="110" t="s">
+      <c r="B3" s="98" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="111"/>
+      <c r="C3" s="99"/>
       <c r="D3" s="53" t="s">
         <v>12</v>
       </c>
@@ -2929,10 +2966,10 @@
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B4" s="124" t="s">
+      <c r="B4" s="118" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="125"/>
+      <c r="C4" s="119"/>
       <c r="D4" s="7"/>
       <c r="E4" s="47">
         <v>3</v>
@@ -2940,10 +2977,10 @@
       <c r="F4" s="47"/>
     </row>
     <row r="5" spans="2:6">
-      <c r="B5" s="102" t="s">
+      <c r="B5" s="100" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="103"/>
+      <c r="C5" s="101"/>
       <c r="D5" s="7" t="s">
         <v>11</v>
       </c>
@@ -2951,10 +2988,10 @@
       <c r="F5" s="47"/>
     </row>
     <row r="6" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B6" s="92" t="s">
+      <c r="B6" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="93"/>
+      <c r="C6" s="105"/>
       <c r="D6" s="8"/>
       <c r="E6" s="44">
         <v>3</v>
@@ -2962,10 +2999,10 @@
       <c r="F6" s="44"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="116" t="s">
+      <c r="B7" s="94" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="117"/>
+      <c r="C7" s="95"/>
       <c r="D7" s="56" t="s">
         <v>10</v>
       </c>
@@ -2973,10 +3010,10 @@
       <c r="F7" s="57"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="96" t="s">
+      <c r="B8" s="90" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="97"/>
+      <c r="C8" s="91"/>
       <c r="D8" s="8"/>
       <c r="E8" s="44">
         <v>3</v>
@@ -2984,10 +3021,10 @@
       <c r="F8" s="44"/>
     </row>
     <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="92" t="s">
+      <c r="B9" s="104" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="93"/>
+      <c r="C9" s="105"/>
       <c r="D9" s="8"/>
       <c r="E9" s="44">
         <v>2</v>
@@ -2995,10 +3032,10 @@
       <c r="F9" s="44"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="102" t="s">
+      <c r="B10" s="100" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="103"/>
+      <c r="C10" s="101"/>
       <c r="D10" s="7" t="s">
         <v>14</v>
       </c>
@@ -3006,10 +3043,10 @@
       <c r="F10" s="47"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="92" t="s">
+      <c r="B11" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="93"/>
+      <c r="C11" s="105"/>
       <c r="D11" s="11"/>
       <c r="E11" s="48">
         <v>2</v>
@@ -3017,19 +3054,19 @@
       <c r="F11" s="48"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="104" t="s">
+      <c r="B12" s="114" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="105"/>
+      <c r="C12" s="115"/>
       <c r="D12" s="8"/>
       <c r="E12" s="44"/>
       <c r="F12" s="44"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="92" t="s">
+      <c r="B13" s="104" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="93"/>
+      <c r="C13" s="105"/>
       <c r="D13" s="8"/>
       <c r="E13" s="44">
         <v>1</v>
@@ -3037,10 +3074,10 @@
       <c r="F13" s="44"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="92" t="s">
+      <c r="B14" s="104" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="93"/>
+      <c r="C14" s="105"/>
       <c r="D14" s="8"/>
       <c r="E14" s="44">
         <v>1</v>
@@ -3048,19 +3085,19 @@
       <c r="F14" s="44"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="104" t="s">
+      <c r="B15" s="114" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="105"/>
+      <c r="C15" s="115"/>
       <c r="D15" s="8"/>
       <c r="E15" s="44"/>
       <c r="F15" s="44"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="96" t="s">
+      <c r="B16" s="90" t="s">
         <v>70</v>
       </c>
-      <c r="C16" s="97"/>
+      <c r="C16" s="91"/>
       <c r="D16" s="8"/>
       <c r="E16" s="44">
         <v>1</v>
@@ -3068,10 +3105,10 @@
       <c r="F16" s="44"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="96" t="s">
+      <c r="B17" s="90" t="s">
         <v>76</v>
       </c>
-      <c r="C17" s="97"/>
+      <c r="C17" s="91"/>
       <c r="D17" s="8"/>
       <c r="E17" s="44">
         <v>1</v>
@@ -3079,26 +3116,16 @@
       <c r="F17" s="44"/>
     </row>
     <row r="18" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B18" s="88" t="s">
+      <c r="B18" s="106" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="89"/>
+      <c r="C18" s="107"/>
       <c r="D18" s="54"/>
       <c r="E18" s="55"/>
       <c r="F18" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B11:C11"/>
@@ -3106,6 +3133,16 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ayato Terao\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B1E12B-8DB3-496D-AF8A-E76030A64821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F864A98-9E50-457E-A13B-26BA95F1A5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="90">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -174,16 +174,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>10/31が締切？</t>
-    <rPh sb="6" eb="7">
-      <t>シ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>キ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>プロト</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -197,13 +187,6 @@
   </si>
   <si>
     <t>マスタ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>9/9~9/11は素材探し</t>
-    <rPh sb="9" eb="12">
-      <t>ソザイサガ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1339,7 +1322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1374,8 +1357,6 @@
     <xf numFmtId="56" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
@@ -1402,7 +1383,6 @@
     </xf>
     <xf numFmtId="56" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1532,16 +1512,88 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1556,108 +1608,35 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="56" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1964,685 +1943,708 @@
   <sheetData>
     <row r="1" spans="2:19" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B2" s="96" t="s">
+      <c r="B2" s="107" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="97"/>
-      <c r="D2" s="53" t="s">
+      <c r="C2" s="108"/>
+      <c r="D2" s="50" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="66" t="s">
+      <c r="F2" s="63" t="s">
         <v>8</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B3" s="98" t="s">
+      <c r="B3" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="99"/>
-      <c r="D3" s="53" t="s">
+      <c r="C3" s="110"/>
+      <c r="D3" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="50">
+      <c r="E3" s="47">
         <f>SUM(E4:E15)</f>
         <v>14</v>
       </c>
-      <c r="F3" s="51">
+      <c r="F3" s="48">
         <f>SUM(F4:F15)</f>
         <v>12</v>
       </c>
-      <c r="G3" s="53" t="s">
-        <v>85</v>
-      </c>
-      <c r="I3" s="71" t="s">
+      <c r="G3" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="I3" s="68" t="s">
+        <v>77</v>
+      </c>
+      <c r="J3" s="72">
+        <f ca="1">TODAY()</f>
+        <v>46294</v>
+      </c>
+      <c r="K3" s="50" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19">
+      <c r="B4" s="111" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="112"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="I4" s="73" t="s">
+        <v>78</v>
+      </c>
+      <c r="J4" s="69">
+        <v>46295</v>
+      </c>
+      <c r="K4" s="67" t="str">
+        <f ca="1">SUM($J4-J3)&amp; "日"</f>
+        <v>1日</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19">
+      <c r="B5" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="92"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="41">
+        <v>2</v>
+      </c>
+      <c r="F5" s="41">
+        <v>2</v>
+      </c>
+      <c r="G5" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="74" t="s">
         <v>79</v>
       </c>
-      <c r="J3" s="75">
-        <f ca="1">TODAY()</f>
-        <v>46293</v>
-      </c>
-      <c r="K3" s="53" t="s">
+      <c r="J5" s="70">
+        <v>46305</v>
+      </c>
+      <c r="K5" s="65" t="str">
+        <f ca="1">SUM($J5-J3)&amp; "日"</f>
+        <v>11日</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19">
+      <c r="B6" s="91" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="92"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="41">
+        <v>1</v>
+      </c>
+      <c r="F6" s="41">
+        <v>2</v>
+      </c>
+      <c r="G6" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" s="75" t="s">
+        <v>80</v>
+      </c>
+      <c r="J6" s="70">
+        <v>46310</v>
+      </c>
+      <c r="K6" s="65" t="str">
+        <f ca="1">SUM($J6-J3)&amp; "日"</f>
+        <v>16日</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19">
+      <c r="B7" s="91" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="92"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="41">
+        <v>1</v>
+      </c>
+      <c r="F7" s="45">
+        <v>1</v>
+      </c>
+      <c r="G7" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="I7" s="76" t="s">
+        <v>81</v>
+      </c>
+      <c r="J7" s="70">
+        <v>46313</v>
+      </c>
+      <c r="K7" s="65" t="str">
+        <f ca="1">SUM($J7-J3)&amp; "日"</f>
+        <v>19日</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19" ht="19.5" thickBot="1">
+      <c r="B8" s="99" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="4" spans="2:19">
-      <c r="B4" s="102" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="103"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="62" t="s">
-        <v>89</v>
-      </c>
-      <c r="I4" s="76" t="s">
-        <v>80</v>
-      </c>
-      <c r="J4" s="72">
-        <v>46295</v>
-      </c>
-      <c r="K4" s="70" t="str">
-        <f ca="1">SUM($J4-J3)&amp; "日"</f>
-        <v>2日</v>
-      </c>
-    </row>
-    <row r="5" spans="2:19">
-      <c r="B5" s="104" t="s">
+      <c r="C8" s="100"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="41">
+        <v>2</v>
+      </c>
+      <c r="F8" s="45">
+        <v>2</v>
+      </c>
+      <c r="G8" s="59" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" s="77" t="s">
+        <v>76</v>
+      </c>
+      <c r="J8" s="71">
+        <v>46314</v>
+      </c>
+      <c r="K8" s="66" t="str">
+        <f ca="1">SUM(J8-J3)&amp; "日"</f>
+        <v>20日</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19">
+      <c r="B9" s="99" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="100"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="42">
+        <v>2</v>
+      </c>
+      <c r="F9" s="42">
+        <v>1</v>
+      </c>
+      <c r="G9" s="59" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19">
+      <c r="B10" s="99" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="105"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="44">
+      <c r="C10" s="100"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="42">
         <v>2</v>
       </c>
-      <c r="F5" s="44">
-        <v>2</v>
-      </c>
-      <c r="G5" s="62" t="s">
-        <v>89</v>
-      </c>
-      <c r="I5" s="77" t="s">
-        <v>81</v>
-      </c>
-      <c r="J5" s="73">
-        <v>46305</v>
-      </c>
-      <c r="K5" s="68" t="str">
-        <f ca="1">SUM($J5-J3)&amp; "日"</f>
-        <v>12日</v>
-      </c>
-    </row>
-    <row r="6" spans="2:19">
-      <c r="B6" s="104" t="s">
+      <c r="F10" s="42"/>
+      <c r="G10" s="58" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19">
+      <c r="B11" s="113" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="114"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="41">
+        <v>1</v>
+      </c>
+      <c r="F11" s="41">
+        <v>1</v>
+      </c>
+      <c r="G11" s="58" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19">
+      <c r="B12" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="105"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="44">
+      <c r="C12" s="100"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="58" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19">
+      <c r="B13" s="95" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="96"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="41">
         <v>1</v>
       </c>
-      <c r="F6" s="44">
-        <v>2</v>
-      </c>
-      <c r="G6" s="62" t="s">
-        <v>89</v>
-      </c>
-      <c r="I6" s="78" t="s">
-        <v>82</v>
-      </c>
-      <c r="J6" s="73">
-        <v>46310</v>
-      </c>
-      <c r="K6" s="68" t="str">
-        <f ca="1">SUM($J6-J3)&amp; "日"</f>
-        <v>17日</v>
-      </c>
-    </row>
-    <row r="7" spans="2:19">
-      <c r="B7" s="104" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" s="105"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="44">
+      <c r="F13" s="41">
         <v>1</v>
       </c>
-      <c r="F7" s="48">
+      <c r="G13" s="58" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19">
+      <c r="B14" s="91" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="92"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="41">
         <v>1</v>
       </c>
-      <c r="G7" s="62" t="s">
-        <v>89</v>
-      </c>
-      <c r="I7" s="79" t="s">
-        <v>83</v>
-      </c>
-      <c r="J7" s="73">
-        <v>46313</v>
-      </c>
-      <c r="K7" s="68" t="str">
-        <f ca="1">SUM($J7-J3)&amp; "日"</f>
-        <v>20日</v>
-      </c>
-    </row>
-    <row r="8" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B8" s="88" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="89"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="44">
-        <v>2</v>
-      </c>
-      <c r="F8" s="48">
-        <v>2</v>
-      </c>
-      <c r="G8" s="62" t="s">
-        <v>89</v>
-      </c>
-      <c r="I8" s="80" t="s">
-        <v>78</v>
-      </c>
-      <c r="J8" s="74">
-        <v>46314</v>
-      </c>
-      <c r="K8" s="69" t="str">
-        <f ca="1">SUM(J8-J3)&amp; "日"</f>
-        <v>21日</v>
-      </c>
-    </row>
-    <row r="9" spans="2:19">
-      <c r="B9" s="88" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="89"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="45">
-        <v>2</v>
-      </c>
-      <c r="F9" s="45">
+      <c r="F14" s="41">
         <v>1</v>
       </c>
-      <c r="G9" s="62" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="10" spans="2:19">
-      <c r="B10" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" s="89"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="45">
-        <v>2</v>
-      </c>
-      <c r="F10" s="45"/>
-      <c r="G10" s="61" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="2:19">
-      <c r="B11" s="92" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" s="93"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="44">
+      <c r="G14" s="58" t="s">
+        <v>87</v>
+      </c>
+      <c r="R14" s="85"/>
+      <c r="S14" s="86"/>
+    </row>
+    <row r="15" spans="2:19" ht="19.5" thickBot="1">
+      <c r="B15" s="93" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="94"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="42">
         <v>1</v>
       </c>
-      <c r="F11" s="44">
+      <c r="F15" s="42">
         <v>1</v>
       </c>
-      <c r="G11" s="61" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="12" spans="2:19">
-      <c r="B12" s="88" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" s="89"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="61" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="2:19">
-      <c r="B13" s="90" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="91"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="44">
+      <c r="G15" s="58" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19">
+      <c r="B16" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="F13" s="44">
-        <v>1</v>
-      </c>
-      <c r="G13" s="61" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" spans="2:19">
-      <c r="B14" s="104" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="105"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="44">
-        <v>1</v>
-      </c>
-      <c r="F14" s="44">
-        <v>1</v>
-      </c>
-      <c r="G14" s="61" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q14" s="129"/>
-      <c r="R14" s="127"/>
-      <c r="S14" s="128"/>
-    </row>
-    <row r="15" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B15" s="110" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="111"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="45">
-        <v>1</v>
-      </c>
-      <c r="F15" s="45">
-        <v>1</v>
-      </c>
-      <c r="G15" s="61" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="16" spans="2:19">
-      <c r="B16" s="100" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="101"/>
+      <c r="C16" s="102"/>
       <c r="D16" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="86">
+      <c r="E16" s="83">
         <f>SUM(E17:E25)</f>
         <v>16</v>
       </c>
-      <c r="F16" s="47">
+      <c r="F16" s="44">
         <v>8</v>
       </c>
-      <c r="G16" s="67" t="s">
-        <v>85</v>
+      <c r="G16" s="64" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="88" t="s">
+      <c r="B17" s="99" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="100"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="81">
+        <v>3</v>
+      </c>
+      <c r="F17" s="41">
+        <v>1</v>
+      </c>
+      <c r="G17" s="58" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="99" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="100"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="81">
+        <v>3</v>
+      </c>
+      <c r="F18" s="41">
+        <v>1</v>
+      </c>
+      <c r="G18" s="58" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="89"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="84">
+      <c r="C19" s="100"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="81">
         <v>3</v>
       </c>
-      <c r="F17" s="44">
+      <c r="F19" s="41">
         <v>1</v>
       </c>
-      <c r="G17" s="61" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="88" t="s">
+      <c r="G19" s="58" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="99" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="89"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="84">
+      <c r="C20" s="100"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="81">
         <v>3</v>
       </c>
-      <c r="F18" s="44">
+      <c r="F20" s="41">
         <v>1</v>
       </c>
-      <c r="G18" s="61" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="88" t="s">
+      <c r="G20" s="58" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="99" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="89"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="84">
+      <c r="C21" s="100"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="82">
+        <v>1</v>
+      </c>
+      <c r="F21" s="41">
+        <v>1</v>
+      </c>
+      <c r="G21" s="58" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" s="113" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="114"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="41">
         <v>3</v>
       </c>
-      <c r="F19" s="44">
+      <c r="G22" s="58" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" s="95" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="96"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="81">
         <v>1</v>
       </c>
-      <c r="G19" s="61" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="88" t="s">
+      <c r="F23" s="41">
+        <v>1</v>
+      </c>
+      <c r="G23" s="58" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7">
+      <c r="B24" s="95" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="96"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="81">
+        <v>1</v>
+      </c>
+      <c r="F24" s="41">
+        <v>1</v>
+      </c>
+      <c r="G24" s="58" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B25" s="97" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="89"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="84">
-        <v>3</v>
-      </c>
-      <c r="F20" s="44">
+      <c r="C25" s="98"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="84">
         <v>1</v>
       </c>
-      <c r="G20" s="61" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7">
-      <c r="B21" s="88" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="89"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="85">
+      <c r="F25" s="43">
         <v>1</v>
       </c>
-      <c r="F21" s="44">
-        <v>1</v>
-      </c>
-      <c r="G21" s="61" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="92" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="93"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="84"/>
-      <c r="F22" s="44">
-        <v>3</v>
-      </c>
-      <c r="G22" s="61" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="90" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="91"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="84">
-        <v>1</v>
-      </c>
-      <c r="F23" s="44">
-        <v>1</v>
-      </c>
-      <c r="G23" s="61" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7">
-      <c r="B24" s="90" t="s">
-        <v>45</v>
-      </c>
-      <c r="C24" s="91"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="84">
-        <v>1</v>
-      </c>
-      <c r="F24" s="44">
-        <v>1</v>
-      </c>
-      <c r="G24" s="61" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B25" s="112" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="113"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="87">
-        <v>1</v>
-      </c>
-      <c r="F25" s="46">
-        <v>1</v>
-      </c>
-      <c r="G25" s="61" t="s">
-        <v>89</v>
+      <c r="G25" s="58" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="2:7">
-      <c r="B26" s="94" t="s">
+      <c r="B26" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="95"/>
-      <c r="D26" s="56" t="s">
+      <c r="C26" s="116"/>
+      <c r="D26" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="57">
+      <c r="E26" s="54">
         <f>SUM(E27:E31)</f>
         <v>12</v>
       </c>
-      <c r="F26" s="57">
+      <c r="F26" s="54">
         <f>SUM(F27,F28,F31)</f>
         <v>8</v>
       </c>
-      <c r="G26" s="67" t="s">
-        <v>85</v>
+      <c r="G26" s="64" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="92" t="s">
+      <c r="B27" s="113" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="114"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="41">
+        <v>5</v>
+      </c>
+      <c r="F27" s="41">
+        <v>5</v>
+      </c>
+      <c r="G27" s="58" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7">
+      <c r="B28" s="113" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="114"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="58" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7">
+      <c r="B29" s="95" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="93"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="44">
-        <v>5</v>
-      </c>
-      <c r="F27" s="44">
-        <v>5</v>
-      </c>
-      <c r="G27" s="61" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7">
-      <c r="B28" s="92" t="s">
+      <c r="C29" s="96"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="41">
+        <v>2</v>
+      </c>
+      <c r="F29" s="41"/>
+      <c r="G29" s="58" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7">
+      <c r="B30" s="95" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="93"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="61" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7">
-      <c r="B29" s="90" t="s">
+      <c r="C30" s="96"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="41">
+        <v>2</v>
+      </c>
+      <c r="F30" s="41"/>
+      <c r="G30" s="58" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B31" s="89" t="s">
         <v>55</v>
       </c>
-      <c r="C29" s="91"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="44">
-        <v>2</v>
-      </c>
-      <c r="F29" s="44"/>
-      <c r="G29" s="61" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7">
-      <c r="B30" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="91"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="44">
-        <v>2</v>
-      </c>
-      <c r="F30" s="44"/>
-      <c r="G30" s="61" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B31" s="108" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" s="109"/>
+      <c r="C31" s="90"/>
       <c r="D31" s="9"/>
-      <c r="E31" s="46">
+      <c r="E31" s="43">
         <v>3</v>
       </c>
-      <c r="F31" s="46">
+      <c r="F31" s="43">
         <v>3</v>
       </c>
-      <c r="G31" s="63" t="s">
-        <v>89</v>
+      <c r="G31" s="60" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="2:7">
-      <c r="B32" s="100" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" s="101"/>
+      <c r="B32" s="101" t="s">
+        <v>60</v>
+      </c>
+      <c r="C32" s="102"/>
       <c r="D32" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="83">
+      <c r="E32" s="80">
         <f>SUM(E33:E40)</f>
         <v>11</v>
       </c>
-      <c r="F32" s="47">
+      <c r="F32" s="44">
         <f>SUM(F34,F36,F37,F39,F40)</f>
         <v>0</v>
       </c>
-      <c r="G32" s="67" t="s">
+      <c r="G32" s="64" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="99" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="100"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="58" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="91" t="s">
+        <v>56</v>
+      </c>
+      <c r="C34" s="92"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="49">
+        <v>2</v>
+      </c>
+      <c r="F34" s="45"/>
+      <c r="G34" s="58" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="B35" s="103" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="104"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="58" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="99" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" s="100"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="40">
+        <v>2</v>
+      </c>
+      <c r="F36" s="41"/>
+      <c r="G36" s="58" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="99" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="100"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="40">
+        <v>2</v>
+      </c>
+      <c r="F37" s="41"/>
+      <c r="G37" s="58" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="103" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="104"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="58" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" s="105" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="106"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="40">
+        <v>2</v>
+      </c>
+      <c r="F39" s="41"/>
+      <c r="G39" s="58" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B40" s="89" t="s">
+        <v>62</v>
+      </c>
+      <c r="C40" s="90"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="46">
+        <v>3</v>
+      </c>
+      <c r="F40" s="43"/>
+      <c r="G40" s="60" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B41" s="87" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="88" t="s">
-        <v>61</v>
-      </c>
-      <c r="C33" s="89"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="61" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7">
-      <c r="B34" s="104" t="s">
-        <v>58</v>
-      </c>
-      <c r="C34" s="105"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="52">
-        <v>2</v>
-      </c>
-      <c r="F34" s="48"/>
-      <c r="G34" s="61" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="114" t="s">
-        <v>4</v>
-      </c>
-      <c r="C35" s="115"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="61" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="88" t="s">
-        <v>59</v>
-      </c>
-      <c r="C36" s="89"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="43">
-        <v>2</v>
-      </c>
-      <c r="F36" s="44"/>
-      <c r="G36" s="61" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7">
-      <c r="B37" s="88" t="s">
-        <v>60</v>
-      </c>
-      <c r="C37" s="89"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="43">
-        <v>2</v>
-      </c>
-      <c r="F37" s="44"/>
-      <c r="G37" s="61" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7">
-      <c r="B38" s="114" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="115"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="44"/>
-      <c r="G38" s="61" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7">
-      <c r="B39" s="116" t="s">
-        <v>63</v>
-      </c>
-      <c r="C39" s="117"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="43">
-        <v>2</v>
-      </c>
-      <c r="F39" s="44"/>
-      <c r="G39" s="61" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B40" s="108" t="s">
-        <v>64</v>
-      </c>
-      <c r="C40" s="109"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="49">
-        <v>3</v>
-      </c>
-      <c r="F40" s="46"/>
-      <c r="G40" s="63" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B41" s="106" t="s">
-        <v>87</v>
-      </c>
-      <c r="C41" s="107"/>
-      <c r="D41" s="54"/>
-      <c r="E41" s="81">
+      <c r="C41" s="88"/>
+      <c r="D41" s="51"/>
+      <c r="E41" s="78">
         <f>SUM(E3+E16+E26+F32)</f>
         <v>42</v>
       </c>
-      <c r="F41" s="82">
+      <c r="F41" s="79">
         <f>SUM(F4:F40)</f>
         <v>47</v>
       </c>
-      <c r="G41" s="54"/>
+      <c r="G41" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B7:C7"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B14:C14"/>
@@ -2659,30 +2661,6 @@
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B19:C19"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2700,11 +2678,11 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="96" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" s="97"/>
-      <c r="D2" s="53" t="s">
+      <c r="B2" s="107" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="108"/>
+      <c r="D2" s="50" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -2715,210 +2693,199 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="98" t="s">
+      <c r="B3" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="99"/>
-      <c r="D3" s="53" t="s">
+      <c r="C3" s="110"/>
+      <c r="D3" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="50"/>
+      <c r="E3" s="47"/>
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="118" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" s="119"/>
+      <c r="B4" s="123" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="124"/>
       <c r="D4" s="7"/>
-      <c r="E4" s="47">
+      <c r="E4" s="44">
         <v>2</v>
       </c>
-      <c r="F4" s="47"/>
+      <c r="F4" s="44"/>
     </row>
     <row r="5" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B5" s="104" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="105"/>
+      <c r="B5" s="91" t="s">
+        <v>69</v>
+      </c>
+      <c r="C5" s="92"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="44">
+      <c r="E5" s="41">
         <v>2</v>
       </c>
-      <c r="F5" s="44"/>
+      <c r="F5" s="41"/>
     </row>
     <row r="6" spans="2:6">
-      <c r="B6" s="100" t="s">
+      <c r="B6" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="101"/>
+      <c r="C6" s="102"/>
       <c r="D6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="104" t="s">
-        <v>67</v>
-      </c>
-      <c r="C7" s="105"/>
+      <c r="B7" s="91" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="92"/>
       <c r="D7" s="8"/>
-      <c r="E7" s="44">
+      <c r="E7" s="41">
         <v>2</v>
       </c>
-      <c r="F7" s="44"/>
+      <c r="F7" s="41"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="104" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" s="105"/>
+      <c r="B8" s="91" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="92"/>
       <c r="D8" s="8"/>
-      <c r="E8" s="44">
+      <c r="E8" s="41">
         <v>3</v>
       </c>
-      <c r="F8" s="44"/>
+      <c r="F8" s="41"/>
     </row>
     <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="104" t="s">
+      <c r="B9" s="91" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="92"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="41">
+        <v>2</v>
+      </c>
+      <c r="F9" s="41"/>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" s="115" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="116"/>
+      <c r="D10" s="53" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11" s="95" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="96"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="41">
+        <v>5</v>
+      </c>
+      <c r="F11" s="41"/>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="B12" s="95" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="105"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="44">
+      <c r="C12" s="96"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="41">
+        <v>1</v>
+      </c>
+      <c r="F12" s="41"/>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13" s="95" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="96"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="41">
         <v>2</v>
       </c>
-      <c r="F9" s="44"/>
-    </row>
-    <row r="10" spans="2:6">
-      <c r="B10" s="94" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="95"/>
-      <c r="D10" s="56" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-    </row>
-    <row r="11" spans="2:6">
-      <c r="B11" s="90" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" s="91"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="44">
-        <v>5</v>
-      </c>
-      <c r="F11" s="44"/>
-    </row>
-    <row r="12" spans="2:6">
-      <c r="B12" s="90" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" s="91"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="44">
-        <v>1</v>
-      </c>
-      <c r="F12" s="44"/>
-    </row>
-    <row r="13" spans="2:6">
-      <c r="B13" s="90" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" s="91"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="44">
-        <v>2</v>
-      </c>
-      <c r="F13" s="44"/>
+      <c r="F13" s="41"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="120" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="121"/>
+      <c r="B14" s="121" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="122"/>
       <c r="D14" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="52"/>
-      <c r="F14" s="48"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="45"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="104" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="105"/>
+      <c r="B15" s="91" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="92"/>
       <c r="D15" s="11"/>
-      <c r="E15" s="52">
+      <c r="E15" s="49">
         <v>5</v>
       </c>
-      <c r="F15" s="48"/>
+      <c r="F15" s="45"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="114" t="s">
+      <c r="B16" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="115"/>
+      <c r="C16" s="104"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="44"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="41"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="104" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="105"/>
+      <c r="B17" s="91" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="92"/>
       <c r="D17" s="8"/>
-      <c r="E17" s="43">
+      <c r="E17" s="40">
         <v>2</v>
       </c>
-      <c r="F17" s="44"/>
+      <c r="F17" s="41"/>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="114" t="s">
+      <c r="B18" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="115"/>
+      <c r="C18" s="104"/>
       <c r="D18" s="8"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="44"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="41"/>
     </row>
     <row r="19" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B19" s="122" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="123"/>
+      <c r="B19" s="117" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="118"/>
       <c r="D19" s="8"/>
-      <c r="E19" s="43">
+      <c r="E19" s="40">
         <v>2</v>
       </c>
-      <c r="F19" s="44"/>
+      <c r="F19" s="41"/>
     </row>
     <row r="20" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B20" s="124" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="125"/>
+      <c r="B20" s="119" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="120"/>
       <c r="D20" s="12"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="51"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
@@ -2927,6 +2894,17 @@
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2940,11 +2918,11 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="96" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" s="97"/>
-      <c r="D2" s="53" t="s">
+      <c r="B2" s="107" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="108"/>
+      <c r="D2" s="50" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
@@ -2955,177 +2933,187 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="98" t="s">
+      <c r="B3" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="99"/>
-      <c r="D3" s="53" t="s">
+      <c r="C3" s="110"/>
+      <c r="D3" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="50"/>
+      <c r="E3" s="47"/>
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B4" s="118" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="119"/>
+      <c r="B4" s="123" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="124"/>
       <c r="D4" s="7"/>
-      <c r="E4" s="47">
+      <c r="E4" s="44">
         <v>3</v>
       </c>
-      <c r="F4" s="47"/>
+      <c r="F4" s="44"/>
     </row>
     <row r="5" spans="2:6">
-      <c r="B5" s="100" t="s">
+      <c r="B5" s="101" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="101"/>
+      <c r="C5" s="102"/>
       <c r="D5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
     </row>
     <row r="6" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B6" s="104" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="105"/>
+      <c r="B6" s="91" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="92"/>
       <c r="D6" s="8"/>
-      <c r="E6" s="44">
+      <c r="E6" s="41">
         <v>3</v>
       </c>
-      <c r="F6" s="44"/>
+      <c r="F6" s="41"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="94" t="s">
+      <c r="B7" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="95"/>
-      <c r="D7" s="56" t="s">
+      <c r="C7" s="116"/>
+      <c r="D7" s="53" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="90" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="91"/>
+      <c r="B8" s="95" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="96"/>
       <c r="D8" s="8"/>
-      <c r="E8" s="44">
+      <c r="E8" s="41">
         <v>3</v>
       </c>
-      <c r="F8" s="44"/>
+      <c r="F8" s="41"/>
     </row>
     <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="104" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="105"/>
+      <c r="B9" s="91" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="92"/>
       <c r="D9" s="8"/>
-      <c r="E9" s="44">
+      <c r="E9" s="41">
         <v>2</v>
       </c>
-      <c r="F9" s="44"/>
+      <c r="F9" s="41"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="100" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="101"/>
+      <c r="B10" s="101" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="102"/>
       <c r="D10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="104" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" s="105"/>
+      <c r="B11" s="91" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" s="92"/>
       <c r="D11" s="11"/>
-      <c r="E11" s="48">
+      <c r="E11" s="45">
         <v>2</v>
       </c>
-      <c r="F11" s="48"/>
+      <c r="F11" s="45"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="114" t="s">
+      <c r="B12" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="115"/>
+      <c r="C12" s="104"/>
       <c r="D12" s="8"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="104" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="105"/>
+      <c r="B13" s="91" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="92"/>
       <c r="D13" s="8"/>
-      <c r="E13" s="44">
+      <c r="E13" s="41">
         <v>1</v>
       </c>
-      <c r="F13" s="44"/>
+      <c r="F13" s="41"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="104" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" s="105"/>
+      <c r="B14" s="91" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="92"/>
       <c r="D14" s="8"/>
-      <c r="E14" s="44">
+      <c r="E14" s="41">
         <v>1</v>
       </c>
-      <c r="F14" s="44"/>
+      <c r="F14" s="41"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="114" t="s">
+      <c r="B15" s="103" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="115"/>
+      <c r="C15" s="104"/>
       <c r="D15" s="8"/>
-      <c r="E15" s="44"/>
-      <c r="F15" s="44"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="90" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="91"/>
+      <c r="B16" s="95" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="96"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="44">
+      <c r="E16" s="41">
         <v>1</v>
       </c>
-      <c r="F16" s="44"/>
+      <c r="F16" s="41"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="90" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="91"/>
+      <c r="B17" s="95" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="96"/>
       <c r="D17" s="8"/>
-      <c r="E17" s="44">
+      <c r="E17" s="41">
         <v>1</v>
       </c>
-      <c r="F17" s="44"/>
+      <c r="F17" s="41"/>
     </row>
     <row r="18" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B18" s="106" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="107"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
+      <c r="B18" s="87" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="88"/>
+      <c r="D18" s="51"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B11:C11"/>
@@ -3133,16 +3121,6 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3151,186 +3129,186 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D63B4141-FE5F-4FCB-9F3D-2486D26F1F00}">
-  <dimension ref="B1:K13"/>
+  <dimension ref="B1:K12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="126" t="s">
+      <c r="C1" s="125" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="125"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
     </row>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="34" t="s">
+      <c r="E2" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="G2" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="35" t="s">
+      <c r="H2" s="33" t="s">
         <v>21</v>
       </c>
       <c r="J2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="2:11">
-      <c r="B3" s="30"/>
-      <c r="D3" s="31">
+      <c r="B3" s="28"/>
+      <c r="D3" s="29">
         <v>46266</v>
       </c>
-      <c r="E3" s="31">
+      <c r="E3" s="29">
         <f>SUM(D3)+1</f>
         <v>46267</v>
       </c>
-      <c r="F3" s="31">
+      <c r="F3" s="29">
         <f t="shared" ref="F3:H3" si="0">SUM(E3)+1</f>
         <v>46268</v>
       </c>
-      <c r="G3" s="31">
+      <c r="G3" s="29">
         <f t="shared" si="0"/>
         <v>46269</v>
       </c>
-      <c r="H3" s="32">
+      <c r="H3" s="30">
         <f t="shared" si="0"/>
         <v>46270</v>
       </c>
-      <c r="J3" s="18"/>
+      <c r="J3" s="16"/>
       <c r="K3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="22">
+      <c r="B4" s="20">
         <f>SUM(H3)+1</f>
         <v>46271</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="19">
         <f>SUM(B4)+1</f>
         <v>46272</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="19">
         <f t="shared" ref="D4:H4" si="1">SUM(C4)+1</f>
         <v>46273</v>
       </c>
-      <c r="E4" s="58">
+      <c r="E4" s="55">
         <f t="shared" si="1"/>
         <v>46274</v>
       </c>
-      <c r="F4" s="58">
+      <c r="F4" s="55">
         <f t="shared" si="1"/>
         <v>46275</v>
       </c>
-      <c r="G4" s="58">
+      <c r="G4" s="55">
         <f t="shared" si="1"/>
         <v>46276</v>
       </c>
-      <c r="H4" s="59">
+      <c r="H4" s="56">
         <f t="shared" si="1"/>
         <v>46277</v>
       </c>
-      <c r="J4" s="19"/>
+      <c r="J4" s="17"/>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="60">
+      <c r="B5" s="57">
         <f>SUM(H4)+1</f>
         <v>46278</v>
       </c>
-      <c r="C5" s="58">
+      <c r="C5" s="55">
         <f>SUM(B5)+1</f>
         <v>46279</v>
       </c>
-      <c r="D5" s="58">
+      <c r="D5" s="55">
         <f t="shared" ref="D5:H5" si="2">SUM(C5)+1</f>
         <v>46280</v>
       </c>
-      <c r="E5" s="58">
+      <c r="E5" s="55">
         <f t="shared" si="2"/>
         <v>46281</v>
       </c>
-      <c r="F5" s="58">
+      <c r="F5" s="55">
         <f t="shared" si="2"/>
         <v>46282</v>
       </c>
-      <c r="G5" s="58">
+      <c r="G5" s="55">
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="H5" s="59">
+      <c r="H5" s="56">
         <f t="shared" si="2"/>
         <v>46284</v>
       </c>
-      <c r="J5" s="20"/>
+      <c r="J5" s="18"/>
       <c r="K5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" s="60">
+      <c r="B6" s="57">
         <f>SUM(H5)+1</f>
         <v>46285</v>
       </c>
-      <c r="C6" s="58">
+      <c r="C6" s="55">
         <f>SUM(B6)+1</f>
         <v>46286</v>
       </c>
-      <c r="D6" s="58">
+      <c r="D6" s="55">
         <f t="shared" ref="D6:H6" si="3">SUM(C6)+1</f>
         <v>46287</v>
       </c>
-      <c r="E6" s="58">
+      <c r="E6" s="55">
         <f t="shared" si="3"/>
         <v>46288</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="55">
         <f t="shared" si="3"/>
         <v>46289</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="55">
         <f t="shared" si="3"/>
         <v>46290</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="56">
         <f t="shared" si="3"/>
         <v>46291</v>
       </c>
-      <c r="J6" s="28"/>
+      <c r="J6" s="26"/>
       <c r="K6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B7" s="38">
+      <c r="B7" s="126">
         <f>SUM(H6)+1</f>
         <v>46292</v>
       </c>
-      <c r="C7" s="39">
+      <c r="C7" s="127">
         <f>SUM(B7)+1</f>
         <v>46293</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="127">
         <f t="shared" ref="D7:E7" si="4">SUM(C7)+1</f>
         <v>46294</v>
       </c>
-      <c r="E7" s="39">
+      <c r="E7" s="36">
         <f t="shared" si="4"/>
         <v>46295</v>
       </c>
@@ -3339,89 +3317,89 @@
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="2:11">
-      <c r="B8" s="30"/>
+      <c r="B8" s="28"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="36">
+      <c r="F8" s="34">
         <f>SUM(E7)+1</f>
         <v>46296</v>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="34">
         <f>SUM(F8)+1</f>
         <v>46297</v>
       </c>
-      <c r="H8" s="37">
+      <c r="H8" s="35">
         <f>SUM(G8)+1</f>
         <v>46298</v>
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="23">
+      <c r="B9" s="21">
         <f>SUM(H8)+1</f>
         <v>46299</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="22">
         <f>SUM(B9)+1</f>
         <v>46300</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="22">
         <f t="shared" ref="D9:H9" si="5">SUM(C9)+1</f>
         <v>46301</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="22">
         <f t="shared" si="5"/>
         <v>46302</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="22">
         <f t="shared" si="5"/>
         <v>46303</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="22">
         <f t="shared" si="5"/>
         <v>46304</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="23">
         <f t="shared" si="5"/>
         <v>46305</v>
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="27">
+      <c r="B10" s="25">
         <f t="shared" ref="B10:B12" si="6">SUM(H9)+1</f>
         <v>46306</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="24">
         <f>SUM(B10)+1</f>
         <v>46307</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="24">
         <f t="shared" ref="D10:G10" si="7">SUM(C10)+1</f>
         <v>46308</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="24">
         <f t="shared" si="7"/>
         <v>46309</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="24">
         <f t="shared" si="7"/>
         <v>46310</v>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="27">
         <f t="shared" si="7"/>
         <v>46311</v>
       </c>
-      <c r="H10" s="65">
+      <c r="H10" s="62">
         <f>SUM(G10)+1</f>
         <v>46312</v>
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="64">
+      <c r="B11" s="61">
         <f t="shared" si="6"/>
         <v>46313</v>
       </c>
-      <c r="C11" s="42">
+      <c r="C11" s="39">
         <f>SUM(B11)+1</f>
         <v>46314</v>
       </c>
@@ -3441,13 +3419,13 @@
         <f t="shared" ref="G11" si="9">SUM(F11)+1</f>
         <v>46318</v>
       </c>
-      <c r="H11" s="40">
+      <c r="H11" s="37">
         <f>SUM(G11)+1</f>
         <v>46319</v>
       </c>
     </row>
     <row r="12" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B12" s="41">
+      <c r="B12" s="38">
         <f t="shared" si="6"/>
         <v>46320</v>
       </c>
@@ -3474,14 +3452,6 @@
       <c r="H12" s="15">
         <f t="shared" si="10"/>
         <v>46326</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11">
-      <c r="B13" t="s">
-        <v>28</v>
-      </c>
-      <c r="H13" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -3505,17 +3475,17 @@
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="2:2">
       <c r="B4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="2:2">
@@ -3525,12 +3495,12 @@
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="2:2">
       <c r="B8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="2:2">
@@ -3540,22 +3510,22 @@
     </row>
     <row r="10" spans="2:2">
       <c r="B10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="2:2">
       <c r="B13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="2:2">

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ayato Terao\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F864A98-9E50-457E-A13B-26BA95F1A5C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7561CED6-177E-4081-807E-0F70A2ED43C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>
@@ -1518,125 +1518,125 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="56" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="56" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1943,10 +1943,10 @@
   <sheetData>
     <row r="1" spans="2:19" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="98" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="108"/>
+      <c r="C2" s="99"/>
       <c r="D2" s="50" t="s">
         <v>9</v>
       </c>
@@ -1961,10 +1961,10 @@
       </c>
     </row>
     <row r="3" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B3" s="109" t="s">
+      <c r="B3" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="110"/>
+      <c r="C3" s="101"/>
       <c r="D3" s="50" t="s">
         <v>12</v>
       </c>
@@ -1984,17 +1984,17 @@
       </c>
       <c r="J3" s="72">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="K3" s="50" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="4" spans="2:19">
-      <c r="B4" s="111" t="s">
+      <c r="B4" s="104" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="112"/>
+      <c r="C4" s="105"/>
       <c r="D4" s="11"/>
       <c r="E4" s="45"/>
       <c r="F4" s="45"/>
@@ -2009,14 +2009,14 @@
       </c>
       <c r="K4" s="67" t="str">
         <f ca="1">SUM($J4-J3)&amp; "日"</f>
-        <v>1日</v>
+        <v>0日</v>
       </c>
     </row>
     <row r="5" spans="2:19">
-      <c r="B5" s="91" t="s">
+      <c r="B5" s="106" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="92"/>
+      <c r="C5" s="107"/>
       <c r="D5" s="8"/>
       <c r="E5" s="41">
         <v>2</v>
@@ -2035,14 +2035,14 @@
       </c>
       <c r="K5" s="65" t="str">
         <f ca="1">SUM($J5-J3)&amp; "日"</f>
-        <v>11日</v>
+        <v>10日</v>
       </c>
     </row>
     <row r="6" spans="2:19">
-      <c r="B6" s="91" t="s">
+      <c r="B6" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="92"/>
+      <c r="C6" s="107"/>
       <c r="D6" s="8"/>
       <c r="E6" s="41">
         <v>1</v>
@@ -2061,14 +2061,14 @@
       </c>
       <c r="K6" s="65" t="str">
         <f ca="1">SUM($J6-J3)&amp; "日"</f>
-        <v>16日</v>
+        <v>15日</v>
       </c>
     </row>
     <row r="7" spans="2:19">
-      <c r="B7" s="91" t="s">
+      <c r="B7" s="106" t="s">
         <v>89</v>
       </c>
-      <c r="C7" s="92"/>
+      <c r="C7" s="107"/>
       <c r="D7" s="8"/>
       <c r="E7" s="41">
         <v>1</v>
@@ -2087,14 +2087,14 @@
       </c>
       <c r="K7" s="65" t="str">
         <f ca="1">SUM($J7-J3)&amp; "日"</f>
-        <v>19日</v>
+        <v>18日</v>
       </c>
     </row>
     <row r="8" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B8" s="99" t="s">
+      <c r="B8" s="90" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="100"/>
+      <c r="C8" s="91"/>
       <c r="D8" s="8"/>
       <c r="E8" s="41">
         <v>2</v>
@@ -2113,14 +2113,14 @@
       </c>
       <c r="K8" s="66" t="str">
         <f ca="1">SUM(J8-J3)&amp; "日"</f>
-        <v>20日</v>
+        <v>19日</v>
       </c>
     </row>
     <row r="9" spans="2:19">
-      <c r="B9" s="99" t="s">
+      <c r="B9" s="90" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="100"/>
+      <c r="C9" s="91"/>
       <c r="D9" s="10"/>
       <c r="E9" s="42">
         <v>2</v>
@@ -2133,10 +2133,10 @@
       </c>
     </row>
     <row r="10" spans="2:19">
-      <c r="B10" s="99" t="s">
+      <c r="B10" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="100"/>
+      <c r="C10" s="91"/>
       <c r="D10" s="10"/>
       <c r="E10" s="42">
         <v>2</v>
@@ -2147,10 +2147,10 @@
       </c>
     </row>
     <row r="11" spans="2:19">
-      <c r="B11" s="113" t="s">
+      <c r="B11" s="94" t="s">
         <v>84</v>
       </c>
-      <c r="C11" s="114"/>
+      <c r="C11" s="95"/>
       <c r="D11" s="8"/>
       <c r="E11" s="41">
         <v>1</v>
@@ -2163,10 +2163,10 @@
       </c>
     </row>
     <row r="12" spans="2:19">
-      <c r="B12" s="99" t="s">
+      <c r="B12" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="100"/>
+      <c r="C12" s="91"/>
       <c r="D12" s="8"/>
       <c r="E12" s="41"/>
       <c r="F12" s="42"/>
@@ -2175,10 +2175,10 @@
       </c>
     </row>
     <row r="13" spans="2:19">
-      <c r="B13" s="95" t="s">
+      <c r="B13" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="96"/>
+      <c r="C13" s="93"/>
       <c r="D13" s="8"/>
       <c r="E13" s="41">
         <v>1</v>
@@ -2191,10 +2191,10 @@
       </c>
     </row>
     <row r="14" spans="2:19">
-      <c r="B14" s="91" t="s">
+      <c r="B14" s="106" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="92"/>
+      <c r="C14" s="107"/>
       <c r="D14" s="8"/>
       <c r="E14" s="41">
         <v>1</v>
@@ -2209,10 +2209,10 @@
       <c r="S14" s="86"/>
     </row>
     <row r="15" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B15" s="93" t="s">
+      <c r="B15" s="112" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="94"/>
+      <c r="C15" s="113"/>
       <c r="D15" s="10"/>
       <c r="E15" s="42">
         <v>1</v>
@@ -2225,10 +2225,10 @@
       </c>
     </row>
     <row r="16" spans="2:19">
-      <c r="B16" s="101" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="102"/>
+      <c r="B16" s="102" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="103"/>
       <c r="D16" s="7" t="s">
         <v>11</v>
       </c>
@@ -2244,10 +2244,10 @@
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="99" t="s">
+      <c r="B17" s="90" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="100"/>
+      <c r="C17" s="91"/>
       <c r="D17" s="8"/>
       <c r="E17" s="81">
         <v>3</v>
@@ -2260,10 +2260,10 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="99" t="s">
+      <c r="B18" s="90" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="100"/>
+      <c r="C18" s="91"/>
       <c r="D18" s="8"/>
       <c r="E18" s="81">
         <v>3</v>
@@ -2276,10 +2276,10 @@
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="99" t="s">
+      <c r="B19" s="90" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="100"/>
+      <c r="C19" s="91"/>
       <c r="D19" s="8"/>
       <c r="E19" s="81">
         <v>3</v>
@@ -2292,10 +2292,10 @@
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="99" t="s">
+      <c r="B20" s="90" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="100"/>
+      <c r="C20" s="91"/>
       <c r="D20" s="10"/>
       <c r="E20" s="81">
         <v>3</v>
@@ -2308,10 +2308,10 @@
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="99" t="s">
+      <c r="B21" s="90" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="100"/>
+      <c r="C21" s="91"/>
       <c r="D21" s="8"/>
       <c r="E21" s="82">
         <v>1</v>
@@ -2324,10 +2324,10 @@
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="113" t="s">
+      <c r="B22" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="114"/>
+      <c r="C22" s="95"/>
       <c r="D22" s="8"/>
       <c r="E22" s="81"/>
       <c r="F22" s="41">
@@ -2338,10 +2338,10 @@
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="95" t="s">
+      <c r="B23" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="96"/>
+      <c r="C23" s="93"/>
       <c r="D23" s="8"/>
       <c r="E23" s="81">
         <v>1</v>
@@ -2354,10 +2354,10 @@
       </c>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="95" t="s">
+      <c r="B24" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="96"/>
+      <c r="C24" s="93"/>
       <c r="D24" s="8"/>
       <c r="E24" s="81">
         <v>1</v>
@@ -2370,10 +2370,10 @@
       </c>
     </row>
     <row r="25" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B25" s="97" t="s">
+      <c r="B25" s="114" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="98"/>
+      <c r="C25" s="115"/>
       <c r="D25" s="9"/>
       <c r="E25" s="84">
         <v>1</v>
@@ -2386,10 +2386,10 @@
       </c>
     </row>
     <row r="26" spans="2:7">
-      <c r="B26" s="115" t="s">
+      <c r="B26" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="116"/>
+      <c r="C26" s="97"/>
       <c r="D26" s="53" t="s">
         <v>10</v>
       </c>
@@ -2406,10 +2406,10 @@
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="113" t="s">
+      <c r="B27" s="94" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="114"/>
+      <c r="C27" s="95"/>
       <c r="D27" s="8"/>
       <c r="E27" s="41">
         <v>5</v>
@@ -2422,10 +2422,10 @@
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="113" t="s">
+      <c r="B28" s="94" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="114"/>
+      <c r="C28" s="95"/>
       <c r="D28" s="8"/>
       <c r="E28" s="41"/>
       <c r="F28" s="41"/>
@@ -2434,10 +2434,10 @@
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="95" t="s">
+      <c r="B29" s="92" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="96"/>
+      <c r="C29" s="93"/>
       <c r="D29" s="8"/>
       <c r="E29" s="41">
         <v>2</v>
@@ -2448,10 +2448,10 @@
       </c>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="95" t="s">
+      <c r="B30" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="96"/>
+      <c r="C30" s="93"/>
       <c r="D30" s="8"/>
       <c r="E30" s="41">
         <v>2</v>
@@ -2462,10 +2462,10 @@
       </c>
     </row>
     <row r="31" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B31" s="89" t="s">
+      <c r="B31" s="110" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="90"/>
+      <c r="C31" s="111"/>
       <c r="D31" s="9"/>
       <c r="E31" s="43">
         <v>3</v>
@@ -2477,11 +2477,11 @@
         <v>87</v>
       </c>
     </row>
-    <row r="32" spans="2:7">
-      <c r="B32" s="101" t="s">
+    <row r="32" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B32" s="102" t="s">
         <v>60</v>
       </c>
-      <c r="C32" s="102"/>
+      <c r="C32" s="103"/>
       <c r="D32" s="7" t="s">
         <v>14</v>
       </c>
@@ -2491,160 +2491,146 @@
       </c>
       <c r="F32" s="44">
         <f>SUM(F34,F36,F37,F39,F40)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G32" s="64" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="99" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B33" s="90" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="100"/>
+      <c r="C33" s="91"/>
       <c r="D33" s="11"/>
       <c r="E33" s="49"/>
       <c r="F33" s="45"/>
-      <c r="G33" s="58" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7">
-      <c r="B34" s="91" t="s">
+      <c r="G33" s="64" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B34" s="106" t="s">
         <v>56</v>
       </c>
-      <c r="C34" s="92"/>
+      <c r="C34" s="107"/>
       <c r="D34" s="11"/>
       <c r="E34" s="49">
         <v>2</v>
       </c>
-      <c r="F34" s="45"/>
-      <c r="G34" s="58" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="103" t="s">
+      <c r="F34" s="45">
+        <v>1</v>
+      </c>
+      <c r="G34" s="64" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B35" s="116" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="104"/>
+      <c r="C35" s="117"/>
       <c r="D35" s="8"/>
       <c r="E35" s="40"/>
       <c r="F35" s="41"/>
-      <c r="G35" s="58" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="99" t="s">
+      <c r="G35" s="64" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B36" s="90" t="s">
         <v>57</v>
       </c>
-      <c r="C36" s="100"/>
+      <c r="C36" s="91"/>
       <c r="D36" s="8"/>
       <c r="E36" s="40">
         <v>2</v>
       </c>
-      <c r="F36" s="41"/>
-      <c r="G36" s="58" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7">
-      <c r="B37" s="99" t="s">
+      <c r="F36" s="41">
+        <v>1</v>
+      </c>
+      <c r="G36" s="64" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B37" s="90" t="s">
         <v>58</v>
       </c>
-      <c r="C37" s="100"/>
+      <c r="C37" s="91"/>
       <c r="D37" s="8"/>
       <c r="E37" s="40">
         <v>2</v>
       </c>
-      <c r="F37" s="41"/>
-      <c r="G37" s="58" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7">
-      <c r="B38" s="103" t="s">
+      <c r="F37" s="41">
+        <v>1</v>
+      </c>
+      <c r="G37" s="64" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B38" s="116" t="s">
         <v>5</v>
       </c>
-      <c r="C38" s="104"/>
+      <c r="C38" s="117"/>
       <c r="D38" s="8"/>
       <c r="E38" s="40"/>
       <c r="F38" s="41"/>
-      <c r="G38" s="58" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7">
-      <c r="B39" s="105" t="s">
+      <c r="G38" s="64" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B39" s="118" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="106"/>
+      <c r="C39" s="119"/>
       <c r="D39" s="8"/>
       <c r="E39" s="40">
         <v>2</v>
       </c>
-      <c r="F39" s="41"/>
-      <c r="G39" s="58" t="s">
-        <v>83</v>
+      <c r="F39" s="41">
+        <v>1</v>
+      </c>
+      <c r="G39" s="64" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B40" s="89" t="s">
+      <c r="B40" s="110" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="90"/>
+      <c r="C40" s="111"/>
       <c r="D40" s="9"/>
       <c r="E40" s="46">
         <v>3</v>
       </c>
-      <c r="F40" s="43"/>
-      <c r="G40" s="60" t="s">
-        <v>83</v>
+      <c r="F40" s="43">
+        <v>1</v>
+      </c>
+      <c r="G40" s="64" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B41" s="87" t="s">
+      <c r="B41" s="108" t="s">
         <v>85</v>
       </c>
-      <c r="C41" s="88"/>
+      <c r="C41" s="109"/>
       <c r="D41" s="51"/>
       <c r="E41" s="78">
         <f>SUM(E3+E16+E26+F32)</f>
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F41" s="79">
         <f>SUM(F4:F40)</f>
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G41" s="51"/>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B7:C7"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B14:C14"/>
@@ -2661,6 +2647,30 @@
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B19:C19"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2678,10 +2688,10 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="98" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="108"/>
+      <c r="C2" s="99"/>
       <c r="D2" s="50" t="s">
         <v>9</v>
       </c>
@@ -2693,10 +2703,10 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="109" t="s">
+      <c r="B3" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="110"/>
+      <c r="C3" s="101"/>
       <c r="D3" s="50" t="s">
         <v>12</v>
       </c>
@@ -2704,10 +2714,10 @@
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="123" t="s">
+      <c r="B4" s="120" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="124"/>
+      <c r="C4" s="121"/>
       <c r="D4" s="7"/>
       <c r="E4" s="44">
         <v>2</v>
@@ -2715,10 +2725,10 @@
       <c r="F4" s="44"/>
     </row>
     <row r="5" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B5" s="91" t="s">
+      <c r="B5" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="92"/>
+      <c r="C5" s="107"/>
       <c r="D5" s="8"/>
       <c r="E5" s="41">
         <v>2</v>
@@ -2726,10 +2736,10 @@
       <c r="F5" s="41"/>
     </row>
     <row r="6" spans="2:6">
-      <c r="B6" s="101" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="102"/>
+      <c r="B6" s="102" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="103"/>
       <c r="D6" s="7" t="s">
         <v>11</v>
       </c>
@@ -2737,32 +2747,36 @@
       <c r="F6" s="44"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="91" t="s">
+      <c r="B7" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="92"/>
+      <c r="C7" s="107"/>
       <c r="D7" s="8"/>
       <c r="E7" s="41">
         <v>2</v>
       </c>
-      <c r="F7" s="41"/>
+      <c r="F7" s="41">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="91" t="s">
+      <c r="B8" s="106" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="92"/>
+      <c r="C8" s="107"/>
       <c r="D8" s="8"/>
       <c r="E8" s="41">
         <v>3</v>
       </c>
-      <c r="F8" s="41"/>
+      <c r="F8" s="41">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="91" t="s">
+      <c r="B9" s="106" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="92"/>
+      <c r="C9" s="107"/>
       <c r="D9" s="8"/>
       <c r="E9" s="41">
         <v>2</v>
@@ -2770,10 +2784,10 @@
       <c r="F9" s="41"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="115" t="s">
+      <c r="B10" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="116"/>
+      <c r="C10" s="97"/>
       <c r="D10" s="53" t="s">
         <v>10</v>
       </c>
@@ -2781,10 +2795,10 @@
       <c r="F10" s="54"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="95" t="s">
+      <c r="B11" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="96"/>
+      <c r="C11" s="93"/>
       <c r="D11" s="8"/>
       <c r="E11" s="41">
         <v>5</v>
@@ -2792,10 +2806,10 @@
       <c r="F11" s="41"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="95" t="s">
+      <c r="B12" s="92" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="96"/>
+      <c r="C12" s="93"/>
       <c r="D12" s="8"/>
       <c r="E12" s="41">
         <v>1</v>
@@ -2803,10 +2817,10 @@
       <c r="F12" s="41"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="95" t="s">
+      <c r="B13" s="92" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="96"/>
+      <c r="C13" s="93"/>
       <c r="D13" s="8"/>
       <c r="E13" s="41">
         <v>2</v>
@@ -2814,10 +2828,10 @@
       <c r="F13" s="41"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="121" t="s">
+      <c r="B14" s="122" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="122"/>
+      <c r="C14" s="123"/>
       <c r="D14" s="11" t="s">
         <v>14</v>
       </c>
@@ -2825,10 +2839,10 @@
       <c r="F14" s="45"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="91" t="s">
+      <c r="B15" s="106" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="92"/>
+      <c r="C15" s="107"/>
       <c r="D15" s="11"/>
       <c r="E15" s="49">
         <v>5</v>
@@ -2836,19 +2850,19 @@
       <c r="F15" s="45"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="103" t="s">
+      <c r="B16" s="116" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="104"/>
+      <c r="C16" s="117"/>
       <c r="D16" s="8"/>
       <c r="E16" s="40"/>
       <c r="F16" s="41"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="91" t="s">
+      <c r="B17" s="106" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="92"/>
+      <c r="C17" s="107"/>
       <c r="D17" s="8"/>
       <c r="E17" s="40">
         <v>2</v>
@@ -2856,19 +2870,19 @@
       <c r="F17" s="41"/>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="103" t="s">
+      <c r="B18" s="116" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="104"/>
+      <c r="C18" s="117"/>
       <c r="D18" s="8"/>
       <c r="E18" s="40"/>
       <c r="F18" s="41"/>
     </row>
     <row r="19" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B19" s="117" t="s">
+      <c r="B19" s="124" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="118"/>
+      <c r="C19" s="125"/>
       <c r="D19" s="8"/>
       <c r="E19" s="40">
         <v>2</v>
@@ -2876,16 +2890,27 @@
       <c r="F19" s="41"/>
     </row>
     <row r="20" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B20" s="119" t="s">
+      <c r="B20" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="120"/>
+      <c r="C20" s="127"/>
       <c r="D20" s="12"/>
       <c r="E20" s="47"/>
       <c r="F20" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
@@ -2894,17 +2919,6 @@
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2918,10 +2932,10 @@
   <sheetData>
     <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="98" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="108"/>
+      <c r="C2" s="99"/>
       <c r="D2" s="50" t="s">
         <v>9</v>
       </c>
@@ -2933,10 +2947,10 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="109" t="s">
+      <c r="B3" s="100" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="110"/>
+      <c r="C3" s="101"/>
       <c r="D3" s="50" t="s">
         <v>12</v>
       </c>
@@ -2944,10 +2958,10 @@
       <c r="F3" s="12"/>
     </row>
     <row r="4" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B4" s="123" t="s">
+      <c r="B4" s="120" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="124"/>
+      <c r="C4" s="121"/>
       <c r="D4" s="7"/>
       <c r="E4" s="44">
         <v>3</v>
@@ -2955,10 +2969,10 @@
       <c r="F4" s="44"/>
     </row>
     <row r="5" spans="2:6">
-      <c r="B5" s="101" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="102"/>
+      <c r="B5" s="102" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="103"/>
       <c r="D5" s="7" t="s">
         <v>11</v>
       </c>
@@ -2966,10 +2980,10 @@
       <c r="F5" s="44"/>
     </row>
     <row r="6" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B6" s="91" t="s">
+      <c r="B6" s="106" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="92"/>
+      <c r="C6" s="107"/>
       <c r="D6" s="8"/>
       <c r="E6" s="41">
         <v>3</v>
@@ -2977,10 +2991,10 @@
       <c r="F6" s="41"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="115" t="s">
+      <c r="B7" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="116"/>
+      <c r="C7" s="97"/>
       <c r="D7" s="53" t="s">
         <v>10</v>
       </c>
@@ -2988,10 +3002,10 @@
       <c r="F7" s="54"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="95" t="s">
+      <c r="B8" s="92" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="96"/>
+      <c r="C8" s="93"/>
       <c r="D8" s="8"/>
       <c r="E8" s="41">
         <v>3</v>
@@ -2999,10 +3013,10 @@
       <c r="F8" s="41"/>
     </row>
     <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="91" t="s">
+      <c r="B9" s="106" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="92"/>
+      <c r="C9" s="107"/>
       <c r="D9" s="8"/>
       <c r="E9" s="41">
         <v>2</v>
@@ -3010,10 +3024,10 @@
       <c r="F9" s="41"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="101" t="s">
+      <c r="B10" s="102" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="102"/>
+      <c r="C10" s="103"/>
       <c r="D10" s="7" t="s">
         <v>14</v>
       </c>
@@ -3021,10 +3035,10 @@
       <c r="F10" s="44"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="91" t="s">
+      <c r="B11" s="106" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="92"/>
+      <c r="C11" s="107"/>
       <c r="D11" s="11"/>
       <c r="E11" s="45">
         <v>2</v>
@@ -3032,19 +3046,19 @@
       <c r="F11" s="45"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="103" t="s">
+      <c r="B12" s="116" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="104"/>
+      <c r="C12" s="117"/>
       <c r="D12" s="8"/>
       <c r="E12" s="41"/>
       <c r="F12" s="41"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="91" t="s">
+      <c r="B13" s="106" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="92"/>
+      <c r="C13" s="107"/>
       <c r="D13" s="8"/>
       <c r="E13" s="41">
         <v>1</v>
@@ -3052,10 +3066,10 @@
       <c r="F13" s="41"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="91" t="s">
+      <c r="B14" s="106" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="92"/>
+      <c r="C14" s="107"/>
       <c r="D14" s="8"/>
       <c r="E14" s="41">
         <v>1</v>
@@ -3063,19 +3077,19 @@
       <c r="F14" s="41"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="103" t="s">
+      <c r="B15" s="116" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="104"/>
+      <c r="C15" s="117"/>
       <c r="D15" s="8"/>
       <c r="E15" s="41"/>
       <c r="F15" s="41"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="95" t="s">
+      <c r="B16" s="92" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="96"/>
+      <c r="C16" s="93"/>
       <c r="D16" s="8"/>
       <c r="E16" s="41">
         <v>1</v>
@@ -3083,10 +3097,10 @@
       <c r="F16" s="41"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="95" t="s">
+      <c r="B17" s="92" t="s">
         <v>74</v>
       </c>
-      <c r="C17" s="96"/>
+      <c r="C17" s="93"/>
       <c r="D17" s="8"/>
       <c r="E17" s="41">
         <v>1</v>
@@ -3094,26 +3108,16 @@
       <c r="F17" s="41"/>
     </row>
     <row r="18" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B18" s="87" t="s">
+      <c r="B18" s="108" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="88"/>
+      <c r="C18" s="109"/>
       <c r="D18" s="51"/>
       <c r="E18" s="52"/>
       <c r="F18" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B11:C11"/>
@@ -3121,6 +3125,16 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3133,13 +3147,13 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="125" t="s">
+      <c r="C1" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
     </row>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
       <c r="B2" s="31" t="s">
@@ -3296,15 +3310,15 @@
       </c>
     </row>
     <row r="7" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B7" s="126">
+      <c r="B7" s="87">
         <f>SUM(H6)+1</f>
         <v>46292</v>
       </c>
-      <c r="C7" s="127">
+      <c r="C7" s="88">
         <f>SUM(B7)+1</f>
         <v>46293</v>
       </c>
-      <c r="D7" s="127">
+      <c r="D7" s="88">
         <f t="shared" ref="D7:E7" si="4">SUM(C7)+1</f>
         <v>46294</v>
       </c>

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ayato Terao\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7561CED6-177E-4081-807E-0F70A2ED43C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A54CC1-F6DA-42CA-86F4-0C75841C5352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="90">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -735,7 +735,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="46">
+  <borders count="49">
     <border>
       <left/>
       <right/>
@@ -847,19 +847,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1186,19 +1173,6 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -1229,48 +1203,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -1296,17 +1235,6 @@
         <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1318,22 +1246,123 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1348,10 +1377,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1369,272 +1395,327 @@
     <xf numFmtId="56" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="56" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1943,691 +2024,672 @@
   <sheetData>
     <row r="1" spans="2:19" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B2" s="98" t="s">
+      <c r="B2" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="99"/>
-      <c r="D2" s="50" t="s">
+      <c r="C2" s="86"/>
+      <c r="D2" s="48" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="63" t="s">
+      <c r="F2" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="G2" s="11" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="3" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B3" s="100" t="s">
+      <c r="B3" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="101"/>
-      <c r="D3" s="50" t="s">
+      <c r="C3" s="88"/>
+      <c r="D3" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="47">
+      <c r="E3" s="45">
         <f>SUM(E4:E15)</f>
         <v>14</v>
       </c>
-      <c r="F3" s="48">
+      <c r="F3" s="46">
         <f>SUM(F4:F15)</f>
-        <v>12</v>
-      </c>
-      <c r="G3" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="I3" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="48" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" s="61" t="s">
         <v>77</v>
       </c>
-      <c r="J3" s="72">
+      <c r="J3" s="64">
         <f ca="1">TODAY()</f>
         <v>46295</v>
       </c>
-      <c r="K3" s="50" t="s">
+      <c r="K3" s="48" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="2:19">
-      <c r="B4" s="104" t="s">
+    <row r="4" spans="2:19" ht="19.5" thickBot="1">
+      <c r="B4" s="89" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="105"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="59" t="s">
+      <c r="C4" s="90"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="I4" s="73" t="s">
+      <c r="I4" s="145" t="s">
         <v>78</v>
       </c>
-      <c r="J4" s="69">
+      <c r="J4" s="64">
         <v>46295</v>
       </c>
-      <c r="K4" s="67" t="str">
+      <c r="K4" s="113" t="str">
         <f ca="1">SUM($J4-J3)&amp; "日"</f>
         <v>0日</v>
       </c>
     </row>
-    <row r="5" spans="2:19">
-      <c r="B5" s="106" t="s">
+    <row r="5" spans="2:19" ht="19.5" thickBot="1">
+      <c r="B5" s="91" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="107"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="41">
+      <c r="C5" s="92"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="39">
         <v>2</v>
       </c>
-      <c r="F5" s="41">
+      <c r="F5" s="39">
         <v>2</v>
       </c>
-      <c r="G5" s="59" t="s">
+      <c r="G5" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="I5" s="74" t="s">
-        <v>79</v>
-      </c>
-      <c r="J5" s="70">
-        <v>46305</v>
-      </c>
-      <c r="K5" s="65" t="str">
-        <f ca="1">SUM($J5-J3)&amp; "日"</f>
-        <v>10日</v>
-      </c>
+      <c r="I5" s="142" t="s">
+        <v>76</v>
+      </c>
+      <c r="J5" s="143">
+        <v>46314</v>
+      </c>
+      <c r="K5" s="144" t="str">
+        <f ca="1">SUM(J5-J3)&amp; "日"</f>
+        <v>19日</v>
+      </c>
+      <c r="Q5" s="140"/>
+      <c r="R5" s="141"/>
+      <c r="S5" s="133"/>
     </row>
     <row r="6" spans="2:19">
-      <c r="B6" s="106" t="s">
+      <c r="B6" s="91" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="107"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="41">
+      <c r="C6" s="92"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="39">
         <v>1</v>
       </c>
-      <c r="F6" s="41">
+      <c r="F6" s="39">
         <v>2</v>
       </c>
-      <c r="G6" s="59" t="s">
+      <c r="G6" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="I6" s="75" t="s">
-        <v>80</v>
-      </c>
-      <c r="J6" s="70">
-        <v>46310</v>
-      </c>
-      <c r="K6" s="65" t="str">
-        <f ca="1">SUM($J6-J3)&amp; "日"</f>
-        <v>15日</v>
-      </c>
+      <c r="Q6" s="140"/>
+      <c r="R6" s="141"/>
+      <c r="S6" s="133"/>
     </row>
     <row r="7" spans="2:19">
-      <c r="B7" s="106" t="s">
+      <c r="B7" s="91" t="s">
         <v>89</v>
       </c>
-      <c r="C7" s="107"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="41">
+      <c r="C7" s="92"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="39">
         <v>1</v>
       </c>
-      <c r="F7" s="45">
+      <c r="F7" s="43">
         <v>1</v>
       </c>
-      <c r="G7" s="59" t="s">
+      <c r="G7" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="I7" s="76" t="s">
-        <v>81</v>
-      </c>
-      <c r="J7" s="70">
-        <v>46313</v>
-      </c>
-      <c r="K7" s="65" t="str">
-        <f ca="1">SUM($J7-J3)&amp; "日"</f>
-        <v>18日</v>
-      </c>
-    </row>
-    <row r="8" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B8" s="90" t="s">
+      <c r="Q7" s="140"/>
+      <c r="R7" s="141"/>
+      <c r="S7" s="133"/>
+    </row>
+    <row r="8" spans="2:19">
+      <c r="B8" s="79" t="s">
         <v>88</v>
       </c>
-      <c r="C8" s="91"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="41">
+      <c r="C8" s="80"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="39">
         <v>2</v>
       </c>
-      <c r="F8" s="45">
+      <c r="F8" s="43">
         <v>2</v>
       </c>
-      <c r="G8" s="59" t="s">
+      <c r="G8" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="I8" s="77" t="s">
-        <v>76</v>
-      </c>
-      <c r="J8" s="71">
-        <v>46314</v>
-      </c>
-      <c r="K8" s="66" t="str">
-        <f ca="1">SUM(J8-J3)&amp; "日"</f>
-        <v>19日</v>
-      </c>
     </row>
     <row r="9" spans="2:19">
-      <c r="B9" s="90" t="s">
+      <c r="B9" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="91"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="42">
+      <c r="C9" s="80"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="40">
         <v>2</v>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="40">
+        <v>2</v>
+      </c>
+      <c r="G9" s="54" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19">
+      <c r="B10" s="79" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="80"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="40">
+        <v>2</v>
+      </c>
+      <c r="F10" s="40">
+        <v>2</v>
+      </c>
+      <c r="G10" s="54" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19">
+      <c r="B11" s="83" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" s="84"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="39">
         <v>1</v>
       </c>
-      <c r="G9" s="59" t="s">
+      <c r="F11" s="39">
+        <v>1</v>
+      </c>
+      <c r="G11" s="53" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="10" spans="2:19">
-      <c r="B10" s="90" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="91"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="42">
-        <v>2</v>
-      </c>
-      <c r="F10" s="42"/>
-      <c r="G10" s="58" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="2:19">
-      <c r="B11" s="94" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" s="95"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="41">
+    <row r="12" spans="2:19">
+      <c r="B12" s="79" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="80"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="53" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19">
+      <c r="B13" s="81" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="82"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="39">
         <v>1</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F13" s="39">
         <v>1</v>
       </c>
-      <c r="G11" s="58" t="s">
+      <c r="G13" s="53" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="2:19">
-      <c r="B12" s="90" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="91"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="58" t="s">
+    <row r="14" spans="2:19">
+      <c r="B14" s="91" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="92"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="39">
+        <v>1</v>
+      </c>
+      <c r="F14" s="39">
+        <v>1</v>
+      </c>
+      <c r="G14" s="53" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="13" spans="2:19">
-      <c r="B13" s="92" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="93"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="41">
+      <c r="R14" s="73"/>
+      <c r="S14" s="74"/>
+    </row>
+    <row r="15" spans="2:19" ht="19.5" thickBot="1">
+      <c r="B15" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="98"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="40">
         <v>1</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F15" s="40">
         <v>1</v>
       </c>
-      <c r="G13" s="58" t="s">
+      <c r="G15" s="53" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="14" spans="2:19">
-      <c r="B14" s="106" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="107"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="41">
+    <row r="16" spans="2:19" ht="19.5" thickBot="1">
+      <c r="B16" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="F14" s="41">
-        <v>1</v>
-      </c>
-      <c r="G14" s="58" t="s">
-        <v>87</v>
-      </c>
-      <c r="R14" s="85"/>
-      <c r="S14" s="86"/>
-    </row>
-    <row r="15" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B15" s="112" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="113"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="42">
-        <v>1</v>
-      </c>
-      <c r="F15" s="42">
-        <v>1</v>
-      </c>
-      <c r="G15" s="58" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="2:19">
-      <c r="B16" s="102" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="103"/>
-      <c r="D16" s="7" t="s">
+      <c r="C16" s="88"/>
+      <c r="D16" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="83">
+      <c r="E16" s="110">
         <f>SUM(E17:E25)</f>
         <v>16</v>
       </c>
-      <c r="F16" s="44">
+      <c r="F16" s="46">
         <v>8</v>
       </c>
-      <c r="G16" s="64" t="s">
-        <v>83</v>
+      <c r="G16" s="48" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="90" t="s">
+      <c r="B17" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="91"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="81">
+      <c r="C17" s="90"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="107">
         <v>3</v>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="43">
         <v>1</v>
       </c>
-      <c r="G17" s="58" t="s">
+      <c r="G17" s="54" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="90" t="s">
+      <c r="B18" s="79" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="91"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="81">
+      <c r="C18" s="80"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="70">
         <v>3</v>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="39">
         <v>1</v>
       </c>
-      <c r="G18" s="58" t="s">
+      <c r="G18" s="53" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="90" t="s">
+      <c r="B19" s="79" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="91"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="81">
+      <c r="C19" s="80"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="70">
         <v>3</v>
       </c>
-      <c r="F19" s="41">
+      <c r="F19" s="39">
         <v>1</v>
       </c>
-      <c r="G19" s="58" t="s">
+      <c r="G19" s="53" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="90" t="s">
+      <c r="B20" s="79" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="91"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="81">
+      <c r="C20" s="80"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="70">
         <v>3</v>
       </c>
-      <c r="F20" s="41">
+      <c r="F20" s="39">
         <v>1</v>
       </c>
-      <c r="G20" s="58" t="s">
+      <c r="G20" s="53" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="90" t="s">
+      <c r="B21" s="79" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="91"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="82">
+      <c r="C21" s="80"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="71">
         <v>1</v>
       </c>
-      <c r="F21" s="41">
+      <c r="F21" s="39">
         <v>1</v>
       </c>
-      <c r="G21" s="58" t="s">
+      <c r="G21" s="53" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="94" t="s">
+      <c r="B22" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="95"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="81"/>
-      <c r="F22" s="41">
+      <c r="C22" s="84"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="39">
         <v>3</v>
       </c>
-      <c r="G22" s="58" t="s">
+      <c r="G22" s="53" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="92" t="s">
+      <c r="B23" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="93"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="81">
+      <c r="C23" s="82"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="70">
         <v>1</v>
       </c>
-      <c r="F23" s="41">
+      <c r="F23" s="39">
         <v>1</v>
       </c>
-      <c r="G23" s="58" t="s">
+      <c r="G23" s="53" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="92" t="s">
+      <c r="B24" s="81" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="93"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="81">
+      <c r="C24" s="82"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="70">
         <v>1</v>
       </c>
-      <c r="F24" s="41">
+      <c r="F24" s="39">
         <v>1</v>
       </c>
-      <c r="G24" s="58" t="s">
+      <c r="G24" s="53" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B25" s="114" t="s">
+      <c r="B25" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="115"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="84">
+      <c r="C25" s="100"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="72">
         <v>1</v>
       </c>
-      <c r="F25" s="43">
+      <c r="F25" s="41">
         <v>1</v>
       </c>
-      <c r="G25" s="58" t="s">
+      <c r="G25" s="53" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="2:7">
-      <c r="B26" s="96" t="s">
+    <row r="26" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B26" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="97"/>
-      <c r="D26" s="53" t="s">
+      <c r="C26" s="88"/>
+      <c r="D26" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="54">
+      <c r="E26" s="46">
         <f>SUM(E27:E31)</f>
         <v>12</v>
       </c>
-      <c r="F26" s="54">
+      <c r="F26" s="46">
         <f>SUM(F27,F28,F31)</f>
         <v>8</v>
       </c>
-      <c r="G26" s="64" t="s">
+      <c r="G26" s="48" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="94" t="s">
+      <c r="B27" s="111" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="95"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="41">
+      <c r="C27" s="112"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="43">
         <v>5</v>
       </c>
-      <c r="F27" s="41">
+      <c r="F27" s="43">
         <v>5</v>
       </c>
-      <c r="G27" s="58" t="s">
+      <c r="G27" s="54" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="94" t="s">
+      <c r="B28" s="83" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="95"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="58" t="s">
+      <c r="C28" s="84"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="53" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="92" t="s">
+      <c r="B29" s="81" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="93"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="41">
+      <c r="C29" s="82"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="39">
         <v>2</v>
       </c>
-      <c r="F29" s="41"/>
-      <c r="G29" s="58" t="s">
+      <c r="F29" s="39"/>
+      <c r="G29" s="53" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="92" t="s">
+      <c r="B30" s="81" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="93"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="41">
+      <c r="C30" s="82"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="39">
         <v>2</v>
       </c>
-      <c r="F30" s="41"/>
-      <c r="G30" s="58" t="s">
+      <c r="F30" s="39"/>
+      <c r="G30" s="53" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B31" s="110" t="s">
+      <c r="B31" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="111"/>
+      <c r="C31" s="109"/>
       <c r="D31" s="9"/>
-      <c r="E31" s="43">
+      <c r="E31" s="40">
         <v>3</v>
       </c>
-      <c r="F31" s="43">
+      <c r="F31" s="40">
         <v>3</v>
       </c>
-      <c r="G31" s="60" t="s">
+      <c r="G31" s="75" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B32" s="102" t="s">
+      <c r="B32" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="C32" s="103"/>
-      <c r="D32" s="7" t="s">
+      <c r="C32" s="88"/>
+      <c r="D32" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="80">
+      <c r="E32" s="45">
         <f>SUM(E33:E40)</f>
         <v>11</v>
       </c>
-      <c r="F32" s="44">
+      <c r="F32" s="110">
         <f>SUM(F34,F36,F37,F39,F40)</f>
         <v>5</v>
       </c>
-      <c r="G32" s="64" t="s">
+      <c r="G32" s="11" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="33" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B33" s="90" t="s">
+    <row r="33" spans="2:7">
+      <c r="B33" s="89" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="91"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="49"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="64" t="s">
+      <c r="C33" s="90"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="107"/>
+      <c r="G33" s="10" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B34" s="106" t="s">
+    <row r="34" spans="2:7">
+      <c r="B34" s="91" t="s">
         <v>56</v>
       </c>
-      <c r="C34" s="107"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="49">
+      <c r="C34" s="92"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="47">
         <v>2</v>
       </c>
-      <c r="F34" s="45">
+      <c r="F34" s="107">
         <v>1</v>
       </c>
-      <c r="G34" s="64" t="s">
+      <c r="G34" s="7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="35" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B35" s="116" t="s">
+    <row r="35" spans="2:7">
+      <c r="B35" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="117"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="41"/>
-      <c r="G35" s="64" t="s">
+      <c r="C35" s="102"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="38"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="36" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B36" s="90" t="s">
+    <row r="36" spans="2:7">
+      <c r="B36" s="79" t="s">
         <v>57</v>
       </c>
-      <c r="C36" s="91"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="40">
+      <c r="C36" s="80"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="38">
         <v>2</v>
       </c>
-      <c r="F36" s="41">
+      <c r="F36" s="70">
         <v>1</v>
       </c>
-      <c r="G36" s="64" t="s">
+      <c r="G36" s="7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="37" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B37" s="90" t="s">
+    <row r="37" spans="2:7">
+      <c r="B37" s="79" t="s">
         <v>58</v>
       </c>
-      <c r="C37" s="91"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="40">
+      <c r="C37" s="80"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="38">
         <v>2</v>
       </c>
-      <c r="F37" s="41">
+      <c r="F37" s="70">
         <v>1</v>
       </c>
-      <c r="G37" s="64" t="s">
+      <c r="G37" s="7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B38" s="116" t="s">
+    <row r="38" spans="2:7">
+      <c r="B38" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="C38" s="117"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="40"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="64" t="s">
+      <c r="C38" s="102"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="7" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="39" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B39" s="118" t="s">
+    <row r="39" spans="2:7">
+      <c r="B39" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="119"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="40">
+      <c r="C39" s="104"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="38">
         <v>2</v>
       </c>
-      <c r="F39" s="41">
+      <c r="F39" s="70">
         <v>1</v>
       </c>
-      <c r="G39" s="64" t="s">
+      <c r="G39" s="7" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="40" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B40" s="110" t="s">
+      <c r="B40" s="95" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="111"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="46">
+      <c r="C40" s="96"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="44">
         <v>3</v>
       </c>
-      <c r="F40" s="43">
+      <c r="F40" s="72">
         <v>1</v>
       </c>
-      <c r="G40" s="64" t="s">
+      <c r="G40" s="8" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="41" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B41" s="108" t="s">
+      <c r="B41" s="93" t="s">
         <v>85</v>
       </c>
-      <c r="C41" s="109"/>
-      <c r="D41" s="51"/>
-      <c r="E41" s="78">
+      <c r="C41" s="94"/>
+      <c r="D41" s="49"/>
+      <c r="E41" s="68">
         <f>SUM(E3+E16+E26+F32)</f>
         <v>47</v>
       </c>
-      <c r="F41" s="79">
-        <f>SUM(F4:F40)</f>
-        <v>57</v>
-      </c>
-      <c r="G41" s="51"/>
+      <c r="F41" s="69">
+        <f>SUM(F3+F16+F26+F32)</f>
+        <v>36</v>
+      </c>
+      <c r="G41" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="40">
@@ -2680,223 +2742,340 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DBF476-724A-4DAE-8D66-8B0809F96B84}">
-  <dimension ref="B1:F20"/>
+  <dimension ref="B1:K20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="3" max="3" width="18.125" customWidth="1"/>
+    <col min="9" max="9" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
-    <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="98" t="s">
+    <row r="1" spans="2:11" ht="19.5" thickBot="1"/>
+    <row r="2" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B2" s="85" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="99"/>
-      <c r="D2" s="50" t="s">
+      <c r="C2" s="86"/>
+      <c r="D2" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="11" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="100" t="s">
+      <c r="G2" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" s="61" t="s">
+        <v>77</v>
+      </c>
+      <c r="J2" s="64">
+        <f ca="1">TODAY()</f>
+        <v>46295</v>
+      </c>
+      <c r="K2" s="48" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B3" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="101"/>
-      <c r="D3" s="50" t="s">
+      <c r="C3" s="88"/>
+      <c r="D3" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="47"/>
-      <c r="F3" s="12"/>
-    </row>
-    <row r="4" spans="2:6">
-      <c r="B4" s="120" t="s">
+      <c r="E3" s="45">
+        <f>SUM(E4:E5)</f>
+        <v>4</v>
+      </c>
+      <c r="F3" s="46">
+        <f>SUM(F4:F5)</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="I3" s="119" t="s">
+        <v>79</v>
+      </c>
+      <c r="J3" s="63">
+        <v>46305</v>
+      </c>
+      <c r="K3" s="59" t="str">
+        <f ca="1">SUM($J3-J2)&amp; "日"</f>
+        <v>10日</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B4" s="89" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="121"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="44">
+      <c r="C4" s="90"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="42">
         <v>2</v>
       </c>
-      <c r="F4" s="44"/>
-    </row>
-    <row r="5" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B5" s="106" t="s">
+      <c r="F4" s="42"/>
+      <c r="G4" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="I4" s="142" t="s">
+        <v>76</v>
+      </c>
+      <c r="J4" s="143">
+        <v>46314</v>
+      </c>
+      <c r="K4" s="144" t="str">
+        <f ca="1">SUM(J4-J2)&amp; "日"</f>
+        <v>19日</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B5" s="108" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="107"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="41">
+      <c r="C5" s="109"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="40">
         <v>2</v>
       </c>
-      <c r="F5" s="41"/>
-    </row>
-    <row r="6" spans="2:6">
-      <c r="B6" s="102" t="s">
+      <c r="F5" s="40"/>
+      <c r="G5" s="118" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B6" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="103"/>
-      <c r="D6" s="7" t="s">
+      <c r="C6" s="88"/>
+      <c r="D6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-    </row>
-    <row r="7" spans="2:6">
-      <c r="B7" s="106" t="s">
+      <c r="E6" s="46">
+        <f>SUM(E7:E9)</f>
+        <v>7</v>
+      </c>
+      <c r="F6" s="46">
+        <f>SUM(F7:F9)</f>
+        <v>3</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11">
+      <c r="B7" s="89" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="107"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="41">
+      <c r="C7" s="90"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="43">
         <v>2</v>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="43">
+        <v>1</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11">
+      <c r="B8" s="79" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="80"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="39">
+        <v>3</v>
+      </c>
+      <c r="F8" s="39">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="2:6">
-      <c r="B8" s="106" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="107"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="41">
-        <v>3</v>
-      </c>
-      <c r="F8" s="41">
+      <c r="G8" s="10" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B9" s="108" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="109"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="40">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="106" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="107"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="41">
+      <c r="F9" s="40"/>
+      <c r="G9" s="118" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B10" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="F9" s="41"/>
-    </row>
-    <row r="10" spans="2:6">
-      <c r="B10" s="96" t="s">
+      <c r="C10" s="88"/>
+      <c r="D10" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="46">
+        <f>SUM(E11:E13)</f>
+        <v>8</v>
+      </c>
+      <c r="F10" s="46">
+        <f>SUM(F11:F13)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11">
+      <c r="B11" s="111" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="112"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="43">
+        <v>5</v>
+      </c>
+      <c r="F11" s="43"/>
+      <c r="G11" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11">
+      <c r="B12" s="83" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="84"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="39">
+        <v>1</v>
+      </c>
+      <c r="F12" s="39"/>
+      <c r="G12" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B13" s="115" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="116"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="40">
         <v>2</v>
       </c>
-      <c r="C10" s="97"/>
-      <c r="D10" s="53" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54"/>
-    </row>
-    <row r="11" spans="2:6">
-      <c r="B11" s="92" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="93"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="41">
-        <v>5</v>
-      </c>
-      <c r="F11" s="41"/>
-    </row>
-    <row r="12" spans="2:6">
-      <c r="B12" s="92" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="93"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="41">
-        <v>1</v>
-      </c>
-      <c r="F12" s="41"/>
-    </row>
-    <row r="13" spans="2:6">
-      <c r="B13" s="92" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="93"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="41">
-        <v>2</v>
-      </c>
-      <c r="F13" s="41"/>
-    </row>
-    <row r="14" spans="2:6">
-      <c r="B14" s="122" t="s">
+      <c r="F13" s="40"/>
+      <c r="G13" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B14" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="123"/>
+      <c r="C14" s="88"/>
       <c r="D14" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="49"/>
-      <c r="F14" s="45"/>
-    </row>
-    <row r="15" spans="2:6">
-      <c r="B15" s="106" t="s">
+      <c r="E14" s="45">
+        <f>SUM(E15+E17+E19)</f>
+        <v>9</v>
+      </c>
+      <c r="F14" s="46">
+        <f>SUM(F15+F17+F19)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11">
+      <c r="B15" s="89" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="107"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="49">
+      <c r="C15" s="90"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="47">
         <v>5</v>
       </c>
-      <c r="F15" s="45"/>
-    </row>
-    <row r="16" spans="2:6">
-      <c r="B16" s="116" t="s">
+      <c r="F15" s="43"/>
+      <c r="G15" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11">
+      <c r="B16" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="117"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="41"/>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17" s="106" t="s">
+      <c r="C16" s="102"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="107"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="40">
+      <c r="C17" s="80"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="38">
         <v>2</v>
       </c>
-      <c r="F17" s="41"/>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="B18" s="116" t="s">
+      <c r="F17" s="39"/>
+      <c r="G17" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="117"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="41"/>
-    </row>
-    <row r="19" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B19" s="124" t="s">
+      <c r="C18" s="102"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B19" s="103" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="125"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="40">
+      <c r="C19" s="104"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="38">
         <v>2</v>
       </c>
-      <c r="F19" s="41"/>
-    </row>
-    <row r="20" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B20" s="126" t="s">
+      <c r="F19" s="39"/>
+      <c r="G19" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B20" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="127"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="48"/>
+      <c r="C20" s="106"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="45">
+        <f>SUM(E3+E6+E10+E14)</f>
+        <v>28</v>
+      </c>
+      <c r="F20" s="46">
+        <f>SUM(F3+F6+F10+F14)</f>
+        <v>3</v>
+      </c>
+      <c r="G20" s="117"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -2927,194 +3106,344 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF80DA5A-1B69-4377-A99E-364B8197EABC}">
-  <dimension ref="B1:F18"/>
+  <dimension ref="B1:L20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="8" max="8" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="2:6" ht="19.5" thickBot="1"/>
-    <row r="2" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B2" s="98" t="s">
+    <row r="1" spans="2:12" ht="19.5" thickBot="1"/>
+    <row r="2" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B2" s="125" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="99"/>
-      <c r="D2" s="50" t="s">
+      <c r="C2" s="128"/>
+      <c r="D2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="48" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B3" s="100" t="s">
+      <c r="G2" s="48" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B3" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="101"/>
-      <c r="D3" s="50" t="s">
+      <c r="C3" s="129"/>
+      <c r="D3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="47"/>
-      <c r="F3" s="12"/>
-    </row>
-    <row r="4" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B4" s="120" t="s">
+      <c r="E3" s="46">
+        <f>SUM(E4)</f>
+        <v>3</v>
+      </c>
+      <c r="F3" s="113">
+        <f>SUM(F4)</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="J3" s="61" t="s">
+        <v>77</v>
+      </c>
+      <c r="K3" s="64">
+        <f ca="1">TODAY()</f>
+        <v>46295</v>
+      </c>
+      <c r="L3" s="48" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B4" s="127" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="121"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="44">
+      <c r="C4" s="130"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="122">
         <v>3</v>
       </c>
-      <c r="F4" s="44"/>
-    </row>
-    <row r="5" spans="2:6">
-      <c r="B5" s="102" t="s">
+      <c r="F4" s="113">
+        <f>SUM(F5)</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="123" t="s">
+        <v>83</v>
+      </c>
+      <c r="J4" s="65" t="s">
+        <v>80</v>
+      </c>
+      <c r="K4" s="62">
+        <v>46310</v>
+      </c>
+      <c r="L4" s="58" t="str">
+        <f ca="1">SUM($L4-I1)&amp; "日"</f>
+        <v>15日</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B5" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="103"/>
-      <c r="D5" s="7" t="s">
+      <c r="C5" s="129"/>
+      <c r="D5" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-    </row>
-    <row r="6" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B6" s="106" t="s">
+      <c r="E5" s="46">
+        <f>SUM(E6)</f>
+        <v>3</v>
+      </c>
+      <c r="F5" s="113">
+        <f t="shared" ref="F5:F6" si="0">SUM(F6)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="48" t="s">
+        <v>83</v>
+      </c>
+      <c r="J5" s="66" t="s">
+        <v>81</v>
+      </c>
+      <c r="K5" s="62">
+        <v>46313</v>
+      </c>
+      <c r="L5" s="58" t="str">
+        <f ca="1">SUM($L5-I1)&amp; "日"</f>
+        <v>18日</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B6" s="127" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="107"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="41">
+      <c r="C6" s="130"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="122">
         <v>3</v>
       </c>
-      <c r="F6" s="41"/>
-    </row>
-    <row r="7" spans="2:6">
-      <c r="B7" s="96" t="s">
+      <c r="F6" s="113">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="123" t="s">
+        <v>83</v>
+      </c>
+      <c r="J6" s="67" t="s">
+        <v>76</v>
+      </c>
+      <c r="K6" s="63">
+        <v>46314</v>
+      </c>
+      <c r="L6" s="59" t="str">
+        <f ca="1">SUM(K6-K3)&amp; "日"</f>
+        <v>19日</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B7" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="97"/>
-      <c r="D7" s="53" t="s">
+      <c r="C7" s="129"/>
+      <c r="D7" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54"/>
-    </row>
-    <row r="8" spans="2:6">
-      <c r="B8" s="92" t="s">
+      <c r="E7" s="46">
+        <f>SUM(E8:E9)</f>
+        <v>5</v>
+      </c>
+      <c r="F7" s="113">
+        <f>SUM(F8:F9)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="48" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12">
+      <c r="B8" s="111" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="93"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="41">
+      <c r="C8" s="131"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="43">
         <v>3</v>
       </c>
-      <c r="F8" s="41"/>
-    </row>
-    <row r="9" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B9" s="106" t="s">
+      <c r="F8" s="60"/>
+      <c r="G8" s="54" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B9" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="107"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="41">
+      <c r="C9" s="132"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="40">
         <v>2</v>
       </c>
-      <c r="F9" s="41"/>
-    </row>
-    <row r="10" spans="2:6">
-      <c r="B10" s="102" t="s">
+      <c r="F9" s="139"/>
+      <c r="G9" s="75" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B10" s="126" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="103"/>
-      <c r="D10" s="7" t="s">
+      <c r="C10" s="129"/>
+      <c r="D10" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-    </row>
-    <row r="11" spans="2:6">
-      <c r="B11" s="106" t="s">
+      <c r="E10" s="46">
+        <f>SUM(E11)</f>
+        <v>2</v>
+      </c>
+      <c r="F10" s="113">
+        <f>SUM(F12+F15)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="48" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B11" s="127" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="107"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="45">
+      <c r="C11" s="130"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="122">
         <v>2</v>
       </c>
-      <c r="F11" s="45"/>
-    </row>
-    <row r="12" spans="2:6">
-      <c r="B12" s="116" t="s">
+      <c r="F11" s="138"/>
+      <c r="G11" s="123" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B12" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="117"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-    </row>
-    <row r="13" spans="2:6">
-      <c r="B13" s="106" t="s">
+      <c r="C12" s="129"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="46">
+        <f>SUM(E13:E14)</f>
+        <v>2</v>
+      </c>
+      <c r="F12" s="113">
+        <f>SUM(F13:F14)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="48" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12">
+      <c r="B13" s="111" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="107"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="41">
+      <c r="C13" s="131"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="43">
         <v>1</v>
       </c>
-      <c r="F13" s="41"/>
-    </row>
-    <row r="14" spans="2:6">
-      <c r="B14" s="106" t="s">
+      <c r="F13" s="60"/>
+      <c r="G13" s="54" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B14" s="124" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="107"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="41">
+      <c r="C14" s="132"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="40">
         <v>1</v>
       </c>
-      <c r="F14" s="41"/>
-    </row>
-    <row r="15" spans="2:6">
-      <c r="B15" s="116" t="s">
+      <c r="F14" s="139"/>
+      <c r="G14" s="75" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B15" s="126" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="117"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-    </row>
-    <row r="16" spans="2:6">
-      <c r="B16" s="92" t="s">
+      <c r="C15" s="129"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="46">
+        <f>SUM(E16:E17)</f>
+        <v>2</v>
+      </c>
+      <c r="F15" s="113">
+        <f>SUM(F16:F17)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="48" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="B16" s="111" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="93"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="41">
+      <c r="C16" s="131"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="43">
         <v>1</v>
       </c>
-      <c r="F16" s="41"/>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17" s="92" t="s">
+      <c r="F16" s="60"/>
+      <c r="G16" s="54" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B17" s="134" t="s">
         <v>74</v>
       </c>
-      <c r="C17" s="93"/>
+      <c r="C17" s="136"/>
       <c r="D17" s="8"/>
       <c r="E17" s="41">
         <v>1</v>
       </c>
-      <c r="F17" s="41"/>
-    </row>
-    <row r="18" spans="2:6" ht="19.5" thickBot="1">
-      <c r="B18" s="108" t="s">
+      <c r="F17" s="59"/>
+      <c r="G17" s="75" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B18" s="135" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="109"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="52"/>
-      <c r="F18" s="52"/>
+      <c r="C18" s="137"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="46">
+        <f>SUM(E3+E5+E7+E10+E12+E15)</f>
+        <v>17</v>
+      </c>
+      <c r="F18" s="46">
+        <f>SUM(F3+F5+F7+F10+F12+F15)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="11"/>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="G19" s="120"/>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="G20" s="121"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -3147,34 +3476,34 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="89" t="s">
+      <c r="C1" s="78" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="89"/>
-      <c r="E1" s="89"/>
-      <c r="F1" s="89"/>
-      <c r="G1" s="89"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
     </row>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="32" t="s">
+      <c r="E2" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="32" t="s">
+      <c r="G2" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="33" t="s">
+      <c r="H2" s="32" t="s">
         <v>21</v>
       </c>
       <c r="J2" t="s">
@@ -3182,147 +3511,147 @@
       </c>
     </row>
     <row r="3" spans="2:11">
-      <c r="B3" s="28"/>
-      <c r="D3" s="29">
+      <c r="B3" s="27"/>
+      <c r="D3" s="28">
         <v>46266</v>
       </c>
-      <c r="E3" s="29">
+      <c r="E3" s="28">
         <f>SUM(D3)+1</f>
         <v>46267</v>
       </c>
-      <c r="F3" s="29">
+      <c r="F3" s="28">
         <f t="shared" ref="F3:H3" si="0">SUM(E3)+1</f>
         <v>46268</v>
       </c>
-      <c r="G3" s="29">
+      <c r="G3" s="28">
         <f t="shared" si="0"/>
         <v>46269</v>
       </c>
-      <c r="H3" s="30">
+      <c r="H3" s="29">
         <f t="shared" si="0"/>
         <v>46270</v>
       </c>
-      <c r="J3" s="16"/>
+      <c r="J3" s="15"/>
       <c r="K3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="20">
+      <c r="B4" s="19">
         <f>SUM(H3)+1</f>
         <v>46271</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="18">
         <f>SUM(B4)+1</f>
         <v>46272</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="18">
         <f t="shared" ref="D4:H4" si="1">SUM(C4)+1</f>
         <v>46273</v>
       </c>
-      <c r="E4" s="55">
+      <c r="E4" s="50">
         <f t="shared" si="1"/>
         <v>46274</v>
       </c>
-      <c r="F4" s="55">
+      <c r="F4" s="50">
         <f t="shared" si="1"/>
         <v>46275</v>
       </c>
-      <c r="G4" s="55">
+      <c r="G4" s="50">
         <f t="shared" si="1"/>
         <v>46276</v>
       </c>
-      <c r="H4" s="56">
+      <c r="H4" s="51">
         <f t="shared" si="1"/>
         <v>46277</v>
       </c>
-      <c r="J4" s="17"/>
+      <c r="J4" s="16"/>
       <c r="K4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="57">
+      <c r="B5" s="52">
         <f>SUM(H4)+1</f>
         <v>46278</v>
       </c>
-      <c r="C5" s="55">
+      <c r="C5" s="50">
         <f>SUM(B5)+1</f>
         <v>46279</v>
       </c>
-      <c r="D5" s="55">
+      <c r="D5" s="50">
         <f t="shared" ref="D5:H5" si="2">SUM(C5)+1</f>
         <v>46280</v>
       </c>
-      <c r="E5" s="55">
+      <c r="E5" s="50">
         <f t="shared" si="2"/>
         <v>46281</v>
       </c>
-      <c r="F5" s="55">
+      <c r="F5" s="50">
         <f t="shared" si="2"/>
         <v>46282</v>
       </c>
-      <c r="G5" s="55">
+      <c r="G5" s="50">
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="H5" s="56">
+      <c r="H5" s="51">
         <f t="shared" si="2"/>
         <v>46284</v>
       </c>
-      <c r="J5" s="18"/>
+      <c r="J5" s="17"/>
       <c r="K5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" s="57">
+      <c r="B6" s="52">
         <f>SUM(H5)+1</f>
         <v>46285</v>
       </c>
-      <c r="C6" s="55">
+      <c r="C6" s="50">
         <f>SUM(B6)+1</f>
         <v>46286</v>
       </c>
-      <c r="D6" s="55">
+      <c r="D6" s="50">
         <f t="shared" ref="D6:H6" si="3">SUM(C6)+1</f>
         <v>46287</v>
       </c>
-      <c r="E6" s="55">
+      <c r="E6" s="50">
         <f t="shared" si="3"/>
         <v>46288</v>
       </c>
-      <c r="F6" s="55">
+      <c r="F6" s="50">
         <f t="shared" si="3"/>
         <v>46289</v>
       </c>
-      <c r="G6" s="55">
+      <c r="G6" s="50">
         <f t="shared" si="3"/>
         <v>46290</v>
       </c>
-      <c r="H6" s="56">
+      <c r="H6" s="51">
         <f t="shared" si="3"/>
         <v>46291</v>
       </c>
-      <c r="J6" s="26"/>
+      <c r="J6" s="25"/>
       <c r="K6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B7" s="87">
+      <c r="B7" s="76">
         <f>SUM(H6)+1</f>
         <v>46292</v>
       </c>
-      <c r="C7" s="88">
+      <c r="C7" s="77">
         <f>SUM(B7)+1</f>
         <v>46293</v>
       </c>
-      <c r="D7" s="88">
+      <c r="D7" s="77">
         <f t="shared" ref="D7:E7" si="4">SUM(C7)+1</f>
         <v>46294</v>
       </c>
-      <c r="E7" s="36">
+      <c r="E7" s="77">
         <f t="shared" si="4"/>
         <v>46295</v>
       </c>
@@ -3331,139 +3660,139 @@
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="2:11">
-      <c r="B8" s="28"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="34">
+      <c r="F8" s="33">
         <f>SUM(E7)+1</f>
         <v>46296</v>
       </c>
-      <c r="G8" s="34">
+      <c r="G8" s="33">
         <f>SUM(F8)+1</f>
         <v>46297</v>
       </c>
-      <c r="H8" s="35">
+      <c r="H8" s="34">
         <f>SUM(G8)+1</f>
         <v>46298</v>
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="21">
+      <c r="B9" s="20">
         <f>SUM(H8)+1</f>
         <v>46299</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="21">
         <f>SUM(B9)+1</f>
         <v>46300</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="21">
         <f t="shared" ref="D9:H9" si="5">SUM(C9)+1</f>
         <v>46301</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="21">
         <f t="shared" si="5"/>
         <v>46302</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="21">
         <f t="shared" si="5"/>
         <v>46303</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="21">
         <f t="shared" si="5"/>
         <v>46304</v>
       </c>
-      <c r="H9" s="23">
+      <c r="H9" s="22">
         <f t="shared" si="5"/>
         <v>46305</v>
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="25">
+      <c r="B10" s="24">
         <f t="shared" ref="B10:B12" si="6">SUM(H9)+1</f>
         <v>46306</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="23">
         <f>SUM(B10)+1</f>
         <v>46307</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="23">
         <f t="shared" ref="D10:G10" si="7">SUM(C10)+1</f>
         <v>46308</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="23">
         <f t="shared" si="7"/>
         <v>46309</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="23">
         <f t="shared" si="7"/>
         <v>46310</v>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="26">
         <f t="shared" si="7"/>
         <v>46311</v>
       </c>
-      <c r="H10" s="62">
+      <c r="H10" s="56">
         <f>SUM(G10)+1</f>
         <v>46312</v>
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="61">
+      <c r="B11" s="55">
         <f t="shared" si="6"/>
         <v>46313</v>
       </c>
-      <c r="C11" s="39">
+      <c r="C11" s="37">
         <f>SUM(B11)+1</f>
         <v>46314</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="12">
         <f t="shared" ref="D11:F11" si="8">SUM(C11)+1</f>
         <v>46315</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="12">
         <f t="shared" si="8"/>
         <v>46316</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="12">
         <f t="shared" si="8"/>
         <v>46317</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="12">
         <f t="shared" ref="G11" si="9">SUM(F11)+1</f>
         <v>46318</v>
       </c>
-      <c r="H11" s="37">
+      <c r="H11" s="35">
         <f>SUM(G11)+1</f>
         <v>46319</v>
       </c>
     </row>
     <row r="12" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B12" s="38">
+      <c r="B12" s="36">
         <f t="shared" si="6"/>
         <v>46320</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C12" s="13">
         <f>SUM(B12)+1</f>
         <v>46321</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="13">
         <f t="shared" ref="D12:H12" si="10">SUM(C12)+1</f>
         <v>46322</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="13">
         <f t="shared" si="10"/>
         <v>46323</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="13">
         <f t="shared" si="10"/>
         <v>46324</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="13">
         <f t="shared" si="10"/>
         <v>46325</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="14">
         <f t="shared" si="10"/>
         <v>46326</v>
       </c>

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ayato Terao\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A54CC1-F6DA-42CA-86F4-0C75841C5352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFC7DCD-77F6-4EAD-8D69-67D1C20481FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="89">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -474,10 +474,6 @@
   </si>
   <si>
     <t>(サウンド）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>テクスチャ</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1351,7 +1347,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1518,205 +1514,192 @@
     </xf>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2024,10 +2007,10 @@
   <sheetData>
     <row r="1" spans="2:19" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="117" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="86"/>
+      <c r="C2" s="118"/>
       <c r="D2" s="48" t="s">
         <v>9</v>
       </c>
@@ -2038,14 +2021,14 @@
         <v>8</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B3" s="87" t="s">
+      <c r="B3" s="111" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="88"/>
+      <c r="C3" s="112"/>
       <c r="D3" s="48" t="s">
         <v>12</v>
       </c>
@@ -2058,46 +2041,46 @@
         <v>15</v>
       </c>
       <c r="G3" s="48" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I3" s="61" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J3" s="64">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="K3" s="48" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B4" s="89" t="s">
+      <c r="B4" s="107" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="90"/>
+      <c r="C4" s="108"/>
       <c r="D4" s="10"/>
       <c r="E4" s="43"/>
       <c r="F4" s="43"/>
       <c r="G4" s="54" t="s">
-        <v>87</v>
-      </c>
-      <c r="I4" s="145" t="s">
-        <v>78</v>
+        <v>86</v>
+      </c>
+      <c r="I4" s="92" t="s">
+        <v>77</v>
       </c>
       <c r="J4" s="64">
         <v>46295</v>
       </c>
-      <c r="K4" s="113" t="str">
+      <c r="K4" s="80" t="str">
         <f ca="1">SUM($J4-J3)&amp; "日"</f>
-        <v>0日</v>
+        <v>-1日</v>
       </c>
     </row>
     <row r="5" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B5" s="91" t="s">
+      <c r="B5" s="97" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="92"/>
+      <c r="C5" s="98"/>
       <c r="D5" s="7"/>
       <c r="E5" s="39">
         <v>2</v>
@@ -2106,27 +2089,26 @@
         <v>2</v>
       </c>
       <c r="G5" s="54" t="s">
-        <v>87</v>
-      </c>
-      <c r="I5" s="142" t="s">
-        <v>76</v>
-      </c>
-      <c r="J5" s="143">
+        <v>86</v>
+      </c>
+      <c r="I5" s="89" t="s">
+        <v>75</v>
+      </c>
+      <c r="J5" s="90">
         <v>46314</v>
       </c>
-      <c r="K5" s="144" t="str">
+      <c r="K5" s="91" t="str">
         <f ca="1">SUM(J5-J3)&amp; "日"</f>
-        <v>19日</v>
-      </c>
-      <c r="Q5" s="140"/>
-      <c r="R5" s="141"/>
-      <c r="S5" s="133"/>
+        <v>18日</v>
+      </c>
+      <c r="R5" s="73"/>
+      <c r="S5" s="74"/>
     </row>
     <row r="6" spans="2:19">
-      <c r="B6" s="91" t="s">
+      <c r="B6" s="97" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="92"/>
+      <c r="C6" s="98"/>
       <c r="D6" s="7"/>
       <c r="E6" s="39">
         <v>1</v>
@@ -2135,17 +2117,16 @@
         <v>2</v>
       </c>
       <c r="G6" s="54" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q6" s="140"/>
-      <c r="R6" s="141"/>
-      <c r="S6" s="133"/>
+        <v>86</v>
+      </c>
+      <c r="R6" s="73"/>
+      <c r="S6" s="74"/>
     </row>
     <row r="7" spans="2:19">
-      <c r="B7" s="91" t="s">
-        <v>89</v>
-      </c>
-      <c r="C7" s="92"/>
+      <c r="B7" s="97" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="98"/>
       <c r="D7" s="7"/>
       <c r="E7" s="39">
         <v>1</v>
@@ -2154,17 +2135,16 @@
         <v>1</v>
       </c>
       <c r="G7" s="54" t="s">
+        <v>86</v>
+      </c>
+      <c r="R7" s="73"/>
+      <c r="S7" s="74"/>
+    </row>
+    <row r="8" spans="2:19">
+      <c r="B8" s="109" t="s">
         <v>87</v>
       </c>
-      <c r="Q7" s="140"/>
-      <c r="R7" s="141"/>
-      <c r="S7" s="133"/>
-    </row>
-    <row r="8" spans="2:19">
-      <c r="B8" s="79" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" s="80"/>
+      <c r="C8" s="110"/>
       <c r="D8" s="7"/>
       <c r="E8" s="39">
         <v>2</v>
@@ -2173,14 +2153,14 @@
         <v>2</v>
       </c>
       <c r="G8" s="54" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="2:19">
-      <c r="B9" s="79" t="s">
+      <c r="B9" s="109" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="80"/>
+      <c r="C9" s="110"/>
       <c r="D9" s="9"/>
       <c r="E9" s="40">
         <v>2</v>
@@ -2189,14 +2169,14 @@
         <v>2</v>
       </c>
       <c r="G9" s="54" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="2:19">
-      <c r="B10" s="79" t="s">
+      <c r="B10" s="109" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="80"/>
+      <c r="C10" s="110"/>
       <c r="D10" s="9"/>
       <c r="E10" s="40">
         <v>2</v>
@@ -2205,14 +2185,14 @@
         <v>2</v>
       </c>
       <c r="G10" s="54" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="2:19">
-      <c r="B11" s="83" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" s="84"/>
+      <c r="B11" s="119" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="120"/>
       <c r="D11" s="7"/>
       <c r="E11" s="39">
         <v>1</v>
@@ -2221,26 +2201,26 @@
         <v>1</v>
       </c>
       <c r="G11" s="53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="2:19">
-      <c r="B12" s="79" t="s">
+      <c r="B12" s="109" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="80"/>
+      <c r="C12" s="110"/>
       <c r="D12" s="7"/>
       <c r="E12" s="39"/>
       <c r="F12" s="40"/>
       <c r="G12" s="53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="2:19">
-      <c r="B13" s="81" t="s">
+      <c r="B13" s="101" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="82"/>
+      <c r="C13" s="102"/>
       <c r="D13" s="7"/>
       <c r="E13" s="39">
         <v>1</v>
@@ -2249,14 +2229,14 @@
         <v>1</v>
       </c>
       <c r="G13" s="53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="2:19">
-      <c r="B14" s="91" t="s">
+      <c r="B14" s="97" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="92"/>
+      <c r="C14" s="98"/>
       <c r="D14" s="7"/>
       <c r="E14" s="39">
         <v>1</v>
@@ -2265,16 +2245,16 @@
         <v>1</v>
       </c>
       <c r="G14" s="53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R14" s="73"/>
       <c r="S14" s="74"/>
     </row>
     <row r="15" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B15" s="97" t="s">
+      <c r="B15" s="99" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="98"/>
+      <c r="C15" s="100"/>
       <c r="D15" s="9"/>
       <c r="E15" s="40">
         <v>1</v>
@@ -2283,18 +2263,18 @@
         <v>1</v>
       </c>
       <c r="G15" s="53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B16" s="87" t="s">
+      <c r="B16" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="C16" s="88"/>
+      <c r="C16" s="112"/>
       <c r="D16" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="110">
+      <c r="E16" s="79">
         <f>SUM(E17:E25)</f>
         <v>16</v>
       </c>
@@ -2302,30 +2282,30 @@
         <v>8</v>
       </c>
       <c r="G16" s="48" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="89" t="s">
+      <c r="B17" s="107" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="90"/>
+      <c r="C17" s="108"/>
       <c r="D17" s="10"/>
-      <c r="E17" s="107">
+      <c r="E17" s="78">
         <v>3</v>
       </c>
       <c r="F17" s="43">
         <v>1</v>
       </c>
       <c r="G17" s="54" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="79" t="s">
+      <c r="B18" s="109" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="80"/>
+      <c r="C18" s="110"/>
       <c r="D18" s="7"/>
       <c r="E18" s="70">
         <v>3</v>
@@ -2334,14 +2314,14 @@
         <v>1</v>
       </c>
       <c r="G18" s="53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="79" t="s">
+      <c r="B19" s="109" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="80"/>
+      <c r="C19" s="110"/>
       <c r="D19" s="7"/>
       <c r="E19" s="70">
         <v>3</v>
@@ -2350,14 +2330,14 @@
         <v>1</v>
       </c>
       <c r="G19" s="53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="79" t="s">
+      <c r="B20" s="109" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="80"/>
+      <c r="C20" s="110"/>
       <c r="D20" s="9"/>
       <c r="E20" s="70">
         <v>3</v>
@@ -2366,14 +2346,14 @@
         <v>1</v>
       </c>
       <c r="G20" s="53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="79" t="s">
+      <c r="B21" s="109" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="80"/>
+      <c r="C21" s="110"/>
       <c r="D21" s="7"/>
       <c r="E21" s="71">
         <v>1</v>
@@ -2382,28 +2362,28 @@
         <v>1</v>
       </c>
       <c r="G21" s="53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="83" t="s">
+      <c r="B22" s="119" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="84"/>
+      <c r="C22" s="120"/>
       <c r="D22" s="7"/>
       <c r="E22" s="70"/>
       <c r="F22" s="39">
         <v>3</v>
       </c>
       <c r="G22" s="53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="81" t="s">
+      <c r="B23" s="101" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="82"/>
+      <c r="C23" s="102"/>
       <c r="D23" s="7"/>
       <c r="E23" s="70">
         <v>1</v>
@@ -2412,14 +2392,14 @@
         <v>1</v>
       </c>
       <c r="G23" s="53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="81" t="s">
+      <c r="B24" s="101" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="82"/>
+      <c r="C24" s="102"/>
       <c r="D24" s="7"/>
       <c r="E24" s="70">
         <v>1</v>
@@ -2428,14 +2408,14 @@
         <v>1</v>
       </c>
       <c r="G24" s="53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B25" s="99" t="s">
+      <c r="B25" s="103" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="100"/>
+      <c r="C25" s="104"/>
       <c r="D25" s="8"/>
       <c r="E25" s="72">
         <v>1</v>
@@ -2444,34 +2424,34 @@
         <v>1</v>
       </c>
       <c r="G25" s="53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B26" s="87" t="s">
+      <c r="B26" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="88"/>
+      <c r="C26" s="112"/>
       <c r="D26" s="11" t="s">
         <v>10</v>
       </c>
       <c r="E26" s="46">
         <f>SUM(E27:E31)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F26" s="46">
         <f>SUM(F27,F28,F31)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G26" s="48" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="111" t="s">
+      <c r="B27" s="121" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="112"/>
+      <c r="C27" s="122"/>
       <c r="D27" s="10"/>
       <c r="E27" s="43">
         <v>5</v>
@@ -2480,54 +2460,64 @@
         <v>5</v>
       </c>
       <c r="G27" s="54" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="83" t="s">
+      <c r="B28" s="119" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="84"/>
+      <c r="C28" s="120"/>
       <c r="D28" s="7"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="53" t="s">
-        <v>83</v>
+      <c r="E28" s="39">
+        <f>SUM(E29:E30)</f>
+        <v>4</v>
+      </c>
+      <c r="F28" s="39">
+        <f>SUM(F29:F30)</f>
+        <v>3</v>
+      </c>
+      <c r="G28" s="54" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="81" t="s">
+      <c r="B29" s="101" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="82"/>
+      <c r="C29" s="102"/>
       <c r="D29" s="7"/>
       <c r="E29" s="39">
         <v>2</v>
       </c>
-      <c r="F29" s="39"/>
-      <c r="G29" s="53" t="s">
-        <v>83</v>
+      <c r="F29" s="39">
+        <v>2</v>
+      </c>
+      <c r="G29" s="54" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="81" t="s">
+      <c r="B30" s="101" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="82"/>
+      <c r="C30" s="102"/>
       <c r="D30" s="7"/>
       <c r="E30" s="39">
         <v>2</v>
       </c>
-      <c r="F30" s="39"/>
-      <c r="G30" s="53" t="s">
-        <v>83</v>
+      <c r="F30" s="39">
+        <v>1</v>
+      </c>
+      <c r="G30" s="54" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B31" s="108" t="s">
+      <c r="B31" s="105" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="109"/>
+      <c r="C31" s="106"/>
       <c r="D31" s="9"/>
       <c r="E31" s="40">
         <v>3</v>
@@ -2535,15 +2525,15 @@
       <c r="F31" s="40">
         <v>3</v>
       </c>
-      <c r="G31" s="75" t="s">
-        <v>87</v>
+      <c r="G31" s="54" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B32" s="87" t="s">
+      <c r="B32" s="111" t="s">
         <v>60</v>
       </c>
-      <c r="C32" s="88"/>
+      <c r="C32" s="112"/>
       <c r="D32" s="11" t="s">
         <v>14</v>
       </c>
@@ -2551,59 +2541,59 @@
         <f>SUM(E33:E40)</f>
         <v>11</v>
       </c>
-      <c r="F32" s="110">
+      <c r="F32" s="79">
         <f>SUM(F34,F36,F37,F39,F40)</f>
         <v>5</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="89" t="s">
+      <c r="B33" s="107" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="90"/>
+      <c r="C33" s="108"/>
       <c r="D33" s="10"/>
       <c r="E33" s="47"/>
-      <c r="F33" s="107"/>
+      <c r="F33" s="78"/>
       <c r="G33" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="91" t="s">
+      <c r="B34" s="97" t="s">
         <v>56</v>
       </c>
-      <c r="C34" s="92"/>
+      <c r="C34" s="98"/>
       <c r="D34" s="10"/>
       <c r="E34" s="47">
         <v>2</v>
       </c>
-      <c r="F34" s="107">
+      <c r="F34" s="78">
         <v>1</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="101" t="s">
+      <c r="B35" s="113" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="102"/>
+      <c r="C35" s="114"/>
       <c r="D35" s="7"/>
       <c r="E35" s="38"/>
       <c r="F35" s="70"/>
       <c r="G35" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="79" t="s">
+      <c r="B36" s="109" t="s">
         <v>57</v>
       </c>
-      <c r="C36" s="80"/>
+      <c r="C36" s="110"/>
       <c r="D36" s="7"/>
       <c r="E36" s="38">
         <v>2</v>
@@ -2612,14 +2602,14 @@
         <v>1</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="79" t="s">
+      <c r="B37" s="109" t="s">
         <v>58</v>
       </c>
-      <c r="C37" s="80"/>
+      <c r="C37" s="110"/>
       <c r="D37" s="7"/>
       <c r="E37" s="38">
         <v>2</v>
@@ -2628,26 +2618,26 @@
         <v>1</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="101" t="s">
+      <c r="B38" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="C38" s="102"/>
+      <c r="C38" s="114"/>
       <c r="D38" s="7"/>
       <c r="E38" s="38"/>
       <c r="F38" s="70"/>
       <c r="G38" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39" spans="2:7">
-      <c r="B39" s="103" t="s">
+      <c r="B39" s="115" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="104"/>
+      <c r="C39" s="116"/>
       <c r="D39" s="7"/>
       <c r="E39" s="38">
         <v>2</v>
@@ -2656,7 +2646,7 @@
         <v>1</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="2:7" ht="19.5" thickBot="1">
@@ -2672,27 +2662,53 @@
         <v>1</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" spans="2:7" ht="19.5" thickBot="1">
       <c r="B41" s="93" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C41" s="94"/>
       <c r="D41" s="49"/>
       <c r="E41" s="68">
         <f>SUM(E3+E16+E26+F32)</f>
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F41" s="69">
         <f>SUM(F3+F16+F26+F32)</f>
-        <v>36</v>
-      </c>
-      <c r="G41" s="49"/>
+        <v>39</v>
+      </c>
+      <c r="G41" s="49" t="s">
+        <v>86</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B7:C7"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B14:C14"/>
@@ -2709,30 +2725,6 @@
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B19:C19"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2742,7 +2734,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DBF476-724A-4DAE-8D66-8B0809F96B84}">
-  <dimension ref="B1:K20"/>
+  <dimension ref="B1:K19"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="3" max="3" width="18.125" customWidth="1"/>
@@ -2752,38 +2744,38 @@
   <sheetData>
     <row r="1" spans="2:11" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="117" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="86"/>
+      <c r="C2" s="118"/>
       <c r="D2" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="114" t="s">
+      <c r="E2" s="81" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>8</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I2" s="61" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J2" s="64">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="K2" s="48" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B3" s="87" t="s">
+      <c r="B3" s="111" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="88"/>
+      <c r="C3" s="112"/>
       <c r="D3" s="48" t="s">
         <v>12</v>
       </c>
@@ -2796,62 +2788,62 @@
         <v>0</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="I3" s="119" t="s">
-        <v>79</v>
+        <v>82</v>
+      </c>
+      <c r="I3" s="84" t="s">
+        <v>78</v>
       </c>
       <c r="J3" s="63">
         <v>46305</v>
       </c>
       <c r="K3" s="59" t="str">
         <f ca="1">SUM($J3-J2)&amp; "日"</f>
-        <v>10日</v>
+        <v>9日</v>
       </c>
     </row>
     <row r="4" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B4" s="89" t="s">
+      <c r="B4" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="90"/>
+      <c r="C4" s="108"/>
       <c r="D4" s="6"/>
       <c r="E4" s="42">
         <v>2</v>
       </c>
       <c r="F4" s="42"/>
       <c r="G4" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="I4" s="142" t="s">
-        <v>76</v>
-      </c>
-      <c r="J4" s="143">
+        <v>82</v>
+      </c>
+      <c r="I4" s="89" t="s">
+        <v>75</v>
+      </c>
+      <c r="J4" s="90">
         <v>46314</v>
       </c>
-      <c r="K4" s="144" t="str">
+      <c r="K4" s="91" t="str">
         <f ca="1">SUM(J4-J2)&amp; "日"</f>
-        <v>19日</v>
+        <v>18日</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B5" s="108" t="s">
+      <c r="B5" s="105" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="109"/>
+      <c r="C5" s="106"/>
       <c r="D5" s="9"/>
       <c r="E5" s="40">
         <v>2</v>
       </c>
       <c r="F5" s="40"/>
-      <c r="G5" s="118" t="s">
-        <v>83</v>
+      <c r="G5" s="83" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B6" s="87" t="s">
+      <c r="B6" s="111" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="88"/>
+      <c r="C6" s="112"/>
       <c r="D6" s="11" t="s">
         <v>11</v>
       </c>
@@ -2864,14 +2856,14 @@
         <v>3</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="2:11">
-      <c r="B7" s="89" t="s">
+      <c r="B7" s="107" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="90"/>
+      <c r="C7" s="108"/>
       <c r="D7" s="10"/>
       <c r="E7" s="43">
         <v>2</v>
@@ -2880,14 +2872,14 @@
         <v>1</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="2:11">
-      <c r="B8" s="79" t="s">
+      <c r="B8" s="109" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="80"/>
+      <c r="C8" s="110"/>
       <c r="D8" s="7"/>
       <c r="E8" s="39">
         <v>3</v>
@@ -2896,200 +2888,175 @@
         <v>2</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B9" s="108" t="s">
+      <c r="B9" s="105" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="109"/>
+      <c r="C9" s="106"/>
       <c r="D9" s="9"/>
       <c r="E9" s="40">
         <v>2</v>
       </c>
       <c r="F9" s="40"/>
-      <c r="G9" s="118" t="s">
-        <v>83</v>
+      <c r="G9" s="83" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B10" s="87" t="s">
+      <c r="B10" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="88"/>
+      <c r="C10" s="112"/>
       <c r="D10" s="11" t="s">
         <v>10</v>
       </c>
       <c r="E10" s="46">
-        <f>SUM(E11:E13)</f>
-        <v>8</v>
+        <f>SUM(E11:E12)</f>
+        <v>3</v>
       </c>
       <c r="F10" s="46">
-        <f>SUM(F11:F13)</f>
+        <f>SUM(F11:F12)</f>
         <v>0</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="111" t="s">
+      <c r="B11" s="119" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="112"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="43">
+      <c r="C11" s="120"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="39">
+        <v>1</v>
+      </c>
+      <c r="F11" s="39"/>
+      <c r="G11" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B12" s="125" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="126"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="40">
+        <v>2</v>
+      </c>
+      <c r="F12" s="40"/>
+      <c r="G12" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B13" s="111" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="112"/>
+      <c r="D13" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="45">
+        <f>SUM(E14+E16+E18)</f>
+        <v>9</v>
+      </c>
+      <c r="F13" s="46">
+        <f>SUM(F14+F16+F18)</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11">
+      <c r="B14" s="107" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="108"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="47">
         <v>5</v>
       </c>
-      <c r="F11" s="43"/>
-      <c r="G11" s="7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11">
-      <c r="B12" s="83" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="84"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="39">
-        <v>1</v>
-      </c>
-      <c r="F12" s="39"/>
-      <c r="G12" s="7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B13" s="115" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="116"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="40">
+      <c r="F14" s="43"/>
+      <c r="G14" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11">
+      <c r="B15" s="113" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="114"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11">
+      <c r="B16" s="109" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="110"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="38">
         <v>2</v>
       </c>
-      <c r="F13" s="40"/>
-      <c r="G13" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B14" s="87" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="88"/>
-      <c r="D14" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="45">
-        <f>SUM(E15+E17+E19)</f>
-        <v>9</v>
-      </c>
-      <c r="F14" s="46">
-        <f>SUM(F15+F17+F19)</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11">
-      <c r="B15" s="89" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="90"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="47">
-        <v>5</v>
-      </c>
-      <c r="F15" s="43"/>
-      <c r="G15" s="7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11">
-      <c r="B16" s="101" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="102"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="38"/>
       <c r="F16" s="39"/>
       <c r="G16" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="79" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" s="80"/>
+      <c r="B17" s="113" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="114"/>
       <c r="D17" s="7"/>
-      <c r="E17" s="38">
-        <v>2</v>
-      </c>
+      <c r="E17" s="38"/>
       <c r="F17" s="39"/>
       <c r="G17" s="7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="101" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="102"/>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B18" s="115" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="116"/>
       <c r="D18" s="7"/>
-      <c r="E18" s="38"/>
+      <c r="E18" s="38">
+        <v>2</v>
+      </c>
       <c r="F18" s="39"/>
-      <c r="G18" s="7" t="s">
-        <v>83</v>
+      <c r="G18" s="8" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B19" s="103" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" s="104"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="38">
-        <v>2</v>
-      </c>
-      <c r="F19" s="39"/>
-      <c r="G19" s="8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B20" s="105" t="s">
+      <c r="B19" s="123" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="106"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="45">
-        <f>SUM(E3+E6+E10+E14)</f>
-        <v>28</v>
-      </c>
-      <c r="F20" s="46">
-        <f>SUM(F3+F6+F10+F14)</f>
+      <c r="C19" s="124"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="45">
+        <f>SUM(E3+E6+E10+E13)</f>
+        <v>23</v>
+      </c>
+      <c r="F19" s="46">
+        <f>SUM(F3+F6+F10+F13)</f>
         <v>3</v>
       </c>
-      <c r="G20" s="117"/>
+      <c r="G19" s="82"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B10:C10"/>
+  <mergeCells count="18">
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
@@ -3098,6 +3065,16 @@
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3106,7 +3083,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF80DA5A-1B69-4377-A99E-364B8197EABC}">
-  <dimension ref="B1:L20"/>
+  <dimension ref="B1:L19"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="8" max="8" width="17.25" bestFit="1" customWidth="1"/>
@@ -3118,10 +3095,10 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B2" s="125" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" s="128"/>
+      <c r="B2" s="138" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="139"/>
       <c r="D2" s="11" t="s">
         <v>9</v>
       </c>
@@ -3132,14 +3109,14 @@
         <v>8</v>
       </c>
       <c r="G2" s="48" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B3" s="126" t="s">
+      <c r="B3" s="133" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="129"/>
+      <c r="C3" s="134"/>
       <c r="D3" s="11" t="s">
         <v>12</v>
       </c>
@@ -3147,42 +3124,42 @@
         <f>SUM(E4)</f>
         <v>3</v>
       </c>
-      <c r="F3" s="113">
+      <c r="F3" s="80">
         <f>SUM(F4)</f>
         <v>0</v>
       </c>
       <c r="G3" s="48" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J3" s="61" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K3" s="64">
         <f ca="1">TODAY()</f>
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="L3" s="48" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B4" s="127" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="130"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="122">
+      <c r="B4" s="131" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="132"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="85">
         <v>3</v>
       </c>
-      <c r="F4" s="113">
+      <c r="F4" s="80">
         <f>SUM(F5)</f>
         <v>0</v>
       </c>
-      <c r="G4" s="123" t="s">
-        <v>83</v>
+      <c r="G4" s="86" t="s">
+        <v>82</v>
       </c>
       <c r="J4" s="65" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K4" s="62">
         <v>46310</v>
@@ -3193,10 +3170,10 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B5" s="126" t="s">
+      <c r="B5" s="133" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="129"/>
+      <c r="C5" s="134"/>
       <c r="D5" s="11" t="s">
         <v>11</v>
       </c>
@@ -3204,15 +3181,15 @@
         <f>SUM(E6)</f>
         <v>3</v>
       </c>
-      <c r="F5" s="113">
+      <c r="F5" s="80">
         <f t="shared" ref="F5:F6" si="0">SUM(F6)</f>
         <v>0</v>
       </c>
       <c r="G5" s="48" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J5" s="66" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K5" s="62">
         <v>46313</v>
@@ -3223,37 +3200,37 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B6" s="127" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" s="130"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="122">
+      <c r="B6" s="131" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="132"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="85">
         <v>3</v>
       </c>
-      <c r="F6" s="113">
+      <c r="F6" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G6" s="123" t="s">
-        <v>83</v>
+      <c r="G6" s="86" t="s">
+        <v>82</v>
       </c>
       <c r="J6" s="67" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K6" s="63">
         <v>46314</v>
       </c>
       <c r="L6" s="59" t="str">
         <f ca="1">SUM(K6-K3)&amp; "日"</f>
-        <v>19日</v>
+        <v>18日</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B7" s="126" t="s">
+      <c r="B7" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="129"/>
+      <c r="C7" s="134"/>
       <c r="D7" s="11" t="s">
         <v>10</v>
       </c>
@@ -3261,47 +3238,47 @@
         <f>SUM(E8:E9)</f>
         <v>5</v>
       </c>
-      <c r="F7" s="113">
+      <c r="F7" s="80">
         <f>SUM(F8:F9)</f>
         <v>0</v>
       </c>
       <c r="G7" s="48" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="2:12">
-      <c r="B8" s="111" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="131"/>
+      <c r="B8" s="121" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="135"/>
       <c r="D8" s="10"/>
       <c r="E8" s="43">
         <v>3</v>
       </c>
       <c r="F8" s="60"/>
       <c r="G8" s="54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B9" s="124" t="s">
+      <c r="B9" s="136" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="132"/>
+      <c r="C9" s="137"/>
       <c r="D9" s="9"/>
       <c r="E9" s="40">
         <v>2</v>
       </c>
-      <c r="F9" s="139"/>
+      <c r="F9" s="88"/>
       <c r="G9" s="75" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B10" s="126" t="s">
+      <c r="B10" s="133" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="129"/>
+      <c r="C10" s="134"/>
       <c r="D10" s="11" t="s">
         <v>14</v>
       </c>
@@ -3309,125 +3286,125 @@
         <f>SUM(E11)</f>
         <v>2</v>
       </c>
-      <c r="F10" s="113">
+      <c r="F10" s="80">
         <f>SUM(F12+F15)</f>
         <v>0</v>
       </c>
       <c r="G10" s="48" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B11" s="127" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="130"/>
-      <c r="D11" s="118"/>
-      <c r="E11" s="122">
+      <c r="B11" s="131" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="132"/>
+      <c r="D11" s="83"/>
+      <c r="E11" s="85">
         <v>2</v>
       </c>
-      <c r="F11" s="138"/>
-      <c r="G11" s="123" t="s">
-        <v>83</v>
+      <c r="F11" s="87"/>
+      <c r="G11" s="86" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B12" s="126" t="s">
+      <c r="B12" s="133" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="129"/>
+      <c r="C12" s="134"/>
       <c r="D12" s="11"/>
       <c r="E12" s="46">
         <f>SUM(E13:E14)</f>
         <v>2</v>
       </c>
-      <c r="F12" s="113">
+      <c r="F12" s="80">
         <f>SUM(F13:F14)</f>
         <v>0</v>
       </c>
       <c r="G12" s="48" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" spans="2:12">
-      <c r="B13" s="111" t="s">
+      <c r="B13" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="131"/>
+      <c r="C13" s="135"/>
       <c r="D13" s="10"/>
       <c r="E13" s="43">
         <v>1</v>
       </c>
       <c r="F13" s="60"/>
       <c r="G13" s="54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B14" s="124" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" s="132"/>
+      <c r="B14" s="136" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="137"/>
       <c r="D14" s="9"/>
       <c r="E14" s="40">
         <v>1</v>
       </c>
-      <c r="F14" s="139"/>
+      <c r="F14" s="88"/>
       <c r="G14" s="75" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B15" s="126" t="s">
+      <c r="B15" s="133" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="129"/>
+      <c r="C15" s="134"/>
       <c r="D15" s="11"/>
       <c r="E15" s="46">
         <f>SUM(E16:E17)</f>
         <v>2</v>
       </c>
-      <c r="F15" s="113">
+      <c r="F15" s="80">
         <f>SUM(F16:F17)</f>
         <v>0</v>
       </c>
       <c r="G15" s="48" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="2:12">
-      <c r="B16" s="111" t="s">
+      <c r="B16" s="121" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="131"/>
+      <c r="C16" s="135"/>
       <c r="D16" s="10"/>
       <c r="E16" s="43">
         <v>1</v>
       </c>
       <c r="F16" s="60"/>
       <c r="G16" s="54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B17" s="134" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="136"/>
+      <c r="B17" s="127" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="128"/>
       <c r="D17" s="8"/>
       <c r="E17" s="41">
         <v>1</v>
       </c>
       <c r="F17" s="59"/>
       <c r="G17" s="75" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B18" s="135" t="s">
+      <c r="B18" s="129" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="137"/>
+      <c r="C18" s="130"/>
       <c r="D18" s="11"/>
       <c r="E18" s="46">
         <f>SUM(E3+E5+E7+E10+E12+E15)</f>
@@ -3440,13 +3417,20 @@
       <c r="G18" s="11"/>
     </row>
     <row r="19" spans="2:7">
-      <c r="G19" s="120"/>
-    </row>
-    <row r="20" spans="2:7">
-      <c r="G20" s="121"/>
+      <c r="G19" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B11:C11"/>
@@ -3454,16 +3438,6 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3476,13 +3450,13 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="78" t="s">
+      <c r="C1" s="140" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
+      <c r="F1" s="140"/>
+      <c r="G1" s="140"/>
     </row>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
       <c r="B2" s="30" t="s">

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ayato Terao\Documents\GitHub\GlassesGame\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFC7DCD-77F6-4EAD-8D69-67D1C20481FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76D85C8-3F6D-4DC6-926D-79251D8D55F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="89">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1347,7 +1347,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1557,6 +1557,66 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1593,70 +1653,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1700,6 +1700,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2007,10 +2010,10 @@
   <sheetData>
     <row r="1" spans="2:19" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="111" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="118"/>
+      <c r="C2" s="112"/>
       <c r="D2" s="48" t="s">
         <v>9</v>
       </c>
@@ -2025,10 +2028,10 @@
       </c>
     </row>
     <row r="3" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B3" s="111" t="s">
+      <c r="B3" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="112"/>
+      <c r="C3" s="106"/>
       <c r="D3" s="48" t="s">
         <v>12</v>
       </c>
@@ -2048,17 +2051,17 @@
       </c>
       <c r="J3" s="64">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="K3" s="48" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="4" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B4" s="107" t="s">
+      <c r="B4" s="95" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="108"/>
+      <c r="C4" s="96"/>
       <c r="D4" s="10"/>
       <c r="E4" s="43"/>
       <c r="F4" s="43"/>
@@ -2073,14 +2076,14 @@
       </c>
       <c r="K4" s="80" t="str">
         <f ca="1">SUM($J4-J3)&amp; "日"</f>
-        <v>-1日</v>
+        <v>-3日</v>
       </c>
     </row>
     <row r="5" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B5" s="97" t="s">
+      <c r="B5" s="117" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="98"/>
+      <c r="C5" s="118"/>
       <c r="D5" s="7"/>
       <c r="E5" s="39">
         <v>2</v>
@@ -2099,16 +2102,16 @@
       </c>
       <c r="K5" s="91" t="str">
         <f ca="1">SUM(J5-J3)&amp; "日"</f>
-        <v>18日</v>
+        <v>16日</v>
       </c>
       <c r="R5" s="73"/>
       <c r="S5" s="74"/>
     </row>
     <row r="6" spans="2:19">
-      <c r="B6" s="97" t="s">
+      <c r="B6" s="117" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="98"/>
+      <c r="C6" s="118"/>
       <c r="D6" s="7"/>
       <c r="E6" s="39">
         <v>1</v>
@@ -2123,10 +2126,10 @@
       <c r="S6" s="74"/>
     </row>
     <row r="7" spans="2:19">
-      <c r="B7" s="97" t="s">
+      <c r="B7" s="117" t="s">
         <v>88</v>
       </c>
-      <c r="C7" s="98"/>
+      <c r="C7" s="118"/>
       <c r="D7" s="7"/>
       <c r="E7" s="39">
         <v>1</v>
@@ -2141,10 +2144,10 @@
       <c r="S7" s="74"/>
     </row>
     <row r="8" spans="2:19">
-      <c r="B8" s="109" t="s">
+      <c r="B8" s="99" t="s">
         <v>87</v>
       </c>
-      <c r="C8" s="110"/>
+      <c r="C8" s="100"/>
       <c r="D8" s="7"/>
       <c r="E8" s="39">
         <v>2</v>
@@ -2157,10 +2160,10 @@
       </c>
     </row>
     <row r="9" spans="2:19">
-      <c r="B9" s="109" t="s">
+      <c r="B9" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="110"/>
+      <c r="C9" s="100"/>
       <c r="D9" s="9"/>
       <c r="E9" s="40">
         <v>2</v>
@@ -2173,10 +2176,10 @@
       </c>
     </row>
     <row r="10" spans="2:19">
-      <c r="B10" s="109" t="s">
+      <c r="B10" s="99" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="100"/>
       <c r="D10" s="9"/>
       <c r="E10" s="40">
         <v>2</v>
@@ -2189,10 +2192,10 @@
       </c>
     </row>
     <row r="11" spans="2:19">
-      <c r="B11" s="119" t="s">
+      <c r="B11" s="101" t="s">
         <v>83</v>
       </c>
-      <c r="C11" s="120"/>
+      <c r="C11" s="102"/>
       <c r="D11" s="7"/>
       <c r="E11" s="39">
         <v>1</v>
@@ -2205,10 +2208,10 @@
       </c>
     </row>
     <row r="12" spans="2:19">
-      <c r="B12" s="109" t="s">
+      <c r="B12" s="99" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="110"/>
+      <c r="C12" s="100"/>
       <c r="D12" s="7"/>
       <c r="E12" s="39"/>
       <c r="F12" s="40"/>
@@ -2217,10 +2220,10 @@
       </c>
     </row>
     <row r="13" spans="2:19">
-      <c r="B13" s="101" t="s">
+      <c r="B13" s="121" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="102"/>
+      <c r="C13" s="122"/>
       <c r="D13" s="7"/>
       <c r="E13" s="39">
         <v>1</v>
@@ -2233,10 +2236,10 @@
       </c>
     </row>
     <row r="14" spans="2:19">
-      <c r="B14" s="97" t="s">
+      <c r="B14" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="98"/>
+      <c r="C14" s="118"/>
       <c r="D14" s="7"/>
       <c r="E14" s="39">
         <v>1</v>
@@ -2251,10 +2254,10 @@
       <c r="S14" s="74"/>
     </row>
     <row r="15" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B15" s="99" t="s">
+      <c r="B15" s="119" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="100"/>
+      <c r="C15" s="120"/>
       <c r="D15" s="9"/>
       <c r="E15" s="40">
         <v>1</v>
@@ -2267,10 +2270,10 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B16" s="111" t="s">
+      <c r="B16" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="C16" s="112"/>
+      <c r="C16" s="106"/>
       <c r="D16" s="11" t="s">
         <v>11</v>
       </c>
@@ -2286,10 +2289,10 @@
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="107" t="s">
+      <c r="B17" s="95" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="108"/>
+      <c r="C17" s="96"/>
       <c r="D17" s="10"/>
       <c r="E17" s="78">
         <v>3</v>
@@ -2302,10 +2305,10 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="109" t="s">
+      <c r="B18" s="99" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="110"/>
+      <c r="C18" s="100"/>
       <c r="D18" s="7"/>
       <c r="E18" s="70">
         <v>3</v>
@@ -2318,10 +2321,10 @@
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="109" t="s">
+      <c r="B19" s="99" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="110"/>
+      <c r="C19" s="100"/>
       <c r="D19" s="7"/>
       <c r="E19" s="70">
         <v>3</v>
@@ -2334,10 +2337,10 @@
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="109" t="s">
+      <c r="B20" s="99" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="110"/>
+      <c r="C20" s="100"/>
       <c r="D20" s="9"/>
       <c r="E20" s="70">
         <v>3</v>
@@ -2350,10 +2353,10 @@
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="109" t="s">
+      <c r="B21" s="99" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="110"/>
+      <c r="C21" s="100"/>
       <c r="D21" s="7"/>
       <c r="E21" s="71">
         <v>1</v>
@@ -2366,10 +2369,10 @@
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="119" t="s">
+      <c r="B22" s="101" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="120"/>
+      <c r="C22" s="102"/>
       <c r="D22" s="7"/>
       <c r="E22" s="70"/>
       <c r="F22" s="39">
@@ -2380,10 +2383,10 @@
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="101" t="s">
+      <c r="B23" s="121" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="102"/>
+      <c r="C23" s="122"/>
       <c r="D23" s="7"/>
       <c r="E23" s="70">
         <v>1</v>
@@ -2396,10 +2399,10 @@
       </c>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="101" t="s">
+      <c r="B24" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="102"/>
+      <c r="C24" s="122"/>
       <c r="D24" s="7"/>
       <c r="E24" s="70">
         <v>1</v>
@@ -2412,10 +2415,10 @@
       </c>
     </row>
     <row r="25" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B25" s="103" t="s">
+      <c r="B25" s="123" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="104"/>
+      <c r="C25" s="124"/>
       <c r="D25" s="8"/>
       <c r="E25" s="72">
         <v>1</v>
@@ -2428,10 +2431,10 @@
       </c>
     </row>
     <row r="26" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B26" s="111" t="s">
+      <c r="B26" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="112"/>
+      <c r="C26" s="106"/>
       <c r="D26" s="11" t="s">
         <v>10</v>
       </c>
@@ -2448,10 +2451,10 @@
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="121" t="s">
+      <c r="B27" s="125" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="122"/>
+      <c r="C27" s="126"/>
       <c r="D27" s="10"/>
       <c r="E27" s="43">
         <v>5</v>
@@ -2464,10 +2467,10 @@
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="119" t="s">
+      <c r="B28" s="101" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="120"/>
+      <c r="C28" s="102"/>
       <c r="D28" s="7"/>
       <c r="E28" s="39">
         <f>SUM(E29:E30)</f>
@@ -2482,10 +2485,10 @@
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="101" t="s">
+      <c r="B29" s="121" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="102"/>
+      <c r="C29" s="122"/>
       <c r="D29" s="7"/>
       <c r="E29" s="39">
         <v>2</v>
@@ -2498,10 +2501,10 @@
       </c>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="101" t="s">
+      <c r="B30" s="121" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="102"/>
+      <c r="C30" s="122"/>
       <c r="D30" s="7"/>
       <c r="E30" s="39">
         <v>2</v>
@@ -2514,10 +2517,10 @@
       </c>
     </row>
     <row r="31" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B31" s="105" t="s">
+      <c r="B31" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="106"/>
+      <c r="C31" s="110"/>
       <c r="D31" s="9"/>
       <c r="E31" s="40">
         <v>3</v>
@@ -2530,10 +2533,10 @@
       </c>
     </row>
     <row r="32" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B32" s="111" t="s">
+      <c r="B32" s="105" t="s">
         <v>60</v>
       </c>
-      <c r="C32" s="112"/>
+      <c r="C32" s="106"/>
       <c r="D32" s="11" t="s">
         <v>14</v>
       </c>
@@ -2550,10 +2553,10 @@
       </c>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="107" t="s">
+      <c r="B33" s="95" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="108"/>
+      <c r="C33" s="96"/>
       <c r="D33" s="10"/>
       <c r="E33" s="47"/>
       <c r="F33" s="78"/>
@@ -2562,10 +2565,10 @@
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="97" t="s">
+      <c r="B34" s="117" t="s">
         <v>56</v>
       </c>
-      <c r="C34" s="98"/>
+      <c r="C34" s="118"/>
       <c r="D34" s="10"/>
       <c r="E34" s="47">
         <v>2</v>
@@ -2578,10 +2581,10 @@
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="113" t="s">
+      <c r="B35" s="97" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="114"/>
+      <c r="C35" s="98"/>
       <c r="D35" s="7"/>
       <c r="E35" s="38"/>
       <c r="F35" s="70"/>
@@ -2590,10 +2593,10 @@
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="109" t="s">
+      <c r="B36" s="99" t="s">
         <v>57</v>
       </c>
-      <c r="C36" s="110"/>
+      <c r="C36" s="100"/>
       <c r="D36" s="7"/>
       <c r="E36" s="38">
         <v>2</v>
@@ -2606,10 +2609,10 @@
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="109" t="s">
+      <c r="B37" s="99" t="s">
         <v>58</v>
       </c>
-      <c r="C37" s="110"/>
+      <c r="C37" s="100"/>
       <c r="D37" s="7"/>
       <c r="E37" s="38">
         <v>2</v>
@@ -2622,10 +2625,10 @@
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="113" t="s">
+      <c r="B38" s="97" t="s">
         <v>5</v>
       </c>
-      <c r="C38" s="114"/>
+      <c r="C38" s="98"/>
       <c r="D38" s="7"/>
       <c r="E38" s="38"/>
       <c r="F38" s="70"/>
@@ -2634,10 +2637,10 @@
       </c>
     </row>
     <row r="39" spans="2:7">
-      <c r="B39" s="115" t="s">
+      <c r="B39" s="107" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="116"/>
+      <c r="C39" s="108"/>
       <c r="D39" s="7"/>
       <c r="E39" s="38">
         <v>2</v>
@@ -2650,10 +2653,10 @@
       </c>
     </row>
     <row r="40" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B40" s="95" t="s">
+      <c r="B40" s="115" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="96"/>
+      <c r="C40" s="116"/>
       <c r="D40" s="8"/>
       <c r="E40" s="44">
         <v>3</v>
@@ -2666,10 +2669,10 @@
       </c>
     </row>
     <row r="41" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B41" s="93" t="s">
+      <c r="B41" s="113" t="s">
         <v>84</v>
       </c>
-      <c r="C41" s="94"/>
+      <c r="C41" s="114"/>
       <c r="D41" s="49"/>
       <c r="E41" s="68">
         <f>SUM(E3+E16+E26+F32)</f>
@@ -2734,7 +2737,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DBF476-724A-4DAE-8D66-8B0809F96B84}">
-  <dimension ref="B1:K19"/>
+  <dimension ref="B1:K20"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="3" max="3" width="18.125" customWidth="1"/>
@@ -2744,10 +2747,10 @@
   <sheetData>
     <row r="1" spans="2:11" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B2" s="117" t="s">
+      <c r="B2" s="111" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="118"/>
+      <c r="C2" s="112"/>
       <c r="D2" s="48" t="s">
         <v>9</v>
       </c>
@@ -2765,27 +2768,27 @@
       </c>
       <c r="J2" s="64">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="K2" s="48" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="3" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B3" s="111" t="s">
+      <c r="B3" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="112"/>
+      <c r="C3" s="106"/>
       <c r="D3" s="48" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="45">
-        <f>SUM(E4:E5)</f>
-        <v>4</v>
+        <f>SUM(E4:E6)</f>
+        <v>6</v>
       </c>
       <c r="F3" s="46">
-        <f>SUM(F4:F5)</f>
-        <v>0</v>
+        <f>SUM(F4:F6)</f>
+        <v>3</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>82</v>
@@ -2798,14 +2801,14 @@
       </c>
       <c r="K3" s="59" t="str">
         <f ca="1">SUM($J3-J2)&amp; "日"</f>
-        <v>9日</v>
+        <v>7日</v>
       </c>
     </row>
     <row r="4" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B4" s="107" t="s">
+      <c r="B4" s="95" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="108"/>
+      <c r="C4" s="96"/>
       <c r="D4" s="6"/>
       <c r="E4" s="42">
         <v>2</v>
@@ -2822,259 +2825,279 @@
       </c>
       <c r="K4" s="91" t="str">
         <f ca="1">SUM(J4-J2)&amp; "日"</f>
-        <v>18日</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B5" s="105" t="s">
+        <v>16日</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11">
+      <c r="B5" s="99" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="100"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="85">
+        <v>2</v>
+      </c>
+      <c r="F5" s="85">
+        <v>3</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5" s="141"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="74"/>
+    </row>
+    <row r="6" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B6" s="109" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="106"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="40">
+      <c r="C6" s="110"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="40">
         <v>2</v>
       </c>
-      <c r="F5" s="40"/>
-      <c r="G5" s="83" t="s">
+      <c r="F6" s="40"/>
+      <c r="G6" s="10" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="6" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B6" s="111" t="s">
+    <row r="7" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B7" s="105" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="112"/>
-      <c r="D6" s="11" t="s">
+      <c r="C7" s="106"/>
+      <c r="D7" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="46">
-        <f>SUM(E7:E9)</f>
+      <c r="E7" s="46">
+        <f>SUM(E8:E10)</f>
         <v>7</v>
       </c>
-      <c r="F6" s="46">
-        <f>SUM(F7:F9)</f>
+      <c r="F7" s="46">
+        <f>SUM(F8:F10)</f>
         <v>3</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G7" s="49" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="2:11">
-      <c r="B7" s="107" t="s">
+    <row r="8" spans="2:11">
+      <c r="B8" s="95" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="108"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="43">
+      <c r="C8" s="96"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="43">
         <v>2</v>
       </c>
-      <c r="F7" s="43">
+      <c r="F8" s="43">
         <v>1</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G8" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11">
+      <c r="B9" s="99" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="100"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="39">
+        <v>3</v>
+      </c>
+      <c r="F9" s="39">
+        <v>2</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B10" s="109" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="110"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="40">
+        <v>2</v>
+      </c>
+      <c r="F10" s="40"/>
+      <c r="G10" s="83" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="2:11">
-      <c r="B8" s="109" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="110"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="39">
+    <row r="11" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B11" s="105" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="106"/>
+      <c r="D11" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="46">
+        <f>SUM(E12:E13)</f>
         <v>3</v>
       </c>
-      <c r="F8" s="39">
+      <c r="F11" s="46">
+        <f>SUM(F12:F13)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11">
+      <c r="B12" s="101" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="102"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="39">
+        <v>1</v>
+      </c>
+      <c r="F12" s="39"/>
+      <c r="G12" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B13" s="103" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="104"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="40">
         <v>2</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="F13" s="40"/>
+      <c r="G13" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="9" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B9" s="105" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" s="106"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="40">
-        <v>2</v>
-      </c>
-      <c r="F9" s="40"/>
-      <c r="G9" s="83" t="s">
+    <row r="14" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B14" s="105" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="106"/>
+      <c r="D14" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="45">
+        <f>SUM(E15+E17+E19)</f>
+        <v>9</v>
+      </c>
+      <c r="F14" s="46">
+        <f>SUM(F15+F17+F19)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B10" s="111" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="112"/>
-      <c r="D10" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="46">
-        <f>SUM(E11:E12)</f>
-        <v>3</v>
-      </c>
-      <c r="F10" s="46">
-        <f>SUM(F11:F12)</f>
-        <v>0</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11">
-      <c r="B11" s="119" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="120"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="39">
-        <v>1</v>
-      </c>
-      <c r="F11" s="39"/>
-      <c r="G11" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B12" s="125" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12" s="126"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="40">
-        <v>2</v>
-      </c>
-      <c r="F12" s="40"/>
-      <c r="G12" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B13" s="111" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="112"/>
-      <c r="D13" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="45">
-        <f>SUM(E14+E16+E18)</f>
-        <v>9</v>
-      </c>
-      <c r="F13" s="46">
-        <f>SUM(F14+F16+F18)</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11">
-      <c r="B14" s="107" t="s">
+    <row r="15" spans="2:11">
+      <c r="B15" s="95" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="108"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="47">
+      <c r="C15" s="96"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="47">
         <v>5</v>
       </c>
-      <c r="F14" s="43"/>
-      <c r="G14" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11">
-      <c r="B15" s="113" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="114"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="39"/>
+      <c r="F15" s="43"/>
       <c r="G15" s="7" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="16" spans="2:11">
-      <c r="B16" s="109" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" s="110"/>
+      <c r="B16" s="97" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="98"/>
       <c r="D16" s="7"/>
-      <c r="E16" s="38">
-        <v>2</v>
-      </c>
+      <c r="E16" s="38"/>
       <c r="F16" s="39"/>
       <c r="G16" s="7" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="113" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="114"/>
+      <c r="B17" s="99" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="100"/>
       <c r="D17" s="7"/>
-      <c r="E17" s="38"/>
+      <c r="E17" s="38">
+        <v>2</v>
+      </c>
       <c r="F17" s="39"/>
       <c r="G17" s="7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B18" s="115" t="s">
+    <row r="18" spans="2:7">
+      <c r="B18" s="97" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="98"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B19" s="107" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="116"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="38">
+      <c r="C19" s="108"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="38">
         <v>2</v>
       </c>
-      <c r="F18" s="39"/>
-      <c r="G18" s="8" t="s">
+      <c r="F19" s="39"/>
+      <c r="G19" s="8" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B19" s="123" t="s">
+    <row r="20" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B20" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="124"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="45">
-        <f>SUM(E3+E6+E10+E13)</f>
-        <v>23</v>
-      </c>
-      <c r="F19" s="46">
-        <f>SUM(F3+F6+F10+F13)</f>
-        <v>3</v>
-      </c>
-      <c r="G19" s="82"/>
+      <c r="C20" s="94"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="45">
+        <f>SUM(E3+E7+E11+E14)</f>
+        <v>25</v>
+      </c>
+      <c r="F20" s="46">
+        <f>SUM(F3+F7+F11+F14)</f>
+        <v>6</v>
+      </c>
+      <c r="G20" s="82"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B6:C6"/>
+  <mergeCells count="19">
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3136,7 +3159,7 @@
       </c>
       <c r="K3" s="64">
         <f ca="1">TODAY()</f>
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="L3" s="48" t="s">
         <v>85</v>
@@ -3223,7 +3246,7 @@
       </c>
       <c r="L6" s="59" t="str">
         <f ca="1">SUM(K6-K3)&amp; "日"</f>
-        <v>18日</v>
+        <v>16日</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="19.5" thickBot="1">
@@ -3247,7 +3270,7 @@
       </c>
     </row>
     <row r="8" spans="2:12">
-      <c r="B8" s="121" t="s">
+      <c r="B8" s="125" t="s">
         <v>73</v>
       </c>
       <c r="C8" s="135"/>
@@ -3327,7 +3350,7 @@
       </c>
     </row>
     <row r="13" spans="2:12">
-      <c r="B13" s="121" t="s">
+      <c r="B13" s="125" t="s">
         <v>68</v>
       </c>
       <c r="C13" s="135"/>
@@ -3373,7 +3396,7 @@
       </c>
     </row>
     <row r="16" spans="2:12">
-      <c r="B16" s="121" t="s">
+      <c r="B16" s="125" t="s">
         <v>68</v>
       </c>
       <c r="C16" s="135"/>

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\Documents\GitHub\GlassesGame\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ayato Terao\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76D85C8-3F6D-4DC6-926D-79251D8D55F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76BF546F-9C19-433D-9389-AF9D33907521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>
@@ -1347,7 +1347,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1557,64 +1557,82 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1629,34 +1647,43 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1669,40 +1696,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2010,10 +2007,10 @@
   <sheetData>
     <row r="1" spans="2:19" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B2" s="111" t="s">
+      <c r="B2" s="101" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="112"/>
+      <c r="C2" s="102"/>
       <c r="D2" s="48" t="s">
         <v>9</v>
       </c>
@@ -2028,20 +2025,20 @@
       </c>
     </row>
     <row r="3" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="106"/>
+      <c r="C3" s="94"/>
       <c r="D3" s="48" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="45">
         <f>SUM(E4:E15)</f>
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F3" s="46">
         <f>SUM(F4:F15)</f>
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G3" s="48" t="s">
         <v>86</v>
@@ -2051,7 +2048,7 @@
       </c>
       <c r="J3" s="64">
         <f ca="1">TODAY()</f>
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="K3" s="48" t="s">
         <v>85</v>
@@ -2063,8 +2060,14 @@
       </c>
       <c r="C4" s="96"/>
       <c r="D4" s="10"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
+      <c r="E4" s="43">
+        <f>SUM(E5:E7)</f>
+        <v>4</v>
+      </c>
+      <c r="F4" s="43">
+        <f>SUM(F5:F7)</f>
+        <v>5</v>
+      </c>
       <c r="G4" s="54" t="s">
         <v>86</v>
       </c>
@@ -2076,7 +2079,7 @@
       </c>
       <c r="K4" s="80" t="str">
         <f ca="1">SUM($J4-J3)&amp; "日"</f>
-        <v>-3日</v>
+        <v>-5日</v>
       </c>
     </row>
     <row r="5" spans="2:19" ht="19.5" thickBot="1">
@@ -2102,7 +2105,7 @@
       </c>
       <c r="K5" s="91" t="str">
         <f ca="1">SUM(J5-J3)&amp; "日"</f>
-        <v>16日</v>
+        <v>14日</v>
       </c>
       <c r="R5" s="73"/>
       <c r="S5" s="74"/>
@@ -2144,10 +2147,10 @@
       <c r="S7" s="74"/>
     </row>
     <row r="8" spans="2:19">
-      <c r="B8" s="99" t="s">
+      <c r="B8" s="97" t="s">
         <v>87</v>
       </c>
-      <c r="C8" s="100"/>
+      <c r="C8" s="98"/>
       <c r="D8" s="7"/>
       <c r="E8" s="39">
         <v>2</v>
@@ -2160,10 +2163,10 @@
       </c>
     </row>
     <row r="9" spans="2:19">
-      <c r="B9" s="99" t="s">
+      <c r="B9" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="100"/>
+      <c r="C9" s="98"/>
       <c r="D9" s="9"/>
       <c r="E9" s="40">
         <v>2</v>
@@ -2176,10 +2179,10 @@
       </c>
     </row>
     <row r="10" spans="2:19">
-      <c r="B10" s="99" t="s">
+      <c r="B10" s="97" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="100"/>
+      <c r="C10" s="98"/>
       <c r="D10" s="9"/>
       <c r="E10" s="40">
         <v>2</v>
@@ -2192,10 +2195,10 @@
       </c>
     </row>
     <row r="11" spans="2:19">
-      <c r="B11" s="101" t="s">
+      <c r="B11" s="103" t="s">
         <v>83</v>
       </c>
-      <c r="C11" s="102"/>
+      <c r="C11" s="104"/>
       <c r="D11" s="7"/>
       <c r="E11" s="39">
         <v>1</v>
@@ -2208,22 +2211,28 @@
       </c>
     </row>
     <row r="12" spans="2:19">
-      <c r="B12" s="99" t="s">
+      <c r="B12" s="97" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="100"/>
+      <c r="C12" s="98"/>
       <c r="D12" s="7"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="40"/>
+      <c r="E12" s="39">
+        <f>SUM(E13:E15)</f>
+        <v>3</v>
+      </c>
+      <c r="F12" s="39">
+        <f>SUM(F13:F15)</f>
+        <v>3</v>
+      </c>
       <c r="G12" s="53" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="13" spans="2:19">
-      <c r="B13" s="121" t="s">
+      <c r="B13" s="113" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="122"/>
+      <c r="C13" s="114"/>
       <c r="D13" s="7"/>
       <c r="E13" s="39">
         <v>1</v>
@@ -2254,10 +2263,10 @@
       <c r="S14" s="74"/>
     </row>
     <row r="15" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B15" s="119" t="s">
+      <c r="B15" s="123" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="120"/>
+      <c r="C15" s="124"/>
       <c r="D15" s="9"/>
       <c r="E15" s="40">
         <v>1</v>
@@ -2270,10 +2279,10 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B16" s="105" t="s">
+      <c r="B16" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="C16" s="106"/>
+      <c r="C16" s="94"/>
       <c r="D16" s="11" t="s">
         <v>11</v>
       </c>
@@ -2305,10 +2314,10 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="99" t="s">
+      <c r="B18" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="100"/>
+      <c r="C18" s="98"/>
       <c r="D18" s="7"/>
       <c r="E18" s="70">
         <v>3</v>
@@ -2321,10 +2330,10 @@
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="99" t="s">
+      <c r="B19" s="97" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="100"/>
+      <c r="C19" s="98"/>
       <c r="D19" s="7"/>
       <c r="E19" s="70">
         <v>3</v>
@@ -2337,10 +2346,10 @@
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="99" t="s">
+      <c r="B20" s="97" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="100"/>
+      <c r="C20" s="98"/>
       <c r="D20" s="9"/>
       <c r="E20" s="70">
         <v>3</v>
@@ -2353,10 +2362,10 @@
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="99" t="s">
+      <c r="B21" s="97" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="100"/>
+      <c r="C21" s="98"/>
       <c r="D21" s="7"/>
       <c r="E21" s="71">
         <v>1</v>
@@ -2369,10 +2378,10 @@
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="101" t="s">
+      <c r="B22" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="102"/>
+      <c r="C22" s="104"/>
       <c r="D22" s="7"/>
       <c r="E22" s="70"/>
       <c r="F22" s="39">
@@ -2383,10 +2392,10 @@
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="121" t="s">
+      <c r="B23" s="113" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="122"/>
+      <c r="C23" s="114"/>
       <c r="D23" s="7"/>
       <c r="E23" s="70">
         <v>1</v>
@@ -2399,10 +2408,10 @@
       </c>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="121" t="s">
+      <c r="B24" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="122"/>
+      <c r="C24" s="114"/>
       <c r="D24" s="7"/>
       <c r="E24" s="70">
         <v>1</v>
@@ -2415,10 +2424,10 @@
       </c>
     </row>
     <row r="25" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B25" s="123" t="s">
+      <c r="B25" s="125" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="124"/>
+      <c r="C25" s="126"/>
       <c r="D25" s="8"/>
       <c r="E25" s="72">
         <v>1</v>
@@ -2431,10 +2440,10 @@
       </c>
     </row>
     <row r="26" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B26" s="105" t="s">
+      <c r="B26" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="106"/>
+      <c r="C26" s="94"/>
       <c r="D26" s="11" t="s">
         <v>10</v>
       </c>
@@ -2451,10 +2460,10 @@
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="125" t="s">
+      <c r="B27" s="115" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="126"/>
+      <c r="C27" s="116"/>
       <c r="D27" s="10"/>
       <c r="E27" s="43">
         <v>5</v>
@@ -2467,10 +2476,10 @@
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="101" t="s">
+      <c r="B28" s="103" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="102"/>
+      <c r="C28" s="104"/>
       <c r="D28" s="7"/>
       <c r="E28" s="39">
         <f>SUM(E29:E30)</f>
@@ -2485,10 +2494,10 @@
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="121" t="s">
+      <c r="B29" s="113" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="122"/>
+      <c r="C29" s="114"/>
       <c r="D29" s="7"/>
       <c r="E29" s="39">
         <v>2</v>
@@ -2501,10 +2510,10 @@
       </c>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="121" t="s">
+      <c r="B30" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="122"/>
+      <c r="C30" s="114"/>
       <c r="D30" s="7"/>
       <c r="E30" s="39">
         <v>2</v>
@@ -2517,10 +2526,10 @@
       </c>
     </row>
     <row r="31" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B31" s="109" t="s">
+      <c r="B31" s="99" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="100"/>
       <c r="D31" s="9"/>
       <c r="E31" s="40">
         <v>3</v>
@@ -2533,10 +2542,10 @@
       </c>
     </row>
     <row r="32" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B32" s="105" t="s">
+      <c r="B32" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="C32" s="106"/>
+      <c r="C32" s="94"/>
       <c r="D32" s="11" t="s">
         <v>14</v>
       </c>
@@ -2581,10 +2590,10 @@
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="97" t="s">
+      <c r="B35" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="98"/>
+      <c r="C35" s="112"/>
       <c r="D35" s="7"/>
       <c r="E35" s="38"/>
       <c r="F35" s="70"/>
@@ -2593,10 +2602,10 @@
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="99" t="s">
+      <c r="B36" s="97" t="s">
         <v>57</v>
       </c>
-      <c r="C36" s="100"/>
+      <c r="C36" s="98"/>
       <c r="D36" s="7"/>
       <c r="E36" s="38">
         <v>2</v>
@@ -2609,10 +2618,10 @@
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="99" t="s">
+      <c r="B37" s="97" t="s">
         <v>58</v>
       </c>
-      <c r="C37" s="100"/>
+      <c r="C37" s="98"/>
       <c r="D37" s="7"/>
       <c r="E37" s="38">
         <v>2</v>
@@ -2625,10 +2634,10 @@
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="97" t="s">
+      <c r="B38" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="C38" s="98"/>
+      <c r="C38" s="112"/>
       <c r="D38" s="7"/>
       <c r="E38" s="38"/>
       <c r="F38" s="70"/>
@@ -2653,10 +2662,10 @@
       </c>
     </row>
     <row r="40" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B40" s="115" t="s">
+      <c r="B40" s="121" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="116"/>
+      <c r="C40" s="122"/>
       <c r="D40" s="8"/>
       <c r="E40" s="44">
         <v>3</v>
@@ -2669,18 +2678,18 @@
       </c>
     </row>
     <row r="41" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B41" s="113" t="s">
+      <c r="B41" s="119" t="s">
         <v>84</v>
       </c>
-      <c r="C41" s="114"/>
+      <c r="C41" s="120"/>
       <c r="D41" s="49"/>
       <c r="E41" s="68">
         <f>SUM(E3+E16+E26+F32)</f>
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F41" s="69">
         <f>SUM(F3+F16+F26+F32)</f>
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G41" s="49" t="s">
         <v>86</v>
@@ -2688,30 +2697,6 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B7:C7"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B14:C14"/>
@@ -2728,6 +2713,30 @@
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B19:C19"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2747,10 +2756,10 @@
   <sheetData>
     <row r="1" spans="2:11" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B2" s="111" t="s">
+      <c r="B2" s="101" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="112"/>
+      <c r="C2" s="102"/>
       <c r="D2" s="48" t="s">
         <v>9</v>
       </c>
@@ -2768,17 +2777,17 @@
       </c>
       <c r="J2" s="64">
         <f ca="1">TODAY()</f>
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="K2" s="48" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="3" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="106"/>
+      <c r="C3" s="94"/>
       <c r="D3" s="48" t="s">
         <v>12</v>
       </c>
@@ -2801,7 +2810,7 @@
       </c>
       <c r="K3" s="59" t="str">
         <f ca="1">SUM($J3-J2)&amp; "日"</f>
-        <v>7日</v>
+        <v>5日</v>
       </c>
     </row>
     <row r="4" spans="2:11" ht="19.5" thickBot="1">
@@ -2825,14 +2834,14 @@
       </c>
       <c r="K4" s="91" t="str">
         <f ca="1">SUM(J4-J2)&amp; "日"</f>
-        <v>16日</v>
+        <v>14日</v>
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="99" t="s">
+      <c r="B5" s="97" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="100"/>
+      <c r="C5" s="98"/>
       <c r="D5" s="83"/>
       <c r="E5" s="85">
         <v>2</v>
@@ -2843,15 +2852,15 @@
       <c r="G5" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="I5" s="141"/>
+      <c r="I5" s="4"/>
       <c r="J5" s="73"/>
       <c r="K5" s="74"/>
     </row>
     <row r="6" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B6" s="109" t="s">
+      <c r="B6" s="99" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="110"/>
+      <c r="C6" s="100"/>
       <c r="D6" s="9"/>
       <c r="E6" s="40">
         <v>2</v>
@@ -2862,10 +2871,10 @@
       </c>
     </row>
     <row r="7" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B7" s="105" t="s">
+      <c r="B7" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="106"/>
+      <c r="C7" s="94"/>
       <c r="D7" s="11" t="s">
         <v>11</v>
       </c>
@@ -2898,10 +2907,10 @@
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="99" t="s">
+      <c r="B9" s="97" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="100"/>
+      <c r="C9" s="98"/>
       <c r="D9" s="7"/>
       <c r="E9" s="39">
         <v>3</v>
@@ -2914,10 +2923,10 @@
       </c>
     </row>
     <row r="10" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B10" s="109" t="s">
+      <c r="B10" s="99" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="110"/>
+      <c r="C10" s="100"/>
       <c r="D10" s="9"/>
       <c r="E10" s="40">
         <v>2</v>
@@ -2928,10 +2937,10 @@
       </c>
     </row>
     <row r="11" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B11" s="105" t="s">
+      <c r="B11" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="106"/>
+      <c r="C11" s="94"/>
       <c r="D11" s="11" t="s">
         <v>10</v>
       </c>
@@ -2948,10 +2957,10 @@
       </c>
     </row>
     <row r="12" spans="2:11">
-      <c r="B12" s="101" t="s">
+      <c r="B12" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="102"/>
+      <c r="C12" s="104"/>
       <c r="D12" s="7"/>
       <c r="E12" s="39">
         <v>1</v>
@@ -2962,10 +2971,10 @@
       </c>
     </row>
     <row r="13" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B13" s="103" t="s">
+      <c r="B13" s="105" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="104"/>
+      <c r="C13" s="106"/>
       <c r="D13" s="9"/>
       <c r="E13" s="40">
         <v>2</v>
@@ -2976,10 +2985,10 @@
       </c>
     </row>
     <row r="14" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B14" s="105" t="s">
+      <c r="B14" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="C14" s="106"/>
+      <c r="C14" s="94"/>
       <c r="D14" s="11" t="s">
         <v>14</v>
       </c>
@@ -3010,10 +3019,10 @@
       </c>
     </row>
     <row r="16" spans="2:11">
-      <c r="B16" s="97" t="s">
+      <c r="B16" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="98"/>
+      <c r="C16" s="112"/>
       <c r="D16" s="7"/>
       <c r="E16" s="38"/>
       <c r="F16" s="39"/>
@@ -3022,10 +3031,10 @@
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="99" t="s">
+      <c r="B17" s="97" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="100"/>
+      <c r="C17" s="98"/>
       <c r="D17" s="7"/>
       <c r="E17" s="38">
         <v>2</v>
@@ -3036,10 +3045,10 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="97" t="s">
+      <c r="B18" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="98"/>
+      <c r="C18" s="112"/>
       <c r="D18" s="7"/>
       <c r="E18" s="38"/>
       <c r="F18" s="39"/>
@@ -3062,10 +3071,10 @@
       </c>
     </row>
     <row r="20" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B20" s="93" t="s">
+      <c r="B20" s="109" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="94"/>
+      <c r="C20" s="110"/>
       <c r="D20" s="11"/>
       <c r="E20" s="45">
         <f>SUM(E3+E7+E11+E14)</f>
@@ -3079,6 +3088,16 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B19:C19"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B9:C9"/>
@@ -3088,16 +3107,6 @@
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3118,10 +3127,10 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B2" s="138" t="s">
+      <c r="B2" s="127" t="s">
         <v>72</v>
       </c>
-      <c r="C2" s="139"/>
+      <c r="C2" s="128"/>
       <c r="D2" s="11" t="s">
         <v>9</v>
       </c>
@@ -3136,10 +3145,10 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B3" s="133" t="s">
+      <c r="B3" s="129" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="134"/>
+      <c r="C3" s="130"/>
       <c r="D3" s="11" t="s">
         <v>12</v>
       </c>
@@ -3159,7 +3168,7 @@
       </c>
       <c r="K3" s="64">
         <f ca="1">TODAY()</f>
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="L3" s="48" t="s">
         <v>85</v>
@@ -3193,10 +3202,10 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B5" s="133" t="s">
+      <c r="B5" s="129" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="134"/>
+      <c r="C5" s="130"/>
       <c r="D5" s="11" t="s">
         <v>11</v>
       </c>
@@ -3246,14 +3255,14 @@
       </c>
       <c r="L6" s="59" t="str">
         <f ca="1">SUM(K6-K3)&amp; "日"</f>
-        <v>16日</v>
+        <v>14日</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B7" s="133" t="s">
+      <c r="B7" s="129" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="134"/>
+      <c r="C7" s="130"/>
       <c r="D7" s="11" t="s">
         <v>10</v>
       </c>
@@ -3270,10 +3279,10 @@
       </c>
     </row>
     <row r="8" spans="2:12">
-      <c r="B8" s="125" t="s">
+      <c r="B8" s="115" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="135"/>
+      <c r="C8" s="133"/>
       <c r="D8" s="10"/>
       <c r="E8" s="43">
         <v>3</v>
@@ -3284,10 +3293,10 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B9" s="136" t="s">
+      <c r="B9" s="134" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="137"/>
+      <c r="C9" s="135"/>
       <c r="D9" s="9"/>
       <c r="E9" s="40">
         <v>2</v>
@@ -3298,10 +3307,10 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B10" s="133" t="s">
+      <c r="B10" s="129" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="134"/>
+      <c r="C10" s="130"/>
       <c r="D10" s="11" t="s">
         <v>14</v>
       </c>
@@ -3332,10 +3341,10 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B12" s="133" t="s">
+      <c r="B12" s="129" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="134"/>
+      <c r="C12" s="130"/>
       <c r="D12" s="11"/>
       <c r="E12" s="46">
         <f>SUM(E13:E14)</f>
@@ -3350,10 +3359,10 @@
       </c>
     </row>
     <row r="13" spans="2:12">
-      <c r="B13" s="125" t="s">
+      <c r="B13" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="135"/>
+      <c r="C13" s="133"/>
       <c r="D13" s="10"/>
       <c r="E13" s="43">
         <v>1</v>
@@ -3364,10 +3373,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B14" s="136" t="s">
+      <c r="B14" s="134" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="137"/>
+      <c r="C14" s="135"/>
       <c r="D14" s="9"/>
       <c r="E14" s="40">
         <v>1</v>
@@ -3378,10 +3387,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B15" s="133" t="s">
+      <c r="B15" s="129" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="134"/>
+      <c r="C15" s="130"/>
       <c r="D15" s="11"/>
       <c r="E15" s="46">
         <f>SUM(E16:E17)</f>
@@ -3396,10 +3405,10 @@
       </c>
     </row>
     <row r="16" spans="2:12">
-      <c r="B16" s="125" t="s">
+      <c r="B16" s="115" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="135"/>
+      <c r="C16" s="133"/>
       <c r="D16" s="10"/>
       <c r="E16" s="43">
         <v>1</v>
@@ -3410,10 +3419,10 @@
       </c>
     </row>
     <row r="17" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B17" s="127" t="s">
+      <c r="B17" s="136" t="s">
         <v>73</v>
       </c>
-      <c r="C17" s="128"/>
+      <c r="C17" s="137"/>
       <c r="D17" s="8"/>
       <c r="E17" s="41">
         <v>1</v>
@@ -3424,10 +3433,10 @@
       </c>
     </row>
     <row r="18" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B18" s="129" t="s">
+      <c r="B18" s="138" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="130"/>
+      <c r="C18" s="139"/>
       <c r="D18" s="11"/>
       <c r="E18" s="46">
         <f>SUM(E3+E5+E7+E10+E12+E15)</f>
@@ -3444,16 +3453,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B11:C11"/>
@@ -3461,6 +3460,16 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ayato Terao\Documents\GitHub\GlassesGame\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76BF546F-9C19-433D-9389-AF9D33907521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F3AE27-0165-4E99-9C09-A99B0AF2FB14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="91">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -618,6 +618,20 @@
   </si>
   <si>
     <t>ージャンプ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テクスチャ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※アルファでサウンドができなかった場合、ベータで実装</t>
+    <rPh sb="17" eb="19">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ジッソウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -657,7 +671,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -730,8 +744,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="49">
+  <borders count="50">
     <border>
       <left/>
       <right/>
@@ -1256,19 +1276,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -1343,11 +1350,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1523,25 +1552,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1557,28 +1583,76 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1593,113 +1667,110 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2007,10 +2078,10 @@
   <sheetData>
     <row r="1" spans="2:19" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B2" s="101" t="s">
+      <c r="B2" s="116" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="102"/>
+      <c r="C2" s="117"/>
       <c r="D2" s="48" t="s">
         <v>9</v>
       </c>
@@ -2025,10 +2096,10 @@
       </c>
     </row>
     <row r="3" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B3" s="93" t="s">
+      <c r="B3" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="94"/>
+      <c r="C3" s="111"/>
       <c r="D3" s="48" t="s">
         <v>12</v>
       </c>
@@ -2055,10 +2126,10 @@
       </c>
     </row>
     <row r="4" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B4" s="95" t="s">
+      <c r="B4" s="106" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="96"/>
+      <c r="C4" s="107"/>
       <c r="D4" s="10"/>
       <c r="E4" s="43">
         <f>SUM(E5:E7)</f>
@@ -2071,7 +2142,7 @@
       <c r="G4" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="I4" s="92" t="s">
+      <c r="I4" s="91" t="s">
         <v>77</v>
       </c>
       <c r="J4" s="64">
@@ -2083,10 +2154,10 @@
       </c>
     </row>
     <row r="5" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B5" s="117" t="s">
+      <c r="B5" s="96" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="118"/>
+      <c r="C5" s="97"/>
       <c r="D5" s="7"/>
       <c r="E5" s="39">
         <v>2</v>
@@ -2097,13 +2168,13 @@
       <c r="G5" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="I5" s="89" t="s">
+      <c r="I5" s="88" t="s">
         <v>75</v>
       </c>
-      <c r="J5" s="90">
+      <c r="J5" s="89">
         <v>46314</v>
       </c>
-      <c r="K5" s="91" t="str">
+      <c r="K5" s="90" t="str">
         <f ca="1">SUM(J5-J3)&amp; "日"</f>
         <v>14日</v>
       </c>
@@ -2111,10 +2182,10 @@
       <c r="S5" s="74"/>
     </row>
     <row r="6" spans="2:19">
-      <c r="B6" s="117" t="s">
+      <c r="B6" s="96" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="118"/>
+      <c r="C6" s="97"/>
       <c r="D6" s="7"/>
       <c r="E6" s="39">
         <v>1</v>
@@ -2129,10 +2200,10 @@
       <c r="S6" s="74"/>
     </row>
     <row r="7" spans="2:19">
-      <c r="B7" s="117" t="s">
+      <c r="B7" s="96" t="s">
         <v>88</v>
       </c>
-      <c r="C7" s="118"/>
+      <c r="C7" s="97"/>
       <c r="D7" s="7"/>
       <c r="E7" s="39">
         <v>1</v>
@@ -2147,10 +2218,10 @@
       <c r="S7" s="74"/>
     </row>
     <row r="8" spans="2:19">
-      <c r="B8" s="97" t="s">
+      <c r="B8" s="108" t="s">
         <v>87</v>
       </c>
-      <c r="C8" s="98"/>
+      <c r="C8" s="109"/>
       <c r="D8" s="7"/>
       <c r="E8" s="39">
         <v>2</v>
@@ -2163,10 +2234,10 @@
       </c>
     </row>
     <row r="9" spans="2:19">
-      <c r="B9" s="97" t="s">
+      <c r="B9" s="108" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="98"/>
+      <c r="C9" s="109"/>
       <c r="D9" s="9"/>
       <c r="E9" s="40">
         <v>2</v>
@@ -2179,10 +2250,10 @@
       </c>
     </row>
     <row r="10" spans="2:19">
-      <c r="B10" s="97" t="s">
+      <c r="B10" s="108" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="98"/>
+      <c r="C10" s="109"/>
       <c r="D10" s="9"/>
       <c r="E10" s="40">
         <v>2</v>
@@ -2195,10 +2266,10 @@
       </c>
     </row>
     <row r="11" spans="2:19">
-      <c r="B11" s="103" t="s">
+      <c r="B11" s="118" t="s">
         <v>83</v>
       </c>
-      <c r="C11" s="104"/>
+      <c r="C11" s="119"/>
       <c r="D11" s="7"/>
       <c r="E11" s="39">
         <v>1</v>
@@ -2211,10 +2282,10 @@
       </c>
     </row>
     <row r="12" spans="2:19">
-      <c r="B12" s="97" t="s">
+      <c r="B12" s="108" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="98"/>
+      <c r="C12" s="109"/>
       <c r="D12" s="7"/>
       <c r="E12" s="39">
         <f>SUM(E13:E15)</f>
@@ -2229,10 +2300,10 @@
       </c>
     </row>
     <row r="13" spans="2:19">
-      <c r="B13" s="113" t="s">
+      <c r="B13" s="100" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="114"/>
+      <c r="C13" s="101"/>
       <c r="D13" s="7"/>
       <c r="E13" s="39">
         <v>1</v>
@@ -2245,10 +2316,10 @@
       </c>
     </row>
     <row r="14" spans="2:19">
-      <c r="B14" s="117" t="s">
+      <c r="B14" s="96" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="118"/>
+      <c r="C14" s="97"/>
       <c r="D14" s="7"/>
       <c r="E14" s="39">
         <v>1</v>
@@ -2263,10 +2334,10 @@
       <c r="S14" s="74"/>
     </row>
     <row r="15" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B15" s="123" t="s">
+      <c r="B15" s="98" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="124"/>
+      <c r="C15" s="99"/>
       <c r="D15" s="9"/>
       <c r="E15" s="40">
         <v>1</v>
@@ -2279,10 +2350,10 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B16" s="93" t="s">
+      <c r="B16" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="C16" s="94"/>
+      <c r="C16" s="111"/>
       <c r="D16" s="11" t="s">
         <v>11</v>
       </c>
@@ -2298,10 +2369,10 @@
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="95" t="s">
+      <c r="B17" s="106" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="96"/>
+      <c r="C17" s="107"/>
       <c r="D17" s="10"/>
       <c r="E17" s="78">
         <v>3</v>
@@ -2314,10 +2385,10 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="97" t="s">
+      <c r="B18" s="108" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="98"/>
+      <c r="C18" s="109"/>
       <c r="D18" s="7"/>
       <c r="E18" s="70">
         <v>3</v>
@@ -2330,10 +2401,10 @@
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="97" t="s">
+      <c r="B19" s="108" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="98"/>
+      <c r="C19" s="109"/>
       <c r="D19" s="7"/>
       <c r="E19" s="70">
         <v>3</v>
@@ -2346,10 +2417,10 @@
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="97" t="s">
+      <c r="B20" s="108" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="98"/>
+      <c r="C20" s="109"/>
       <c r="D20" s="9"/>
       <c r="E20" s="70">
         <v>3</v>
@@ -2362,10 +2433,10 @@
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="97" t="s">
+      <c r="B21" s="108" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="98"/>
+      <c r="C21" s="109"/>
       <c r="D21" s="7"/>
       <c r="E21" s="71">
         <v>1</v>
@@ -2378,10 +2449,10 @@
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="103" t="s">
+      <c r="B22" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="104"/>
+      <c r="C22" s="119"/>
       <c r="D22" s="7"/>
       <c r="E22" s="70"/>
       <c r="F22" s="39">
@@ -2392,10 +2463,10 @@
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="113" t="s">
+      <c r="B23" s="100" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="114"/>
+      <c r="C23" s="101"/>
       <c r="D23" s="7"/>
       <c r="E23" s="70">
         <v>1</v>
@@ -2408,10 +2479,10 @@
       </c>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="113" t="s">
+      <c r="B24" s="100" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="114"/>
+      <c r="C24" s="101"/>
       <c r="D24" s="7"/>
       <c r="E24" s="70">
         <v>1</v>
@@ -2424,10 +2495,10 @@
       </c>
     </row>
     <row r="25" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B25" s="125" t="s">
+      <c r="B25" s="102" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="126"/>
+      <c r="C25" s="103"/>
       <c r="D25" s="8"/>
       <c r="E25" s="72">
         <v>1</v>
@@ -2440,10 +2511,10 @@
       </c>
     </row>
     <row r="26" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B26" s="93" t="s">
+      <c r="B26" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="94"/>
+      <c r="C26" s="111"/>
       <c r="D26" s="11" t="s">
         <v>10</v>
       </c>
@@ -2460,10 +2531,10 @@
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="115" t="s">
+      <c r="B27" s="120" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="116"/>
+      <c r="C27" s="121"/>
       <c r="D27" s="10"/>
       <c r="E27" s="43">
         <v>5</v>
@@ -2476,10 +2547,10 @@
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="103" t="s">
+      <c r="B28" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="104"/>
+      <c r="C28" s="119"/>
       <c r="D28" s="7"/>
       <c r="E28" s="39">
         <f>SUM(E29:E30)</f>
@@ -2494,10 +2565,10 @@
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="113" t="s">
+      <c r="B29" s="100" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="114"/>
+      <c r="C29" s="101"/>
       <c r="D29" s="7"/>
       <c r="E29" s="39">
         <v>2</v>
@@ -2510,10 +2581,10 @@
       </c>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="113" t="s">
+      <c r="B30" s="100" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="114"/>
+      <c r="C30" s="101"/>
       <c r="D30" s="7"/>
       <c r="E30" s="39">
         <v>2</v>
@@ -2526,10 +2597,10 @@
       </c>
     </row>
     <row r="31" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B31" s="99" t="s">
+      <c r="B31" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="100"/>
+      <c r="C31" s="105"/>
       <c r="D31" s="9"/>
       <c r="E31" s="40">
         <v>3</v>
@@ -2542,10 +2613,10 @@
       </c>
     </row>
     <row r="32" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B32" s="93" t="s">
+      <c r="B32" s="110" t="s">
         <v>60</v>
       </c>
-      <c r="C32" s="94"/>
+      <c r="C32" s="111"/>
       <c r="D32" s="11" t="s">
         <v>14</v>
       </c>
@@ -2562,10 +2633,10 @@
       </c>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="95" t="s">
+      <c r="B33" s="106" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="96"/>
+      <c r="C33" s="107"/>
       <c r="D33" s="10"/>
       <c r="E33" s="47"/>
       <c r="F33" s="78"/>
@@ -2574,10 +2645,10 @@
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="117" t="s">
+      <c r="B34" s="96" t="s">
         <v>56</v>
       </c>
-      <c r="C34" s="118"/>
+      <c r="C34" s="97"/>
       <c r="D34" s="10"/>
       <c r="E34" s="47">
         <v>2</v>
@@ -2590,10 +2661,10 @@
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="111" t="s">
+      <c r="B35" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="112"/>
+      <c r="C35" s="113"/>
       <c r="D35" s="7"/>
       <c r="E35" s="38"/>
       <c r="F35" s="70"/>
@@ -2602,10 +2673,10 @@
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="97" t="s">
+      <c r="B36" s="108" t="s">
         <v>57</v>
       </c>
-      <c r="C36" s="98"/>
+      <c r="C36" s="109"/>
       <c r="D36" s="7"/>
       <c r="E36" s="38">
         <v>2</v>
@@ -2618,10 +2689,10 @@
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="97" t="s">
+      <c r="B37" s="108" t="s">
         <v>58</v>
       </c>
-      <c r="C37" s="98"/>
+      <c r="C37" s="109"/>
       <c r="D37" s="7"/>
       <c r="E37" s="38">
         <v>2</v>
@@ -2634,10 +2705,10 @@
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="111" t="s">
+      <c r="B38" s="112" t="s">
         <v>5</v>
       </c>
-      <c r="C38" s="112"/>
+      <c r="C38" s="113"/>
       <c r="D38" s="7"/>
       <c r="E38" s="38"/>
       <c r="F38" s="70"/>
@@ -2646,10 +2717,10 @@
       </c>
     </row>
     <row r="39" spans="2:7">
-      <c r="B39" s="107" t="s">
+      <c r="B39" s="114" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="108"/>
+      <c r="C39" s="115"/>
       <c r="D39" s="7"/>
       <c r="E39" s="38">
         <v>2</v>
@@ -2662,10 +2733,10 @@
       </c>
     </row>
     <row r="40" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B40" s="121" t="s">
+      <c r="B40" s="94" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="122"/>
+      <c r="C40" s="95"/>
       <c r="D40" s="8"/>
       <c r="E40" s="44">
         <v>3</v>
@@ -2678,10 +2749,10 @@
       </c>
     </row>
     <row r="41" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B41" s="119" t="s">
+      <c r="B41" s="92" t="s">
         <v>84</v>
       </c>
-      <c r="C41" s="120"/>
+      <c r="C41" s="93"/>
       <c r="D41" s="49"/>
       <c r="E41" s="68">
         <f>SUM(E3+E16+E26+F32)</f>
@@ -2697,6 +2768,30 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B7:C7"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B14:C14"/>
@@ -2713,30 +2808,6 @@
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B19:C19"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2746,7 +2817,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DBF476-724A-4DAE-8D66-8B0809F96B84}">
-  <dimension ref="B1:K20"/>
+  <dimension ref="B1:K23"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="3" max="3" width="18.125" customWidth="1"/>
@@ -2756,17 +2827,17 @@
   <sheetData>
     <row r="1" spans="2:11" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B2" s="101" t="s">
+      <c r="B2" s="116" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="102"/>
-      <c r="D2" s="48" t="s">
+      <c r="C2" s="143"/>
+      <c r="D2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="81" t="s">
+      <c r="E2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="48" t="s">
         <v>8</v>
       </c>
       <c r="G2" s="11" t="s">
@@ -2784,25 +2855,25 @@
       </c>
     </row>
     <row r="3" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B3" s="93" t="s">
+      <c r="B3" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="94"/>
-      <c r="D3" s="48" t="s">
+      <c r="C3" s="144"/>
+      <c r="D3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="45">
-        <f>SUM(E4:E6)</f>
-        <v>6</v>
+      <c r="E3" s="46">
+        <f>SUM(E4:E7)</f>
+        <v>8</v>
       </c>
       <c r="F3" s="46">
-        <f>SUM(F4:F6)</f>
-        <v>3</v>
-      </c>
-      <c r="G3" s="11" t="s">
+        <f>SUM(F4:F7)</f>
+        <v>5</v>
+      </c>
+      <c r="G3" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="I3" s="84" t="s">
+      <c r="I3" s="83" t="s">
         <v>78</v>
       </c>
       <c r="J3" s="63">
@@ -2814,299 +2885,327 @@
       </c>
     </row>
     <row r="4" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B4" s="95" t="s">
+      <c r="B4" s="106" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="96"/>
+      <c r="C4" s="145"/>
       <c r="D4" s="6"/>
       <c r="E4" s="42">
         <v>2</v>
       </c>
       <c r="F4" s="42"/>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="I4" s="89" t="s">
+      <c r="I4" s="88" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="90">
+      <c r="J4" s="89">
         <v>46314</v>
       </c>
-      <c r="K4" s="91" t="str">
+      <c r="K4" s="90" t="str">
         <f ca="1">SUM(J4-J2)&amp; "日"</f>
         <v>14日</v>
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="97" t="s">
+      <c r="B5" s="140" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="141"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="39">
+        <v>2</v>
+      </c>
+      <c r="F5" s="39"/>
+      <c r="G5" s="54" t="s">
+        <v>82</v>
+      </c>
+      <c r="I5" s="154"/>
+      <c r="J5" s="138"/>
+      <c r="K5" s="139"/>
+    </row>
+    <row r="6" spans="2:11">
+      <c r="B6" s="108" t="s">
         <v>66</v>
       </c>
-      <c r="C5" s="98"/>
-      <c r="D5" s="83"/>
-      <c r="E5" s="85">
+      <c r="C6" s="142"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="39">
         <v>2</v>
       </c>
-      <c r="F5" s="85">
+      <c r="F6" s="39">
+        <v>5</v>
+      </c>
+      <c r="G6" s="54" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="73"/>
+      <c r="K6" s="74"/>
+    </row>
+    <row r="7" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B7" s="104" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="146"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="40">
+        <v>2</v>
+      </c>
+      <c r="F7" s="40"/>
+      <c r="G7" s="85" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B8" s="110" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="144"/>
+      <c r="D8" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="46">
+        <f>SUM(E9:E11)</f>
+        <v>7</v>
+      </c>
+      <c r="F8" s="46">
+        <f>SUM(F9:F11)</f>
         <v>3</v>
       </c>
-      <c r="G5" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="74"/>
-    </row>
-    <row r="6" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B6" s="99" t="s">
+      <c r="G8" s="48" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11">
+      <c r="B9" s="106" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="145"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="43">
+        <v>2</v>
+      </c>
+      <c r="F9" s="43">
+        <v>1</v>
+      </c>
+      <c r="G9" s="54" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11">
+      <c r="B10" s="108" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="142"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="39">
+        <v>3</v>
+      </c>
+      <c r="F10" s="39">
+        <v>2</v>
+      </c>
+      <c r="G10" s="54" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B11" s="104" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="146"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="40">
+        <v>2</v>
+      </c>
+      <c r="F11" s="40"/>
+      <c r="G11" s="85" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B12" s="110" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="144"/>
+      <c r="D12" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="46">
+        <f>SUM(E13:E14)</f>
+        <v>3</v>
+      </c>
+      <c r="F12" s="46">
+        <f>SUM(F13:F14)</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="48" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11">
+      <c r="B13" s="118" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="147"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="39">
+        <v>1</v>
+      </c>
+      <c r="F13" s="39"/>
+      <c r="G13" s="53" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B14" s="123" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="100"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="40">
+      <c r="C14" s="148"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="40">
         <v>2</v>
       </c>
-      <c r="F6" s="40"/>
-      <c r="G6" s="10" t="s">
+      <c r="F14" s="40"/>
+      <c r="G14" s="75" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B7" s="93" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="94"/>
-      <c r="D7" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="46">
-        <f>SUM(E8:E10)</f>
-        <v>7</v>
-      </c>
-      <c r="F7" s="46">
-        <f>SUM(F8:F10)</f>
-        <v>3</v>
-      </c>
-      <c r="G7" s="49" t="s">
+    <row r="15" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B15" s="110" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="144"/>
+      <c r="D15" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="46">
+        <f>SUM(E16+E18+E20)</f>
+        <v>9</v>
+      </c>
+      <c r="F15" s="46">
+        <f>SUM(F16+F18+F20)</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="48" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="8" spans="2:11">
-      <c r="B8" s="95" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="96"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="43">
+    <row r="16" spans="2:11">
+      <c r="B16" s="106" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="145"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="43">
+        <v>5</v>
+      </c>
+      <c r="F16" s="43"/>
+      <c r="G16" s="53" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="112" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="149"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="53" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="108" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="142"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="39">
         <v>2</v>
       </c>
-      <c r="F8" s="43">
-        <v>1</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11">
-      <c r="B9" s="97" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="98"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="39">
-        <v>3</v>
-      </c>
-      <c r="F9" s="39">
+      <c r="F18" s="39"/>
+      <c r="G18" s="53" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="112" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="149"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="53" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B20" s="114" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="150"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="41">
         <v>2</v>
       </c>
-      <c r="G9" s="10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B10" s="99" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" s="100"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="40">
-        <v>2</v>
-      </c>
-      <c r="F10" s="40"/>
-      <c r="G10" s="83" t="s">
+      <c r="F20" s="39"/>
+      <c r="G20" s="152" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B11" s="93" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="94"/>
-      <c r="D11" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="46">
-        <f>SUM(E12:E13)</f>
-        <v>3</v>
-      </c>
-      <c r="F11" s="46">
-        <f>SUM(F12:F13)</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11">
-      <c r="B12" s="103" t="s">
-        <v>71</v>
-      </c>
-      <c r="C12" s="104"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="39">
-        <v>1</v>
-      </c>
-      <c r="F12" s="39"/>
-      <c r="G12" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B13" s="105" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="106"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="40">
-        <v>2</v>
-      </c>
-      <c r="F13" s="40"/>
-      <c r="G13" s="9" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B14" s="93" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="94"/>
-      <c r="D14" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="45">
-        <f>SUM(E15+E17+E19)</f>
-        <v>9</v>
-      </c>
-      <c r="F14" s="46">
-        <f>SUM(F15+F17+F19)</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11">
-      <c r="B15" s="95" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="96"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="47">
-        <v>5</v>
-      </c>
-      <c r="F15" s="43"/>
-      <c r="G15" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11">
-      <c r="B16" s="111" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="112"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="97" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" s="98"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="38">
-        <v>2</v>
-      </c>
-      <c r="F17" s="39"/>
-      <c r="G17" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="111" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="112"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="7" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B19" s="107" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" s="108"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="38">
-        <v>2</v>
-      </c>
-      <c r="F19" s="39"/>
-      <c r="G19" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B20" s="109" t="s">
+    <row r="21" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B21" s="122" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="110"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="45">
-        <f>SUM(E3+E7+E11+E14)</f>
-        <v>25</v>
-      </c>
-      <c r="F20" s="46">
-        <f>SUM(F3+F7+F11+F14)</f>
-        <v>6</v>
-      </c>
-      <c r="G20" s="82"/>
+      <c r="C21" s="151"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="45">
+        <f>SUM(E3+E8+E12+E15)</f>
+        <v>27</v>
+      </c>
+      <c r="F21" s="46">
+        <f>SUM(F3+F8+F12+F15)</f>
+        <v>8</v>
+      </c>
+      <c r="G21" s="81"/>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" s="153" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="153"/>
+      <c r="D23" s="153"/>
+      <c r="E23" s="153"/>
+      <c r="F23" s="153"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="21">
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3127,10 +3226,10 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B2" s="127" t="s">
+      <c r="B2" s="135" t="s">
         <v>72</v>
       </c>
-      <c r="C2" s="128"/>
+      <c r="C2" s="136"/>
       <c r="D2" s="11" t="s">
         <v>9</v>
       </c>
@@ -3145,10 +3244,10 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B3" s="129" t="s">
+      <c r="B3" s="130" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="130"/>
+      <c r="C3" s="131"/>
       <c r="D3" s="11" t="s">
         <v>12</v>
       </c>
@@ -3175,19 +3274,19 @@
       </c>
     </row>
     <row r="4" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B4" s="131" t="s">
+      <c r="B4" s="128" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="132"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="85">
+      <c r="C4" s="129"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="84">
         <v>3</v>
       </c>
       <c r="F4" s="80">
         <f>SUM(F5)</f>
         <v>0</v>
       </c>
-      <c r="G4" s="86" t="s">
+      <c r="G4" s="85" t="s">
         <v>82</v>
       </c>
       <c r="J4" s="65" t="s">
@@ -3202,10 +3301,10 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B5" s="129" t="s">
+      <c r="B5" s="130" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="130"/>
+      <c r="C5" s="131"/>
       <c r="D5" s="11" t="s">
         <v>11</v>
       </c>
@@ -3232,19 +3331,19 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B6" s="131" t="s">
+      <c r="B6" s="128" t="s">
         <v>74</v>
       </c>
-      <c r="C6" s="132"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="85">
+      <c r="C6" s="129"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="84">
         <v>3</v>
       </c>
       <c r="F6" s="80">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G6" s="86" t="s">
+      <c r="G6" s="85" t="s">
         <v>82</v>
       </c>
       <c r="J6" s="67" t="s">
@@ -3259,10 +3358,10 @@
       </c>
     </row>
     <row r="7" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B7" s="129" t="s">
+      <c r="B7" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="130"/>
+      <c r="C7" s="131"/>
       <c r="D7" s="11" t="s">
         <v>10</v>
       </c>
@@ -3279,10 +3378,10 @@
       </c>
     </row>
     <row r="8" spans="2:12">
-      <c r="B8" s="115" t="s">
+      <c r="B8" s="120" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="133"/>
+      <c r="C8" s="132"/>
       <c r="D8" s="10"/>
       <c r="E8" s="43">
         <v>3</v>
@@ -3293,24 +3392,24 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B9" s="134" t="s">
+      <c r="B9" s="133" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="135"/>
+      <c r="C9" s="134"/>
       <c r="D9" s="9"/>
       <c r="E9" s="40">
         <v>2</v>
       </c>
-      <c r="F9" s="88"/>
+      <c r="F9" s="87"/>
       <c r="G9" s="75" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B10" s="129" t="s">
+      <c r="B10" s="130" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="130"/>
+      <c r="C10" s="131"/>
       <c r="D10" s="11" t="s">
         <v>14</v>
       </c>
@@ -3327,24 +3426,24 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B11" s="131" t="s">
+      <c r="B11" s="128" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="132"/>
-      <c r="D11" s="83"/>
-      <c r="E11" s="85">
+      <c r="C11" s="129"/>
+      <c r="D11" s="82"/>
+      <c r="E11" s="84">
         <v>2</v>
       </c>
-      <c r="F11" s="87"/>
-      <c r="G11" s="86" t="s">
+      <c r="F11" s="86"/>
+      <c r="G11" s="85" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B12" s="129" t="s">
+      <c r="B12" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="130"/>
+      <c r="C12" s="131"/>
       <c r="D12" s="11"/>
       <c r="E12" s="46">
         <f>SUM(E13:E14)</f>
@@ -3359,10 +3458,10 @@
       </c>
     </row>
     <row r="13" spans="2:12">
-      <c r="B13" s="115" t="s">
+      <c r="B13" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="133"/>
+      <c r="C13" s="132"/>
       <c r="D13" s="10"/>
       <c r="E13" s="43">
         <v>1</v>
@@ -3373,24 +3472,24 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B14" s="134" t="s">
+      <c r="B14" s="133" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="135"/>
+      <c r="C14" s="134"/>
       <c r="D14" s="9"/>
       <c r="E14" s="40">
         <v>1</v>
       </c>
-      <c r="F14" s="88"/>
+      <c r="F14" s="87"/>
       <c r="G14" s="75" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B15" s="129" t="s">
+      <c r="B15" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="130"/>
+      <c r="C15" s="131"/>
       <c r="D15" s="11"/>
       <c r="E15" s="46">
         <f>SUM(E16:E17)</f>
@@ -3405,10 +3504,10 @@
       </c>
     </row>
     <row r="16" spans="2:12">
-      <c r="B16" s="115" t="s">
+      <c r="B16" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="133"/>
+      <c r="C16" s="132"/>
       <c r="D16" s="10"/>
       <c r="E16" s="43">
         <v>1</v>
@@ -3419,10 +3518,10 @@
       </c>
     </row>
     <row r="17" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B17" s="136" t="s">
+      <c r="B17" s="124" t="s">
         <v>73</v>
       </c>
-      <c r="C17" s="137"/>
+      <c r="C17" s="125"/>
       <c r="D17" s="8"/>
       <c r="E17" s="41">
         <v>1</v>
@@ -3433,10 +3532,10 @@
       </c>
     </row>
     <row r="18" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B18" s="138" t="s">
+      <c r="B18" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="139"/>
+      <c r="C18" s="127"/>
       <c r="D18" s="11"/>
       <c r="E18" s="46">
         <f>SUM(E3+E5+E7+E10+E12+E15)</f>
@@ -3453,6 +3552,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B11:C11"/>
@@ -3460,16 +3569,6 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3482,13 +3581,13 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="140" t="s">
+      <c r="C1" s="137" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
     </row>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
       <c r="B2" s="30" t="s">

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F3AE27-0165-4E99-9C09-A99B0AF2FB14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E62EF4C-B75A-4C2E-B9EA-1B6D10E93697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1376,7 +1376,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="155">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1583,6 +1583,111 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1595,88 +1700,52 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1689,88 +1758,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2078,10 +2069,10 @@
   <sheetData>
     <row r="1" spans="2:19" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="102" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="117"/>
+      <c r="C2" s="123"/>
       <c r="D2" s="48" t="s">
         <v>9</v>
       </c>
@@ -2096,10 +2087,10 @@
       </c>
     </row>
     <row r="3" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B3" s="110" t="s">
+      <c r="B3" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="111"/>
+      <c r="C3" s="122"/>
       <c r="D3" s="48" t="s">
         <v>12</v>
       </c>
@@ -2119,17 +2110,17 @@
       </c>
       <c r="J3" s="64">
         <f ca="1">TODAY()</f>
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="K3" s="48" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="4" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B4" s="106" t="s">
+      <c r="B4" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="107"/>
+      <c r="C4" s="124"/>
       <c r="D4" s="10"/>
       <c r="E4" s="43">
         <f>SUM(E5:E7)</f>
@@ -2150,14 +2141,14 @@
       </c>
       <c r="K4" s="80" t="str">
         <f ca="1">SUM($J4-J3)&amp; "日"</f>
-        <v>-5日</v>
+        <v>-7日</v>
       </c>
     </row>
     <row r="5" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B5" s="96" t="s">
+      <c r="B5" s="125" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="97"/>
+      <c r="C5" s="126"/>
       <c r="D5" s="7"/>
       <c r="E5" s="39">
         <v>2</v>
@@ -2176,16 +2167,16 @@
       </c>
       <c r="K5" s="90" t="str">
         <f ca="1">SUM(J5-J3)&amp; "日"</f>
-        <v>14日</v>
+        <v>12日</v>
       </c>
       <c r="R5" s="73"/>
       <c r="S5" s="74"/>
     </row>
     <row r="6" spans="2:19">
-      <c r="B6" s="96" t="s">
+      <c r="B6" s="125" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="97"/>
+      <c r="C6" s="126"/>
       <c r="D6" s="7"/>
       <c r="E6" s="39">
         <v>1</v>
@@ -2200,10 +2191,10 @@
       <c r="S6" s="74"/>
     </row>
     <row r="7" spans="2:19">
-      <c r="B7" s="96" t="s">
+      <c r="B7" s="125" t="s">
         <v>88</v>
       </c>
-      <c r="C7" s="97"/>
+      <c r="C7" s="126"/>
       <c r="D7" s="7"/>
       <c r="E7" s="39">
         <v>1</v>
@@ -2218,10 +2209,10 @@
       <c r="S7" s="74"/>
     </row>
     <row r="8" spans="2:19">
-      <c r="B8" s="108" t="s">
+      <c r="B8" s="98" t="s">
         <v>87</v>
       </c>
-      <c r="C8" s="109"/>
+      <c r="C8" s="116"/>
       <c r="D8" s="7"/>
       <c r="E8" s="39">
         <v>2</v>
@@ -2234,10 +2225,10 @@
       </c>
     </row>
     <row r="9" spans="2:19">
-      <c r="B9" s="108" t="s">
+      <c r="B9" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="109"/>
+      <c r="C9" s="116"/>
       <c r="D9" s="9"/>
       <c r="E9" s="40">
         <v>2</v>
@@ -2250,10 +2241,10 @@
       </c>
     </row>
     <row r="10" spans="2:19">
-      <c r="B10" s="108" t="s">
+      <c r="B10" s="98" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="109"/>
+      <c r="C10" s="116"/>
       <c r="D10" s="9"/>
       <c r="E10" s="40">
         <v>2</v>
@@ -2266,7 +2257,7 @@
       </c>
     </row>
     <row r="11" spans="2:19">
-      <c r="B11" s="118" t="s">
+      <c r="B11" s="106" t="s">
         <v>83</v>
       </c>
       <c r="C11" s="119"/>
@@ -2282,10 +2273,10 @@
       </c>
     </row>
     <row r="12" spans="2:19">
-      <c r="B12" s="108" t="s">
+      <c r="B12" s="98" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="109"/>
+      <c r="C12" s="116"/>
       <c r="D12" s="7"/>
       <c r="E12" s="39">
         <f>SUM(E13:E15)</f>
@@ -2300,10 +2291,10 @@
       </c>
     </row>
     <row r="13" spans="2:19">
-      <c r="B13" s="100" t="s">
+      <c r="B13" s="117" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="101"/>
+      <c r="C13" s="118"/>
       <c r="D13" s="7"/>
       <c r="E13" s="39">
         <v>1</v>
@@ -2316,10 +2307,10 @@
       </c>
     </row>
     <row r="14" spans="2:19">
-      <c r="B14" s="96" t="s">
+      <c r="B14" s="125" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="97"/>
+      <c r="C14" s="126"/>
       <c r="D14" s="7"/>
       <c r="E14" s="39">
         <v>1</v>
@@ -2334,10 +2325,10 @@
       <c r="S14" s="74"/>
     </row>
     <row r="15" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B15" s="98" t="s">
+      <c r="B15" s="131" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="99"/>
+      <c r="C15" s="132"/>
       <c r="D15" s="9"/>
       <c r="E15" s="40">
         <v>1</v>
@@ -2350,10 +2341,10 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B16" s="110" t="s">
+      <c r="B16" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="C16" s="111"/>
+      <c r="C16" s="122"/>
       <c r="D16" s="11" t="s">
         <v>11</v>
       </c>
@@ -2369,10 +2360,10 @@
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="106" t="s">
+      <c r="B17" s="96" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="107"/>
+      <c r="C17" s="124"/>
       <c r="D17" s="10"/>
       <c r="E17" s="78">
         <v>3</v>
@@ -2385,10 +2376,10 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="108" t="s">
+      <c r="B18" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="109"/>
+      <c r="C18" s="116"/>
       <c r="D18" s="7"/>
       <c r="E18" s="70">
         <v>3</v>
@@ -2401,10 +2392,10 @@
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="108" t="s">
+      <c r="B19" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="109"/>
+      <c r="C19" s="116"/>
       <c r="D19" s="7"/>
       <c r="E19" s="70">
         <v>3</v>
@@ -2417,10 +2408,10 @@
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="108" t="s">
+      <c r="B20" s="98" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="109"/>
+      <c r="C20" s="116"/>
       <c r="D20" s="9"/>
       <c r="E20" s="70">
         <v>3</v>
@@ -2433,10 +2424,10 @@
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="108" t="s">
+      <c r="B21" s="98" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="109"/>
+      <c r="C21" s="116"/>
       <c r="D21" s="7"/>
       <c r="E21" s="71">
         <v>1</v>
@@ -2449,7 +2440,7 @@
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="118" t="s">
+      <c r="B22" s="106" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="119"/>
@@ -2463,10 +2454,10 @@
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="100" t="s">
+      <c r="B23" s="117" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="101"/>
+      <c r="C23" s="118"/>
       <c r="D23" s="7"/>
       <c r="E23" s="70">
         <v>1</v>
@@ -2479,10 +2470,10 @@
       </c>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="100" t="s">
+      <c r="B24" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="101"/>
+      <c r="C24" s="118"/>
       <c r="D24" s="7"/>
       <c r="E24" s="70">
         <v>1</v>
@@ -2495,10 +2486,10 @@
       </c>
     </row>
     <row r="25" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B25" s="102" t="s">
+      <c r="B25" s="133" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="103"/>
+      <c r="C25" s="134"/>
       <c r="D25" s="8"/>
       <c r="E25" s="72">
         <v>1</v>
@@ -2511,10 +2502,10 @@
       </c>
     </row>
     <row r="26" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B26" s="110" t="s">
+      <c r="B26" s="94" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="111"/>
+      <c r="C26" s="122"/>
       <c r="D26" s="11" t="s">
         <v>10</v>
       </c>
@@ -2547,7 +2538,7 @@
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="118" t="s">
+      <c r="B28" s="106" t="s">
         <v>52</v>
       </c>
       <c r="C28" s="119"/>
@@ -2565,10 +2556,10 @@
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="100" t="s">
+      <c r="B29" s="117" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="101"/>
+      <c r="C29" s="118"/>
       <c r="D29" s="7"/>
       <c r="E29" s="39">
         <v>2</v>
@@ -2581,10 +2572,10 @@
       </c>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="100" t="s">
+      <c r="B30" s="117" t="s">
         <v>54</v>
       </c>
-      <c r="C30" s="101"/>
+      <c r="C30" s="118"/>
       <c r="D30" s="7"/>
       <c r="E30" s="39">
         <v>2</v>
@@ -2597,10 +2588,10 @@
       </c>
     </row>
     <row r="31" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B31" s="104" t="s">
+      <c r="B31" s="100" t="s">
         <v>55</v>
       </c>
-      <c r="C31" s="105"/>
+      <c r="C31" s="135"/>
       <c r="D31" s="9"/>
       <c r="E31" s="40">
         <v>3</v>
@@ -2613,10 +2604,10 @@
       </c>
     </row>
     <row r="32" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B32" s="110" t="s">
+      <c r="B32" s="94" t="s">
         <v>60</v>
       </c>
-      <c r="C32" s="111"/>
+      <c r="C32" s="122"/>
       <c r="D32" s="11" t="s">
         <v>14</v>
       </c>
@@ -2633,10 +2624,10 @@
       </c>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="106" t="s">
+      <c r="B33" s="96" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="107"/>
+      <c r="C33" s="124"/>
       <c r="D33" s="10"/>
       <c r="E33" s="47"/>
       <c r="F33" s="78"/>
@@ -2645,10 +2636,10 @@
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="96" t="s">
+      <c r="B34" s="125" t="s">
         <v>56</v>
       </c>
-      <c r="C34" s="97"/>
+      <c r="C34" s="126"/>
       <c r="D34" s="10"/>
       <c r="E34" s="47">
         <v>2</v>
@@ -2661,10 +2652,10 @@
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="112" t="s">
+      <c r="B35" s="114" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="113"/>
+      <c r="C35" s="136"/>
       <c r="D35" s="7"/>
       <c r="E35" s="38"/>
       <c r="F35" s="70"/>
@@ -2673,10 +2664,10 @@
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="108" t="s">
+      <c r="B36" s="98" t="s">
         <v>57</v>
       </c>
-      <c r="C36" s="109"/>
+      <c r="C36" s="116"/>
       <c r="D36" s="7"/>
       <c r="E36" s="38">
         <v>2</v>
@@ -2689,10 +2680,10 @@
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="108" t="s">
+      <c r="B37" s="98" t="s">
         <v>58</v>
       </c>
-      <c r="C37" s="109"/>
+      <c r="C37" s="116"/>
       <c r="D37" s="7"/>
       <c r="E37" s="38">
         <v>2</v>
@@ -2705,10 +2696,10 @@
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="112" t="s">
+      <c r="B38" s="114" t="s">
         <v>5</v>
       </c>
-      <c r="C38" s="113"/>
+      <c r="C38" s="136"/>
       <c r="D38" s="7"/>
       <c r="E38" s="38"/>
       <c r="F38" s="70"/>
@@ -2717,10 +2708,10 @@
       </c>
     </row>
     <row r="39" spans="2:7">
-      <c r="B39" s="114" t="s">
+      <c r="B39" s="110" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="115"/>
+      <c r="C39" s="137"/>
       <c r="D39" s="7"/>
       <c r="E39" s="38">
         <v>2</v>
@@ -2733,10 +2724,10 @@
       </c>
     </row>
     <row r="40" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B40" s="94" t="s">
+      <c r="B40" s="129" t="s">
         <v>62</v>
       </c>
-      <c r="C40" s="95"/>
+      <c r="C40" s="130"/>
       <c r="D40" s="8"/>
       <c r="E40" s="44">
         <v>3</v>
@@ -2749,10 +2740,10 @@
       </c>
     </row>
     <row r="41" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B41" s="92" t="s">
+      <c r="B41" s="127" t="s">
         <v>84</v>
       </c>
-      <c r="C41" s="93"/>
+      <c r="C41" s="128"/>
       <c r="D41" s="49"/>
       <c r="E41" s="68">
         <f>SUM(E3+E16+E26+F32)</f>
@@ -2768,30 +2759,6 @@
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B7:C7"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B14:C14"/>
@@ -2808,6 +2775,30 @@
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B19:C19"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2827,10 +2818,10 @@
   <sheetData>
     <row r="1" spans="2:11" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B2" s="116" t="s">
+      <c r="B2" s="102" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="143"/>
+      <c r="C2" s="103"/>
       <c r="D2" s="11" t="s">
         <v>9</v>
       </c>
@@ -2848,17 +2839,17 @@
       </c>
       <c r="J2" s="64">
         <f ca="1">TODAY()</f>
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="K2" s="48" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="3" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B3" s="110" t="s">
+      <c r="B3" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="144"/>
+      <c r="C3" s="95"/>
       <c r="D3" s="11" t="s">
         <v>12</v>
       </c>
@@ -2868,7 +2859,7 @@
       </c>
       <c r="F3" s="46">
         <f>SUM(F4:F7)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G3" s="48" t="s">
         <v>82</v>
@@ -2881,21 +2872,23 @@
       </c>
       <c r="K3" s="59" t="str">
         <f ca="1">SUM($J3-J2)&amp; "日"</f>
-        <v>5日</v>
+        <v>3日</v>
       </c>
     </row>
     <row r="4" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B4" s="106" t="s">
+      <c r="B4" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="145"/>
+      <c r="C4" s="97"/>
       <c r="D4" s="6"/>
       <c r="E4" s="42">
         <v>2</v>
       </c>
-      <c r="F4" s="42"/>
+      <c r="F4" s="42">
+        <v>2</v>
+      </c>
       <c r="G4" s="54" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I4" s="88" t="s">
         <v>75</v>
@@ -2905,31 +2898,33 @@
       </c>
       <c r="K4" s="90" t="str">
         <f ca="1">SUM(J4-J2)&amp; "日"</f>
-        <v>14日</v>
+        <v>12日</v>
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="140" t="s">
+      <c r="B5" s="104" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="141"/>
+      <c r="C5" s="105"/>
       <c r="D5" s="7"/>
       <c r="E5" s="39">
         <v>2</v>
       </c>
-      <c r="F5" s="39"/>
+      <c r="F5" s="39">
+        <v>2</v>
+      </c>
       <c r="G5" s="54" t="s">
-        <v>82</v>
-      </c>
-      <c r="I5" s="154"/>
-      <c r="J5" s="138"/>
-      <c r="K5" s="139"/>
+        <v>86</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="74"/>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" s="108" t="s">
+      <c r="B6" s="98" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="142"/>
+      <c r="C6" s="99"/>
       <c r="D6" s="7"/>
       <c r="E6" s="39">
         <v>2</v>
@@ -2945,10 +2940,10 @@
       <c r="K6" s="74"/>
     </row>
     <row r="7" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B7" s="104" t="s">
+      <c r="B7" s="100" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="146"/>
+      <c r="C7" s="101"/>
       <c r="D7" s="9"/>
       <c r="E7" s="40">
         <v>2</v>
@@ -2959,10 +2954,10 @@
       </c>
     </row>
     <row r="8" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B8" s="110" t="s">
+      <c r="B8" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="144"/>
+      <c r="C8" s="95"/>
       <c r="D8" s="11" t="s">
         <v>11</v>
       </c>
@@ -2979,10 +2974,10 @@
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="106" t="s">
+      <c r="B9" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="145"/>
+      <c r="C9" s="97"/>
       <c r="D9" s="10"/>
       <c r="E9" s="43">
         <v>2</v>
@@ -2995,10 +2990,10 @@
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="108" t="s">
+      <c r="B10" s="98" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="142"/>
+      <c r="C10" s="99"/>
       <c r="D10" s="7"/>
       <c r="E10" s="39">
         <v>3</v>
@@ -3011,10 +3006,10 @@
       </c>
     </row>
     <row r="11" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B11" s="104" t="s">
+      <c r="B11" s="100" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="146"/>
+      <c r="C11" s="101"/>
       <c r="D11" s="9"/>
       <c r="E11" s="40">
         <v>2</v>
@@ -3025,10 +3020,10 @@
       </c>
     </row>
     <row r="12" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B12" s="110" t="s">
+      <c r="B12" s="94" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="144"/>
+      <c r="C12" s="95"/>
       <c r="D12" s="11" t="s">
         <v>10</v>
       </c>
@@ -3045,10 +3040,10 @@
       </c>
     </row>
     <row r="13" spans="2:11">
-      <c r="B13" s="118" t="s">
+      <c r="B13" s="106" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="147"/>
+      <c r="C13" s="107"/>
       <c r="D13" s="7"/>
       <c r="E13" s="39">
         <v>1</v>
@@ -3059,10 +3054,10 @@
       </c>
     </row>
     <row r="14" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B14" s="123" t="s">
+      <c r="B14" s="108" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="148"/>
+      <c r="C14" s="109"/>
       <c r="D14" s="9"/>
       <c r="E14" s="40">
         <v>2</v>
@@ -3073,10 +3068,10 @@
       </c>
     </row>
     <row r="15" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B15" s="110" t="s">
+      <c r="B15" s="94" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="144"/>
+      <c r="C15" s="95"/>
       <c r="D15" s="11" t="s">
         <v>14</v>
       </c>
@@ -3093,10 +3088,10 @@
       </c>
     </row>
     <row r="16" spans="2:11">
-      <c r="B16" s="106" t="s">
+      <c r="B16" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="145"/>
+      <c r="C16" s="97"/>
       <c r="D16" s="10"/>
       <c r="E16" s="43">
         <v>5</v>
@@ -3107,10 +3102,10 @@
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="112" t="s">
+      <c r="B17" s="114" t="s">
         <v>4</v>
       </c>
-      <c r="C17" s="149"/>
+      <c r="C17" s="115"/>
       <c r="D17" s="7"/>
       <c r="E17" s="39"/>
       <c r="F17" s="39"/>
@@ -3119,10 +3114,10 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="108" t="s">
+      <c r="B18" s="98" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="142"/>
+      <c r="C18" s="99"/>
       <c r="D18" s="7"/>
       <c r="E18" s="39">
         <v>2</v>
@@ -3133,10 +3128,10 @@
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="112" t="s">
+      <c r="B19" s="114" t="s">
         <v>5</v>
       </c>
-      <c r="C19" s="149"/>
+      <c r="C19" s="115"/>
       <c r="D19" s="7"/>
       <c r="E19" s="39"/>
       <c r="F19" s="39"/>
@@ -3145,24 +3140,24 @@
       </c>
     </row>
     <row r="20" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B20" s="114" t="s">
+      <c r="B20" s="110" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="150"/>
+      <c r="C20" s="111"/>
       <c r="D20" s="7"/>
       <c r="E20" s="41">
         <v>2</v>
       </c>
       <c r="F20" s="39"/>
-      <c r="G20" s="152" t="s">
+      <c r="G20" s="92" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B21" s="122" t="s">
+      <c r="B21" s="112" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="151"/>
+      <c r="C21" s="113"/>
       <c r="D21" s="11"/>
       <c r="E21" s="45">
         <f>SUM(E3+E8+E12+E15)</f>
@@ -3170,32 +3165,32 @@
       </c>
       <c r="F21" s="46">
         <f>SUM(F3+F8+F12+F15)</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G21" s="81"/>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="153" t="s">
+      <c r="B23" s="93" t="s">
         <v>90</v>
       </c>
-      <c r="C23" s="153"/>
-      <c r="D23" s="153"/>
-      <c r="E23" s="153"/>
-      <c r="F23" s="153"/>
+      <c r="C23" s="93"/>
+      <c r="D23" s="93"/>
+      <c r="E23" s="93"/>
+      <c r="F23" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
@@ -3226,10 +3221,10 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B2" s="135" t="s">
+      <c r="B2" s="138" t="s">
         <v>72</v>
       </c>
-      <c r="C2" s="136"/>
+      <c r="C2" s="139"/>
       <c r="D2" s="11" t="s">
         <v>9</v>
       </c>
@@ -3244,10 +3239,10 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B3" s="130" t="s">
+      <c r="B3" s="140" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="131"/>
+      <c r="C3" s="141"/>
       <c r="D3" s="11" t="s">
         <v>12</v>
       </c>
@@ -3267,17 +3262,17 @@
       </c>
       <c r="K3" s="64">
         <f ca="1">TODAY()</f>
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="L3" s="48" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B4" s="128" t="s">
+      <c r="B4" s="142" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="129"/>
+      <c r="C4" s="143"/>
       <c r="D4" s="82"/>
       <c r="E4" s="84">
         <v>3</v>
@@ -3301,10 +3296,10 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B5" s="130" t="s">
+      <c r="B5" s="140" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="131"/>
+      <c r="C5" s="141"/>
       <c r="D5" s="11" t="s">
         <v>11</v>
       </c>
@@ -3331,10 +3326,10 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B6" s="128" t="s">
+      <c r="B6" s="142" t="s">
         <v>74</v>
       </c>
-      <c r="C6" s="129"/>
+      <c r="C6" s="143"/>
       <c r="D6" s="82"/>
       <c r="E6" s="84">
         <v>3</v>
@@ -3354,14 +3349,14 @@
       </c>
       <c r="L6" s="59" t="str">
         <f ca="1">SUM(K6-K3)&amp; "日"</f>
-        <v>14日</v>
+        <v>12日</v>
       </c>
     </row>
     <row r="7" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B7" s="130" t="s">
+      <c r="B7" s="140" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="131"/>
+      <c r="C7" s="141"/>
       <c r="D7" s="11" t="s">
         <v>10</v>
       </c>
@@ -3381,7 +3376,7 @@
       <c r="B8" s="120" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="132"/>
+      <c r="C8" s="144"/>
       <c r="D8" s="10"/>
       <c r="E8" s="43">
         <v>3</v>
@@ -3392,10 +3387,10 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B9" s="133" t="s">
+      <c r="B9" s="145" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="134"/>
+      <c r="C9" s="146"/>
       <c r="D9" s="9"/>
       <c r="E9" s="40">
         <v>2</v>
@@ -3406,10 +3401,10 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B10" s="130" t="s">
+      <c r="B10" s="140" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="131"/>
+      <c r="C10" s="141"/>
       <c r="D10" s="11" t="s">
         <v>14</v>
       </c>
@@ -3426,10 +3421,10 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B11" s="128" t="s">
+      <c r="B11" s="142" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="129"/>
+      <c r="C11" s="143"/>
       <c r="D11" s="82"/>
       <c r="E11" s="84">
         <v>2</v>
@@ -3440,10 +3435,10 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B12" s="130" t="s">
+      <c r="B12" s="140" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="131"/>
+      <c r="C12" s="141"/>
       <c r="D12" s="11"/>
       <c r="E12" s="46">
         <f>SUM(E13:E14)</f>
@@ -3461,7 +3456,7 @@
       <c r="B13" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="C13" s="132"/>
+      <c r="C13" s="144"/>
       <c r="D13" s="10"/>
       <c r="E13" s="43">
         <v>1</v>
@@ -3472,10 +3467,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B14" s="133" t="s">
+      <c r="B14" s="145" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="134"/>
+      <c r="C14" s="146"/>
       <c r="D14" s="9"/>
       <c r="E14" s="40">
         <v>1</v>
@@ -3486,10 +3481,10 @@
       </c>
     </row>
     <row r="15" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B15" s="130" t="s">
+      <c r="B15" s="140" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="131"/>
+      <c r="C15" s="141"/>
       <c r="D15" s="11"/>
       <c r="E15" s="46">
         <f>SUM(E16:E17)</f>
@@ -3507,7 +3502,7 @@
       <c r="B16" s="120" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="132"/>
+      <c r="C16" s="144"/>
       <c r="D16" s="10"/>
       <c r="E16" s="43">
         <v>1</v>
@@ -3518,10 +3513,10 @@
       </c>
     </row>
     <row r="17" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B17" s="124" t="s">
+      <c r="B17" s="147" t="s">
         <v>73</v>
       </c>
-      <c r="C17" s="125"/>
+      <c r="C17" s="148"/>
       <c r="D17" s="8"/>
       <c r="E17" s="41">
         <v>1</v>
@@ -3532,10 +3527,10 @@
       </c>
     </row>
     <row r="18" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B18" s="126" t="s">
+      <c r="B18" s="149" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="127"/>
+      <c r="C18" s="150"/>
       <c r="D18" s="11"/>
       <c r="E18" s="46">
         <f>SUM(E3+E5+E7+E10+E12+E15)</f>
@@ -3552,16 +3547,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B11:C11"/>
@@ -3569,6 +3554,16 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3581,13 +3576,13 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="137" t="s">
+      <c r="C1" s="151" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="137"/>
-      <c r="E1" s="137"/>
-      <c r="F1" s="137"/>
-      <c r="G1" s="137"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="151"/>
+      <c r="G1" s="151"/>
     </row>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
       <c r="B2" s="30" t="s">

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\Documents\GitHub\GlassesGame\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ayato Terao\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E62EF4C-B75A-4C2E-B9EA-1B6D10E93697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B558CF5A-53E3-4113-BEF2-E34EA1F839BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="96">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -346,16 +346,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>仮マップ制作</t>
-    <rPh sb="0" eb="1">
-      <t>カリ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>セイサク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>アイテム</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -477,13 +467,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ゲーム内BGM</t>
-    <rPh sb="3" eb="4">
-      <t>ナイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>やること(β・Ｍ)</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -632,6 +615,46 @@
     <rPh sb="24" eb="26">
       <t>ジッソウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>歩行</t>
+    <rPh sb="0" eb="2">
+      <t>ホコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダッシュ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジャンプ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マップ制作</t>
+    <rPh sb="3" eb="5">
+      <t>セイサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボタン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵の増加</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ギミック</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -751,7 +774,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="50">
+  <borders count="53">
     <border>
       <left/>
       <right/>
@@ -902,19 +925,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1160,17 +1170,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -1255,6 +1254,50 @@
     </border>
     <border>
       <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
@@ -1263,59 +1306,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1372,11 +1362,85 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1384,7 +1448,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1399,10 +1463,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1417,19 +1478,17 @@
     <xf numFmtId="56" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="56" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1437,331 +1496,377 @@
     <xf numFmtId="56" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="56" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2050,7 +2155,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B1:S41"/>
+  <dimension ref="B1:S43"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9" style="4" customWidth="1"/>
@@ -2069,723 +2174,718 @@
   <sheetData>
     <row r="1" spans="2:19" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B2" s="102" t="s">
+      <c r="B2" s="81" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="123"/>
-      <c r="D2" s="48" t="s">
+      <c r="C2" s="115"/>
+      <c r="D2" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="11" t="s">
-        <v>81</v>
+      <c r="G2" s="10" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B3" s="94" t="s">
+      <c r="B3" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="122"/>
-      <c r="D3" s="48" t="s">
+      <c r="C3" s="113"/>
+      <c r="D3" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="45">
+      <c r="E3" s="40">
         <f>SUM(E4:E15)</f>
         <v>21</v>
       </c>
-      <c r="F3" s="46">
+      <c r="F3" s="40">
         <f>SUM(F4:F15)</f>
         <v>23</v>
       </c>
-      <c r="G3" s="48" t="s">
-        <v>86</v>
-      </c>
-      <c r="I3" s="61" t="s">
-        <v>76</v>
-      </c>
-      <c r="J3" s="64">
+      <c r="G3" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="J3" s="53">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
-      </c>
-      <c r="K3" s="48" t="s">
-        <v>85</v>
+        <v>46303</v>
+      </c>
+      <c r="K3" s="41" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B4" s="96" t="s">
+      <c r="B4" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="124"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="43">
+      <c r="C4" s="111"/>
+      <c r="D4" s="155"/>
+      <c r="E4" s="39">
         <f>SUM(E5:E7)</f>
         <v>4</v>
       </c>
-      <c r="F4" s="43">
+      <c r="F4" s="39">
         <f>SUM(F5:F7)</f>
         <v>5</v>
       </c>
-      <c r="G4" s="54" t="s">
+      <c r="G4" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I4" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="J4" s="53">
+        <v>46295</v>
+      </c>
+      <c r="K4" s="65" t="str">
+        <f ca="1">SUM($J4-J3)&amp; "日"</f>
+        <v>-8日</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" ht="19.5" thickBot="1">
+      <c r="B5" s="102" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="103"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="35">
+        <v>2</v>
+      </c>
+      <c r="F5" s="35">
+        <v>2</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I5" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="J5" s="73">
+        <v>46314</v>
+      </c>
+      <c r="K5" s="74" t="str">
+        <f ca="1">SUM(J5-J3)&amp; "日"</f>
+        <v>11日</v>
+      </c>
+      <c r="R5" s="58"/>
+      <c r="S5" s="59"/>
+    </row>
+    <row r="6" spans="2:19">
+      <c r="B6" s="102" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="103"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="35">
+        <v>1</v>
+      </c>
+      <c r="F6" s="35">
+        <v>2</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="R6" s="58"/>
+      <c r="S6" s="59"/>
+    </row>
+    <row r="7" spans="2:19">
+      <c r="B7" s="102" t="s">
         <v>86</v>
       </c>
-      <c r="I4" s="91" t="s">
-        <v>77</v>
-      </c>
-      <c r="J4" s="64">
-        <v>46295</v>
-      </c>
-      <c r="K4" s="80" t="str">
-        <f ca="1">SUM($J4-J3)&amp; "日"</f>
-        <v>-7日</v>
-      </c>
-    </row>
-    <row r="5" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B5" s="125" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="126"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="39">
+      <c r="C7" s="103"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="35">
+        <v>1</v>
+      </c>
+      <c r="F7" s="39">
+        <v>1</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="R7" s="58"/>
+      <c r="S7" s="59"/>
+    </row>
+    <row r="8" spans="2:19">
+      <c r="B8" s="89" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="112"/>
+      <c r="D8" s="79"/>
+      <c r="E8" s="35">
         <v>2</v>
       </c>
-      <c r="F5" s="39">
+      <c r="F8" s="39">
         <v>2</v>
       </c>
-      <c r="G5" s="54" t="s">
-        <v>86</v>
-      </c>
-      <c r="I5" s="88" t="s">
-        <v>75</v>
-      </c>
-      <c r="J5" s="89">
-        <v>46314</v>
-      </c>
-      <c r="K5" s="90" t="str">
-        <f ca="1">SUM(J5-J3)&amp; "日"</f>
-        <v>12日</v>
-      </c>
-      <c r="R5" s="73"/>
-      <c r="S5" s="74"/>
-    </row>
-    <row r="6" spans="2:19">
-      <c r="B6" s="125" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="126"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="39">
+      <c r="G8" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19">
+      <c r="B9" s="89" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="112"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="36">
+        <v>2</v>
+      </c>
+      <c r="F9" s="36">
+        <v>2</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19">
+      <c r="B10" s="89" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="112"/>
+      <c r="D10" s="80"/>
+      <c r="E10" s="36">
+        <v>2</v>
+      </c>
+      <c r="F10" s="36">
+        <v>2</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19">
+      <c r="B11" s="94" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="116"/>
+      <c r="D11" s="79"/>
+      <c r="E11" s="35">
         <v>1</v>
       </c>
-      <c r="F6" s="39">
-        <v>2</v>
-      </c>
-      <c r="G6" s="54" t="s">
-        <v>86</v>
-      </c>
-      <c r="R6" s="73"/>
-      <c r="S6" s="74"/>
-    </row>
-    <row r="7" spans="2:19">
-      <c r="B7" s="125" t="s">
-        <v>88</v>
-      </c>
-      <c r="C7" s="126"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="39">
+      <c r="F11" s="35">
         <v>1</v>
       </c>
-      <c r="F7" s="43">
-        <v>1</v>
-      </c>
-      <c r="G7" s="54" t="s">
-        <v>86</v>
-      </c>
-      <c r="R7" s="73"/>
-      <c r="S7" s="74"/>
-    </row>
-    <row r="8" spans="2:19">
-      <c r="B8" s="98" t="s">
-        <v>87</v>
-      </c>
-      <c r="C8" s="116"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="39">
-        <v>2</v>
-      </c>
-      <c r="F8" s="43">
-        <v>2</v>
-      </c>
-      <c r="G8" s="54" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" spans="2:19">
-      <c r="B9" s="98" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="116"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="40">
-        <v>2</v>
-      </c>
-      <c r="F9" s="40">
-        <v>2</v>
-      </c>
-      <c r="G9" s="54" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="2:19">
-      <c r="B10" s="98" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="116"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="40">
-        <v>2</v>
-      </c>
-      <c r="F10" s="40">
-        <v>2</v>
-      </c>
-      <c r="G10" s="54" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="2:19">
-      <c r="B11" s="106" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" s="119"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="39">
-        <v>1</v>
-      </c>
-      <c r="F11" s="39">
-        <v>1</v>
-      </c>
-      <c r="G11" s="53" t="s">
-        <v>86</v>
+      <c r="G11" s="6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="2:19">
-      <c r="B12" s="98" t="s">
+      <c r="B12" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="116"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="39">
+      <c r="C12" s="112"/>
+      <c r="D12" s="79"/>
+      <c r="E12" s="35">
         <f>SUM(E13:E15)</f>
         <v>3</v>
       </c>
-      <c r="F12" s="39">
+      <c r="F12" s="35">
         <f>SUM(F13:F15)</f>
         <v>3</v>
       </c>
-      <c r="G12" s="53" t="s">
-        <v>86</v>
+      <c r="G12" s="6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="2:19">
-      <c r="B13" s="117" t="s">
+      <c r="B13" s="106" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="118"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="39">
+      <c r="C13" s="107"/>
+      <c r="D13" s="79"/>
+      <c r="E13" s="35">
         <v>1</v>
       </c>
-      <c r="F13" s="39">
+      <c r="F13" s="35">
         <v>1</v>
       </c>
-      <c r="G13" s="53" t="s">
-        <v>86</v>
+      <c r="G13" s="6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="2:19">
-      <c r="B14" s="125" t="s">
+      <c r="B14" s="102" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="126"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="39">
+      <c r="C14" s="103"/>
+      <c r="D14" s="79"/>
+      <c r="E14" s="35">
         <v>1</v>
       </c>
-      <c r="F14" s="39">
+      <c r="F14" s="35">
         <v>1</v>
       </c>
-      <c r="G14" s="53" t="s">
-        <v>86</v>
-      </c>
-      <c r="R14" s="73"/>
-      <c r="S14" s="74"/>
+      <c r="G14" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="R14" s="58"/>
+      <c r="S14" s="59"/>
     </row>
     <row r="15" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B15" s="131" t="s">
+      <c r="B15" s="104" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="132"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="40">
+      <c r="C15" s="105"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="36">
         <v>1</v>
       </c>
-      <c r="F15" s="40">
+      <c r="F15" s="36">
         <v>1</v>
       </c>
-      <c r="G15" s="53" t="s">
-        <v>86</v>
+      <c r="G15" s="6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="16" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B16" s="94" t="s">
+      <c r="B16" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="C16" s="122"/>
-      <c r="D16" s="11" t="s">
+      <c r="C16" s="113"/>
+      <c r="D16" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="79">
+      <c r="E16" s="40">
         <f>SUM(E17:E25)</f>
         <v>16</v>
       </c>
-      <c r="F16" s="46">
+      <c r="F16" s="40">
         <v>8</v>
       </c>
-      <c r="G16" s="48" t="s">
-        <v>86</v>
+      <c r="G16" s="10" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="96" t="s">
+      <c r="B17" s="85" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="124"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="78">
+      <c r="C17" s="111"/>
+      <c r="D17" s="155"/>
+      <c r="E17" s="39">
         <v>3</v>
       </c>
-      <c r="F17" s="43">
+      <c r="F17" s="39">
         <v>1</v>
       </c>
-      <c r="G17" s="54" t="s">
-        <v>86</v>
+      <c r="G17" s="9" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="98" t="s">
+      <c r="B18" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="116"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="70">
+      <c r="C18" s="112"/>
+      <c r="D18" s="79"/>
+      <c r="E18" s="35">
         <v>3</v>
       </c>
-      <c r="F18" s="39">
+      <c r="F18" s="35">
         <v>1</v>
       </c>
-      <c r="G18" s="53" t="s">
-        <v>86</v>
+      <c r="G18" s="6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="89" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="116"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="70">
+      <c r="C19" s="112"/>
+      <c r="D19" s="79"/>
+      <c r="E19" s="35">
         <v>3</v>
       </c>
-      <c r="F19" s="39">
+      <c r="F19" s="35">
         <v>1</v>
       </c>
-      <c r="G19" s="53" t="s">
-        <v>86</v>
+      <c r="G19" s="6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="98" t="s">
+      <c r="B20" s="89" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="116"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="70">
+      <c r="C20" s="112"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="35">
         <v>3</v>
       </c>
-      <c r="F20" s="39">
+      <c r="F20" s="35">
         <v>1</v>
       </c>
-      <c r="G20" s="53" t="s">
-        <v>86</v>
+      <c r="G20" s="6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="98" t="s">
+      <c r="B21" s="89" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="116"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="71">
+      <c r="C21" s="112"/>
+      <c r="D21" s="79"/>
+      <c r="E21" s="68">
         <v>1</v>
       </c>
-      <c r="F21" s="39">
+      <c r="F21" s="35">
         <v>1</v>
       </c>
-      <c r="G21" s="53" t="s">
-        <v>86</v>
+      <c r="G21" s="6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="106" t="s">
+      <c r="B22" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="119"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="70"/>
-      <c r="F22" s="39">
+      <c r="C22" s="116"/>
+      <c r="D22" s="79"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35">
         <v>3</v>
       </c>
-      <c r="G22" s="53" t="s">
-        <v>86</v>
+      <c r="G22" s="6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="117" t="s">
+      <c r="B23" s="106" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="118"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="70">
+      <c r="C23" s="107"/>
+      <c r="D23" s="79"/>
+      <c r="E23" s="35">
         <v>1</v>
       </c>
-      <c r="F23" s="39">
+      <c r="F23" s="35">
         <v>1</v>
       </c>
-      <c r="G23" s="53" t="s">
-        <v>86</v>
+      <c r="G23" s="6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="117" t="s">
+      <c r="B24" s="106" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="118"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="70">
+      <c r="C24" s="107"/>
+      <c r="D24" s="79"/>
+      <c r="E24" s="35">
         <v>1</v>
       </c>
-      <c r="F24" s="39">
+      <c r="F24" s="35">
         <v>1</v>
       </c>
-      <c r="G24" s="53" t="s">
-        <v>86</v>
+      <c r="G24" s="6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B25" s="133" t="s">
+      <c r="B25" s="108" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="134"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="72">
+      <c r="C25" s="109"/>
+      <c r="D25" s="162"/>
+      <c r="E25" s="37">
         <v>1</v>
       </c>
-      <c r="F25" s="41">
+      <c r="F25" s="37">
         <v>1</v>
       </c>
-      <c r="G25" s="53" t="s">
-        <v>86</v>
+      <c r="G25" s="6" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B26" s="94" t="s">
+      <c r="B26" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="122"/>
-      <c r="D26" s="11" t="s">
+      <c r="C26" s="113"/>
+      <c r="D26" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="46">
+      <c r="E26" s="40">
         <f>SUM(E27:E31)</f>
         <v>16</v>
       </c>
-      <c r="F26" s="46">
+      <c r="F26" s="40">
         <f>SUM(F27,F28,F31)</f>
         <v>11</v>
       </c>
-      <c r="G26" s="48" t="s">
-        <v>82</v>
+      <c r="G26" s="10" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="120" t="s">
+      <c r="B27" s="117" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" s="118"/>
+      <c r="D27" s="155"/>
+      <c r="E27" s="39">
+        <v>5</v>
+      </c>
+      <c r="F27" s="39">
+        <v>5</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7">
+      <c r="B28" s="94" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="121"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="43">
-        <v>5</v>
-      </c>
-      <c r="F27" s="43">
-        <v>5</v>
-      </c>
-      <c r="G27" s="54" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7">
-      <c r="B28" s="106" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" s="119"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="39">
+      <c r="C28" s="116"/>
+      <c r="D28" s="79"/>
+      <c r="E28" s="35">
         <f>SUM(E29:E30)</f>
         <v>4</v>
       </c>
-      <c r="F28" s="39">
+      <c r="F28" s="35">
         <f>SUM(F29:F30)</f>
         <v>3</v>
       </c>
-      <c r="G28" s="54" t="s">
-        <v>86</v>
+      <c r="G28" s="9" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="117" t="s">
+      <c r="B29" s="106" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="107"/>
+      <c r="D29" s="79"/>
+      <c r="E29" s="35">
+        <v>2</v>
+      </c>
+      <c r="F29" s="35">
+        <v>2</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7">
+      <c r="B30" s="106" t="s">
         <v>53</v>
       </c>
-      <c r="C29" s="118"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="39">
+      <c r="C30" s="107"/>
+      <c r="D30" s="79"/>
+      <c r="E30" s="35">
         <v>2</v>
       </c>
-      <c r="F29" s="39">
+      <c r="F30" s="35">
+        <v>1</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B31" s="87" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="110"/>
+      <c r="D31" s="80"/>
+      <c r="E31" s="36">
+        <v>3</v>
+      </c>
+      <c r="F31" s="36">
+        <v>3</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B32" s="83" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" s="113"/>
+      <c r="D32" s="76" t="s">
+        <v>14</v>
+      </c>
+      <c r="E32" s="40">
+        <f>SUM(E33:E41)</f>
+        <v>11</v>
+      </c>
+      <c r="F32" s="40">
+        <f>SUM(F34,F36,F37,F40,F41)</f>
+        <v>5</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="85" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="111"/>
+      <c r="D33" s="155"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="102" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" s="103"/>
+      <c r="D34" s="155"/>
+      <c r="E34" s="39">
         <v>2</v>
       </c>
-      <c r="G29" s="54" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7">
-      <c r="B30" s="117" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="118"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="39">
+      <c r="F34" s="39">
+        <v>1</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="B35" s="100" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="114"/>
+      <c r="D35" s="79"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="89" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="112"/>
+      <c r="D36" s="79"/>
+      <c r="E36" s="35">
         <v>2</v>
       </c>
-      <c r="F30" s="39">
+      <c r="F36" s="35">
         <v>1</v>
       </c>
-      <c r="G30" s="54" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B31" s="100" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="135"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="40">
+      <c r="G36" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="89" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" s="112"/>
+      <c r="D37" s="79"/>
+      <c r="E37" s="35">
+        <v>2</v>
+      </c>
+      <c r="F37" s="35">
+        <v>1</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="89" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" s="112"/>
+      <c r="D38" s="79"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="6"/>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" s="100" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="114"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="35"/>
+      <c r="G39" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7">
+      <c r="B40" s="161" t="s">
+        <v>60</v>
+      </c>
+      <c r="C40" s="160"/>
+      <c r="D40" s="156"/>
+      <c r="E40" s="35">
+        <v>2</v>
+      </c>
+      <c r="F40" s="35">
+        <v>1</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7">
+      <c r="B41" s="94" t="s">
+        <v>61</v>
+      </c>
+      <c r="C41" s="144"/>
+      <c r="D41" s="156"/>
+      <c r="E41" s="35">
         <v>3</v>
       </c>
-      <c r="F31" s="40">
-        <v>3</v>
-      </c>
-      <c r="G31" s="54" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B32" s="94" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32" s="122"/>
-      <c r="D32" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E32" s="45">
-        <f>SUM(E33:E40)</f>
-        <v>11</v>
-      </c>
-      <c r="F32" s="79">
-        <f>SUM(F34,F36,F37,F39,F40)</f>
-        <v>5</v>
-      </c>
-      <c r="G32" s="11" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="96" t="s">
-        <v>59</v>
-      </c>
-      <c r="C33" s="124"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="47"/>
-      <c r="F33" s="78"/>
-      <c r="G33" s="10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7">
-      <c r="B34" s="125" t="s">
-        <v>56</v>
-      </c>
-      <c r="C34" s="126"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="47">
-        <v>2</v>
-      </c>
-      <c r="F34" s="78">
+      <c r="F41" s="35">
         <v>1</v>
       </c>
-      <c r="G34" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="114" t="s">
-        <v>4</v>
-      </c>
-      <c r="C35" s="136"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="38"/>
-      <c r="F35" s="70"/>
-      <c r="G35" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="98" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" s="116"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="38">
-        <v>2</v>
-      </c>
-      <c r="F36" s="70">
-        <v>1</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7">
-      <c r="B37" s="98" t="s">
-        <v>58</v>
-      </c>
-      <c r="C37" s="116"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="38">
-        <v>2</v>
-      </c>
-      <c r="F37" s="70">
-        <v>1</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7">
-      <c r="B38" s="114" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="136"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="38"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7">
-      <c r="B39" s="110" t="s">
-        <v>61</v>
-      </c>
-      <c r="C39" s="137"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="38">
-        <v>2</v>
-      </c>
-      <c r="F39" s="70">
-        <v>1</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B40" s="129" t="s">
-        <v>62</v>
-      </c>
-      <c r="C40" s="130"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="44">
-        <v>3</v>
-      </c>
-      <c r="F40" s="72">
-        <v>1</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B41" s="127" t="s">
+      <c r="G41" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C41" s="128"/>
-      <c r="D41" s="49"/>
-      <c r="E41" s="68">
+    </row>
+    <row r="42" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B42" s="128" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" s="163"/>
+      <c r="D42" s="78"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="8"/>
+    </row>
+    <row r="43" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B43" s="98" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" s="164"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="40">
         <f>SUM(E3+E16+E26+F32)</f>
         <v>58</v>
       </c>
-      <c r="F41" s="69">
+      <c r="F43" s="40">
         <f>SUM(F3+F16+F26+F32)</f>
         <v>47</v>
       </c>
-      <c r="G41" s="49" t="s">
-        <v>86</v>
+      <c r="G43" s="10" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B35:C35"/>
+  <mergeCells count="42">
     <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B42:C42"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="B28:C28"/>
@@ -2799,6 +2899,33 @@
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2808,7 +2935,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DBF476-724A-4DAE-8D66-8B0809F96B84}">
-  <dimension ref="B1:K23"/>
+  <dimension ref="B1:M28"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="3" max="3" width="18.125" customWidth="1"/>
@@ -2816,400 +2943,506 @@
     <col min="10" max="10" width="11.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="19.5" thickBot="1"/>
-    <row r="2" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B2" s="102" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="103"/>
-      <c r="D2" s="11" t="s">
+    <row r="1" spans="2:13" ht="19.5" thickBot="1"/>
+    <row r="2" spans="2:13" ht="19.5" thickBot="1">
+      <c r="B2" s="81" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="82"/>
+      <c r="D2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="48" t="s">
+      <c r="F2" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="I2" s="61" t="s">
-        <v>76</v>
-      </c>
-      <c r="J2" s="64">
+      <c r="G2" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="I2" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="J2" s="53">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
-      </c>
-      <c r="K2" s="48" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B3" s="94" t="s">
+        <v>46303</v>
+      </c>
+      <c r="K2" s="41" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" ht="19.5" thickBot="1">
+      <c r="B3" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="95"/>
-      <c r="D3" s="11" t="s">
+      <c r="C3" s="84"/>
+      <c r="D3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="46">
+      <c r="E3" s="40">
         <f>SUM(E4:E7)</f>
         <v>8</v>
       </c>
-      <c r="F3" s="46">
+      <c r="F3" s="64">
         <f>SUM(F4:F7)</f>
         <v>9</v>
       </c>
-      <c r="G3" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="I3" s="83" t="s">
-        <v>78</v>
-      </c>
-      <c r="J3" s="63">
+      <c r="G3" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I3" s="67" t="s">
+        <v>76</v>
+      </c>
+      <c r="J3" s="52">
         <v>46305</v>
       </c>
-      <c r="K3" s="59" t="str">
+      <c r="K3" s="48" t="str">
         <f ca="1">SUM($J3-J2)&amp; "日"</f>
-        <v>3日</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B4" s="96" t="s">
+        <v>2日</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" ht="19.5" thickBot="1">
+      <c r="B4" s="85" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="86"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="38">
+        <v>2</v>
+      </c>
+      <c r="F4" s="149">
+        <v>2</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I4" s="72" t="s">
+        <v>73</v>
+      </c>
+      <c r="J4" s="73">
+        <v>46314</v>
+      </c>
+      <c r="K4" s="74" t="str">
+        <f ca="1">SUM(J4-J2)&amp; "日"</f>
+        <v>11日</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13">
+      <c r="B5" s="91" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="92"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="35">
+        <v>2</v>
+      </c>
+      <c r="F5" s="57">
+        <v>2</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="59"/>
+    </row>
+    <row r="6" spans="2:13">
+      <c r="B6" s="89" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="97"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="42">
+      <c r="C6" s="90"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="35">
         <v>2</v>
       </c>
-      <c r="F4" s="42">
+      <c r="F6" s="57">
+        <v>5</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="58"/>
+      <c r="K6" s="59"/>
+    </row>
+    <row r="7" spans="2:13">
+      <c r="B7" s="87" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="88"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="36">
         <v>2</v>
       </c>
-      <c r="G4" s="54" t="s">
-        <v>86</v>
-      </c>
-      <c r="I4" s="88" t="s">
-        <v>75</v>
-      </c>
-      <c r="J4" s="89">
-        <v>46314</v>
-      </c>
-      <c r="K4" s="90" t="str">
-        <f ca="1">SUM(J4-J2)&amp; "日"</f>
-        <v>12日</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11">
-      <c r="B5" s="104" t="s">
+      <c r="F7" s="150"/>
+      <c r="G7" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="I7" s="93" t="s">
+        <v>88</v>
+      </c>
+      <c r="J7" s="93"/>
+      <c r="K7" s="93"/>
+      <c r="L7" s="93"/>
+      <c r="M7" s="93"/>
+    </row>
+    <row r="8" spans="2:13">
+      <c r="B8" s="145" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="105"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="39">
+      <c r="C8" s="147"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="35">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="57"/>
+      <c r="G8" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13">
+      <c r="B9" s="145" t="s">
+        <v>90</v>
+      </c>
+      <c r="C9" s="147"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="35">
+        <v>0.5</v>
+      </c>
+      <c r="F9" s="57"/>
+      <c r="G9" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13">
+      <c r="B10" s="145" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="147"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="35">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="57"/>
+      <c r="G10" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" ht="19.5" thickBot="1">
+      <c r="B11" s="152" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="153"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="36">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="150"/>
+      <c r="G11" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" ht="19.5" thickBot="1">
+      <c r="B12" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="84"/>
+      <c r="D12" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="40">
+        <f>SUM(E13:E16)</f>
+        <v>11</v>
+      </c>
+      <c r="F12" s="64">
+        <f>SUM(F13:F16)</f>
+        <v>3</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13">
+      <c r="B13" s="85" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="86"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="39">
         <v>2</v>
       </c>
-      <c r="F5" s="39">
+      <c r="F13" s="63">
+        <v>1</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13">
+      <c r="B14" s="89" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" s="112"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="39">
+        <v>4</v>
+      </c>
+      <c r="F14" s="63"/>
+      <c r="G14" s="9" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13">
+      <c r="B15" s="89" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="90"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="35">
+        <v>3</v>
+      </c>
+      <c r="F15" s="57">
         <v>2</v>
       </c>
-      <c r="G5" s="54" t="s">
-        <v>86</v>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="73"/>
-      <c r="K5" s="74"/>
-    </row>
-    <row r="6" spans="2:11">
-      <c r="B6" s="98" t="s">
+      <c r="G15" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13">
+      <c r="B16" s="94" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="95"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="35">
+        <v>2</v>
+      </c>
+      <c r="F16" s="57"/>
+      <c r="G16" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="154" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="151"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="35">
+        <v>1</v>
+      </c>
+      <c r="F17" s="57"/>
+      <c r="G17" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B18" s="157" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18" s="158"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="36">
+        <v>1</v>
+      </c>
+      <c r="F18" s="150"/>
+      <c r="G18" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B19" s="83" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="84"/>
+      <c r="D19" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="40">
+        <f>SUM(E20:E21)</f>
+        <v>3</v>
+      </c>
+      <c r="F19" s="64">
+        <f>SUM(F20:F21)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="94" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="95"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="35">
+        <v>1</v>
+      </c>
+      <c r="F20" s="57"/>
+      <c r="G20" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B21" s="96" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" s="97"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="36">
+        <v>2</v>
+      </c>
+      <c r="F21" s="150"/>
+      <c r="G21" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B22" s="83" t="s">
+        <v>59</v>
+      </c>
+      <c r="C22" s="84"/>
+      <c r="D22" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="40">
+        <f>SUM(E23+E25+E27)</f>
+        <v>9</v>
+      </c>
+      <c r="F22" s="64">
+        <f>SUM(F23+F25+F27)</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" s="85" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="86"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="39">
+        <v>5</v>
+      </c>
+      <c r="F23" s="63"/>
+      <c r="G23" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7">
+      <c r="B24" s="100" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="101"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7">
+      <c r="B25" s="89" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="99"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="39">
+      <c r="C25" s="90"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="35">
         <v>2</v>
       </c>
-      <c r="F6" s="39">
+      <c r="F25" s="57"/>
+      <c r="G25" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7">
+      <c r="B26" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="54" t="s">
-        <v>86</v>
-      </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="73"/>
-      <c r="K6" s="74"/>
-    </row>
-    <row r="7" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B7" s="100" t="s">
-        <v>69</v>
-      </c>
-      <c r="C7" s="101"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="40">
+      <c r="C26" s="101"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B27" s="146" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="148"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="37">
         <v>2</v>
       </c>
-      <c r="F7" s="40"/>
-      <c r="G7" s="85" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B8" s="94" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="95"/>
-      <c r="D8" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="46">
-        <f>SUM(E9:E11)</f>
-        <v>7</v>
-      </c>
-      <c r="F8" s="46">
-        <f>SUM(F9:F11)</f>
-        <v>3</v>
-      </c>
-      <c r="G8" s="48" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11">
-      <c r="B9" s="96" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="97"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="43">
-        <v>2</v>
-      </c>
-      <c r="F9" s="43">
-        <v>1</v>
-      </c>
-      <c r="G9" s="54" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11">
-      <c r="B10" s="98" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="99"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="39">
-        <v>3</v>
-      </c>
-      <c r="F10" s="39">
-        <v>2</v>
-      </c>
-      <c r="G10" s="54" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B11" s="100" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" s="101"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="40">
-        <v>2</v>
-      </c>
-      <c r="F11" s="40"/>
-      <c r="G11" s="85" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B12" s="94" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="95"/>
-      <c r="D12" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="46">
-        <f>SUM(E13:E14)</f>
-        <v>3</v>
-      </c>
-      <c r="F12" s="46">
-        <f>SUM(F13:F14)</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="48" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11">
-      <c r="B13" s="106" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" s="107"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="39">
-        <v>1</v>
-      </c>
-      <c r="F13" s="39"/>
-      <c r="G13" s="53" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B14" s="108" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" s="109"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="40">
-        <v>2</v>
-      </c>
-      <c r="F14" s="40"/>
-      <c r="G14" s="75" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B15" s="94" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="95"/>
-      <c r="D15" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E15" s="46">
-        <f>SUM(E16+E18+E20)</f>
-        <v>9</v>
-      </c>
-      <c r="F15" s="46">
-        <f>SUM(F16+F18+F20)</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="48" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11">
-      <c r="B16" s="96" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="97"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="43">
-        <v>5</v>
-      </c>
-      <c r="F16" s="43"/>
-      <c r="G16" s="53" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="114" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" s="115"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="53" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="98" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="99"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="39">
-        <v>2</v>
-      </c>
-      <c r="F18" s="39"/>
-      <c r="G18" s="53" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="114" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" s="115"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="53" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B20" s="110" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="111"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="41">
-        <v>2</v>
-      </c>
-      <c r="F20" s="39"/>
-      <c r="G20" s="92" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B21" s="112" t="s">
+      <c r="F27" s="57"/>
+      <c r="G27" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B28" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="113"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="45">
-        <f>SUM(E3+E8+E12+E15)</f>
-        <v>27</v>
-      </c>
-      <c r="F21" s="46">
-        <f>SUM(F3+F8+F12+F15)</f>
+      <c r="C28" s="99"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="40">
+        <f>SUM(E3+E12+E19+E22)</f>
+        <v>31</v>
+      </c>
+      <c r="F28" s="64">
+        <f>SUM(F3+F12+F19+F22)</f>
         <v>12</v>
       </c>
-      <c r="G21" s="81"/>
-    </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="93" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" s="93"/>
-      <c r="D23" s="93"/>
-      <c r="E23" s="93"/>
-      <c r="F23" s="93"/>
+      <c r="G28" s="159"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="28">
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="I7:M7"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="E12 E3" formulaRange="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF80DA5A-1B69-4377-A99E-364B8197EABC}">
-  <dimension ref="B1:L19"/>
+  <dimension ref="B1:L21"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="8" max="8" width="17.25" bestFit="1" customWidth="1"/>
@@ -3221,349 +3454,379 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B2" s="138" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" s="139"/>
-      <c r="D2" s="11" t="s">
+      <c r="B2" s="130" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="131"/>
+      <c r="D2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="48" t="s">
+      <c r="F2" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="48" t="s">
-        <v>81</v>
+      <c r="G2" s="41" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B3" s="140" t="s">
+      <c r="B3" s="125" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="141"/>
-      <c r="D3" s="11" t="s">
+      <c r="C3" s="126"/>
+      <c r="D3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="46">
+      <c r="E3" s="40">
         <f>SUM(E4)</f>
         <v>3</v>
       </c>
-      <c r="F3" s="80">
+      <c r="F3" s="65">
         <f>SUM(F4)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="J3" s="61" t="s">
-        <v>76</v>
-      </c>
-      <c r="K3" s="64">
+      <c r="G3" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="J3" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="K3" s="53">
         <f ca="1">TODAY()</f>
-        <v>46302</v>
-      </c>
-      <c r="L3" s="48" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B4" s="142" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="143"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="84">
+        <v>46303</v>
+      </c>
+      <c r="L3" s="41" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12">
+      <c r="B4" s="136" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="137"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="139">
         <v>3</v>
       </c>
-      <c r="F4" s="80">
-        <f>SUM(F5)</f>
+      <c r="F4" s="135">
+        <f>SUM(F6)</f>
         <v>0</v>
       </c>
-      <c r="G4" s="85" t="s">
-        <v>82</v>
-      </c>
-      <c r="J4" s="65" t="s">
-        <v>79</v>
-      </c>
-      <c r="K4" s="62">
+      <c r="G4" s="140" t="s">
+        <v>80</v>
+      </c>
+      <c r="J4" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" s="51">
         <v>46310</v>
       </c>
-      <c r="L4" s="58" t="str">
+      <c r="L4" s="47" t="str">
         <f ca="1">SUM($L4-I1)&amp; "日"</f>
         <v>15日</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B5" s="140" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="141"/>
-      <c r="D5" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="46">
-        <f>SUM(E6)</f>
+      <c r="B5" s="87" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="110"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="36">
         <v>3</v>
       </c>
-      <c r="F5" s="80">
-        <f t="shared" ref="F5:F6" si="0">SUM(F6)</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="48" t="s">
-        <v>82</v>
-      </c>
-      <c r="J5" s="66" t="s">
-        <v>80</v>
-      </c>
-      <c r="K5" s="62">
+      <c r="F5" s="71"/>
+      <c r="G5" s="60"/>
+      <c r="J5" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="K5" s="51">
         <v>46313</v>
       </c>
-      <c r="L5" s="58" t="str">
+      <c r="L5" s="47" t="str">
         <f ca="1">SUM($L5-I1)&amp; "日"</f>
         <v>18日</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B6" s="142" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" s="143"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="84">
+      <c r="B6" s="125" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="126"/>
+      <c r="D6" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="40">
+        <f>SUM(E7)</f>
         <v>3</v>
       </c>
-      <c r="F6" s="80">
-        <f t="shared" si="0"/>
+      <c r="F6" s="65">
+        <f t="shared" ref="F6" si="0">SUM(F7)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="85" t="s">
-        <v>82</v>
-      </c>
-      <c r="J6" s="67" t="s">
-        <v>75</v>
-      </c>
-      <c r="K6" s="63">
+      <c r="G6" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="J6" s="56" t="s">
+        <v>73</v>
+      </c>
+      <c r="K6" s="52">
         <v>46314</v>
       </c>
-      <c r="L6" s="59" t="str">
+      <c r="L6" s="48" t="str">
         <f ca="1">SUM(K6-K3)&amp; "日"</f>
-        <v>12日</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B7" s="140" t="s">
+        <v>11日</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12">
+      <c r="B7" s="123" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="124"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="68">
+        <v>3</v>
+      </c>
+      <c r="F7" s="135">
+        <f>SUM(F9)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="69" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B8" s="87" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="110"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="36">
+        <v>3</v>
+      </c>
+      <c r="F8" s="71"/>
+      <c r="G8" s="60"/>
+      <c r="J8" s="142"/>
+      <c r="K8" s="133"/>
+      <c r="L8" s="134"/>
+    </row>
+    <row r="9" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B9" s="125" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="141"/>
-      <c r="D7" s="11" t="s">
+      <c r="C9" s="126"/>
+      <c r="D9" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="46">
-        <f>SUM(E8:E9)</f>
+      <c r="E9" s="40">
+        <f>SUM(E10:E11)</f>
         <v>5</v>
       </c>
-      <c r="F7" s="80">
-        <f>SUM(F8:F9)</f>
+      <c r="F9" s="65">
+        <f>SUM(F10:F11)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="48" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12">
-      <c r="B8" s="120" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" s="144"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="43">
+      <c r="G9" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="141"/>
+    </row>
+    <row r="10" spans="2:12">
+      <c r="B10" s="117" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="127"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="39">
         <v>3</v>
       </c>
-      <c r="F8" s="60"/>
-      <c r="G8" s="54" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B9" s="145" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="146"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="40">
+      <c r="F10" s="49"/>
+      <c r="G10" s="45" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B11" s="128" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="129"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="36">
         <v>2</v>
       </c>
-      <c r="F9" s="87"/>
-      <c r="G9" s="75" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B10" s="140" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" s="141"/>
-      <c r="D10" s="11" t="s">
+      <c r="F11" s="71"/>
+      <c r="G11" s="60" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B12" s="125" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="126"/>
+      <c r="D12" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="46">
-        <f>SUM(E11)</f>
+      <c r="E12" s="40">
+        <f>SUM(E13)</f>
         <v>2</v>
       </c>
-      <c r="F10" s="80">
-        <f>SUM(F12+F15)</f>
+      <c r="F12" s="65">
+        <f>SUM(F14+F17)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="48" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B11" s="142" t="s">
-        <v>73</v>
-      </c>
-      <c r="C11" s="143"/>
-      <c r="D11" s="82"/>
-      <c r="E11" s="84">
+      <c r="G12" s="41" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B13" s="123" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="124"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="68">
         <v>2</v>
       </c>
-      <c r="F11" s="86"/>
-      <c r="G11" s="85" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B12" s="140" t="s">
+      <c r="F13" s="70"/>
+      <c r="G13" s="69" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B14" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="C12" s="141"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="46">
-        <f>SUM(E13:E14)</f>
+      <c r="C14" s="126"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="40">
+        <f>SUM(E15:E16)</f>
         <v>2</v>
       </c>
-      <c r="F12" s="80">
-        <f>SUM(F13:F14)</f>
+      <c r="F14" s="65">
+        <f>SUM(F15:F16)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="48" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12">
-      <c r="B13" s="120" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" s="144"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="43">
+      <c r="G14" s="41" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="B15" s="117" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="127"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="39">
         <v>1</v>
       </c>
-      <c r="F13" s="60"/>
-      <c r="G13" s="54" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B14" s="145" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="146"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="40">
+      <c r="F15" s="49"/>
+      <c r="G15" s="45" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B16" s="128" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="129"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="36">
         <v>1</v>
       </c>
-      <c r="F14" s="87"/>
-      <c r="G14" s="75" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B15" s="140" t="s">
+      <c r="F16" s="71"/>
+      <c r="G16" s="60" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B17" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="141"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="46">
-        <f>SUM(E16:E17)</f>
+      <c r="C17" s="126"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="40">
+        <f>SUM(E18:E19)</f>
         <v>2</v>
       </c>
-      <c r="F15" s="80">
-        <f>SUM(F16:F17)</f>
+      <c r="F17" s="65">
+        <f>SUM(F18:F19)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="48" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12">
-      <c r="B16" s="120" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" s="144"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="43">
+      <c r="G17" s="41" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="117" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="127"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="39">
         <v>1</v>
       </c>
-      <c r="F16" s="60"/>
-      <c r="G16" s="54" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B17" s="147" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="148"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="41">
+      <c r="F18" s="49"/>
+      <c r="G18" s="45" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B19" s="119" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="120"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="37">
         <v>1</v>
       </c>
-      <c r="F17" s="59"/>
-      <c r="G17" s="75" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B18" s="149" t="s">
+      <c r="F19" s="48"/>
+      <c r="G19" s="60" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B20" s="121" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="150"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="46">
-        <f>SUM(E3+E5+E7+E10+E12+E15)</f>
+      <c r="C20" s="122"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="40">
+        <f>SUM(E3+E6+E9+E12+E14+E17)</f>
         <v>17</v>
       </c>
-      <c r="F18" s="46">
-        <f>SUM(F3+F5+F7+F10+F12+F15)</f>
+      <c r="F20" s="40">
+        <f>SUM(F3+F6+F9+F12+F14+F17)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="11"/>
-    </row>
-    <row r="19" spans="2:7">
-      <c r="G19" s="4"/>
+      <c r="G20" s="10"/>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="G21" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="B17:C17"/>
+  <mergeCells count="19">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B6:C6"/>
     <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B17:C17"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3576,34 +3839,34 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="151" t="s">
+      <c r="C1" s="132" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
-      <c r="F1" s="151"/>
-      <c r="G1" s="151"/>
+      <c r="D1" s="132"/>
+      <c r="E1" s="132"/>
+      <c r="F1" s="132"/>
+      <c r="G1" s="132"/>
     </row>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="31" t="s">
+      <c r="F2" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="32" t="s">
+      <c r="H2" s="29" t="s">
         <v>21</v>
       </c>
       <c r="J2" t="s">
@@ -3611,147 +3874,147 @@
       </c>
     </row>
     <row r="3" spans="2:11">
-      <c r="B3" s="27"/>
-      <c r="D3" s="28">
+      <c r="B3" s="24"/>
+      <c r="D3" s="25">
         <v>46266</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="25">
         <f>SUM(D3)+1</f>
         <v>46267</v>
       </c>
-      <c r="F3" s="28">
+      <c r="F3" s="25">
         <f t="shared" ref="F3:H3" si="0">SUM(E3)+1</f>
         <v>46268</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="25">
         <f t="shared" si="0"/>
         <v>46269</v>
       </c>
-      <c r="H3" s="29">
+      <c r="H3" s="26">
         <f t="shared" si="0"/>
         <v>46270</v>
       </c>
-      <c r="J3" s="15"/>
+      <c r="J3" s="14"/>
       <c r="K3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="19">
+      <c r="B4" s="18">
         <f>SUM(H3)+1</f>
         <v>46271</v>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="17">
         <f>SUM(B4)+1</f>
         <v>46272</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="17">
         <f t="shared" ref="D4:H4" si="1">SUM(C4)+1</f>
         <v>46273</v>
       </c>
-      <c r="E4" s="50">
+      <c r="E4" s="42">
         <f t="shared" si="1"/>
         <v>46274</v>
       </c>
-      <c r="F4" s="50">
+      <c r="F4" s="42">
         <f t="shared" si="1"/>
         <v>46275</v>
       </c>
-      <c r="G4" s="50">
+      <c r="G4" s="42">
         <f t="shared" si="1"/>
         <v>46276</v>
       </c>
-      <c r="H4" s="51">
+      <c r="H4" s="43">
         <f t="shared" si="1"/>
         <v>46277</v>
       </c>
-      <c r="J4" s="16"/>
+      <c r="J4" s="15"/>
       <c r="K4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="52">
+      <c r="B5" s="44">
         <f>SUM(H4)+1</f>
         <v>46278</v>
       </c>
-      <c r="C5" s="50">
+      <c r="C5" s="42">
         <f>SUM(B5)+1</f>
         <v>46279</v>
       </c>
-      <c r="D5" s="50">
+      <c r="D5" s="42">
         <f t="shared" ref="D5:H5" si="2">SUM(C5)+1</f>
         <v>46280</v>
       </c>
-      <c r="E5" s="50">
+      <c r="E5" s="42">
         <f t="shared" si="2"/>
         <v>46281</v>
       </c>
-      <c r="F5" s="50">
+      <c r="F5" s="42">
         <f t="shared" si="2"/>
         <v>46282</v>
       </c>
-      <c r="G5" s="50">
+      <c r="G5" s="42">
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="H5" s="51">
+      <c r="H5" s="43">
         <f t="shared" si="2"/>
         <v>46284</v>
       </c>
-      <c r="J5" s="17"/>
+      <c r="J5" s="16"/>
       <c r="K5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" s="52">
+      <c r="B6" s="44">
         <f>SUM(H5)+1</f>
         <v>46285</v>
       </c>
-      <c r="C6" s="50">
+      <c r="C6" s="42">
         <f>SUM(B6)+1</f>
         <v>46286</v>
       </c>
-      <c r="D6" s="50">
+      <c r="D6" s="42">
         <f t="shared" ref="D6:H6" si="3">SUM(C6)+1</f>
         <v>46287</v>
       </c>
-      <c r="E6" s="50">
+      <c r="E6" s="42">
         <f t="shared" si="3"/>
         <v>46288</v>
       </c>
-      <c r="F6" s="50">
+      <c r="F6" s="42">
         <f t="shared" si="3"/>
         <v>46289</v>
       </c>
-      <c r="G6" s="50">
+      <c r="G6" s="42">
         <f t="shared" si="3"/>
         <v>46290</v>
       </c>
-      <c r="H6" s="51">
+      <c r="H6" s="43">
         <f t="shared" si="3"/>
         <v>46291</v>
       </c>
-      <c r="J6" s="25"/>
+      <c r="J6" s="23"/>
       <c r="K6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B7" s="76">
+      <c r="B7" s="61">
         <f>SUM(H6)+1</f>
         <v>46292</v>
       </c>
-      <c r="C7" s="77">
+      <c r="C7" s="62">
         <f>SUM(B7)+1</f>
         <v>46293</v>
       </c>
-      <c r="D7" s="77">
+      <c r="D7" s="62">
         <f t="shared" ref="D7:E7" si="4">SUM(C7)+1</f>
         <v>46294</v>
       </c>
-      <c r="E7" s="77">
+      <c r="E7" s="62">
         <f t="shared" si="4"/>
         <v>46295</v>
       </c>
@@ -3760,139 +4023,139 @@
       <c r="H7" s="2"/>
     </row>
     <row r="8" spans="2:11">
-      <c r="B8" s="27"/>
+      <c r="B8" s="24"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="33">
+      <c r="F8" s="30">
         <f>SUM(E7)+1</f>
         <v>46296</v>
       </c>
-      <c r="G8" s="33">
+      <c r="G8" s="30">
         <f>SUM(F8)+1</f>
         <v>46297</v>
       </c>
-      <c r="H8" s="34">
+      <c r="H8" s="31">
         <f>SUM(G8)+1</f>
         <v>46298</v>
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="20">
+      <c r="B9" s="19">
         <f>SUM(H8)+1</f>
         <v>46299</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="20">
         <f>SUM(B9)+1</f>
         <v>46300</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D9" s="42">
         <f t="shared" ref="D9:H9" si="5">SUM(C9)+1</f>
         <v>46301</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="20">
         <f t="shared" si="5"/>
         <v>46302</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="20">
         <f t="shared" si="5"/>
         <v>46303</v>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="20">
         <f t="shared" si="5"/>
         <v>46304</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="21">
         <f t="shared" si="5"/>
         <v>46305</v>
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="24">
+      <c r="B10" s="19">
         <f t="shared" ref="B10:B12" si="6">SUM(H9)+1</f>
         <v>46306</v>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="20">
         <f>SUM(B10)+1</f>
         <v>46307</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="22">
         <f t="shared" ref="D10:G10" si="7">SUM(C10)+1</f>
         <v>46308</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="22">
         <f t="shared" si="7"/>
         <v>46309</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="22">
         <f t="shared" si="7"/>
         <v>46310</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="22">
         <f t="shared" si="7"/>
         <v>46311</v>
       </c>
-      <c r="H10" s="56">
+      <c r="H10" s="143">
         <f>SUM(G10)+1</f>
         <v>46312</v>
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="55">
+      <c r="B11" s="46">
         <f t="shared" si="6"/>
         <v>46313</v>
       </c>
-      <c r="C11" s="37">
+      <c r="C11" s="34">
         <f>SUM(B11)+1</f>
         <v>46314</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <f t="shared" ref="D11:F11" si="8">SUM(C11)+1</f>
         <v>46315</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="11">
         <f t="shared" si="8"/>
         <v>46316</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="11">
         <f t="shared" si="8"/>
         <v>46317</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="11">
         <f t="shared" ref="G11" si="9">SUM(F11)+1</f>
         <v>46318</v>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="32">
         <f>SUM(G11)+1</f>
         <v>46319</v>
       </c>
     </row>
     <row r="12" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B12" s="36">
+      <c r="B12" s="33">
         <f t="shared" si="6"/>
         <v>46320</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="12">
         <f>SUM(B12)+1</f>
         <v>46321</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="12">
         <f t="shared" ref="D12:H12" si="10">SUM(C12)+1</f>
         <v>46322</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="12">
         <f t="shared" si="10"/>
         <v>46323</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="12">
         <f t="shared" si="10"/>
         <v>46324</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="12">
         <f t="shared" si="10"/>
         <v>46325</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="13">
         <f t="shared" si="10"/>
         <v>46326</v>
       </c>

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ayato Terao\Documents\GitHub\GlassesGame\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B558CF5A-53E3-4113-BEF2-E34EA1F839BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B989A7-A14F-47E5-B29C-0B1CDB8CCAF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="98">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -655,6 +655,17 @@
   </si>
   <si>
     <t>ギミック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポーズ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(寺尾)</t>
+    <rPh sb="1" eb="3">
+      <t>テラオ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1440,7 +1451,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1622,45 +1633,77 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1673,6 +1716,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1685,24 +1734,63 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1712,28 +1800,43 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1746,127 +1849,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2174,10 +2160,10 @@
   <sheetData>
     <row r="1" spans="2:19" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B2" s="81" t="s">
+      <c r="B2" s="116" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="115"/>
+      <c r="C2" s="129"/>
       <c r="D2" s="77" t="s">
         <v>9</v>
       </c>
@@ -2192,10 +2178,10 @@
       </c>
     </row>
     <row r="3" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B3" s="83" t="s">
+      <c r="B3" s="101" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="113"/>
+      <c r="C3" s="128"/>
       <c r="D3" s="77" t="s">
         <v>12</v>
       </c>
@@ -2222,11 +2208,11 @@
       </c>
     </row>
     <row r="4" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B4" s="85" t="s">
+      <c r="B4" s="103" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="111"/>
-      <c r="D4" s="155"/>
+      <c r="C4" s="130"/>
+      <c r="D4" s="89"/>
       <c r="E4" s="39">
         <f>SUM(E5:E7)</f>
         <v>4</v>
@@ -2250,10 +2236,10 @@
       </c>
     </row>
     <row r="5" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B5" s="102" t="s">
+      <c r="B5" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="103"/>
+      <c r="C5" s="131"/>
       <c r="D5" s="79"/>
       <c r="E5" s="35">
         <v>2</v>
@@ -2278,10 +2264,10 @@
       <c r="S5" s="59"/>
     </row>
     <row r="6" spans="2:19">
-      <c r="B6" s="102" t="s">
+      <c r="B6" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="103"/>
+      <c r="C6" s="131"/>
       <c r="D6" s="79"/>
       <c r="E6" s="35">
         <v>1</v>
@@ -2296,10 +2282,10 @@
       <c r="S6" s="59"/>
     </row>
     <row r="7" spans="2:19">
-      <c r="B7" s="102" t="s">
+      <c r="B7" s="92" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="103"/>
+      <c r="C7" s="131"/>
       <c r="D7" s="79"/>
       <c r="E7" s="35">
         <v>1</v>
@@ -2314,10 +2300,10 @@
       <c r="S7" s="59"/>
     </row>
     <row r="8" spans="2:19">
-      <c r="B8" s="89" t="s">
+      <c r="B8" s="98" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="112"/>
+      <c r="C8" s="99"/>
       <c r="D8" s="79"/>
       <c r="E8" s="35">
         <v>2</v>
@@ -2330,10 +2316,10 @@
       </c>
     </row>
     <row r="9" spans="2:19">
-      <c r="B9" s="89" t="s">
+      <c r="B9" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="112"/>
+      <c r="C9" s="99"/>
       <c r="D9" s="80"/>
       <c r="E9" s="36">
         <v>2</v>
@@ -2346,10 +2332,10 @@
       </c>
     </row>
     <row r="10" spans="2:19">
-      <c r="B10" s="89" t="s">
+      <c r="B10" s="98" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="112"/>
+      <c r="C10" s="99"/>
       <c r="D10" s="80"/>
       <c r="E10" s="36">
         <v>2</v>
@@ -2362,10 +2348,10 @@
       </c>
     </row>
     <row r="11" spans="2:19">
-      <c r="B11" s="94" t="s">
+      <c r="B11" s="106" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="116"/>
+      <c r="C11" s="125"/>
       <c r="D11" s="79"/>
       <c r="E11" s="35">
         <v>1</v>
@@ -2378,10 +2364,10 @@
       </c>
     </row>
     <row r="12" spans="2:19">
-      <c r="B12" s="89" t="s">
+      <c r="B12" s="98" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="112"/>
+      <c r="C12" s="99"/>
       <c r="D12" s="79"/>
       <c r="E12" s="35">
         <f>SUM(E13:E15)</f>
@@ -2396,10 +2382,10 @@
       </c>
     </row>
     <row r="13" spans="2:19">
-      <c r="B13" s="106" t="s">
+      <c r="B13" s="96" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="107"/>
+      <c r="C13" s="124"/>
       <c r="D13" s="79"/>
       <c r="E13" s="35">
         <v>1</v>
@@ -2412,10 +2398,10 @@
       </c>
     </row>
     <row r="14" spans="2:19">
-      <c r="B14" s="102" t="s">
+      <c r="B14" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="103"/>
+      <c r="C14" s="131"/>
       <c r="D14" s="79"/>
       <c r="E14" s="35">
         <v>1</v>
@@ -2430,10 +2416,10 @@
       <c r="S14" s="59"/>
     </row>
     <row r="15" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B15" s="104" t="s">
+      <c r="B15" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="105"/>
+      <c r="C15" s="134"/>
       <c r="D15" s="80"/>
       <c r="E15" s="36">
         <v>1</v>
@@ -2446,10 +2432,10 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B16" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="113"/>
+      <c r="B16" s="101" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="128"/>
       <c r="D16" s="76" t="s">
         <v>11</v>
       </c>
@@ -2465,11 +2451,11 @@
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="85" t="s">
+      <c r="B17" s="103" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="111"/>
-      <c r="D17" s="155"/>
+      <c r="C17" s="130"/>
+      <c r="D17" s="89"/>
       <c r="E17" s="39">
         <v>3</v>
       </c>
@@ -2481,10 +2467,10 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="89" t="s">
+      <c r="B18" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="112"/>
+      <c r="C18" s="99"/>
       <c r="D18" s="79"/>
       <c r="E18" s="35">
         <v>3</v>
@@ -2497,10 +2483,10 @@
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="89" t="s">
+      <c r="B19" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="112"/>
+      <c r="C19" s="99"/>
       <c r="D19" s="79"/>
       <c r="E19" s="35">
         <v>3</v>
@@ -2513,10 +2499,10 @@
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="89" t="s">
+      <c r="B20" s="98" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="112"/>
+      <c r="C20" s="99"/>
       <c r="D20" s="80"/>
       <c r="E20" s="35">
         <v>3</v>
@@ -2529,10 +2515,10 @@
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="89" t="s">
+      <c r="B21" s="98" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="112"/>
+      <c r="C21" s="99"/>
       <c r="D21" s="79"/>
       <c r="E21" s="68">
         <v>1</v>
@@ -2545,10 +2531,10 @@
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="94" t="s">
+      <c r="B22" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="116"/>
+      <c r="C22" s="125"/>
       <c r="D22" s="79"/>
       <c r="E22" s="35"/>
       <c r="F22" s="35">
@@ -2559,10 +2545,10 @@
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="106" t="s">
+      <c r="B23" s="96" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="107"/>
+      <c r="C23" s="124"/>
       <c r="D23" s="79"/>
       <c r="E23" s="35">
         <v>1</v>
@@ -2575,10 +2561,10 @@
       </c>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="106" t="s">
+      <c r="B24" s="96" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="107"/>
+      <c r="C24" s="124"/>
       <c r="D24" s="79"/>
       <c r="E24" s="35">
         <v>1</v>
@@ -2591,11 +2577,11 @@
       </c>
     </row>
     <row r="25" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B25" s="108" t="s">
+      <c r="B25" s="135" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="109"/>
-      <c r="D25" s="162"/>
+      <c r="C25" s="136"/>
+      <c r="D25" s="91"/>
       <c r="E25" s="37">
         <v>1</v>
       </c>
@@ -2607,10 +2593,10 @@
       </c>
     </row>
     <row r="26" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B26" s="83" t="s">
+      <c r="B26" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="113"/>
+      <c r="C26" s="128"/>
       <c r="D26" s="76" t="s">
         <v>10</v>
       </c>
@@ -2623,15 +2609,15 @@
         <v>11</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="117" t="s">
+      <c r="B27" s="126" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="118"/>
-      <c r="D27" s="155"/>
+      <c r="C27" s="127"/>
+      <c r="D27" s="89"/>
       <c r="E27" s="39">
         <v>5</v>
       </c>
@@ -2643,10 +2629,10 @@
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="94" t="s">
+      <c r="B28" s="106" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="116"/>
+      <c r="C28" s="125"/>
       <c r="D28" s="79"/>
       <c r="E28" s="35">
         <f>SUM(E29:E30)</f>
@@ -2661,10 +2647,10 @@
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="106" t="s">
+      <c r="B29" s="96" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="107"/>
+      <c r="C29" s="124"/>
       <c r="D29" s="79"/>
       <c r="E29" s="35">
         <v>2</v>
@@ -2677,10 +2663,10 @@
       </c>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="106" t="s">
+      <c r="B30" s="96" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="107"/>
+      <c r="C30" s="124"/>
       <c r="D30" s="79"/>
       <c r="E30" s="35">
         <v>2</v>
@@ -2693,10 +2679,10 @@
       </c>
     </row>
     <row r="31" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B31" s="87" t="s">
+      <c r="B31" s="118" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="110"/>
+      <c r="C31" s="137"/>
       <c r="D31" s="80"/>
       <c r="E31" s="36">
         <v>3</v>
@@ -2709,16 +2695,16 @@
       </c>
     </row>
     <row r="32" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B32" s="83" t="s">
+      <c r="B32" s="101" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="113"/>
+      <c r="C32" s="128"/>
       <c r="D32" s="76" t="s">
         <v>14</v>
       </c>
       <c r="E32" s="40">
-        <f>SUM(E33:E41)</f>
-        <v>11</v>
+        <f>SUM(E33:E42)</f>
+        <v>13</v>
       </c>
       <c r="F32" s="40">
         <f>SUM(F34,F36,F37,F40,F41)</f>
@@ -2729,11 +2715,11 @@
       </c>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="85" t="s">
+      <c r="B33" s="103" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="111"/>
-      <c r="D33" s="155"/>
+      <c r="C33" s="130"/>
+      <c r="D33" s="89"/>
       <c r="E33" s="39"/>
       <c r="F33" s="39"/>
       <c r="G33" s="9" t="s">
@@ -2741,11 +2727,11 @@
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="102" t="s">
+      <c r="B34" s="92" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="103"/>
-      <c r="D34" s="155"/>
+      <c r="C34" s="131"/>
+      <c r="D34" s="89"/>
       <c r="E34" s="39">
         <v>2</v>
       </c>
@@ -2757,10 +2743,10 @@
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="100" t="s">
+      <c r="B35" s="114" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="114"/>
+      <c r="C35" s="138"/>
       <c r="D35" s="79"/>
       <c r="E35" s="35"/>
       <c r="F35" s="35"/>
@@ -2769,10 +2755,10 @@
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="89" t="s">
+      <c r="B36" s="98" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="112"/>
+      <c r="C36" s="99"/>
       <c r="D36" s="79"/>
       <c r="E36" s="35">
         <v>2</v>
@@ -2785,10 +2771,10 @@
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="89" t="s">
+      <c r="B37" s="98" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="112"/>
+      <c r="C37" s="99"/>
       <c r="D37" s="79"/>
       <c r="E37" s="35">
         <v>2</v>
@@ -2801,20 +2787,26 @@
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="89" t="s">
+      <c r="B38" s="98" t="s">
         <v>93</v>
       </c>
-      <c r="C38" s="112"/>
+      <c r="C38" s="99"/>
       <c r="D38" s="79"/>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35"/>
-      <c r="G38" s="6"/>
+      <c r="E38" s="35">
+        <v>1</v>
+      </c>
+      <c r="F38" s="35">
+        <v>1</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="39" spans="2:7">
-      <c r="B39" s="100" t="s">
+      <c r="B39" s="114" t="s">
         <v>5</v>
       </c>
-      <c r="C39" s="114"/>
+      <c r="C39" s="138"/>
       <c r="D39" s="79"/>
       <c r="E39" s="35"/>
       <c r="F39" s="35"/>
@@ -2823,11 +2815,11 @@
       </c>
     </row>
     <row r="40" spans="2:7">
-      <c r="B40" s="161" t="s">
+      <c r="B40" s="139" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="160"/>
-      <c r="D40" s="156"/>
+      <c r="C40" s="140"/>
+      <c r="D40" s="88"/>
       <c r="E40" s="35">
         <v>2</v>
       </c>
@@ -2839,11 +2831,11 @@
       </c>
     </row>
     <row r="41" spans="2:7">
-      <c r="B41" s="94" t="s">
+      <c r="B41" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="C41" s="144"/>
-      <c r="D41" s="156"/>
+      <c r="C41" s="133"/>
+      <c r="D41" s="88"/>
       <c r="E41" s="35">
         <v>3</v>
       </c>
@@ -2855,20 +2847,26 @@
       </c>
     </row>
     <row r="42" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B42" s="128" t="s">
+      <c r="B42" s="122" t="s">
         <v>93</v>
       </c>
-      <c r="C42" s="163"/>
+      <c r="C42" s="123"/>
       <c r="D42" s="78"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="8"/>
+      <c r="E42" s="36">
+        <v>1</v>
+      </c>
+      <c r="F42" s="36">
+        <v>1</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="43" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B43" s="98" t="s">
+      <c r="B43" s="112" t="s">
         <v>82</v>
       </c>
-      <c r="C43" s="164"/>
+      <c r="C43" s="132"/>
       <c r="D43" s="76"/>
       <c r="E43" s="40">
         <f>SUM(E3+E16+E26+F32)</f>
@@ -2884,32 +2882,6 @@
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B7:C7"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B14:C14"/>
@@ -2926,6 +2898,32 @@
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B26:C26"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2935,7 +2933,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DBF476-724A-4DAE-8D66-8B0809F96B84}">
-  <dimension ref="B1:M28"/>
+  <dimension ref="B1:M29"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="3" max="3" width="18.125" customWidth="1"/>
@@ -2945,10 +2943,10 @@
   <sheetData>
     <row r="1" spans="2:13" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B2" s="81" t="s">
+      <c r="B2" s="116" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="82"/>
+      <c r="C2" s="117"/>
       <c r="D2" s="10" t="s">
         <v>9</v>
       </c>
@@ -2973,10 +2971,10 @@
       </c>
     </row>
     <row r="3" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B3" s="83" t="s">
+      <c r="B3" s="101" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="84"/>
+      <c r="C3" s="102"/>
       <c r="D3" s="10" t="s">
         <v>12</v>
       </c>
@@ -3003,15 +3001,15 @@
       </c>
     </row>
     <row r="4" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B4" s="85" t="s">
+      <c r="B4" s="103" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="86"/>
+      <c r="C4" s="104"/>
       <c r="D4" s="5"/>
       <c r="E4" s="38">
         <v>2</v>
       </c>
-      <c r="F4" s="149">
+      <c r="F4" s="86">
         <v>2</v>
       </c>
       <c r="G4" s="9" t="s">
@@ -3029,10 +3027,10 @@
       </c>
     </row>
     <row r="5" spans="2:13">
-      <c r="B5" s="91" t="s">
+      <c r="B5" s="120" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="92"/>
+      <c r="C5" s="121"/>
       <c r="D5" s="6"/>
       <c r="E5" s="35">
         <v>2</v>
@@ -3048,10 +3046,10 @@
       <c r="K5" s="59"/>
     </row>
     <row r="6" spans="2:13">
-      <c r="B6" s="89" t="s">
+      <c r="B6" s="98" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="90"/>
+      <c r="C6" s="105"/>
       <c r="D6" s="6"/>
       <c r="E6" s="35">
         <v>2</v>
@@ -3067,31 +3065,32 @@
       <c r="K6" s="59"/>
     </row>
     <row r="7" spans="2:13">
-      <c r="B7" s="87" t="s">
+      <c r="B7" s="118" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="88"/>
+      <c r="C7" s="119"/>
       <c r="D7" s="8"/>
       <c r="E7" s="36">
+        <f>SUM(E8+E9+E10+E11)</f>
         <v>2</v>
       </c>
-      <c r="F7" s="150"/>
+      <c r="F7" s="87"/>
       <c r="G7" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="I7" s="93" t="s">
+      <c r="I7" s="100" t="s">
         <v>88</v>
       </c>
-      <c r="J7" s="93"/>
-      <c r="K7" s="93"/>
-      <c r="L7" s="93"/>
-      <c r="M7" s="93"/>
+      <c r="J7" s="100"/>
+      <c r="K7" s="100"/>
+      <c r="L7" s="100"/>
+      <c r="M7" s="100"/>
     </row>
     <row r="8" spans="2:13">
-      <c r="B8" s="145" t="s">
+      <c r="B8" s="92" t="s">
         <v>89</v>
       </c>
-      <c r="C8" s="147"/>
+      <c r="C8" s="93"/>
       <c r="D8" s="6"/>
       <c r="E8" s="35">
         <v>0.5</v>
@@ -3102,10 +3101,10 @@
       </c>
     </row>
     <row r="9" spans="2:13">
-      <c r="B9" s="145" t="s">
+      <c r="B9" s="92" t="s">
         <v>90</v>
       </c>
-      <c r="C9" s="147"/>
+      <c r="C9" s="93"/>
       <c r="D9" s="6"/>
       <c r="E9" s="35">
         <v>0.5</v>
@@ -3116,10 +3115,10 @@
       </c>
     </row>
     <row r="10" spans="2:13">
-      <c r="B10" s="145" t="s">
+      <c r="B10" s="92" t="s">
         <v>91</v>
       </c>
-      <c r="C10" s="147"/>
+      <c r="C10" s="93"/>
       <c r="D10" s="6"/>
       <c r="E10" s="35">
         <v>0.5</v>
@@ -3130,24 +3129,24 @@
       </c>
     </row>
     <row r="11" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B11" s="152" t="s">
+      <c r="B11" s="94" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="153"/>
+      <c r="C11" s="95"/>
       <c r="D11" s="8"/>
       <c r="E11" s="36">
         <v>0.5</v>
       </c>
-      <c r="F11" s="150"/>
+      <c r="F11" s="87"/>
       <c r="G11" s="8" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="12" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B12" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="84"/>
+      <c r="B12" s="101" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="102"/>
       <c r="D12" s="10" t="s">
         <v>11</v>
       </c>
@@ -3164,10 +3163,10 @@
       </c>
     </row>
     <row r="13" spans="2:13">
-      <c r="B13" s="85" t="s">
+      <c r="B13" s="103" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="86"/>
+      <c r="C13" s="104"/>
       <c r="D13" s="9"/>
       <c r="E13" s="39">
         <v>2</v>
@@ -3180,10 +3179,10 @@
       </c>
     </row>
     <row r="14" spans="2:13">
-      <c r="B14" s="89" t="s">
+      <c r="B14" s="98" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="112"/>
+      <c r="C14" s="99"/>
       <c r="D14" s="9"/>
       <c r="E14" s="39">
         <v>4</v>
@@ -3194,10 +3193,10 @@
       </c>
     </row>
     <row r="15" spans="2:13">
-      <c r="B15" s="89" t="s">
+      <c r="B15" s="98" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="90"/>
+      <c r="C15" s="105"/>
       <c r="D15" s="6"/>
       <c r="E15" s="35">
         <v>3</v>
@@ -3210,10 +3209,10 @@
       </c>
     </row>
     <row r="16" spans="2:13">
-      <c r="B16" s="94" t="s">
+      <c r="B16" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="95"/>
+      <c r="C16" s="107"/>
       <c r="D16" s="6"/>
       <c r="E16" s="35">
         <v>2</v>
@@ -3224,10 +3223,10 @@
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="154" t="s">
+      <c r="B17" s="96" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="151"/>
+      <c r="C17" s="97"/>
       <c r="D17" s="6"/>
       <c r="E17" s="35">
         <v>1</v>
@@ -3238,24 +3237,24 @@
       </c>
     </row>
     <row r="18" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B18" s="157" t="s">
+      <c r="B18" s="108" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="158"/>
+      <c r="C18" s="109"/>
       <c r="D18" s="8"/>
       <c r="E18" s="36">
         <v>1</v>
       </c>
-      <c r="F18" s="150"/>
+      <c r="F18" s="87"/>
       <c r="G18" s="8" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B19" s="83" t="s">
+      <c r="B19" s="101" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="84"/>
+      <c r="C19" s="102"/>
       <c r="D19" s="10" t="s">
         <v>10</v>
       </c>
@@ -3272,10 +3271,10 @@
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="94" t="s">
+      <c r="B20" s="106" t="s">
         <v>95</v>
       </c>
-      <c r="C20" s="95"/>
+      <c r="C20" s="107"/>
       <c r="D20" s="6"/>
       <c r="E20" s="35">
         <v>1</v>
@@ -3286,33 +3285,33 @@
       </c>
     </row>
     <row r="21" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B21" s="96" t="s">
+      <c r="B21" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="97"/>
+      <c r="C21" s="109"/>
       <c r="D21" s="8"/>
       <c r="E21" s="36">
         <v>2</v>
       </c>
-      <c r="F21" s="150"/>
+      <c r="F21" s="87"/>
       <c r="G21" s="8" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B22" s="83" t="s">
+      <c r="B22" s="101" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="84"/>
+      <c r="C22" s="102"/>
       <c r="D22" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E22" s="40">
-        <f>SUM(E23+E25+E27)</f>
-        <v>9</v>
+        <f>SUM(E23+E24+E26+E28)</f>
+        <v>11</v>
       </c>
       <c r="F22" s="64">
-        <f>SUM(F23+F25+F27)</f>
+        <f>SUM(F23+F26+F28)</f>
         <v>0</v>
       </c>
       <c r="G22" s="10" t="s">
@@ -3320,10 +3319,10 @@
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="85" t="s">
+      <c r="B23" s="103" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="86"/>
+      <c r="C23" s="104"/>
       <c r="D23" s="9"/>
       <c r="E23" s="39">
         <v>5</v>
@@ -3334,96 +3333,91 @@
       </c>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="100" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="101"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="57"/>
+      <c r="B24" s="98" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" s="99"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="39">
+        <v>2</v>
+      </c>
+      <c r="F24" s="63"/>
       <c r="G24" s="6" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="25" spans="2:7">
-      <c r="B25" s="89" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="90"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="35">
-        <v>2</v>
-      </c>
+      <c r="B25" s="114" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="115"/>
+      <c r="D25" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="E25" s="35"/>
       <c r="F25" s="57"/>
       <c r="G25" s="6" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="26" spans="2:7">
-      <c r="B26" s="100" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="101"/>
+      <c r="B26" s="98" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" s="105"/>
       <c r="D26" s="6"/>
-      <c r="E26" s="35"/>
+      <c r="E26" s="35">
+        <v>2</v>
+      </c>
       <c r="F26" s="57"/>
       <c r="G26" s="6" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B27" s="146" t="s">
+    <row r="27" spans="2:7">
+      <c r="B27" s="114" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="115"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B28" s="110" t="s">
         <v>66</v>
       </c>
-      <c r="C27" s="148"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="37">
+      <c r="C28" s="111"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="37">
         <v>2</v>
       </c>
-      <c r="F27" s="57"/>
-      <c r="G27" s="7" t="s">
+      <c r="F28" s="57"/>
+      <c r="G28" s="7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B28" s="98" t="s">
+    <row r="29" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B29" s="112" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="99"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="40">
+      <c r="C29" s="113"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="40">
         <f>SUM(E3+E12+E19+E22)</f>
-        <v>31</v>
-      </c>
-      <c r="F28" s="64">
+        <v>33</v>
+      </c>
+      <c r="F29" s="64">
         <f>SUM(F3+F12+F19+F22)</f>
         <v>12</v>
       </c>
-      <c r="G28" s="159"/>
+      <c r="G29" s="90"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="I7:M7"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
+  <mergeCells count="29">
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
@@ -3431,6 +3425,28 @@
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="I7:M7"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3454,10 +3470,10 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B2" s="130" t="s">
+      <c r="B2" s="141" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="131"/>
+      <c r="C2" s="142"/>
       <c r="D2" s="10" t="s">
         <v>9</v>
       </c>
@@ -3472,10 +3488,10 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B3" s="125" t="s">
+      <c r="B3" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="126"/>
+      <c r="C3" s="144"/>
       <c r="D3" s="10" t="s">
         <v>12</v>
       </c>
@@ -3502,19 +3518,19 @@
       </c>
     </row>
     <row r="4" spans="2:12">
-      <c r="B4" s="136" t="s">
+      <c r="B4" s="145" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="137"/>
-      <c r="D4" s="138"/>
-      <c r="E4" s="139">
+      <c r="C4" s="146"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="83">
         <v>3</v>
       </c>
-      <c r="F4" s="135">
+      <c r="F4" s="81">
         <f>SUM(F6)</f>
         <v>0</v>
       </c>
-      <c r="G4" s="140" t="s">
+      <c r="G4" s="84" t="s">
         <v>80</v>
       </c>
       <c r="J4" s="54" t="s">
@@ -3529,10 +3545,10 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B5" s="87" t="s">
+      <c r="B5" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="110"/>
+      <c r="C5" s="137"/>
       <c r="D5" s="8"/>
       <c r="E5" s="36">
         <v>3</v>
@@ -3551,10 +3567,10 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B6" s="125" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="126"/>
+      <c r="B6" s="143" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="144"/>
       <c r="D6" s="10" t="s">
         <v>11</v>
       </c>
@@ -3581,15 +3597,15 @@
       </c>
     </row>
     <row r="7" spans="2:12">
-      <c r="B7" s="123" t="s">
+      <c r="B7" s="149" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="124"/>
+      <c r="C7" s="150"/>
       <c r="D7" s="66"/>
       <c r="E7" s="68">
         <v>3</v>
       </c>
-      <c r="F7" s="135">
+      <c r="F7" s="81">
         <f>SUM(F9)</f>
         <v>0</v>
       </c>
@@ -3598,25 +3614,25 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B8" s="87" t="s">
+      <c r="B8" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="110"/>
+      <c r="C8" s="137"/>
       <c r="D8" s="8"/>
       <c r="E8" s="36">
         <v>3</v>
       </c>
       <c r="F8" s="71"/>
       <c r="G8" s="60"/>
-      <c r="J8" s="142"/>
-      <c r="K8" s="133"/>
-      <c r="L8" s="134"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="58"/>
+      <c r="L8" s="59"/>
     </row>
     <row r="9" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B9" s="125" t="s">
+      <c r="B9" s="143" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="126"/>
+      <c r="C9" s="144"/>
       <c r="D9" s="10" t="s">
         <v>10</v>
       </c>
@@ -3631,13 +3647,12 @@
       <c r="G9" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="141"/>
     </row>
     <row r="10" spans="2:12">
-      <c r="B10" s="117" t="s">
+      <c r="B10" s="126" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="127"/>
+      <c r="C10" s="147"/>
       <c r="D10" s="9"/>
       <c r="E10" s="39">
         <v>3</v>
@@ -3648,10 +3663,10 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B11" s="128" t="s">
+      <c r="B11" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="129"/>
+      <c r="C11" s="148"/>
       <c r="D11" s="8"/>
       <c r="E11" s="36">
         <v>2</v>
@@ -3662,10 +3677,10 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B12" s="125" t="s">
+      <c r="B12" s="143" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="126"/>
+      <c r="C12" s="144"/>
       <c r="D12" s="10" t="s">
         <v>14</v>
       </c>
@@ -3682,10 +3697,10 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B13" s="123" t="s">
+      <c r="B13" s="149" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="124"/>
+      <c r="C13" s="150"/>
       <c r="D13" s="66"/>
       <c r="E13" s="68">
         <v>2</v>
@@ -3696,10 +3711,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B14" s="125" t="s">
+      <c r="B14" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="126"/>
+      <c r="C14" s="144"/>
       <c r="D14" s="10"/>
       <c r="E14" s="40">
         <f>SUM(E15:E16)</f>
@@ -3714,10 +3729,10 @@
       </c>
     </row>
     <row r="15" spans="2:12">
-      <c r="B15" s="117" t="s">
+      <c r="B15" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="127"/>
+      <c r="C15" s="147"/>
       <c r="D15" s="9"/>
       <c r="E15" s="39">
         <v>1</v>
@@ -3728,10 +3743,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B16" s="128" t="s">
+      <c r="B16" s="122" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="129"/>
+      <c r="C16" s="148"/>
       <c r="D16" s="8"/>
       <c r="E16" s="36">
         <v>1</v>
@@ -3742,10 +3757,10 @@
       </c>
     </row>
     <row r="17" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B17" s="125" t="s">
+      <c r="B17" s="143" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="126"/>
+      <c r="C17" s="144"/>
       <c r="D17" s="10"/>
       <c r="E17" s="40">
         <f>SUM(E18:E19)</f>
@@ -3760,10 +3775,10 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="117" t="s">
+      <c r="B18" s="126" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="127"/>
+      <c r="C18" s="147"/>
       <c r="D18" s="9"/>
       <c r="E18" s="39">
         <v>1</v>
@@ -3774,10 +3789,10 @@
       </c>
     </row>
     <row r="19" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B19" s="119" t="s">
+      <c r="B19" s="151" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="120"/>
+      <c r="C19" s="152"/>
       <c r="D19" s="7"/>
       <c r="E19" s="37">
         <v>1</v>
@@ -3788,10 +3803,10 @@
       </c>
     </row>
     <row r="20" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B20" s="121" t="s">
+      <c r="B20" s="153" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="122"/>
+      <c r="C20" s="154"/>
       <c r="D20" s="10"/>
       <c r="E20" s="40">
         <f>SUM(E3+E6+E9+E12+E14+E17)</f>
@@ -3808,6 +3823,18 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
@@ -3815,18 +3842,6 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3839,13 +3854,13 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="132" t="s">
+      <c r="C1" s="155" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="132"/>
-      <c r="E1" s="132"/>
-      <c r="F1" s="132"/>
-      <c r="G1" s="132"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="155"/>
+      <c r="G1" s="155"/>
     </row>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
       <c r="B2" s="27" t="s">
@@ -4095,7 +4110,7 @@
         <f t="shared" si="7"/>
         <v>46311</v>
       </c>
-      <c r="H10" s="143">
+      <c r="H10" s="85">
         <f>SUM(G10)+1</f>
         <v>46312</v>
       </c>

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\Documents\GitHub\GlassesGame\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\OneDrive\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51B989A7-A14F-47E5-B29C-0B1CDB8CCAF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F372F0-C6DC-4080-9C55-3053C54C1A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="599" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="107">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -665,6 +665,63 @@
     <t>(寺尾)</t>
     <rPh sb="1" eb="3">
       <t>テラオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フェード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>寺尾</t>
+    <rPh sb="0" eb="2">
+      <t>テラオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームオーバー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー　効果音</t>
+    <rPh sb="2" eb="5">
+      <t>コウカオン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>合計</t>
+    <rPh sb="0" eb="2">
+      <t>ゴウケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>プロト総コスト</t>
+    <rPh sb="3" eb="4">
+      <t>ソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アルファ総コスト</t>
+    <rPh sb="4" eb="5">
+      <t>ソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雰囲気づくり</t>
+    <rPh sb="0" eb="3">
+      <t>フンイキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>提出日</t>
+    <rPh sb="0" eb="3">
+      <t>テイシュツビ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -785,7 +842,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="53">
+  <borders count="52">
     <border>
       <left/>
       <right/>
@@ -1111,17 +1168,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -1422,36 +1468,34 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1490,7 +1534,7 @@
     <xf numFmtId="56" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1502,8 +1546,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
@@ -1525,335 +1567,367 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="37" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="0" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="56" fontId="0" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2142,29 +2216,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B1:S43"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="9" style="4" customWidth="1"/>
-    <col min="2" max="2" width="17.125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="17.09765625" style="4" customWidth="1"/>
     <col min="3" max="3" width="9" style="4"/>
-    <col min="4" max="4" width="6.25" style="4" customWidth="1"/>
-    <col min="5" max="5" width="7.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.19921875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7.09765625" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="9" style="4"/>
-    <col min="9" max="9" width="17.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.09765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.3984375" style="4" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9" style="4"/>
     <col min="12" max="12" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="19.5" thickBot="1"/>
-    <row r="2" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B2" s="116" t="s">
+    <row r="1" spans="2:19" ht="18.600000000000001" thickBot="1"/>
+    <row r="2" spans="2:19" ht="18.600000000000001" thickBot="1">
+      <c r="B2" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="129"/>
-      <c r="D2" s="77" t="s">
+      <c r="C2" s="127"/>
+      <c r="D2" s="72" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="10" t="s">
@@ -2177,220 +2251,259 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B3" s="101" t="s">
+    <row r="3" spans="2:19" ht="18.600000000000001" thickBot="1">
+      <c r="B3" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="128"/>
-      <c r="D3" s="77" t="s">
+      <c r="C3" s="123"/>
+      <c r="D3" s="72" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="40">
+      <c r="E3" s="38">
         <f>SUM(E4:E15)</f>
         <v>21</v>
       </c>
-      <c r="F3" s="40">
+      <c r="F3" s="38">
         <f>SUM(F4:F15)</f>
         <v>23</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="I3" s="50" t="s">
+      <c r="I3" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="J3" s="53">
+      <c r="J3" s="51">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
-      </c>
-      <c r="K3" s="41" t="s">
+        <v>46304</v>
+      </c>
+      <c r="K3" s="39" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B4" s="103" t="s">
+    <row r="4" spans="2:19" ht="18.600000000000001" thickBot="1">
+      <c r="B4" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="130"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="39">
+      <c r="C4" s="122"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="37">
         <f>SUM(E5:E7)</f>
         <v>4</v>
       </c>
-      <c r="F4" s="39">
+      <c r="F4" s="37">
         <f>SUM(F5:F7)</f>
         <v>5</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="I4" s="75" t="s">
+      <c r="I4" s="70" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="53">
+      <c r="J4" s="51">
         <v>46295</v>
       </c>
-      <c r="K4" s="65" t="str">
+      <c r="K4" s="60" t="str">
         <f ca="1">SUM($J4-J3)&amp; "日"</f>
-        <v>-8日</v>
-      </c>
-    </row>
-    <row r="5" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B5" s="92" t="s">
+        <v>-9日</v>
+      </c>
+    </row>
+    <row r="5" spans="2:19" ht="18.600000000000001" thickBot="1">
+      <c r="B5" s="108" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="131"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="35">
+      <c r="C5" s="116"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="33">
         <v>2</v>
       </c>
-      <c r="F5" s="35">
+      <c r="F5" s="33">
         <v>2</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="I5" s="72" t="s">
+      <c r="I5" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="J5" s="73">
+      <c r="J5" s="68">
         <v>46314</v>
       </c>
-      <c r="K5" s="74" t="str">
+      <c r="K5" s="69" t="str">
         <f ca="1">SUM(J5-J3)&amp; "日"</f>
-        <v>11日</v>
-      </c>
-      <c r="R5" s="58"/>
-      <c r="S5" s="59"/>
-    </row>
-    <row r="6" spans="2:19">
-      <c r="B6" s="92" t="s">
+        <v>10日</v>
+      </c>
+      <c r="R5" s="55"/>
+      <c r="S5" s="56"/>
+    </row>
+    <row r="6" spans="2:19" ht="18.600000000000001" thickBot="1">
+      <c r="B6" s="108" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="131"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="35">
+      <c r="C6" s="116"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="33">
         <v>1</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="33">
         <v>2</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="R6" s="58"/>
-      <c r="S6" s="59"/>
-    </row>
-    <row r="7" spans="2:19">
-      <c r="B7" s="92" t="s">
+      <c r="R6" s="55"/>
+      <c r="S6" s="56"/>
+    </row>
+    <row r="7" spans="2:19" ht="18.600000000000001" thickBot="1">
+      <c r="B7" s="108" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="131"/>
-      <c r="D7" s="79"/>
-      <c r="E7" s="35">
+      <c r="C7" s="116"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="33">
         <v>1</v>
       </c>
-      <c r="F7" s="39">
+      <c r="F7" s="37">
         <v>1</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="R7" s="58"/>
-      <c r="S7" s="59"/>
+      <c r="I7" s="160" t="s">
+        <v>103</v>
+      </c>
+      <c r="J7" s="161"/>
+      <c r="R7" s="55"/>
+      <c r="S7" s="56"/>
     </row>
     <row r="8" spans="2:19">
-      <c r="B8" s="98" t="s">
+      <c r="B8" s="96" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="99"/>
-      <c r="D8" s="79"/>
-      <c r="E8" s="35">
+      <c r="C8" s="104"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="33">
         <v>2</v>
       </c>
-      <c r="F8" s="39">
+      <c r="F8" s="37">
         <v>2</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>84</v>
       </c>
+      <c r="I8" s="148" t="s">
+        <v>99</v>
+      </c>
+      <c r="J8" s="151">
+        <f>SUM(E3)</f>
+        <v>21</v>
+      </c>
     </row>
     <row r="9" spans="2:19">
-      <c r="B9" s="98" t="s">
+      <c r="B9" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="99"/>
-      <c r="D9" s="80"/>
-      <c r="E9" s="36">
+      <c r="C9" s="104"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="34">
         <v>2</v>
       </c>
-      <c r="F9" s="36">
+      <c r="F9" s="34">
         <v>2</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>84</v>
       </c>
+      <c r="I9" s="149" t="s">
+        <v>11</v>
+      </c>
+      <c r="J9" s="152">
+        <f>SUM(E16)</f>
+        <v>16</v>
+      </c>
     </row>
     <row r="10" spans="2:19">
-      <c r="B10" s="98" t="s">
+      <c r="B10" s="96" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="99"/>
-      <c r="D10" s="80"/>
-      <c r="E10" s="36">
+      <c r="C10" s="104"/>
+      <c r="D10" s="75"/>
+      <c r="E10" s="34">
         <v>2</v>
       </c>
-      <c r="F10" s="36">
+      <c r="F10" s="34">
         <v>2</v>
       </c>
       <c r="G10" s="9" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="11" spans="2:19">
-      <c r="B11" s="106" t="s">
+      <c r="I10" s="149" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="152">
+        <f>SUM(E26)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" ht="18.600000000000001" thickBot="1">
+      <c r="B11" s="105" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="125"/>
-      <c r="D11" s="79"/>
-      <c r="E11" s="35">
+      <c r="C11" s="128"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="33">
         <v>1</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="33">
         <v>1</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="12" spans="2:19">
-      <c r="B12" s="98" t="s">
+      <c r="I11" s="150" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="153">
+        <f>SUM(E32)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" ht="18.600000000000001" thickBot="1">
+      <c r="B12" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="99"/>
-      <c r="D12" s="79"/>
-      <c r="E12" s="35">
+      <c r="C12" s="104"/>
+      <c r="D12" s="74"/>
+      <c r="E12" s="33">
         <f>SUM(E13:E15)</f>
         <v>3</v>
       </c>
-      <c r="F12" s="35">
+      <c r="F12" s="33">
         <f>SUM(F13:F15)</f>
         <v>3</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>84</v>
       </c>
+      <c r="I12" s="159" t="s">
+        <v>102</v>
+      </c>
+      <c r="J12" s="83">
+        <f>SUM(J8:J11)</f>
+        <v>66</v>
+      </c>
     </row>
     <row r="13" spans="2:19">
-      <c r="B13" s="96" t="s">
+      <c r="B13" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="124"/>
-      <c r="D13" s="79"/>
-      <c r="E13" s="35">
+      <c r="C13" s="118"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="33">
         <v>1</v>
       </c>
-      <c r="F13" s="35">
+      <c r="F13" s="33">
         <v>1</v>
       </c>
       <c r="G13" s="6" t="s">
@@ -2398,52 +2511,52 @@
       </c>
     </row>
     <row r="14" spans="2:19">
-      <c r="B14" s="92" t="s">
+      <c r="B14" s="108" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="131"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="35">
+      <c r="C14" s="116"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="33">
         <v>1</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="33">
         <v>1</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="R14" s="58"/>
-      <c r="S14" s="59"/>
-    </row>
-    <row r="15" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B15" s="94" t="s">
+      <c r="R14" s="55"/>
+      <c r="S14" s="56"/>
+    </row>
+    <row r="15" spans="2:19" ht="18.600000000000001" thickBot="1">
+      <c r="B15" s="110" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="134"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="36">
+      <c r="C15" s="117"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="34">
         <v>1</v>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="34">
         <v>1</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B16" s="101" t="s">
+    <row r="16" spans="2:19" ht="18.600000000000001" thickBot="1">
+      <c r="B16" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="C16" s="128"/>
-      <c r="D16" s="76" t="s">
+      <c r="C16" s="123"/>
+      <c r="D16" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="40">
+      <c r="E16" s="38">
         <f>SUM(E17:E25)</f>
         <v>16</v>
       </c>
-      <c r="F16" s="40">
+      <c r="F16" s="38">
         <v>8</v>
       </c>
       <c r="G16" s="10" t="s">
@@ -2451,15 +2564,15 @@
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="103" t="s">
+      <c r="B17" s="92" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="130"/>
-      <c r="D17" s="89"/>
-      <c r="E17" s="39">
+      <c r="C17" s="122"/>
+      <c r="D17" s="82"/>
+      <c r="E17" s="37">
         <v>3</v>
       </c>
-      <c r="F17" s="39">
+      <c r="F17" s="37">
         <v>1</v>
       </c>
       <c r="G17" s="9" t="s">
@@ -2467,15 +2580,15 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="98" t="s">
+      <c r="B18" s="96" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="99"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="35">
+      <c r="C18" s="104"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="33">
         <v>3</v>
       </c>
-      <c r="F18" s="35">
+      <c r="F18" s="33">
         <v>1</v>
       </c>
       <c r="G18" s="6" t="s">
@@ -2483,15 +2596,15 @@
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="98" t="s">
+      <c r="B19" s="96" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="99"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="35">
+      <c r="C19" s="104"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="33">
         <v>3</v>
       </c>
-      <c r="F19" s="35">
+      <c r="F19" s="33">
         <v>1</v>
       </c>
       <c r="G19" s="6" t="s">
@@ -2499,15 +2612,15 @@
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="98" t="s">
+      <c r="B20" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="99"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="35">
+      <c r="C20" s="104"/>
+      <c r="D20" s="75"/>
+      <c r="E20" s="33">
         <v>3</v>
       </c>
-      <c r="F20" s="35">
+      <c r="F20" s="33">
         <v>1</v>
       </c>
       <c r="G20" s="6" t="s">
@@ -2515,15 +2628,15 @@
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="98" t="s">
+      <c r="B21" s="96" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="99"/>
-      <c r="D21" s="79"/>
-      <c r="E21" s="68">
+      <c r="C21" s="104"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="63">
         <v>1</v>
       </c>
-      <c r="F21" s="35">
+      <c r="F21" s="33">
         <v>1</v>
       </c>
       <c r="G21" s="6" t="s">
@@ -2531,13 +2644,13 @@
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="106" t="s">
+      <c r="B22" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="125"/>
-      <c r="D22" s="79"/>
-      <c r="E22" s="35"/>
-      <c r="F22" s="35">
+      <c r="C22" s="128"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33">
         <v>3</v>
       </c>
       <c r="G22" s="6" t="s">
@@ -2545,15 +2658,15 @@
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="96" t="s">
+      <c r="B23" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="124"/>
-      <c r="D23" s="79"/>
-      <c r="E23" s="35">
+      <c r="C23" s="118"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="33">
         <v>1</v>
       </c>
-      <c r="F23" s="35">
+      <c r="F23" s="33">
         <v>1</v>
       </c>
       <c r="G23" s="6" t="s">
@@ -2561,50 +2674,50 @@
       </c>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="96" t="s">
+      <c r="B24" s="112" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="124"/>
-      <c r="D24" s="79"/>
-      <c r="E24" s="35">
+      <c r="C24" s="118"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="33">
         <v>1</v>
       </c>
-      <c r="F24" s="35">
+      <c r="F24" s="33">
         <v>1</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B25" s="135" t="s">
+    <row r="25" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B25" s="119" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="136"/>
-      <c r="D25" s="91"/>
-      <c r="E25" s="37">
+      <c r="C25" s="120"/>
+      <c r="D25" s="84"/>
+      <c r="E25" s="35">
         <v>1</v>
       </c>
-      <c r="F25" s="37">
+      <c r="F25" s="35">
         <v>1</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B26" s="101" t="s">
+    <row r="26" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B26" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="128"/>
-      <c r="D26" s="76" t="s">
+      <c r="C26" s="123"/>
+      <c r="D26" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="40">
+      <c r="E26" s="38">
         <f>SUM(E27:E31)</f>
         <v>16</v>
       </c>
-      <c r="F26" s="40">
+      <c r="F26" s="38">
         <f>SUM(F27,F28,F31)</f>
         <v>11</v>
       </c>
@@ -2613,15 +2726,15 @@
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="126" t="s">
+      <c r="B27" s="131" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="127"/>
-      <c r="D27" s="89"/>
-      <c r="E27" s="39">
+      <c r="C27" s="132"/>
+      <c r="D27" s="82"/>
+      <c r="E27" s="37">
         <v>5</v>
       </c>
-      <c r="F27" s="39">
+      <c r="F27" s="37">
         <v>5</v>
       </c>
       <c r="G27" s="9" t="s">
@@ -2629,16 +2742,16 @@
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="106" t="s">
+      <c r="B28" s="105" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="125"/>
-      <c r="D28" s="79"/>
-      <c r="E28" s="35">
+      <c r="C28" s="128"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="33">
         <f>SUM(E29:E30)</f>
         <v>4</v>
       </c>
-      <c r="F28" s="35">
+      <c r="F28" s="33">
         <f>SUM(F29:F30)</f>
         <v>3</v>
       </c>
@@ -2647,15 +2760,15 @@
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="96" t="s">
+      <c r="B29" s="112" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="124"/>
-      <c r="D29" s="79"/>
-      <c r="E29" s="35">
+      <c r="C29" s="118"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="33">
         <v>2</v>
       </c>
-      <c r="F29" s="35">
+      <c r="F29" s="33">
         <v>2</v>
       </c>
       <c r="G29" s="9" t="s">
@@ -2663,50 +2776,50 @@
       </c>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="96" t="s">
+      <c r="B30" s="112" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="124"/>
-      <c r="D30" s="79"/>
-      <c r="E30" s="35">
+      <c r="C30" s="118"/>
+      <c r="D30" s="74"/>
+      <c r="E30" s="33">
         <v>2</v>
       </c>
-      <c r="F30" s="35">
+      <c r="F30" s="33">
         <v>1</v>
       </c>
       <c r="G30" s="9" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B31" s="118" t="s">
+    <row r="31" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B31" s="94" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="137"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="36">
+      <c r="C31" s="121"/>
+      <c r="D31" s="75"/>
+      <c r="E31" s="34">
         <v>3</v>
       </c>
-      <c r="F31" s="36">
+      <c r="F31" s="34">
         <v>3</v>
       </c>
       <c r="G31" s="9" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="32" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B32" s="101" t="s">
+    <row r="32" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B32" s="90" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="128"/>
-      <c r="D32" s="76" t="s">
+      <c r="C32" s="123"/>
+      <c r="D32" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="40">
+      <c r="E32" s="38">
         <f>SUM(E33:E42)</f>
         <v>13</v>
       </c>
-      <c r="F32" s="40">
+      <c r="F32" s="38">
         <f>SUM(F34,F36,F37,F40,F41)</f>
         <v>5</v>
       </c>
@@ -2715,27 +2828,27 @@
       </c>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="103" t="s">
+      <c r="B33" s="92" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="130"/>
-      <c r="D33" s="89"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
+      <c r="C33" s="122"/>
+      <c r="D33" s="82"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="37"/>
       <c r="G33" s="9" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="92" t="s">
+      <c r="B34" s="108" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="131"/>
-      <c r="D34" s="89"/>
-      <c r="E34" s="39">
+      <c r="C34" s="116"/>
+      <c r="D34" s="82"/>
+      <c r="E34" s="37">
         <v>2</v>
       </c>
-      <c r="F34" s="39">
+      <c r="F34" s="37">
         <v>1</v>
       </c>
       <c r="G34" s="6" t="s">
@@ -2743,27 +2856,27 @@
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="114" t="s">
+      <c r="B35" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="138"/>
-      <c r="D35" s="79"/>
-      <c r="E35" s="35"/>
-      <c r="F35" s="35"/>
+      <c r="C35" s="124"/>
+      <c r="D35" s="74"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33"/>
       <c r="G35" s="6" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="98" t="s">
+      <c r="B36" s="96" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="99"/>
-      <c r="D36" s="79"/>
-      <c r="E36" s="35">
+      <c r="C36" s="104"/>
+      <c r="D36" s="74"/>
+      <c r="E36" s="33">
         <v>2</v>
       </c>
-      <c r="F36" s="35">
+      <c r="F36" s="33">
         <v>1</v>
       </c>
       <c r="G36" s="6" t="s">
@@ -2771,15 +2884,15 @@
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="98" t="s">
+      <c r="B37" s="96" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="99"/>
-      <c r="D37" s="79"/>
-      <c r="E37" s="35">
+      <c r="C37" s="104"/>
+      <c r="D37" s="74"/>
+      <c r="E37" s="33">
         <v>2</v>
       </c>
-      <c r="F37" s="35">
+      <c r="F37" s="33">
         <v>1</v>
       </c>
       <c r="G37" s="6" t="s">
@@ -2787,15 +2900,15 @@
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="98" t="s">
+      <c r="B38" s="96" t="s">
         <v>93</v>
       </c>
-      <c r="C38" s="99"/>
-      <c r="D38" s="79"/>
-      <c r="E38" s="35">
+      <c r="C38" s="104"/>
+      <c r="D38" s="74"/>
+      <c r="E38" s="33">
         <v>1</v>
       </c>
-      <c r="F38" s="35">
+      <c r="F38" s="33">
         <v>1</v>
       </c>
       <c r="G38" s="6" t="s">
@@ -2803,27 +2916,27 @@
       </c>
     </row>
     <row r="39" spans="2:7">
-      <c r="B39" s="114" t="s">
+      <c r="B39" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="C39" s="138"/>
-      <c r="D39" s="79"/>
-      <c r="E39" s="35"/>
-      <c r="F39" s="35"/>
+      <c r="C39" s="124"/>
+      <c r="D39" s="74"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
       <c r="G39" s="6" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="40" spans="2:7">
-      <c r="B40" s="139" t="s">
+      <c r="B40" s="125" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="140"/>
-      <c r="D40" s="88"/>
-      <c r="E40" s="35">
+      <c r="C40" s="126"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="33">
         <v>2</v>
       </c>
-      <c r="F40" s="35">
+      <c r="F40" s="33">
         <v>1</v>
       </c>
       <c r="G40" s="6" t="s">
@@ -2831,48 +2944,48 @@
       </c>
     </row>
     <row r="41" spans="2:7">
-      <c r="B41" s="106" t="s">
+      <c r="B41" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="C41" s="133"/>
-      <c r="D41" s="88"/>
-      <c r="E41" s="35">
+      <c r="C41" s="115"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="33">
         <v>3</v>
       </c>
-      <c r="F41" s="35">
+      <c r="F41" s="33">
         <v>1</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="42" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B42" s="122" t="s">
+    <row r="42" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B42" s="129" t="s">
         <v>93</v>
       </c>
-      <c r="C42" s="123"/>
-      <c r="D42" s="78"/>
-      <c r="E42" s="36">
+      <c r="C42" s="130"/>
+      <c r="D42" s="73"/>
+      <c r="E42" s="34">
         <v>1</v>
       </c>
-      <c r="F42" s="36">
+      <c r="F42" s="34">
         <v>1</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B43" s="112" t="s">
+    <row r="43" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B43" s="100" t="s">
         <v>82</v>
       </c>
-      <c r="C43" s="132"/>
-      <c r="D43" s="76"/>
-      <c r="E43" s="40">
+      <c r="C43" s="114"/>
+      <c r="D43" s="71"/>
+      <c r="E43" s="38">
         <f>SUM(E3+E16+E26+F32)</f>
         <v>58</v>
       </c>
-      <c r="F43" s="40">
+      <c r="F43" s="38">
         <f>SUM(F3+F16+F26+F32)</f>
         <v>47</v>
       </c>
@@ -2881,7 +2994,34 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="42">
+  <mergeCells count="43">
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B14:C14"/>
@@ -2898,560 +3038,719 @@
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B26:C26"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="F12 E4:F4 E28:F28" formulaRange="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DBF476-724A-4DAE-8D66-8B0809F96B84}">
-  <dimension ref="B1:M29"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="B1:M39"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="3" max="3" width="18.125" customWidth="1"/>
-    <col min="9" max="9" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.09765625" customWidth="1"/>
+    <col min="9" max="9" width="19.09765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="19.5" thickBot="1"/>
-    <row r="2" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B2" s="116" t="s">
+    <row r="1" spans="2:13" ht="18.600000000000001" thickBot="1"/>
+    <row r="2" spans="2:13" ht="18.600000000000001" thickBot="1">
+      <c r="B2" s="88" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="117"/>
+      <c r="C2" s="89"/>
       <c r="D2" s="10" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="76" t="s">
+      <c r="F2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="I2" s="50" t="s">
+      <c r="I2" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="J2" s="53">
+      <c r="J2" s="51">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
-      </c>
-      <c r="K2" s="41" t="s">
+        <v>46304</v>
+      </c>
+      <c r="K2" s="39" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B3" s="101" t="s">
+    <row r="3" spans="2:13" ht="18.600000000000001" thickBot="1">
+      <c r="B3" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="102"/>
+      <c r="C3" s="91"/>
       <c r="D3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="40">
+      <c r="E3" s="38">
         <f>SUM(E4:E7)</f>
         <v>8</v>
       </c>
-      <c r="F3" s="64">
+      <c r="F3" s="38">
         <f>SUM(F4:F7)</f>
         <v>9</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="67" t="s">
+      <c r="I3" s="62" t="s">
         <v>76</v>
       </c>
-      <c r="J3" s="52">
+      <c r="J3" s="50">
         <v>46305</v>
       </c>
-      <c r="K3" s="48" t="str">
+      <c r="K3" s="46" t="str">
         <f ca="1">SUM($J3-J2)&amp; "日"</f>
-        <v>2日</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B4" s="103" t="s">
+        <v>1日</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" ht="18.600000000000001" thickBot="1">
+      <c r="B4" s="92" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="104"/>
+      <c r="C4" s="93"/>
       <c r="D4" s="5"/>
-      <c r="E4" s="38">
+      <c r="E4" s="36">
         <v>2</v>
       </c>
-      <c r="F4" s="86">
+      <c r="F4" s="36">
         <v>2</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="I4" s="72" t="s">
+      <c r="G4" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="I4" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="J4" s="73">
+      <c r="J4" s="68">
         <v>46314</v>
       </c>
-      <c r="K4" s="74" t="str">
+      <c r="K4" s="69" t="str">
         <f ca="1">SUM(J4-J2)&amp; "日"</f>
-        <v>11日</v>
+        <v>10日</v>
       </c>
     </row>
     <row r="5" spans="2:13">
-      <c r="B5" s="120" t="s">
+      <c r="B5" s="98" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="121"/>
+      <c r="C5" s="99"/>
       <c r="D5" s="6"/>
-      <c r="E5" s="35">
+      <c r="E5" s="33">
         <v>2</v>
       </c>
-      <c r="F5" s="57">
+      <c r="F5" s="33">
         <v>2</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="43" t="s">
         <v>84</v>
       </c>
       <c r="I5" s="4"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="59"/>
+      <c r="J5" s="55"/>
+      <c r="K5" s="56"/>
     </row>
     <row r="6" spans="2:13">
-      <c r="B6" s="98" t="s">
+      <c r="B6" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="105"/>
+      <c r="C6" s="97"/>
       <c r="D6" s="6"/>
-      <c r="E6" s="35">
+      <c r="E6" s="33">
         <v>2</v>
       </c>
-      <c r="F6" s="57">
+      <c r="F6" s="33">
         <v>5</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="43" t="s">
         <v>84</v>
       </c>
       <c r="I6" s="4"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="59"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="56"/>
     </row>
     <row r="7" spans="2:13">
-      <c r="B7" s="118" t="s">
+      <c r="B7" s="94" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="119"/>
+      <c r="C7" s="95"/>
       <c r="D7" s="8"/>
-      <c r="E7" s="36">
+      <c r="E7" s="34">
         <f>SUM(E8+E9+E10+E11)</f>
         <v>2</v>
       </c>
-      <c r="F7" s="87"/>
-      <c r="G7" s="6" t="s">
+      <c r="F7" s="34"/>
+      <c r="G7" s="85" t="s">
         <v>80</v>
       </c>
-      <c r="I7" s="100" t="s">
+      <c r="I7" s="107" t="s">
         <v>88</v>
       </c>
-      <c r="J7" s="100"/>
-      <c r="K7" s="100"/>
-      <c r="L7" s="100"/>
-      <c r="M7" s="100"/>
-    </row>
-    <row r="8" spans="2:13">
-      <c r="B8" s="92" t="s">
+      <c r="J7" s="107"/>
+      <c r="K7" s="107"/>
+      <c r="L7" s="107"/>
+      <c r="M7" s="107"/>
+    </row>
+    <row r="8" spans="2:13" ht="18.600000000000001" thickBot="1">
+      <c r="B8" s="108" t="s">
         <v>89</v>
       </c>
-      <c r="C8" s="93"/>
+      <c r="C8" s="109"/>
       <c r="D8" s="6"/>
-      <c r="E8" s="35">
+      <c r="E8" s="33">
         <v>0.5</v>
       </c>
-      <c r="F8" s="57"/>
-      <c r="G8" s="6" t="s">
+      <c r="F8" s="33"/>
+      <c r="G8" s="85" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="9" spans="2:13">
-      <c r="B9" s="92" t="s">
+    <row r="9" spans="2:13" ht="18.600000000000001" thickBot="1">
+      <c r="B9" s="108" t="s">
         <v>90</v>
       </c>
-      <c r="C9" s="93"/>
+      <c r="C9" s="109"/>
       <c r="D9" s="6"/>
-      <c r="E9" s="35">
+      <c r="E9" s="33">
         <v>0.5</v>
       </c>
-      <c r="F9" s="57"/>
-      <c r="G9" s="6" t="s">
+      <c r="F9" s="33"/>
+      <c r="G9" s="85" t="s">
         <v>80</v>
       </c>
+      <c r="I9" s="162" t="s">
+        <v>104</v>
+      </c>
+      <c r="J9" s="163"/>
     </row>
     <row r="10" spans="2:13">
-      <c r="B10" s="92" t="s">
+      <c r="B10" s="108" t="s">
         <v>91</v>
       </c>
-      <c r="C10" s="93"/>
+      <c r="C10" s="109"/>
       <c r="D10" s="6"/>
-      <c r="E10" s="35">
+      <c r="E10" s="33">
         <v>0.5</v>
       </c>
-      <c r="F10" s="57"/>
-      <c r="G10" s="6" t="s">
+      <c r="F10" s="33"/>
+      <c r="G10" s="85" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="11" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B11" s="94" t="s">
+      <c r="I10" s="148" t="s">
+        <v>99</v>
+      </c>
+      <c r="J10" s="151">
+        <f>SUM(F3+E28)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13">
+      <c r="B11" s="110" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="95"/>
+      <c r="C11" s="111"/>
       <c r="D11" s="8"/>
-      <c r="E11" s="36">
+      <c r="E11" s="34">
         <v>0.5</v>
       </c>
-      <c r="F11" s="87"/>
-      <c r="G11" s="8" t="s">
+      <c r="F11" s="34"/>
+      <c r="G11" s="57" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="12" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B12" s="101" t="s">
+      <c r="I11" s="149" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11" s="152">
+        <f>SUM(E13)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" ht="18.600000000000001" thickBot="1">
+      <c r="B12" s="165" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="166"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="35">
+        <v>4</v>
+      </c>
+      <c r="F12" s="35"/>
+      <c r="G12" s="164"/>
+      <c r="I12" s="149" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="152">
+        <f>SUM(E20)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" ht="18.600000000000001" thickBot="1">
+      <c r="B13" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="102"/>
-      <c r="D12" s="10" t="s">
+      <c r="C13" s="91"/>
+      <c r="D13" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="40">
-        <f>SUM(E13:E16)</f>
+      <c r="E13" s="38">
+        <f>SUM(E14:E17)</f>
         <v>11</v>
       </c>
-      <c r="F12" s="64">
-        <f>SUM(F13:F16)</f>
+      <c r="F13" s="38">
+        <f>SUM(F14:F17)</f>
         <v>3</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G13" s="39" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="13" spans="2:13">
-      <c r="B13" s="103" t="s">
+      <c r="I13" s="150" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="153">
+        <f>SUM(E25)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" ht="18.600000000000001" thickBot="1">
+      <c r="B14" s="92" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="104"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="39">
+      <c r="C14" s="93"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="37">
         <v>2</v>
       </c>
-      <c r="F13" s="63">
+      <c r="F14" s="37">
         <v>1</v>
       </c>
-      <c r="G13" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13">
-      <c r="B14" s="98" t="s">
+      <c r="G14" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="I14" s="159" t="s">
+        <v>102</v>
+      </c>
+      <c r="J14" s="83">
+        <f>SUM(J10:J13)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13">
+      <c r="B15" s="96" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="99"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="39">
+      <c r="C15" s="97"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="37">
         <v>4</v>
       </c>
-      <c r="F14" s="63"/>
-      <c r="G14" s="9" t="s">
+      <c r="F15" s="37"/>
+      <c r="G15" s="43" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="2:13">
-      <c r="B15" s="98" t="s">
+    <row r="16" spans="2:13">
+      <c r="B16" s="96" t="s">
         <v>65</v>
       </c>
-      <c r="C15" s="105"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="35">
+      <c r="C16" s="97"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="33">
         <v>3</v>
       </c>
-      <c r="F15" s="57">
+      <c r="F16" s="33">
         <v>2</v>
       </c>
-      <c r="G15" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13">
-      <c r="B16" s="106" t="s">
+      <c r="G16" s="43" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="105" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="107"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="35">
+      <c r="C17" s="106"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="33">
         <v>2</v>
       </c>
-      <c r="F16" s="57"/>
-      <c r="G16" s="6" t="s">
+      <c r="F17" s="33"/>
+      <c r="G17" s="85" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="96" t="s">
+    <row r="18" spans="2:7">
+      <c r="B18" s="112" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="97"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="35">
+      <c r="C18" s="113"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="33">
         <v>1</v>
       </c>
-      <c r="F17" s="57"/>
-      <c r="G17" s="6" t="s">
+      <c r="F18" s="33"/>
+      <c r="G18" s="85" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B18" s="108" t="s">
+    <row r="19" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B19" s="86" t="s">
         <v>47</v>
       </c>
-      <c r="C18" s="109"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="36">
+      <c r="C19" s="87"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="34">
         <v>1</v>
       </c>
-      <c r="F18" s="87"/>
-      <c r="G18" s="8" t="s">
+      <c r="F19" s="34"/>
+      <c r="G19" s="57" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B19" s="101" t="s">
+    <row r="20" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B20" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="102"/>
-      <c r="D19" s="10" t="s">
+      <c r="C20" s="91"/>
+      <c r="D20" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E19" s="40">
-        <f>SUM(E20:E21)</f>
+      <c r="E20" s="38">
+        <f>SUM(E21:E22)</f>
         <v>3</v>
       </c>
-      <c r="F19" s="64">
-        <f>SUM(F20:F21)</f>
+      <c r="F20" s="38">
+        <f>SUM(F21:F22)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G20" s="39" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="106" t="s">
+    <row r="21" spans="2:7">
+      <c r="B21" s="105" t="s">
         <v>95</v>
       </c>
-      <c r="C20" s="107"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="35">
+      <c r="C21" s="106"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="33">
         <v>1</v>
       </c>
-      <c r="F20" s="57"/>
-      <c r="G20" s="6" t="s">
+      <c r="F21" s="33"/>
+      <c r="G21" s="85" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B21" s="108" t="s">
+    <row r="22" spans="2:7">
+      <c r="B22" s="86" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="109"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="36">
+      <c r="C22" s="87"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="34">
         <v>2</v>
       </c>
-      <c r="F21" s="87"/>
-      <c r="G21" s="8" t="s">
+      <c r="F22" s="34"/>
+      <c r="G22" s="57" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B22" s="101" t="s">
+    <row r="23" spans="2:7">
+      <c r="B23" s="94" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="121"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="57"/>
+    </row>
+    <row r="24" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B24" s="167" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" s="168"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="164"/>
+    </row>
+    <row r="25" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B25" s="90" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="102"/>
-      <c r="D22" s="10" t="s">
+      <c r="C25" s="91"/>
+      <c r="D25" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E22" s="40">
-        <f>SUM(E23+E24+E26+E28)</f>
+      <c r="E25" s="38">
+        <f>SUM(E26+E27+E29+E34)</f>
         <v>11</v>
       </c>
-      <c r="F22" s="64">
-        <f>SUM(F23+F26+F28)</f>
+      <c r="F25" s="38">
+        <f>SUM(F26+F29+F34)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="G25" s="39" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="103" t="s">
+    <row r="26" spans="2:7">
+      <c r="B26" s="92" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="104"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="39">
+      <c r="C26" s="93"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="37">
         <v>5</v>
       </c>
-      <c r="F23" s="63"/>
-      <c r="G23" s="6" t="s">
+      <c r="F26" s="37"/>
+      <c r="G26" s="85" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
-      <c r="B24" s="98" t="s">
+    <row r="27" spans="2:7">
+      <c r="B27" s="96" t="s">
         <v>96</v>
       </c>
-      <c r="C24" s="99"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="39">
+      <c r="C27" s="97"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="37">
         <v>2</v>
       </c>
-      <c r="F24" s="63"/>
-      <c r="G24" s="6" t="s">
+      <c r="F27" s="37"/>
+      <c r="G27" s="85" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
-      <c r="B25" s="114" t="s">
+    <row r="28" spans="2:7">
+      <c r="B28" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="115"/>
-      <c r="D25" s="6" t="s">
+      <c r="C28" s="103"/>
+      <c r="D28" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E25" s="35"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="6" t="s">
+      <c r="E28" s="33">
+        <f>SUM(E29:E31)</f>
+        <v>6</v>
+      </c>
+      <c r="F28" s="33"/>
+      <c r="G28" s="85" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="2:7">
-      <c r="B26" s="98" t="s">
+    <row r="29" spans="2:7">
+      <c r="B29" s="96" t="s">
         <v>66</v>
       </c>
-      <c r="C26" s="105"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="35">
+      <c r="C29" s="97"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="33">
         <v>2</v>
       </c>
-      <c r="F26" s="57"/>
-      <c r="G26" s="6" t="s">
+      <c r="F29" s="33"/>
+      <c r="G29" s="85" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="2:7">
-      <c r="B27" s="114" t="s">
+    <row r="30" spans="2:7">
+      <c r="B30" s="96" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" s="97"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="33">
+        <v>2</v>
+      </c>
+      <c r="F30" s="33">
+        <v>2</v>
+      </c>
+      <c r="G30" s="85" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7">
+      <c r="B31" s="96" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" s="104"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="33">
+        <f>SUM(E32)</f>
+        <v>2</v>
+      </c>
+      <c r="F31" s="33"/>
+      <c r="G31" s="85" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7">
+      <c r="B32" s="156" t="s">
+        <v>101</v>
+      </c>
+      <c r="C32" s="157"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="33">
+        <v>2</v>
+      </c>
+      <c r="F32" s="33"/>
+      <c r="G32" s="85" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="115"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="35"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="6" t="s">
+      <c r="C33" s="103"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="85" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B28" s="110" t="s">
+    <row r="34" spans="2:7">
+      <c r="B34" s="154" t="s">
         <v>66</v>
       </c>
-      <c r="C28" s="111"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="37">
+      <c r="C34" s="155"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="34">
         <v>2</v>
       </c>
-      <c r="F28" s="57"/>
-      <c r="G28" s="7" t="s">
+      <c r="F34" s="34"/>
+      <c r="G34" s="57" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B29" s="112" t="s">
+    <row r="35" spans="2:7">
+      <c r="B35" s="96" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" s="97"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="57" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="102" t="s">
+        <v>100</v>
+      </c>
+      <c r="C36" s="103"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="57" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="154" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37" s="155"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="33">
+        <v>2</v>
+      </c>
+      <c r="F37" s="33"/>
+      <c r="G37" s="57" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B38" s="94" t="s">
+        <v>98</v>
+      </c>
+      <c r="C38" s="95"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="34">
+        <v>2</v>
+      </c>
+      <c r="F38" s="34"/>
+      <c r="G38" s="57" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B39" s="100" t="s">
         <v>34</v>
       </c>
-      <c r="C29" s="113"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="40">
-        <f>SUM(E3+E12+E19+E22)</f>
+      <c r="C39" s="101"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="38">
+        <f>SUM(E3+E13+E20+E25)</f>
         <v>33</v>
       </c>
-      <c r="F29" s="64">
-        <f>SUM(F3+F12+F19+F22)</f>
+      <c r="F39" s="38">
+        <f>SUM(F3+F13+F20+F25)</f>
         <v>12</v>
       </c>
-      <c r="G29" s="90"/>
+      <c r="G39" s="158"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="B18:C18"/>
+  <mergeCells count="40">
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="I7:M7"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B19:C19"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="I7:M7"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="E12 E3" formulaRange="1"/>
+    <ignoredError sqref="E13 E3" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3459,61 +3758,61 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF80DA5A-1B69-4377-A99E-364B8197EABC}">
   <dimension ref="B1:L21"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="8" max="8" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="19.5" thickBot="1"/>
-    <row r="2" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B2" s="141" t="s">
+    <row r="1" spans="2:12" ht="18.600000000000001" thickBot="1"/>
+    <row r="2" spans="2:12" ht="18.600000000000001" thickBot="1">
+      <c r="B2" s="143" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="142"/>
+      <c r="C2" s="144"/>
       <c r="D2" s="10" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="41" t="s">
+      <c r="F2" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="41" t="s">
+      <c r="G2" s="39" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B3" s="143" t="s">
+    <row r="3" spans="2:12" ht="18.600000000000001" thickBot="1">
+      <c r="B3" s="139" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="144"/>
+      <c r="C3" s="140"/>
       <c r="D3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="40">
+      <c r="E3" s="38">
         <f>SUM(E4)</f>
         <v>3</v>
       </c>
-      <c r="F3" s="65">
+      <c r="F3" s="60">
         <f>SUM(F4)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="J3" s="50" t="s">
+      <c r="J3" s="48" t="s">
         <v>74</v>
       </c>
-      <c r="K3" s="53">
+      <c r="K3" s="51">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
-      </c>
-      <c r="L3" s="41" t="s">
+        <v>46304</v>
+      </c>
+      <c r="L3" s="39" t="s">
         <v>83</v>
       </c>
     </row>
@@ -3522,297 +3821,297 @@
         <v>71</v>
       </c>
       <c r="C4" s="146"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="83">
+      <c r="D4" s="77"/>
+      <c r="E4" s="78">
         <v>3</v>
       </c>
-      <c r="F4" s="81">
+      <c r="F4" s="76">
         <f>SUM(F6)</f>
         <v>0</v>
       </c>
-      <c r="G4" s="84" t="s">
+      <c r="G4" s="79" t="s">
         <v>80</v>
       </c>
-      <c r="J4" s="54" t="s">
+      <c r="J4" s="52" t="s">
         <v>77</v>
       </c>
-      <c r="K4" s="51">
+      <c r="K4" s="49">
         <v>46310</v>
       </c>
-      <c r="L4" s="47" t="str">
+      <c r="L4" s="45" t="str">
         <f ca="1">SUM($L4-I1)&amp; "日"</f>
         <v>15日</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B5" s="118" t="s">
+    <row r="5" spans="2:12" ht="18.600000000000001" thickBot="1">
+      <c r="B5" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="137"/>
+      <c r="C5" s="121"/>
       <c r="D5" s="8"/>
-      <c r="E5" s="36">
+      <c r="E5" s="34">
         <v>3</v>
       </c>
-      <c r="F5" s="71"/>
-      <c r="G5" s="60"/>
-      <c r="J5" s="55" t="s">
+      <c r="F5" s="66"/>
+      <c r="G5" s="57"/>
+      <c r="J5" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="K5" s="51">
+      <c r="K5" s="49">
         <v>46313</v>
       </c>
-      <c r="L5" s="47" t="str">
+      <c r="L5" s="45" t="str">
         <f ca="1">SUM($L5-I1)&amp; "日"</f>
         <v>18日</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B6" s="143" t="s">
+    <row r="6" spans="2:12" ht="18.600000000000001" thickBot="1">
+      <c r="B6" s="139" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="144"/>
+      <c r="C6" s="140"/>
       <c r="D6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="40">
+      <c r="E6" s="38">
         <f>SUM(E7)</f>
         <v>3</v>
       </c>
-      <c r="F6" s="65">
+      <c r="F6" s="60">
         <f t="shared" ref="F6" si="0">SUM(F7)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="41" t="s">
+      <c r="G6" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="J6" s="56" t="s">
+      <c r="J6" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="K6" s="52">
+      <c r="K6" s="50">
         <v>46314</v>
       </c>
-      <c r="L6" s="48" t="str">
+      <c r="L6" s="46" t="str">
         <f ca="1">SUM(K6-K3)&amp; "日"</f>
-        <v>11日</v>
+        <v>10日</v>
       </c>
     </row>
     <row r="7" spans="2:12">
-      <c r="B7" s="149" t="s">
+      <c r="B7" s="137" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="150"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="68">
+      <c r="C7" s="138"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="63">
         <v>3</v>
       </c>
-      <c r="F7" s="81">
+      <c r="F7" s="76">
         <f>SUM(F9)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="69" t="s">
+      <c r="G7" s="64" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B8" s="118" t="s">
+    <row r="8" spans="2:12" ht="18.600000000000001" thickBot="1">
+      <c r="B8" s="94" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="137"/>
+      <c r="C8" s="121"/>
       <c r="D8" s="8"/>
-      <c r="E8" s="36">
+      <c r="E8" s="34">
         <v>3</v>
       </c>
-      <c r="F8" s="71"/>
-      <c r="G8" s="60"/>
+      <c r="F8" s="66"/>
+      <c r="G8" s="57"/>
       <c r="J8" s="4"/>
-      <c r="K8" s="58"/>
-      <c r="L8" s="59"/>
-    </row>
-    <row r="9" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B9" s="143" t="s">
+      <c r="K8" s="55"/>
+      <c r="L8" s="56"/>
+    </row>
+    <row r="9" spans="2:12" ht="18.600000000000001" thickBot="1">
+      <c r="B9" s="139" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="144"/>
+      <c r="C9" s="140"/>
       <c r="D9" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="40">
+      <c r="E9" s="38">
         <f>SUM(E10:E11)</f>
         <v>5</v>
       </c>
-      <c r="F9" s="65">
+      <c r="F9" s="60">
         <f>SUM(F10:F11)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="41" t="s">
+      <c r="G9" s="39" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="10" spans="2:12">
-      <c r="B10" s="126" t="s">
+      <c r="B10" s="131" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="147"/>
+      <c r="C10" s="141"/>
       <c r="D10" s="9"/>
-      <c r="E10" s="39">
+      <c r="E10" s="37">
         <v>3</v>
       </c>
-      <c r="F10" s="49"/>
-      <c r="G10" s="45" t="s">
+      <c r="F10" s="47"/>
+      <c r="G10" s="43" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B11" s="122" t="s">
+    <row r="11" spans="2:12" ht="18.600000000000001" thickBot="1">
+      <c r="B11" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="148"/>
+      <c r="C11" s="142"/>
       <c r="D11" s="8"/>
-      <c r="E11" s="36">
+      <c r="E11" s="34">
         <v>2</v>
       </c>
-      <c r="F11" s="71"/>
-      <c r="G11" s="60" t="s">
+      <c r="F11" s="66"/>
+      <c r="G11" s="57" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B12" s="143" t="s">
+    <row r="12" spans="2:12" ht="18.600000000000001" thickBot="1">
+      <c r="B12" s="139" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="144"/>
+      <c r="C12" s="140"/>
       <c r="D12" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="40">
+      <c r="E12" s="38">
         <f>SUM(E13)</f>
         <v>2</v>
       </c>
-      <c r="F12" s="65">
+      <c r="F12" s="60">
         <f>SUM(F14+F17)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="41" t="s">
+      <c r="G12" s="39" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B13" s="149" t="s">
+    <row r="13" spans="2:12" ht="18.600000000000001" thickBot="1">
+      <c r="B13" s="137" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="150"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="68">
+      <c r="C13" s="138"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="63">
         <v>2</v>
       </c>
-      <c r="F13" s="70"/>
-      <c r="G13" s="69" t="s">
+      <c r="F13" s="65"/>
+      <c r="G13" s="64" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B14" s="143" t="s">
+    <row r="14" spans="2:12" ht="18.600000000000001" thickBot="1">
+      <c r="B14" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="144"/>
+      <c r="C14" s="140"/>
       <c r="D14" s="10"/>
-      <c r="E14" s="40">
+      <c r="E14" s="38">
         <f>SUM(E15:E16)</f>
         <v>2</v>
       </c>
-      <c r="F14" s="65">
+      <c r="F14" s="60">
         <f>SUM(F15:F16)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="41" t="s">
+      <c r="G14" s="39" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="15" spans="2:12">
-      <c r="B15" s="126" t="s">
+      <c r="B15" s="131" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="147"/>
+      <c r="C15" s="141"/>
       <c r="D15" s="9"/>
-      <c r="E15" s="39">
+      <c r="E15" s="37">
         <v>1</v>
       </c>
-      <c r="F15" s="49"/>
-      <c r="G15" s="45" t="s">
+      <c r="F15" s="47"/>
+      <c r="G15" s="43" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B16" s="122" t="s">
+    <row r="16" spans="2:12" ht="18.600000000000001" thickBot="1">
+      <c r="B16" s="129" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="148"/>
+      <c r="C16" s="142"/>
       <c r="D16" s="8"/>
-      <c r="E16" s="36">
+      <c r="E16" s="34">
         <v>1</v>
       </c>
-      <c r="F16" s="71"/>
-      <c r="G16" s="60" t="s">
+      <c r="F16" s="66"/>
+      <c r="G16" s="57" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B17" s="143" t="s">
+    <row r="17" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B17" s="139" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="144"/>
+      <c r="C17" s="140"/>
       <c r="D17" s="10"/>
-      <c r="E17" s="40">
+      <c r="E17" s="38">
         <f>SUM(E18:E19)</f>
         <v>2</v>
       </c>
-      <c r="F17" s="65">
+      <c r="F17" s="60">
         <f>SUM(F18:F19)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="41" t="s">
+      <c r="G17" s="39" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="126" t="s">
+      <c r="B18" s="131" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="147"/>
+      <c r="C18" s="141"/>
       <c r="D18" s="9"/>
-      <c r="E18" s="39">
+      <c r="E18" s="37">
         <v>1</v>
       </c>
-      <c r="F18" s="49"/>
-      <c r="G18" s="45" t="s">
+      <c r="F18" s="47"/>
+      <c r="G18" s="43" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B19" s="151" t="s">
+    <row r="19" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B19" s="133" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="152"/>
+      <c r="C19" s="134"/>
       <c r="D19" s="7"/>
-      <c r="E19" s="37">
+      <c r="E19" s="35">
         <v>1</v>
       </c>
-      <c r="F19" s="48"/>
-      <c r="G19" s="60" t="s">
+      <c r="F19" s="46"/>
+      <c r="G19" s="57" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B20" s="153" t="s">
+    <row r="20" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B20" s="135" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="154"/>
+      <c r="C20" s="136"/>
       <c r="D20" s="10"/>
-      <c r="E20" s="40">
+      <c r="E20" s="38">
         <f>SUM(E3+E6+E9+E12+E14+E17)</f>
         <v>17</v>
       </c>
-      <c r="F20" s="40">
+      <c r="F20" s="38">
         <f>SUM(F3+F6+F9+F12+F14+F17)</f>
         <v>0</v>
       </c>
@@ -3823,6 +4122,18 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B13:C13"/>
@@ -3830,18 +4141,6 @@
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B8:C8"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3851,18 +4150,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D63B4141-FE5F-4FCB-9F3D-2486D26F1F00}">
   <dimension ref="B1:K12"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="155" t="s">
+      <c r="C1" s="147" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="155"/>
-      <c r="G1" s="155"/>
-    </row>
-    <row r="2" spans="2:11" ht="19.5" thickBot="1">
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+    </row>
+    <row r="2" spans="2:11" ht="18.600000000000001" thickBot="1">
       <c r="B2" s="27" t="s">
         <v>15</v>
       </c>
@@ -3927,19 +4226,19 @@
         <f t="shared" ref="D4:H4" si="1">SUM(C4)+1</f>
         <v>46273</v>
       </c>
-      <c r="E4" s="42">
+      <c r="E4" s="40">
         <f t="shared" si="1"/>
         <v>46274</v>
       </c>
-      <c r="F4" s="42">
+      <c r="F4" s="40">
         <f t="shared" si="1"/>
         <v>46275</v>
       </c>
-      <c r="G4" s="42">
+      <c r="G4" s="40">
         <f t="shared" si="1"/>
         <v>46276</v>
       </c>
-      <c r="H4" s="43">
+      <c r="H4" s="41">
         <f t="shared" si="1"/>
         <v>46277</v>
       </c>
@@ -3949,31 +4248,31 @@
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="44">
+      <c r="B5" s="42">
         <f>SUM(H4)+1</f>
         <v>46278</v>
       </c>
-      <c r="C5" s="42">
+      <c r="C5" s="40">
         <f>SUM(B5)+1</f>
         <v>46279</v>
       </c>
-      <c r="D5" s="42">
+      <c r="D5" s="40">
         <f t="shared" ref="D5:H5" si="2">SUM(C5)+1</f>
         <v>46280</v>
       </c>
-      <c r="E5" s="42">
+      <c r="E5" s="40">
         <f t="shared" si="2"/>
         <v>46281</v>
       </c>
-      <c r="F5" s="42">
+      <c r="F5" s="40">
         <f t="shared" si="2"/>
         <v>46282</v>
       </c>
-      <c r="G5" s="42">
+      <c r="G5" s="40">
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="H5" s="43">
+      <c r="H5" s="41">
         <f t="shared" si="2"/>
         <v>46284</v>
       </c>
@@ -3983,31 +4282,31 @@
       </c>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" s="44">
+      <c r="B6" s="42">
         <f>SUM(H5)+1</f>
         <v>46285</v>
       </c>
-      <c r="C6" s="42">
+      <c r="C6" s="40">
         <f>SUM(B6)+1</f>
         <v>46286</v>
       </c>
-      <c r="D6" s="42">
+      <c r="D6" s="40">
         <f t="shared" ref="D6:H6" si="3">SUM(C6)+1</f>
         <v>46287</v>
       </c>
-      <c r="E6" s="42">
+      <c r="E6" s="40">
         <f t="shared" si="3"/>
         <v>46288</v>
       </c>
-      <c r="F6" s="42">
+      <c r="F6" s="40">
         <f t="shared" si="3"/>
         <v>46289</v>
       </c>
-      <c r="G6" s="42">
+      <c r="G6" s="40">
         <f t="shared" si="3"/>
         <v>46290</v>
       </c>
-      <c r="H6" s="43">
+      <c r="H6" s="41">
         <f t="shared" si="3"/>
         <v>46291</v>
       </c>
@@ -4016,67 +4315,71 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B7" s="61">
+    <row r="7" spans="2:11" ht="18.600000000000001" thickBot="1">
+      <c r="B7" s="58">
         <f>SUM(H6)+1</f>
         <v>46292</v>
       </c>
-      <c r="C7" s="62">
+      <c r="C7" s="59">
         <f>SUM(B7)+1</f>
         <v>46293</v>
       </c>
-      <c r="D7" s="62">
+      <c r="D7" s="59">
         <f t="shared" ref="D7:E7" si="4">SUM(C7)+1</f>
         <v>46294</v>
       </c>
-      <c r="E7" s="62">
+      <c r="E7" s="59">
         <f t="shared" si="4"/>
         <v>46295</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="2"/>
+      <c r="J7" s="171"/>
+      <c r="K7" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="8" spans="2:11">
       <c r="B8" s="24"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="30">
+      <c r="F8" s="169">
         <f>SUM(E7)+1</f>
         <v>46296</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="169">
         <f>SUM(F8)+1</f>
         <v>46297</v>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="170">
         <f>SUM(G8)+1</f>
         <v>46298</v>
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="19">
+      <c r="B9" s="42">
         <f>SUM(H8)+1</f>
         <v>46299</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="40">
         <f>SUM(B9)+1</f>
         <v>46300</v>
       </c>
-      <c r="D9" s="42">
+      <c r="D9" s="40">
         <f t="shared" ref="D9:H9" si="5">SUM(C9)+1</f>
         <v>46301</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="40">
         <f t="shared" si="5"/>
         <v>46302</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="40">
         <f t="shared" si="5"/>
         <v>46303</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="40">
         <f t="shared" si="5"/>
         <v>46304</v>
       </c>
@@ -4110,17 +4413,17 @@
         <f t="shared" si="7"/>
         <v>46311</v>
       </c>
-      <c r="H10" s="85">
+      <c r="H10" s="80">
         <f>SUM(G10)+1</f>
         <v>46312</v>
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="46">
+      <c r="B11" s="44">
         <f t="shared" si="6"/>
         <v>46313</v>
       </c>
-      <c r="C11" s="34">
+      <c r="C11" s="32">
         <f>SUM(B11)+1</f>
         <v>46314</v>
       </c>
@@ -4140,13 +4443,13 @@
         <f t="shared" ref="G11" si="9">SUM(F11)+1</f>
         <v>46318</v>
       </c>
-      <c r="H11" s="32">
+      <c r="H11" s="30">
         <f>SUM(G11)+1</f>
         <v>46319</v>
       </c>
     </row>
-    <row r="12" spans="2:11" ht="19.5" thickBot="1">
-      <c r="B12" s="33">
+    <row r="12" spans="2:11" ht="18.600000000000001" thickBot="1">
+      <c r="B12" s="31">
         <f t="shared" si="6"/>
         <v>46320</v>
       </c>
@@ -4187,7 +4490,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F8B42D-C760-44A9-BC69-9B00588EFF82}">
   <dimension ref="B2:B14"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" t="s">

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\OneDrive\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13F372F0-C6DC-4080-9C55-3053C54C1A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6FB84F0-B4F9-4CC4-ABDA-D77921C8F97D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="599" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="109">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -684,13 +684,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ー　効果音</t>
-    <rPh sb="2" eb="5">
-      <t>コウカオン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>合計</t>
     <rPh sb="0" eb="2">
       <t>ゴウケイ</t>
@@ -723,6 +716,18 @@
     <rPh sb="0" eb="3">
       <t>テイシュツビ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー　ボタン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー　BGM</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1495,7 +1500,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1692,242 +1697,233 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2234,10 +2230,10 @@
   <sheetData>
     <row r="1" spans="2:19" ht="18.600000000000001" thickBot="1"/>
     <row r="2" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="112" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="127"/>
+      <c r="C2" s="113"/>
       <c r="D2" s="72" t="s">
         <v>9</v>
       </c>
@@ -2252,10 +2248,10 @@
       </c>
     </row>
     <row r="3" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B3" s="90" t="s">
+      <c r="B3" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="123"/>
+      <c r="C3" s="111"/>
       <c r="D3" s="72" t="s">
         <v>12</v>
       </c>
@@ -2275,17 +2271,17 @@
       </c>
       <c r="J3" s="51">
         <f ca="1">TODAY()</f>
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="K3" s="39" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="4" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B4" s="92" t="s">
+      <c r="B4" s="114" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="122"/>
+      <c r="C4" s="115"/>
       <c r="D4" s="82"/>
       <c r="E4" s="37">
         <f>SUM(E5:E7)</f>
@@ -2306,14 +2302,14 @@
       </c>
       <c r="K4" s="60" t="str">
         <f ca="1">SUM($J4-J3)&amp; "日"</f>
-        <v>-9日</v>
+        <v>-11日</v>
       </c>
     </row>
     <row r="5" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B5" s="108" t="s">
+      <c r="B5" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="116"/>
+      <c r="C5" s="117"/>
       <c r="D5" s="74"/>
       <c r="E5" s="33">
         <v>2</v>
@@ -2332,16 +2328,16 @@
       </c>
       <c r="K5" s="69" t="str">
         <f ca="1">SUM(J5-J3)&amp; "日"</f>
-        <v>10日</v>
+        <v>8日</v>
       </c>
       <c r="R5" s="55"/>
       <c r="S5" s="56"/>
     </row>
     <row r="6" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B6" s="108" t="s">
+      <c r="B6" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="116"/>
+      <c r="C6" s="117"/>
       <c r="D6" s="74"/>
       <c r="E6" s="33">
         <v>1</v>
@@ -2356,10 +2352,10 @@
       <c r="S6" s="56"/>
     </row>
     <row r="7" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B7" s="108" t="s">
+      <c r="B7" s="116" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="116"/>
+      <c r="C7" s="117"/>
       <c r="D7" s="74"/>
       <c r="E7" s="33">
         <v>1</v>
@@ -2370,18 +2366,18 @@
       <c r="G7" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="I7" s="160" t="s">
-        <v>103</v>
-      </c>
-      <c r="J7" s="161"/>
+      <c r="I7" s="98" t="s">
+        <v>102</v>
+      </c>
+      <c r="J7" s="99"/>
       <c r="R7" s="55"/>
       <c r="S7" s="56"/>
     </row>
     <row r="8" spans="2:19">
-      <c r="B8" s="96" t="s">
+      <c r="B8" s="102" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="104"/>
+      <c r="C8" s="103"/>
       <c r="D8" s="74"/>
       <c r="E8" s="33">
         <v>2</v>
@@ -2392,19 +2388,19 @@
       <c r="G8" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="I8" s="148" t="s">
+      <c r="I8" s="86" t="s">
         <v>99</v>
       </c>
-      <c r="J8" s="151">
+      <c r="J8" s="89">
         <f>SUM(E3)</f>
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="2:19">
-      <c r="B9" s="96" t="s">
+      <c r="B9" s="102" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="104"/>
+      <c r="C9" s="103"/>
       <c r="D9" s="75"/>
       <c r="E9" s="34">
         <v>2</v>
@@ -2415,19 +2411,19 @@
       <c r="G9" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="I9" s="149" t="s">
+      <c r="I9" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="J9" s="152">
+      <c r="J9" s="90">
         <f>SUM(E16)</f>
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="2:19">
-      <c r="B10" s="96" t="s">
+      <c r="B10" s="102" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="104"/>
+      <c r="C10" s="103"/>
       <c r="D10" s="75"/>
       <c r="E10" s="34">
         <v>2</v>
@@ -2438,19 +2434,19 @@
       <c r="G10" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="I10" s="149" t="s">
+      <c r="I10" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="J10" s="152">
+      <c r="J10" s="90">
         <f>SUM(E26)</f>
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B11" s="105" t="s">
+      <c r="B11" s="106" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="128"/>
+      <c r="C11" s="107"/>
       <c r="D11" s="74"/>
       <c r="E11" s="33">
         <v>1</v>
@@ -2461,19 +2457,19 @@
       <c r="G11" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="I11" s="150" t="s">
+      <c r="I11" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="153">
+      <c r="J11" s="91">
         <f>SUM(E32)</f>
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B12" s="96" t="s">
+      <c r="B12" s="102" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="104"/>
+      <c r="C12" s="103"/>
       <c r="D12" s="74"/>
       <c r="E12" s="33">
         <f>SUM(E13:E15)</f>
@@ -2486,8 +2482,8 @@
       <c r="G12" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="I12" s="159" t="s">
-        <v>102</v>
+      <c r="I12" s="93" t="s">
+        <v>101</v>
       </c>
       <c r="J12" s="83">
         <f>SUM(J8:J11)</f>
@@ -2495,10 +2491,10 @@
       </c>
     </row>
     <row r="13" spans="2:19">
-      <c r="B13" s="112" t="s">
+      <c r="B13" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="118"/>
+      <c r="C13" s="105"/>
       <c r="D13" s="74"/>
       <c r="E13" s="33">
         <v>1</v>
@@ -2511,10 +2507,10 @@
       </c>
     </row>
     <row r="14" spans="2:19">
-      <c r="B14" s="108" t="s">
+      <c r="B14" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="116"/>
+      <c r="C14" s="117"/>
       <c r="D14" s="74"/>
       <c r="E14" s="33">
         <v>1</v>
@@ -2529,10 +2525,10 @@
       <c r="S14" s="56"/>
     </row>
     <row r="15" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B15" s="110" t="s">
+      <c r="B15" s="119" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="117"/>
+      <c r="C15" s="120"/>
       <c r="D15" s="75"/>
       <c r="E15" s="34">
         <v>1</v>
@@ -2545,10 +2541,10 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B16" s="90" t="s">
+      <c r="B16" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="C16" s="123"/>
+      <c r="C16" s="111"/>
       <c r="D16" s="71" t="s">
         <v>11</v>
       </c>
@@ -2564,10 +2560,10 @@
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="92" t="s">
+      <c r="B17" s="114" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="122"/>
+      <c r="C17" s="115"/>
       <c r="D17" s="82"/>
       <c r="E17" s="37">
         <v>3</v>
@@ -2580,10 +2576,10 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="96" t="s">
+      <c r="B18" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="104"/>
+      <c r="C18" s="103"/>
       <c r="D18" s="74"/>
       <c r="E18" s="33">
         <v>3</v>
@@ -2596,10 +2592,10 @@
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="96" t="s">
+      <c r="B19" s="102" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="104"/>
+      <c r="C19" s="103"/>
       <c r="D19" s="74"/>
       <c r="E19" s="33">
         <v>3</v>
@@ -2612,10 +2608,10 @@
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="96" t="s">
+      <c r="B20" s="102" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="104"/>
+      <c r="C20" s="103"/>
       <c r="D20" s="75"/>
       <c r="E20" s="33">
         <v>3</v>
@@ -2628,10 +2624,10 @@
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="96" t="s">
+      <c r="B21" s="102" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="104"/>
+      <c r="C21" s="103"/>
       <c r="D21" s="74"/>
       <c r="E21" s="63">
         <v>1</v>
@@ -2644,10 +2640,10 @@
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="105" t="s">
+      <c r="B22" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="128"/>
+      <c r="C22" s="107"/>
       <c r="D22" s="74"/>
       <c r="E22" s="33"/>
       <c r="F22" s="33">
@@ -2658,10 +2654,10 @@
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="112" t="s">
+      <c r="B23" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="118"/>
+      <c r="C23" s="105"/>
       <c r="D23" s="74"/>
       <c r="E23" s="33">
         <v>1</v>
@@ -2674,10 +2670,10 @@
       </c>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="112" t="s">
+      <c r="B24" s="104" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="118"/>
+      <c r="C24" s="105"/>
       <c r="D24" s="74"/>
       <c r="E24" s="33">
         <v>1</v>
@@ -2690,10 +2686,10 @@
       </c>
     </row>
     <row r="25" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B25" s="119" t="s">
+      <c r="B25" s="121" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="120"/>
+      <c r="C25" s="122"/>
       <c r="D25" s="84"/>
       <c r="E25" s="35">
         <v>1</v>
@@ -2706,10 +2702,10 @@
       </c>
     </row>
     <row r="26" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B26" s="90" t="s">
+      <c r="B26" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="123"/>
+      <c r="C26" s="111"/>
       <c r="D26" s="71" t="s">
         <v>10</v>
       </c>
@@ -2726,10 +2722,10 @@
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="131" t="s">
+      <c r="B27" s="108" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="132"/>
+      <c r="C27" s="109"/>
       <c r="D27" s="82"/>
       <c r="E27" s="37">
         <v>5</v>
@@ -2742,10 +2738,10 @@
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="105" t="s">
+      <c r="B28" s="106" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="128"/>
+      <c r="C28" s="107"/>
       <c r="D28" s="74"/>
       <c r="E28" s="33">
         <f>SUM(E29:E30)</f>
@@ -2760,10 +2756,10 @@
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="112" t="s">
+      <c r="B29" s="104" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="118"/>
+      <c r="C29" s="105"/>
       <c r="D29" s="74"/>
       <c r="E29" s="33">
         <v>2</v>
@@ -2776,10 +2772,10 @@
       </c>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="112" t="s">
+      <c r="B30" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="118"/>
+      <c r="C30" s="105"/>
       <c r="D30" s="74"/>
       <c r="E30" s="33">
         <v>2</v>
@@ -2792,10 +2788,10 @@
       </c>
     </row>
     <row r="31" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B31" s="94" t="s">
+      <c r="B31" s="123" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="121"/>
+      <c r="C31" s="124"/>
       <c r="D31" s="75"/>
       <c r="E31" s="34">
         <v>3</v>
@@ -2808,10 +2804,10 @@
       </c>
     </row>
     <row r="32" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B32" s="90" t="s">
+      <c r="B32" s="110" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="123"/>
+      <c r="C32" s="111"/>
       <c r="D32" s="71" t="s">
         <v>14</v>
       </c>
@@ -2828,10 +2824,10 @@
       </c>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="92" t="s">
+      <c r="B33" s="114" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="122"/>
+      <c r="C33" s="115"/>
       <c r="D33" s="82"/>
       <c r="E33" s="37"/>
       <c r="F33" s="37"/>
@@ -2840,10 +2836,10 @@
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="108" t="s">
+      <c r="B34" s="116" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="116"/>
+      <c r="C34" s="117"/>
       <c r="D34" s="82"/>
       <c r="E34" s="37">
         <v>2</v>
@@ -2856,10 +2852,10 @@
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="102" t="s">
+      <c r="B35" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="124"/>
+      <c r="C35" s="126"/>
       <c r="D35" s="74"/>
       <c r="E35" s="33"/>
       <c r="F35" s="33"/>
@@ -2868,10 +2864,10 @@
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="96" t="s">
+      <c r="B36" s="102" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="104"/>
+      <c r="C36" s="103"/>
       <c r="D36" s="74"/>
       <c r="E36" s="33">
         <v>2</v>
@@ -2884,10 +2880,10 @@
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="96" t="s">
+      <c r="B37" s="102" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="104"/>
+      <c r="C37" s="103"/>
       <c r="D37" s="74"/>
       <c r="E37" s="33">
         <v>2</v>
@@ -2900,10 +2896,10 @@
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="96" t="s">
+      <c r="B38" s="102" t="s">
         <v>93</v>
       </c>
-      <c r="C38" s="104"/>
+      <c r="C38" s="103"/>
       <c r="D38" s="74"/>
       <c r="E38" s="33">
         <v>1</v>
@@ -2916,10 +2912,10 @@
       </c>
     </row>
     <row r="39" spans="2:7">
-      <c r="B39" s="102" t="s">
+      <c r="B39" s="125" t="s">
         <v>5</v>
       </c>
-      <c r="C39" s="124"/>
+      <c r="C39" s="126"/>
       <c r="D39" s="74"/>
       <c r="E39" s="33"/>
       <c r="F39" s="33"/>
@@ -2928,10 +2924,10 @@
       </c>
     </row>
     <row r="40" spans="2:7">
-      <c r="B40" s="125" t="s">
+      <c r="B40" s="127" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="126"/>
+      <c r="C40" s="128"/>
       <c r="D40" s="81"/>
       <c r="E40" s="33">
         <v>2</v>
@@ -2944,10 +2940,10 @@
       </c>
     </row>
     <row r="41" spans="2:7">
-      <c r="B41" s="105" t="s">
+      <c r="B41" s="106" t="s">
         <v>61</v>
       </c>
-      <c r="C41" s="115"/>
+      <c r="C41" s="118"/>
       <c r="D41" s="81"/>
       <c r="E41" s="33">
         <v>3</v>
@@ -2960,10 +2956,10 @@
       </c>
     </row>
     <row r="42" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B42" s="129" t="s">
+      <c r="B42" s="100" t="s">
         <v>93</v>
       </c>
-      <c r="C42" s="130"/>
+      <c r="C42" s="101"/>
       <c r="D42" s="73"/>
       <c r="E42" s="34">
         <v>1</v>
@@ -2976,10 +2972,10 @@
       </c>
     </row>
     <row r="43" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B43" s="100" t="s">
+      <c r="B43" s="164" t="s">
         <v>82</v>
       </c>
-      <c r="C43" s="114"/>
+      <c r="C43" s="166"/>
       <c r="D43" s="71"/>
       <c r="E43" s="38">
         <f>SUM(E3+E16+E26+F32)</f>
@@ -2995,33 +2991,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B14:C14"/>
@@ -3038,6 +3007,33 @@
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B38:C38"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3050,7 +3046,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DBF476-724A-4DAE-8D66-8B0809F96B84}">
-  <dimension ref="B1:M39"/>
+  <dimension ref="B1:M44"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="3" max="3" width="18.09765625" customWidth="1"/>
@@ -3060,10 +3056,10 @@
   <sheetData>
     <row r="1" spans="2:13" ht="18.600000000000001" thickBot="1"/>
     <row r="2" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="112" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="89"/>
+      <c r="C2" s="148"/>
       <c r="D2" s="10" t="s">
         <v>9</v>
       </c>
@@ -3081,17 +3077,17 @@
       </c>
       <c r="J2" s="51">
         <f ca="1">TODAY()</f>
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="K2" s="39" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B3" s="90" t="s">
+      <c r="B3" s="110" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="91"/>
+      <c r="C3" s="134"/>
       <c r="D3" s="10" t="s">
         <v>12</v>
       </c>
@@ -3100,8 +3096,8 @@
         <v>8</v>
       </c>
       <c r="F3" s="38">
-        <f>SUM(F4:F7)</f>
-        <v>9</v>
+        <f>SUM(F4+F6+F12)</f>
+        <v>7</v>
       </c>
       <c r="G3" s="39" t="s">
         <v>80</v>
@@ -3114,14 +3110,14 @@
       </c>
       <c r="K3" s="46" t="str">
         <f ca="1">SUM($J3-J2)&amp; "日"</f>
-        <v>1日</v>
+        <v>-1日</v>
       </c>
     </row>
     <row r="4" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B4" s="92" t="s">
+      <c r="B4" s="114" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="93"/>
+      <c r="C4" s="135"/>
       <c r="D4" s="5"/>
       <c r="E4" s="36">
         <v>2</v>
@@ -3140,14 +3136,14 @@
       </c>
       <c r="K4" s="69" t="str">
         <f ca="1">SUM(J4-J2)&amp; "日"</f>
-        <v>10日</v>
+        <v>8日</v>
       </c>
     </row>
     <row r="5" spans="2:13">
-      <c r="B5" s="98" t="s">
+      <c r="B5" s="149" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="99"/>
+      <c r="C5" s="150"/>
       <c r="D5" s="6"/>
       <c r="E5" s="33">
         <v>2</v>
@@ -3163,10 +3159,10 @@
       <c r="K5" s="56"/>
     </row>
     <row r="6" spans="2:13">
-      <c r="B6" s="96" t="s">
+      <c r="B6" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="97"/>
+      <c r="C6" s="136"/>
       <c r="D6" s="6"/>
       <c r="E6" s="33">
         <v>2</v>
@@ -3182,125 +3178,138 @@
       <c r="K6" s="56"/>
     </row>
     <row r="7" spans="2:13">
-      <c r="B7" s="94" t="s">
+      <c r="B7" s="123" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="95"/>
+      <c r="C7" s="132"/>
       <c r="D7" s="8"/>
       <c r="E7" s="34">
         <f>SUM(E8+E9+E10+E11)</f>
         <v>2</v>
       </c>
-      <c r="F7" s="34"/>
+      <c r="F7" s="34">
+        <f>SUM(F8:F11)</f>
+        <v>2</v>
+      </c>
       <c r="G7" s="85" t="s">
         <v>80</v>
       </c>
-      <c r="I7" s="107" t="s">
+      <c r="I7" s="133" t="s">
         <v>88</v>
       </c>
-      <c r="J7" s="107"/>
-      <c r="K7" s="107"/>
-      <c r="L7" s="107"/>
-      <c r="M7" s="107"/>
+      <c r="J7" s="133"/>
+      <c r="K7" s="133"/>
+      <c r="L7" s="133"/>
+      <c r="M7" s="133"/>
     </row>
     <row r="8" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B8" s="108" t="s">
+      <c r="B8" s="116" t="s">
         <v>89</v>
       </c>
-      <c r="C8" s="109"/>
+      <c r="C8" s="138"/>
       <c r="D8" s="6"/>
       <c r="E8" s="33">
         <v>0.5</v>
       </c>
-      <c r="F8" s="33"/>
+      <c r="F8" s="33">
+        <v>0.5</v>
+      </c>
       <c r="G8" s="85" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B9" s="108" t="s">
+      <c r="B9" s="116" t="s">
         <v>90</v>
       </c>
-      <c r="C9" s="109"/>
+      <c r="C9" s="138"/>
       <c r="D9" s="6"/>
       <c r="E9" s="33">
         <v>0.5</v>
       </c>
-      <c r="F9" s="33"/>
+      <c r="F9" s="33">
+        <v>0.5</v>
+      </c>
       <c r="G9" s="85" t="s">
-        <v>80</v>
-      </c>
-      <c r="I9" s="162" t="s">
-        <v>104</v>
-      </c>
-      <c r="J9" s="163"/>
+        <v>84</v>
+      </c>
+      <c r="I9" s="140" t="s">
+        <v>103</v>
+      </c>
+      <c r="J9" s="141"/>
     </row>
     <row r="10" spans="2:13">
-      <c r="B10" s="108" t="s">
+      <c r="B10" s="116" t="s">
         <v>91</v>
       </c>
-      <c r="C10" s="109"/>
+      <c r="C10" s="138"/>
       <c r="D10" s="6"/>
       <c r="E10" s="33">
         <v>0.5</v>
       </c>
-      <c r="F10" s="33"/>
+      <c r="F10" s="33">
+        <v>0.5</v>
+      </c>
       <c r="G10" s="85" t="s">
-        <v>80</v>
-      </c>
-      <c r="I10" s="148" t="s">
+        <v>84</v>
+      </c>
+      <c r="I10" s="86" t="s">
         <v>99</v>
       </c>
-      <c r="J10" s="151">
+      <c r="J10" s="89">
         <f>SUM(F3+E28)</f>
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="2:13">
-      <c r="B11" s="110" t="s">
+      <c r="B11" s="119" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="111"/>
+      <c r="C11" s="139"/>
       <c r="D11" s="8"/>
       <c r="E11" s="34">
         <v>0.5</v>
       </c>
-      <c r="F11" s="34"/>
+      <c r="F11" s="33">
+        <v>0.5</v>
+      </c>
       <c r="G11" s="57" t="s">
         <v>80</v>
       </c>
-      <c r="I11" s="149" t="s">
+      <c r="I11" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="J11" s="152">
+      <c r="J11" s="90">
         <f>SUM(E13)</f>
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B12" s="165" t="s">
-        <v>105</v>
-      </c>
-      <c r="C12" s="166"/>
+      <c r="B12" s="142" t="s">
+        <v>104</v>
+      </c>
+      <c r="C12" s="143"/>
       <c r="D12" s="7"/>
       <c r="E12" s="35">
         <v>4</v>
       </c>
       <c r="F12" s="35"/>
-      <c r="G12" s="164"/>
-      <c r="I12" s="149" t="s">
+      <c r="G12" s="57" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="J12" s="152">
+      <c r="J12" s="90">
         <f>SUM(E20)</f>
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B13" s="90" t="s">
+      <c r="B13" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="91"/>
+      <c r="C13" s="134"/>
       <c r="D13" s="10" t="s">
         <v>11</v>
       </c>
@@ -3315,19 +3324,19 @@
       <c r="G13" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="I13" s="150" t="s">
+      <c r="I13" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="J13" s="153">
+      <c r="J13" s="91">
         <f>SUM(E25)</f>
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B14" s="92" t="s">
+      <c r="B14" s="114" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="93"/>
+      <c r="C14" s="135"/>
       <c r="D14" s="9"/>
       <c r="E14" s="37">
         <v>2</v>
@@ -3338,19 +3347,19 @@
       <c r="G14" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="I14" s="159" t="s">
-        <v>102</v>
+      <c r="I14" s="93" t="s">
+        <v>101</v>
       </c>
       <c r="J14" s="83">
         <f>SUM(J10:J13)</f>
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="2:13">
-      <c r="B15" s="96" t="s">
+      <c r="B15" s="102" t="s">
         <v>94</v>
       </c>
-      <c r="C15" s="97"/>
+      <c r="C15" s="136"/>
       <c r="D15" s="9"/>
       <c r="E15" s="37">
         <v>4</v>
@@ -3361,10 +3370,10 @@
       </c>
     </row>
     <row r="16" spans="2:13">
-      <c r="B16" s="96" t="s">
+      <c r="B16" s="102" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="97"/>
+      <c r="C16" s="136"/>
       <c r="D16" s="6"/>
       <c r="E16" s="33">
         <v>3</v>
@@ -3377,10 +3386,10 @@
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="105" t="s">
+      <c r="B17" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="106"/>
+      <c r="C17" s="137"/>
       <c r="D17" s="6"/>
       <c r="E17" s="33">
         <v>2</v>
@@ -3391,10 +3400,10 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="112" t="s">
+      <c r="B18" s="104" t="s">
         <v>89</v>
       </c>
-      <c r="C18" s="113"/>
+      <c r="C18" s="151"/>
       <c r="D18" s="6"/>
       <c r="E18" s="33">
         <v>1</v>
@@ -3405,10 +3414,10 @@
       </c>
     </row>
     <row r="19" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B19" s="86" t="s">
+      <c r="B19" s="144" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="87"/>
+      <c r="C19" s="145"/>
       <c r="D19" s="8"/>
       <c r="E19" s="34">
         <v>1</v>
@@ -3419,10 +3428,10 @@
       </c>
     </row>
     <row r="20" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B20" s="90" t="s">
+      <c r="B20" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="91"/>
+      <c r="C20" s="134"/>
       <c r="D20" s="10" t="s">
         <v>10</v>
       </c>
@@ -3431,18 +3440,18 @@
         <v>3</v>
       </c>
       <c r="F20" s="38">
-        <f>SUM(F21:F22)</f>
-        <v>0</v>
+        <f>SUM(F21:F24)</f>
+        <v>6</v>
       </c>
       <c r="G20" s="39" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="105" t="s">
+      <c r="B21" s="106" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="106"/>
+      <c r="C21" s="137"/>
       <c r="D21" s="6"/>
       <c r="E21" s="33">
         <v>1</v>
@@ -3453,10 +3462,10 @@
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="86" t="s">
+      <c r="B22" s="144" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="87"/>
+      <c r="C22" s="145"/>
       <c r="D22" s="8"/>
       <c r="E22" s="34">
         <v>2</v>
@@ -3467,39 +3476,51 @@
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="94" t="s">
+      <c r="B23" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="121"/>
+      <c r="C23" s="124"/>
       <c r="D23" s="8"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="57"/>
+      <c r="E23" s="34">
+        <v>5</v>
+      </c>
+      <c r="F23" s="34">
+        <v>5</v>
+      </c>
+      <c r="G23" s="57" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="24" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B24" s="167" t="s">
+      <c r="B24" s="146" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="168"/>
+      <c r="C24" s="147"/>
       <c r="D24" s="7"/>
-      <c r="E24" s="35"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="164"/>
+      <c r="E24" s="35">
+        <v>1</v>
+      </c>
+      <c r="F24" s="35">
+        <v>1</v>
+      </c>
+      <c r="G24" s="57" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="25" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B25" s="90" t="s">
+      <c r="B25" s="110" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="91"/>
+      <c r="C25" s="134"/>
       <c r="D25" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E25" s="38">
-        <f>SUM(E26+E27+E29+E34)</f>
+        <f>SUM(E26+E27+E29+E39)</f>
         <v>11</v>
       </c>
       <c r="F25" s="38">
-        <f>SUM(F26+F29+F34)</f>
+        <f>SUM(F26+F29+F39)</f>
         <v>0</v>
       </c>
       <c r="G25" s="39" t="s">
@@ -3507,10 +3528,10 @@
       </c>
     </row>
     <row r="26" spans="2:7">
-      <c r="B26" s="92" t="s">
+      <c r="B26" s="114" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="93"/>
+      <c r="C26" s="135"/>
       <c r="D26" s="9"/>
       <c r="E26" s="37">
         <v>5</v>
@@ -3521,10 +3542,10 @@
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="96" t="s">
+      <c r="B27" s="102" t="s">
         <v>96</v>
       </c>
-      <c r="C27" s="97"/>
+      <c r="C27" s="136"/>
       <c r="D27" s="9"/>
       <c r="E27" s="37">
         <v>2</v>
@@ -3535,15 +3556,15 @@
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="102" t="s">
+      <c r="B28" s="125" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="103"/>
+      <c r="C28" s="129"/>
       <c r="D28" s="6" t="s">
         <v>97</v>
       </c>
       <c r="E28" s="33">
-        <f>SUM(E29:E31)</f>
+        <f>SUM(E29:E33)</f>
         <v>6</v>
       </c>
       <c r="F28" s="33"/>
@@ -3552,10 +3573,10 @@
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="96" t="s">
+      <c r="B29" s="102" t="s">
         <v>66</v>
       </c>
-      <c r="C29" s="97"/>
+      <c r="C29" s="136"/>
       <c r="D29" s="6"/>
       <c r="E29" s="33">
         <v>2</v>
@@ -3566,10 +3587,10 @@
       </c>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="96" t="s">
+      <c r="B30" s="102" t="s">
         <v>98</v>
       </c>
-      <c r="C30" s="97"/>
+      <c r="C30" s="136"/>
       <c r="D30" s="6"/>
       <c r="E30" s="33">
         <v>2</v>
@@ -3582,133 +3603,212 @@
       </c>
     </row>
     <row r="31" spans="2:7">
-      <c r="B31" s="96" t="s">
-        <v>93</v>
-      </c>
-      <c r="C31" s="104"/>
+      <c r="B31" s="102" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="103"/>
       <c r="D31" s="6"/>
-      <c r="E31" s="33">
-        <f>SUM(E32)</f>
-        <v>2</v>
-      </c>
+      <c r="E31" s="33"/>
       <c r="F31" s="33"/>
-      <c r="G31" s="85" t="s">
-        <v>80</v>
-      </c>
+      <c r="G31" s="85"/>
     </row>
     <row r="32" spans="2:7">
-      <c r="B32" s="156" t="s">
-        <v>101</v>
-      </c>
-      <c r="C32" s="157"/>
+      <c r="B32" s="102" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" s="103"/>
       <c r="D32" s="6"/>
-      <c r="E32" s="33">
-        <v>2</v>
-      </c>
+      <c r="E32" s="33"/>
       <c r="F32" s="33"/>
-      <c r="G32" s="85" t="s">
-        <v>80</v>
-      </c>
+      <c r="G32" s="85"/>
     </row>
     <row r="33" spans="2:7">
       <c r="B33" s="102" t="s">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="C33" s="103"/>
       <c r="D33" s="6"/>
-      <c r="E33" s="33"/>
+      <c r="E33" s="33">
+        <f>SUM(E34)</f>
+        <v>2</v>
+      </c>
       <c r="F33" s="33"/>
       <c r="G33" s="85" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="154" t="s">
+      <c r="B34" s="116" t="s">
+        <v>107</v>
+      </c>
+      <c r="C34" s="117"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="33">
+        <v>2</v>
+      </c>
+      <c r="F34" s="33"/>
+      <c r="G34" s="85" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="B35" s="125" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="129"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="33"/>
+      <c r="F35" s="33"/>
+      <c r="G35" s="85"/>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="130" t="s">
         <v>66</v>
       </c>
-      <c r="C34" s="155"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="34">
-        <v>2</v>
-      </c>
-      <c r="F34" s="34"/>
-      <c r="G34" s="57" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="96" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35" s="97"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="57" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="102" t="s">
-        <v>100</v>
-      </c>
-      <c r="C36" s="103"/>
+      <c r="C36" s="131"/>
       <c r="D36" s="6"/>
       <c r="E36" s="33"/>
       <c r="F36" s="33"/>
-      <c r="G36" s="57" t="s">
+      <c r="G36" s="85"/>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="102" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" s="136"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="33"/>
+      <c r="F37" s="33"/>
+      <c r="G37" s="85"/>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="125" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="129"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="85" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="2:7">
-      <c r="B37" s="154" t="s">
+    <row r="39" spans="2:7">
+      <c r="B39" s="130" t="s">
         <v>66</v>
       </c>
-      <c r="C37" s="155"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="33">
+      <c r="C39" s="131"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="34">
         <v>2</v>
       </c>
-      <c r="F37" s="33"/>
-      <c r="G37" s="57" t="s">
+      <c r="F39" s="34"/>
+      <c r="G39" s="57" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B38" s="94" t="s">
+    <row r="40" spans="2:7">
+      <c r="B40" s="102" t="s">
         <v>98</v>
       </c>
-      <c r="C38" s="95"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="34">
+      <c r="C40" s="136"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="57" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7">
+      <c r="B41" s="125" t="s">
+        <v>100</v>
+      </c>
+      <c r="C41" s="129"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="57" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7">
+      <c r="B42" s="130" t="s">
+        <v>66</v>
+      </c>
+      <c r="C42" s="131"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="33">
         <v>2</v>
       </c>
-      <c r="F38" s="34"/>
-      <c r="G38" s="57" t="s">
+      <c r="F42" s="33"/>
+      <c r="G42" s="57" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="39" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B39" s="100" t="s">
+    <row r="43" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B43" s="123" t="s">
+        <v>98</v>
+      </c>
+      <c r="C43" s="132"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="34">
+        <v>2</v>
+      </c>
+      <c r="F43" s="34"/>
+      <c r="G43" s="57" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B44" s="164" t="s">
         <v>34</v>
       </c>
-      <c r="C39" s="101"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="38">
+      <c r="C44" s="165"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="38">
         <f>SUM(E3+E13+E20+E25)</f>
         <v>33</v>
       </c>
-      <c r="F39" s="38">
+      <c r="F44" s="38">
         <f>SUM(F3+F13+F20+F25)</f>
-        <v>12</v>
-      </c>
-      <c r="G39" s="158"/>
+        <v>16</v>
+      </c>
+      <c r="G44" s="92"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="45">
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
     <mergeCell ref="I7:M7"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
@@ -3722,30 +3822,6 @@
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B18:C18"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3769,10 +3845,10 @@
   <sheetData>
     <row r="1" spans="2:12" ht="18.600000000000001" thickBot="1"/>
     <row r="2" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B2" s="143" t="s">
+      <c r="B2" s="152" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="144"/>
+      <c r="C2" s="153"/>
       <c r="D2" s="10" t="s">
         <v>9</v>
       </c>
@@ -3787,10 +3863,10 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B3" s="139" t="s">
+      <c r="B3" s="154" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="140"/>
+      <c r="C3" s="155"/>
       <c r="D3" s="10" t="s">
         <v>12</v>
       </c>
@@ -3810,17 +3886,17 @@
       </c>
       <c r="K3" s="51">
         <f ca="1">TODAY()</f>
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="L3" s="39" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="4" spans="2:12">
-      <c r="B4" s="145" t="s">
+      <c r="B4" s="156" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="146"/>
+      <c r="C4" s="157"/>
       <c r="D4" s="77"/>
       <c r="E4" s="78">
         <v>3</v>
@@ -3844,10 +3920,10 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B5" s="94" t="s">
+      <c r="B5" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="121"/>
+      <c r="C5" s="124"/>
       <c r="D5" s="8"/>
       <c r="E5" s="34">
         <v>3</v>
@@ -3866,10 +3942,10 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B6" s="139" t="s">
+      <c r="B6" s="154" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="140"/>
+      <c r="C6" s="155"/>
       <c r="D6" s="10" t="s">
         <v>11</v>
       </c>
@@ -3892,14 +3968,14 @@
       </c>
       <c r="L6" s="46" t="str">
         <f ca="1">SUM(K6-K3)&amp; "日"</f>
-        <v>10日</v>
+        <v>8日</v>
       </c>
     </row>
     <row r="7" spans="2:12">
-      <c r="B7" s="137" t="s">
+      <c r="B7" s="160" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="138"/>
+      <c r="C7" s="161"/>
       <c r="D7" s="61"/>
       <c r="E7" s="63">
         <v>3</v>
@@ -3913,10 +3989,10 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B8" s="94" t="s">
+      <c r="B8" s="123" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="121"/>
+      <c r="C8" s="124"/>
       <c r="D8" s="8"/>
       <c r="E8" s="34">
         <v>3</v>
@@ -3928,10 +4004,10 @@
       <c r="L8" s="56"/>
     </row>
     <row r="9" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B9" s="139" t="s">
+      <c r="B9" s="154" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="140"/>
+      <c r="C9" s="155"/>
       <c r="D9" s="10" t="s">
         <v>10</v>
       </c>
@@ -3948,10 +4024,10 @@
       </c>
     </row>
     <row r="10" spans="2:12">
-      <c r="B10" s="131" t="s">
+      <c r="B10" s="108" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="141"/>
+      <c r="C10" s="158"/>
       <c r="D10" s="9"/>
       <c r="E10" s="37">
         <v>3</v>
@@ -3962,10 +4038,10 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B11" s="129" t="s">
+      <c r="B11" s="100" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="142"/>
+      <c r="C11" s="159"/>
       <c r="D11" s="8"/>
       <c r="E11" s="34">
         <v>2</v>
@@ -3976,10 +4052,10 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B12" s="139" t="s">
+      <c r="B12" s="154" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="140"/>
+      <c r="C12" s="155"/>
       <c r="D12" s="10" t="s">
         <v>14</v>
       </c>
@@ -3996,10 +4072,10 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B13" s="137" t="s">
+      <c r="B13" s="160" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="138"/>
+      <c r="C13" s="161"/>
       <c r="D13" s="61"/>
       <c r="E13" s="63">
         <v>2</v>
@@ -4010,10 +4086,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B14" s="139" t="s">
+      <c r="B14" s="154" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="140"/>
+      <c r="C14" s="155"/>
       <c r="D14" s="10"/>
       <c r="E14" s="38">
         <f>SUM(E15:E16)</f>
@@ -4028,10 +4104,10 @@
       </c>
     </row>
     <row r="15" spans="2:12">
-      <c r="B15" s="131" t="s">
+      <c r="B15" s="108" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="141"/>
+      <c r="C15" s="158"/>
       <c r="D15" s="9"/>
       <c r="E15" s="37">
         <v>1</v>
@@ -4042,10 +4118,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B16" s="129" t="s">
+      <c r="B16" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="142"/>
+      <c r="C16" s="159"/>
       <c r="D16" s="8"/>
       <c r="E16" s="34">
         <v>1</v>
@@ -4056,10 +4132,10 @@
       </c>
     </row>
     <row r="17" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B17" s="139" t="s">
+      <c r="B17" s="154" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="140"/>
+      <c r="C17" s="155"/>
       <c r="D17" s="10"/>
       <c r="E17" s="38">
         <f>SUM(E18:E19)</f>
@@ -4074,10 +4150,10 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="131" t="s">
+      <c r="B18" s="108" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="141"/>
+      <c r="C18" s="158"/>
       <c r="D18" s="9"/>
       <c r="E18" s="37">
         <v>1</v>
@@ -4088,10 +4164,10 @@
       </c>
     </row>
     <row r="19" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B19" s="133" t="s">
+      <c r="B19" s="162" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="134"/>
+      <c r="C19" s="163"/>
       <c r="D19" s="7"/>
       <c r="E19" s="35">
         <v>1</v>
@@ -4102,10 +4178,10 @@
       </c>
     </row>
     <row r="20" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B20" s="135" t="s">
+      <c r="B20" s="167" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="136"/>
+      <c r="C20" s="168"/>
       <c r="D20" s="10"/>
       <c r="E20" s="38">
         <f>SUM(E3+E6+E9+E12+E14+E17)</f>
@@ -4122,6 +4198,18 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
@@ -4129,18 +4217,6 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4153,13 +4229,13 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="147" t="s">
+      <c r="C1" s="97" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
     </row>
     <row r="2" spans="2:11" ht="18.600000000000001" thickBot="1">
       <c r="B2" s="27" t="s">
@@ -4335,9 +4411,9 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="2"/>
-      <c r="J7" s="171"/>
+      <c r="J7" s="96"/>
       <c r="K7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="2:11">
@@ -4345,15 +4421,15 @@
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="169">
+      <c r="F8" s="94">
         <f>SUM(E7)+1</f>
         <v>46296</v>
       </c>
-      <c r="G8" s="169">
+      <c r="G8" s="94">
         <f>SUM(F8)+1</f>
         <v>46297</v>
       </c>
-      <c r="H8" s="170">
+      <c r="H8" s="95">
         <f>SUM(G8)+1</f>
         <v>46298</v>
       </c>

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\OneDrive\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6FB84F0-B4F9-4CC4-ABDA-D77921C8F97D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1EFB2AE-1B46-46B8-8296-C41CD8623BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="109">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -1500,7 +1500,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="169">
+  <cellXfs count="171">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1907,6 +1907,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2972,10 +2978,10 @@
       </c>
     </row>
     <row r="43" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B43" s="164" t="s">
+      <c r="B43" s="166" t="s">
         <v>82</v>
       </c>
-      <c r="C43" s="166"/>
+      <c r="C43" s="168"/>
       <c r="D43" s="71"/>
       <c r="E43" s="38">
         <f>SUM(E3+E16+E26+F32)</f>
@@ -3257,8 +3263,8 @@
         <v>99</v>
       </c>
       <c r="J10" s="89">
-        <f>SUM(F3+E28)</f>
-        <v>13</v>
+        <f>SUM(F3+E27+E28)</f>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="2:13">
@@ -3352,7 +3358,7 @@
       </c>
       <c r="J14" s="83">
         <f>SUM(J10:J13)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="2:13">
@@ -3546,7 +3552,9 @@
         <v>96</v>
       </c>
       <c r="C27" s="136"/>
-      <c r="D27" s="9"/>
+      <c r="D27" s="6" t="s">
+        <v>97</v>
+      </c>
       <c r="E27" s="37">
         <v>2</v>
       </c>
@@ -3613,20 +3621,20 @@
       <c r="G31" s="85"/>
     </row>
     <row r="32" spans="2:7">
-      <c r="B32" s="102" t="s">
+      <c r="B32" s="164" t="s">
         <v>108</v>
       </c>
-      <c r="C32" s="103"/>
+      <c r="C32" s="165"/>
       <c r="D32" s="6"/>
       <c r="E32" s="33"/>
       <c r="F32" s="33"/>
       <c r="G32" s="85"/>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="102" t="s">
+      <c r="B33" s="164" t="s">
         <v>106</v>
       </c>
-      <c r="C33" s="103"/>
+      <c r="C33" s="165"/>
       <c r="D33" s="6"/>
       <c r="E33" s="33">
         <f>SUM(E34)</f>
@@ -3760,10 +3768,10 @@
       </c>
     </row>
     <row r="44" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B44" s="164" t="s">
+      <c r="B44" s="166" t="s">
         <v>34</v>
       </c>
-      <c r="C44" s="165"/>
+      <c r="C44" s="167"/>
       <c r="D44" s="10"/>
       <c r="E44" s="38">
         <f>SUM(E3+E13+E20+E25)</f>
@@ -4178,10 +4186,10 @@
       </c>
     </row>
     <row r="20" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B20" s="167" t="s">
+      <c r="B20" s="169" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="168"/>
+      <c r="C20" s="170"/>
       <c r="D20" s="10"/>
       <c r="E20" s="38">
         <f>SUM(E3+E6+E9+E12+E14+E17)</f>

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\OneDrive\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1EFB2AE-1B46-46B8-8296-C41CD8623BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB0FB4B8-3468-40D9-97D8-6BA4D9B7787C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="117">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -719,15 +719,62 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>SE</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ー　ボタン</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ー　BGM</t>
+    <t>(雰囲気づくり)</t>
+    <rPh sb="1" eb="4">
+      <t>フンイキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ロビーライト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スポットライト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>暗闇</t>
+    <rPh sb="0" eb="2">
+      <t>クラヤミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>背景</t>
+    <rPh sb="0" eb="2">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　　　ー　コンティニュー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　　　ー　操作方法</t>
+    <rPh sb="5" eb="9">
+      <t>ソウサホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　　　ー　タイトルに戻る</t>
+    <rPh sb="10" eb="11">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ボタンSE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー　ボタンSE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">               ー　BGM</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1500,7 +1547,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="171">
+  <cellXfs count="198">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1708,226 +1755,305 @@
     <xf numFmtId="56" fontId="0" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2236,10 +2362,10 @@
   <sheetData>
     <row r="1" spans="2:19" ht="18.600000000000001" thickBot="1"/>
     <row r="2" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="113"/>
+      <c r="C2" s="149"/>
       <c r="D2" s="72" t="s">
         <v>9</v>
       </c>
@@ -2254,22 +2380,22 @@
       </c>
     </row>
     <row r="3" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B3" s="110" t="s">
+      <c r="B3" s="107" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="111"/>
-      <c r="D3" s="72" t="s">
+      <c r="C3" s="145"/>
+      <c r="D3" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="38">
+      <c r="E3" s="190">
         <f>SUM(E4:E15)</f>
         <v>21</v>
       </c>
-      <c r="F3" s="38">
+      <c r="F3" s="190">
         <f>SUM(F4:F15)</f>
         <v>23</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="70" t="s">
         <v>84</v>
       </c>
       <c r="I3" s="48" t="s">
@@ -2277,17 +2403,17 @@
       </c>
       <c r="J3" s="51">
         <f ca="1">TODAY()</f>
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="K3" s="39" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="4" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="109" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="115"/>
+      <c r="C4" s="144"/>
       <c r="D4" s="82"/>
       <c r="E4" s="37">
         <f>SUM(E5:E7)</f>
@@ -2308,14 +2434,14 @@
       </c>
       <c r="K4" s="60" t="str">
         <f ca="1">SUM($J4-J3)&amp; "日"</f>
-        <v>-11日</v>
+        <v>-12日</v>
       </c>
     </row>
     <row r="5" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B5" s="116" t="s">
+      <c r="B5" s="124" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="117"/>
+      <c r="C5" s="125"/>
       <c r="D5" s="74"/>
       <c r="E5" s="33">
         <v>2</v>
@@ -2334,16 +2460,16 @@
       </c>
       <c r="K5" s="69" t="str">
         <f ca="1">SUM(J5-J3)&amp; "日"</f>
-        <v>8日</v>
+        <v>7日</v>
       </c>
       <c r="R5" s="55"/>
       <c r="S5" s="56"/>
     </row>
     <row r="6" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B6" s="116" t="s">
+      <c r="B6" s="124" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="117"/>
+      <c r="C6" s="125"/>
       <c r="D6" s="74"/>
       <c r="E6" s="33">
         <v>1</v>
@@ -2358,10 +2484,10 @@
       <c r="S6" s="56"/>
     </row>
     <row r="7" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B7" s="116" t="s">
+      <c r="B7" s="124" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="117"/>
+      <c r="C7" s="125"/>
       <c r="D7" s="74"/>
       <c r="E7" s="33">
         <v>1</v>
@@ -2372,18 +2498,18 @@
       <c r="G7" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="I7" s="98" t="s">
+      <c r="I7" s="151" t="s">
         <v>102</v>
       </c>
-      <c r="J7" s="99"/>
+      <c r="J7" s="152"/>
       <c r="R7" s="55"/>
       <c r="S7" s="56"/>
     </row>
     <row r="8" spans="2:19">
-      <c r="B8" s="102" t="s">
+      <c r="B8" s="113" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="103"/>
+      <c r="C8" s="123"/>
       <c r="D8" s="74"/>
       <c r="E8" s="33">
         <v>2</v>
@@ -2403,10 +2529,10 @@
       </c>
     </row>
     <row r="9" spans="2:19">
-      <c r="B9" s="102" t="s">
+      <c r="B9" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="103"/>
+      <c r="C9" s="123"/>
       <c r="D9" s="75"/>
       <c r="E9" s="34">
         <v>2</v>
@@ -2426,10 +2552,10 @@
       </c>
     </row>
     <row r="10" spans="2:19">
-      <c r="B10" s="102" t="s">
+      <c r="B10" s="113" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="103"/>
+      <c r="C10" s="123"/>
       <c r="D10" s="75"/>
       <c r="E10" s="34">
         <v>2</v>
@@ -2449,10 +2575,10 @@
       </c>
     </row>
     <row r="11" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B11" s="106" t="s">
+      <c r="B11" s="132" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="107"/>
+      <c r="C11" s="150"/>
       <c r="D11" s="74"/>
       <c r="E11" s="33">
         <v>1</v>
@@ -2472,10 +2598,10 @@
       </c>
     </row>
     <row r="12" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B12" s="102" t="s">
+      <c r="B12" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="103"/>
+      <c r="C12" s="123"/>
       <c r="D12" s="74"/>
       <c r="E12" s="33">
         <f>SUM(E13:E15)</f>
@@ -2497,10 +2623,10 @@
       </c>
     </row>
     <row r="13" spans="2:19">
-      <c r="B13" s="104" t="s">
+      <c r="B13" s="117" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="105"/>
+      <c r="C13" s="141"/>
       <c r="D13" s="74"/>
       <c r="E13" s="33">
         <v>1</v>
@@ -2513,10 +2639,10 @@
       </c>
     </row>
     <row r="14" spans="2:19">
-      <c r="B14" s="116" t="s">
+      <c r="B14" s="124" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="117"/>
+      <c r="C14" s="125"/>
       <c r="D14" s="74"/>
       <c r="E14" s="33">
         <v>1</v>
@@ -2531,10 +2657,10 @@
       <c r="S14" s="56"/>
     </row>
     <row r="15" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B15" s="119" t="s">
+      <c r="B15" s="135" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="120"/>
+      <c r="C15" s="140"/>
       <c r="D15" s="75"/>
       <c r="E15" s="34">
         <v>1</v>
@@ -2547,29 +2673,29 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B16" s="110" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="111"/>
-      <c r="D16" s="71" t="s">
+      <c r="B16" s="107" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="145"/>
+      <c r="D16" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="38">
+      <c r="E16" s="190">
         <f>SUM(E17:E25)</f>
         <v>16</v>
       </c>
-      <c r="F16" s="38">
+      <c r="F16" s="190">
         <v>8</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="70" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="114" t="s">
+      <c r="B17" s="109" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="115"/>
+      <c r="C17" s="144"/>
       <c r="D17" s="82"/>
       <c r="E17" s="37">
         <v>3</v>
@@ -2582,10 +2708,10 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="102" t="s">
+      <c r="B18" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="103"/>
+      <c r="C18" s="123"/>
       <c r="D18" s="74"/>
       <c r="E18" s="33">
         <v>3</v>
@@ -2598,10 +2724,10 @@
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="102" t="s">
+      <c r="B19" s="113" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="103"/>
+      <c r="C19" s="123"/>
       <c r="D19" s="74"/>
       <c r="E19" s="33">
         <v>3</v>
@@ -2614,10 +2740,10 @@
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="102" t="s">
+      <c r="B20" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="103"/>
+      <c r="C20" s="123"/>
       <c r="D20" s="75"/>
       <c r="E20" s="33">
         <v>3</v>
@@ -2630,10 +2756,10 @@
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="102" t="s">
+      <c r="B21" s="113" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="103"/>
+      <c r="C21" s="123"/>
       <c r="D21" s="74"/>
       <c r="E21" s="63">
         <v>1</v>
@@ -2646,10 +2772,10 @@
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="106" t="s">
+      <c r="B22" s="132" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="107"/>
+      <c r="C22" s="150"/>
       <c r="D22" s="74"/>
       <c r="E22" s="33"/>
       <c r="F22" s="33">
@@ -2660,10 +2786,10 @@
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="104" t="s">
+      <c r="B23" s="117" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="105"/>
+      <c r="C23" s="141"/>
       <c r="D23" s="74"/>
       <c r="E23" s="33">
         <v>1</v>
@@ -2676,10 +2802,10 @@
       </c>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="104" t="s">
+      <c r="B24" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="105"/>
+      <c r="C24" s="141"/>
       <c r="D24" s="74"/>
       <c r="E24" s="33">
         <v>1</v>
@@ -2692,10 +2818,10 @@
       </c>
     </row>
     <row r="25" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B25" s="121" t="s">
+      <c r="B25" s="142" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="122"/>
+      <c r="C25" s="143"/>
       <c r="D25" s="84"/>
       <c r="E25" s="35">
         <v>1</v>
@@ -2708,30 +2834,30 @@
       </c>
     </row>
     <row r="26" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B26" s="110" t="s">
+      <c r="B26" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="111"/>
-      <c r="D26" s="71" t="s">
+      <c r="C26" s="145"/>
+      <c r="D26" s="97" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="38">
+      <c r="E26" s="190">
         <f>SUM(E27:E31)</f>
         <v>16</v>
       </c>
-      <c r="F26" s="38">
+      <c r="F26" s="190">
         <f>SUM(F27,F28,F31)</f>
         <v>11</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="G26" s="70" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="108" t="s">
+      <c r="B27" s="155" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="109"/>
+      <c r="C27" s="156"/>
       <c r="D27" s="82"/>
       <c r="E27" s="37">
         <v>5</v>
@@ -2744,10 +2870,10 @@
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="106" t="s">
+      <c r="B28" s="132" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="107"/>
+      <c r="C28" s="150"/>
       <c r="D28" s="74"/>
       <c r="E28" s="33">
         <f>SUM(E29:E30)</f>
@@ -2762,10 +2888,10 @@
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="104" t="s">
+      <c r="B29" s="117" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="105"/>
+      <c r="C29" s="141"/>
       <c r="D29" s="74"/>
       <c r="E29" s="33">
         <v>2</v>
@@ -2778,10 +2904,10 @@
       </c>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="104" t="s">
+      <c r="B30" s="117" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="105"/>
+      <c r="C30" s="141"/>
       <c r="D30" s="74"/>
       <c r="E30" s="33">
         <v>2</v>
@@ -2794,10 +2920,10 @@
       </c>
     </row>
     <row r="31" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B31" s="123" t="s">
+      <c r="B31" s="111" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="124"/>
+      <c r="C31" s="128"/>
       <c r="D31" s="75"/>
       <c r="E31" s="34">
         <v>3</v>
@@ -2810,30 +2936,30 @@
       </c>
     </row>
     <row r="32" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B32" s="110" t="s">
+      <c r="B32" s="107" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="111"/>
-      <c r="D32" s="71" t="s">
+      <c r="C32" s="145"/>
+      <c r="D32" s="97" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="38">
+      <c r="E32" s="190">
         <f>SUM(E33:E42)</f>
         <v>13</v>
       </c>
-      <c r="F32" s="38">
+      <c r="F32" s="190">
         <f>SUM(F34,F36,F37,F40,F41)</f>
         <v>5</v>
       </c>
-      <c r="G32" s="10" t="s">
+      <c r="G32" s="70" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="114" t="s">
+      <c r="B33" s="109" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="115"/>
+      <c r="C33" s="144"/>
       <c r="D33" s="82"/>
       <c r="E33" s="37"/>
       <c r="F33" s="37"/>
@@ -2842,10 +2968,10 @@
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="116" t="s">
+      <c r="B34" s="124" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="117"/>
+      <c r="C34" s="125"/>
       <c r="D34" s="82"/>
       <c r="E34" s="37">
         <v>2</v>
@@ -2858,22 +2984,22 @@
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="125" t="s">
+      <c r="B35" s="121" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="126"/>
-      <c r="D35" s="74"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="33"/>
-      <c r="G35" s="6" t="s">
+      <c r="C35" s="146"/>
+      <c r="D35" s="99"/>
+      <c r="E35" s="191"/>
+      <c r="F35" s="191"/>
+      <c r="G35" s="188" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="102" t="s">
+      <c r="B36" s="113" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="103"/>
+      <c r="C36" s="123"/>
       <c r="D36" s="74"/>
       <c r="E36" s="33">
         <v>2</v>
@@ -2886,10 +3012,10 @@
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="102" t="s">
+      <c r="B37" s="113" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="103"/>
+      <c r="C37" s="123"/>
       <c r="D37" s="74"/>
       <c r="E37" s="33">
         <v>2</v>
@@ -2902,10 +3028,10 @@
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="102" t="s">
+      <c r="B38" s="113" t="s">
         <v>93</v>
       </c>
-      <c r="C38" s="103"/>
+      <c r="C38" s="123"/>
       <c r="D38" s="74"/>
       <c r="E38" s="33">
         <v>1</v>
@@ -2918,22 +3044,22 @@
       </c>
     </row>
     <row r="39" spans="2:7">
-      <c r="B39" s="125" t="s">
+      <c r="B39" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="C39" s="126"/>
-      <c r="D39" s="74"/>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
-      <c r="G39" s="6" t="s">
+      <c r="C39" s="146"/>
+      <c r="D39" s="99"/>
+      <c r="E39" s="191"/>
+      <c r="F39" s="191"/>
+      <c r="G39" s="188" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="40" spans="2:7">
-      <c r="B40" s="127" t="s">
+      <c r="B40" s="147" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="128"/>
+      <c r="C40" s="148"/>
       <c r="D40" s="81"/>
       <c r="E40" s="33">
         <v>2</v>
@@ -2946,10 +3072,10 @@
       </c>
     </row>
     <row r="41" spans="2:7">
-      <c r="B41" s="106" t="s">
+      <c r="B41" s="132" t="s">
         <v>61</v>
       </c>
-      <c r="C41" s="118"/>
+      <c r="C41" s="139"/>
       <c r="D41" s="81"/>
       <c r="E41" s="33">
         <v>3</v>
@@ -2962,10 +3088,10 @@
       </c>
     </row>
     <row r="42" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B42" s="100" t="s">
+      <c r="B42" s="153" t="s">
         <v>93</v>
       </c>
-      <c r="C42" s="101"/>
+      <c r="C42" s="154"/>
       <c r="D42" s="73"/>
       <c r="E42" s="34">
         <v>1</v>
@@ -2978,10 +3104,10 @@
       </c>
     </row>
     <row r="43" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B43" s="166" t="s">
+      <c r="B43" s="196" t="s">
         <v>82</v>
       </c>
-      <c r="C43" s="168"/>
+      <c r="C43" s="197"/>
       <c r="D43" s="71"/>
       <c r="E43" s="38">
         <f>SUM(E3+E16+E26+F32)</f>
@@ -2997,6 +3123,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B14:C14"/>
@@ -3013,33 +3166,6 @@
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B38:C38"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3052,20 +3178,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DBF476-724A-4DAE-8D66-8B0809F96B84}">
-  <dimension ref="B1:M44"/>
+  <dimension ref="B1:M50"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="3" max="3" width="18.09765625" customWidth="1"/>
-    <col min="9" max="9" width="19.09765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="18.600000000000001" thickBot="1"/>
     <row r="2" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="105" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="148"/>
+      <c r="C2" s="106"/>
       <c r="D2" s="10" t="s">
         <v>9</v>
       </c>
@@ -3083,29 +3209,29 @@
       </c>
       <c r="J2" s="51">
         <f ca="1">TODAY()</f>
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="K2" s="39" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B3" s="110" t="s">
+      <c r="B3" s="107" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="134"/>
-      <c r="D3" s="10" t="s">
+      <c r="C3" s="108"/>
+      <c r="D3" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="38">
+      <c r="E3" s="190">
         <f>SUM(E4:E7)</f>
         <v>8</v>
       </c>
-      <c r="F3" s="38">
-        <f>SUM(F4+F6+F12)</f>
-        <v>7</v>
-      </c>
-      <c r="G3" s="39" t="s">
+      <c r="F3" s="190">
+        <f>SUM(F4+F6+F13)</f>
+        <v>7.5</v>
+      </c>
+      <c r="G3" s="98" t="s">
         <v>80</v>
       </c>
       <c r="I3" s="62" t="s">
@@ -3116,14 +3242,14 @@
       </c>
       <c r="K3" s="46" t="str">
         <f ca="1">SUM($J3-J2)&amp; "日"</f>
-        <v>-1日</v>
+        <v>-2日</v>
       </c>
     </row>
     <row r="4" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B4" s="114" t="s">
+      <c r="B4" s="109" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="135"/>
+      <c r="C4" s="110"/>
       <c r="D4" s="5"/>
       <c r="E4" s="36">
         <v>2</v>
@@ -3142,14 +3268,14 @@
       </c>
       <c r="K4" s="69" t="str">
         <f ca="1">SUM(J4-J2)&amp; "日"</f>
-        <v>8日</v>
+        <v>7日</v>
       </c>
     </row>
     <row r="5" spans="2:13">
-      <c r="B5" s="149" t="s">
+      <c r="B5" s="115" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="150"/>
+      <c r="C5" s="116"/>
       <c r="D5" s="6"/>
       <c r="E5" s="33">
         <v>2</v>
@@ -3165,10 +3291,10 @@
       <c r="K5" s="56"/>
     </row>
     <row r="6" spans="2:13">
-      <c r="B6" s="102" t="s">
+      <c r="B6" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="136"/>
+      <c r="C6" s="114"/>
       <c r="D6" s="6"/>
       <c r="E6" s="33">
         <v>2</v>
@@ -3184,10 +3310,10 @@
       <c r="K6" s="56"/>
     </row>
     <row r="7" spans="2:13">
-      <c r="B7" s="123" t="s">
+      <c r="B7" s="111" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="132"/>
+      <c r="C7" s="112"/>
       <c r="D7" s="8"/>
       <c r="E7" s="34">
         <f>SUM(E8+E9+E10+E11)</f>
@@ -3195,272 +3321,276 @@
       </c>
       <c r="F7" s="34">
         <f>SUM(F8:F11)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G7" s="85" t="s">
         <v>80</v>
       </c>
-      <c r="I7" s="133" t="s">
+      <c r="I7" s="131" t="s">
         <v>88</v>
       </c>
-      <c r="J7" s="133"/>
-      <c r="K7" s="133"/>
-      <c r="L7" s="133"/>
-      <c r="M7" s="133"/>
+      <c r="J7" s="131"/>
+      <c r="K7" s="131"/>
+      <c r="L7" s="131"/>
+      <c r="M7" s="131"/>
     </row>
     <row r="8" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B8" s="116" t="s">
+      <c r="B8" s="124" t="s">
         <v>89</v>
       </c>
-      <c r="C8" s="138"/>
+      <c r="C8" s="134"/>
       <c r="D8" s="6"/>
       <c r="E8" s="33">
         <v>0.5</v>
       </c>
       <c r="F8" s="33">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G8" s="85" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="9" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B9" s="116" t="s">
+      <c r="B9" s="124" t="s">
         <v>90</v>
       </c>
-      <c r="C9" s="138"/>
+      <c r="C9" s="134"/>
       <c r="D9" s="6"/>
       <c r="E9" s="33">
         <v>0.5</v>
       </c>
       <c r="F9" s="33">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G9" s="85" t="s">
         <v>84</v>
       </c>
-      <c r="I9" s="140" t="s">
+      <c r="I9" s="137" t="s">
         <v>103</v>
       </c>
-      <c r="J9" s="141"/>
+      <c r="J9" s="138"/>
     </row>
     <row r="10" spans="2:13">
-      <c r="B10" s="116" t="s">
+      <c r="B10" s="124" t="s">
         <v>91</v>
       </c>
-      <c r="C10" s="138"/>
+      <c r="C10" s="134"/>
       <c r="D10" s="6"/>
       <c r="E10" s="33">
         <v>0.5</v>
       </c>
       <c r="F10" s="33">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G10" s="85" t="s">
         <v>84</v>
       </c>
-      <c r="I10" s="86" t="s">
+      <c r="I10" s="177" t="s">
         <v>99</v>
       </c>
       <c r="J10" s="89">
-        <f>SUM(F3+E27+E28)</f>
-        <v>15</v>
+        <f>SUM(F3+E31+E38)</f>
+        <v>15.5</v>
       </c>
     </row>
     <row r="11" spans="2:13">
-      <c r="B11" s="119" t="s">
+      <c r="B11" s="135" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="139"/>
+      <c r="C11" s="136"/>
       <c r="D11" s="8"/>
       <c r="E11" s="34">
         <v>0.5</v>
       </c>
       <c r="F11" s="33">
+        <v>1</v>
+      </c>
+      <c r="G11" s="85" t="s">
+        <v>84</v>
+      </c>
+      <c r="I11" s="178" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11" s="90">
+        <f>SUM(E17)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13">
+      <c r="B12" s="124" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="125"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="34">
         <v>0.5</v>
       </c>
-      <c r="G11" s="57" t="s">
+      <c r="F12" s="34">
+        <v>1</v>
+      </c>
+      <c r="G12" s="85" t="s">
+        <v>84</v>
+      </c>
+      <c r="I12" s="178" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="90">
+        <f>SUM(E24)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" ht="18.600000000000001" thickBot="1">
+      <c r="B13" s="111" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="112"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="34">
+        <v>4</v>
+      </c>
+      <c r="F13" s="34">
+        <f>SUM(F14:F16)</f>
+        <v>0.5</v>
+      </c>
+      <c r="G13" s="57" t="s">
         <v>80</v>
       </c>
-      <c r="I11" s="87" t="s">
+      <c r="I13" s="179" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="91">
+        <f>SUM(E29)</f>
         <v>11</v>
       </c>
-      <c r="J11" s="90">
-        <f>SUM(E13)</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B12" s="142" t="s">
-        <v>104</v>
-      </c>
-      <c r="C12" s="143"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="35">
-        <v>4</v>
-      </c>
-      <c r="F12" s="35"/>
-      <c r="G12" s="57" t="s">
+    </row>
+    <row r="14" spans="2:13" ht="18.600000000000001" thickBot="1">
+      <c r="B14" s="174" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="180"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="33">
+        <v>1</v>
+      </c>
+      <c r="F14" s="33"/>
+      <c r="G14" s="57" t="s">
         <v>80</v>
-      </c>
-      <c r="I12" s="87" t="s">
-        <v>10</v>
-      </c>
-      <c r="J12" s="90">
-        <f>SUM(E20)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B13" s="110" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="134"/>
-      <c r="D13" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="38">
-        <f>SUM(E14:E17)</f>
-        <v>11</v>
-      </c>
-      <c r="F13" s="38">
-        <f>SUM(F14:F17)</f>
-        <v>3</v>
-      </c>
-      <c r="G13" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="I13" s="88" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="91">
-        <f>SUM(E25)</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B14" s="114" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" s="135"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="37">
-        <v>2</v>
-      </c>
-      <c r="F14" s="37">
-        <v>1</v>
-      </c>
-      <c r="G14" s="43" t="s">
-        <v>84</v>
       </c>
       <c r="I14" s="93" t="s">
         <v>101</v>
       </c>
       <c r="J14" s="83">
         <f>SUM(J10:J13)</f>
-        <v>40</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="15" spans="2:13">
-      <c r="B15" s="102" t="s">
+      <c r="B15" s="174" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="180"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="33">
+        <v>4</v>
+      </c>
+      <c r="F15" s="33"/>
+      <c r="G15" s="57" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" ht="18.600000000000001" thickBot="1">
+      <c r="B16" s="175" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="181"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="35">
+        <v>1</v>
+      </c>
+      <c r="F16" s="35">
+        <v>0.5</v>
+      </c>
+      <c r="G16" s="102" t="s">
+        <v>84</v>
+      </c>
+      <c r="I16" s="176"/>
+      <c r="J16" s="176"/>
+      <c r="K16" s="176"/>
+    </row>
+    <row r="17" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B17" s="172" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="173"/>
+      <c r="D17" s="193" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="194">
+        <f>SUM(E18:E21)</f>
+        <v>11</v>
+      </c>
+      <c r="F17" s="194">
+        <f>SUM(F18:F21)</f>
+        <v>3</v>
+      </c>
+      <c r="G17" s="195" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="109" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="110"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="37">
+        <v>2</v>
+      </c>
+      <c r="F18" s="37">
+        <v>1</v>
+      </c>
+      <c r="G18" s="43" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="113" t="s">
         <v>94</v>
       </c>
-      <c r="C15" s="136"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="37">
+      <c r="C19" s="114"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="37">
         <v>4</v>
       </c>
-      <c r="F15" s="37"/>
-      <c r="G15" s="43" t="s">
+      <c r="F19" s="37"/>
+      <c r="G19" s="43" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="2:13">
-      <c r="B16" s="102" t="s">
+    <row r="20" spans="2:7">
+      <c r="B20" s="113" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="136"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="33">
+      <c r="C20" s="114"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="33">
         <v>3</v>
       </c>
-      <c r="F16" s="33">
+      <c r="F20" s="33">
         <v>2</v>
       </c>
-      <c r="G16" s="43" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="106" t="s">
+      <c r="G20" s="43" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="132" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="137"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="33">
-        <v>2</v>
-      </c>
-      <c r="F17" s="33"/>
-      <c r="G17" s="85" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="104" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" s="151"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="33">
-        <v>1</v>
-      </c>
-      <c r="F18" s="33"/>
-      <c r="G18" s="85" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B19" s="144" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19" s="145"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="34">
-        <v>1</v>
-      </c>
-      <c r="F19" s="34"/>
-      <c r="G19" s="57" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B20" s="110" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" s="134"/>
-      <c r="D20" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="38">
-        <f>SUM(E21:E22)</f>
-        <v>3</v>
-      </c>
-      <c r="F20" s="38">
-        <f>SUM(F21:F24)</f>
-        <v>6</v>
-      </c>
-      <c r="G20" s="39" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7">
-      <c r="B21" s="106" t="s">
-        <v>95</v>
-      </c>
-      <c r="C21" s="137"/>
+      <c r="C21" s="133"/>
       <c r="D21" s="6"/>
       <c r="E21" s="33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="33"/>
       <c r="G21" s="85" t="s">
@@ -3468,373 +3598,504 @@
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="144" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="145"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="34">
-        <v>2</v>
-      </c>
-      <c r="F22" s="34"/>
-      <c r="G22" s="57" t="s">
+      <c r="B22" s="117" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="118"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="33">
+        <v>1</v>
+      </c>
+      <c r="F22" s="33"/>
+      <c r="G22" s="85" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="123" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="124"/>
+    <row r="23" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B23" s="103" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="104"/>
       <c r="D23" s="8"/>
       <c r="E23" s="34">
+        <v>1</v>
+      </c>
+      <c r="F23" s="34"/>
+      <c r="G23" s="57" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B24" s="107" t="s">
+        <v>2</v>
+      </c>
+      <c r="C24" s="108"/>
+      <c r="D24" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="190">
+        <f>SUM(E25:E26)</f>
+        <v>3</v>
+      </c>
+      <c r="F24" s="190">
+        <f>SUM(F25:F28)</f>
+        <v>6</v>
+      </c>
+      <c r="G24" s="98" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7">
+      <c r="B25" s="132" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="133"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="33">
+        <v>1</v>
+      </c>
+      <c r="F25" s="33"/>
+      <c r="G25" s="85" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7">
+      <c r="B26" s="103" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="104"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="34">
+        <v>2</v>
+      </c>
+      <c r="F26" s="34"/>
+      <c r="G26" s="57" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7">
+      <c r="B27" s="111" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="128"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="34">
         <v>5</v>
       </c>
-      <c r="F23" s="34">
+      <c r="F27" s="34">
         <v>5</v>
       </c>
-      <c r="G23" s="57" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B24" s="146" t="s">
+      <c r="G27" s="57" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B28" s="129" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="147"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="35">
-        <v>1</v>
-      </c>
-      <c r="F24" s="35">
-        <v>1</v>
-      </c>
-      <c r="G24" s="57" t="s">
+      <c r="C28" s="130"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="35">
+        <v>1</v>
+      </c>
+      <c r="F28" s="35">
+        <v>1</v>
+      </c>
+      <c r="G28" s="57" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B25" s="110" t="s">
+    <row r="29" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B29" s="107" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="134"/>
-      <c r="D25" s="10" t="s">
+      <c r="C29" s="108"/>
+      <c r="D29" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="38">
-        <f>SUM(E26+E27+E29+E39)</f>
+      <c r="E29" s="190">
+        <f>SUM(E30+E31+E39+E45)</f>
         <v>11</v>
       </c>
-      <c r="F25" s="38">
-        <f>SUM(F26+F29+F39)</f>
+      <c r="F29" s="190">
+        <f>SUM(F30+F39+F45)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="39" t="s">
+      <c r="G29" s="98" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="2:7">
-      <c r="B26" s="114" t="s">
+    <row r="30" spans="2:7">
+      <c r="B30" s="109" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="135"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="37">
+      <c r="C30" s="110"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="37">
         <v>5</v>
       </c>
-      <c r="F26" s="37"/>
-      <c r="G26" s="85" t="s">
+      <c r="F30" s="37"/>
+      <c r="G30" s="85" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="2:7">
-      <c r="B27" s="102" t="s">
+    <row r="31" spans="2:7">
+      <c r="B31" s="121" t="s">
         <v>96</v>
       </c>
-      <c r="C27" s="136"/>
-      <c r="D27" s="6" t="s">
+      <c r="C31" s="122"/>
+      <c r="D31" s="188" t="s">
         <v>97</v>
       </c>
-      <c r="E27" s="37">
+      <c r="E31" s="189">
         <v>2</v>
       </c>
-      <c r="F27" s="37"/>
-      <c r="G27" s="85" t="s">
+      <c r="F31" s="189"/>
+      <c r="G31" s="100" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7">
+      <c r="B32" s="113" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" s="123"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="F32" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="G32" s="85" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="113" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" s="123"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="37">
+        <f>SUM(E34+E35+E36+E37)</f>
+        <v>7</v>
+      </c>
+      <c r="F33" s="37">
+        <f>SUM(F34+F35+F36+F37)</f>
+        <v>6</v>
+      </c>
+      <c r="G33" s="85" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="184" t="s">
+        <v>111</v>
+      </c>
+      <c r="C34" s="185"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="37">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="F34" s="37">
+        <v>1.5</v>
+      </c>
+      <c r="G34" s="85" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="B35" s="184" t="s">
+        <v>112</v>
+      </c>
+      <c r="C35" s="185"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="37">
+        <v>2</v>
+      </c>
+      <c r="F35" s="37">
+        <v>1.5</v>
+      </c>
+      <c r="G35" s="85" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="184" t="s">
+        <v>113</v>
+      </c>
+      <c r="C36" s="185"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="37">
+        <v>2</v>
+      </c>
+      <c r="F36" s="37">
+        <v>1.5</v>
+      </c>
+      <c r="G36" s="85" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="182" t="s">
+        <v>114</v>
+      </c>
+      <c r="C37" s="183"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="37">
+        <v>1</v>
+      </c>
+      <c r="F37" s="37">
+        <v>1.5</v>
+      </c>
+      <c r="G37" s="85" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="121" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" s="122"/>
+      <c r="D38" s="188" t="s">
+        <v>97</v>
+      </c>
+      <c r="E38" s="191">
+        <f>SUM(E39:E43)</f>
+        <v>6</v>
+      </c>
+      <c r="F38" s="191"/>
+      <c r="G38" s="100" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="2:7">
-      <c r="B28" s="125" t="s">
-        <v>4</v>
-      </c>
-      <c r="C28" s="129"/>
-      <c r="D28" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="E28" s="33">
-        <f>SUM(E29:E33)</f>
-        <v>6</v>
-      </c>
-      <c r="F28" s="33"/>
-      <c r="G28" s="85" t="s">
+    <row r="39" spans="2:7">
+      <c r="B39" s="113" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="114"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="33">
+        <v>2</v>
+      </c>
+      <c r="F39" s="33"/>
+      <c r="G39" s="85" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
-      <c r="B29" s="102" t="s">
-        <v>66</v>
-      </c>
-      <c r="C29" s="136"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="33">
+    <row r="40" spans="2:7">
+      <c r="B40" s="113" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" s="114"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="33">
         <v>2</v>
       </c>
-      <c r="F29" s="33"/>
-      <c r="G29" s="85" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7">
-      <c r="B30" s="102" t="s">
-        <v>98</v>
-      </c>
-      <c r="C30" s="136"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="33">
+      <c r="F40" s="33">
         <v>2</v>
       </c>
-      <c r="F30" s="33">
-        <v>2</v>
-      </c>
-      <c r="G30" s="85" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7">
-      <c r="B31" s="102" t="s">
+      <c r="G40" s="85" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7">
+      <c r="B41" s="113" t="s">
         <v>67</v>
       </c>
-      <c r="C31" s="103"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="33"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="85"/>
-    </row>
-    <row r="32" spans="2:7">
-      <c r="B32" s="164" t="s">
-        <v>108</v>
-      </c>
-      <c r="C32" s="165"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="85"/>
-    </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="164" t="s">
-        <v>106</v>
-      </c>
-      <c r="C33" s="165"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="33">
-        <f>SUM(E34)</f>
-        <v>2</v>
-      </c>
-      <c r="F33" s="33"/>
-      <c r="G33" s="85" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7">
-      <c r="B34" s="116" t="s">
-        <v>107</v>
-      </c>
-      <c r="C34" s="117"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="33">
-        <v>2</v>
-      </c>
-      <c r="F34" s="33"/>
-      <c r="G34" s="85" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="125" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="129"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="33"/>
-      <c r="G35" s="85"/>
-    </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="130" t="s">
-        <v>66</v>
-      </c>
-      <c r="C36" s="131"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="85"/>
-    </row>
-    <row r="37" spans="2:7">
-      <c r="B37" s="102" t="s">
-        <v>98</v>
-      </c>
-      <c r="C37" s="136"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="85"/>
-    </row>
-    <row r="38" spans="2:7">
-      <c r="B38" s="125" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="129"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="33"/>
-      <c r="G38" s="85" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7">
-      <c r="B39" s="130" t="s">
-        <v>66</v>
-      </c>
-      <c r="C39" s="131"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="34">
-        <v>2</v>
-      </c>
-      <c r="F39" s="34"/>
-      <c r="G39" s="57" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7">
-      <c r="B40" s="102" t="s">
-        <v>98</v>
-      </c>
-      <c r="C40" s="136"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="57" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7">
-      <c r="B41" s="125" t="s">
-        <v>100</v>
-      </c>
-      <c r="C41" s="129"/>
+      <c r="C41" s="123"/>
       <c r="D41" s="6"/>
-      <c r="E41" s="33"/>
+      <c r="E41" s="33">
+        <f>SUM(E42+E43)</f>
+        <v>1</v>
+      </c>
       <c r="F41" s="33"/>
-      <c r="G41" s="57" t="s">
-        <v>80</v>
+      <c r="G41" s="85" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="42" spans="2:7">
-      <c r="B42" s="130" t="s">
-        <v>66</v>
-      </c>
-      <c r="C42" s="131"/>
+      <c r="B42" s="186" t="s">
+        <v>116</v>
+      </c>
+      <c r="C42" s="187"/>
       <c r="D42" s="6"/>
       <c r="E42" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="F42" s="33"/>
+      <c r="G42" s="85" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7">
+      <c r="B43" s="124" t="s">
+        <v>115</v>
+      </c>
+      <c r="C43" s="125"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="33">
+        <v>0.5</v>
+      </c>
+      <c r="F43" s="33"/>
+      <c r="G43" s="85" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7">
+      <c r="B44" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="122"/>
+      <c r="D44" s="188"/>
+      <c r="E44" s="191"/>
+      <c r="F44" s="191"/>
+      <c r="G44" s="100" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7">
+      <c r="B45" s="126" t="s">
+        <v>66</v>
+      </c>
+      <c r="C45" s="127"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="34">
         <v>2</v>
       </c>
-      <c r="F42" s="33"/>
-      <c r="G42" s="57" t="s">
+      <c r="F45" s="34"/>
+      <c r="G45" s="57" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="43" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B43" s="123" t="s">
+    <row r="46" spans="2:7">
+      <c r="B46" s="113" t="s">
         <v>98</v>
       </c>
-      <c r="C43" s="132"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="34">
+      <c r="C46" s="114"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="34"/>
+      <c r="F46" s="34"/>
+      <c r="G46" s="57" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7">
+      <c r="B47" s="121" t="s">
+        <v>100</v>
+      </c>
+      <c r="C47" s="122"/>
+      <c r="D47" s="188"/>
+      <c r="E47" s="191"/>
+      <c r="F47" s="191"/>
+      <c r="G47" s="192" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7">
+      <c r="B48" s="126" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" s="127"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="33">
         <v>2</v>
       </c>
-      <c r="F43" s="34"/>
-      <c r="G43" s="57" t="s">
+      <c r="F48" s="33"/>
+      <c r="G48" s="57" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="44" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B44" s="166" t="s">
+    <row r="49" spans="2:7" ht="18.600000000000001" thickBot="1">
+      <c r="B49" s="111" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" s="112"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="34">
+        <v>2</v>
+      </c>
+      <c r="F49" s="34"/>
+      <c r="G49" s="57" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7">
+      <c r="B50" s="119" t="s">
         <v>34</v>
       </c>
-      <c r="C44" s="167"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="38">
-        <f>SUM(E3+E13+E20+E25)</f>
+      <c r="C50" s="120"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="38">
+        <f>SUM(E3+E17+E24+E29)</f>
         <v>33</v>
       </c>
-      <c r="F44" s="38">
-        <f>SUM(F3+F13+F20+F25)</f>
-        <v>16</v>
-      </c>
-      <c r="G44" s="92"/>
+      <c r="F50" s="38">
+        <f>SUM(F3+F17+F24+F29)</f>
+        <v>16.5</v>
+      </c>
+      <c r="G50" s="92"/>
     </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="51">
+    <mergeCell ref="I7:M7"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="B19:C19"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B23:C23"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="I7:M7"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B21:C21"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="E13 E3" formulaRange="1"/>
+    <ignoredError sqref="E17 E3" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3853,10 +4114,10 @@
   <sheetData>
     <row r="1" spans="2:12" ht="18.600000000000001" thickBot="1"/>
     <row r="2" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B2" s="152" t="s">
+      <c r="B2" s="167" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="153"/>
+      <c r="C2" s="168"/>
       <c r="D2" s="10" t="s">
         <v>9</v>
       </c>
@@ -3871,10 +4132,10 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B3" s="154" t="s">
+      <c r="B3" s="163" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="155"/>
+      <c r="C3" s="164"/>
       <c r="D3" s="10" t="s">
         <v>12</v>
       </c>
@@ -3894,17 +4155,17 @@
       </c>
       <c r="K3" s="51">
         <f ca="1">TODAY()</f>
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="L3" s="39" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="4" spans="2:12">
-      <c r="B4" s="156" t="s">
+      <c r="B4" s="169" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="157"/>
+      <c r="C4" s="170"/>
       <c r="D4" s="77"/>
       <c r="E4" s="78">
         <v>3</v>
@@ -3928,10 +4189,10 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B5" s="123" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="124"/>
+      <c r="B5" s="111" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="128"/>
       <c r="D5" s="8"/>
       <c r="E5" s="34">
         <v>3</v>
@@ -3950,10 +4211,10 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B6" s="154" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="155"/>
+      <c r="B6" s="163" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="164"/>
       <c r="D6" s="10" t="s">
         <v>11</v>
       </c>
@@ -3976,14 +4237,14 @@
       </c>
       <c r="L6" s="46" t="str">
         <f ca="1">SUM(K6-K3)&amp; "日"</f>
-        <v>8日</v>
+        <v>7日</v>
       </c>
     </row>
     <row r="7" spans="2:12">
-      <c r="B7" s="160" t="s">
+      <c r="B7" s="161" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="161"/>
+      <c r="C7" s="162"/>
       <c r="D7" s="61"/>
       <c r="E7" s="63">
         <v>3</v>
@@ -3997,10 +4258,10 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B8" s="123" t="s">
+      <c r="B8" s="111" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="124"/>
+      <c r="C8" s="128"/>
       <c r="D8" s="8"/>
       <c r="E8" s="34">
         <v>3</v>
@@ -4012,10 +4273,10 @@
       <c r="L8" s="56"/>
     </row>
     <row r="9" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B9" s="154" t="s">
+      <c r="B9" s="163" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="155"/>
+      <c r="C9" s="164"/>
       <c r="D9" s="10" t="s">
         <v>10</v>
       </c>
@@ -4032,10 +4293,10 @@
       </c>
     </row>
     <row r="10" spans="2:12">
-      <c r="B10" s="108" t="s">
+      <c r="B10" s="155" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="158"/>
+      <c r="C10" s="165"/>
       <c r="D10" s="9"/>
       <c r="E10" s="37">
         <v>3</v>
@@ -4046,10 +4307,10 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B11" s="100" t="s">
+      <c r="B11" s="153" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="159"/>
+      <c r="C11" s="166"/>
       <c r="D11" s="8"/>
       <c r="E11" s="34">
         <v>2</v>
@@ -4060,10 +4321,10 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B12" s="154" t="s">
+      <c r="B12" s="163" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="155"/>
+      <c r="C12" s="164"/>
       <c r="D12" s="10" t="s">
         <v>14</v>
       </c>
@@ -4080,10 +4341,10 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B13" s="160" t="s">
+      <c r="B13" s="161" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="161"/>
+      <c r="C13" s="162"/>
       <c r="D13" s="61"/>
       <c r="E13" s="63">
         <v>2</v>
@@ -4094,10 +4355,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B14" s="154" t="s">
+      <c r="B14" s="163" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="155"/>
+      <c r="C14" s="164"/>
       <c r="D14" s="10"/>
       <c r="E14" s="38">
         <f>SUM(E15:E16)</f>
@@ -4112,10 +4373,10 @@
       </c>
     </row>
     <row r="15" spans="2:12">
-      <c r="B15" s="108" t="s">
+      <c r="B15" s="155" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="158"/>
+      <c r="C15" s="165"/>
       <c r="D15" s="9"/>
       <c r="E15" s="37">
         <v>1</v>
@@ -4126,10 +4387,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B16" s="100" t="s">
+      <c r="B16" s="153" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="159"/>
+      <c r="C16" s="166"/>
       <c r="D16" s="8"/>
       <c r="E16" s="34">
         <v>1</v>
@@ -4140,10 +4401,10 @@
       </c>
     </row>
     <row r="17" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B17" s="154" t="s">
+      <c r="B17" s="163" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="155"/>
+      <c r="C17" s="164"/>
       <c r="D17" s="10"/>
       <c r="E17" s="38">
         <f>SUM(E18:E19)</f>
@@ -4158,10 +4419,10 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="108" t="s">
+      <c r="B18" s="155" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="158"/>
+      <c r="C18" s="165"/>
       <c r="D18" s="9"/>
       <c r="E18" s="37">
         <v>1</v>
@@ -4172,10 +4433,10 @@
       </c>
     </row>
     <row r="19" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B19" s="162" t="s">
+      <c r="B19" s="157" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="163"/>
+      <c r="C19" s="158"/>
       <c r="D19" s="7"/>
       <c r="E19" s="35">
         <v>1</v>
@@ -4186,10 +4447,10 @@
       </c>
     </row>
     <row r="20" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B20" s="169" t="s">
+      <c r="B20" s="159" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="170"/>
+      <c r="C20" s="160"/>
       <c r="D20" s="10"/>
       <c r="E20" s="38">
         <f>SUM(E3+E6+E9+E12+E14+E17)</f>
@@ -4206,6 +4467,18 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B13:C13"/>
@@ -4213,18 +4486,6 @@
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B8:C8"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4237,13 +4498,13 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="97" t="s">
+      <c r="C1" s="171" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
     </row>
     <row r="2" spans="2:11" ht="18.600000000000001" thickBot="1">
       <c r="B2" s="27" t="s">

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\OneDrive\Documents\GitHub\GlassesGame\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB0FB4B8-3468-40D9-97D8-6BA4D9B7787C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75609BC6-8B68-4443-9C2A-DDC4338F485A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="599" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="120">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -775,6 +775,24 @@
   </si>
   <si>
     <t xml:space="preserve">               ー　BGM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カメラ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー　揺れ</t>
+    <rPh sb="2" eb="3">
+      <t>ユ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1コスト1時間</t>
+    <rPh sb="5" eb="7">
+      <t>ジカン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1547,15 +1565,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="199">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1581,9 +1596,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="56" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
@@ -1608,9 +1621,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1773,97 +1783,76 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1881,40 +1870,85 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1929,12 +1963,75 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1945,115 +2042,45 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2344,812 +2371,785 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B1:S43"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9" style="4" customWidth="1"/>
-    <col min="2" max="2" width="17.09765625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="17.125" style="4" customWidth="1"/>
     <col min="3" max="3" width="9" style="4"/>
-    <col min="4" max="4" width="6.19921875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="7.09765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.25" style="4" customWidth="1"/>
+    <col min="5" max="5" width="7.125" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="9" style="4"/>
-    <col min="9" max="9" width="17.09765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.375" style="4" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9" style="4"/>
     <col min="12" max="12" width="9" style="4" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="18.600000000000001" thickBot="1"/>
-    <row r="2" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B2" s="105" t="s">
+    <row r="1" spans="2:19" ht="19.5" thickBot="1"/>
+    <row r="2" spans="2:19" ht="19.5" thickBot="1">
+      <c r="B2" s="151" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="149"/>
-      <c r="D2" s="72" t="s">
+      <c r="C2" s="164"/>
+      <c r="D2" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="9" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B3" s="107" t="s">
+    <row r="3" spans="2:19" ht="19.5" thickBot="1">
+      <c r="B3" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="145"/>
-      <c r="D3" s="101" t="s">
+      <c r="C3" s="163"/>
+      <c r="D3" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="190">
+      <c r="E3" s="107">
         <f>SUM(E4:E15)</f>
         <v>21</v>
       </c>
-      <c r="F3" s="190">
+      <c r="F3" s="107">
         <f>SUM(F4:F15)</f>
         <v>23</v>
       </c>
-      <c r="G3" s="70" t="s">
-        <v>84</v>
-      </c>
-      <c r="I3" s="48" t="s">
+      <c r="G3" s="66" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="J3" s="51">
+      <c r="J3" s="47">
         <f ca="1">TODAY()</f>
         <v>46307</v>
       </c>
-      <c r="K3" s="39" t="s">
+      <c r="K3" s="35" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="4" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B4" s="109" t="s">
+    <row r="4" spans="2:19" ht="19.5" thickBot="1">
+      <c r="B4" s="116" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="144"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="37">
+      <c r="C4" s="165"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="33">
         <f>SUM(E5:E7)</f>
         <v>4</v>
       </c>
-      <c r="F4" s="37">
+      <c r="F4" s="33">
         <f>SUM(F5:F7)</f>
         <v>5</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="I4" s="70" t="s">
+      <c r="G4" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I4" s="66" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="51">
+      <c r="J4" s="47">
         <v>46295</v>
       </c>
-      <c r="K4" s="60" t="str">
+      <c r="K4" s="56" t="str">
         <f ca="1">SUM($J4-J3)&amp; "日"</f>
         <v>-12日</v>
       </c>
     </row>
-    <row r="5" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B5" s="124" t="s">
+    <row r="5" spans="2:19" ht="19.5" thickBot="1">
+      <c r="B5" s="122" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="125"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="33">
+      <c r="C5" s="134"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="30">
         <v>2</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="30">
         <v>2</v>
       </c>
-      <c r="G5" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="I5" s="67" t="s">
+      <c r="G5" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I5" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="J5" s="68">
+      <c r="J5" s="64">
         <v>46314</v>
       </c>
-      <c r="K5" s="69" t="str">
+      <c r="K5" s="65" t="str">
         <f ca="1">SUM(J5-J3)&amp; "日"</f>
         <v>7日</v>
       </c>
-      <c r="R5" s="55"/>
-      <c r="S5" s="56"/>
-    </row>
-    <row r="6" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B6" s="124" t="s">
+      <c r="R5" s="51"/>
+      <c r="S5" s="52"/>
+    </row>
+    <row r="6" spans="2:19" ht="19.5" thickBot="1">
+      <c r="B6" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="125"/>
-      <c r="D6" s="74"/>
-      <c r="E6" s="33">
-        <v>1</v>
-      </c>
-      <c r="F6" s="33">
+      <c r="C6" s="134"/>
+      <c r="D6" s="70"/>
+      <c r="E6" s="30">
+        <v>1</v>
+      </c>
+      <c r="F6" s="30">
         <v>2</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="R6" s="55"/>
-      <c r="S6" s="56"/>
-    </row>
-    <row r="7" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B7" s="124" t="s">
+      <c r="G6" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="R6" s="51"/>
+      <c r="S6" s="52"/>
+    </row>
+    <row r="7" spans="2:19" ht="19.5" thickBot="1">
+      <c r="B7" s="122" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="125"/>
-      <c r="D7" s="74"/>
-      <c r="E7" s="33">
-        <v>1</v>
-      </c>
-      <c r="F7" s="37">
-        <v>1</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="I7" s="151" t="s">
+      <c r="C7" s="134"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="30">
+        <v>1</v>
+      </c>
+      <c r="F7" s="33">
+        <v>1</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I7" s="155" t="s">
         <v>102</v>
       </c>
-      <c r="J7" s="152"/>
-      <c r="R7" s="55"/>
-      <c r="S7" s="56"/>
+      <c r="J7" s="156"/>
+      <c r="R7" s="51"/>
+      <c r="S7" s="52"/>
     </row>
     <row r="8" spans="2:19">
-      <c r="B8" s="113" t="s">
+      <c r="B8" s="118" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="123"/>
-      <c r="D8" s="74"/>
-      <c r="E8" s="33">
+      <c r="C8" s="144"/>
+      <c r="D8" s="70"/>
+      <c r="E8" s="30">
         <v>2</v>
       </c>
-      <c r="F8" s="37">
+      <c r="F8" s="33">
         <v>2</v>
       </c>
-      <c r="G8" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="I8" s="86" t="s">
+      <c r="G8" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I8" s="82" t="s">
         <v>99</v>
       </c>
-      <c r="J8" s="89">
+      <c r="J8" s="85">
         <f>SUM(E3)</f>
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="2:19">
-      <c r="B9" s="113" t="s">
+      <c r="B9" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="123"/>
-      <c r="D9" s="75"/>
-      <c r="E9" s="34">
+      <c r="C9" s="144"/>
+      <c r="D9" s="71"/>
+      <c r="E9" s="31">
         <v>2</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="31">
         <v>2</v>
       </c>
-      <c r="G9" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="I9" s="87" t="s">
+      <c r="G9" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I9" s="83" t="s">
         <v>11</v>
       </c>
-      <c r="J9" s="90">
+      <c r="J9" s="86">
         <f>SUM(E16)</f>
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="2:19">
-      <c r="B10" s="113" t="s">
+      <c r="B10" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="123"/>
-      <c r="D10" s="75"/>
-      <c r="E10" s="34">
+      <c r="C10" s="144"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="31">
         <v>2</v>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="31">
         <v>2</v>
       </c>
-      <c r="G10" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="I10" s="87" t="s">
+      <c r="G10" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="I10" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="J10" s="90">
+      <c r="J10" s="86">
         <f>SUM(E26)</f>
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B11" s="132" t="s">
+    <row r="11" spans="2:19" ht="19.5" thickBot="1">
+      <c r="B11" s="120" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="150"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="33">
-        <v>1</v>
-      </c>
-      <c r="F11" s="33">
-        <v>1</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="I11" s="88" t="s">
+      <c r="C11" s="160"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="30">
+        <v>1</v>
+      </c>
+      <c r="F11" s="30">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="I11" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="91">
+      <c r="J11" s="87">
         <f>SUM(E32)</f>
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B12" s="113" t="s">
+    <row r="12" spans="2:19" ht="19.5" thickBot="1">
+      <c r="B12" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="123"/>
-      <c r="D12" s="74"/>
-      <c r="E12" s="33">
+      <c r="C12" s="144"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="30">
         <f>SUM(E13:E15)</f>
         <v>3</v>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="30">
         <f>SUM(F13:F15)</f>
         <v>3</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="I12" s="93" t="s">
+      <c r="G12" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="I12" s="89" t="s">
         <v>101</v>
       </c>
-      <c r="J12" s="83">
+      <c r="J12" s="79">
         <f>SUM(J8:J11)</f>
         <v>66</v>
       </c>
     </row>
     <row r="13" spans="2:19">
-      <c r="B13" s="117" t="s">
+      <c r="B13" s="130" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="141"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="33">
-        <v>1</v>
-      </c>
-      <c r="F13" s="33">
-        <v>1</v>
-      </c>
-      <c r="G13" s="6" t="s">
+      <c r="C13" s="159"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="30">
+        <v>1</v>
+      </c>
+      <c r="F13" s="30">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="14" spans="2:19">
-      <c r="B14" s="124" t="s">
+      <c r="B14" s="122" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="125"/>
-      <c r="D14" s="74"/>
-      <c r="E14" s="33">
-        <v>1</v>
-      </c>
-      <c r="F14" s="33">
-        <v>1</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="R14" s="55"/>
-      <c r="S14" s="56"/>
-    </row>
-    <row r="15" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B15" s="135" t="s">
+      <c r="C14" s="134"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="30">
+        <v>1</v>
+      </c>
+      <c r="F14" s="30">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="R14" s="51"/>
+      <c r="S14" s="52"/>
+    </row>
+    <row r="15" spans="2:19" ht="19.5" thickBot="1">
+      <c r="B15" s="124" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="140"/>
-      <c r="D15" s="75"/>
-      <c r="E15" s="34">
-        <v>1</v>
-      </c>
-      <c r="F15" s="34">
-        <v>1</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="16" spans="2:19" ht="18.600000000000001" thickBot="1">
-      <c r="B16" s="107" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="145"/>
-      <c r="D16" s="97" t="s">
+      <c r="C15" s="167"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="31">
+        <v>1</v>
+      </c>
+      <c r="F15" s="31">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19" ht="19.5" thickBot="1">
+      <c r="B16" s="137" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="163"/>
+      <c r="D16" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="190">
+      <c r="E16" s="107">
         <f>SUM(E17:E25)</f>
         <v>16</v>
       </c>
-      <c r="F16" s="190">
+      <c r="F16" s="107">
         <v>8</v>
       </c>
-      <c r="G16" s="70" t="s">
+      <c r="G16" s="66" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="109" t="s">
+      <c r="B17" s="116" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="144"/>
-      <c r="D17" s="82"/>
-      <c r="E17" s="37">
+      <c r="C17" s="165"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="33">
         <v>3</v>
       </c>
-      <c r="F17" s="37">
-        <v>1</v>
-      </c>
-      <c r="G17" s="9" t="s">
+      <c r="F17" s="33">
+        <v>1</v>
+      </c>
+      <c r="G17" s="8" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="113" t="s">
+      <c r="B18" s="118" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="123"/>
-      <c r="D18" s="74"/>
-      <c r="E18" s="33">
+      <c r="C18" s="144"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="30">
         <v>3</v>
       </c>
-      <c r="F18" s="33">
-        <v>1</v>
-      </c>
-      <c r="G18" s="6" t="s">
+      <c r="F18" s="30">
+        <v>1</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="113" t="s">
+      <c r="B19" s="118" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="123"/>
-      <c r="D19" s="74"/>
-      <c r="E19" s="33">
+      <c r="C19" s="144"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="30">
         <v>3</v>
       </c>
-      <c r="F19" s="33">
-        <v>1</v>
-      </c>
-      <c r="G19" s="6" t="s">
+      <c r="F19" s="30">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="113" t="s">
+      <c r="B20" s="118" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="123"/>
-      <c r="D20" s="75"/>
-      <c r="E20" s="33">
+      <c r="C20" s="144"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="30">
         <v>3</v>
       </c>
-      <c r="F20" s="33">
-        <v>1</v>
-      </c>
-      <c r="G20" s="6" t="s">
+      <c r="F20" s="30">
+        <v>1</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="113" t="s">
+      <c r="B21" s="118" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="123"/>
-      <c r="D21" s="74"/>
-      <c r="E21" s="63">
-        <v>1</v>
-      </c>
-      <c r="F21" s="33">
-        <v>1</v>
-      </c>
-      <c r="G21" s="6" t="s">
+      <c r="C21" s="144"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="59">
+        <v>1</v>
+      </c>
+      <c r="F21" s="30">
+        <v>1</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="132" t="s">
+      <c r="B22" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="150"/>
-      <c r="D22" s="74"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33">
+      <c r="C22" s="160"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30">
         <v>3</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="5" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="117" t="s">
+      <c r="B23" s="130" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="141"/>
-      <c r="D23" s="74"/>
-      <c r="E23" s="33">
-        <v>1</v>
-      </c>
-      <c r="F23" s="33">
-        <v>1</v>
-      </c>
-      <c r="G23" s="6" t="s">
+      <c r="C23" s="159"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="30">
+        <v>1</v>
+      </c>
+      <c r="F23" s="30">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="117" t="s">
+      <c r="B24" s="130" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="141"/>
-      <c r="D24" s="74"/>
-      <c r="E24" s="33">
-        <v>1</v>
-      </c>
-      <c r="F24" s="33">
-        <v>1</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B25" s="142" t="s">
+      <c r="C24" s="159"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="30">
+        <v>1</v>
+      </c>
+      <c r="F24" s="30">
+        <v>1</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B25" s="132" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="143"/>
-      <c r="D25" s="84"/>
-      <c r="E25" s="35">
-        <v>1</v>
-      </c>
-      <c r="F25" s="35">
-        <v>1</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B26" s="107" t="s">
+      <c r="C25" s="168"/>
+      <c r="D25" s="80"/>
+      <c r="E25" s="32">
+        <v>1</v>
+      </c>
+      <c r="F25" s="32">
+        <v>1</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B26" s="137" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="145"/>
-      <c r="D26" s="97" t="s">
+      <c r="C26" s="163"/>
+      <c r="D26" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="190">
+      <c r="E26" s="107">
         <f>SUM(E27:E31)</f>
         <v>16</v>
       </c>
-      <c r="F26" s="190">
+      <c r="F26" s="107">
         <f>SUM(F27,F28,F31)</f>
         <v>11</v>
       </c>
-      <c r="G26" s="70" t="s">
+      <c r="G26" s="66" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="155" t="s">
+      <c r="B27" s="161" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="156"/>
-      <c r="D27" s="82"/>
-      <c r="E27" s="37">
+      <c r="C27" s="162"/>
+      <c r="D27" s="78"/>
+      <c r="E27" s="33">
         <v>5</v>
       </c>
-      <c r="F27" s="37">
+      <c r="F27" s="33">
         <v>5</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="8" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="132" t="s">
+      <c r="B28" s="120" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="150"/>
-      <c r="D28" s="74"/>
-      <c r="E28" s="33">
+      <c r="C28" s="160"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="30">
         <f>SUM(E29:E30)</f>
         <v>4</v>
       </c>
-      <c r="F28" s="33">
+      <c r="F28" s="30">
         <f>SUM(F29:F30)</f>
         <v>3</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="8" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="117" t="s">
+      <c r="B29" s="130" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="141"/>
-      <c r="D29" s="74"/>
-      <c r="E29" s="33">
+      <c r="C29" s="159"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="30">
         <v>2</v>
       </c>
-      <c r="F29" s="33">
+      <c r="F29" s="30">
         <v>2</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="8" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="117" t="s">
+      <c r="B30" s="130" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="141"/>
-      <c r="D30" s="74"/>
-      <c r="E30" s="33">
+      <c r="C30" s="159"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="30">
         <v>2</v>
       </c>
-      <c r="F30" s="33">
-        <v>1</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B31" s="111" t="s">
+      <c r="F30" s="30">
+        <v>1</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B31" s="128" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="128"/>
-      <c r="D31" s="75"/>
-      <c r="E31" s="34">
+      <c r="C31" s="141"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="31">
         <v>3</v>
       </c>
-      <c r="F31" s="34">
+      <c r="F31" s="31">
         <v>3</v>
       </c>
-      <c r="G31" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B32" s="107" t="s">
+      <c r="G31" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B32" s="137" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="145"/>
-      <c r="D32" s="97" t="s">
+      <c r="C32" s="163"/>
+      <c r="D32" s="93" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="190">
+      <c r="E32" s="107">
         <f>SUM(E33:E42)</f>
         <v>13</v>
       </c>
-      <c r="F32" s="190">
+      <c r="F32" s="107">
         <f>SUM(F34,F36,F37,F40,F41)</f>
         <v>5</v>
       </c>
-      <c r="G32" s="70" t="s">
+      <c r="G32" s="66" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="109" t="s">
+      <c r="B33" s="116" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="144"/>
-      <c r="D33" s="82"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="9" t="s">
+      <c r="C33" s="165"/>
+      <c r="D33" s="78"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="8" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="124" t="s">
+      <c r="B34" s="122" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="125"/>
-      <c r="D34" s="82"/>
-      <c r="E34" s="37">
+      <c r="C34" s="134"/>
+      <c r="D34" s="78"/>
+      <c r="E34" s="33">
         <v>2</v>
       </c>
-      <c r="F34" s="37">
-        <v>1</v>
-      </c>
-      <c r="G34" s="6" t="s">
+      <c r="F34" s="33">
+        <v>1</v>
+      </c>
+      <c r="G34" s="5" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="121" t="s">
+      <c r="B35" s="149" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="146"/>
-      <c r="D35" s="99"/>
-      <c r="E35" s="191"/>
-      <c r="F35" s="191"/>
-      <c r="G35" s="188" t="s">
+      <c r="C35" s="169"/>
+      <c r="D35" s="95"/>
+      <c r="E35" s="108"/>
+      <c r="F35" s="108"/>
+      <c r="G35" s="105" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="113" t="s">
+      <c r="B36" s="118" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="123"/>
-      <c r="D36" s="74"/>
-      <c r="E36" s="33">
+      <c r="C36" s="144"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="30">
         <v>2</v>
       </c>
-      <c r="F36" s="33">
-        <v>1</v>
-      </c>
-      <c r="G36" s="6" t="s">
+      <c r="F36" s="30">
+        <v>1</v>
+      </c>
+      <c r="G36" s="5" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="113" t="s">
+      <c r="B37" s="118" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="123"/>
-      <c r="D37" s="74"/>
-      <c r="E37" s="33">
+      <c r="C37" s="144"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="30">
         <v>2</v>
       </c>
-      <c r="F37" s="33">
-        <v>1</v>
-      </c>
-      <c r="G37" s="6" t="s">
+      <c r="F37" s="30">
+        <v>1</v>
+      </c>
+      <c r="G37" s="5" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="113" t="s">
+      <c r="B38" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="C38" s="123"/>
-      <c r="D38" s="74"/>
-      <c r="E38" s="33">
-        <v>1</v>
-      </c>
-      <c r="F38" s="33">
-        <v>1</v>
-      </c>
-      <c r="G38" s="6" t="s">
+      <c r="C38" s="144"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="30">
+        <v>1</v>
+      </c>
+      <c r="F38" s="30">
+        <v>1</v>
+      </c>
+      <c r="G38" s="5" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="39" spans="2:7">
-      <c r="B39" s="121" t="s">
+      <c r="B39" s="149" t="s">
         <v>5</v>
       </c>
-      <c r="C39" s="146"/>
-      <c r="D39" s="99"/>
-      <c r="E39" s="191"/>
-      <c r="F39" s="191"/>
-      <c r="G39" s="188" t="s">
+      <c r="C39" s="169"/>
+      <c r="D39" s="95"/>
+      <c r="E39" s="108"/>
+      <c r="F39" s="108"/>
+      <c r="G39" s="105" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="40" spans="2:7">
-      <c r="B40" s="147" t="s">
+      <c r="B40" s="170" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="148"/>
-      <c r="D40" s="81"/>
-      <c r="E40" s="33">
+      <c r="C40" s="171"/>
+      <c r="D40" s="77"/>
+      <c r="E40" s="30">
         <v>2</v>
       </c>
-      <c r="F40" s="33">
-        <v>1</v>
-      </c>
-      <c r="G40" s="6" t="s">
+      <c r="F40" s="30">
+        <v>1</v>
+      </c>
+      <c r="G40" s="5" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="41" spans="2:7">
-      <c r="B41" s="132" t="s">
+      <c r="B41" s="120" t="s">
         <v>61</v>
       </c>
-      <c r="C41" s="139"/>
-      <c r="D41" s="81"/>
-      <c r="E41" s="33">
+      <c r="C41" s="166"/>
+      <c r="D41" s="77"/>
+      <c r="E41" s="30">
         <v>3</v>
       </c>
-      <c r="F41" s="33">
-        <v>1</v>
-      </c>
-      <c r="G41" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B42" s="153" t="s">
+      <c r="F41" s="30">
+        <v>1</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B42" s="157" t="s">
         <v>93</v>
       </c>
-      <c r="C42" s="154"/>
-      <c r="D42" s="73"/>
-      <c r="E42" s="34">
-        <v>1</v>
-      </c>
-      <c r="F42" s="34">
-        <v>1</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B43" s="196" t="s">
+      <c r="C42" s="158"/>
+      <c r="D42" s="69"/>
+      <c r="E42" s="31">
+        <v>1</v>
+      </c>
+      <c r="F42" s="31">
+        <v>1</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B43" s="147" t="s">
         <v>82</v>
       </c>
       <c r="C43" s="197"/>
-      <c r="D43" s="71"/>
-      <c r="E43" s="38">
+      <c r="D43" s="67"/>
+      <c r="E43" s="34">
         <f>SUM(E3+E16+E26+F32)</f>
         <v>58</v>
       </c>
-      <c r="F43" s="38">
+      <c r="F43" s="34">
         <f>SUM(F3+F16+F26+F32)</f>
         <v>47</v>
       </c>
-      <c r="G43" s="10" t="s">
+      <c r="G43" s="9" t="s">
         <v>84</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B14:C14"/>
@@ -3166,6 +3166,33 @@
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B38:C38"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3178,924 +3205,971 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DBF476-724A-4DAE-8D66-8B0809F96B84}">
-  <dimension ref="B1:M50"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="B1:M52"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="3" max="3" width="18.09765625" customWidth="1"/>
-    <col min="9" max="9" width="18.19921875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.125" customWidth="1"/>
+    <col min="9" max="9" width="18.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="18.600000000000001" thickBot="1"/>
-    <row r="2" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B2" s="105" t="s">
+    <row r="1" spans="2:13" ht="19.5" thickBot="1"/>
+    <row r="2" spans="2:13" ht="19.5" thickBot="1">
+      <c r="B2" s="151" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="106"/>
-      <c r="D2" s="10" t="s">
+      <c r="C2" s="152"/>
+      <c r="D2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="G2" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="I2" s="48" t="s">
+      <c r="I2" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="J2" s="51">
+      <c r="J2" s="47">
         <f ca="1">TODAY()</f>
         <v>46307</v>
       </c>
-      <c r="K2" s="39" t="s">
+      <c r="K2" s="35" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B3" s="107" t="s">
+    <row r="3" spans="2:13" ht="19.5" thickBot="1">
+      <c r="B3" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="108"/>
-      <c r="D3" s="70" t="s">
+      <c r="C3" s="138"/>
+      <c r="D3" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="190">
-        <f>SUM(E4:E7)</f>
-        <v>8</v>
-      </c>
-      <c r="F3" s="190">
-        <f>SUM(F4+F6+F13)</f>
-        <v>7.5</v>
-      </c>
-      <c r="G3" s="98" t="s">
+      <c r="E3" s="107">
+        <f>SUM(E4+E6+E8+E9+E15)</f>
+        <v>13</v>
+      </c>
+      <c r="F3" s="107">
+        <f>SUM(F4+F6+F9+F8+F15)</f>
+        <v>20.5</v>
+      </c>
+      <c r="G3" s="94" t="s">
         <v>80</v>
       </c>
-      <c r="I3" s="62" t="s">
+      <c r="I3" s="58" t="s">
         <v>76</v>
       </c>
-      <c r="J3" s="50">
+      <c r="J3" s="46">
         <v>46305</v>
       </c>
-      <c r="K3" s="46" t="str">
+      <c r="K3" s="42" t="str">
         <f ca="1">SUM($J3-J2)&amp; "日"</f>
         <v>-2日</v>
       </c>
     </row>
-    <row r="4" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B4" s="109" t="s">
+    <row r="4" spans="2:13" ht="19.5" thickBot="1">
+      <c r="B4" s="116" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="110"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="36">
+      <c r="C4" s="117"/>
+      <c r="D4" s="189"/>
+      <c r="E4" s="190">
         <v>2</v>
       </c>
-      <c r="F4" s="36">
+      <c r="F4" s="190">
         <v>2</v>
       </c>
-      <c r="G4" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="I4" s="67" t="s">
+      <c r="G4" s="101" t="s">
+        <v>84</v>
+      </c>
+      <c r="I4" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="J4" s="68">
+      <c r="J4" s="64">
         <v>46314</v>
       </c>
-      <c r="K4" s="69" t="str">
+      <c r="K4" s="65" t="str">
         <f ca="1">SUM(J4-J2)&amp; "日"</f>
         <v>7日</v>
       </c>
     </row>
     <row r="5" spans="2:13">
-      <c r="B5" s="115" t="s">
+      <c r="B5" s="153" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="116"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="33">
+      <c r="C5" s="154"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="30">
         <v>2</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="30">
         <v>2</v>
       </c>
-      <c r="G5" s="43" t="s">
+      <c r="G5" s="39" t="s">
         <v>84</v>
       </c>
       <c r="I5" s="4"/>
-      <c r="J5" s="55"/>
-      <c r="K5" s="56"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="52"/>
     </row>
     <row r="6" spans="2:13">
-      <c r="B6" s="113" t="s">
+      <c r="B6" s="118" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="144"/>
+      <c r="D6" s="191"/>
+      <c r="E6" s="192">
+        <f>SUM(E7)</f>
+        <v>3</v>
+      </c>
+      <c r="F6" s="192">
+        <f>SUM(F7)</f>
+        <v>3</v>
+      </c>
+      <c r="G6" s="101" t="s">
+        <v>84</v>
+      </c>
+      <c r="I6" s="4"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="52"/>
+    </row>
+    <row r="7" spans="2:13">
+      <c r="B7" s="187" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="188"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="30">
+        <v>3</v>
+      </c>
+      <c r="F7" s="30">
+        <v>3</v>
+      </c>
+      <c r="G7" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="I7" s="113" t="s">
+        <v>88</v>
+      </c>
+      <c r="J7" s="113"/>
+      <c r="K7" s="113"/>
+      <c r="L7" s="113"/>
+      <c r="M7" s="113"/>
+    </row>
+    <row r="8" spans="2:13">
+      <c r="B8" s="118" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="114"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="33">
+      <c r="C8" s="119"/>
+      <c r="D8" s="191"/>
+      <c r="E8" s="192">
         <v>2</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F8" s="192">
         <v>5</v>
       </c>
-      <c r="G6" s="43" t="s">
-        <v>84</v>
-      </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="55"/>
-      <c r="K6" s="56"/>
-    </row>
-    <row r="7" spans="2:13">
-      <c r="B7" s="111" t="s">
+      <c r="G8" s="101" t="s">
+        <v>84</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="52"/>
+    </row>
+    <row r="9" spans="2:13">
+      <c r="B9" s="128" t="s">
         <v>68</v>
       </c>
-      <c r="C7" s="112"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="34">
-        <f>SUM(E8+E9+E10+E11)</f>
+      <c r="C9" s="129"/>
+      <c r="D9" s="193"/>
+      <c r="E9" s="194">
+        <f>SUM(E10+E11+E12+E13)</f>
         <v>2</v>
       </c>
-      <c r="F7" s="34">
-        <f>SUM(F8:F11)</f>
+      <c r="F9" s="194">
+        <f>SUM(F10:F13)</f>
         <v>4</v>
       </c>
-      <c r="G7" s="85" t="s">
+      <c r="G9" s="99" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" ht="19.5" thickBot="1">
+      <c r="B10" s="122" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="123"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="30">
+        <v>1</v>
+      </c>
+      <c r="G10" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="I10" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" ht="19.5" thickBot="1">
+      <c r="B11" s="122" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="123"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="30">
+        <v>1</v>
+      </c>
+      <c r="G11" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="I11" s="126" t="s">
+        <v>103</v>
+      </c>
+      <c r="J11" s="127"/>
+    </row>
+    <row r="12" spans="2:13">
+      <c r="B12" s="122" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="123"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="F12" s="30">
+        <v>1</v>
+      </c>
+      <c r="G12" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="I12" s="102" t="s">
+        <v>99</v>
+      </c>
+      <c r="J12" s="85">
+        <f>SUM(F3+E33+E40)</f>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13">
+      <c r="B13" s="124" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="125"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="31">
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="30">
+        <v>1</v>
+      </c>
+      <c r="G13" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="I13" s="103" t="s">
+        <v>11</v>
+      </c>
+      <c r="J13" s="86">
+        <f>SUM(E19)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13">
+      <c r="B14" s="122" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="134"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="31">
+        <v>0.5</v>
+      </c>
+      <c r="F14" s="31">
+        <v>1</v>
+      </c>
+      <c r="G14" s="81" t="s">
+        <v>84</v>
+      </c>
+      <c r="I14" s="103" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="86">
+        <f>SUM(E26)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" ht="19.5" thickBot="1">
+      <c r="B15" s="128" t="s">
+        <v>104</v>
+      </c>
+      <c r="C15" s="129"/>
+      <c r="D15" s="193"/>
+      <c r="E15" s="194">
+        <v>4</v>
+      </c>
+      <c r="F15" s="194">
+        <f>SUM(F16:F18)</f>
+        <v>6.5</v>
+      </c>
+      <c r="G15" s="100" t="s">
+        <v>84</v>
+      </c>
+      <c r="I15" s="104" t="s">
+        <v>14</v>
+      </c>
+      <c r="J15" s="87">
+        <f>SUM(E31)</f>
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:13" ht="19.5" thickBot="1">
+      <c r="B16" s="130" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" s="131"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="30">
+        <v>1</v>
+      </c>
+      <c r="F16" s="30">
+        <v>1</v>
+      </c>
+      <c r="G16" s="53" t="s">
+        <v>84</v>
+      </c>
+      <c r="I16" s="198" t="s">
+        <v>101</v>
+      </c>
+      <c r="J16" s="79">
+        <f>SUM(J12:J15)</f>
+        <v>66.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="131"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="30">
+        <v>5</v>
+      </c>
+      <c r="F17" s="30">
+        <v>5</v>
+      </c>
+      <c r="G17" s="53" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B18" s="132" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="133"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="32">
+        <v>1</v>
+      </c>
+      <c r="F18" s="32">
+        <v>0.5</v>
+      </c>
+      <c r="G18" s="98" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B19" s="114" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="115"/>
+      <c r="D19" s="110" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="111">
+        <f>SUM(E20:E23)</f>
+        <v>11</v>
+      </c>
+      <c r="F19" s="111">
+        <f>SUM(F20:F23)</f>
+        <v>3</v>
+      </c>
+      <c r="G19" s="112" t="s">
         <v>80</v>
       </c>
-      <c r="I7" s="131" t="s">
-        <v>88</v>
-      </c>
-      <c r="J7" s="131"/>
-      <c r="K7" s="131"/>
-      <c r="L7" s="131"/>
-      <c r="M7" s="131"/>
-    </row>
-    <row r="8" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B8" s="124" t="s">
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="116" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="117"/>
+      <c r="D20" s="195"/>
+      <c r="E20" s="196">
+        <v>2</v>
+      </c>
+      <c r="F20" s="196">
+        <v>1</v>
+      </c>
+      <c r="G20" s="101" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="118" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="119"/>
+      <c r="D21" s="195"/>
+      <c r="E21" s="196">
+        <v>4</v>
+      </c>
+      <c r="F21" s="196"/>
+      <c r="G21" s="101" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" s="118" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="119"/>
+      <c r="D22" s="191"/>
+      <c r="E22" s="192">
+        <v>3</v>
+      </c>
+      <c r="F22" s="192">
+        <v>2</v>
+      </c>
+      <c r="G22" s="101" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7">
+      <c r="B23" s="120" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="121"/>
+      <c r="D23" s="191"/>
+      <c r="E23" s="192">
+        <v>2</v>
+      </c>
+      <c r="F23" s="192"/>
+      <c r="G23" s="99" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7">
+      <c r="B24" s="130" t="s">
         <v>89</v>
       </c>
-      <c r="C8" s="134"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="33">
+      <c r="C24" s="131"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="30">
+        <v>1</v>
+      </c>
+      <c r="F24" s="30"/>
+      <c r="G24" s="81" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B25" s="135" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="136"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="31">
+        <v>1</v>
+      </c>
+      <c r="F25" s="31"/>
+      <c r="G25" s="53" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B26" s="137" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26" s="138"/>
+      <c r="D26" s="66" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="107">
+        <f>SUM(E27+E29)</f>
+        <v>6</v>
+      </c>
+      <c r="F26" s="107">
+        <f>SUM(F27:F30)</f>
+        <v>6</v>
+      </c>
+      <c r="G26" s="94" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7">
+      <c r="B27" s="120" t="s">
+        <v>95</v>
+      </c>
+      <c r="C27" s="121"/>
+      <c r="D27" s="191"/>
+      <c r="E27" s="192">
+        <v>1</v>
+      </c>
+      <c r="F27" s="192"/>
+      <c r="G27" s="99" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7">
+      <c r="B28" s="135" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" s="136"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="31">
+        <v>2</v>
+      </c>
+      <c r="F28" s="31"/>
+      <c r="G28" s="53" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7">
+      <c r="B29" s="128" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="141"/>
+      <c r="D29" s="193"/>
+      <c r="E29" s="194">
+        <v>5</v>
+      </c>
+      <c r="F29" s="194">
+        <v>5</v>
+      </c>
+      <c r="G29" s="100" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B30" s="142" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="143"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="32">
+        <v>1</v>
+      </c>
+      <c r="F30" s="32">
+        <v>1</v>
+      </c>
+      <c r="G30" s="53" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B31" s="137" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" s="138"/>
+      <c r="D31" s="66" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="107">
+        <f>SUM(E32+E33+E41+E47)</f>
+        <v>16.5</v>
+      </c>
+      <c r="F31" s="107">
+        <f>SUM(F32+F41+F47)</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="94" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7">
+      <c r="B32" s="116" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="117"/>
+      <c r="D32" s="195"/>
+      <c r="E32" s="196">
+        <v>5</v>
+      </c>
+      <c r="F32" s="196"/>
+      <c r="G32" s="99" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="149" t="s">
+        <v>96</v>
+      </c>
+      <c r="C33" s="150"/>
+      <c r="D33" s="105" t="s">
+        <v>97</v>
+      </c>
+      <c r="E33" s="106">
+        <f>SUM(E34+E35)</f>
+        <v>7.5</v>
+      </c>
+      <c r="F33" s="106">
+        <f>SUM(F34+F35)</f>
+        <v>6.5</v>
+      </c>
+      <c r="G33" s="96" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="118" t="s">
+        <v>110</v>
+      </c>
+      <c r="C34" s="144"/>
+      <c r="D34" s="191"/>
+      <c r="E34" s="196">
         <v>0.5</v>
       </c>
-      <c r="F8" s="33">
-        <v>1</v>
-      </c>
-      <c r="G8" s="85" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B9" s="124" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" s="134"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="33">
+      <c r="F34" s="196">
         <v>0.5</v>
       </c>
-      <c r="F9" s="33">
-        <v>1</v>
-      </c>
-      <c r="G9" s="85" t="s">
-        <v>84</v>
-      </c>
-      <c r="I9" s="137" t="s">
-        <v>103</v>
-      </c>
-      <c r="J9" s="138"/>
-    </row>
-    <row r="10" spans="2:13">
-      <c r="B10" s="124" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="134"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="33">
-        <v>0.5</v>
-      </c>
-      <c r="F10" s="33">
-        <v>1</v>
-      </c>
-      <c r="G10" s="85" t="s">
-        <v>84</v>
-      </c>
-      <c r="I10" s="177" t="s">
-        <v>99</v>
-      </c>
-      <c r="J10" s="89">
-        <f>SUM(F3+E31+E38)</f>
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13">
-      <c r="B11" s="135" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="136"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="34">
-        <v>0.5</v>
-      </c>
-      <c r="F11" s="33">
-        <v>1</v>
-      </c>
-      <c r="G11" s="85" t="s">
-        <v>84</v>
-      </c>
-      <c r="I11" s="178" t="s">
-        <v>11</v>
-      </c>
-      <c r="J11" s="90">
-        <f>SUM(E17)</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13">
-      <c r="B12" s="124" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="125"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="34">
-        <v>0.5</v>
-      </c>
-      <c r="F12" s="34">
-        <v>1</v>
-      </c>
-      <c r="G12" s="85" t="s">
-        <v>84</v>
-      </c>
-      <c r="I12" s="178" t="s">
-        <v>10</v>
-      </c>
-      <c r="J12" s="90">
-        <f>SUM(E24)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B13" s="111" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="112"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="34">
-        <v>4</v>
-      </c>
-      <c r="F13" s="34">
-        <f>SUM(F14:F16)</f>
-        <v>0.5</v>
-      </c>
-      <c r="G13" s="57" t="s">
-        <v>80</v>
-      </c>
-      <c r="I13" s="179" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="91">
-        <f>SUM(E29)</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B14" s="174" t="s">
-        <v>107</v>
-      </c>
-      <c r="C14" s="180"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="33">
-        <v>1</v>
-      </c>
-      <c r="F14" s="33"/>
-      <c r="G14" s="57" t="s">
-        <v>80</v>
-      </c>
-      <c r="I14" s="93" t="s">
-        <v>101</v>
-      </c>
-      <c r="J14" s="83">
-        <f>SUM(J10:J13)</f>
-        <v>40.5</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13">
-      <c r="B15" s="174" t="s">
-        <v>108</v>
-      </c>
-      <c r="C15" s="180"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="33">
-        <v>4</v>
-      </c>
-      <c r="F15" s="33"/>
-      <c r="G15" s="57" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="2:13" ht="18.600000000000001" thickBot="1">
-      <c r="B16" s="175" t="s">
-        <v>109</v>
-      </c>
-      <c r="C16" s="181"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="35">
-        <v>1</v>
-      </c>
-      <c r="F16" s="35">
-        <v>0.5</v>
-      </c>
-      <c r="G16" s="102" t="s">
-        <v>84</v>
-      </c>
-      <c r="I16" s="176"/>
-      <c r="J16" s="176"/>
-      <c r="K16" s="176"/>
-    </row>
-    <row r="17" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B17" s="172" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="173"/>
-      <c r="D17" s="193" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="194">
-        <f>SUM(E18:E21)</f>
-        <v>11</v>
-      </c>
-      <c r="F17" s="194">
-        <f>SUM(F18:F21)</f>
-        <v>3</v>
-      </c>
-      <c r="G17" s="195" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="109" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="110"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="37">
-        <v>2</v>
-      </c>
-      <c r="F18" s="37">
-        <v>1</v>
-      </c>
-      <c r="G18" s="43" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="113" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" s="114"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="37">
-        <v>4</v>
-      </c>
-      <c r="F19" s="37"/>
-      <c r="G19" s="43" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="113" t="s">
-        <v>65</v>
-      </c>
-      <c r="C20" s="114"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="33">
-        <v>3</v>
-      </c>
-      <c r="F20" s="33">
-        <v>2</v>
-      </c>
-      <c r="G20" s="43" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7">
-      <c r="B21" s="132" t="s">
-        <v>69</v>
-      </c>
-      <c r="C21" s="133"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="33">
-        <v>2</v>
-      </c>
-      <c r="F21" s="33"/>
-      <c r="G21" s="85" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="117" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" s="118"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="33">
-        <v>1</v>
-      </c>
-      <c r="F22" s="33"/>
-      <c r="G22" s="85" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B23" s="103" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="104"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="34">
-        <v>1</v>
-      </c>
-      <c r="F23" s="34"/>
-      <c r="G23" s="57" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B24" s="107" t="s">
-        <v>2</v>
-      </c>
-      <c r="C24" s="108"/>
-      <c r="D24" s="70" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="190">
-        <f>SUM(E25:E26)</f>
-        <v>3</v>
-      </c>
-      <c r="F24" s="190">
-        <f>SUM(F25:F28)</f>
+      <c r="G34" s="99" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="B35" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="C35" s="144"/>
+      <c r="D35" s="191"/>
+      <c r="E35" s="196">
+        <f>SUM(E36+E37+E38+E39)</f>
+        <v>7</v>
+      </c>
+      <c r="F35" s="196">
+        <f>SUM(F36+F37+F38+F39)</f>
         <v>6</v>
       </c>
-      <c r="G24" s="98" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7">
-      <c r="B25" s="132" t="s">
-        <v>95</v>
-      </c>
-      <c r="C25" s="133"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="33">
-        <v>1</v>
-      </c>
-      <c r="F25" s="33"/>
-      <c r="G25" s="85" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7">
-      <c r="B26" s="103" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" s="104"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="34">
-        <v>2</v>
-      </c>
-      <c r="F26" s="34"/>
-      <c r="G26" s="57" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7">
-      <c r="B27" s="111" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="128"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="34">
-        <v>5</v>
-      </c>
-      <c r="F27" s="34">
-        <v>5</v>
-      </c>
-      <c r="G27" s="57" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B28" s="129" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" s="130"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="35">
-        <v>1</v>
-      </c>
-      <c r="F28" s="35">
-        <v>1</v>
-      </c>
-      <c r="G28" s="57" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B29" s="107" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" s="108"/>
-      <c r="D29" s="70" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="190">
-        <f>SUM(E30+E31+E39+E45)</f>
-        <v>11</v>
-      </c>
-      <c r="F29" s="190">
-        <f>SUM(F30+F39+F45)</f>
-        <v>0</v>
-      </c>
-      <c r="G29" s="98" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7">
-      <c r="B30" s="109" t="s">
-        <v>63</v>
-      </c>
-      <c r="C30" s="110"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="37">
-        <v>5</v>
-      </c>
-      <c r="F30" s="37"/>
-      <c r="G30" s="85" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7">
-      <c r="B31" s="121" t="s">
-        <v>96</v>
-      </c>
-      <c r="C31" s="122"/>
-      <c r="D31" s="188" t="s">
-        <v>97</v>
-      </c>
-      <c r="E31" s="189">
-        <v>2</v>
-      </c>
-      <c r="F31" s="189"/>
-      <c r="G31" s="100" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7">
-      <c r="B32" s="113" t="s">
-        <v>110</v>
-      </c>
-      <c r="C32" s="123"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="37">
-        <v>0.5</v>
-      </c>
-      <c r="F32" s="37">
-        <v>0.5</v>
-      </c>
-      <c r="G32" s="85" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="113" t="s">
-        <v>93</v>
-      </c>
-      <c r="C33" s="123"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="37">
-        <f>SUM(E34+E35+E36+E37)</f>
-        <v>7</v>
-      </c>
-      <c r="F33" s="37">
-        <f>SUM(F34+F35+F36+F37)</f>
-        <v>6</v>
-      </c>
-      <c r="G33" s="85" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7">
-      <c r="B34" s="184" t="s">
+      <c r="G35" s="99" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="145" t="s">
         <v>111</v>
       </c>
-      <c r="C34" s="185"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="37">
+      <c r="C36" s="146"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="33">
         <f>2</f>
         <v>2</v>
       </c>
-      <c r="F34" s="37">
+      <c r="F36" s="33">
         <v>1.5</v>
       </c>
-      <c r="G34" s="85" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="184" t="s">
+      <c r="G36" s="81" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="145" t="s">
         <v>112</v>
       </c>
-      <c r="C35" s="185"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="37">
+      <c r="C37" s="146"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="33">
         <v>2</v>
       </c>
-      <c r="F35" s="37">
+      <c r="F37" s="33">
         <v>1.5</v>
       </c>
-      <c r="G35" s="85" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="184" t="s">
+      <c r="G37" s="81" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="145" t="s">
         <v>113</v>
       </c>
-      <c r="C36" s="185"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="37">
+      <c r="C38" s="146"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="33">
         <v>2</v>
       </c>
-      <c r="F36" s="37">
+      <c r="F38" s="33">
         <v>1.5</v>
       </c>
-      <c r="G36" s="85" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7">
-      <c r="B37" s="182" t="s">
+      <c r="G38" s="81" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" s="122" t="s">
         <v>114</v>
       </c>
-      <c r="C37" s="183"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="37">
-        <v>1</v>
-      </c>
-      <c r="F37" s="37">
+      <c r="C39" s="134"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="33">
+        <v>1</v>
+      </c>
+      <c r="F39" s="33">
         <v>1.5</v>
       </c>
-      <c r="G37" s="85" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7">
-      <c r="B38" s="121" t="s">
+      <c r="G39" s="81" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7">
+      <c r="B40" s="149" t="s">
         <v>4</v>
       </c>
-      <c r="C38" s="122"/>
-      <c r="D38" s="188" t="s">
+      <c r="C40" s="150"/>
+      <c r="D40" s="105" t="s">
         <v>97</v>
       </c>
-      <c r="E38" s="191">
-        <f>SUM(E39:E43)</f>
-        <v>6</v>
-      </c>
-      <c r="F38" s="191"/>
-      <c r="G38" s="100" t="s">
+      <c r="E40" s="108">
+        <f>SUM(E41:E43)</f>
+        <v>5</v>
+      </c>
+      <c r="F40" s="108"/>
+      <c r="G40" s="96" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="39" spans="2:7">
-      <c r="B39" s="113" t="s">
+    <row r="41" spans="2:7">
+      <c r="B41" s="118" t="s">
         <v>66</v>
       </c>
-      <c r="C39" s="114"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="33">
+      <c r="C41" s="119"/>
+      <c r="D41" s="191"/>
+      <c r="E41" s="192">
         <v>2</v>
       </c>
-      <c r="F39" s="33"/>
-      <c r="G39" s="85" t="s">
+      <c r="F41" s="192"/>
+      <c r="G41" s="99" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="2:7">
-      <c r="B40" s="113" t="s">
+    <row r="42" spans="2:7">
+      <c r="B42" s="118" t="s">
         <v>98</v>
       </c>
-      <c r="C40" s="114"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="33">
+      <c r="C42" s="119"/>
+      <c r="D42" s="191"/>
+      <c r="E42" s="192">
         <v>2</v>
       </c>
-      <c r="F40" s="33">
+      <c r="F42" s="192">
         <v>2</v>
       </c>
-      <c r="G40" s="85" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7">
-      <c r="B41" s="113" t="s">
+      <c r="G42" s="99" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7">
+      <c r="B43" s="118" t="s">
         <v>67</v>
       </c>
-      <c r="C41" s="123"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="33">
-        <f>SUM(E42+E43)</f>
-        <v>1</v>
-      </c>
-      <c r="F41" s="33"/>
-      <c r="G41" s="85" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7">
-      <c r="B42" s="186" t="s">
+      <c r="C43" s="144"/>
+      <c r="D43" s="191"/>
+      <c r="E43" s="192">
+        <f>SUM(E44+E45)</f>
+        <v>1</v>
+      </c>
+      <c r="F43" s="192"/>
+      <c r="G43" s="99" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7">
+      <c r="B44" s="145" t="s">
         <v>116</v>
       </c>
-      <c r="C42" s="187"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="33">
+      <c r="C44" s="146"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="30">
         <v>0.5</v>
       </c>
-      <c r="F42" s="33"/>
-      <c r="G42" s="85" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7">
-      <c r="B43" s="124" t="s">
+      <c r="F44" s="30"/>
+      <c r="G44" s="81" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7">
+      <c r="B45" s="122" t="s">
         <v>115</v>
       </c>
-      <c r="C43" s="125"/>
-      <c r="D43" s="6"/>
-      <c r="E43" s="33">
+      <c r="C45" s="134"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="30">
         <v>0.5</v>
       </c>
-      <c r="F43" s="33"/>
-      <c r="G43" s="85" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7">
-      <c r="B44" s="121" t="s">
+      <c r="F45" s="30"/>
+      <c r="G45" s="81" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7">
+      <c r="B46" s="149" t="s">
         <v>5</v>
       </c>
-      <c r="C44" s="122"/>
-      <c r="D44" s="188"/>
-      <c r="E44" s="191"/>
-      <c r="F44" s="191"/>
-      <c r="G44" s="100" t="s">
+      <c r="C46" s="150"/>
+      <c r="D46" s="105"/>
+      <c r="E46" s="108"/>
+      <c r="F46" s="108"/>
+      <c r="G46" s="96" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="2:7">
-      <c r="B45" s="126" t="s">
+    <row r="47" spans="2:7">
+      <c r="B47" s="139" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="127"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="34">
+      <c r="C47" s="140"/>
+      <c r="D47" s="193"/>
+      <c r="E47" s="194">
         <v>2</v>
       </c>
-      <c r="F45" s="34"/>
-      <c r="G45" s="57" t="s">
+      <c r="F47" s="194"/>
+      <c r="G47" s="100" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="46" spans="2:7">
-      <c r="B46" s="113" t="s">
+    <row r="48" spans="2:7">
+      <c r="B48" s="118" t="s">
         <v>98</v>
       </c>
-      <c r="C46" s="114"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="34"/>
-      <c r="F46" s="34"/>
-      <c r="G46" s="57" t="s">
+      <c r="C48" s="119"/>
+      <c r="D48" s="193"/>
+      <c r="E48" s="194"/>
+      <c r="F48" s="194"/>
+      <c r="G48" s="100" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="47" spans="2:7">
-      <c r="B47" s="121" t="s">
+    <row r="49" spans="2:7">
+      <c r="B49" s="149" t="s">
         <v>100</v>
       </c>
-      <c r="C47" s="122"/>
-      <c r="D47" s="188"/>
-      <c r="E47" s="191"/>
-      <c r="F47" s="191"/>
-      <c r="G47" s="192" t="s">
+      <c r="C49" s="150"/>
+      <c r="D49" s="105"/>
+      <c r="E49" s="108"/>
+      <c r="F49" s="108"/>
+      <c r="G49" s="109" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="48" spans="2:7">
-      <c r="B48" s="126" t="s">
+    <row r="50" spans="2:7">
+      <c r="B50" s="139" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="127"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="33">
+      <c r="C50" s="140"/>
+      <c r="D50" s="191"/>
+      <c r="E50" s="192">
         <v>2</v>
       </c>
-      <c r="F48" s="33"/>
-      <c r="G48" s="57" t="s">
+      <c r="F50" s="192"/>
+      <c r="G50" s="100" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="49" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B49" s="111" t="s">
+    <row r="51" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B51" s="128" t="s">
         <v>98</v>
       </c>
-      <c r="C49" s="112"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="34">
+      <c r="C51" s="129"/>
+      <c r="D51" s="193"/>
+      <c r="E51" s="194">
         <v>2</v>
       </c>
-      <c r="F49" s="34"/>
-      <c r="G49" s="57" t="s">
+      <c r="F51" s="194"/>
+      <c r="G51" s="100" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="50" spans="2:7">
-      <c r="B50" s="119" t="s">
+    <row r="52" spans="2:7">
+      <c r="B52" s="147" t="s">
         <v>34</v>
       </c>
-      <c r="C50" s="120"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="38">
-        <f>SUM(E3+E17+E24+E29)</f>
-        <v>33</v>
-      </c>
-      <c r="F50" s="38">
-        <f>SUM(F3+F17+F24+F29)</f>
-        <v>16.5</v>
-      </c>
-      <c r="G50" s="92"/>
+      <c r="C52" s="148"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="34">
+        <f>SUM(E3+E19+E26+E31)</f>
+        <v>46.5</v>
+      </c>
+      <c r="F52" s="34">
+        <f>SUM(F3+F19+F26+F31)</f>
+        <v>29.5</v>
+      </c>
+      <c r="G52" s="88"/>
     </row>
   </sheetData>
-  <mergeCells count="51">
-    <mergeCell ref="I7:M7"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
+  <mergeCells count="53">
     <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B23:C23"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="I7:M7"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="E17 E3" formulaRange="1"/>
+    <ignoredError sqref="E19" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4103,370 +4177,382 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF80DA5A-1B69-4377-A99E-364B8197EABC}">
   <dimension ref="B1:L21"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="8" max="8" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.09765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="18.600000000000001" thickBot="1"/>
-    <row r="2" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B2" s="167" t="s">
+    <row r="1" spans="2:12" ht="19.5" thickBot="1"/>
+    <row r="2" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B2" s="172" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="168"/>
-      <c r="D2" s="10" t="s">
+      <c r="C2" s="173"/>
+      <c r="D2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="F2" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="G2" s="35" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B3" s="163" t="s">
+    <row r="3" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B3" s="174" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="164"/>
-      <c r="D3" s="10" t="s">
+      <c r="C3" s="175"/>
+      <c r="D3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="38">
+      <c r="E3" s="34">
         <f>SUM(E4)</f>
         <v>3</v>
       </c>
-      <c r="F3" s="60">
+      <c r="F3" s="56">
         <f>SUM(F4)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="39" t="s">
+      <c r="G3" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="J3" s="48" t="s">
+      <c r="J3" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="K3" s="51">
+      <c r="K3" s="47">
         <f ca="1">TODAY()</f>
         <v>46307</v>
       </c>
-      <c r="L3" s="39" t="s">
+      <c r="L3" s="35" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="4" spans="2:12">
-      <c r="B4" s="169" t="s">
+      <c r="B4" s="176" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="170"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="78">
+      <c r="C4" s="177"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="74">
         <v>3</v>
       </c>
-      <c r="F4" s="76">
+      <c r="F4" s="72">
         <f>SUM(F6)</f>
         <v>0</v>
       </c>
-      <c r="G4" s="79" t="s">
+      <c r="G4" s="75" t="s">
         <v>80</v>
       </c>
-      <c r="J4" s="52" t="s">
+      <c r="J4" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="K4" s="49">
+      <c r="K4" s="45">
         <v>46310</v>
       </c>
-      <c r="L4" s="45" t="str">
+      <c r="L4" s="41" t="str">
         <f ca="1">SUM($L4-I1)&amp; "日"</f>
         <v>15日</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B5" s="111" t="s">
+    <row r="5" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B5" s="128" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="128"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="34">
+      <c r="C5" s="141"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="31">
         <v>3</v>
       </c>
-      <c r="F5" s="66"/>
-      <c r="G5" s="57"/>
-      <c r="J5" s="53" t="s">
+      <c r="F5" s="62"/>
+      <c r="G5" s="53"/>
+      <c r="J5" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="K5" s="49">
+      <c r="K5" s="45">
         <v>46313</v>
       </c>
-      <c r="L5" s="45" t="str">
+      <c r="L5" s="41" t="str">
         <f ca="1">SUM($L5-I1)&amp; "日"</f>
         <v>18日</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B6" s="163" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="164"/>
-      <c r="D6" s="10" t="s">
+    <row r="6" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B6" s="174" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="175"/>
+      <c r="D6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="38">
+      <c r="E6" s="34">
         <f>SUM(E7)</f>
         <v>3</v>
       </c>
-      <c r="F6" s="60">
+      <c r="F6" s="56">
         <f t="shared" ref="F6" si="0">SUM(F7)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="39" t="s">
+      <c r="G6" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="J6" s="54" t="s">
+      <c r="J6" s="50" t="s">
         <v>73</v>
       </c>
-      <c r="K6" s="50">
+      <c r="K6" s="46">
         <v>46314</v>
       </c>
-      <c r="L6" s="46" t="str">
+      <c r="L6" s="42" t="str">
         <f ca="1">SUM(K6-K3)&amp; "日"</f>
         <v>7日</v>
       </c>
     </row>
     <row r="7" spans="2:12">
-      <c r="B7" s="161" t="s">
+      <c r="B7" s="180" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="162"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="63">
+      <c r="C7" s="181"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="59">
         <v>3</v>
       </c>
-      <c r="F7" s="76">
+      <c r="F7" s="72">
         <f>SUM(F9)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="60" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B8" s="111" t="s">
+    <row r="8" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B8" s="128" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="128"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="34">
+      <c r="C8" s="141"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="31">
         <v>3</v>
       </c>
-      <c r="F8" s="66"/>
-      <c r="G8" s="57"/>
+      <c r="F8" s="62"/>
+      <c r="G8" s="53"/>
       <c r="J8" s="4"/>
-      <c r="K8" s="55"/>
-      <c r="L8" s="56"/>
-    </row>
-    <row r="9" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B9" s="163" t="s">
+      <c r="K8" s="51"/>
+      <c r="L8" s="52"/>
+    </row>
+    <row r="9" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B9" s="174" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="164"/>
-      <c r="D9" s="10" t="s">
+      <c r="C9" s="175"/>
+      <c r="D9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="34">
         <f>SUM(E10:E11)</f>
         <v>5</v>
       </c>
-      <c r="F9" s="60">
+      <c r="F9" s="56">
         <f>SUM(F10:F11)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="39" t="s">
+      <c r="G9" s="35" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="10" spans="2:12">
-      <c r="B10" s="155" t="s">
+      <c r="B10" s="161" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="165"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="37">
+      <c r="C10" s="178"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="33">
         <v>3</v>
       </c>
-      <c r="F10" s="47"/>
-      <c r="G10" s="43" t="s">
+      <c r="F10" s="43"/>
+      <c r="G10" s="39" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B11" s="153" t="s">
+    <row r="11" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B11" s="157" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="166"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="34">
+      <c r="C11" s="179"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="31">
         <v>2</v>
       </c>
-      <c r="F11" s="66"/>
-      <c r="G11" s="57" t="s">
+      <c r="F11" s="62"/>
+      <c r="G11" s="53" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="12" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B12" s="163" t="s">
+    <row r="12" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B12" s="174" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="164"/>
-      <c r="D12" s="10" t="s">
+      <c r="C12" s="175"/>
+      <c r="D12" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="38">
+      <c r="E12" s="34">
         <f>SUM(E13)</f>
         <v>2</v>
       </c>
-      <c r="F12" s="60">
+      <c r="F12" s="56">
         <f>SUM(F14+F17)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="39" t="s">
+      <c r="G12" s="35" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B13" s="161" t="s">
+    <row r="13" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B13" s="180" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="162"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="63">
+      <c r="C13" s="181"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="59">
         <v>2</v>
       </c>
-      <c r="F13" s="65"/>
-      <c r="G13" s="64" t="s">
+      <c r="F13" s="61"/>
+      <c r="G13" s="60" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B14" s="163" t="s">
+    <row r="14" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B14" s="174" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="164"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="38">
+      <c r="C14" s="175"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="34">
         <f>SUM(E15:E16)</f>
         <v>2</v>
       </c>
-      <c r="F14" s="60">
+      <c r="F14" s="56">
         <f>SUM(F15:F16)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="39" t="s">
+      <c r="G14" s="35" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="15" spans="2:12">
-      <c r="B15" s="155" t="s">
+      <c r="B15" s="161" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="165"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="37">
-        <v>1</v>
-      </c>
-      <c r="F15" s="47"/>
-      <c r="G15" s="43" t="s">
+      <c r="C15" s="178"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="33">
+        <v>1</v>
+      </c>
+      <c r="F15" s="43"/>
+      <c r="G15" s="39" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="18.600000000000001" thickBot="1">
-      <c r="B16" s="153" t="s">
+    <row r="16" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B16" s="157" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="166"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="34">
-        <v>1</v>
-      </c>
-      <c r="F16" s="66"/>
-      <c r="G16" s="57" t="s">
+      <c r="C16" s="179"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="31">
+        <v>1</v>
+      </c>
+      <c r="F16" s="62"/>
+      <c r="G16" s="53" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B17" s="163" t="s">
+    <row r="17" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B17" s="174" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="164"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="38">
+      <c r="C17" s="175"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="34">
         <f>SUM(E18:E19)</f>
         <v>2</v>
       </c>
-      <c r="F17" s="60">
+      <c r="F17" s="56">
         <f>SUM(F18:F19)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="39" t="s">
+      <c r="G17" s="35" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="155" t="s">
+      <c r="B18" s="161" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="165"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="37">
-        <v>1</v>
-      </c>
-      <c r="F18" s="47"/>
-      <c r="G18" s="43" t="s">
+      <c r="C18" s="178"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="33">
+        <v>1</v>
+      </c>
+      <c r="F18" s="43"/>
+      <c r="G18" s="39" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B19" s="157" t="s">
+    <row r="19" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B19" s="182" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="158"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="35">
-        <v>1</v>
-      </c>
-      <c r="F19" s="46"/>
-      <c r="G19" s="57" t="s">
+      <c r="C19" s="183"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="32">
+        <v>1</v>
+      </c>
+      <c r="F19" s="42"/>
+      <c r="G19" s="53" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="2:7" ht="18.600000000000001" thickBot="1">
-      <c r="B20" s="159" t="s">
+    <row r="20" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B20" s="184" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="160"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="38">
+      <c r="C20" s="185"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="34">
         <f>SUM(E3+E6+E9+E12+E14+E17)</f>
         <v>17</v>
       </c>
-      <c r="F20" s="38">
+      <c r="F20" s="34">
         <f>SUM(F3+F6+F9+F12+F14+F17)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="10"/>
+      <c r="G20" s="9"/>
     </row>
     <row r="21" spans="2:7">
       <c r="G21" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
@@ -4474,18 +4560,6 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4495,37 +4569,37 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D63B4141-FE5F-4FCB-9F3D-2486D26F1F00}">
   <dimension ref="B1:K12"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="171" t="s">
+      <c r="C1" s="186" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
-      <c r="F1" s="171"/>
-      <c r="G1" s="171"/>
-    </row>
-    <row r="2" spans="2:11" ht="18.600000000000001" thickBot="1">
-      <c r="B2" s="27" t="s">
+      <c r="D1" s="186"/>
+      <c r="E1" s="186"/>
+      <c r="F1" s="186"/>
+      <c r="G1" s="186"/>
+    </row>
+    <row r="2" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="28" t="s">
+      <c r="E2" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="28" t="s">
+      <c r="F2" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="28" t="s">
+      <c r="G2" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="H2" s="26" t="s">
         <v>21</v>
       </c>
       <c r="J2" t="s">
@@ -4533,292 +4607,292 @@
       </c>
     </row>
     <row r="3" spans="2:11">
-      <c r="B3" s="24"/>
-      <c r="D3" s="25">
+      <c r="B3" s="21"/>
+      <c r="D3" s="22">
         <v>46266</v>
       </c>
-      <c r="E3" s="25">
+      <c r="E3" s="22">
         <f>SUM(D3)+1</f>
         <v>46267</v>
       </c>
-      <c r="F3" s="25">
+      <c r="F3" s="22">
         <f t="shared" ref="F3:H3" si="0">SUM(E3)+1</f>
         <v>46268</v>
       </c>
-      <c r="G3" s="25">
+      <c r="G3" s="22">
         <f t="shared" si="0"/>
         <v>46269</v>
       </c>
-      <c r="H3" s="26">
+      <c r="H3" s="23">
         <f t="shared" si="0"/>
         <v>46270</v>
       </c>
-      <c r="J3" s="14"/>
+      <c r="J3" s="13"/>
       <c r="K3" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" spans="2:11">
-      <c r="B4" s="18">
+      <c r="B4" s="17">
         <f>SUM(H3)+1</f>
         <v>46271</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="16">
         <f>SUM(B4)+1</f>
         <v>46272</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="16">
         <f t="shared" ref="D4:H4" si="1">SUM(C4)+1</f>
         <v>46273</v>
       </c>
-      <c r="E4" s="40">
+      <c r="E4" s="36">
         <f t="shared" si="1"/>
         <v>46274</v>
       </c>
-      <c r="F4" s="40">
+      <c r="F4" s="36">
         <f t="shared" si="1"/>
         <v>46275</v>
       </c>
-      <c r="G4" s="40">
+      <c r="G4" s="36">
         <f t="shared" si="1"/>
         <v>46276</v>
       </c>
-      <c r="H4" s="41">
+      <c r="H4" s="37">
         <f t="shared" si="1"/>
         <v>46277</v>
       </c>
-      <c r="J4" s="15"/>
+      <c r="J4" s="14"/>
       <c r="K4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="2:11">
-      <c r="B5" s="42">
+      <c r="B5" s="38">
         <f>SUM(H4)+1</f>
         <v>46278</v>
       </c>
-      <c r="C5" s="40">
+      <c r="C5" s="36">
         <f>SUM(B5)+1</f>
         <v>46279</v>
       </c>
-      <c r="D5" s="40">
+      <c r="D5" s="36">
         <f t="shared" ref="D5:H5" si="2">SUM(C5)+1</f>
         <v>46280</v>
       </c>
-      <c r="E5" s="40">
+      <c r="E5" s="36">
         <f t="shared" si="2"/>
         <v>46281</v>
       </c>
-      <c r="F5" s="40">
+      <c r="F5" s="36">
         <f t="shared" si="2"/>
         <v>46282</v>
       </c>
-      <c r="G5" s="40">
+      <c r="G5" s="36">
         <f t="shared" si="2"/>
         <v>46283</v>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="37">
         <f t="shared" si="2"/>
         <v>46284</v>
       </c>
-      <c r="J5" s="16"/>
+      <c r="J5" s="15"/>
       <c r="K5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="2:11">
-      <c r="B6" s="42">
+      <c r="B6" s="38">
         <f>SUM(H5)+1</f>
         <v>46285</v>
       </c>
-      <c r="C6" s="40">
+      <c r="C6" s="36">
         <f>SUM(B6)+1</f>
         <v>46286</v>
       </c>
-      <c r="D6" s="40">
+      <c r="D6" s="36">
         <f t="shared" ref="D6:H6" si="3">SUM(C6)+1</f>
         <v>46287</v>
       </c>
-      <c r="E6" s="40">
+      <c r="E6" s="36">
         <f t="shared" si="3"/>
         <v>46288</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="36">
         <f t="shared" si="3"/>
         <v>46289</v>
       </c>
-      <c r="G6" s="40">
+      <c r="G6" s="36">
         <f t="shared" si="3"/>
         <v>46290</v>
       </c>
-      <c r="H6" s="41">
+      <c r="H6" s="37">
         <f t="shared" si="3"/>
         <v>46291</v>
       </c>
-      <c r="J6" s="23"/>
+      <c r="J6" s="20"/>
       <c r="K6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="18.600000000000001" thickBot="1">
-      <c r="B7" s="58">
+    <row r="7" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B7" s="54">
         <f>SUM(H6)+1</f>
         <v>46292</v>
       </c>
-      <c r="C7" s="59">
+      <c r="C7" s="55">
         <f>SUM(B7)+1</f>
         <v>46293</v>
       </c>
-      <c r="D7" s="59">
+      <c r="D7" s="55">
         <f t="shared" ref="D7:E7" si="4">SUM(C7)+1</f>
         <v>46294</v>
       </c>
-      <c r="E7" s="59">
+      <c r="E7" s="55">
         <f t="shared" si="4"/>
         <v>46295</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="2"/>
-      <c r="J7" s="96"/>
+      <c r="J7" s="92"/>
       <c r="K7" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="8" spans="2:11">
-      <c r="B8" s="24"/>
+      <c r="B8" s="21"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="94">
+      <c r="F8" s="90">
         <f>SUM(E7)+1</f>
         <v>46296</v>
       </c>
-      <c r="G8" s="94">
+      <c r="G8" s="90">
         <f>SUM(F8)+1</f>
         <v>46297</v>
       </c>
-      <c r="H8" s="95">
+      <c r="H8" s="91">
         <f>SUM(G8)+1</f>
         <v>46298</v>
       </c>
     </row>
     <row r="9" spans="2:11">
-      <c r="B9" s="42">
+      <c r="B9" s="38">
         <f>SUM(H8)+1</f>
         <v>46299</v>
       </c>
-      <c r="C9" s="40">
+      <c r="C9" s="36">
         <f>SUM(B9)+1</f>
         <v>46300</v>
       </c>
-      <c r="D9" s="40">
+      <c r="D9" s="36">
         <f t="shared" ref="D9:H9" si="5">SUM(C9)+1</f>
         <v>46301</v>
       </c>
-      <c r="E9" s="40">
+      <c r="E9" s="36">
         <f t="shared" si="5"/>
         <v>46302</v>
       </c>
-      <c r="F9" s="40">
+      <c r="F9" s="36">
         <f t="shared" si="5"/>
         <v>46303</v>
       </c>
-      <c r="G9" s="40">
+      <c r="G9" s="36">
         <f t="shared" si="5"/>
         <v>46304</v>
       </c>
-      <c r="H9" s="21">
+      <c r="H9" s="37">
         <f t="shared" si="5"/>
         <v>46305</v>
       </c>
     </row>
     <row r="10" spans="2:11">
-      <c r="B10" s="19">
+      <c r="B10" s="38">
         <f t="shared" ref="B10:B12" si="6">SUM(H9)+1</f>
         <v>46306</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="18">
         <f>SUM(B10)+1</f>
         <v>46307</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="19">
         <f t="shared" ref="D10:G10" si="7">SUM(C10)+1</f>
         <v>46308</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="19">
         <f t="shared" si="7"/>
         <v>46309</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="19">
         <f t="shared" si="7"/>
         <v>46310</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="19">
         <f t="shared" si="7"/>
         <v>46311</v>
       </c>
-      <c r="H10" s="80">
+      <c r="H10" s="76">
         <f>SUM(G10)+1</f>
         <v>46312</v>
       </c>
     </row>
     <row r="11" spans="2:11">
-      <c r="B11" s="44">
+      <c r="B11" s="40">
         <f t="shared" si="6"/>
         <v>46313</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="29">
         <f>SUM(B11)+1</f>
         <v>46314</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <f t="shared" ref="D11:F11" si="8">SUM(C11)+1</f>
         <v>46315</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="10">
         <f t="shared" si="8"/>
         <v>46316</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="10">
         <f t="shared" si="8"/>
         <v>46317</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="10">
         <f t="shared" ref="G11" si="9">SUM(F11)+1</f>
         <v>46318</v>
       </c>
-      <c r="H11" s="30">
+      <c r="H11" s="27">
         <f>SUM(G11)+1</f>
         <v>46319</v>
       </c>
     </row>
-    <row r="12" spans="2:11" ht="18.600000000000001" thickBot="1">
-      <c r="B12" s="31">
+    <row r="12" spans="2:11" ht="19.5" thickBot="1">
+      <c r="B12" s="28">
         <f t="shared" si="6"/>
         <v>46320</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="11">
         <f>SUM(B12)+1</f>
         <v>46321</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11">
         <f t="shared" ref="D12:H12" si="10">SUM(C12)+1</f>
         <v>46322</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="11">
         <f t="shared" si="10"/>
         <v>46323</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="11">
         <f t="shared" si="10"/>
         <v>46324</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="11">
         <f t="shared" si="10"/>
         <v>46325</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="12">
         <f t="shared" si="10"/>
         <v>46326</v>
       </c>
@@ -4835,7 +4909,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52F8B42D-C760-44A9-BC69-9B00588EFF82}">
   <dimension ref="B2:B14"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" t="s">

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75609BC6-8B68-4443-9C2A-DDC4338F485A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1920484-5A3F-43D1-A911-8EFB03214C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="599" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\Documents\GitHub\GlassesGame\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FunasakoYuga\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1920484-5A3F-43D1-A911-8EFB03214C03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D36E81-1609-46F9-B9A5-4C0D2D062A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="121">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -793,6 +793,10 @@
     <rPh sb="5" eb="7">
       <t>ジカン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完了</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1565,7 +1569,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="199">
+  <cellXfs count="197">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1825,6 +1829,129 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1834,27 +1961,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1870,85 +1976,46 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1963,43 +2030,40 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2008,80 +2072,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2389,10 +2387,10 @@
   <sheetData>
     <row r="1" spans="2:19" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B2" s="151" t="s">
+      <c r="B2" s="124" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="164"/>
+      <c r="C2" s="174"/>
       <c r="D2" s="68" t="s">
         <v>9</v>
       </c>
@@ -2407,10 +2405,10 @@
       </c>
     </row>
     <row r="3" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B3" s="137" t="s">
+      <c r="B3" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="163"/>
+      <c r="C3" s="170"/>
       <c r="D3" s="97" t="s">
         <v>12</v>
       </c>
@@ -2430,17 +2428,17 @@
       </c>
       <c r="J3" s="47">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="K3" s="35" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="4" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B4" s="116" t="s">
+      <c r="B4" s="128" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="165"/>
+      <c r="C4" s="169"/>
       <c r="D4" s="78"/>
       <c r="E4" s="33">
         <f>SUM(E5:E7)</f>
@@ -2461,14 +2459,14 @@
       </c>
       <c r="K4" s="56" t="str">
         <f ca="1">SUM($J4-J3)&amp; "日"</f>
-        <v>-12日</v>
+        <v>-13日</v>
       </c>
     </row>
     <row r="5" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B5" s="122" t="s">
+      <c r="B5" s="139" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="134"/>
+      <c r="C5" s="140"/>
       <c r="D5" s="70"/>
       <c r="E5" s="30">
         <v>2</v>
@@ -2487,16 +2485,16 @@
       </c>
       <c r="K5" s="65" t="str">
         <f ca="1">SUM(J5-J3)&amp; "日"</f>
-        <v>7日</v>
+        <v>6日</v>
       </c>
       <c r="R5" s="51"/>
       <c r="S5" s="52"/>
     </row>
     <row r="6" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B6" s="122" t="s">
+      <c r="B6" s="139" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="134"/>
+      <c r="C6" s="140"/>
       <c r="D6" s="70"/>
       <c r="E6" s="30">
         <v>1</v>
@@ -2511,10 +2509,10 @@
       <c r="S6" s="52"/>
     </row>
     <row r="7" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B7" s="122" t="s">
+      <c r="B7" s="139" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="134"/>
+      <c r="C7" s="140"/>
       <c r="D7" s="70"/>
       <c r="E7" s="30">
         <v>1</v>
@@ -2525,18 +2523,18 @@
       <c r="G7" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="I7" s="155" t="s">
+      <c r="I7" s="176" t="s">
         <v>102</v>
       </c>
-      <c r="J7" s="156"/>
+      <c r="J7" s="177"/>
       <c r="R7" s="51"/>
       <c r="S7" s="52"/>
     </row>
     <row r="8" spans="2:19">
-      <c r="B8" s="118" t="s">
+      <c r="B8" s="132" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="144"/>
+      <c r="C8" s="138"/>
       <c r="D8" s="70"/>
       <c r="E8" s="30">
         <v>2</v>
@@ -2556,10 +2554,10 @@
       </c>
     </row>
     <row r="9" spans="2:19">
-      <c r="B9" s="118" t="s">
+      <c r="B9" s="132" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="144"/>
+      <c r="C9" s="138"/>
       <c r="D9" s="71"/>
       <c r="E9" s="31">
         <v>2</v>
@@ -2579,10 +2577,10 @@
       </c>
     </row>
     <row r="10" spans="2:19">
-      <c r="B10" s="118" t="s">
+      <c r="B10" s="132" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="144"/>
+      <c r="C10" s="138"/>
       <c r="D10" s="71"/>
       <c r="E10" s="31">
         <v>2</v>
@@ -2602,10 +2600,10 @@
       </c>
     </row>
     <row r="11" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B11" s="120" t="s">
+      <c r="B11" s="152" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="160"/>
+      <c r="C11" s="175"/>
       <c r="D11" s="70"/>
       <c r="E11" s="30">
         <v>1</v>
@@ -2625,10 +2623,10 @@
       </c>
     </row>
     <row r="12" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B12" s="118" t="s">
+      <c r="B12" s="132" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="144"/>
+      <c r="C12" s="138"/>
       <c r="D12" s="70"/>
       <c r="E12" s="30">
         <f>SUM(E13:E15)</f>
@@ -2650,10 +2648,10 @@
       </c>
     </row>
     <row r="13" spans="2:19">
-      <c r="B13" s="130" t="s">
+      <c r="B13" s="136" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="159"/>
+      <c r="C13" s="167"/>
       <c r="D13" s="70"/>
       <c r="E13" s="30">
         <v>1</v>
@@ -2666,10 +2664,10 @@
       </c>
     </row>
     <row r="14" spans="2:19">
-      <c r="B14" s="122" t="s">
+      <c r="B14" s="139" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="134"/>
+      <c r="C14" s="140"/>
       <c r="D14" s="70"/>
       <c r="E14" s="30">
         <v>1</v>
@@ -2684,10 +2682,10 @@
       <c r="S14" s="52"/>
     </row>
     <row r="15" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B15" s="124" t="s">
+      <c r="B15" s="158" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="167"/>
+      <c r="C15" s="166"/>
       <c r="D15" s="71"/>
       <c r="E15" s="31">
         <v>1</v>
@@ -2700,10 +2698,10 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B16" s="137" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="163"/>
+      <c r="B16" s="126" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="170"/>
       <c r="D16" s="93" t="s">
         <v>11</v>
       </c>
@@ -2719,10 +2717,10 @@
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="116" t="s">
+      <c r="B17" s="128" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="165"/>
+      <c r="C17" s="169"/>
       <c r="D17" s="78"/>
       <c r="E17" s="33">
         <v>3</v>
@@ -2735,10 +2733,10 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="118" t="s">
+      <c r="B18" s="132" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="144"/>
+      <c r="C18" s="138"/>
       <c r="D18" s="70"/>
       <c r="E18" s="30">
         <v>3</v>
@@ -2751,10 +2749,10 @@
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="118" t="s">
+      <c r="B19" s="132" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="144"/>
+      <c r="C19" s="138"/>
       <c r="D19" s="70"/>
       <c r="E19" s="30">
         <v>3</v>
@@ -2767,10 +2765,10 @@
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="118" t="s">
+      <c r="B20" s="132" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="144"/>
+      <c r="C20" s="138"/>
       <c r="D20" s="71"/>
       <c r="E20" s="30">
         <v>3</v>
@@ -2783,10 +2781,10 @@
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="118" t="s">
+      <c r="B21" s="132" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="144"/>
+      <c r="C21" s="138"/>
       <c r="D21" s="70"/>
       <c r="E21" s="59">
         <v>1</v>
@@ -2799,10 +2797,10 @@
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="120" t="s">
+      <c r="B22" s="152" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="160"/>
+      <c r="C22" s="175"/>
       <c r="D22" s="70"/>
       <c r="E22" s="30"/>
       <c r="F22" s="30">
@@ -2813,10 +2811,10 @@
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="130" t="s">
+      <c r="B23" s="136" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="159"/>
+      <c r="C23" s="167"/>
       <c r="D23" s="70"/>
       <c r="E23" s="30">
         <v>1</v>
@@ -2829,10 +2827,10 @@
       </c>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="130" t="s">
+      <c r="B24" s="136" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="159"/>
+      <c r="C24" s="167"/>
       <c r="D24" s="70"/>
       <c r="E24" s="30">
         <v>1</v>
@@ -2845,7 +2843,7 @@
       </c>
     </row>
     <row r="25" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B25" s="132" t="s">
+      <c r="B25" s="162" t="s">
         <v>50</v>
       </c>
       <c r="C25" s="168"/>
@@ -2861,10 +2859,10 @@
       </c>
     </row>
     <row r="26" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B26" s="137" t="s">
+      <c r="B26" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="163"/>
+      <c r="C26" s="170"/>
       <c r="D26" s="93" t="s">
         <v>10</v>
       </c>
@@ -2881,10 +2879,10 @@
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="161" t="s">
+      <c r="B27" s="180" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="162"/>
+      <c r="C27" s="181"/>
       <c r="D27" s="78"/>
       <c r="E27" s="33">
         <v>5</v>
@@ -2897,10 +2895,10 @@
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="120" t="s">
+      <c r="B28" s="152" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="160"/>
+      <c r="C28" s="175"/>
       <c r="D28" s="70"/>
       <c r="E28" s="30">
         <f>SUM(E29:E30)</f>
@@ -2915,10 +2913,10 @@
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="130" t="s">
+      <c r="B29" s="136" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="159"/>
+      <c r="C29" s="167"/>
       <c r="D29" s="70"/>
       <c r="E29" s="30">
         <v>2</v>
@@ -2931,10 +2929,10 @@
       </c>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="130" t="s">
+      <c r="B30" s="136" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="159"/>
+      <c r="C30" s="167"/>
       <c r="D30" s="70"/>
       <c r="E30" s="30">
         <v>2</v>
@@ -2947,10 +2945,10 @@
       </c>
     </row>
     <row r="31" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B31" s="128" t="s">
+      <c r="B31" s="130" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="141"/>
+      <c r="C31" s="149"/>
       <c r="D31" s="71"/>
       <c r="E31" s="31">
         <v>3</v>
@@ -2963,10 +2961,10 @@
       </c>
     </row>
     <row r="32" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B32" s="137" t="s">
+      <c r="B32" s="126" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="163"/>
+      <c r="C32" s="170"/>
       <c r="D32" s="93" t="s">
         <v>14</v>
       </c>
@@ -2983,10 +2981,10 @@
       </c>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="116" t="s">
+      <c r="B33" s="128" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="165"/>
+      <c r="C33" s="169"/>
       <c r="D33" s="78"/>
       <c r="E33" s="33"/>
       <c r="F33" s="33"/>
@@ -2995,10 +2993,10 @@
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="122" t="s">
+      <c r="B34" s="139" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="134"/>
+      <c r="C34" s="140"/>
       <c r="D34" s="78"/>
       <c r="E34" s="33">
         <v>2</v>
@@ -3011,10 +3009,10 @@
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="149" t="s">
+      <c r="B35" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="169"/>
+      <c r="C35" s="171"/>
       <c r="D35" s="95"/>
       <c r="E35" s="108"/>
       <c r="F35" s="108"/>
@@ -3023,10 +3021,10 @@
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="118" t="s">
+      <c r="B36" s="132" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="144"/>
+      <c r="C36" s="138"/>
       <c r="D36" s="70"/>
       <c r="E36" s="30">
         <v>2</v>
@@ -3039,10 +3037,10 @@
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="118" t="s">
+      <c r="B37" s="132" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="144"/>
+      <c r="C37" s="138"/>
       <c r="D37" s="70"/>
       <c r="E37" s="30">
         <v>2</v>
@@ -3055,10 +3053,10 @@
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="118" t="s">
+      <c r="B38" s="132" t="s">
         <v>93</v>
       </c>
-      <c r="C38" s="144"/>
+      <c r="C38" s="138"/>
       <c r="D38" s="70"/>
       <c r="E38" s="30">
         <v>1</v>
@@ -3071,10 +3069,10 @@
       </c>
     </row>
     <row r="39" spans="2:7">
-      <c r="B39" s="149" t="s">
+      <c r="B39" s="143" t="s">
         <v>5</v>
       </c>
-      <c r="C39" s="169"/>
+      <c r="C39" s="171"/>
       <c r="D39" s="95"/>
       <c r="E39" s="108"/>
       <c r="F39" s="108"/>
@@ -3083,10 +3081,10 @@
       </c>
     </row>
     <row r="40" spans="2:7">
-      <c r="B40" s="170" t="s">
+      <c r="B40" s="172" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="171"/>
+      <c r="C40" s="173"/>
       <c r="D40" s="77"/>
       <c r="E40" s="30">
         <v>2</v>
@@ -3099,10 +3097,10 @@
       </c>
     </row>
     <row r="41" spans="2:7">
-      <c r="B41" s="120" t="s">
+      <c r="B41" s="152" t="s">
         <v>61</v>
       </c>
-      <c r="C41" s="166"/>
+      <c r="C41" s="165"/>
       <c r="D41" s="77"/>
       <c r="E41" s="30">
         <v>3</v>
@@ -3115,10 +3113,10 @@
       </c>
     </row>
     <row r="42" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B42" s="157" t="s">
+      <c r="B42" s="178" t="s">
         <v>93</v>
       </c>
-      <c r="C42" s="158"/>
+      <c r="C42" s="179"/>
       <c r="D42" s="69"/>
       <c r="E42" s="31">
         <v>1</v>
@@ -3131,10 +3129,10 @@
       </c>
     </row>
     <row r="43" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B43" s="147" t="s">
+      <c r="B43" s="141" t="s">
         <v>82</v>
       </c>
-      <c r="C43" s="197"/>
+      <c r="C43" s="164"/>
       <c r="D43" s="67"/>
       <c r="E43" s="34">
         <f>SUM(E3+E16+E26+F32)</f>
@@ -3150,6 +3148,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B14:C14"/>
@@ -3166,33 +3191,6 @@
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B38:C38"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3215,10 +3213,10 @@
   <sheetData>
     <row r="1" spans="2:13" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B2" s="151" t="s">
+      <c r="B2" s="124" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="152"/>
+      <c r="C2" s="125"/>
       <c r="D2" s="9" t="s">
         <v>9</v>
       </c>
@@ -3236,17 +3234,17 @@
       </c>
       <c r="J2" s="47">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="K2" s="35" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B3" s="137" t="s">
+      <c r="B3" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="138"/>
+      <c r="C3" s="127"/>
       <c r="D3" s="66" t="s">
         <v>12</v>
       </c>
@@ -3269,19 +3267,19 @@
       </c>
       <c r="K3" s="42" t="str">
         <f ca="1">SUM($J3-J2)&amp; "日"</f>
-        <v>-2日</v>
+        <v>-3日</v>
       </c>
     </row>
     <row r="4" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B4" s="116" t="s">
+      <c r="B4" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="117"/>
-      <c r="D4" s="189"/>
-      <c r="E4" s="190">
+      <c r="C4" s="129"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="114">
         <v>2</v>
       </c>
-      <c r="F4" s="190">
+      <c r="F4" s="114">
         <v>2</v>
       </c>
       <c r="G4" s="101" t="s">
@@ -3295,14 +3293,14 @@
       </c>
       <c r="K4" s="65" t="str">
         <f ca="1">SUM(J4-J2)&amp; "日"</f>
-        <v>7日</v>
+        <v>6日</v>
       </c>
     </row>
     <row r="5" spans="2:13">
-      <c r="B5" s="153" t="s">
+      <c r="B5" s="134" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="154"/>
+      <c r="C5" s="135"/>
       <c r="D5" s="5"/>
       <c r="E5" s="30">
         <v>2</v>
@@ -3318,16 +3316,16 @@
       <c r="K5" s="52"/>
     </row>
     <row r="6" spans="2:13">
-      <c r="B6" s="118" t="s">
+      <c r="B6" s="132" t="s">
         <v>117</v>
       </c>
-      <c r="C6" s="144"/>
-      <c r="D6" s="191"/>
-      <c r="E6" s="192">
+      <c r="C6" s="138"/>
+      <c r="D6" s="115"/>
+      <c r="E6" s="116">
         <f>SUM(E7)</f>
         <v>3</v>
       </c>
-      <c r="F6" s="192">
+      <c r="F6" s="116">
         <f>SUM(F7)</f>
         <v>3</v>
       </c>
@@ -3339,10 +3337,10 @@
       <c r="K6" s="52"/>
     </row>
     <row r="7" spans="2:13">
-      <c r="B7" s="187" t="s">
+      <c r="B7" s="139" t="s">
         <v>118</v>
       </c>
-      <c r="C7" s="188"/>
+      <c r="C7" s="140"/>
       <c r="D7" s="5"/>
       <c r="E7" s="30">
         <v>3</v>
@@ -3353,24 +3351,24 @@
       <c r="G7" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="I7" s="113" t="s">
+      <c r="I7" s="154" t="s">
         <v>88</v>
       </c>
-      <c r="J7" s="113"/>
-      <c r="K7" s="113"/>
-      <c r="L7" s="113"/>
-      <c r="M7" s="113"/>
+      <c r="J7" s="154"/>
+      <c r="K7" s="154"/>
+      <c r="L7" s="154"/>
+      <c r="M7" s="154"/>
     </row>
     <row r="8" spans="2:13">
-      <c r="B8" s="118" t="s">
+      <c r="B8" s="132" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="119"/>
-      <c r="D8" s="191"/>
-      <c r="E8" s="192">
+      <c r="C8" s="133"/>
+      <c r="D8" s="115"/>
+      <c r="E8" s="116">
         <v>2</v>
       </c>
-      <c r="F8" s="192">
+      <c r="F8" s="116">
         <v>5</v>
       </c>
       <c r="G8" s="101" t="s">
@@ -3381,16 +3379,16 @@
       <c r="K8" s="52"/>
     </row>
     <row r="9" spans="2:13">
-      <c r="B9" s="128" t="s">
+      <c r="B9" s="130" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="129"/>
-      <c r="D9" s="193"/>
-      <c r="E9" s="194">
+      <c r="C9" s="131"/>
+      <c r="D9" s="117"/>
+      <c r="E9" s="118">
         <f>SUM(E10+E11+E12+E13)</f>
         <v>2</v>
       </c>
-      <c r="F9" s="194">
+      <c r="F9" s="118">
         <f>SUM(F10:F13)</f>
         <v>4</v>
       </c>
@@ -3399,10 +3397,10 @@
       </c>
     </row>
     <row r="10" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B10" s="122" t="s">
+      <c r="B10" s="139" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="123"/>
+      <c r="C10" s="157"/>
       <c r="D10" s="5"/>
       <c r="E10" s="30">
         <v>0.5</v>
@@ -3418,10 +3416,10 @@
       </c>
     </row>
     <row r="11" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B11" s="122" t="s">
+      <c r="B11" s="139" t="s">
         <v>90</v>
       </c>
-      <c r="C11" s="123"/>
+      <c r="C11" s="157"/>
       <c r="D11" s="5"/>
       <c r="E11" s="30">
         <v>0.5</v>
@@ -3432,16 +3430,16 @@
       <c r="G11" s="81" t="s">
         <v>84</v>
       </c>
-      <c r="I11" s="126" t="s">
+      <c r="I11" s="160" t="s">
         <v>103</v>
       </c>
-      <c r="J11" s="127"/>
+      <c r="J11" s="161"/>
     </row>
     <row r="12" spans="2:13">
-      <c r="B12" s="122" t="s">
+      <c r="B12" s="139" t="s">
         <v>91</v>
       </c>
-      <c r="C12" s="123"/>
+      <c r="C12" s="157"/>
       <c r="D12" s="5"/>
       <c r="E12" s="30">
         <v>0.5</v>
@@ -3461,10 +3459,10 @@
       </c>
     </row>
     <row r="13" spans="2:13">
-      <c r="B13" s="124" t="s">
+      <c r="B13" s="158" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="125"/>
+      <c r="C13" s="159"/>
       <c r="D13" s="7"/>
       <c r="E13" s="31">
         <v>0.5</v>
@@ -3484,10 +3482,10 @@
       </c>
     </row>
     <row r="14" spans="2:13">
-      <c r="B14" s="122" t="s">
+      <c r="B14" s="139" t="s">
         <v>100</v>
       </c>
-      <c r="C14" s="134"/>
+      <c r="C14" s="140"/>
       <c r="D14" s="7"/>
       <c r="E14" s="31">
         <v>0.5</v>
@@ -3507,15 +3505,15 @@
       </c>
     </row>
     <row r="15" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B15" s="128" t="s">
+      <c r="B15" s="130" t="s">
         <v>104</v>
       </c>
-      <c r="C15" s="129"/>
-      <c r="D15" s="193"/>
-      <c r="E15" s="194">
+      <c r="C15" s="131"/>
+      <c r="D15" s="117"/>
+      <c r="E15" s="118">
         <v>4</v>
       </c>
-      <c r="F15" s="194">
+      <c r="F15" s="118">
         <f>SUM(F16:F18)</f>
         <v>6.5</v>
       </c>
@@ -3531,10 +3529,10 @@
       </c>
     </row>
     <row r="16" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B16" s="130" t="s">
+      <c r="B16" s="136" t="s">
         <v>107</v>
       </c>
-      <c r="C16" s="131"/>
+      <c r="C16" s="137"/>
       <c r="D16" s="5"/>
       <c r="E16" s="30">
         <v>1</v>
@@ -3545,7 +3543,7 @@
       <c r="G16" s="53" t="s">
         <v>84</v>
       </c>
-      <c r="I16" s="198" t="s">
+      <c r="I16" s="121" t="s">
         <v>101</v>
       </c>
       <c r="J16" s="79">
@@ -3554,10 +3552,10 @@
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="130" t="s">
+      <c r="B17" s="136" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="131"/>
+      <c r="C17" s="137"/>
       <c r="D17" s="5"/>
       <c r="E17" s="30">
         <v>5</v>
@@ -3570,10 +3568,10 @@
       </c>
     </row>
     <row r="18" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B18" s="132" t="s">
+      <c r="B18" s="162" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="133"/>
+      <c r="C18" s="163"/>
       <c r="D18" s="6"/>
       <c r="E18" s="32">
         <v>1</v>
@@ -3586,10 +3584,10 @@
       </c>
     </row>
     <row r="19" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B19" s="114" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="115"/>
+      <c r="B19" s="155" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="156"/>
       <c r="D19" s="110" t="s">
         <v>11</v>
       </c>
@@ -3606,15 +3604,15 @@
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="116" t="s">
+      <c r="B20" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="117"/>
-      <c r="D20" s="195"/>
-      <c r="E20" s="196">
+      <c r="C20" s="129"/>
+      <c r="D20" s="119"/>
+      <c r="E20" s="120">
         <v>2</v>
       </c>
-      <c r="F20" s="196">
+      <c r="F20" s="120">
         <v>1</v>
       </c>
       <c r="G20" s="101" t="s">
@@ -3622,29 +3620,29 @@
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="118" t="s">
+      <c r="B21" s="132" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="119"/>
-      <c r="D21" s="195"/>
-      <c r="E21" s="196">
+      <c r="C21" s="133"/>
+      <c r="D21" s="119"/>
+      <c r="E21" s="120">
         <v>4</v>
       </c>
-      <c r="F21" s="196"/>
+      <c r="F21" s="120"/>
       <c r="G21" s="101" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="118" t="s">
+      <c r="B22" s="132" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="119"/>
-      <c r="D22" s="191"/>
-      <c r="E22" s="192">
+      <c r="C22" s="133"/>
+      <c r="D22" s="115"/>
+      <c r="E22" s="116">
         <v>3</v>
       </c>
-      <c r="F22" s="192">
+      <c r="F22" s="116">
         <v>2</v>
       </c>
       <c r="G22" s="101" t="s">
@@ -3652,24 +3650,24 @@
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="120" t="s">
+      <c r="B23" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="C23" s="121"/>
-      <c r="D23" s="191"/>
-      <c r="E23" s="192">
+      <c r="C23" s="153"/>
+      <c r="D23" s="115"/>
+      <c r="E23" s="116">
         <v>2</v>
       </c>
-      <c r="F23" s="192"/>
+      <c r="F23" s="116"/>
       <c r="G23" s="99" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="130" t="s">
+      <c r="B24" s="136" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="131"/>
+      <c r="C24" s="137"/>
       <c r="D24" s="5"/>
       <c r="E24" s="30">
         <v>1</v>
@@ -3680,10 +3678,10 @@
       </c>
     </row>
     <row r="25" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B25" s="135" t="s">
+      <c r="B25" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="136"/>
+      <c r="C25" s="123"/>
       <c r="D25" s="7"/>
       <c r="E25" s="31">
         <v>1</v>
@@ -3694,10 +3692,10 @@
       </c>
     </row>
     <row r="26" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B26" s="137" t="s">
+      <c r="B26" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="138"/>
+      <c r="C26" s="127"/>
       <c r="D26" s="66" t="s">
         <v>10</v>
       </c>
@@ -3714,24 +3712,24 @@
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="120" t="s">
+      <c r="B27" s="152" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="121"/>
-      <c r="D27" s="191"/>
-      <c r="E27" s="192">
-        <v>1</v>
-      </c>
-      <c r="F27" s="192"/>
+      <c r="C27" s="153"/>
+      <c r="D27" s="115"/>
+      <c r="E27" s="116">
+        <v>1</v>
+      </c>
+      <c r="F27" s="116"/>
       <c r="G27" s="99" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="135" t="s">
+      <c r="B28" s="122" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="136"/>
+      <c r="C28" s="123"/>
       <c r="D28" s="7"/>
       <c r="E28" s="31">
         <v>2</v>
@@ -3742,15 +3740,15 @@
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="128" t="s">
+      <c r="B29" s="130" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="141"/>
-      <c r="D29" s="193"/>
-      <c r="E29" s="194">
+      <c r="C29" s="149"/>
+      <c r="D29" s="117"/>
+      <c r="E29" s="118">
         <v>5</v>
       </c>
-      <c r="F29" s="194">
+      <c r="F29" s="118">
         <v>5</v>
       </c>
       <c r="G29" s="100" t="s">
@@ -3758,10 +3756,10 @@
       </c>
     </row>
     <row r="30" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B30" s="142" t="s">
+      <c r="B30" s="150" t="s">
         <v>87</v>
       </c>
-      <c r="C30" s="143"/>
+      <c r="C30" s="151"/>
       <c r="D30" s="6"/>
       <c r="E30" s="32">
         <v>1</v>
@@ -3774,10 +3772,10 @@
       </c>
     </row>
     <row r="31" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B31" s="137" t="s">
+      <c r="B31" s="126" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="138"/>
+      <c r="C31" s="127"/>
       <c r="D31" s="66" t="s">
         <v>14</v>
       </c>
@@ -3794,24 +3792,24 @@
       </c>
     </row>
     <row r="32" spans="2:7">
-      <c r="B32" s="116" t="s">
+      <c r="B32" s="128" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="117"/>
-      <c r="D32" s="195"/>
-      <c r="E32" s="196">
+      <c r="C32" s="129"/>
+      <c r="D32" s="119"/>
+      <c r="E32" s="120">
         <v>5</v>
       </c>
-      <c r="F32" s="196"/>
+      <c r="F32" s="120"/>
       <c r="G32" s="99" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="149" t="s">
+      <c r="B33" s="143" t="s">
         <v>96</v>
       </c>
-      <c r="C33" s="150"/>
+      <c r="C33" s="144"/>
       <c r="D33" s="105" t="s">
         <v>97</v>
       </c>
@@ -3828,15 +3826,15 @@
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="118" t="s">
+      <c r="B34" s="132" t="s">
         <v>110</v>
       </c>
-      <c r="C34" s="144"/>
-      <c r="D34" s="191"/>
-      <c r="E34" s="196">
+      <c r="C34" s="138"/>
+      <c r="D34" s="115"/>
+      <c r="E34" s="120">
         <v>0.5</v>
       </c>
-      <c r="F34" s="196">
+      <c r="F34" s="120">
         <v>0.5</v>
       </c>
       <c r="G34" s="99" t="s">
@@ -3844,16 +3842,16 @@
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="118" t="s">
+      <c r="B35" s="132" t="s">
         <v>93</v>
       </c>
-      <c r="C35" s="144"/>
-      <c r="D35" s="191"/>
-      <c r="E35" s="196">
+      <c r="C35" s="138"/>
+      <c r="D35" s="115"/>
+      <c r="E35" s="120">
         <f>SUM(E36+E37+E38+E39)</f>
         <v>7</v>
       </c>
-      <c r="F35" s="196">
+      <c r="F35" s="120">
         <f>SUM(F36+F37+F38+F39)</f>
         <v>6</v>
       </c>
@@ -3911,10 +3909,10 @@
       </c>
     </row>
     <row r="39" spans="2:7">
-      <c r="B39" s="122" t="s">
+      <c r="B39" s="139" t="s">
         <v>114</v>
       </c>
-      <c r="C39" s="134"/>
+      <c r="C39" s="140"/>
       <c r="D39" s="5"/>
       <c r="E39" s="33">
         <v>1</v>
@@ -3927,10 +3925,10 @@
       </c>
     </row>
     <row r="40" spans="2:7">
-      <c r="B40" s="149" t="s">
+      <c r="B40" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="C40" s="150"/>
+      <c r="C40" s="144"/>
       <c r="D40" s="105" t="s">
         <v>97</v>
       </c>
@@ -3944,29 +3942,29 @@
       </c>
     </row>
     <row r="41" spans="2:7">
-      <c r="B41" s="118" t="s">
+      <c r="B41" s="132" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="119"/>
-      <c r="D41" s="191"/>
-      <c r="E41" s="192">
+      <c r="C41" s="133"/>
+      <c r="D41" s="115"/>
+      <c r="E41" s="116">
         <v>2</v>
       </c>
-      <c r="F41" s="192"/>
+      <c r="F41" s="116"/>
       <c r="G41" s="99" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="42" spans="2:7">
-      <c r="B42" s="118" t="s">
+      <c r="B42" s="132" t="s">
         <v>98</v>
       </c>
-      <c r="C42" s="119"/>
-      <c r="D42" s="191"/>
-      <c r="E42" s="192">
+      <c r="C42" s="133"/>
+      <c r="D42" s="115"/>
+      <c r="E42" s="116">
         <v>2</v>
       </c>
-      <c r="F42" s="192">
+      <c r="F42" s="116">
         <v>2</v>
       </c>
       <c r="G42" s="99" t="s">
@@ -3974,16 +3972,16 @@
       </c>
     </row>
     <row r="43" spans="2:7">
-      <c r="B43" s="118" t="s">
+      <c r="B43" s="132" t="s">
         <v>67</v>
       </c>
-      <c r="C43" s="144"/>
-      <c r="D43" s="191"/>
-      <c r="E43" s="192">
+      <c r="C43" s="138"/>
+      <c r="D43" s="115"/>
+      <c r="E43" s="116">
         <f>SUM(E44+E45)</f>
         <v>1</v>
       </c>
-      <c r="F43" s="192"/>
+      <c r="F43" s="116"/>
       <c r="G43" s="99" t="s">
         <v>84</v>
       </c>
@@ -4003,10 +4001,10 @@
       </c>
     </row>
     <row r="45" spans="2:7">
-      <c r="B45" s="122" t="s">
+      <c r="B45" s="139" t="s">
         <v>115</v>
       </c>
-      <c r="C45" s="134"/>
+      <c r="C45" s="140"/>
       <c r="D45" s="5"/>
       <c r="E45" s="30">
         <v>0.5</v>
@@ -4017,10 +4015,10 @@
       </c>
     </row>
     <row r="46" spans="2:7">
-      <c r="B46" s="149" t="s">
+      <c r="B46" s="143" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="150"/>
+      <c r="C46" s="144"/>
       <c r="D46" s="105"/>
       <c r="E46" s="108"/>
       <c r="F46" s="108"/>
@@ -4029,36 +4027,36 @@
       </c>
     </row>
     <row r="47" spans="2:7">
-      <c r="B47" s="139" t="s">
+      <c r="B47" s="147" t="s">
         <v>66</v>
       </c>
-      <c r="C47" s="140"/>
-      <c r="D47" s="193"/>
-      <c r="E47" s="194">
+      <c r="C47" s="148"/>
+      <c r="D47" s="117"/>
+      <c r="E47" s="118">
         <v>2</v>
       </c>
-      <c r="F47" s="194"/>
+      <c r="F47" s="118"/>
       <c r="G47" s="100" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="2:7">
-      <c r="B48" s="118" t="s">
+      <c r="B48" s="132" t="s">
         <v>98</v>
       </c>
-      <c r="C48" s="119"/>
-      <c r="D48" s="193"/>
-      <c r="E48" s="194"/>
-      <c r="F48" s="194"/>
+      <c r="C48" s="133"/>
+      <c r="D48" s="117"/>
+      <c r="E48" s="118"/>
+      <c r="F48" s="118"/>
       <c r="G48" s="100" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="49" spans="2:7">
-      <c r="B49" s="149" t="s">
+      <c r="B49" s="143" t="s">
         <v>100</v>
       </c>
-      <c r="C49" s="150"/>
+      <c r="C49" s="144"/>
       <c r="D49" s="105"/>
       <c r="E49" s="108"/>
       <c r="F49" s="108"/>
@@ -4067,38 +4065,38 @@
       </c>
     </row>
     <row r="50" spans="2:7">
-      <c r="B50" s="139" t="s">
+      <c r="B50" s="147" t="s">
         <v>66</v>
       </c>
-      <c r="C50" s="140"/>
-      <c r="D50" s="191"/>
-      <c r="E50" s="192">
+      <c r="C50" s="148"/>
+      <c r="D50" s="115"/>
+      <c r="E50" s="116">
         <v>2</v>
       </c>
-      <c r="F50" s="192"/>
+      <c r="F50" s="116"/>
       <c r="G50" s="100" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="51" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B51" s="128" t="s">
+      <c r="B51" s="130" t="s">
         <v>98</v>
       </c>
-      <c r="C51" s="129"/>
-      <c r="D51" s="193"/>
-      <c r="E51" s="194">
+      <c r="C51" s="131"/>
+      <c r="D51" s="117"/>
+      <c r="E51" s="118">
         <v>2</v>
       </c>
-      <c r="F51" s="194"/>
+      <c r="F51" s="118"/>
       <c r="G51" s="100" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="52" spans="2:7">
-      <c r="B52" s="147" t="s">
+      <c r="B52" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="C52" s="148"/>
+      <c r="C52" s="142"/>
       <c r="D52" s="9"/>
       <c r="E52" s="34">
         <f>SUM(E3+E19+E26+E31)</f>
@@ -4112,43 +4110,6 @@
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B39:C39"/>
     <mergeCell ref="I7:M7"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
@@ -4165,6 +4126,43 @@
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4188,10 +4186,10 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B2" s="172" t="s">
+      <c r="B2" s="192" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="173"/>
+      <c r="C2" s="193"/>
       <c r="D2" s="9" t="s">
         <v>9</v>
       </c>
@@ -4206,10 +4204,10 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B3" s="174" t="s">
+      <c r="B3" s="188" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="175"/>
+      <c r="C3" s="189"/>
       <c r="D3" s="9" t="s">
         <v>12</v>
       </c>
@@ -4229,17 +4227,17 @@
       </c>
       <c r="K3" s="47">
         <f ca="1">TODAY()</f>
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="L3" s="35" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="4" spans="2:12">
-      <c r="B4" s="176" t="s">
+      <c r="B4" s="194" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="177"/>
+      <c r="C4" s="195"/>
       <c r="D4" s="73"/>
       <c r="E4" s="74">
         <v>3</v>
@@ -4263,10 +4261,10 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B5" s="128" t="s">
+      <c r="B5" s="130" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="141"/>
+      <c r="C5" s="149"/>
       <c r="D5" s="7"/>
       <c r="E5" s="31">
         <v>3</v>
@@ -4285,10 +4283,10 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B6" s="174" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="175"/>
+      <c r="B6" s="188" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="189"/>
       <c r="D6" s="9" t="s">
         <v>11</v>
       </c>
@@ -4311,14 +4309,14 @@
       </c>
       <c r="L6" s="42" t="str">
         <f ca="1">SUM(K6-K3)&amp; "日"</f>
-        <v>7日</v>
+        <v>6日</v>
       </c>
     </row>
     <row r="7" spans="2:12">
-      <c r="B7" s="180" t="s">
+      <c r="B7" s="186" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="181"/>
+      <c r="C7" s="187"/>
       <c r="D7" s="57"/>
       <c r="E7" s="59">
         <v>3</v>
@@ -4332,10 +4330,10 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B8" s="128" t="s">
+      <c r="B8" s="130" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="141"/>
+      <c r="C8" s="149"/>
       <c r="D8" s="7"/>
       <c r="E8" s="31">
         <v>3</v>
@@ -4347,10 +4345,10 @@
       <c r="L8" s="52"/>
     </row>
     <row r="9" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B9" s="174" t="s">
+      <c r="B9" s="188" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="175"/>
+      <c r="C9" s="189"/>
       <c r="D9" s="9" t="s">
         <v>10</v>
       </c>
@@ -4367,10 +4365,10 @@
       </c>
     </row>
     <row r="10" spans="2:12">
-      <c r="B10" s="161" t="s">
+      <c r="B10" s="180" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="178"/>
+      <c r="C10" s="190"/>
       <c r="D10" s="8"/>
       <c r="E10" s="33">
         <v>3</v>
@@ -4381,10 +4379,10 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B11" s="157" t="s">
+      <c r="B11" s="178" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="179"/>
+      <c r="C11" s="191"/>
       <c r="D11" s="7"/>
       <c r="E11" s="31">
         <v>2</v>
@@ -4395,10 +4393,10 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B12" s="174" t="s">
+      <c r="B12" s="188" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="175"/>
+      <c r="C12" s="189"/>
       <c r="D12" s="9" t="s">
         <v>14</v>
       </c>
@@ -4415,10 +4413,10 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B13" s="180" t="s">
+      <c r="B13" s="186" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="181"/>
+      <c r="C13" s="187"/>
       <c r="D13" s="57"/>
       <c r="E13" s="59">
         <v>2</v>
@@ -4429,10 +4427,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B14" s="174" t="s">
+      <c r="B14" s="188" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="175"/>
+      <c r="C14" s="189"/>
       <c r="D14" s="9"/>
       <c r="E14" s="34">
         <f>SUM(E15:E16)</f>
@@ -4447,10 +4445,10 @@
       </c>
     </row>
     <row r="15" spans="2:12">
-      <c r="B15" s="161" t="s">
+      <c r="B15" s="180" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="178"/>
+      <c r="C15" s="190"/>
       <c r="D15" s="8"/>
       <c r="E15" s="33">
         <v>1</v>
@@ -4461,10 +4459,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B16" s="157" t="s">
+      <c r="B16" s="178" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="179"/>
+      <c r="C16" s="191"/>
       <c r="D16" s="7"/>
       <c r="E16" s="31">
         <v>1</v>
@@ -4475,10 +4473,10 @@
       </c>
     </row>
     <row r="17" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B17" s="174" t="s">
+      <c r="B17" s="188" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="175"/>
+      <c r="C17" s="189"/>
       <c r="D17" s="9"/>
       <c r="E17" s="34">
         <f>SUM(E18:E19)</f>
@@ -4493,10 +4491,10 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="161" t="s">
+      <c r="B18" s="180" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="178"/>
+      <c r="C18" s="190"/>
       <c r="D18" s="8"/>
       <c r="E18" s="33">
         <v>1</v>
@@ -4541,6 +4539,18 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B13:C13"/>
@@ -4548,18 +4558,6 @@
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B8:C8"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4572,13 +4570,13 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <sheetData>
     <row r="1" spans="2:11" ht="36" thickBot="1">
-      <c r="C1" s="186" t="s">
+      <c r="C1" s="196" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="186"/>
-      <c r="E1" s="186"/>
-      <c r="F1" s="186"/>
-      <c r="G1" s="186"/>
+      <c r="D1" s="196"/>
+      <c r="E1" s="196"/>
+      <c r="F1" s="196"/>
+      <c r="G1" s="196"/>
     </row>
     <row r="2" spans="2:11" ht="19.5" thickBot="1">
       <c r="B2" s="24" t="s">

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FunasakoYuga\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D36E81-1609-46F9-B9A5-4C0D2D062A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA794882-ECE0-4537-99B0-9EFC32EF44BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4023,7 +4023,7 @@
       <c r="E46" s="108"/>
       <c r="F46" s="108"/>
       <c r="G46" s="96" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="2:7">
@@ -4049,7 +4049,7 @@
       <c r="E48" s="118"/>
       <c r="F48" s="118"/>
       <c r="G48" s="100" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49" spans="2:7">

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FunasakoYuga\Documents\GitHub\GlassesGame\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ayato Terao\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA794882-ECE0-4537-99B0-9EFC32EF44BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C7CA7C-DB4F-4012-B782-699188101ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>
@@ -1856,73 +1856,100 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1931,91 +1958,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="51" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2030,12 +1994,78 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2046,36 +2076,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="41" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2387,10 +2387,10 @@
   <sheetData>
     <row r="1" spans="2:19" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B2" s="124" t="s">
+      <c r="B2" s="160" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="174"/>
+      <c r="C2" s="173"/>
       <c r="D2" s="68" t="s">
         <v>9</v>
       </c>
@@ -2405,10 +2405,10 @@
       </c>
     </row>
     <row r="3" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B3" s="126" t="s">
+      <c r="B3" s="146" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="170"/>
+      <c r="C3" s="172"/>
       <c r="D3" s="97" t="s">
         <v>12</v>
       </c>
@@ -2435,10 +2435,10 @@
       </c>
     </row>
     <row r="4" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B4" s="128" t="s">
+      <c r="B4" s="125" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="169"/>
+      <c r="C4" s="174"/>
       <c r="D4" s="78"/>
       <c r="E4" s="33">
         <f>SUM(E5:E7)</f>
@@ -2463,10 +2463,10 @@
       </c>
     </row>
     <row r="5" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B5" s="139" t="s">
+      <c r="B5" s="131" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="140"/>
+      <c r="C5" s="143"/>
       <c r="D5" s="70"/>
       <c r="E5" s="30">
         <v>2</v>
@@ -2491,10 +2491,10 @@
       <c r="S5" s="52"/>
     </row>
     <row r="6" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B6" s="139" t="s">
+      <c r="B6" s="131" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="140"/>
+      <c r="C6" s="143"/>
       <c r="D6" s="70"/>
       <c r="E6" s="30">
         <v>1</v>
@@ -2509,10 +2509,10 @@
       <c r="S6" s="52"/>
     </row>
     <row r="7" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B7" s="139" t="s">
+      <c r="B7" s="131" t="s">
         <v>86</v>
       </c>
-      <c r="C7" s="140"/>
+      <c r="C7" s="143"/>
       <c r="D7" s="70"/>
       <c r="E7" s="30">
         <v>1</v>
@@ -2523,18 +2523,18 @@
       <c r="G7" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="I7" s="176" t="s">
+      <c r="I7" s="164" t="s">
         <v>102</v>
       </c>
-      <c r="J7" s="177"/>
+      <c r="J7" s="165"/>
       <c r="R7" s="51"/>
       <c r="S7" s="52"/>
     </row>
     <row r="8" spans="2:19">
-      <c r="B8" s="132" t="s">
+      <c r="B8" s="127" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="138"/>
+      <c r="C8" s="153"/>
       <c r="D8" s="70"/>
       <c r="E8" s="30">
         <v>2</v>
@@ -2554,10 +2554,10 @@
       </c>
     </row>
     <row r="9" spans="2:19">
-      <c r="B9" s="132" t="s">
+      <c r="B9" s="127" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="138"/>
+      <c r="C9" s="153"/>
       <c r="D9" s="71"/>
       <c r="E9" s="31">
         <v>2</v>
@@ -2577,10 +2577,10 @@
       </c>
     </row>
     <row r="10" spans="2:19">
-      <c r="B10" s="132" t="s">
+      <c r="B10" s="127" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="138"/>
+      <c r="C10" s="153"/>
       <c r="D10" s="71"/>
       <c r="E10" s="31">
         <v>2</v>
@@ -2600,10 +2600,10 @@
       </c>
     </row>
     <row r="11" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B11" s="152" t="s">
+      <c r="B11" s="129" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="175"/>
+      <c r="C11" s="169"/>
       <c r="D11" s="70"/>
       <c r="E11" s="30">
         <v>1</v>
@@ -2623,10 +2623,10 @@
       </c>
     </row>
     <row r="12" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B12" s="132" t="s">
+      <c r="B12" s="127" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="138"/>
+      <c r="C12" s="153"/>
       <c r="D12" s="70"/>
       <c r="E12" s="30">
         <f>SUM(E13:E15)</f>
@@ -2648,10 +2648,10 @@
       </c>
     </row>
     <row r="13" spans="2:19">
-      <c r="B13" s="136" t="s">
+      <c r="B13" s="139" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="167"/>
+      <c r="C13" s="168"/>
       <c r="D13" s="70"/>
       <c r="E13" s="30">
         <v>1</v>
@@ -2664,10 +2664,10 @@
       </c>
     </row>
     <row r="14" spans="2:19">
-      <c r="B14" s="139" t="s">
+      <c r="B14" s="131" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="140"/>
+      <c r="C14" s="143"/>
       <c r="D14" s="70"/>
       <c r="E14" s="30">
         <v>1</v>
@@ -2682,10 +2682,10 @@
       <c r="S14" s="52"/>
     </row>
     <row r="15" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B15" s="158" t="s">
+      <c r="B15" s="133" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="166"/>
+      <c r="C15" s="177"/>
       <c r="D15" s="71"/>
       <c r="E15" s="31">
         <v>1</v>
@@ -2698,10 +2698,10 @@
       </c>
     </row>
     <row r="16" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B16" s="126" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="170"/>
+      <c r="B16" s="146" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="172"/>
       <c r="D16" s="93" t="s">
         <v>11</v>
       </c>
@@ -2717,10 +2717,10 @@
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="128" t="s">
+      <c r="B17" s="125" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="169"/>
+      <c r="C17" s="174"/>
       <c r="D17" s="78"/>
       <c r="E17" s="33">
         <v>3</v>
@@ -2733,10 +2733,10 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="132" t="s">
+      <c r="B18" s="127" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="138"/>
+      <c r="C18" s="153"/>
       <c r="D18" s="70"/>
       <c r="E18" s="30">
         <v>3</v>
@@ -2749,10 +2749,10 @@
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="132" t="s">
+      <c r="B19" s="127" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="138"/>
+      <c r="C19" s="153"/>
       <c r="D19" s="70"/>
       <c r="E19" s="30">
         <v>3</v>
@@ -2765,10 +2765,10 @@
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="132" t="s">
+      <c r="B20" s="127" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="138"/>
+      <c r="C20" s="153"/>
       <c r="D20" s="71"/>
       <c r="E20" s="30">
         <v>3</v>
@@ -2781,10 +2781,10 @@
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="132" t="s">
+      <c r="B21" s="127" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="138"/>
+      <c r="C21" s="153"/>
       <c r="D21" s="70"/>
       <c r="E21" s="59">
         <v>1</v>
@@ -2797,10 +2797,10 @@
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="152" t="s">
+      <c r="B22" s="129" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="175"/>
+      <c r="C22" s="169"/>
       <c r="D22" s="70"/>
       <c r="E22" s="30"/>
       <c r="F22" s="30">
@@ -2811,10 +2811,10 @@
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="136" t="s">
+      <c r="B23" s="139" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="167"/>
+      <c r="C23" s="168"/>
       <c r="D23" s="70"/>
       <c r="E23" s="30">
         <v>1</v>
@@ -2827,10 +2827,10 @@
       </c>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="136" t="s">
+      <c r="B24" s="139" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="167"/>
+      <c r="C24" s="168"/>
       <c r="D24" s="70"/>
       <c r="E24" s="30">
         <v>1</v>
@@ -2843,10 +2843,10 @@
       </c>
     </row>
     <row r="25" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B25" s="162" t="s">
+      <c r="B25" s="141" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="168"/>
+      <c r="C25" s="178"/>
       <c r="D25" s="80"/>
       <c r="E25" s="32">
         <v>1</v>
@@ -2859,10 +2859,10 @@
       </c>
     </row>
     <row r="26" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B26" s="126" t="s">
+      <c r="B26" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="170"/>
+      <c r="C26" s="172"/>
       <c r="D26" s="93" t="s">
         <v>10</v>
       </c>
@@ -2879,10 +2879,10 @@
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="180" t="s">
+      <c r="B27" s="170" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="181"/>
+      <c r="C27" s="171"/>
       <c r="D27" s="78"/>
       <c r="E27" s="33">
         <v>5</v>
@@ -2895,10 +2895,10 @@
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="152" t="s">
+      <c r="B28" s="129" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="175"/>
+      <c r="C28" s="169"/>
       <c r="D28" s="70"/>
       <c r="E28" s="30">
         <f>SUM(E29:E30)</f>
@@ -2913,10 +2913,10 @@
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="136" t="s">
+      <c r="B29" s="139" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="167"/>
+      <c r="C29" s="168"/>
       <c r="D29" s="70"/>
       <c r="E29" s="30">
         <v>2</v>
@@ -2929,10 +2929,10 @@
       </c>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="136" t="s">
+      <c r="B30" s="139" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="167"/>
+      <c r="C30" s="168"/>
       <c r="D30" s="70"/>
       <c r="E30" s="30">
         <v>2</v>
@@ -2945,10 +2945,10 @@
       </c>
     </row>
     <row r="31" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B31" s="130" t="s">
+      <c r="B31" s="137" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="149"/>
+      <c r="C31" s="150"/>
       <c r="D31" s="71"/>
       <c r="E31" s="31">
         <v>3</v>
@@ -2961,10 +2961,10 @@
       </c>
     </row>
     <row r="32" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B32" s="126" t="s">
+      <c r="B32" s="146" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="170"/>
+      <c r="C32" s="172"/>
       <c r="D32" s="93" t="s">
         <v>14</v>
       </c>
@@ -2981,10 +2981,10 @@
       </c>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="128" t="s">
+      <c r="B33" s="125" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="169"/>
+      <c r="C33" s="174"/>
       <c r="D33" s="78"/>
       <c r="E33" s="33"/>
       <c r="F33" s="33"/>
@@ -2993,10 +2993,10 @@
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="139" t="s">
+      <c r="B34" s="131" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="140"/>
+      <c r="C34" s="143"/>
       <c r="D34" s="78"/>
       <c r="E34" s="33">
         <v>2</v>
@@ -3009,10 +3009,10 @@
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="143" t="s">
+      <c r="B35" s="158" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="171"/>
+      <c r="C35" s="179"/>
       <c r="D35" s="95"/>
       <c r="E35" s="108"/>
       <c r="F35" s="108"/>
@@ -3021,10 +3021,10 @@
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="132" t="s">
+      <c r="B36" s="127" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="138"/>
+      <c r="C36" s="153"/>
       <c r="D36" s="70"/>
       <c r="E36" s="30">
         <v>2</v>
@@ -3037,10 +3037,10 @@
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="132" t="s">
+      <c r="B37" s="127" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="138"/>
+      <c r="C37" s="153"/>
       <c r="D37" s="70"/>
       <c r="E37" s="30">
         <v>2</v>
@@ -3053,10 +3053,10 @@
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="132" t="s">
+      <c r="B38" s="127" t="s">
         <v>93</v>
       </c>
-      <c r="C38" s="138"/>
+      <c r="C38" s="153"/>
       <c r="D38" s="70"/>
       <c r="E38" s="30">
         <v>1</v>
@@ -3069,10 +3069,10 @@
       </c>
     </row>
     <row r="39" spans="2:7">
-      <c r="B39" s="143" t="s">
+      <c r="B39" s="158" t="s">
         <v>5</v>
       </c>
-      <c r="C39" s="171"/>
+      <c r="C39" s="179"/>
       <c r="D39" s="95"/>
       <c r="E39" s="108"/>
       <c r="F39" s="108"/>
@@ -3081,10 +3081,10 @@
       </c>
     </row>
     <row r="40" spans="2:7">
-      <c r="B40" s="172" t="s">
+      <c r="B40" s="180" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="173"/>
+      <c r="C40" s="181"/>
       <c r="D40" s="77"/>
       <c r="E40" s="30">
         <v>2</v>
@@ -3097,10 +3097,10 @@
       </c>
     </row>
     <row r="41" spans="2:7">
-      <c r="B41" s="152" t="s">
+      <c r="B41" s="129" t="s">
         <v>61</v>
       </c>
-      <c r="C41" s="165"/>
+      <c r="C41" s="176"/>
       <c r="D41" s="77"/>
       <c r="E41" s="30">
         <v>3</v>
@@ -3113,10 +3113,10 @@
       </c>
     </row>
     <row r="42" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B42" s="178" t="s">
+      <c r="B42" s="166" t="s">
         <v>93</v>
       </c>
-      <c r="C42" s="179"/>
+      <c r="C42" s="167"/>
       <c r="D42" s="69"/>
       <c r="E42" s="31">
         <v>1</v>
@@ -3129,10 +3129,10 @@
       </c>
     </row>
     <row r="43" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B43" s="141" t="s">
+      <c r="B43" s="156" t="s">
         <v>82</v>
       </c>
-      <c r="C43" s="164"/>
+      <c r="C43" s="175"/>
       <c r="D43" s="67"/>
       <c r="E43" s="34">
         <f>SUM(E3+E16+E26+F32)</f>
@@ -3148,33 +3148,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B12:C12"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B14:C14"/>
@@ -3191,6 +3164,33 @@
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B38:C38"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3213,10 +3213,10 @@
   <sheetData>
     <row r="1" spans="2:13" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B2" s="124" t="s">
+      <c r="B2" s="160" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="125"/>
+      <c r="C2" s="161"/>
       <c r="D2" s="9" t="s">
         <v>9</v>
       </c>
@@ -3241,10 +3241,10 @@
       </c>
     </row>
     <row r="3" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B3" s="126" t="s">
+      <c r="B3" s="146" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="127"/>
+      <c r="C3" s="147"/>
       <c r="D3" s="66" t="s">
         <v>12</v>
       </c>
@@ -3257,7 +3257,7 @@
         <v>20.5</v>
       </c>
       <c r="G3" s="94" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="I3" s="58" t="s">
         <v>76</v>
@@ -3271,10 +3271,10 @@
       </c>
     </row>
     <row r="4" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B4" s="128" t="s">
+      <c r="B4" s="125" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="129"/>
+      <c r="C4" s="126"/>
       <c r="D4" s="113"/>
       <c r="E4" s="114">
         <v>2</v>
@@ -3297,10 +3297,10 @@
       </c>
     </row>
     <row r="5" spans="2:13">
-      <c r="B5" s="134" t="s">
+      <c r="B5" s="162" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="135"/>
+      <c r="C5" s="163"/>
       <c r="D5" s="5"/>
       <c r="E5" s="30">
         <v>2</v>
@@ -3316,10 +3316,10 @@
       <c r="K5" s="52"/>
     </row>
     <row r="6" spans="2:13">
-      <c r="B6" s="132" t="s">
+      <c r="B6" s="127" t="s">
         <v>117</v>
       </c>
-      <c r="C6" s="138"/>
+      <c r="C6" s="153"/>
       <c r="D6" s="115"/>
       <c r="E6" s="116">
         <f>SUM(E7)</f>
@@ -3337,10 +3337,10 @@
       <c r="K6" s="52"/>
     </row>
     <row r="7" spans="2:13">
-      <c r="B7" s="139" t="s">
+      <c r="B7" s="131" t="s">
         <v>118</v>
       </c>
-      <c r="C7" s="140"/>
+      <c r="C7" s="143"/>
       <c r="D7" s="5"/>
       <c r="E7" s="30">
         <v>3</v>
@@ -3351,19 +3351,19 @@
       <c r="G7" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="I7" s="154" t="s">
+      <c r="I7" s="122" t="s">
         <v>88</v>
       </c>
-      <c r="J7" s="154"/>
-      <c r="K7" s="154"/>
-      <c r="L7" s="154"/>
-      <c r="M7" s="154"/>
+      <c r="J7" s="122"/>
+      <c r="K7" s="122"/>
+      <c r="L7" s="122"/>
+      <c r="M7" s="122"/>
     </row>
     <row r="8" spans="2:13">
-      <c r="B8" s="132" t="s">
+      <c r="B8" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="133"/>
+      <c r="C8" s="128"/>
       <c r="D8" s="115"/>
       <c r="E8" s="116">
         <v>2</v>
@@ -3379,10 +3379,10 @@
       <c r="K8" s="52"/>
     </row>
     <row r="9" spans="2:13">
-      <c r="B9" s="130" t="s">
+      <c r="B9" s="137" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="131"/>
+      <c r="C9" s="138"/>
       <c r="D9" s="117"/>
       <c r="E9" s="118">
         <f>SUM(E10+E11+E12+E13)</f>
@@ -3397,10 +3397,10 @@
       </c>
     </row>
     <row r="10" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B10" s="139" t="s">
+      <c r="B10" s="131" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="157"/>
+      <c r="C10" s="132"/>
       <c r="D10" s="5"/>
       <c r="E10" s="30">
         <v>0.5</v>
@@ -3416,10 +3416,10 @@
       </c>
     </row>
     <row r="11" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B11" s="139" t="s">
+      <c r="B11" s="131" t="s">
         <v>90</v>
       </c>
-      <c r="C11" s="157"/>
+      <c r="C11" s="132"/>
       <c r="D11" s="5"/>
       <c r="E11" s="30">
         <v>0.5</v>
@@ -3430,16 +3430,16 @@
       <c r="G11" s="81" t="s">
         <v>84</v>
       </c>
-      <c r="I11" s="160" t="s">
+      <c r="I11" s="135" t="s">
         <v>103</v>
       </c>
-      <c r="J11" s="161"/>
+      <c r="J11" s="136"/>
     </row>
     <row r="12" spans="2:13">
-      <c r="B12" s="139" t="s">
+      <c r="B12" s="131" t="s">
         <v>91</v>
       </c>
-      <c r="C12" s="157"/>
+      <c r="C12" s="132"/>
       <c r="D12" s="5"/>
       <c r="E12" s="30">
         <v>0.5</v>
@@ -3459,10 +3459,10 @@
       </c>
     </row>
     <row r="13" spans="2:13">
-      <c r="B13" s="158" t="s">
+      <c r="B13" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="159"/>
+      <c r="C13" s="134"/>
       <c r="D13" s="7"/>
       <c r="E13" s="31">
         <v>0.5</v>
@@ -3482,10 +3482,10 @@
       </c>
     </row>
     <row r="14" spans="2:13">
-      <c r="B14" s="139" t="s">
+      <c r="B14" s="131" t="s">
         <v>100</v>
       </c>
-      <c r="C14" s="140"/>
+      <c r="C14" s="143"/>
       <c r="D14" s="7"/>
       <c r="E14" s="31">
         <v>0.5</v>
@@ -3505,10 +3505,10 @@
       </c>
     </row>
     <row r="15" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B15" s="130" t="s">
+      <c r="B15" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="C15" s="131"/>
+      <c r="C15" s="138"/>
       <c r="D15" s="117"/>
       <c r="E15" s="118">
         <v>4</v>
@@ -3529,10 +3529,10 @@
       </c>
     </row>
     <row r="16" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B16" s="136" t="s">
+      <c r="B16" s="139" t="s">
         <v>107</v>
       </c>
-      <c r="C16" s="137"/>
+      <c r="C16" s="140"/>
       <c r="D16" s="5"/>
       <c r="E16" s="30">
         <v>1</v>
@@ -3552,10 +3552,10 @@
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="136" t="s">
+      <c r="B17" s="139" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="137"/>
+      <c r="C17" s="140"/>
       <c r="D17" s="5"/>
       <c r="E17" s="30">
         <v>5</v>
@@ -3568,10 +3568,10 @@
       </c>
     </row>
     <row r="18" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B18" s="162" t="s">
+      <c r="B18" s="141" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="163"/>
+      <c r="C18" s="142"/>
       <c r="D18" s="6"/>
       <c r="E18" s="32">
         <v>1</v>
@@ -3584,10 +3584,10 @@
       </c>
     </row>
     <row r="19" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B19" s="155" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="156"/>
+      <c r="B19" s="123" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="124"/>
       <c r="D19" s="110" t="s">
         <v>11</v>
       </c>
@@ -3604,10 +3604,10 @@
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="128" t="s">
+      <c r="B20" s="125" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="129"/>
+      <c r="C20" s="126"/>
       <c r="D20" s="119"/>
       <c r="E20" s="120">
         <v>2</v>
@@ -3620,10 +3620,10 @@
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="132" t="s">
+      <c r="B21" s="127" t="s">
         <v>94</v>
       </c>
-      <c r="C21" s="133"/>
+      <c r="C21" s="128"/>
       <c r="D21" s="119"/>
       <c r="E21" s="120">
         <v>4</v>
@@ -3634,10 +3634,10 @@
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="132" t="s">
+      <c r="B22" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="133"/>
+      <c r="C22" s="128"/>
       <c r="D22" s="115"/>
       <c r="E22" s="116">
         <v>3</v>
@@ -3650,10 +3650,10 @@
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="152" t="s">
+      <c r="B23" s="129" t="s">
         <v>69</v>
       </c>
-      <c r="C23" s="153"/>
+      <c r="C23" s="130"/>
       <c r="D23" s="115"/>
       <c r="E23" s="116">
         <v>2</v>
@@ -3664,10 +3664,10 @@
       </c>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="136" t="s">
+      <c r="B24" s="139" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="137"/>
+      <c r="C24" s="140"/>
       <c r="D24" s="5"/>
       <c r="E24" s="30">
         <v>1</v>
@@ -3678,10 +3678,10 @@
       </c>
     </row>
     <row r="25" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B25" s="122" t="s">
+      <c r="B25" s="144" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="123"/>
+      <c r="C25" s="145"/>
       <c r="D25" s="7"/>
       <c r="E25" s="31">
         <v>1</v>
@@ -3692,10 +3692,10 @@
       </c>
     </row>
     <row r="26" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B26" s="126" t="s">
+      <c r="B26" s="146" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="127"/>
+      <c r="C26" s="147"/>
       <c r="D26" s="66" t="s">
         <v>10</v>
       </c>
@@ -3712,10 +3712,10 @@
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="152" t="s">
+      <c r="B27" s="129" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="153"/>
+      <c r="C27" s="130"/>
       <c r="D27" s="115"/>
       <c r="E27" s="116">
         <v>1</v>
@@ -3726,10 +3726,10 @@
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="122" t="s">
+      <c r="B28" s="144" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="123"/>
+      <c r="C28" s="145"/>
       <c r="D28" s="7"/>
       <c r="E28" s="31">
         <v>2</v>
@@ -3740,10 +3740,10 @@
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="130" t="s">
+      <c r="B29" s="137" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="149"/>
+      <c r="C29" s="150"/>
       <c r="D29" s="117"/>
       <c r="E29" s="118">
         <v>5</v>
@@ -3756,10 +3756,10 @@
       </c>
     </row>
     <row r="30" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B30" s="150" t="s">
+      <c r="B30" s="151" t="s">
         <v>87</v>
       </c>
-      <c r="C30" s="151"/>
+      <c r="C30" s="152"/>
       <c r="D30" s="6"/>
       <c r="E30" s="32">
         <v>1</v>
@@ -3772,10 +3772,10 @@
       </c>
     </row>
     <row r="31" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B31" s="126" t="s">
+      <c r="B31" s="146" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="127"/>
+      <c r="C31" s="147"/>
       <c r="D31" s="66" t="s">
         <v>14</v>
       </c>
@@ -3792,10 +3792,10 @@
       </c>
     </row>
     <row r="32" spans="2:7">
-      <c r="B32" s="128" t="s">
+      <c r="B32" s="125" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="129"/>
+      <c r="C32" s="126"/>
       <c r="D32" s="119"/>
       <c r="E32" s="120">
         <v>5</v>
@@ -3806,10 +3806,10 @@
       </c>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="143" t="s">
+      <c r="B33" s="158" t="s">
         <v>96</v>
       </c>
-      <c r="C33" s="144"/>
+      <c r="C33" s="159"/>
       <c r="D33" s="105" t="s">
         <v>97</v>
       </c>
@@ -3826,10 +3826,10 @@
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="132" t="s">
+      <c r="B34" s="127" t="s">
         <v>110</v>
       </c>
-      <c r="C34" s="138"/>
+      <c r="C34" s="153"/>
       <c r="D34" s="115"/>
       <c r="E34" s="120">
         <v>0.5</v>
@@ -3842,10 +3842,10 @@
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="132" t="s">
+      <c r="B35" s="127" t="s">
         <v>93</v>
       </c>
-      <c r="C35" s="138"/>
+      <c r="C35" s="153"/>
       <c r="D35" s="115"/>
       <c r="E35" s="120">
         <f>SUM(E36+E37+E38+E39)</f>
@@ -3860,10 +3860,10 @@
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="145" t="s">
+      <c r="B36" s="154" t="s">
         <v>111</v>
       </c>
-      <c r="C36" s="146"/>
+      <c r="C36" s="155"/>
       <c r="D36" s="5"/>
       <c r="E36" s="33">
         <f>2</f>
@@ -3877,10 +3877,10 @@
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="145" t="s">
+      <c r="B37" s="154" t="s">
         <v>112</v>
       </c>
-      <c r="C37" s="146"/>
+      <c r="C37" s="155"/>
       <c r="D37" s="5"/>
       <c r="E37" s="33">
         <v>2</v>
@@ -3893,10 +3893,10 @@
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="145" t="s">
+      <c r="B38" s="154" t="s">
         <v>113</v>
       </c>
-      <c r="C38" s="146"/>
+      <c r="C38" s="155"/>
       <c r="D38" s="5"/>
       <c r="E38" s="33">
         <v>2</v>
@@ -3909,10 +3909,10 @@
       </c>
     </row>
     <row r="39" spans="2:7">
-      <c r="B39" s="139" t="s">
+      <c r="B39" s="131" t="s">
         <v>114</v>
       </c>
-      <c r="C39" s="140"/>
+      <c r="C39" s="143"/>
       <c r="D39" s="5"/>
       <c r="E39" s="33">
         <v>1</v>
@@ -3925,10 +3925,10 @@
       </c>
     </row>
     <row r="40" spans="2:7">
-      <c r="B40" s="143" t="s">
+      <c r="B40" s="158" t="s">
         <v>4</v>
       </c>
-      <c r="C40" s="144"/>
+      <c r="C40" s="159"/>
       <c r="D40" s="105" t="s">
         <v>97</v>
       </c>
@@ -3942,10 +3942,10 @@
       </c>
     </row>
     <row r="41" spans="2:7">
-      <c r="B41" s="132" t="s">
+      <c r="B41" s="127" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="133"/>
+      <c r="C41" s="128"/>
       <c r="D41" s="115"/>
       <c r="E41" s="116">
         <v>2</v>
@@ -3956,10 +3956,10 @@
       </c>
     </row>
     <row r="42" spans="2:7">
-      <c r="B42" s="132" t="s">
+      <c r="B42" s="127" t="s">
         <v>98</v>
       </c>
-      <c r="C42" s="133"/>
+      <c r="C42" s="128"/>
       <c r="D42" s="115"/>
       <c r="E42" s="116">
         <v>2</v>
@@ -3972,10 +3972,10 @@
       </c>
     </row>
     <row r="43" spans="2:7">
-      <c r="B43" s="132" t="s">
+      <c r="B43" s="127" t="s">
         <v>67</v>
       </c>
-      <c r="C43" s="138"/>
+      <c r="C43" s="153"/>
       <c r="D43" s="115"/>
       <c r="E43" s="116">
         <f>SUM(E44+E45)</f>
@@ -3987,10 +3987,10 @@
       </c>
     </row>
     <row r="44" spans="2:7">
-      <c r="B44" s="145" t="s">
+      <c r="B44" s="154" t="s">
         <v>116</v>
       </c>
-      <c r="C44" s="146"/>
+      <c r="C44" s="155"/>
       <c r="D44" s="5"/>
       <c r="E44" s="30">
         <v>0.5</v>
@@ -4001,10 +4001,10 @@
       </c>
     </row>
     <row r="45" spans="2:7">
-      <c r="B45" s="139" t="s">
+      <c r="B45" s="131" t="s">
         <v>115</v>
       </c>
-      <c r="C45" s="140"/>
+      <c r="C45" s="143"/>
       <c r="D45" s="5"/>
       <c r="E45" s="30">
         <v>0.5</v>
@@ -4015,10 +4015,10 @@
       </c>
     </row>
     <row r="46" spans="2:7">
-      <c r="B46" s="143" t="s">
+      <c r="B46" s="158" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="144"/>
+      <c r="C46" s="159"/>
       <c r="D46" s="105"/>
       <c r="E46" s="108"/>
       <c r="F46" s="108"/>
@@ -4027,10 +4027,10 @@
       </c>
     </row>
     <row r="47" spans="2:7">
-      <c r="B47" s="147" t="s">
+      <c r="B47" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C47" s="148"/>
+      <c r="C47" s="149"/>
       <c r="D47" s="117"/>
       <c r="E47" s="118">
         <v>2</v>
@@ -4041,10 +4041,10 @@
       </c>
     </row>
     <row r="48" spans="2:7">
-      <c r="B48" s="132" t="s">
+      <c r="B48" s="127" t="s">
         <v>98</v>
       </c>
-      <c r="C48" s="133"/>
+      <c r="C48" s="128"/>
       <c r="D48" s="117"/>
       <c r="E48" s="118"/>
       <c r="F48" s="118"/>
@@ -4053,10 +4053,10 @@
       </c>
     </row>
     <row r="49" spans="2:7">
-      <c r="B49" s="143" t="s">
+      <c r="B49" s="158" t="s">
         <v>100</v>
       </c>
-      <c r="C49" s="144"/>
+      <c r="C49" s="159"/>
       <c r="D49" s="105"/>
       <c r="E49" s="108"/>
       <c r="F49" s="108"/>
@@ -4065,10 +4065,10 @@
       </c>
     </row>
     <row r="50" spans="2:7">
-      <c r="B50" s="147" t="s">
+      <c r="B50" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="C50" s="148"/>
+      <c r="C50" s="149"/>
       <c r="D50" s="115"/>
       <c r="E50" s="116">
         <v>2</v>
@@ -4079,10 +4079,10 @@
       </c>
     </row>
     <row r="51" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B51" s="130" t="s">
+      <c r="B51" s="137" t="s">
         <v>98</v>
       </c>
-      <c r="C51" s="131"/>
+      <c r="C51" s="138"/>
       <c r="D51" s="117"/>
       <c r="E51" s="118">
         <v>2</v>
@@ -4093,10 +4093,10 @@
       </c>
     </row>
     <row r="52" spans="2:7">
-      <c r="B52" s="141" t="s">
+      <c r="B52" s="156" t="s">
         <v>34</v>
       </c>
-      <c r="C52" s="142"/>
+      <c r="C52" s="157"/>
       <c r="D52" s="9"/>
       <c r="E52" s="34">
         <f>SUM(E3+E19+E26+E31)</f>
@@ -4110,6 +4110,43 @@
     </row>
   </sheetData>
   <mergeCells count="53">
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B39:C39"/>
     <mergeCell ref="I7:M7"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
@@ -4126,43 +4163,6 @@
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4186,10 +4186,10 @@
   <sheetData>
     <row r="1" spans="2:12" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B2" s="192" t="s">
+      <c r="B2" s="182" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="193"/>
+      <c r="C2" s="183"/>
       <c r="D2" s="9" t="s">
         <v>9</v>
       </c>
@@ -4204,10 +4204,10 @@
       </c>
     </row>
     <row r="3" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B3" s="188" t="s">
+      <c r="B3" s="184" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="189"/>
+      <c r="C3" s="185"/>
       <c r="D3" s="9" t="s">
         <v>12</v>
       </c>
@@ -4234,10 +4234,10 @@
       </c>
     </row>
     <row r="4" spans="2:12">
-      <c r="B4" s="194" t="s">
+      <c r="B4" s="186" t="s">
         <v>71</v>
       </c>
-      <c r="C4" s="195"/>
+      <c r="C4" s="187"/>
       <c r="D4" s="73"/>
       <c r="E4" s="74">
         <v>3</v>
@@ -4261,10 +4261,10 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B5" s="130" t="s">
+      <c r="B5" s="137" t="s">
         <v>106</v>
       </c>
-      <c r="C5" s="149"/>
+      <c r="C5" s="150"/>
       <c r="D5" s="7"/>
       <c r="E5" s="31">
         <v>3</v>
@@ -4283,10 +4283,10 @@
       </c>
     </row>
     <row r="6" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B6" s="188" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="189"/>
+      <c r="B6" s="184" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="185"/>
       <c r="D6" s="9" t="s">
         <v>11</v>
       </c>
@@ -4313,10 +4313,10 @@
       </c>
     </row>
     <row r="7" spans="2:12">
-      <c r="B7" s="186" t="s">
+      <c r="B7" s="190" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="187"/>
+      <c r="C7" s="191"/>
       <c r="D7" s="57"/>
       <c r="E7" s="59">
         <v>3</v>
@@ -4330,10 +4330,10 @@
       </c>
     </row>
     <row r="8" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B8" s="130" t="s">
+      <c r="B8" s="137" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="149"/>
+      <c r="C8" s="150"/>
       <c r="D8" s="7"/>
       <c r="E8" s="31">
         <v>3</v>
@@ -4345,10 +4345,10 @@
       <c r="L8" s="52"/>
     </row>
     <row r="9" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B9" s="188" t="s">
+      <c r="B9" s="184" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="189"/>
+      <c r="C9" s="185"/>
       <c r="D9" s="9" t="s">
         <v>10</v>
       </c>
@@ -4365,10 +4365,10 @@
       </c>
     </row>
     <row r="10" spans="2:12">
-      <c r="B10" s="180" t="s">
+      <c r="B10" s="170" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="190"/>
+      <c r="C10" s="188"/>
       <c r="D10" s="8"/>
       <c r="E10" s="33">
         <v>3</v>
@@ -4379,10 +4379,10 @@
       </c>
     </row>
     <row r="11" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B11" s="178" t="s">
+      <c r="B11" s="166" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="191"/>
+      <c r="C11" s="189"/>
       <c r="D11" s="7"/>
       <c r="E11" s="31">
         <v>2</v>
@@ -4393,10 +4393,10 @@
       </c>
     </row>
     <row r="12" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B12" s="188" t="s">
+      <c r="B12" s="184" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="189"/>
+      <c r="C12" s="185"/>
       <c r="D12" s="9" t="s">
         <v>14</v>
       </c>
@@ -4413,10 +4413,10 @@
       </c>
     </row>
     <row r="13" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B13" s="186" t="s">
+      <c r="B13" s="190" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="187"/>
+      <c r="C13" s="191"/>
       <c r="D13" s="57"/>
       <c r="E13" s="59">
         <v>2</v>
@@ -4427,10 +4427,10 @@
       </c>
     </row>
     <row r="14" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B14" s="188" t="s">
+      <c r="B14" s="184" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="189"/>
+      <c r="C14" s="185"/>
       <c r="D14" s="9"/>
       <c r="E14" s="34">
         <f>SUM(E15:E16)</f>
@@ -4445,10 +4445,10 @@
       </c>
     </row>
     <row r="15" spans="2:12">
-      <c r="B15" s="180" t="s">
+      <c r="B15" s="170" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="190"/>
+      <c r="C15" s="188"/>
       <c r="D15" s="8"/>
       <c r="E15" s="33">
         <v>1</v>
@@ -4459,10 +4459,10 @@
       </c>
     </row>
     <row r="16" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B16" s="178" t="s">
+      <c r="B16" s="166" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="191"/>
+      <c r="C16" s="189"/>
       <c r="D16" s="7"/>
       <c r="E16" s="31">
         <v>1</v>
@@ -4473,10 +4473,10 @@
       </c>
     </row>
     <row r="17" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B17" s="188" t="s">
+      <c r="B17" s="184" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="189"/>
+      <c r="C17" s="185"/>
       <c r="D17" s="9"/>
       <c r="E17" s="34">
         <f>SUM(E18:E19)</f>
@@ -4491,10 +4491,10 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="180" t="s">
+      <c r="B18" s="170" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="190"/>
+      <c r="C18" s="188"/>
       <c r="D18" s="8"/>
       <c r="E18" s="33">
         <v>1</v>
@@ -4505,10 +4505,10 @@
       </c>
     </row>
     <row r="19" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B19" s="182" t="s">
+      <c r="B19" s="192" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="183"/>
+      <c r="C19" s="193"/>
       <c r="D19" s="6"/>
       <c r="E19" s="32">
         <v>1</v>
@@ -4519,10 +4519,10 @@
       </c>
     </row>
     <row r="20" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B20" s="184" t="s">
+      <c r="B20" s="194" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="185"/>
+      <c r="C20" s="195"/>
       <c r="D20" s="9"/>
       <c r="E20" s="34">
         <f>SUM(E3+E6+E9+E12+E14+E17)</f>
@@ -4539,6 +4539,18 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
@@ -4546,18 +4558,6 @@
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GlassesGameコスト表.xlsx
+++ b/GlassesGameコスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ayato Terao\Documents\GitHub\GlassesGame\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C7CA7C-DB4F-4012-B782-699188101ADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4359C20C-0F83-4AD9-AC64-508DE45DAE5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="599" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="プロト" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,11 @@
     <sheet name="スケジュール" sheetId="3" r:id="rId4"/>
     <sheet name="素材" sheetId="4" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">アルファ!$G$2:$G$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">プロト!$G$2:$G$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">ベータ・マスター!$G$2:$G$22</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="123">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -463,10 +468,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>(サウンド）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>やること(β・Ｍ)</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -654,10 +655,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ギミック</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ポーズ</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -770,10 +767,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ー　ボタンSE</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t xml:space="preserve">               ー　BGM</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -797,6 +790,32 @@
   </si>
   <si>
     <t>完了</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー　ボタン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">               ー　SE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マニュアル(操作方法)</t>
+    <rPh sb="6" eb="10">
+      <t>ソウサホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>終了</t>
+    <rPh sb="0" eb="2">
+      <t>シュウリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スタート</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -916,7 +935,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="52">
+  <borders count="55">
     <border>
       <left/>
       <right/>
@@ -1565,11 +1584,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="197">
+  <cellXfs count="199">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -1600,7 +1656,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="56" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="56" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
@@ -1758,14 +1813,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="56" fontId="0" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
@@ -1880,9 +1931,6 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="45" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1922,12 +1970,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2066,26 +2108,65 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="40" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="43" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="52" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
@@ -2387,11 +2468,11 @@
   <sheetData>
     <row r="1" spans="2:19" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B2" s="160" t="s">
+      <c r="B2" s="152" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="173"/>
-      <c r="D2" s="68" t="s">
+      <c r="C2" s="165"/>
+      <c r="D2" s="67" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="9" t="s">
@@ -2401,752 +2482,753 @@
         <v>8</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B3" s="146" t="s">
+      <c r="B3" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="172"/>
-      <c r="D3" s="97" t="s">
+      <c r="C3" s="164"/>
+      <c r="D3" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="107">
+      <c r="E3" s="102">
         <f>SUM(E4:E15)</f>
         <v>21</v>
       </c>
-      <c r="F3" s="107">
+      <c r="F3" s="102">
         <f>SUM(F4:F15)</f>
         <v>23</v>
       </c>
-      <c r="G3" s="66" t="s">
-        <v>84</v>
-      </c>
-      <c r="I3" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="J3" s="47">
+      <c r="G3" s="65" t="s">
+        <v>83</v>
+      </c>
+      <c r="I3" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" s="46">
         <f ca="1">TODAY()</f>
         <v>46308</v>
       </c>
-      <c r="K3" s="35" t="s">
-        <v>83</v>
+      <c r="K3" s="34" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B4" s="125" t="s">
+      <c r="B4" s="120" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="174"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="33">
+      <c r="C4" s="166"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="32">
         <f>SUM(E5:E7)</f>
         <v>4</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="32">
         <f>SUM(F5:F7)</f>
         <v>5</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="I4" s="66" t="s">
-        <v>75</v>
-      </c>
-      <c r="J4" s="47">
+        <v>83</v>
+      </c>
+      <c r="I4" s="65" t="s">
+        <v>74</v>
+      </c>
+      <c r="J4" s="46">
         <v>46295</v>
       </c>
-      <c r="K4" s="56" t="str">
+      <c r="K4" s="55" t="str">
         <f ca="1">SUM($J4-J3)&amp; "日"</f>
         <v>-13日</v>
       </c>
     </row>
     <row r="5" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B5" s="131" t="s">
+      <c r="B5" s="125" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="143"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="30">
+      <c r="C5" s="137"/>
+      <c r="D5" s="69"/>
+      <c r="E5" s="29">
         <v>2</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="29">
         <v>2</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="I5" s="63" t="s">
-        <v>73</v>
-      </c>
-      <c r="J5" s="64">
+        <v>83</v>
+      </c>
+      <c r="I5" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="J5" s="63">
         <v>46314</v>
       </c>
-      <c r="K5" s="65" t="str">
+      <c r="K5" s="64" t="str">
         <f ca="1">SUM(J5-J3)&amp; "日"</f>
         <v>6日</v>
       </c>
-      <c r="R5" s="51"/>
-      <c r="S5" s="52"/>
+      <c r="R5" s="50"/>
+      <c r="S5" s="51"/>
     </row>
     <row r="6" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B6" s="131" t="s">
+      <c r="B6" s="125" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="143"/>
-      <c r="D6" s="70"/>
-      <c r="E6" s="30">
-        <v>1</v>
-      </c>
-      <c r="F6" s="30">
+      <c r="C6" s="137"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="29">
+        <v>1</v>
+      </c>
+      <c r="F6" s="29">
         <v>2</v>
       </c>
       <c r="G6" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="R6" s="50"/>
+      <c r="S6" s="51"/>
+    </row>
+    <row r="7" spans="2:19" ht="19.5" thickBot="1">
+      <c r="B7" s="125" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="137"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="29">
+        <v>1</v>
+      </c>
+      <c r="F7" s="32">
+        <v>1</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I7" s="156" t="s">
+        <v>100</v>
+      </c>
+      <c r="J7" s="157"/>
+      <c r="R7" s="50"/>
+      <c r="S7" s="51"/>
+    </row>
+    <row r="8" spans="2:19">
+      <c r="B8" s="122" t="s">
         <v>84</v>
       </c>
-      <c r="R6" s="51"/>
-      <c r="S6" s="52"/>
-    </row>
-    <row r="7" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B7" s="131" t="s">
-        <v>86</v>
-      </c>
-      <c r="C7" s="143"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="30">
-        <v>1</v>
-      </c>
-      <c r="F7" s="33">
-        <v>1</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="I7" s="164" t="s">
-        <v>102</v>
-      </c>
-      <c r="J7" s="165"/>
-      <c r="R7" s="51"/>
-      <c r="S7" s="52"/>
-    </row>
-    <row r="8" spans="2:19">
-      <c r="B8" s="127" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" s="153"/>
-      <c r="D8" s="70"/>
-      <c r="E8" s="30">
+      <c r="C8" s="145"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="29">
         <v>2</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="32">
         <v>2</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="I8" s="82" t="s">
-        <v>99</v>
-      </c>
-      <c r="J8" s="85">
+        <v>83</v>
+      </c>
+      <c r="I8" s="77" t="s">
+        <v>97</v>
+      </c>
+      <c r="J8" s="81">
         <f>SUM(E3)</f>
         <v>21</v>
       </c>
     </row>
     <row r="9" spans="2:19">
-      <c r="B9" s="127" t="s">
+      <c r="B9" s="122" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="153"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="31">
+      <c r="C9" s="145"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="30">
         <v>2</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="30">
         <v>2</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="I9" s="83" t="s">
+        <v>83</v>
+      </c>
+      <c r="I9" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="J9" s="86">
+      <c r="J9" s="82">
         <f>SUM(E16)</f>
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="2:19">
-      <c r="B10" s="127" t="s">
+      <c r="B10" s="122" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="153"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="31">
+      <c r="C10" s="145"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="30">
         <v>2</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="30">
         <v>2</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="I10" s="83" t="s">
+        <v>83</v>
+      </c>
+      <c r="I10" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="J10" s="86">
+      <c r="J10" s="82">
         <f>SUM(E26)</f>
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B11" s="129" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" s="169"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="30">
-        <v>1</v>
-      </c>
-      <c r="F11" s="30">
+      <c r="B11" s="124" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="161"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="29">
+        <v>1</v>
+      </c>
+      <c r="F11" s="29">
         <v>1</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I11" s="84" t="s">
+        <v>83</v>
+      </c>
+      <c r="I11" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="87">
+      <c r="J11" s="83">
         <f>SUM(E32)</f>
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B12" s="127" t="s">
+      <c r="B12" s="122" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="153"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="30">
+      <c r="C12" s="145"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="29">
         <f>SUM(E13:E15)</f>
         <v>3</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="29">
         <f>SUM(F13:F15)</f>
         <v>3</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="I12" s="89" t="s">
-        <v>101</v>
-      </c>
-      <c r="J12" s="79">
+        <v>83</v>
+      </c>
+      <c r="I12" s="116" t="s">
+        <v>99</v>
+      </c>
+      <c r="J12" s="78">
         <f>SUM(J8:J11)</f>
         <v>66</v>
       </c>
     </row>
     <row r="13" spans="2:19">
-      <c r="B13" s="139" t="s">
+      <c r="B13" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="168"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="30">
-        <v>1</v>
-      </c>
-      <c r="F13" s="30">
+      <c r="C13" s="160"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="29">
+        <v>1</v>
+      </c>
+      <c r="F13" s="29">
         <v>1</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="2:19">
-      <c r="B14" s="131" t="s">
+      <c r="B14" s="125" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="143"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="30">
-        <v>1</v>
-      </c>
-      <c r="F14" s="30">
+      <c r="C14" s="137"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="29">
+        <v>1</v>
+      </c>
+      <c r="F14" s="29">
         <v>1</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="R14" s="51"/>
-      <c r="S14" s="52"/>
+        <v>83</v>
+      </c>
+      <c r="R14" s="50"/>
+      <c r="S14" s="51"/>
     </row>
     <row r="15" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B15" s="133" t="s">
+      <c r="B15" s="127" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="177"/>
-      <c r="D15" s="71"/>
-      <c r="E15" s="31">
-        <v>1</v>
-      </c>
-      <c r="F15" s="31">
+      <c r="C15" s="169"/>
+      <c r="D15" s="70"/>
+      <c r="E15" s="30">
+        <v>1</v>
+      </c>
+      <c r="F15" s="30">
         <v>1</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="2:19" ht="19.5" thickBot="1">
-      <c r="B16" s="146" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="172"/>
-      <c r="D16" s="93" t="s">
+      <c r="B16" s="138" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="164"/>
+      <c r="D16" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="E16" s="107">
+      <c r="E16" s="102">
         <f>SUM(E17:E25)</f>
         <v>16</v>
       </c>
-      <c r="F16" s="107">
+      <c r="F16" s="102">
         <v>8</v>
       </c>
-      <c r="G16" s="66" t="s">
-        <v>84</v>
+      <c r="G16" s="65" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="125" t="s">
+      <c r="B17" s="120" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="174"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="33">
+      <c r="C17" s="166"/>
+      <c r="D17" s="77"/>
+      <c r="E17" s="32">
         <v>3</v>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="32">
         <v>1</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="127" t="s">
+      <c r="B18" s="122" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="153"/>
-      <c r="D18" s="70"/>
-      <c r="E18" s="30">
+      <c r="C18" s="145"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="29">
         <v>3</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="29">
         <v>1</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="B19" s="127" t="s">
+      <c r="B19" s="122" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="153"/>
-      <c r="D19" s="70"/>
-      <c r="E19" s="30">
+      <c r="C19" s="145"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="29">
         <v>3</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="29">
         <v>1</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="127" t="s">
+      <c r="B20" s="122" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="153"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="30">
+      <c r="C20" s="145"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="29">
         <v>3</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="29">
         <v>1</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="2:7">
-      <c r="B21" s="127" t="s">
+      <c r="B21" s="122" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="153"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="59">
-        <v>1</v>
-      </c>
-      <c r="F21" s="30">
+      <c r="C21" s="145"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="58">
+        <v>1</v>
+      </c>
+      <c r="F21" s="29">
         <v>1</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="2:7">
-      <c r="B22" s="129" t="s">
+      <c r="B22" s="124" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="169"/>
-      <c r="D22" s="70"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30">
+      <c r="C22" s="161"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29">
         <v>3</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="2:7">
-      <c r="B23" s="139" t="s">
+      <c r="B23" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="168"/>
-      <c r="D23" s="70"/>
-      <c r="E23" s="30">
-        <v>1</v>
-      </c>
-      <c r="F23" s="30">
+      <c r="C23" s="160"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="29">
+        <v>1</v>
+      </c>
+      <c r="F23" s="29">
         <v>1</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="2:7">
-      <c r="B24" s="139" t="s">
+      <c r="B24" s="133" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="168"/>
-      <c r="D24" s="70"/>
-      <c r="E24" s="30">
-        <v>1</v>
-      </c>
-      <c r="F24" s="30">
+      <c r="C24" s="160"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="29">
+        <v>1</v>
+      </c>
+      <c r="F24" s="29">
         <v>1</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B25" s="141" t="s">
+      <c r="B25" s="135" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="178"/>
-      <c r="D25" s="80"/>
-      <c r="E25" s="32">
-        <v>1</v>
-      </c>
-      <c r="F25" s="32">
+      <c r="C25" s="170"/>
+      <c r="D25" s="79"/>
+      <c r="E25" s="31">
+        <v>1</v>
+      </c>
+      <c r="F25" s="31">
         <v>1</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B26" s="146" t="s">
+      <c r="B26" s="138" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="172"/>
-      <c r="D26" s="93" t="s">
+      <c r="C26" s="164"/>
+      <c r="D26" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="107">
+      <c r="E26" s="102">
         <f>SUM(E27:E31)</f>
         <v>16</v>
       </c>
-      <c r="F26" s="107">
+      <c r="F26" s="102">
         <f>SUM(F27,F28,F31)</f>
         <v>11</v>
       </c>
-      <c r="G26" s="66" t="s">
-        <v>84</v>
+      <c r="G26" s="65" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="170" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" s="171"/>
-      <c r="D27" s="78"/>
-      <c r="E27" s="33">
+      <c r="B27" s="162" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" s="163"/>
+      <c r="D27" s="77"/>
+      <c r="E27" s="32">
         <v>5</v>
       </c>
-      <c r="F27" s="33">
+      <c r="F27" s="32">
         <v>5</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="2:7">
-      <c r="B28" s="129" t="s">
+      <c r="B28" s="124" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="169"/>
-      <c r="D28" s="70"/>
-      <c r="E28" s="30">
+      <c r="C28" s="161"/>
+      <c r="D28" s="69"/>
+      <c r="E28" s="29">
         <f>SUM(E29:E30)</f>
         <v>4</v>
       </c>
-      <c r="F28" s="30">
+      <c r="F28" s="29">
         <f>SUM(F29:F30)</f>
         <v>3</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="2:7">
-      <c r="B29" s="139" t="s">
+      <c r="B29" s="133" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="168"/>
-      <c r="D29" s="70"/>
-      <c r="E29" s="30">
+      <c r="C29" s="160"/>
+      <c r="D29" s="69"/>
+      <c r="E29" s="29">
         <v>2</v>
       </c>
-      <c r="F29" s="30">
+      <c r="F29" s="29">
         <v>2</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="139" t="s">
+      <c r="B30" s="133" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="168"/>
-      <c r="D30" s="70"/>
-      <c r="E30" s="30">
+      <c r="C30" s="160"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="29">
         <v>2</v>
       </c>
-      <c r="F30" s="30">
+      <c r="F30" s="29">
         <v>1</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B31" s="137" t="s">
+      <c r="B31" s="131" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="150"/>
-      <c r="D31" s="71"/>
-      <c r="E31" s="31">
+      <c r="C31" s="142"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="30">
         <v>3</v>
       </c>
-      <c r="F31" s="31">
+      <c r="F31" s="30">
         <v>3</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B32" s="146" t="s">
+      <c r="B32" s="138" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="172"/>
-      <c r="D32" s="93" t="s">
+      <c r="C32" s="164"/>
+      <c r="D32" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="107">
+      <c r="E32" s="102">
         <f>SUM(E33:E42)</f>
         <v>13</v>
       </c>
-      <c r="F32" s="107">
+      <c r="F32" s="102">
         <f>SUM(F34,F36,F37,F40,F41)</f>
         <v>5</v>
       </c>
-      <c r="G32" s="66" t="s">
-        <v>84</v>
+      <c r="G32" s="65" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="2:7">
-      <c r="B33" s="125" t="s">
+      <c r="B33" s="120" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="174"/>
-      <c r="D33" s="78"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="33"/>
+      <c r="C33" s="166"/>
+      <c r="D33" s="77"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="32"/>
       <c r="G33" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="2:7">
-      <c r="B34" s="131" t="s">
+      <c r="B34" s="125" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="143"/>
-      <c r="D34" s="78"/>
-      <c r="E34" s="33">
+      <c r="C34" s="137"/>
+      <c r="D34" s="77"/>
+      <c r="E34" s="32">
         <v>2</v>
       </c>
-      <c r="F34" s="33">
+      <c r="F34" s="32">
         <v>1</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="2:7">
-      <c r="B35" s="158" t="s">
+      <c r="B35" s="150" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="179"/>
-      <c r="D35" s="95"/>
-      <c r="E35" s="108"/>
-      <c r="F35" s="108"/>
-      <c r="G35" s="105" t="s">
-        <v>84</v>
+      <c r="C35" s="171"/>
+      <c r="D35" s="90"/>
+      <c r="E35" s="103"/>
+      <c r="F35" s="103"/>
+      <c r="G35" s="100" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="2:7">
-      <c r="B36" s="127" t="s">
+      <c r="B36" s="122" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="153"/>
-      <c r="D36" s="70"/>
-      <c r="E36" s="30">
+      <c r="C36" s="145"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="29">
         <v>2</v>
       </c>
-      <c r="F36" s="30">
+      <c r="F36" s="29">
         <v>1</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="127" t="s">
+      <c r="B37" s="122" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="153"/>
-      <c r="D37" s="70"/>
-      <c r="E37" s="30">
+      <c r="C37" s="145"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="29">
         <v>2</v>
       </c>
-      <c r="F37" s="30">
+      <c r="F37" s="29">
         <v>1</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38" spans="2:7">
-      <c r="B38" s="127" t="s">
-        <v>93</v>
-      </c>
-      <c r="C38" s="153"/>
-      <c r="D38" s="70"/>
-      <c r="E38" s="30">
-        <v>1</v>
-      </c>
-      <c r="F38" s="30">
+      <c r="B38" s="122" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" s="145"/>
+      <c r="D38" s="69"/>
+      <c r="E38" s="29">
+        <v>1</v>
+      </c>
+      <c r="F38" s="29">
         <v>1</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="2:7">
-      <c r="B39" s="158" t="s">
+      <c r="B39" s="150" t="s">
         <v>5</v>
       </c>
-      <c r="C39" s="179"/>
-      <c r="D39" s="95"/>
-      <c r="E39" s="108"/>
-      <c r="F39" s="108"/>
-      <c r="G39" s="105" t="s">
-        <v>84</v>
+      <c r="C39" s="171"/>
+      <c r="D39" s="90"/>
+      <c r="E39" s="103"/>
+      <c r="F39" s="103"/>
+      <c r="G39" s="100" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="40" spans="2:7">
-      <c r="B40" s="180" t="s">
+      <c r="B40" s="172" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="181"/>
-      <c r="D40" s="77"/>
-      <c r="E40" s="30">
+      <c r="C40" s="173"/>
+      <c r="D40" s="76"/>
+      <c r="E40" s="29">
         <v>2</v>
       </c>
-      <c r="F40" s="30">
+      <c r="F40" s="29">
         <v>1</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="2:7">
-      <c r="B41" s="129" t="s">
+      <c r="B41" s="124" t="s">
         <v>61</v>
       </c>
-      <c r="C41" s="176"/>
-      <c r="D41" s="77"/>
-      <c r="E41" s="30">
+      <c r="C41" s="168"/>
+      <c r="D41" s="76"/>
+      <c r="E41" s="29">
         <v>3</v>
       </c>
-      <c r="F41" s="30">
+      <c r="F41" s="29">
         <v>1</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B42" s="166" t="s">
-        <v>93</v>
-      </c>
-      <c r="C42" s="167"/>
-      <c r="D42" s="69"/>
-      <c r="E42" s="31">
-        <v>1</v>
-      </c>
-      <c r="F42" s="31">
+      <c r="B42" s="158" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" s="159"/>
+      <c r="D42" s="68"/>
+      <c r="E42" s="30">
+        <v>1</v>
+      </c>
+      <c r="F42" s="30">
         <v>1</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B43" s="156" t="s">
-        <v>82</v>
-      </c>
-      <c r="C43" s="175"/>
-      <c r="D43" s="67"/>
-      <c r="E43" s="34">
+      <c r="B43" s="148" t="s">
+        <v>81</v>
+      </c>
+      <c r="C43" s="167"/>
+      <c r="D43" s="66"/>
+      <c r="E43" s="33">
         <f>SUM(E3+E16+E26+F32)</f>
         <v>58</v>
       </c>
-      <c r="F43" s="34">
+      <c r="F43" s="33">
         <f>SUM(F3+F16+F26+F32)</f>
         <v>47</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="G2:G42" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="43">
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B41:C41"/>
@@ -3203,7 +3285,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0DBF476-724A-4DAE-8D66-8B0809F96B84}">
-  <dimension ref="B1:M52"/>
+  <dimension ref="B1:M49"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="3" max="3" width="18.125" customWidth="1"/>
@@ -3213,10 +3295,10 @@
   <sheetData>
     <row r="1" spans="2:13" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B2" s="160" t="s">
+      <c r="B2" s="152" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="161"/>
+      <c r="C2" s="153"/>
       <c r="D2" s="9" t="s">
         <v>9</v>
       </c>
@@ -3226,932 +3308,930 @@
       <c r="F2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="35" t="s">
-        <v>79</v>
-      </c>
-      <c r="I2" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="J2" s="47">
+      <c r="G2" s="34" t="s">
+        <v>78</v>
+      </c>
+      <c r="I2" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="J2" s="46">
         <f ca="1">TODAY()</f>
         <v>46308</v>
       </c>
-      <c r="K2" s="35" t="s">
-        <v>83</v>
+      <c r="K2" s="34" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B3" s="146" t="s">
+      <c r="B3" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="147"/>
-      <c r="D3" s="66" t="s">
+      <c r="C3" s="139"/>
+      <c r="D3" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="107">
+      <c r="E3" s="102">
         <f>SUM(E4+E6+E8+E9+E15)</f>
-        <v>13</v>
-      </c>
-      <c r="F3" s="107">
+        <v>13.5</v>
+      </c>
+      <c r="F3" s="102">
         <f>SUM(F4+F6+F9+F8+F15)</f>
-        <v>20.5</v>
-      </c>
-      <c r="G3" s="94" t="s">
-        <v>84</v>
-      </c>
-      <c r="I3" s="58" t="s">
-        <v>76</v>
-      </c>
-      <c r="J3" s="46">
-        <v>46305</v>
-      </c>
-      <c r="K3" s="42" t="str">
+        <v>21.5</v>
+      </c>
+      <c r="G3" s="89" t="s">
+        <v>83</v>
+      </c>
+      <c r="I3" s="57" t="s">
+        <v>75</v>
+      </c>
+      <c r="J3" s="45">
+        <v>46307</v>
+      </c>
+      <c r="K3" s="41" t="str">
         <f ca="1">SUM($J3-J2)&amp; "日"</f>
-        <v>-3日</v>
+        <v>-1日</v>
       </c>
     </row>
     <row r="4" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B4" s="125" t="s">
+      <c r="B4" s="120" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="126"/>
-      <c r="D4" s="113"/>
-      <c r="E4" s="114">
+      <c r="C4" s="121"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="109">
         <v>2</v>
       </c>
-      <c r="F4" s="114">
+      <c r="F4" s="109">
         <v>2</v>
       </c>
-      <c r="G4" s="101" t="s">
-        <v>84</v>
-      </c>
-      <c r="I4" s="63" t="s">
-        <v>73</v>
-      </c>
-      <c r="J4" s="64">
+      <c r="G4" s="96" t="s">
+        <v>83</v>
+      </c>
+      <c r="I4" s="62" t="s">
+        <v>72</v>
+      </c>
+      <c r="J4" s="63">
         <v>46314</v>
       </c>
-      <c r="K4" s="65" t="str">
+      <c r="K4" s="64" t="str">
         <f ca="1">SUM(J4-J2)&amp; "日"</f>
         <v>6日</v>
       </c>
     </row>
     <row r="5" spans="2:13">
-      <c r="B5" s="162" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" s="163"/>
+      <c r="B5" s="154" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="155"/>
       <c r="D5" s="5"/>
-      <c r="E5" s="30">
+      <c r="E5" s="29">
         <v>2</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="29">
         <v>2</v>
       </c>
-      <c r="G5" s="39" t="s">
-        <v>84</v>
+      <c r="G5" s="38" t="s">
+        <v>83</v>
       </c>
       <c r="I5" s="4"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="52"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="51"/>
     </row>
     <row r="6" spans="2:13">
-      <c r="B6" s="127" t="s">
-        <v>117</v>
-      </c>
-      <c r="C6" s="153"/>
-      <c r="D6" s="115"/>
-      <c r="E6" s="116">
+      <c r="B6" s="122" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="145"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="111">
         <f>SUM(E7)</f>
         <v>3</v>
       </c>
-      <c r="F6" s="116">
+      <c r="F6" s="111">
         <f>SUM(F7)</f>
         <v>3</v>
       </c>
-      <c r="G6" s="101" t="s">
-        <v>84</v>
+      <c r="G6" s="96" t="s">
+        <v>83</v>
       </c>
       <c r="I6" s="4"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="52"/>
+      <c r="J6" s="50"/>
+      <c r="K6" s="51"/>
     </row>
     <row r="7" spans="2:13">
-      <c r="B7" s="131" t="s">
-        <v>118</v>
-      </c>
-      <c r="C7" s="143"/>
+      <c r="B7" s="125" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="137"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <v>3</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="29">
         <v>3</v>
       </c>
-      <c r="G7" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="I7" s="122" t="s">
+      <c r="G7" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="I7" s="117" t="s">
+        <v>87</v>
+      </c>
+      <c r="J7" s="117"/>
+      <c r="K7" s="117"/>
+      <c r="L7" s="117"/>
+      <c r="M7" s="117"/>
+    </row>
+    <row r="8" spans="2:13">
+      <c r="B8" s="122" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="123"/>
+      <c r="D8" s="110"/>
+      <c r="E8" s="111">
+        <v>2</v>
+      </c>
+      <c r="F8" s="111">
+        <v>5</v>
+      </c>
+      <c r="G8" s="96" t="s">
+        <v>83</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="50"/>
+      <c r="K8" s="51"/>
+    </row>
+    <row r="9" spans="2:13">
+      <c r="B9" s="131" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="132"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="113">
+        <f>SUM(E10:E14)</f>
+        <v>2.5</v>
+      </c>
+      <c r="F9" s="113">
+        <f>SUM(F10:F14)</f>
+        <v>5</v>
+      </c>
+      <c r="G9" s="94" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" ht="19.5" thickBot="1">
+      <c r="B10" s="125" t="s">
         <v>88</v>
       </c>
-      <c r="J7" s="122"/>
-      <c r="K7" s="122"/>
-      <c r="L7" s="122"/>
-      <c r="M7" s="122"/>
-    </row>
-    <row r="8" spans="2:13">
-      <c r="B8" s="127" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="128"/>
-      <c r="D8" s="115"/>
-      <c r="E8" s="116">
-        <v>2</v>
-      </c>
-      <c r="F8" s="116">
-        <v>5</v>
-      </c>
-      <c r="G8" s="101" t="s">
-        <v>84</v>
-      </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="52"/>
-    </row>
-    <row r="9" spans="2:13">
-      <c r="B9" s="137" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="138"/>
-      <c r="D9" s="117"/>
-      <c r="E9" s="118">
-        <f>SUM(E10+E11+E12+E13)</f>
-        <v>2</v>
-      </c>
-      <c r="F9" s="118">
-        <f>SUM(F10:F13)</f>
+      <c r="C10" s="126"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="29">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="29">
+        <v>1</v>
+      </c>
+      <c r="G10" s="80" t="s">
+        <v>83</v>
+      </c>
+      <c r="I10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" ht="19.5" thickBot="1">
+      <c r="B11" s="125" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="126"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="29">
+        <v>0.5</v>
+      </c>
+      <c r="F11" s="29">
+        <v>1</v>
+      </c>
+      <c r="G11" s="80" t="s">
+        <v>83</v>
+      </c>
+      <c r="I11" s="129" t="s">
+        <v>101</v>
+      </c>
+      <c r="J11" s="130"/>
+    </row>
+    <row r="12" spans="2:13">
+      <c r="B12" s="125" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="126"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="29">
+        <v>0.5</v>
+      </c>
+      <c r="F12" s="29">
+        <v>1</v>
+      </c>
+      <c r="G12" s="80" t="s">
+        <v>83</v>
+      </c>
+      <c r="I12" s="97" t="s">
+        <v>97</v>
+      </c>
+      <c r="J12" s="81">
+        <f>SUM(E3+E28+E35)</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13">
+      <c r="B13" s="127" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="128"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="F13" s="29">
+        <v>1</v>
+      </c>
+      <c r="G13" s="80" t="s">
+        <v>83</v>
+      </c>
+      <c r="I13" s="98" t="s">
+        <v>11</v>
+      </c>
+      <c r="J13" s="82">
+        <f>SUM(E19)</f>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13">
+      <c r="B14" s="125" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" s="137"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="F14" s="30">
+        <v>1</v>
+      </c>
+      <c r="G14" s="80" t="s">
+        <v>83</v>
+      </c>
+      <c r="I14" s="98" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="82">
+        <f>SUM(E23)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" ht="19.5" thickBot="1">
+      <c r="B15" s="131" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15" s="132"/>
+      <c r="D15" s="112"/>
+      <c r="E15" s="113">
         <v>4</v>
       </c>
-      <c r="G9" s="99" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B10" s="131" t="s">
-        <v>89</v>
-      </c>
-      <c r="C10" s="132"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="F10" s="30">
-        <v>1</v>
-      </c>
-      <c r="G10" s="81" t="s">
-        <v>84</v>
-      </c>
-      <c r="I10" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B11" s="131" t="s">
-        <v>90</v>
-      </c>
-      <c r="C11" s="132"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="F11" s="30">
-        <v>1</v>
-      </c>
-      <c r="G11" s="81" t="s">
-        <v>84</v>
-      </c>
-      <c r="I11" s="135" t="s">
-        <v>103</v>
-      </c>
-      <c r="J11" s="136"/>
-    </row>
-    <row r="12" spans="2:13">
-      <c r="B12" s="131" t="s">
-        <v>91</v>
-      </c>
-      <c r="C12" s="132"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="F12" s="30">
-        <v>1</v>
-      </c>
-      <c r="G12" s="81" t="s">
-        <v>84</v>
-      </c>
-      <c r="I12" s="102" t="s">
-        <v>99</v>
-      </c>
-      <c r="J12" s="85">
-        <f>SUM(F3+E33+E40)</f>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13">
-      <c r="B13" s="133" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="134"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="31">
-        <v>0.5</v>
-      </c>
-      <c r="F13" s="30">
-        <v>1</v>
-      </c>
-      <c r="G13" s="81" t="s">
-        <v>84</v>
-      </c>
-      <c r="I13" s="103" t="s">
-        <v>11</v>
-      </c>
-      <c r="J13" s="86">
-        <f>SUM(E19)</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="2:13">
-      <c r="B14" s="131" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" s="143"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="31">
-        <v>0.5</v>
-      </c>
-      <c r="F14" s="31">
-        <v>1</v>
-      </c>
-      <c r="G14" s="81" t="s">
-        <v>84</v>
-      </c>
-      <c r="I14" s="103" t="s">
-        <v>10</v>
-      </c>
-      <c r="J14" s="86">
-        <f>SUM(E26)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B15" s="137" t="s">
-        <v>104</v>
-      </c>
-      <c r="C15" s="138"/>
-      <c r="D15" s="117"/>
-      <c r="E15" s="118">
-        <v>4</v>
-      </c>
-      <c r="F15" s="118">
+      <c r="F15" s="113">
         <f>SUM(F16:F18)</f>
         <v>6.5</v>
       </c>
-      <c r="G15" s="100" t="s">
-        <v>84</v>
-      </c>
-      <c r="I15" s="104" t="s">
+      <c r="G15" s="95" t="s">
+        <v>83</v>
+      </c>
+      <c r="I15" s="99" t="s">
         <v>14</v>
       </c>
-      <c r="J15" s="87">
-        <f>SUM(E31)</f>
-        <v>16.5</v>
+      <c r="J15" s="83">
+        <f>SUM(E26)</f>
+        <v>18.5</v>
       </c>
     </row>
     <row r="16" spans="2:13" ht="19.5" thickBot="1">
-      <c r="B16" s="139" t="s">
+      <c r="B16" s="133" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="134"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="29">
+        <v>1</v>
+      </c>
+      <c r="F16" s="29">
+        <v>1</v>
+      </c>
+      <c r="G16" s="52" t="s">
+        <v>83</v>
+      </c>
+      <c r="I16" s="116" t="s">
+        <v>99</v>
+      </c>
+      <c r="J16" s="78">
+        <f>SUM(J12:J15)</f>
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="133" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="134"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="29">
+        <v>5</v>
+      </c>
+      <c r="F17" s="29">
+        <v>5</v>
+      </c>
+      <c r="G17" s="52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B18" s="135" t="s">
         <v>107</v>
       </c>
-      <c r="C16" s="140"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="30">
-        <v>1</v>
-      </c>
-      <c r="F16" s="30">
-        <v>1</v>
-      </c>
-      <c r="G16" s="53" t="s">
-        <v>84</v>
-      </c>
-      <c r="I16" s="121" t="s">
-        <v>101</v>
-      </c>
-      <c r="J16" s="79">
-        <f>SUM(J12:J15)</f>
-        <v>66.5</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7">
-      <c r="B17" s="139" t="s">
+      <c r="C18" s="136"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="31">
+        <v>1</v>
+      </c>
+      <c r="F18" s="31">
+        <v>0.5</v>
+      </c>
+      <c r="G18" s="93" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B19" s="118" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="119"/>
+      <c r="D19" s="105" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="106">
+        <f>SUM(E20:E22)</f>
+        <v>9</v>
+      </c>
+      <c r="F19" s="106">
+        <f>SUM(F20:F22)</f>
+        <v>3</v>
+      </c>
+      <c r="G19" s="107" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="120" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="121"/>
+      <c r="D20" s="114"/>
+      <c r="E20" s="115">
+        <v>2</v>
+      </c>
+      <c r="F20" s="115">
+        <v>1</v>
+      </c>
+      <c r="G20" s="96" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="122" t="s">
+        <v>93</v>
+      </c>
+      <c r="C21" s="123"/>
+      <c r="D21" s="114"/>
+      <c r="E21" s="115">
+        <v>4</v>
+      </c>
+      <c r="F21" s="115"/>
+      <c r="G21" s="96" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B22" s="122" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" s="123"/>
+      <c r="D22" s="110"/>
+      <c r="E22" s="111">
+        <v>3</v>
+      </c>
+      <c r="F22" s="111">
+        <v>2</v>
+      </c>
+      <c r="G22" s="96" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B23" s="138" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="139"/>
+      <c r="D23" s="65" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="102">
+        <f>SUM(E24:E25)</f>
+        <v>6</v>
+      </c>
+      <c r="F23" s="102">
+        <f>SUM(F24:F25)</f>
+        <v>6</v>
+      </c>
+      <c r="G23" s="89" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7">
+      <c r="B24" s="131" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="142"/>
+      <c r="D24" s="112"/>
+      <c r="E24" s="113">
+        <v>5</v>
+      </c>
+      <c r="F24" s="113">
+        <v>5</v>
+      </c>
+      <c r="G24" s="95" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B25" s="143" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="144"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="31">
+        <v>1</v>
+      </c>
+      <c r="F25" s="31">
+        <v>1</v>
+      </c>
+      <c r="G25" s="52" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B26" s="138" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="139"/>
+      <c r="D26" s="65" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="102">
+        <f>SUM(E28+E35+E44+E47)</f>
+        <v>18.5</v>
+      </c>
+      <c r="F26" s="102">
+        <f>SUM(F28+F35+F44+F47)</f>
+        <v>19.5</v>
+      </c>
+      <c r="G26" s="89" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7">
+      <c r="B27" s="120" t="s">
+        <v>63</v>
+      </c>
+      <c r="C27" s="121"/>
+      <c r="D27" s="114"/>
+      <c r="E27" s="115">
+        <v>5</v>
+      </c>
+      <c r="F27" s="115">
+        <v>2</v>
+      </c>
+      <c r="G27" s="94" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7">
+      <c r="B28" s="150" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="151"/>
+      <c r="D28" s="100" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" s="101">
+        <f>SUM(E29+E30)</f>
+        <v>7.5</v>
+      </c>
+      <c r="F28" s="101">
+        <f>SUM(F29+F30)</f>
+        <v>6.5</v>
+      </c>
+      <c r="G28" s="91" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7">
+      <c r="B29" s="122" t="s">
         <v>108</v>
       </c>
-      <c r="C17" s="140"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="30">
-        <v>5</v>
-      </c>
-      <c r="F17" s="30">
-        <v>5</v>
-      </c>
-      <c r="G17" s="53" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B18" s="141" t="s">
+      <c r="C29" s="145"/>
+      <c r="D29" s="110"/>
+      <c r="E29" s="115">
+        <v>0.5</v>
+      </c>
+      <c r="F29" s="115">
+        <v>0.5</v>
+      </c>
+      <c r="G29" s="94" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7">
+      <c r="B30" s="122" t="s">
+        <v>92</v>
+      </c>
+      <c r="C30" s="145"/>
+      <c r="D30" s="110"/>
+      <c r="E30" s="115">
+        <f>SUM(E31+E32+E33+E34)</f>
+        <v>7</v>
+      </c>
+      <c r="F30" s="115">
+        <f>SUM(F31+F32+F33+F34)</f>
+        <v>6</v>
+      </c>
+      <c r="G30" s="94" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7">
+      <c r="B31" s="146" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="142"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="32">
-        <v>1</v>
-      </c>
-      <c r="F18" s="32">
-        <v>0.5</v>
-      </c>
-      <c r="G18" s="98" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B19" s="123" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="124"/>
-      <c r="D19" s="110" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="111">
-        <f>SUM(E20:E23)</f>
-        <v>11</v>
-      </c>
-      <c r="F19" s="111">
-        <f>SUM(F20:F23)</f>
-        <v>3</v>
-      </c>
-      <c r="G19" s="112" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7">
-      <c r="B20" s="125" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="126"/>
-      <c r="D20" s="119"/>
-      <c r="E20" s="120">
-        <v>2</v>
-      </c>
-      <c r="F20" s="120">
-        <v>1</v>
-      </c>
-      <c r="G20" s="101" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7">
-      <c r="B21" s="127" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" s="128"/>
-      <c r="D21" s="119"/>
-      <c r="E21" s="120">
-        <v>4</v>
-      </c>
-      <c r="F21" s="120"/>
-      <c r="G21" s="101" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7">
-      <c r="B22" s="127" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="128"/>
-      <c r="D22" s="115"/>
-      <c r="E22" s="116">
-        <v>3</v>
-      </c>
-      <c r="F22" s="116">
-        <v>2</v>
-      </c>
-      <c r="G22" s="101" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7">
-      <c r="B23" s="129" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="130"/>
-      <c r="D23" s="115"/>
-      <c r="E23" s="116">
-        <v>2</v>
-      </c>
-      <c r="F23" s="116"/>
-      <c r="G23" s="99" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7">
-      <c r="B24" s="139" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" s="140"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="30">
-        <v>1</v>
-      </c>
-      <c r="F24" s="30"/>
-      <c r="G24" s="81" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B25" s="144" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="145"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="31">
-        <v>1</v>
-      </c>
-      <c r="F25" s="31"/>
-      <c r="G25" s="53" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B26" s="146" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" s="147"/>
-      <c r="D26" s="66" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="107">
-        <f>SUM(E27+E29)</f>
-        <v>6</v>
-      </c>
-      <c r="F26" s="107">
-        <f>SUM(F27:F30)</f>
-        <v>6</v>
-      </c>
-      <c r="G26" s="94" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7">
-      <c r="B27" s="129" t="s">
-        <v>95</v>
-      </c>
-      <c r="C27" s="130"/>
-      <c r="D27" s="115"/>
-      <c r="E27" s="116">
-        <v>1</v>
-      </c>
-      <c r="F27" s="116"/>
-      <c r="G27" s="99" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7">
-      <c r="B28" s="144" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" s="145"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="31">
-        <v>2</v>
-      </c>
-      <c r="F28" s="31"/>
-      <c r="G28" s="53" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7">
-      <c r="B29" s="137" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="150"/>
-      <c r="D29" s="117"/>
-      <c r="E29" s="118">
-        <v>5</v>
-      </c>
-      <c r="F29" s="118">
-        <v>5</v>
-      </c>
-      <c r="G29" s="100" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B30" s="151" t="s">
-        <v>87</v>
-      </c>
-      <c r="C30" s="152"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="32">
-        <v>1</v>
-      </c>
-      <c r="F30" s="32">
-        <v>1</v>
-      </c>
-      <c r="G30" s="53" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B31" s="146" t="s">
-        <v>59</v>
-      </c>
       <c r="C31" s="147"/>
-      <c r="D31" s="66" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="107">
-        <f>SUM(E32+E33+E41+E47)</f>
-        <v>16.5</v>
-      </c>
-      <c r="F31" s="107">
-        <f>SUM(F32+F41+F47)</f>
-        <v>0</v>
-      </c>
-      <c r="G31" s="94" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7">
-      <c r="B32" s="125" t="s">
-        <v>63</v>
-      </c>
-      <c r="C32" s="126"/>
-      <c r="D32" s="119"/>
-      <c r="E32" s="120">
-        <v>5</v>
-      </c>
-      <c r="F32" s="120"/>
-      <c r="G32" s="99" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7">
-      <c r="B33" s="158" t="s">
-        <v>96</v>
-      </c>
-      <c r="C33" s="159"/>
-      <c r="D33" s="105" t="s">
-        <v>97</v>
-      </c>
-      <c r="E33" s="106">
-        <f>SUM(E34+E35)</f>
-        <v>7.5</v>
-      </c>
-      <c r="F33" s="106">
-        <f>SUM(F34+F35)</f>
-        <v>6.5</v>
-      </c>
-      <c r="G33" s="96" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7">
-      <c r="B34" s="127" t="s">
-        <v>110</v>
-      </c>
-      <c r="C34" s="153"/>
-      <c r="D34" s="115"/>
-      <c r="E34" s="120">
-        <v>0.5</v>
-      </c>
-      <c r="F34" s="120">
-        <v>0.5</v>
-      </c>
-      <c r="G34" s="99" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="127" t="s">
-        <v>93</v>
-      </c>
-      <c r="C35" s="153"/>
-      <c r="D35" s="115"/>
-      <c r="E35" s="120">
-        <f>SUM(E36+E37+E38+E39)</f>
-        <v>7</v>
-      </c>
-      <c r="F35" s="120">
-        <f>SUM(F36+F37+F38+F39)</f>
-        <v>6</v>
-      </c>
-      <c r="G35" s="99" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="154" t="s">
-        <v>111</v>
-      </c>
-      <c r="C36" s="155"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="33">
+      <c r="D31" s="5"/>
+      <c r="E31" s="32">
         <f>2</f>
         <v>2</v>
       </c>
-      <c r="F36" s="33">
+      <c r="F31" s="32">
         <v>1.5</v>
       </c>
-      <c r="G36" s="81" t="s">
-        <v>84</v>
+      <c r="G31" s="80" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7">
+      <c r="B32" s="146" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" s="147"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="32">
+        <v>2</v>
+      </c>
+      <c r="F32" s="32">
+        <v>1.5</v>
+      </c>
+      <c r="G32" s="80" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="146" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" s="147"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="32">
+        <v>2</v>
+      </c>
+      <c r="F33" s="32">
+        <v>1.5</v>
+      </c>
+      <c r="G33" s="80" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7">
+      <c r="B34" s="125" t="s">
+        <v>112</v>
+      </c>
+      <c r="C34" s="137"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="32">
+        <v>1</v>
+      </c>
+      <c r="F34" s="32">
+        <v>1.5</v>
+      </c>
+      <c r="G34" s="80" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
+      <c r="B35" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" s="151"/>
+      <c r="D35" s="100" t="s">
+        <v>95</v>
+      </c>
+      <c r="E35" s="103">
+        <f>SUM(E36+E37+E40)</f>
+        <v>6</v>
+      </c>
+      <c r="F35" s="103">
+        <f>SUM(F36+F37+F40)</f>
+        <v>8</v>
+      </c>
+      <c r="G35" s="91" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
+      <c r="B36" s="122" t="s">
+        <v>96</v>
+      </c>
+      <c r="C36" s="123"/>
+      <c r="D36" s="110"/>
+      <c r="E36" s="111">
+        <v>2</v>
+      </c>
+      <c r="F36" s="111">
+        <v>2</v>
+      </c>
+      <c r="G36" s="94" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="2:7">
-      <c r="B37" s="154" t="s">
-        <v>112</v>
-      </c>
-      <c r="C37" s="155"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="33">
+      <c r="B37" s="122" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" s="145"/>
+      <c r="D37" s="110"/>
+      <c r="E37" s="111">
+        <f>SUM(E38+E41)</f>
+        <v>2.5</v>
+      </c>
+      <c r="F37" s="111">
+        <f>SUM(F38+F41)</f>
+        <v>3</v>
+      </c>
+      <c r="G37" s="94" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="146" t="s">
+        <v>113</v>
+      </c>
+      <c r="C38" s="147"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="29">
         <v>2</v>
       </c>
-      <c r="F37" s="33">
+      <c r="F38" s="29">
+        <v>2</v>
+      </c>
+      <c r="G38" s="80" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" s="146" t="s">
+        <v>119</v>
+      </c>
+      <c r="C39" s="147"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="29">
+        <v>0.5</v>
+      </c>
+      <c r="F39" s="29">
+        <v>1</v>
+      </c>
+      <c r="G39" s="80" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7">
+      <c r="B40" s="122" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" s="145"/>
+      <c r="D40" s="110"/>
+      <c r="E40" s="111">
+        <f>SUM(E41:E43)</f>
         <v>1.5</v>
       </c>
-      <c r="G37" s="81" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7">
-      <c r="B38" s="154" t="s">
-        <v>113</v>
-      </c>
-      <c r="C38" s="155"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="33">
+      <c r="F40" s="111">
+        <f>SUM(F41:F43)</f>
+        <v>3</v>
+      </c>
+      <c r="G40" s="94" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7">
+      <c r="B41" s="125" t="s">
+        <v>122</v>
+      </c>
+      <c r="C41" s="137"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="29">
+        <v>0.5</v>
+      </c>
+      <c r="F41" s="29">
+        <v>1</v>
+      </c>
+      <c r="G41" s="80" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7">
+      <c r="B42" s="125" t="s">
+        <v>120</v>
+      </c>
+      <c r="C42" s="137"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="29">
+        <v>0.5</v>
+      </c>
+      <c r="F42" s="29">
+        <v>1</v>
+      </c>
+      <c r="G42" s="80" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7">
+      <c r="B43" s="125" t="s">
+        <v>121</v>
+      </c>
+      <c r="C43" s="137"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="29">
+        <v>0.5</v>
+      </c>
+      <c r="F43" s="29">
+        <v>1</v>
+      </c>
+      <c r="G43" s="80" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7">
+      <c r="B44" s="150" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="151"/>
+      <c r="D44" s="100"/>
+      <c r="E44" s="103">
+        <f>SUM(E45:E46)</f>
+        <v>3</v>
+      </c>
+      <c r="F44" s="103">
+        <f>SUM(F45:F46)</f>
+        <v>3</v>
+      </c>
+      <c r="G44" s="91" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7">
+      <c r="B45" s="140" t="s">
+        <v>66</v>
+      </c>
+      <c r="C45" s="141"/>
+      <c r="D45" s="112"/>
+      <c r="E45" s="113">
         <v>2</v>
       </c>
-      <c r="F38" s="33">
-        <v>1.5</v>
-      </c>
-      <c r="G38" s="81" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7">
-      <c r="B39" s="131" t="s">
-        <v>114</v>
-      </c>
-      <c r="C39" s="143"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="33">
-        <v>1</v>
-      </c>
-      <c r="F39" s="33">
-        <v>1.5</v>
-      </c>
-      <c r="G39" s="81" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7">
-      <c r="B40" s="158" t="s">
-        <v>4</v>
-      </c>
-      <c r="C40" s="159"/>
-      <c r="D40" s="105" t="s">
-        <v>97</v>
-      </c>
-      <c r="E40" s="108">
-        <f>SUM(E41:E43)</f>
-        <v>5</v>
-      </c>
-      <c r="F40" s="108"/>
-      <c r="G40" s="96" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7">
-      <c r="B41" s="127" t="s">
-        <v>66</v>
-      </c>
-      <c r="C41" s="128"/>
-      <c r="D41" s="115"/>
-      <c r="E41" s="116">
+      <c r="F45" s="113">
         <v>2</v>
       </c>
-      <c r="F41" s="116"/>
-      <c r="G41" s="99" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7">
-      <c r="B42" s="127" t="s">
+      <c r="G45" s="95" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7">
+      <c r="B46" s="122" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="123"/>
+      <c r="D46" s="112"/>
+      <c r="E46" s="113">
+        <v>1</v>
+      </c>
+      <c r="F46" s="113">
+        <v>1</v>
+      </c>
+      <c r="G46" s="95" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7">
+      <c r="B47" s="150" t="s">
         <v>98</v>
       </c>
-      <c r="C42" s="128"/>
-      <c r="D42" s="115"/>
-      <c r="E42" s="116">
+      <c r="C47" s="151"/>
+      <c r="D47" s="100"/>
+      <c r="E47" s="103">
+        <f>SUM(E48:E48)</f>
         <v>2</v>
       </c>
-      <c r="F42" s="116">
+      <c r="F47" s="103">
+        <f>SUM(F48:F48)</f>
         <v>2</v>
       </c>
-      <c r="G42" s="99" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7">
-      <c r="B43" s="127" t="s">
-        <v>67</v>
-      </c>
-      <c r="C43" s="153"/>
-      <c r="D43" s="115"/>
-      <c r="E43" s="116">
-        <f>SUM(E44+E45)</f>
-        <v>1</v>
-      </c>
-      <c r="F43" s="116"/>
-      <c r="G43" s="99" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7">
-      <c r="B44" s="154" t="s">
-        <v>116</v>
-      </c>
-      <c r="C44" s="155"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="F44" s="30"/>
-      <c r="G44" s="81" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="45" spans="2:7">
-      <c r="B45" s="131" t="s">
-        <v>115</v>
-      </c>
-      <c r="C45" s="143"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="30">
-        <v>0.5</v>
-      </c>
-      <c r="F45" s="30"/>
-      <c r="G45" s="81" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="46" spans="2:7">
-      <c r="B46" s="158" t="s">
-        <v>5</v>
-      </c>
-      <c r="C46" s="159"/>
-      <c r="D46" s="105"/>
-      <c r="E46" s="108"/>
-      <c r="F46" s="108"/>
-      <c r="G46" s="96" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="47" spans="2:7">
-      <c r="B47" s="148" t="s">
-        <v>66</v>
-      </c>
-      <c r="C47" s="149"/>
-      <c r="D47" s="117"/>
-      <c r="E47" s="118">
+      <c r="G47" s="104" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B48" s="131" t="s">
+        <v>96</v>
+      </c>
+      <c r="C48" s="132"/>
+      <c r="D48" s="112"/>
+      <c r="E48" s="113">
         <v>2</v>
       </c>
-      <c r="F47" s="118"/>
-      <c r="G47" s="100" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="48" spans="2:7">
-      <c r="B48" s="127" t="s">
-        <v>98</v>
-      </c>
-      <c r="C48" s="128"/>
-      <c r="D48" s="117"/>
-      <c r="E48" s="118"/>
-      <c r="F48" s="118"/>
-      <c r="G48" s="100" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="2:7">
-      <c r="B49" s="158" t="s">
-        <v>100</v>
-      </c>
-      <c r="C49" s="159"/>
-      <c r="D49" s="105"/>
-      <c r="E49" s="108"/>
-      <c r="F49" s="108"/>
-      <c r="G49" s="109" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="50" spans="2:7">
-      <c r="B50" s="148" t="s">
-        <v>66</v>
-      </c>
-      <c r="C50" s="149"/>
-      <c r="D50" s="115"/>
-      <c r="E50" s="116">
+      <c r="F48" s="113">
         <v>2</v>
       </c>
-      <c r="F50" s="116"/>
-      <c r="G50" s="100" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="51" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B51" s="137" t="s">
-        <v>98</v>
-      </c>
-      <c r="C51" s="138"/>
-      <c r="D51" s="117"/>
-      <c r="E51" s="118">
-        <v>2</v>
-      </c>
-      <c r="F51" s="118"/>
-      <c r="G51" s="100" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="52" spans="2:7">
-      <c r="B52" s="156" t="s">
+      <c r="G48" s="95" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" ht="19.5" thickBot="1">
+      <c r="B49" s="148" t="s">
         <v>34</v>
       </c>
-      <c r="C52" s="157"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="34">
-        <f>SUM(E3+E19+E26+E31)</f>
-        <v>46.5</v>
-      </c>
-      <c r="F52" s="34">
-        <f>SUM(F3+F19+F26+F31)</f>
-        <v>29.5</v>
-      </c>
-      <c r="G52" s="88"/>
+      <c r="C49" s="149"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="33">
+        <f>SUM(E3+E19+E23+E26)</f>
+        <v>47</v>
+      </c>
+      <c r="F49" s="33">
+        <f>SUM(F3+F19+F23+F26)</f>
+        <v>50</v>
+      </c>
+      <c r="G49" s="84"/>
     </row>
   </sheetData>
-  <mergeCells count="53">
-    <mergeCell ref="B25:C25"/>
+  <autoFilter ref="G2:G49" xr:uid="{E0DBF476-724A-4DAE-8D66-8B0809F96B84}"/>
+  <mergeCells count="50">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B28:C28"/>
     <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B34:C34"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B45:C45"/>
     <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B34:C34"/>
     <mergeCell ref="I7:M7"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
@@ -4165,6 +4245,11 @@
     <mergeCell ref="B14:C14"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
+  <conditionalFormatting sqref="G2">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="完了">
+      <formula>NOT(ISERROR(SEARCH("完了",G2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError sqref="E19" formulaRange="1"/>
@@ -4174,383 +4259,438 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF80DA5A-1B69-4377-A99E-364B8197EABC}">
-  <dimension ref="B1:L21"/>
+  <dimension ref="B1:M26"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="8" max="8" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="17.25" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="19.5" thickBot="1"/>
     <row r="2" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B2" s="182" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" s="183"/>
+      <c r="B2" s="174" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="175"/>
       <c r="D2" s="9" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="35" t="s">
-        <v>79</v>
+      <c r="G2" s="34" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B3" s="184" t="s">
+      <c r="B3" s="176" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="185"/>
+      <c r="C3" s="177"/>
       <c r="D3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="34">
+      <c r="E3" s="33">
         <f>SUM(E4)</f>
         <v>3</v>
       </c>
-      <c r="F3" s="56">
+      <c r="F3" s="55">
         <f>SUM(F4)</f>
         <v>0</v>
       </c>
-      <c r="G3" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="J3" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="K3" s="47">
+      <c r="G3" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="I3" s="43" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" s="46">
         <f ca="1">TODAY()</f>
         <v>46308</v>
       </c>
-      <c r="L3" s="35" t="s">
-        <v>83</v>
+      <c r="K3" s="34" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="2:12">
-      <c r="B4" s="186" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="187"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="74">
+      <c r="B4" s="178" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="179"/>
+      <c r="D4" s="72"/>
+      <c r="E4" s="73">
         <v>3</v>
       </c>
-      <c r="F4" s="72">
-        <f>SUM(F6)</f>
-        <v>0</v>
-      </c>
-      <c r="G4" s="75" t="s">
-        <v>80</v>
-      </c>
-      <c r="J4" s="48" t="s">
+      <c r="F4" s="71"/>
+      <c r="G4" s="74" t="s">
+        <v>79</v>
+      </c>
+      <c r="I4" s="47" t="s">
+        <v>76</v>
+      </c>
+      <c r="J4" s="44">
+        <v>46310</v>
+      </c>
+      <c r="K4" s="40" t="str">
+        <f ca="1">SUM($J4-$J3)&amp; "日"</f>
+        <v>2日</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="19.5" thickBot="1">
+      <c r="B5" s="131" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="142"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="30">
+        <v>3</v>
+      </c>
+      <c r="F5" s="61"/>
+      <c r="G5" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="K4" s="45">
-        <v>46310</v>
-      </c>
-      <c r="L4" s="41" t="str">
-        <f ca="1">SUM($L4-I1)&amp; "日"</f>
-        <v>15日</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B5" s="137" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" s="150"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="31">
-        <v>3</v>
-      </c>
-      <c r="F5" s="62"/>
-      <c r="G5" s="53"/>
-      <c r="J5" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="K5" s="45">
+      <c r="J5" s="44">
         <v>46313</v>
       </c>
-      <c r="L5" s="41" t="str">
-        <f ca="1">SUM($L5-I1)&amp; "日"</f>
-        <v>18日</v>
+      <c r="K5" s="40" t="str">
+        <f t="shared" ref="K5:K6" si="0">SUM($J5-$J4)&amp; "日"</f>
+        <v>3日</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B6" s="184" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="185"/>
+      <c r="B6" s="176" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="177"/>
       <c r="D6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="33">
         <f>SUM(E7)</f>
         <v>3</v>
       </c>
-      <c r="F6" s="56">
-        <f t="shared" ref="F6" si="0">SUM(F7)</f>
+      <c r="F6" s="55">
+        <f t="shared" ref="F6" si="1">SUM(F7)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="J6" s="50" t="s">
-        <v>73</v>
-      </c>
-      <c r="K6" s="46">
+      <c r="G6" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="I6" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="J6" s="45">
         <v>46314</v>
       </c>
-      <c r="L6" s="42" t="str">
-        <f ca="1">SUM(K6-K3)&amp; "日"</f>
+      <c r="K6" s="41" t="str">
+        <f ca="1">SUM($J6-$J3)&amp; "日"</f>
         <v>6日</v>
       </c>
     </row>
     <row r="7" spans="2:12">
-      <c r="B7" s="190" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" s="191"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="59">
+      <c r="B7" s="182" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="183"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="58">
         <v>3</v>
       </c>
-      <c r="F7" s="72">
-        <f>SUM(F9)</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="60" t="s">
-        <v>80</v>
+      <c r="F7" s="71"/>
+      <c r="G7" s="59" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B8" s="137" t="s">
+      <c r="B8" s="131" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="150"/>
+      <c r="C8" s="142"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="31">
+      <c r="E8" s="30">
         <v>3</v>
       </c>
-      <c r="F8" s="62"/>
-      <c r="G8" s="53"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="52" t="s">
+        <v>79</v>
+      </c>
       <c r="J8" s="4"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="52"/>
+      <c r="K8" s="50"/>
+      <c r="L8" s="51"/>
     </row>
     <row r="9" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B9" s="184" t="s">
+      <c r="B9" s="176" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="185"/>
+      <c r="C9" s="177"/>
       <c r="D9" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="33">
         <f>SUM(E10:E11)</f>
         <v>5</v>
       </c>
-      <c r="F9" s="56">
+      <c r="F9" s="55">
         <f>SUM(F10:F11)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="35" t="s">
-        <v>80</v>
+      <c r="G9" s="34" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="2:12">
-      <c r="B10" s="170" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="188"/>
+      <c r="B10" s="162" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="180"/>
       <c r="D10" s="8"/>
-      <c r="E10" s="33">
+      <c r="E10" s="32">
         <v>3</v>
       </c>
-      <c r="F10" s="43"/>
-      <c r="G10" s="39" t="s">
-        <v>80</v>
+      <c r="F10" s="42"/>
+      <c r="G10" s="38" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B11" s="166" t="s">
+      <c r="B11" s="158" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="189"/>
+      <c r="C11" s="181"/>
       <c r="D11" s="7"/>
-      <c r="E11" s="31">
+      <c r="E11" s="30">
         <v>2</v>
       </c>
-      <c r="F11" s="62"/>
-      <c r="G11" s="53" t="s">
-        <v>80</v>
+      <c r="F11" s="61"/>
+      <c r="G11" s="52" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B12" s="184" t="s">
+      <c r="B12" s="176" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="185"/>
+      <c r="C12" s="177"/>
       <c r="D12" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="34">
+      <c r="E12" s="33">
         <f>SUM(E13)</f>
         <v>2</v>
       </c>
-      <c r="F12" s="56">
-        <f>SUM(F14+F17)</f>
+      <c r="F12" s="55">
+        <f>SUM(F14+F20)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="35" t="s">
-        <v>80</v>
+      <c r="G12" s="34" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B13" s="190" t="s">
-        <v>71</v>
-      </c>
-      <c r="C13" s="191"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="59">
+      <c r="B13" s="182" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="183"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="58">
         <v>2</v>
       </c>
-      <c r="F13" s="61"/>
-      <c r="G13" s="60" t="s">
-        <v>80</v>
+      <c r="F13" s="60"/>
+      <c r="G13" s="59" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B14" s="184" t="s">
+      <c r="B14" s="176" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="185"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="34">
+      <c r="C14" s="177"/>
+      <c r="D14" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" s="33">
         <f>SUM(E15:E16)</f>
+        <v>3</v>
+      </c>
+      <c r="F14" s="55">
+        <f>SUM(F16:F16)</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="34" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="B15" s="195" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="196"/>
+      <c r="E15" s="197">
         <v>2</v>
       </c>
-      <c r="F14" s="56">
-        <f>SUM(F15:F16)</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="35" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12">
-      <c r="B15" s="170" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" s="188"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="33">
-        <v>1</v>
-      </c>
-      <c r="F15" s="43"/>
-      <c r="G15" s="39" t="s">
-        <v>80</v>
+      <c r="F15" s="198"/>
+      <c r="G15" s="74" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="19.5" thickBot="1">
-      <c r="B16" s="166" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="189"/>
+      <c r="B16" s="158" t="s">
+        <v>70</v>
+      </c>
+      <c r="C16" s="181"/>
       <c r="D16" s="7"/>
-      <c r="E16" s="31">
-        <v>1</v>
-      </c>
-      <c r="F16" s="62"/>
-      <c r="G16" s="53" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="19.5" thickBot="1">
-      <c r="B17" s="184" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="185"/>
+      <c r="E16" s="30">
+        <v>1</v>
+      </c>
+      <c r="F16" s="61"/>
+      <c r="G16" s="52" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" ht="19.5" thickBot="1">
+      <c r="B17" s="176" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="177"/>
       <c r="D17" s="9"/>
-      <c r="E17" s="34">
+      <c r="E17" s="33">
         <f>SUM(E18:E19)</f>
-        <v>2</v>
-      </c>
-      <c r="F17" s="56">
+        <v>3</v>
+      </c>
+      <c r="F17" s="55">
         <f>SUM(F18:F19)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="35" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="170" t="s">
+      <c r="G17" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="L17" s="189"/>
+    </row>
+    <row r="18" spans="2:13">
+      <c r="B18" s="185" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="186"/>
+      <c r="E18" s="193">
+        <v>2</v>
+      </c>
+      <c r="F18" s="194"/>
+      <c r="G18" s="74" t="s">
+        <v>79</v>
+      </c>
+      <c r="H18" s="192"/>
+      <c r="I18" s="192"/>
+      <c r="J18" s="190"/>
+      <c r="K18" s="191"/>
+      <c r="L18" s="191"/>
+      <c r="M18" s="190"/>
+    </row>
+    <row r="19" spans="2:13" ht="19.5" thickBot="1">
+      <c r="B19" s="158" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="181"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="30">
+        <v>1</v>
+      </c>
+      <c r="F19" s="61"/>
+      <c r="G19" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13">
+      <c r="B20" s="138" t="s">
+        <v>5</v